--- a/data/Apr/Data.xlsx
+++ b/data/Apr/Data.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Freelance\TextInputter\data\Apr\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9DA653F-A7D1-4939-AF77-178936C5F569}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EF437A4-6A6D-48EA-AD38-BC22F5942578}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01-04" sheetId="4" r:id="rId1"/>
+    <sheet name="02-04" sheetId="6" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="167">
   <si>
     <t>THU 4</t>
   </si>
@@ -101,6 +102,12 @@
     <t>HD006847</t>
   </si>
   <si>
+    <t>Số 17 đường số 13 phường bình hưng hòa</t>
+  </si>
+  <si>
+    <t>binh tan</t>
+  </si>
+  <si>
     <t>AT 01-04</t>
   </si>
   <si>
@@ -119,6 +126,9 @@
     <t>Chung cư cardinal court toà B</t>
   </si>
   <si>
+    <t>7</t>
+  </si>
+  <si>
     <t>Quỳnh Giao</t>
   </si>
   <si>
@@ -137,7 +147,7 @@
     <t>HD006825</t>
   </si>
   <si>
-    <t>7</t>
+    <t>Block D chung cư ecogreen, 107 Nguyễn Văn Linh, Tân Thuận Tây</t>
   </si>
   <si>
     <t>Thu Ba DS</t>
@@ -152,123 +162,159 @@
     <t>binh thanh</t>
   </si>
   <si>
+    <t>Quỳnh Anh</t>
+  </si>
+  <si>
+    <t>HD006833</t>
+  </si>
+  <si>
+    <t>754 Nguyễn xiển p. long bình</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>a.quyen</t>
+  </si>
+  <si>
+    <t>Ngọc Mơ</t>
+  </si>
+  <si>
+    <t>HD006858</t>
+  </si>
+  <si>
+    <t>107/7 huỳnh an khương p5</t>
+  </si>
+  <si>
+    <t>go vap</t>
+  </si>
+  <si>
+    <t>Bé My</t>
+  </si>
+  <si>
+    <t>HD006884</t>
+  </si>
+  <si>
+    <t>304/45 đường số 8 bình hưng hoà a</t>
+  </si>
+  <si>
+    <t>kha (yayang)</t>
+  </si>
+  <si>
+    <t>HD006667</t>
+  </si>
+  <si>
+    <t>Toà nhà Conic Riverside, block A Đường số 1, KDC Conic, phường 7</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>Nguyễn TC Tiên</t>
+  </si>
+  <si>
+    <t>HD006773</t>
+  </si>
+  <si>
+    <t>6 Thạch Thị Thanh, Tân Định</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>Nguyễn thị huệ fb Jannie vu</t>
+  </si>
+  <si>
+    <t>HD006846</t>
+  </si>
+  <si>
+    <t>136 đông hưng thuận 3 phường đông hưng</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>Thuy Duong_FB: Soominate</t>
+  </si>
+  <si>
+    <t>HD006785</t>
+  </si>
+  <si>
+    <t>386/27/4 xo viet nghe tinh, p. 25</t>
+  </si>
+  <si>
+    <t>Kim Thanh</t>
+  </si>
+  <si>
+    <t>HD006722</t>
+  </si>
+  <si>
+    <t>108/69a trần quang diệu</t>
+  </si>
+  <si>
+    <t>Ngoc Venus</t>
+  </si>
+  <si>
+    <t>HD006867</t>
+  </si>
+  <si>
+    <t>69 phố tiểu nam, p Tân Phú</t>
+  </si>
+  <si>
+    <t>đổi hàng</t>
+  </si>
+  <si>
+    <t>Tâm Trương</t>
+  </si>
+  <si>
+    <t>HD006794</t>
+  </si>
+  <si>
+    <t>The Antonia, Block B, Nguyễn Lương Bằng, Đường số 19, Phường Tân Phú</t>
+  </si>
+  <si>
+    <t>Thiên Lan</t>
+  </si>
+  <si>
+    <t>HD006844</t>
+  </si>
+  <si>
+    <t>132/1 TL28, phường Thạnh Lộc</t>
+  </si>
+  <si>
+    <t>Nguyễn Thị Huyền Trân</t>
+  </si>
+  <si>
+    <t>HD006674</t>
+  </si>
+  <si>
+    <t>Chung cư ecogreen block D 39 b nguyễn Văn Linh, P Tân Thuận</t>
+  </si>
+  <si>
+    <t>X.Anh</t>
+  </si>
+  <si>
+    <t>HD006728</t>
+  </si>
+  <si>
+    <t>Căn 603, lô B2 chung cư orchard parkview, 130-132 hồng hà, p. Đức Nhuận</t>
+  </si>
+  <si>
+    <t>phu nhuan</t>
+  </si>
+  <si>
+    <t>Khánh Như</t>
+  </si>
+  <si>
+    <t>HD006868</t>
+  </si>
+  <si>
+    <t>688/23/1c Hương Lộ 2, phường Bình Trị Đông A</t>
+  </si>
+  <si>
     <t>hàng sỉ</t>
   </si>
   <si>
-    <t>Ngọc Mơ</t>
-  </si>
-  <si>
-    <t>HD006858</t>
-  </si>
-  <si>
-    <t>107/7 huỳnh an khương p5</t>
-  </si>
-  <si>
-    <t>go vap</t>
-  </si>
-  <si>
-    <t>Bé My</t>
-  </si>
-  <si>
-    <t>HD006884</t>
-  </si>
-  <si>
-    <t>304/45 đường số 8 bình hưng hoà a</t>
-  </si>
-  <si>
-    <t>binh tan</t>
-  </si>
-  <si>
-    <t>kha (yayang)</t>
-  </si>
-  <si>
-    <t>HD006667</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>Nguyễn TC Tiên</t>
-  </si>
-  <si>
-    <t>HD006773</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>Nguyễn thị huệ fb Jannie vu</t>
-  </si>
-  <si>
-    <t>HD006846</t>
-  </si>
-  <si>
-    <t>Thuy Duong_FB: Soominate</t>
-  </si>
-  <si>
-    <t>HD006785</t>
-  </si>
-  <si>
-    <t>Kim Thanh</t>
-  </si>
-  <si>
-    <t>HD006722</t>
-  </si>
-  <si>
-    <t>108/69a trần quang diệu</t>
-  </si>
-  <si>
-    <t>Ngoc Venus</t>
-  </si>
-  <si>
-    <t>HD006867</t>
-  </si>
-  <si>
-    <t>HD006794</t>
-  </si>
-  <si>
-    <t>Thiên Lan</t>
-  </si>
-  <si>
-    <t>HD006844</t>
-  </si>
-  <si>
-    <t>132/1 TL28, phường Thạnh Lộc</t>
-  </si>
-  <si>
-    <t>Nguyễn Thị Huyền Trân</t>
-  </si>
-  <si>
-    <t>HD006674</t>
-  </si>
-  <si>
-    <t>Chung cư ecogreen block D 39 b nguyễn Văn Linh, P Tân Thuận</t>
-  </si>
-  <si>
-    <t>X.Anh</t>
-  </si>
-  <si>
-    <t>HD006728</t>
-  </si>
-  <si>
-    <t>Khánh Như</t>
-  </si>
-  <si>
-    <t>HD006868</t>
-  </si>
-  <si>
-    <t>688/23/1c Hương Lộ 2, phường Bình Trị Đông A</t>
-  </si>
-  <si>
-    <t>6 Thạch Thị Thanh, Tân Định</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>386/27/4 xo viet nghe tinh, p. 25</t>
-  </si>
-  <si>
     <t>Kim Liên</t>
   </si>
   <si>
@@ -278,42 +324,6 @@
     <t>tan binh</t>
   </si>
   <si>
-    <t>Căn 603, lô B2 chung cư orchard parkview, 130-132 hồng hà, p. Đức Nhuận</t>
-  </si>
-  <si>
-    <t>phu nhuan</t>
-  </si>
-  <si>
-    <t>đổi hàng</t>
-  </si>
-  <si>
-    <t>754 Nguyễn xiển p. long bình</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>a.quyen</t>
-  </si>
-  <si>
-    <t>Quỳnh Anh</t>
-  </si>
-  <si>
-    <t>HD006833</t>
-  </si>
-  <si>
-    <t>69 phố tiểu nam, p Tân Phú</t>
-  </si>
-  <si>
-    <t>Số 17 đường số 13 phường bình hưng hòa</t>
-  </si>
-  <si>
-    <t>Toà nhà Conic Riverside, block A Đường số 1, KDC Conic, phường 7</t>
-  </si>
-  <si>
-    <t>Block D chung cư ecogreen, 107 Nguyễn Văn Linh, Tân Thuận Tây</t>
-  </si>
-  <si>
     <t>Jess-9244</t>
   </si>
   <si>
@@ -323,13 +333,211 @@
     <t>6</t>
   </si>
   <si>
-    <t>The Antonia, Block B, Nguyễn Lương Bằng, Đường số 19, Phường Tân Phú</t>
-  </si>
-  <si>
-    <t>Tâm Trương</t>
-  </si>
-  <si>
-    <t>136 đông hưng thuận 3 phường đông hưng</t>
+    <t>THU 5</t>
+  </si>
+  <si>
+    <t>NGAY 2-4</t>
+  </si>
+  <si>
+    <t>Soipin - Hiền Đăng</t>
+  </si>
+  <si>
+    <t>AT 02-04</t>
+  </si>
+  <si>
+    <t>02-04-2026</t>
+  </si>
+  <si>
+    <t>Hoàng anh</t>
+  </si>
+  <si>
+    <t>c.hieu</t>
+  </si>
+  <si>
+    <t>Nt hai yen</t>
+  </si>
+  <si>
+    <t>HD006947</t>
+  </si>
+  <si>
+    <t>Toà landmark 2</t>
+  </si>
+  <si>
+    <t>Thùy Dương</t>
+  </si>
+  <si>
+    <t>HD007101</t>
+  </si>
+  <si>
+    <t>2087 Huỳnh Tấn Phát</t>
+  </si>
+  <si>
+    <t>nha be</t>
+  </si>
+  <si>
+    <t>Hồng Khanh fb Hoàng Thị Lộc</t>
+  </si>
+  <si>
+    <t>HD007069</t>
+  </si>
+  <si>
+    <t>HD007091</t>
+  </si>
+  <si>
+    <t>số 25a đường 22 sình hưng hòa a</t>
+  </si>
+  <si>
+    <t>Nguyệt Nguyễn Thị Minh</t>
+  </si>
+  <si>
+    <t>HD007068</t>
+  </si>
+  <si>
+    <t>35 Lý Văn Phức phường Tân Định</t>
+  </si>
+  <si>
+    <t>Lê Quốc Khánh_FE: My Le</t>
+  </si>
+  <si>
+    <t>HD006896</t>
+  </si>
+  <si>
+    <t>Hẻm 132, 132/78 nguyễn hữu cảnh</t>
+  </si>
+  <si>
+    <t>HD007115</t>
+  </si>
+  <si>
+    <t>3/51/4 thành thái p14</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>Linh Hạ</t>
+  </si>
+  <si>
+    <t>HD006999</t>
+  </si>
+  <si>
+    <t>854 tạ quang bửu chung cư gia việt phường 5</t>
+  </si>
+  <si>
+    <t>HD006977</t>
+  </si>
+  <si>
+    <t>Kim Minh</t>
+  </si>
+  <si>
+    <t>HD006908</t>
+  </si>
+  <si>
+    <t>Địa chỉ : 189A Cống Quỳnh p.Cầu Ông Lãnh</t>
+  </si>
+  <si>
+    <t>Cẩm Tú</t>
+  </si>
+  <si>
+    <t>HD006777</t>
+  </si>
+  <si>
+    <t>Chung cư west gate an gia Cẩm Tú</t>
+  </si>
+  <si>
+    <t>binh chanh</t>
+  </si>
+  <si>
+    <t>Phương Kim</t>
+  </si>
+  <si>
+    <t>HD007131</t>
+  </si>
+  <si>
+    <t>213/6 đường số 1,p6</t>
+  </si>
+  <si>
+    <t>Hiếu Lee</t>
+  </si>
+  <si>
+    <t>HD007067</t>
+  </si>
+  <si>
+    <t>Tuyết Mai</t>
+  </si>
+  <si>
+    <t>276/3/45/11/17 Mã lò, Phường Bình Trị Đông A</t>
+  </si>
+  <si>
+    <t>Linh Tiêu</t>
+  </si>
+  <si>
+    <t>HD006958</t>
+  </si>
+  <si>
+    <t>97 Ký Con,p Nguyễn Thái Bình</t>
+  </si>
+  <si>
+    <t>Bình Trần</t>
+  </si>
+  <si>
+    <t>41/8 Mai Lão Bạng, Phường 13</t>
+  </si>
+  <si>
+    <t>Phương Thảo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">189/46a Bạch Đằng, phường Hạnh Thông </t>
+  </si>
+  <si>
+    <t>Nguyễn Thị Thùy Trang</t>
+  </si>
+  <si>
+    <t>HD007013</t>
+  </si>
+  <si>
+    <t>41A huỳnh tịnh của p19</t>
+  </si>
+  <si>
+    <t>132 khu dân cư Tân tiến, Tân Thới Hiệp</t>
+  </si>
+  <si>
+    <t>Mén HM</t>
+  </si>
+  <si>
+    <t>Nguyễn Trương Phương Oanh</t>
+  </si>
+  <si>
+    <t>125/42/2 Bùi Đình Tuý, phường 14</t>
+  </si>
+  <si>
+    <t>1080, Đỗ Mười, phường linh trung</t>
+  </si>
+  <si>
+    <t>thu duc</t>
+  </si>
+  <si>
+    <t>Xe Anh Khương</t>
+  </si>
+  <si>
+    <t>71/39/31 Nguyễn Bặc, Phường 3</t>
+  </si>
+  <si>
+    <t>Yến Oanh</t>
+  </si>
+  <si>
+    <t>HD005268</t>
+  </si>
+  <si>
+    <t>33 Đ Ng~ hữu thọ Tân hưng</t>
+  </si>
+  <si>
+    <t>Nguyễn Thị Kim Thoa</t>
+  </si>
+  <si>
+    <t>HD007102</t>
+  </si>
+  <si>
+    <t>Chung cu folita him lam</t>
   </si>
 </sst>
 </file>
@@ -352,7 +560,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -382,6 +590,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -395,7 +609,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -405,6 +619,8 @@
     <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="49" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="49" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -684,14 +900,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2FF9190-3DF4-4972-9F11-28F172D3E32B}">
   <dimension ref="A1:P23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="1" max="2" width="9.140625" customWidth="1"/>
     <col min="3" max="3" width="26.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9.5703125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="67" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="9.140625" customWidth="1"/>
     <col min="12" max="12" width="10.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -764,10 +982,10 @@
         <v>20</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>46</v>
+        <v>22</v>
       </c>
       <c r="G3" s="7">
         <v>0</v>
@@ -780,13 +998,13 @@
         <v>-30</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="K3" s="7" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="L3" s="7" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -794,16 +1012,16 @@
         <v>18</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="G4" s="7">
         <v>850</v>
@@ -816,13 +1034,13 @@
         <v>820</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="K4" s="7" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="L4" s="7" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -830,16 +1048,16 @@
         <v>18</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G5" s="7">
         <v>695</v>
@@ -852,13 +1070,13 @@
         <v>670</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="K5" s="7" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="L5" s="7" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -866,16 +1084,16 @@
         <v>18</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>91</v>
+        <v>36</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="G6" s="7">
         <v>740</v>
@@ -888,13 +1106,13 @@
         <v>710</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="K6" s="7" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="L6" s="7" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -902,16 +1120,16 @@
         <v>18</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G7" s="3">
         <v>0</v>
@@ -924,13 +1142,13 @@
         <v>-20</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -938,16 +1156,16 @@
         <v>18</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>86</v>
+        <v>41</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>87</v>
+        <v>42</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>83</v>
+        <v>43</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>84</v>
+        <v>44</v>
       </c>
       <c r="G8" s="5">
         <v>780</v>
@@ -960,13 +1178,13 @@
         <v>750</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>85</v>
+        <v>45</v>
       </c>
       <c r="K8" s="5" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="L8" s="5" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -974,16 +1192,16 @@
         <v>18</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="G9" s="3">
         <v>615</v>
@@ -996,13 +1214,13 @@
         <v>590</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -1010,16 +1228,16 @@
         <v>18</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>46</v>
+        <v>22</v>
       </c>
       <c r="G10" s="7">
         <v>610</v>
@@ -1032,13 +1250,13 @@
         <v>580</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="K10" s="7" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="L10" s="7" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -1046,16 +1264,16 @@
         <v>18</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>90</v>
+        <v>55</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="G11" s="7">
         <v>0</v>
@@ -1068,13 +1286,13 @@
         <v>-25</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="K11" s="7" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="L11" s="7" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="12" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -1082,16 +1300,16 @@
         <v>18</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="G12" s="3">
         <v>845</v>
@@ -1104,13 +1322,13 @@
         <v>820</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="13" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -1118,16 +1336,16 @@
         <v>18</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>97</v>
+        <v>63</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="G13" s="7">
         <v>750</v>
@@ -1140,13 +1358,13 @@
         <v>720</v>
       </c>
       <c r="J13" s="7" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="K13" s="7" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="L13" s="7" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="14" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -1154,16 +1372,16 @@
         <v>18</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G14" s="3">
         <v>1630</v>
@@ -1176,13 +1394,13 @@
         <v>1610</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="15" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -1190,16 +1408,16 @@
         <v>18</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G15" s="3">
         <v>405</v>
@@ -1212,13 +1430,13 @@
         <v>380</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="16" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -1226,16 +1444,16 @@
         <v>18</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>88</v>
+        <v>73</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="G16" s="7">
         <v>30</v>
@@ -1248,16 +1466,16 @@
         <v>0</v>
       </c>
       <c r="J16" s="7" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="K16" s="7" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="L16" s="7" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="M16" s="7" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
     </row>
     <row r="17" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -1265,16 +1483,16 @@
         <v>18</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="G17" s="7">
         <v>1640</v>
@@ -1287,13 +1505,13 @@
         <v>1610</v>
       </c>
       <c r="J17" s="7" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="K17" s="7" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="L17" s="7" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -1301,16 +1519,16 @@
         <v>18</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="D18" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="F18" s="8" t="s">
         <v>64</v>
-      </c>
-      <c r="E18" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="F18" s="8" t="s">
-        <v>52</v>
       </c>
       <c r="G18" s="7">
         <v>590</v>
@@ -1323,13 +1541,13 @@
         <v>560</v>
       </c>
       <c r="J18" s="7" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="K18" s="7" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="L18" s="7" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="19" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -1337,16 +1555,16 @@
         <v>18</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="G19" s="7">
         <v>850</v>
@@ -1359,13 +1577,13 @@
         <v>820</v>
       </c>
       <c r="J19" s="7" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="K19" s="7" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="L19" s="7" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="20" spans="1:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -1373,16 +1591,16 @@
         <v>18</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>69</v>
+        <v>84</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G20" s="3">
         <v>20</v>
@@ -1395,16 +1613,16 @@
         <v>0</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="L20" s="3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
     </row>
     <row r="21" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -1412,16 +1630,16 @@
         <v>18</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>72</v>
+        <v>89</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>46</v>
+        <v>22</v>
       </c>
       <c r="G21" s="7">
         <v>820</v>
@@ -1434,30 +1652,30 @@
         <v>790</v>
       </c>
       <c r="J21" s="7" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="K21" s="7" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="L21" s="7" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="22" spans="1:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>38</v>
+        <v>91</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>78</v>
+        <v>93</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>79</v>
+        <v>94</v>
       </c>
       <c r="G22" s="3">
         <v>0</v>
@@ -1470,30 +1688,30 @@
         <v>-30</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="L22" s="3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="23" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>38</v>
+        <v>91</v>
       </c>
       <c r="B23" s="7" t="s">
         <v>18</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="F23" s="8" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="G23" s="7">
         <v>0</v>
@@ -1506,13 +1724,883 @@
         <v>-30</v>
       </c>
       <c r="J23" s="7" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="K23" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L23" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CCBE8099-4F3D-4B80-A775-7DFD50F2A00C}">
+  <dimension ref="A1:P24"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="27.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="42.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B1" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="G3" s="3">
+        <v>70</v>
+      </c>
+      <c r="H3" s="3">
+        <v>70</v>
+      </c>
+      <c r="I3" s="3">
+        <f>G3-H3</f>
+        <v>0</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="G4" s="9">
+        <v>0</v>
+      </c>
+      <c r="H4" s="9">
+        <v>30</v>
+      </c>
+      <c r="I4" s="9">
+        <f t="shared" ref="I4:I24" si="0">G4-H4</f>
+        <v>-30</v>
+      </c>
+      <c r="J4" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="K4" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L4" s="9" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="G5" s="3">
+        <v>0</v>
+      </c>
+      <c r="H5" s="3">
+        <v>30</v>
+      </c>
+      <c r="I5" s="3">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="G6" s="3">
+        <v>30</v>
+      </c>
+      <c r="H6" s="3">
+        <v>30</v>
+      </c>
+      <c r="I6" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L6" s="3" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="G7" s="3">
+        <v>530</v>
+      </c>
+      <c r="H7" s="3">
+        <v>30</v>
+      </c>
+      <c r="I7" s="3">
+        <f t="shared" si="0"/>
+        <v>500</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L7" s="3" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="G8" s="3">
+        <v>740</v>
+      </c>
+      <c r="H8" s="3">
+        <v>20</v>
+      </c>
+      <c r="I8" s="3">
+        <f t="shared" si="0"/>
+        <v>720</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="G9" s="7">
+        <v>35</v>
+      </c>
+      <c r="H9" s="7">
+        <v>35</v>
+      </c>
+      <c r="I9" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J9" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="K9" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L9" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="M9" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="G10" s="3">
+        <v>0</v>
+      </c>
+      <c r="H10" s="3">
+        <v>30</v>
+      </c>
+      <c r="I10" s="3">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L10" s="3" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="F11" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="L23" s="7" t="s">
-        <v>23</v>
+      <c r="G11" s="7">
+        <v>870</v>
+      </c>
+      <c r="H11" s="7">
+        <v>30</v>
+      </c>
+      <c r="I11" s="7">
+        <f t="shared" si="0"/>
+        <v>840</v>
+      </c>
+      <c r="J11" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="K11" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L11" s="7" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="F12" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="G12" s="9">
+        <v>695</v>
+      </c>
+      <c r="H12" s="9">
+        <v>25</v>
+      </c>
+      <c r="I12" s="9">
+        <f t="shared" si="0"/>
+        <v>670</v>
+      </c>
+      <c r="J12" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="K12" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L12" s="9" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="G13" s="3">
+        <v>510</v>
+      </c>
+      <c r="H13" s="3">
+        <v>20</v>
+      </c>
+      <c r="I13" s="3">
+        <f t="shared" si="0"/>
+        <v>490</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K13" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L13" s="3" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="E14" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="F14" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="G14" s="9">
+        <v>775</v>
+      </c>
+      <c r="H14" s="9">
+        <v>25</v>
+      </c>
+      <c r="I14" s="9">
+        <f t="shared" si="0"/>
+        <v>750</v>
+      </c>
+      <c r="J14" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="K14" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L14" s="9" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="G15" s="7">
+        <v>0</v>
+      </c>
+      <c r="H15" s="7">
+        <v>25</v>
+      </c>
+      <c r="I15" s="7">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J15" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="K15" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L15" s="7" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="G16" s="3">
+        <v>0</v>
+      </c>
+      <c r="H16" s="3">
+        <v>20</v>
+      </c>
+      <c r="I16" s="3">
+        <f t="shared" si="0"/>
+        <v>-20</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K16" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L16" s="3" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="17" spans="2:12" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="G17" s="7">
+        <v>650</v>
+      </c>
+      <c r="H17" s="7">
+        <v>30</v>
+      </c>
+      <c r="I17" s="7">
+        <f t="shared" si="0"/>
+        <v>620</v>
+      </c>
+      <c r="J17" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="K17" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L17" s="7" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="18" spans="2:12" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="D18" s="9" t="s">
+        <v>130</v>
+      </c>
+      <c r="E18" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="F18" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="G18" s="9">
+        <v>895</v>
+      </c>
+      <c r="H18" s="9">
+        <v>25</v>
+      </c>
+      <c r="I18" s="9">
+        <f t="shared" si="0"/>
+        <v>870</v>
+      </c>
+      <c r="J18" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="K18" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L18" s="9" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="19" spans="2:12" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="F19" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="G19" s="7">
+        <v>1215</v>
+      </c>
+      <c r="H19" s="7">
+        <v>35</v>
+      </c>
+      <c r="I19" s="7">
+        <f t="shared" si="0"/>
+        <v>1180</v>
+      </c>
+      <c r="J19" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="K19" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L19" s="7" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="20" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="G20" s="3">
+        <v>915</v>
+      </c>
+      <c r="H20" s="3">
+        <v>25</v>
+      </c>
+      <c r="I20" s="3">
+        <f t="shared" si="0"/>
+        <v>890</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L20" s="3" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="21" spans="2:12" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="F21" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="G21" s="7">
+        <v>740</v>
+      </c>
+      <c r="H21" s="7">
+        <v>30</v>
+      </c>
+      <c r="I21" s="7">
+        <f t="shared" si="0"/>
+        <v>710</v>
+      </c>
+      <c r="J21" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="K21" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L21" s="7" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="22" spans="2:12" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="F22" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G22" s="7">
+        <v>770</v>
+      </c>
+      <c r="H22" s="7">
+        <v>30</v>
+      </c>
+      <c r="I22" s="7">
+        <f t="shared" si="0"/>
+        <v>740</v>
+      </c>
+      <c r="J22" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="K22" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L22" s="7" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="23" spans="2:12" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C23" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="D23" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="E23" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="F23" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="G23" s="9">
+        <v>695</v>
+      </c>
+      <c r="H23" s="9">
+        <v>25</v>
+      </c>
+      <c r="I23" s="9">
+        <f t="shared" si="0"/>
+        <v>670</v>
+      </c>
+      <c r="J23" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="K23" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L23" s="9" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="24" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="G24" s="3">
+        <v>0</v>
+      </c>
+      <c r="H24" s="3">
+        <v>20</v>
+      </c>
+      <c r="I24" s="3">
+        <f t="shared" si="0"/>
+        <v>-20</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K24" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L24" s="3" t="s">
+        <v>102</v>
       </c>
     </row>
   </sheetData>

--- a/data/Apr/Data.xlsx
+++ b/data/Apr/Data.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Freelance\TextInputter\data\Apr\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EF437A4-6A6D-48EA-AD38-BC22F5942578}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7F9556D-7094-44D0-9DB0-45E229EB2302}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01-04" sheetId="4" r:id="rId1"/>
     <sheet name="02-04" sheetId="6" r:id="rId2"/>
+    <sheet name="03-04" sheetId="7" r:id="rId3"/>
+    <sheet name="04-04" sheetId="8" r:id="rId4"/>
+    <sheet name="06-04" sheetId="9" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1603" uniqueCount="587">
   <si>
     <t>THU 4</t>
   </si>
@@ -342,45 +345,78 @@
     <t>Soipin - Hiền Đăng</t>
   </si>
   <si>
+    <t>Xe Anh Khương</t>
+  </si>
+  <si>
+    <t>02-04-2026</t>
+  </si>
+  <si>
+    <t>Hoàng anh</t>
+  </si>
+  <si>
+    <t>71/39/31 Nguyễn Bặc, Phường 3</t>
+  </si>
+  <si>
+    <t>c.hieu</t>
+  </si>
+  <si>
+    <t>Nt hai yen</t>
+  </si>
+  <si>
+    <t>132 khu dân cư Tân tiến, Tân Thới Hiệp</t>
+  </si>
+  <si>
+    <t>Phương Thảo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">189/46a Bạch Đằng, phường Hạnh Thông </t>
+  </si>
+  <si>
+    <t>Bình Trần</t>
+  </si>
+  <si>
+    <t>41/8 Mai Lão Bạng, Phường 13</t>
+  </si>
+  <si>
+    <t>Mén HM</t>
+  </si>
+  <si>
+    <t>HD006947</t>
+  </si>
+  <si>
+    <t>Toà landmark 2</t>
+  </si>
+  <si>
+    <t>Thùy Dương</t>
+  </si>
+  <si>
+    <t>HD007101</t>
+  </si>
+  <si>
+    <t>2087 Huỳnh Tấn Phát</t>
+  </si>
+  <si>
+    <t>nha be</t>
+  </si>
+  <si>
     <t>AT 02-04</t>
   </si>
   <si>
-    <t>02-04-2026</t>
-  </si>
-  <si>
-    <t>Hoàng anh</t>
-  </si>
-  <si>
-    <t>c.hieu</t>
-  </si>
-  <si>
-    <t>Nt hai yen</t>
-  </si>
-  <si>
-    <t>HD006947</t>
-  </si>
-  <si>
-    <t>Toà landmark 2</t>
-  </si>
-  <si>
-    <t>Thùy Dương</t>
-  </si>
-  <si>
-    <t>HD007101</t>
-  </si>
-  <si>
-    <t>2087 Huỳnh Tấn Phát</t>
-  </si>
-  <si>
-    <t>nha be</t>
-  </si>
-  <si>
     <t>Hồng Khanh fb Hoàng Thị Lộc</t>
   </si>
   <si>
     <t>HD007069</t>
   </si>
   <si>
+    <t>1080, Đỗ Mười, phường linh trung</t>
+  </si>
+  <si>
+    <t>thu duc</t>
+  </si>
+  <si>
+    <t>Nguyễn Thị Kim Thoa</t>
+  </si>
+  <si>
     <t>HD007091</t>
   </si>
   <si>
@@ -423,9 +459,24 @@
     <t>854 tạ quang bửu chung cư gia việt phường 5</t>
   </si>
   <si>
+    <t>Nguyễn Trương Phương Oanh</t>
+  </si>
+  <si>
     <t>HD006977</t>
   </si>
   <si>
+    <t>125/42/2 Bùi Đình Tuý, phường 14</t>
+  </si>
+  <si>
+    <t>Yến Oanh</t>
+  </si>
+  <si>
+    <t>HD005268</t>
+  </si>
+  <si>
+    <t>33 Đ Ng~ hữu thọ Tân hưng</t>
+  </si>
+  <si>
     <t>Kim Minh</t>
   </si>
   <si>
@@ -462,9 +513,15 @@
     <t>HD007067</t>
   </si>
   <si>
+    <t>Chung cu folita him lam</t>
+  </si>
+  <si>
     <t>Tuyết Mai</t>
   </si>
   <si>
+    <t>HD007102</t>
+  </si>
+  <si>
     <t>276/3/45/11/17 Mã lò, Phường Bình Trị Đông A</t>
   </si>
   <si>
@@ -477,18 +534,6 @@
     <t>97 Ký Con,p Nguyễn Thái Bình</t>
   </si>
   <si>
-    <t>Bình Trần</t>
-  </si>
-  <si>
-    <t>41/8 Mai Lão Bạng, Phường 13</t>
-  </si>
-  <si>
-    <t>Phương Thảo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">189/46a Bạch Đằng, phường Hạnh Thông </t>
-  </si>
-  <si>
     <t>Nguyễn Thị Thùy Trang</t>
   </si>
   <si>
@@ -498,53 +543,1271 @@
     <t>41A huỳnh tịnh của p19</t>
   </si>
   <si>
-    <t>132 khu dân cư Tân tiến, Tân Thới Hiệp</t>
-  </si>
-  <si>
-    <t>Mén HM</t>
-  </si>
-  <si>
-    <t>Nguyễn Trương Phương Oanh</t>
-  </si>
-  <si>
-    <t>125/42/2 Bùi Đình Tuý, phường 14</t>
-  </si>
-  <si>
-    <t>1080, Đỗ Mười, phường linh trung</t>
-  </si>
-  <si>
-    <t>thu duc</t>
-  </si>
-  <si>
-    <t>Xe Anh Khương</t>
-  </si>
-  <si>
-    <t>71/39/31 Nguyễn Bặc, Phường 3</t>
-  </si>
-  <si>
-    <t>Yến Oanh</t>
-  </si>
-  <si>
-    <t>HD005268</t>
-  </si>
-  <si>
-    <t>33 Đ Ng~ hữu thọ Tân hưng</t>
-  </si>
-  <si>
-    <t>Nguyễn Thị Kim Thoa</t>
-  </si>
-  <si>
-    <t>HD007102</t>
-  </si>
-  <si>
-    <t>Chung cu folita him lam</t>
+    <t>THU 6</t>
+  </si>
+  <si>
+    <t>NGAY 3-4</t>
+  </si>
+  <si>
+    <t>Liễu ( fb Lina Nguyễn)</t>
+  </si>
+  <si>
+    <t>HD007408</t>
+  </si>
+  <si>
+    <t>261C Nguyễn Văn Trỗi, P10</t>
+  </si>
+  <si>
+    <t>03-04-2026</t>
+  </si>
+  <si>
+    <t>Emily fb Trần Nguyễn Ngọc Bích</t>
+  </si>
+  <si>
+    <t>HD007272</t>
+  </si>
+  <si>
+    <t>36/15 yên thế p2</t>
+  </si>
+  <si>
+    <t>dolly dolly</t>
+  </si>
+  <si>
+    <t>HD007490</t>
+  </si>
+  <si>
+    <t>21 võ trường toản thảo điền</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>Trương Tiểu Băng</t>
+  </si>
+  <si>
+    <t>HD007429</t>
+  </si>
+  <si>
+    <t>84 thống nhất phường 10</t>
+  </si>
+  <si>
+    <t>chị như</t>
+  </si>
+  <si>
+    <t>HD007285</t>
+  </si>
+  <si>
+    <t>j stay deluxe apartments 476 trần hưng đạo p2 chợ quán</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>AT 03-04</t>
+  </si>
+  <si>
+    <t>Minh Thư</t>
+  </si>
+  <si>
+    <t>HD007493</t>
+  </si>
+  <si>
+    <t>6/24 tân chánh hiệp 36, p trung mỹ tây</t>
+  </si>
+  <si>
+    <t>Mị Nương</t>
+  </si>
+  <si>
+    <t>HD007511</t>
+  </si>
+  <si>
+    <t>33 nguyễn hữu thọ chung cư sunrise city view block A</t>
+  </si>
+  <si>
+    <t>Lâm Thảo Nhi</t>
+  </si>
+  <si>
+    <t>HD007443</t>
+  </si>
+  <si>
+    <t>173D Đặng Văn Ngữ</t>
+  </si>
+  <si>
+    <t>Ngô Hoàng Ánh</t>
+  </si>
+  <si>
+    <t>HD007350</t>
+  </si>
+  <si>
+    <t>235 QL13 Cũ</t>
+  </si>
+  <si>
+    <t>Lê Thị Hoài Phương</t>
+  </si>
+  <si>
+    <t>HD007406</t>
+  </si>
+  <si>
+    <t>572/19/18 Âu cơ. Phường bảy hiền</t>
+  </si>
+  <si>
+    <t>Ngọc Mai</t>
+  </si>
+  <si>
+    <t>HD007587</t>
+  </si>
+  <si>
+    <t>số 639 quốc lộ 13, phường hiệp bình phước</t>
+  </si>
+  <si>
+    <t>Annie Annie</t>
+  </si>
+  <si>
+    <t>HD007516</t>
+  </si>
+  <si>
+    <t>110 đường 14 Him Lam tân hưng</t>
+  </si>
+  <si>
+    <t>Thanh Trúc Lê</t>
+  </si>
+  <si>
+    <t>HD007541</t>
+  </si>
+  <si>
+    <t>116/154/13 tổ 80 khu phố 3 Phường trung mỹ Tây</t>
+  </si>
+  <si>
+    <t>Nhi Nhi</t>
+  </si>
+  <si>
+    <t>HD007561</t>
+  </si>
+  <si>
+    <t>chung cư sunrise city view block B</t>
+  </si>
+  <si>
+    <t>Xuân Xuân</t>
+  </si>
+  <si>
+    <t>HD007551</t>
+  </si>
+  <si>
+    <t>Địa chỉ đối diện 210/12 trịnh đình trọng, p tan phu</t>
+  </si>
+  <si>
+    <t>tan phu</t>
+  </si>
+  <si>
+    <t>Bùi Thị Cẩm Dung (inst: zunzunggg)</t>
+  </si>
+  <si>
+    <t>HD005892</t>
+  </si>
+  <si>
+    <t>T2-35 Khu Manhattan vinhomes Grand Park, Long Bình</t>
+  </si>
+  <si>
+    <t>chị ngọc</t>
+  </si>
+  <si>
+    <t>HD007306</t>
+  </si>
+  <si>
+    <t>C4/68 phạm hùng</t>
+  </si>
+  <si>
+    <t>HD007592</t>
+  </si>
+  <si>
+    <t>Nuong Huynh</t>
+  </si>
+  <si>
+    <t>HD007570</t>
+  </si>
+  <si>
+    <t>67 mai chí thọ phường an phú</t>
+  </si>
+  <si>
+    <t>Tranh ( mẹ e nhận ghi tên Tranh )</t>
+  </si>
+  <si>
+    <t>HD007313</t>
+  </si>
+  <si>
+    <t>245A/14D Ba Đình p8</t>
+  </si>
+  <si>
+    <t>Thu Ba Nguyễn</t>
+  </si>
+  <si>
+    <t>HD007575</t>
+  </si>
+  <si>
+    <t>chung cư Tô Hiến Thành 339/34A Tô Hiến Thành p12</t>
+  </si>
+  <si>
+    <t>Thảo Vy</t>
+  </si>
+  <si>
+    <t>HD007327</t>
+  </si>
+  <si>
+    <t>Dạ 163/14/41 Tô Hiến Thành phường Hoà Hưng</t>
+  </si>
+  <si>
+    <t>Kim Thi</t>
+  </si>
+  <si>
+    <t>HD007183</t>
+  </si>
+  <si>
+    <t>219/78 trần văn đang</t>
+  </si>
+  <si>
+    <t>Như Hoàng</t>
+  </si>
+  <si>
+    <t>HD006996</t>
+  </si>
+  <si>
+    <t>130 châu văn liêm p11</t>
+  </si>
+  <si>
+    <t>Thiên Tú</t>
+  </si>
+  <si>
+    <t>HD007273</t>
+  </si>
+  <si>
+    <t>B1706 Chung cư Đất Phương Nam, 241 Chu Văn An</t>
+  </si>
+  <si>
+    <t>Nguyệt LẠI</t>
+  </si>
+  <si>
+    <t>HD007430</t>
+  </si>
+  <si>
+    <t>111/8/2/62 Đặng Thùy Trâm, F13</t>
+  </si>
+  <si>
+    <t>Ngọc Anh</t>
+  </si>
+  <si>
+    <t>HD007286</t>
+  </si>
+  <si>
+    <t>Toà MP7 - chung cư Mizuki Park - Bình Hưng</t>
+  </si>
+  <si>
+    <t>Phạm Thị Bảo Trân</t>
+  </si>
+  <si>
+    <t>HD007243</t>
+  </si>
+  <si>
+    <t>Block B Chung Cư Urban Green, Đường Số 6, Hiệp Bình</t>
+  </si>
+  <si>
+    <t>Tramm Anh</t>
+  </si>
+  <si>
+    <t>HD007233</t>
+  </si>
+  <si>
+    <t>246 lý thường kiệt</t>
+  </si>
+  <si>
+    <t>Kiều Phương Thao</t>
+  </si>
+  <si>
+    <t>HD007212</t>
+  </si>
+  <si>
+    <t>290/5/15 Nơ Trang Long F12</t>
+  </si>
+  <si>
+    <t>Linh Phan</t>
+  </si>
+  <si>
+    <t>HD007200</t>
+  </si>
+  <si>
+    <t>6 thái văn lung p. bến nghé</t>
+  </si>
+  <si>
+    <t>Duyên Nguyễn</t>
+  </si>
+  <si>
+    <t>HD007196</t>
+  </si>
+  <si>
+    <t>1244/64/7 Lê Đức Thọ, p13</t>
+  </si>
+  <si>
+    <t>gộp</t>
+  </si>
+  <si>
+    <t>Hạnh Hạnh</t>
+  </si>
+  <si>
+    <t>HD007529</t>
+  </si>
+  <si>
+    <t>334 tô hiến thành p14 Chung cư kingdom101 block a</t>
+  </si>
+  <si>
+    <t>Quỳnh Như</t>
+  </si>
+  <si>
+    <t>HD007058</t>
+  </si>
+  <si>
+    <t>66/68, Phổ Quang, Phường 2</t>
+  </si>
+  <si>
+    <t>HD007059</t>
+  </si>
+  <si>
+    <t>HD007195</t>
+  </si>
+  <si>
+    <t>6/24 tấn chánh hiệp 36, p trung mỹ tây</t>
+  </si>
+  <si>
+    <t>Kim</t>
+  </si>
+  <si>
+    <t>HD007057</t>
+  </si>
+  <si>
+    <t>Lumiere Boulevard Block B Vinhome grand park , Phường Long Bình</t>
+  </si>
+  <si>
+    <t>Huỳnh Như</t>
+  </si>
+  <si>
+    <t>HD007431</t>
+  </si>
+  <si>
+    <t>Block B chung cư Mia đường 9a kdc trung sơn bình Hưng</t>
+  </si>
+  <si>
+    <t>Mercy Nguyễn Pmu</t>
+  </si>
+  <si>
+    <t>HD007354</t>
+  </si>
+  <si>
+    <t>298/16/8B Tân Hoà Đông P bình trị đông</t>
+  </si>
+  <si>
+    <t>Nguyen Ngoc</t>
+  </si>
+  <si>
+    <t>HD007390</t>
+  </si>
+  <si>
+    <t>Toà Nhà Victory Tân Phú</t>
+  </si>
+  <si>
+    <t>Công Thanh - Bảo Trân</t>
+  </si>
+  <si>
+    <t>HD007401</t>
+  </si>
+  <si>
+    <t>Giao về 63/5 dương đình hội, phước long B</t>
+  </si>
+  <si>
+    <t>HD007574</t>
+  </si>
+  <si>
+    <t>đặng - fb Kim Lee</t>
+  </si>
+  <si>
+    <t>HD007191</t>
+  </si>
+  <si>
+    <t>3/44 ấp nhị tân, xã tân thới nhì</t>
+  </si>
+  <si>
+    <t>hoc mon</t>
+  </si>
+  <si>
+    <t>Tram Anh Nguyen</t>
+  </si>
+  <si>
+    <t>HD005110</t>
+  </si>
+  <si>
+    <t>Topaz phoenix Ib phường 4</t>
+  </si>
+  <si>
+    <t>Đan Phạm Ngọc Hùng</t>
+  </si>
+  <si>
+    <t>HD007393</t>
+  </si>
+  <si>
+    <t>Số 25 đường 265, P. Hiệp Phú</t>
+  </si>
+  <si>
+    <t>NGA ANNA</t>
+  </si>
+  <si>
+    <t>375 tân thới hiệp 21, Tổ 3, Kp3</t>
+  </si>
+  <si>
+    <t>LISA</t>
+  </si>
+  <si>
+    <t>685 tân sơn phường 12</t>
+  </si>
+  <si>
+    <t>BELLA TRẦN</t>
+  </si>
+  <si>
+    <t>66đường 17 p10</t>
+  </si>
+  <si>
+    <t>Ly Clara Selena</t>
+  </si>
+  <si>
+    <t>403 tân sơn p12</t>
+  </si>
+  <si>
+    <t>TUYẾT NHI</t>
+  </si>
+  <si>
+    <t>170F Tân Hoà Đông f14</t>
+  </si>
+  <si>
+    <t>THU 7</t>
+  </si>
+  <si>
+    <t>NGAY 4-4</t>
+  </si>
+  <si>
+    <t>đăng - fb Kim Lee.</t>
+  </si>
+  <si>
+    <t>HD007875</t>
+  </si>
+  <si>
+    <t>AT 04-04</t>
+  </si>
+  <si>
+    <t>04-04-2026</t>
+  </si>
+  <si>
+    <t>Trâm</t>
+  </si>
+  <si>
+    <t>HD007872</t>
+  </si>
+  <si>
+    <t>3 trịnh khắc lập, p. thạnh mỹ lợi, tp. thủ đức ( dc cũ)</t>
+  </si>
+  <si>
+    <t>Trương Quỳnh Như</t>
+  </si>
+  <si>
+    <t>HD007799</t>
+  </si>
+  <si>
+    <t>27/62/34 thanh xuân 33</t>
+  </si>
+  <si>
+    <t>Trang Hồ Vĩnh Như</t>
+  </si>
+  <si>
+    <t>HD007699</t>
+  </si>
+  <si>
+    <t>35 đặng đức thuật, chung cư RIVERPARK PREMIER Block A, p.Tân Phong ( kế bên tiệm bánh tour les Jours)</t>
+  </si>
+  <si>
+    <t>Ji Ah</t>
+  </si>
+  <si>
+    <t>HD007814</t>
+  </si>
+  <si>
+    <t>89 lê thị chợ phú thuận Chung cư Skyline</t>
+  </si>
+  <si>
+    <t>Nguyễn Tố Mai</t>
+  </si>
+  <si>
+    <t>HD007743</t>
+  </si>
+  <si>
+    <t>413/8 lê văn sỹ p12</t>
+  </si>
+  <si>
+    <t>Nhi</t>
+  </si>
+  <si>
+    <t>HD007616</t>
+  </si>
+  <si>
+    <t>13/7 phú thọ f1</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>THÁI HÀ</t>
+  </si>
+  <si>
+    <t>HD007696</t>
+  </si>
+  <si>
+    <t>inden ressidence Empire city thủ thiêm</t>
+  </si>
+  <si>
+    <t>Trà Giang</t>
+  </si>
+  <si>
+    <t>HD007851</t>
+  </si>
+  <si>
+    <t>523 mã lò bình hưng hoà a</t>
+  </si>
+  <si>
+    <t>Hạnh Bùi</t>
+  </si>
+  <si>
+    <t>HD007610</t>
+  </si>
+  <si>
+    <t>31 Đường số 12, P. Trường Thọ, 1994 Nail Room</t>
+  </si>
+  <si>
+    <t>Trang Phạm</t>
+  </si>
+  <si>
+    <t>HD007577</t>
+  </si>
+  <si>
+    <t>16/3 đường số 51 p hiệp bình chánh kp8</t>
+  </si>
+  <si>
+    <t>Dung Nguyễn</t>
+  </si>
+  <si>
+    <t>HD007760</t>
+  </si>
+  <si>
+    <t>322/8 đào sư tích phước lộc</t>
+  </si>
+  <si>
+    <t>Tươi Em</t>
+  </si>
+  <si>
+    <t>HD007580</t>
+  </si>
+  <si>
+    <t>129 Nguyễn Thái Bình p3 Tân An</t>
+  </si>
+  <si>
+    <t>Lê Thuỷ Tiên</t>
+  </si>
+  <si>
+    <t>HD007708</t>
+  </si>
+  <si>
+    <t>Chung cư Safira Khang điền 454 võ chí công</t>
+  </si>
+  <si>
+    <t>Nguyễn Như Ngọc</t>
+  </si>
+  <si>
+    <t>HD007870</t>
+  </si>
+  <si>
+    <t>965/16/23h đg quang trung p14</t>
+  </si>
+  <si>
+    <t>Alice</t>
+  </si>
+  <si>
+    <t>HD007761</t>
+  </si>
+  <si>
+    <t>39 an nhơn phường 17</t>
+  </si>
+  <si>
+    <t>Phương Nhi Lê Ngọc</t>
+  </si>
+  <si>
+    <t>HD007868</t>
+  </si>
+  <si>
+    <t>Hẻm 83 Đường Tân Thới Hiệp 8, Phường Tân Thới Hiệp</t>
+  </si>
+  <si>
+    <t>cao cường - fb Phan Hoài Thu</t>
+  </si>
+  <si>
+    <t>HD007855</t>
+  </si>
+  <si>
+    <t>128/13 lê đức thọ, phường 6</t>
+  </si>
+  <si>
+    <t>shop chịu ship</t>
+  </si>
+  <si>
+    <t>Mai Vu</t>
+  </si>
+  <si>
+    <t>HD007426</t>
+  </si>
+  <si>
+    <t>160/7 bùi đinh túy p12</t>
+  </si>
+  <si>
+    <t>Nguyễn Đào</t>
+  </si>
+  <si>
+    <t>HD007889</t>
+  </si>
+  <si>
+    <t>670/59/16 đoàn văn bơ p16</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>Amyy Hoang- Phương Uyên</t>
+  </si>
+  <si>
+    <t>HD007867</t>
+  </si>
+  <si>
+    <t>1D/2 tổ 58, khu phố 7, phường Trung Mỹ Tây</t>
+  </si>
+  <si>
+    <t>Linh Hồ.</t>
+  </si>
+  <si>
+    <t>HD007756</t>
+  </si>
+  <si>
+    <t>Chung cư Đức Khải phường Tân Mỹ  Block B4</t>
+  </si>
+  <si>
+    <t>Aren</t>
+  </si>
+  <si>
+    <t>HD007021</t>
+  </si>
+  <si>
+    <t>793/10 trần xuân soạn, phường tân hưng</t>
+  </si>
+  <si>
+    <t>Thúy Nga</t>
+  </si>
+  <si>
+    <t>HD007622</t>
+  </si>
+  <si>
+    <t>45a đường 3/2</t>
+  </si>
+  <si>
+    <t>Thụy fb Kim Ngọc Anh</t>
+  </si>
+  <si>
+    <t>HD007621</t>
+  </si>
+  <si>
+    <t>Chung cư parcspi ng, 537 nguyễn duy trinh, phường bình trưng đông</t>
+  </si>
+  <si>
+    <t>Alina Joy</t>
+  </si>
+  <si>
+    <t>HD007881</t>
+  </si>
+  <si>
+    <t>Tháp B cc goldview p1</t>
+  </si>
+  <si>
+    <t>Kim Dung Lý</t>
+  </si>
+  <si>
+    <t>HD007853</t>
+  </si>
+  <si>
+    <t>3024 phạm thế hiển P7</t>
+  </si>
+  <si>
+    <t>Note : Bổng Kẹo</t>
+  </si>
+  <si>
+    <t>HD007318</t>
+  </si>
+  <si>
+    <t>124 đường 24b bình trị đông</t>
+  </si>
+  <si>
+    <t>Nguyễn Thiên Nga</t>
+  </si>
+  <si>
+    <t>HD007827</t>
+  </si>
+  <si>
+    <t>481/42 Trường Chinh, phường 14</t>
+  </si>
+  <si>
+    <t>An Hy</t>
+  </si>
+  <si>
+    <t>HD007387</t>
+  </si>
+  <si>
+    <t>Vinhomes Central Park – Park 6A 6B Vinhomes Tân Cảng, Phường 22</t>
+  </si>
+  <si>
+    <t>Trâm Trâm</t>
+  </si>
+  <si>
+    <t>HD007697</t>
+  </si>
+  <si>
+    <t>188 nguyễn xí p26</t>
+  </si>
+  <si>
+    <t>Angelaberr - Air Malay (inst happyodenky).</t>
+  </si>
+  <si>
+    <t>HD007869</t>
+  </si>
+  <si>
+    <t>1416 Trần Thị Trọng, Phường 15</t>
+  </si>
+  <si>
+    <t>BN10247</t>
+  </si>
+  <si>
+    <t>HD007213</t>
+  </si>
+  <si>
+    <t>163 Đường Trương Thị Hoa, phường Tân Thới Hiệp</t>
+  </si>
+  <si>
+    <t>Jennytram</t>
+  </si>
+  <si>
+    <t>HD007659</t>
+  </si>
+  <si>
+    <t>418/4 trường sa p2</t>
+  </si>
+  <si>
+    <t>Thị Thị</t>
+  </si>
+  <si>
+    <t>HD007791</t>
+  </si>
+  <si>
+    <t>545 trần hưng đạo b phương 14</t>
+  </si>
+  <si>
+    <t>Name: Yors Sreypouch Phone Number: 077905987</t>
+  </si>
+  <si>
+    <t>HD007871</t>
+  </si>
+  <si>
+    <t>301 phạm ngũ lão</t>
+  </si>
+  <si>
+    <t>SU ANH</t>
+  </si>
+  <si>
+    <t>22/40 Yên Thế, P2</t>
+  </si>
+  <si>
+    <t>Trần Thảo</t>
+  </si>
+  <si>
+    <t>Số 262/26/3 Lũy Bán Bích, phường Tân Phú</t>
+  </si>
+  <si>
+    <t>NGÂN KIM</t>
+  </si>
+  <si>
+    <t>T8-20 mahattan vinhomes Grand park , phường long bình</t>
+  </si>
+  <si>
+    <t>NGA LINH</t>
+  </si>
+  <si>
+    <t>137/31/21 phan anh . Kp 12 . Bình trị đông</t>
+  </si>
+  <si>
+    <t>Kiều Filler</t>
+  </si>
+  <si>
+    <t>HD006142</t>
+  </si>
+  <si>
+    <t>166/48c thích quảng Đức</t>
+  </si>
+  <si>
+    <t>luu tra</t>
+  </si>
+  <si>
+    <t>30-03-2026</t>
+  </si>
+  <si>
+    <t>đơn trả</t>
+  </si>
+  <si>
+    <t>x</t>
+  </si>
+  <si>
+    <t>xx</t>
+  </si>
+  <si>
+    <t>THU 2</t>
+  </si>
+  <si>
+    <t>NGAY 6-4</t>
+  </si>
+  <si>
+    <t>Uyên Hana</t>
+  </si>
+  <si>
+    <t>HD008160</t>
+  </si>
+  <si>
+    <t>32 phan văn sửu p13</t>
+  </si>
+  <si>
+    <t>06-04-2026</t>
+  </si>
+  <si>
+    <t>Nic Nic</t>
+  </si>
+  <si>
+    <t>HD008240</t>
+  </si>
+  <si>
+    <t>AT 06-04</t>
+  </si>
+  <si>
+    <t>Tran Thi Khanh Linh</t>
+  </si>
+  <si>
+    <t>HD008286</t>
+  </si>
+  <si>
+    <t>Thúy Duy</t>
+  </si>
+  <si>
+    <t>Bùi Vĩ Thương</t>
+  </si>
+  <si>
+    <t>HD008410</t>
+  </si>
+  <si>
+    <t>3273 phạm thế hiển, p7</t>
+  </si>
+  <si>
+    <t>HD008072</t>
+  </si>
+  <si>
+    <t>Ngọc Diệu</t>
+  </si>
+  <si>
+    <t>HD008453</t>
+  </si>
+  <si>
+    <t>Hạnh Huỳnh</t>
+  </si>
+  <si>
+    <t>HD008244</t>
+  </si>
+  <si>
+    <t>42A, đường Mã Lò, phường Bình Trị Đông A</t>
+  </si>
+  <si>
+    <t>Vo Ngoc Han</t>
+  </si>
+  <si>
+    <t>HD008134</t>
+  </si>
+  <si>
+    <t>150 Thành Thái, p12</t>
+  </si>
+  <si>
+    <t>Quỳnh Hương</t>
+  </si>
+  <si>
+    <t>HD008283</t>
+  </si>
+  <si>
+    <t>Ngo Thuy Linh</t>
+  </si>
+  <si>
+    <t>HD008187</t>
+  </si>
+  <si>
+    <t>Hồng Ngọc</t>
+  </si>
+  <si>
+    <t>HD008458</t>
+  </si>
+  <si>
+    <t>575/11A tỉnh lộ 10</t>
+  </si>
+  <si>
+    <t>HD007954</t>
+  </si>
+  <si>
+    <t>Dung Phamm</t>
+  </si>
+  <si>
+    <t>HD008440</t>
+  </si>
+  <si>
+    <t>HD008413</t>
+  </si>
+  <si>
+    <t>chung cư linh trung đường 16 linh trung</t>
+  </si>
+  <si>
+    <t>HD008275</t>
+  </si>
+  <si>
+    <t>Trần Ngọc Bích.</t>
+  </si>
+  <si>
+    <t>HD008448</t>
+  </si>
+  <si>
+    <t>Lê Huyền Trang</t>
+  </si>
+  <si>
+    <t>HD007992</t>
+  </si>
+  <si>
+    <t>Huỳnh Huỳnh Như</t>
+  </si>
+  <si>
+    <t>HD008318</t>
+  </si>
+  <si>
+    <t>Hiền</t>
+  </si>
+  <si>
+    <t>HD008424</t>
+  </si>
+  <si>
+    <t>Shin</t>
+  </si>
+  <si>
+    <t>HD008285</t>
+  </si>
+  <si>
+    <t>chị Vân - fb Nguyễn Linh</t>
+  </si>
+  <si>
+    <t>HD008230</t>
+  </si>
+  <si>
+    <t>130 Đoàn văn bơ P Khánh Hội</t>
+  </si>
+  <si>
+    <t>Ánh nguyên - fb Thao Suong Hoang</t>
+  </si>
+  <si>
+    <t>HD008237</t>
+  </si>
+  <si>
+    <t>Miêu Trần</t>
+  </si>
+  <si>
+    <t>HD007974</t>
+  </si>
+  <si>
+    <t>HD008460</t>
+  </si>
+  <si>
+    <t>Elly Nguyễn</t>
+  </si>
+  <si>
+    <t>HD008436</t>
+  </si>
+  <si>
+    <t>431/7b đường Phan Văn Trị phường 7</t>
+  </si>
+  <si>
+    <t>Kim Chúc</t>
+  </si>
+  <si>
+    <t>HD008071</t>
+  </si>
+  <si>
+    <t>Hẻm 188/73 Nguyễn thị minh khai đakao</t>
+  </si>
+  <si>
+    <t>Kim Hạnh</t>
+  </si>
+  <si>
+    <t>HD008246</t>
+  </si>
+  <si>
+    <t>650 sư vạn hạnh p12</t>
+  </si>
+  <si>
+    <t>Ngọc Ngân</t>
+  </si>
+  <si>
+    <t>HD007961</t>
+  </si>
+  <si>
+    <t>HD008114</t>
+  </si>
+  <si>
+    <t>Trà An</t>
+  </si>
+  <si>
+    <t>HD008241</t>
+  </si>
+  <si>
+    <t>33 Trần Đình Xu, Phường Cầu Ông Lãnh</t>
+  </si>
+  <si>
+    <t>Lài Lê</t>
+  </si>
+  <si>
+    <t>HD008139</t>
+  </si>
+  <si>
+    <t>Ngô Bích Hợp</t>
+  </si>
+  <si>
+    <t>HD008151</t>
+  </si>
+  <si>
+    <t>83 song hành an phú ( chung cư estella hight tháp 4)</t>
+  </si>
+  <si>
+    <t>Hà Trần</t>
+  </si>
+  <si>
+    <t>HD008126</t>
+  </si>
+  <si>
+    <t>Ngọc Dung</t>
+  </si>
+  <si>
+    <t>HD007989</t>
+  </si>
+  <si>
+    <t>B1 chung cư starlight phường 11.</t>
+  </si>
+  <si>
+    <t>Van Huynh ft Trương Mỹ Linh</t>
+  </si>
+  <si>
+    <t>Anna Le</t>
+  </si>
+  <si>
+    <t>HD008155</t>
+  </si>
+  <si>
+    <t>112 bến vân đồn, phường 9</t>
+  </si>
+  <si>
+    <t>Nguyên Nguyễn</t>
+  </si>
+  <si>
+    <t>HD007920</t>
+  </si>
+  <si>
+    <t>106A Vành Đai Trong, khu phố 13, P.An Lạc</t>
+  </si>
+  <si>
+    <t>Vy Lê</t>
+  </si>
+  <si>
+    <t>119F/31b đặng chất p.chánh hưng</t>
+  </si>
+  <si>
+    <t>Thảo Hiền</t>
+  </si>
+  <si>
+    <t>HD008235</t>
+  </si>
+  <si>
+    <t>32 đường số 54, Thạnh Mỹ Lợi</t>
+  </si>
+  <si>
+    <t>HD008108</t>
+  </si>
+  <si>
+    <t>192 Nguyễn văn hưởng thảo điền</t>
+  </si>
+  <si>
+    <t>HD008229</t>
+  </si>
+  <si>
+    <t>HD008127</t>
+  </si>
+  <si>
+    <t>NANA CHONG</t>
+  </si>
+  <si>
+    <t>NGUYÊN NGUYÊN</t>
+  </si>
+  <si>
+    <t>12 TÔN ĐẢN P13</t>
+  </si>
+  <si>
+    <t>375 tân thới hiệp 21, Tổ 3,Kp3</t>
+  </si>
+  <si>
+    <t>BOS BMB</t>
+  </si>
+  <si>
+    <t>108 đường 85 tân hưng</t>
+  </si>
+  <si>
+    <t>225/4a đường tam bình phường tam phú</t>
+  </si>
+  <si>
+    <t>HD008205</t>
+  </si>
+  <si>
+    <t>539/22 hương lộ 3 phường bình hưng hòa</t>
+  </si>
+  <si>
+    <t>Thi Thi</t>
+  </si>
+  <si>
+    <t>15 lô c cư xá phủ lâm D phường 10</t>
+  </si>
+  <si>
+    <t>132 Le van quoi p bình hưng hòa a</t>
+  </si>
+  <si>
+    <t>Saigon Royal Residences, Nguyễn Trường Tộ, phường 13</t>
+  </si>
+  <si>
+    <t>37 nguyễn văn hưởng thảo điền</t>
+  </si>
+  <si>
+    <t>310 tô ngọc vân -tam phú</t>
+  </si>
+  <si>
+    <t>Thúy Ly</t>
+  </si>
+  <si>
+    <t>Phương Thao</t>
+  </si>
+  <si>
+    <t>137/18 âu dương lân</t>
+  </si>
+  <si>
+    <t>43/3 Cửu Long p2</t>
+  </si>
+  <si>
+    <t>737-739 hồng bàng, phường bình tây</t>
+  </si>
+  <si>
+    <t>Đường số 15, Phường Tân Phú The Peak Midtown Phú Mỹ Hưng</t>
+  </si>
+  <si>
+    <t>180 nguyễn tất thành</t>
+  </si>
+  <si>
+    <t>278-283 chung cư grand riverside đường Bến Vân Đồn, phường 2</t>
+  </si>
+  <si>
+    <t>56 đường số 1 khu dân cư hirnlam Tân Hưng</t>
+  </si>
+  <si>
+    <t>Số 6 nguyễn biểu.P1</t>
+  </si>
+  <si>
+    <t>Huỳnh Quế Trinh</t>
+  </si>
+  <si>
+    <t>166 đường số 1, khu phố 25, phường Bình Hưng Hòa</t>
+  </si>
+  <si>
+    <t>Số 5a, Tống Văn Hên, phường 15</t>
+  </si>
+  <si>
+    <t>Nguyễn Tiên</t>
+  </si>
+  <si>
+    <t>326 trần quang khải tân định</t>
+  </si>
+  <si>
+    <t>F4/19 ấp 6c đường liên ấp 2/6, Xã Vĩnh Lộc A</t>
+  </si>
+  <si>
+    <t>200 đường 3/2 phường Hoà Hưng Chưng cư Hà Đô, Toà Iris 4</t>
+  </si>
+  <si>
+    <t>HD008396</t>
+  </si>
+  <si>
+    <t>130/21 trần thị trọng. P15</t>
+  </si>
+  <si>
+    <t>Note : Bống Kẹo</t>
+  </si>
+  <si>
+    <t>HD007921</t>
+  </si>
+  <si>
+    <t>HX008403</t>
+  </si>
+  <si>
+    <t>Lâm Oanh</t>
+  </si>
+  <si>
+    <t>102 phan văn hớn</t>
+  </si>
+  <si>
+    <t>Người Nhận : FB HUYEN VUONG</t>
+  </si>
+  <si>
+    <t>Số 78 Đường Số 7, P. Bình Hưng Hòa</t>
+  </si>
+  <si>
+    <t>535/59/4C THỐNG NHẤT P16</t>
+  </si>
+  <si>
+    <t>WIND XPRESS</t>
+  </si>
+  <si>
+    <t>Thanh Hằng (Vivi Kosalim)</t>
+  </si>
+  <si>
+    <t>605 Âu Cơ, Phường Phú Trung</t>
+  </si>
+  <si>
+    <t>66 đường 17 p10</t>
+  </si>
+  <si>
+    <t>119 hoàng diệu 2 linh trung</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -558,6 +1821,19 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="7">
@@ -609,7 +1885,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -621,6 +1897,11 @@
     <xf numFmtId="49" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="49" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="3" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="3" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1743,10 +3024,12 @@
   <dimension ref="A1:P24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="1" max="2" width="9.140625" customWidth="1"/>
     <col min="3" max="3" width="27.85546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9.5703125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="42.5703125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="9.140625" customWidth="1"/>
     <col min="12" max="12" width="10.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1819,7 +3102,7 @@
         <v>100</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>159</v>
+        <v>101</v>
       </c>
       <c r="F3" s="4" t="s">
         <v>97</v>
@@ -1831,7 +3114,7 @@
         <v>70</v>
       </c>
       <c r="I3" s="3">
-        <f>G3-H3</f>
+        <f t="shared" ref="I3:I24" si="0">G3-H3</f>
         <v>0</v>
       </c>
       <c r="J3" s="3" t="s">
@@ -1855,23 +3138,23 @@
         <v>103</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>160</v>
+        <v>104</v>
       </c>
       <c r="F4" s="9" t="s">
         <v>94</v>
       </c>
       <c r="G4" s="9">
+        <v>30</v>
+      </c>
+      <c r="H4" s="9">
+        <v>30</v>
+      </c>
+      <c r="I4" s="9">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H4" s="9">
-        <v>30</v>
-      </c>
-      <c r="I4" s="9">
-        <f t="shared" ref="I4:I24" si="0">G4-H4</f>
-        <v>-30</v>
-      </c>
       <c r="J4" s="9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K4" s="9" t="s">
         <v>24</v>
@@ -1888,23 +3171,23 @@
         <v>18</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>153</v>
+        <v>107</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>64</v>
       </c>
       <c r="G5" s="3">
+        <v>30</v>
+      </c>
+      <c r="H5" s="3">
+        <v>30</v>
+      </c>
+      <c r="I5" s="3">
+        <f t="shared" si="0"/>
         <v>0</v>
-      </c>
-      <c r="H5" s="3">
-        <v>30</v>
-      </c>
-      <c r="I5" s="3">
-        <f t="shared" si="0"/>
-        <v>-30</v>
       </c>
       <c r="J5" s="3" t="s">
         <v>24</v>
@@ -1924,10 +3207,10 @@
         <v>18</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>148</v>
+        <v>108</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>149</v>
+        <v>109</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>49</v>
@@ -1960,10 +3243,10 @@
         <v>18</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>146</v>
+        <v>110</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>147</v>
+        <v>111</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>94</v>
@@ -1993,13 +3276,13 @@
         <v>18</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>154</v>
+        <v>112</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>40</v>
@@ -2029,16 +3312,16 @@
         <v>18</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="G9" s="7">
         <v>35</v>
@@ -2051,7 +3334,7 @@
         <v>0</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="K9" s="7" t="s">
         <v>24</v>
@@ -2068,16 +3351,16 @@
         <v>18</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>157</v>
+        <v>122</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>158</v>
+        <v>123</v>
       </c>
       <c r="G10" s="3">
         <v>0</v>
@@ -2104,13 +3387,13 @@
         <v>18</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>164</v>
+        <v>124</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="F11" s="7" t="s">
         <v>22</v>
@@ -2126,7 +3409,7 @@
         <v>840</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="K11" s="7" t="s">
         <v>24</v>
@@ -2140,13 +3423,13 @@
         <v>18</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="F12" s="9" t="s">
         <v>60</v>
@@ -2162,7 +3445,7 @@
         <v>670</v>
       </c>
       <c r="J12" s="9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K12" s="9" t="s">
         <v>24</v>
@@ -2176,13 +3459,13 @@
         <v>18</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="F13" s="3" t="s">
         <v>40</v>
@@ -2212,16 +3495,16 @@
         <v>18</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>148</v>
+        <v>108</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="G14" s="9">
         <v>775</v>
@@ -2234,7 +3517,7 @@
         <v>750</v>
       </c>
       <c r="J14" s="9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K14" s="9" t="s">
         <v>24</v>
@@ -2248,13 +3531,13 @@
         <v>18</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>126</v>
+        <v>137</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>127</v>
+        <v>138</v>
       </c>
       <c r="F15" s="7" t="s">
         <v>56</v>
@@ -2270,7 +3553,7 @@
         <v>-25</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="K15" s="7" t="s">
         <v>24</v>
@@ -2284,13 +3567,13 @@
         <v>18</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>155</v>
+        <v>139</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>156</v>
+        <v>141</v>
       </c>
       <c r="F16" s="3" t="s">
         <v>40</v>
@@ -2320,13 +3603,13 @@
         <v>18</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>161</v>
+        <v>142</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>162</v>
+        <v>143</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>163</v>
+        <v>144</v>
       </c>
       <c r="F17" s="7" t="s">
         <v>29</v>
@@ -2342,7 +3625,7 @@
         <v>620</v>
       </c>
       <c r="J17" s="7" t="s">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="K17" s="7" t="s">
         <v>24</v>
@@ -2356,13 +3639,13 @@
         <v>18</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>129</v>
+        <v>145</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>130</v>
+        <v>146</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>131</v>
+        <v>147</v>
       </c>
       <c r="F18" s="10" t="s">
         <v>60</v>
@@ -2378,7 +3661,7 @@
         <v>870</v>
       </c>
       <c r="J18" s="9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K18" s="9" t="s">
         <v>24</v>
@@ -2392,16 +3675,16 @@
         <v>18</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>132</v>
+        <v>148</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>133</v>
+        <v>149</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>134</v>
+        <v>150</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>135</v>
+        <v>151</v>
       </c>
       <c r="G19" s="7">
         <v>1215</v>
@@ -2414,7 +3697,7 @@
         <v>1180</v>
       </c>
       <c r="J19" s="7" t="s">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="K19" s="7" t="s">
         <v>24</v>
@@ -2428,13 +3711,13 @@
         <v>18</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>136</v>
+        <v>152</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>137</v>
+        <v>153</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>138</v>
+        <v>154</v>
       </c>
       <c r="F20" s="3" t="s">
         <v>49</v>
@@ -2464,13 +3747,13 @@
         <v>18</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="F21" s="7" t="s">
         <v>29</v>
@@ -2486,7 +3769,7 @@
         <v>710</v>
       </c>
       <c r="J21" s="7" t="s">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="K21" s="7" t="s">
         <v>24</v>
@@ -2500,13 +3783,13 @@
         <v>18</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>141</v>
+        <v>158</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>142</v>
+        <v>160</v>
       </c>
       <c r="F22" s="7" t="s">
         <v>22</v>
@@ -2522,7 +3805,7 @@
         <v>740</v>
       </c>
       <c r="J22" s="7" t="s">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="K22" s="7" t="s">
         <v>24</v>
@@ -2536,13 +3819,13 @@
         <v>18</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>143</v>
+        <v>161</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>144</v>
+        <v>162</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>145</v>
+        <v>163</v>
       </c>
       <c r="F23" s="9" t="s">
         <v>60</v>
@@ -2558,7 +3841,7 @@
         <v>670</v>
       </c>
       <c r="J23" s="9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K23" s="9" t="s">
         <v>24</v>
@@ -2572,13 +3855,13 @@
         <v>18</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>150</v>
+        <v>164</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>151</v>
+        <v>165</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>152</v>
+        <v>166</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>40</v>
@@ -2606,4 +3889,5731 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:P53"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="2" width="9.140625" customWidth="1"/>
+    <col min="3" max="3" width="32.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="68.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="9.140625" customWidth="1"/>
+    <col min="12" max="12" width="10.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B1" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="G3" s="3">
+        <v>680</v>
+      </c>
+      <c r="H3" s="3">
+        <v>20</v>
+      </c>
+      <c r="I3" s="3">
+        <f t="shared" ref="I3:I34" si="0">G3-H3</f>
+        <v>660</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="G4" s="3">
+        <v>685</v>
+      </c>
+      <c r="H4" s="3">
+        <v>25</v>
+      </c>
+      <c r="I4" s="3">
+        <f t="shared" si="0"/>
+        <v>660</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="G5" s="3">
+        <v>1500</v>
+      </c>
+      <c r="H5" s="3">
+        <v>30</v>
+      </c>
+      <c r="I5" s="3">
+        <f t="shared" si="0"/>
+        <v>1470</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="G6" s="3">
+        <v>0</v>
+      </c>
+      <c r="H6" s="3">
+        <v>25</v>
+      </c>
+      <c r="I6" s="3">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L6" s="3" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>184</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="G7" s="7">
+        <v>20</v>
+      </c>
+      <c r="H7" s="7">
+        <v>20</v>
+      </c>
+      <c r="I7" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J7" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="K7" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L7" s="7" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="G8" s="7">
+        <v>820</v>
+      </c>
+      <c r="H8" s="7">
+        <v>30</v>
+      </c>
+      <c r="I8" s="7">
+        <f t="shared" si="0"/>
+        <v>790</v>
+      </c>
+      <c r="J8" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="K8" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L8" s="7" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>191</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>192</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="G9" s="7">
+        <v>1330</v>
+      </c>
+      <c r="H9" s="7">
+        <v>30</v>
+      </c>
+      <c r="I9" s="7">
+        <f t="shared" si="0"/>
+        <v>1300</v>
+      </c>
+      <c r="J9" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="K9" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L9" s="7" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="G10" s="3">
+        <v>0</v>
+      </c>
+      <c r="H10" s="3">
+        <v>20</v>
+      </c>
+      <c r="I10" s="3">
+        <f t="shared" si="0"/>
+        <v>-20</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L10" s="3" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="G11" s="3">
+        <v>690</v>
+      </c>
+      <c r="H11" s="3">
+        <v>30</v>
+      </c>
+      <c r="I11" s="3">
+        <f t="shared" si="0"/>
+        <v>660</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K11" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L11" s="3" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>202</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="G12" s="7">
+        <v>375</v>
+      </c>
+      <c r="H12" s="7">
+        <v>25</v>
+      </c>
+      <c r="I12" s="7">
+        <f t="shared" si="0"/>
+        <v>350</v>
+      </c>
+      <c r="J12" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="K12" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L12" s="7" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="G13" s="3">
+        <v>0</v>
+      </c>
+      <c r="H13" s="3">
+        <v>30</v>
+      </c>
+      <c r="I13" s="3">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K13" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L13" s="3" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>206</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>207</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="G14" s="7">
+        <v>830</v>
+      </c>
+      <c r="H14" s="7">
+        <v>30</v>
+      </c>
+      <c r="I14" s="7">
+        <f t="shared" si="0"/>
+        <v>800</v>
+      </c>
+      <c r="J14" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="K14" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L14" s="7" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>209</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>210</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>211</v>
+      </c>
+      <c r="F15" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="G15" s="7">
+        <v>380</v>
+      </c>
+      <c r="H15" s="7">
+        <v>30</v>
+      </c>
+      <c r="I15" s="7">
+        <f t="shared" si="0"/>
+        <v>350</v>
+      </c>
+      <c r="J15" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="K15" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L15" s="7" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="F16" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="G16" s="7">
+        <v>670</v>
+      </c>
+      <c r="H16" s="7">
+        <v>30</v>
+      </c>
+      <c r="I16" s="7">
+        <f t="shared" si="0"/>
+        <v>640</v>
+      </c>
+      <c r="J16" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="K16" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L16" s="7" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="17" spans="2:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>217</v>
+      </c>
+      <c r="F17" s="8" t="s">
+        <v>218</v>
+      </c>
+      <c r="G17" s="7">
+        <v>365</v>
+      </c>
+      <c r="H17" s="7">
+        <v>25</v>
+      </c>
+      <c r="I17" s="7">
+        <f t="shared" si="0"/>
+        <v>340</v>
+      </c>
+      <c r="J17" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="K17" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L17" s="7" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="18" spans="2:13" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="G18" s="5">
+        <v>30</v>
+      </c>
+      <c r="H18" s="5">
+        <v>30</v>
+      </c>
+      <c r="I18" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J18" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="K18" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L18" s="5" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="19" spans="2:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>224</v>
+      </c>
+      <c r="F19" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="G19" s="7">
+        <v>1460</v>
+      </c>
+      <c r="H19" s="7">
+        <v>30</v>
+      </c>
+      <c r="I19" s="7">
+        <f t="shared" si="0"/>
+        <v>1430</v>
+      </c>
+      <c r="J19" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="K19" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L19" s="7" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="20" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3">
+        <v>20</v>
+      </c>
+      <c r="I20" s="3">
+        <f t="shared" si="0"/>
+        <v>-20</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L20" s="3" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="21" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="G21" s="3">
+        <v>1480</v>
+      </c>
+      <c r="H21" s="3">
+        <v>30</v>
+      </c>
+      <c r="I21" s="3">
+        <f t="shared" si="0"/>
+        <v>1450</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K21" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L21" s="3" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="22" spans="2:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>231</v>
+      </c>
+      <c r="F22" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="G22" s="7">
+        <v>1440</v>
+      </c>
+      <c r="H22" s="7">
+        <v>30</v>
+      </c>
+      <c r="I22" s="7">
+        <f t="shared" si="0"/>
+        <v>1410</v>
+      </c>
+      <c r="J22" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="K22" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L22" s="7" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="23" spans="2:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>232</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>233</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>234</v>
+      </c>
+      <c r="F23" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="G23" s="7">
+        <v>375</v>
+      </c>
+      <c r="H23" s="7">
+        <v>25</v>
+      </c>
+      <c r="I23" s="7">
+        <f t="shared" si="0"/>
+        <v>350</v>
+      </c>
+      <c r="J23" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="K23" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L23" s="7" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="24" spans="2:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>235</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>236</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="F24" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="G24" s="7">
+        <v>745</v>
+      </c>
+      <c r="H24" s="7">
+        <v>25</v>
+      </c>
+      <c r="I24" s="7">
+        <f t="shared" si="0"/>
+        <v>720</v>
+      </c>
+      <c r="J24" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="K24" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L24" s="7" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="25" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G25" s="3">
+        <v>685</v>
+      </c>
+      <c r="H25" s="3">
+        <v>25</v>
+      </c>
+      <c r="I25" s="3">
+        <f t="shared" si="0"/>
+        <v>660</v>
+      </c>
+      <c r="J25" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K25" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L25" s="3" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="26" spans="2:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>241</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>242</v>
+      </c>
+      <c r="E26" s="7" t="s">
+        <v>243</v>
+      </c>
+      <c r="F26" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="G26" s="7">
+        <v>30</v>
+      </c>
+      <c r="H26" s="7">
+        <v>30</v>
+      </c>
+      <c r="I26" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J26" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="K26" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L26" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="M26" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="27" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G27" s="3">
+        <v>770</v>
+      </c>
+      <c r="H27" s="3">
+        <v>20</v>
+      </c>
+      <c r="I27" s="3">
+        <f t="shared" si="0"/>
+        <v>750</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K27" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L27" s="3" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="28" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G28" s="3">
+        <v>680</v>
+      </c>
+      <c r="H28" s="3">
+        <v>20</v>
+      </c>
+      <c r="I28" s="3">
+        <f t="shared" si="0"/>
+        <v>660</v>
+      </c>
+      <c r="J28" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K28" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L28" s="3" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="29" spans="2:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="E29" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="F29" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="G29" s="7">
+        <v>695</v>
+      </c>
+      <c r="H29" s="7">
+        <v>35</v>
+      </c>
+      <c r="I29" s="7">
+        <f t="shared" si="0"/>
+        <v>660</v>
+      </c>
+      <c r="J29" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="K29" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L29" s="7" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="30" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="G30" s="3">
+        <v>1030</v>
+      </c>
+      <c r="H30" s="3">
+        <v>30</v>
+      </c>
+      <c r="I30" s="3">
+        <f t="shared" si="0"/>
+        <v>1000</v>
+      </c>
+      <c r="J30" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K30" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L30" s="3" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="31" spans="2:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B31" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>256</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>257</v>
+      </c>
+      <c r="E31" s="7" t="s">
+        <v>258</v>
+      </c>
+      <c r="F31" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="G31" s="7">
+        <v>765</v>
+      </c>
+      <c r="H31" s="7">
+        <v>25</v>
+      </c>
+      <c r="I31" s="7">
+        <f t="shared" si="0"/>
+        <v>740</v>
+      </c>
+      <c r="J31" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="K31" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L31" s="7" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="32" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B32" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G32" s="3">
+        <v>680</v>
+      </c>
+      <c r="H32" s="3">
+        <v>20</v>
+      </c>
+      <c r="I32" s="3">
+        <f t="shared" si="0"/>
+        <v>660</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K32" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L32" s="3" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B33" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>262</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>263</v>
+      </c>
+      <c r="E33" s="7" t="s">
+        <v>264</v>
+      </c>
+      <c r="F33" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="G33" s="7">
+        <v>680</v>
+      </c>
+      <c r="H33" s="7">
+        <v>20</v>
+      </c>
+      <c r="I33" s="7">
+        <f t="shared" si="0"/>
+        <v>660</v>
+      </c>
+      <c r="J33" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="K33" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L33" s="7" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B34" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="F34" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="G34" s="3">
+        <v>685</v>
+      </c>
+      <c r="H34" s="3">
+        <v>25</v>
+      </c>
+      <c r="I34" s="3">
+        <f t="shared" si="0"/>
+        <v>660</v>
+      </c>
+      <c r="J34" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K34" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L34" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="M34" s="3" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B35" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>269</v>
+      </c>
+      <c r="D35" s="7" t="s">
+        <v>270</v>
+      </c>
+      <c r="E35" s="7" t="s">
+        <v>271</v>
+      </c>
+      <c r="F35" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="G35" s="7">
+        <v>815</v>
+      </c>
+      <c r="H35" s="7">
+        <v>25</v>
+      </c>
+      <c r="I35" s="7">
+        <f t="shared" ref="I35:I53" si="1">G35-H35</f>
+        <v>790</v>
+      </c>
+      <c r="J35" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="K35" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L35" s="7" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B36" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="F36" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="G36" s="3">
+        <v>820</v>
+      </c>
+      <c r="H36" s="3">
+        <v>0</v>
+      </c>
+      <c r="I36" s="3">
+        <f t="shared" si="1"/>
+        <v>820</v>
+      </c>
+      <c r="J36" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K36" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L36" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="M36" s="3" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B37" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="F37" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="G37" s="3">
+        <v>1585</v>
+      </c>
+      <c r="H37" s="3">
+        <v>25</v>
+      </c>
+      <c r="I37" s="3">
+        <f t="shared" si="1"/>
+        <v>1560</v>
+      </c>
+      <c r="J37" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K37" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L37" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="M37" s="3" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B38" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C38" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="D38" s="7" t="s">
+        <v>276</v>
+      </c>
+      <c r="E38" s="7" t="s">
+        <v>277</v>
+      </c>
+      <c r="F38" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="G38" s="7">
+        <v>690</v>
+      </c>
+      <c r="H38" s="7">
+        <v>30</v>
+      </c>
+      <c r="I38" s="7">
+        <f t="shared" si="1"/>
+        <v>660</v>
+      </c>
+      <c r="J38" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="K38" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L38" s="7" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B39" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>278</v>
+      </c>
+      <c r="D39" s="5" t="s">
+        <v>279</v>
+      </c>
+      <c r="E39" s="5" t="s">
+        <v>280</v>
+      </c>
+      <c r="F39" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="G39" s="5">
+        <v>920</v>
+      </c>
+      <c r="H39" s="5">
+        <v>30</v>
+      </c>
+      <c r="I39" s="5">
+        <f t="shared" si="1"/>
+        <v>890</v>
+      </c>
+      <c r="J39" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="K39" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L39" s="5" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B40" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C40" s="7" t="s">
+        <v>281</v>
+      </c>
+      <c r="D40" s="7" t="s">
+        <v>282</v>
+      </c>
+      <c r="E40" s="7" t="s">
+        <v>283</v>
+      </c>
+      <c r="F40" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="G40" s="7">
+        <v>765</v>
+      </c>
+      <c r="H40" s="7">
+        <v>35</v>
+      </c>
+      <c r="I40" s="7">
+        <f t="shared" si="1"/>
+        <v>730</v>
+      </c>
+      <c r="J40" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="K40" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L40" s="7" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B41" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C41" s="7" t="s">
+        <v>284</v>
+      </c>
+      <c r="D41" s="7" t="s">
+        <v>285</v>
+      </c>
+      <c r="E41" s="7" t="s">
+        <v>286</v>
+      </c>
+      <c r="F41" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G41" s="7">
+        <v>690</v>
+      </c>
+      <c r="H41" s="7">
+        <v>30</v>
+      </c>
+      <c r="I41" s="7">
+        <f t="shared" si="1"/>
+        <v>660</v>
+      </c>
+      <c r="J41" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="K41" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L41" s="7" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B42" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C42" s="7" t="s">
+        <v>287</v>
+      </c>
+      <c r="D42" s="7" t="s">
+        <v>288</v>
+      </c>
+      <c r="E42" s="7" t="s">
+        <v>289</v>
+      </c>
+      <c r="F42" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="G42" s="7">
+        <v>890</v>
+      </c>
+      <c r="H42" s="7">
+        <v>30</v>
+      </c>
+      <c r="I42" s="7">
+        <f t="shared" si="1"/>
+        <v>860</v>
+      </c>
+      <c r="J42" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="K42" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L42" s="7" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B43" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C43" s="5" t="s">
+        <v>290</v>
+      </c>
+      <c r="D43" s="5" t="s">
+        <v>291</v>
+      </c>
+      <c r="E43" s="5" t="s">
+        <v>292</v>
+      </c>
+      <c r="F43" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="G43" s="5">
+        <v>0</v>
+      </c>
+      <c r="H43" s="5">
+        <v>30</v>
+      </c>
+      <c r="I43" s="5">
+        <f t="shared" si="1"/>
+        <v>-30</v>
+      </c>
+      <c r="J43" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="K43" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L43" s="5" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B44" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="F44" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="G44" s="3">
+        <v>1050</v>
+      </c>
+      <c r="H44" s="3">
+        <v>0</v>
+      </c>
+      <c r="I44" s="3">
+        <f t="shared" si="1"/>
+        <v>1050</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K44" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L44" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="M44" s="3" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B45" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C45" s="7" t="s">
+        <v>294</v>
+      </c>
+      <c r="D45" s="7" t="s">
+        <v>295</v>
+      </c>
+      <c r="E45" s="7" t="s">
+        <v>296</v>
+      </c>
+      <c r="F45" s="8" t="s">
+        <v>297</v>
+      </c>
+      <c r="G45" s="7">
+        <v>695</v>
+      </c>
+      <c r="H45" s="7">
+        <v>35</v>
+      </c>
+      <c r="I45" s="7">
+        <f t="shared" si="1"/>
+        <v>660</v>
+      </c>
+      <c r="J45" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="K45" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L45" s="7" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B46" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C46" s="7" t="s">
+        <v>298</v>
+      </c>
+      <c r="D46" s="7" t="s">
+        <v>299</v>
+      </c>
+      <c r="E46" s="7" t="s">
+        <v>300</v>
+      </c>
+      <c r="F46" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="G46" s="7">
+        <v>845</v>
+      </c>
+      <c r="H46" s="7">
+        <v>25</v>
+      </c>
+      <c r="I46" s="7">
+        <f t="shared" si="1"/>
+        <v>820</v>
+      </c>
+      <c r="J46" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="K46" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L46" s="7" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B47" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C47" s="5" t="s">
+        <v>301</v>
+      </c>
+      <c r="D47" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="E47" s="5" t="s">
+        <v>303</v>
+      </c>
+      <c r="F47" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="G47" s="5">
+        <v>690</v>
+      </c>
+      <c r="H47" s="5">
+        <v>30</v>
+      </c>
+      <c r="I47" s="5">
+        <f t="shared" si="1"/>
+        <v>660</v>
+      </c>
+      <c r="J47" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="K47" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L47" s="5" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="B48" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C48" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="E48" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="F48" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="G48" s="7">
+        <v>0</v>
+      </c>
+      <c r="H48" s="7">
+        <v>30</v>
+      </c>
+      <c r="I48" s="7">
+        <f t="shared" si="1"/>
+        <v>-30</v>
+      </c>
+      <c r="J48" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="K48" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L48" s="7" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="B49" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C49" s="7" t="s">
+        <v>304</v>
+      </c>
+      <c r="E49" s="7" t="s">
+        <v>305</v>
+      </c>
+      <c r="F49" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="G49" s="7">
+        <v>0</v>
+      </c>
+      <c r="H49" s="7">
+        <v>35</v>
+      </c>
+      <c r="I49" s="7">
+        <f t="shared" si="1"/>
+        <v>-35</v>
+      </c>
+      <c r="J49" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="K49" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L49" s="7" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="F50" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="G50" s="3">
+        <v>30</v>
+      </c>
+      <c r="H50" s="3">
+        <v>30</v>
+      </c>
+      <c r="I50" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J50" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K50" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L50" s="3" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="B51" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C51" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="E51" s="7" t="s">
+        <v>309</v>
+      </c>
+      <c r="F51" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="G51" s="7">
+        <v>35</v>
+      </c>
+      <c r="H51" s="7">
+        <v>35</v>
+      </c>
+      <c r="I51" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J51" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="K51" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L51" s="7" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="F52" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="G52" s="3">
+        <v>30</v>
+      </c>
+      <c r="H52" s="3">
+        <v>30</v>
+      </c>
+      <c r="I52" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K52" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L52" s="3" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="B53" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C53" s="7" t="s">
+        <v>312</v>
+      </c>
+      <c r="E53" s="7" t="s">
+        <v>313</v>
+      </c>
+      <c r="F53" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="G53" s="7">
+        <v>0</v>
+      </c>
+      <c r="H53" s="7">
+        <v>30</v>
+      </c>
+      <c r="I53" s="7">
+        <f t="shared" si="1"/>
+        <v>-30</v>
+      </c>
+      <c r="J53" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="K53" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L53" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="M53" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:Q44"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="2" width="9.140625" customWidth="1"/>
+    <col min="3" max="3" width="45.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="95.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="9.140625" customWidth="1"/>
+    <col min="12" max="12" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B1" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>317</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>296</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>297</v>
+      </c>
+      <c r="G3" s="7">
+        <v>735</v>
+      </c>
+      <c r="H3" s="7">
+        <v>35</v>
+      </c>
+      <c r="I3" s="7">
+        <f t="shared" ref="I3:I42" si="0">G3-H3</f>
+        <v>700</v>
+      </c>
+      <c r="J3" s="7" t="s">
+        <v>318</v>
+      </c>
+      <c r="K3" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L3" s="7" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="G4" s="3">
+        <v>700</v>
+      </c>
+      <c r="H4" s="3">
+        <v>30</v>
+      </c>
+      <c r="I4" s="3">
+        <f t="shared" si="0"/>
+        <v>670</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>323</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>324</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>325</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="G5" s="7">
+        <v>760</v>
+      </c>
+      <c r="H5" s="7">
+        <v>30</v>
+      </c>
+      <c r="I5" s="7">
+        <f t="shared" si="0"/>
+        <v>730</v>
+      </c>
+      <c r="J5" s="7" t="s">
+        <v>318</v>
+      </c>
+      <c r="K5" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L5" s="7" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>326</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>327</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>328</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="G6" s="7">
+        <v>690</v>
+      </c>
+      <c r="H6" s="7">
+        <v>30</v>
+      </c>
+      <c r="I6" s="7">
+        <f t="shared" si="0"/>
+        <v>660</v>
+      </c>
+      <c r="J6" s="7" t="s">
+        <v>318</v>
+      </c>
+      <c r="K6" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L6" s="7" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>330</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>331</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="G7" s="7">
+        <v>920</v>
+      </c>
+      <c r="H7" s="7">
+        <v>30</v>
+      </c>
+      <c r="I7" s="7">
+        <f t="shared" si="0"/>
+        <v>890</v>
+      </c>
+      <c r="J7" s="7" t="s">
+        <v>318</v>
+      </c>
+      <c r="K7" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L7" s="7" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>332</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>333</v>
+      </c>
+      <c r="E8" s="9" t="s">
+        <v>334</v>
+      </c>
+      <c r="F8" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="G8" s="9">
+        <v>0</v>
+      </c>
+      <c r="H8" s="9">
+        <v>25</v>
+      </c>
+      <c r="I8" s="9">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J8" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="K8" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L8" s="9" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>335</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>336</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>337</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>338</v>
+      </c>
+      <c r="G9" s="7">
+        <v>375</v>
+      </c>
+      <c r="H9" s="7">
+        <v>25</v>
+      </c>
+      <c r="I9" s="7">
+        <f t="shared" si="0"/>
+        <v>350</v>
+      </c>
+      <c r="J9" s="7" t="s">
+        <v>318</v>
+      </c>
+      <c r="K9" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L9" s="7" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="G10" s="3">
+        <v>720</v>
+      </c>
+      <c r="H10" s="3">
+        <v>30</v>
+      </c>
+      <c r="I10" s="3">
+        <f t="shared" si="0"/>
+        <v>690</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L10" s="3" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>342</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>343</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>344</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G11" s="7">
+        <v>720</v>
+      </c>
+      <c r="H11" s="7">
+        <v>30</v>
+      </c>
+      <c r="I11" s="7">
+        <f t="shared" si="0"/>
+        <v>690</v>
+      </c>
+      <c r="J11" s="7" t="s">
+        <v>318</v>
+      </c>
+      <c r="K11" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L11" s="7" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="G12" s="3">
+        <v>730</v>
+      </c>
+      <c r="H12" s="3">
+        <v>30</v>
+      </c>
+      <c r="I12" s="3">
+        <f t="shared" si="0"/>
+        <v>700</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L12" s="3" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="G13" s="3">
+        <v>890</v>
+      </c>
+      <c r="H13" s="3">
+        <v>30</v>
+      </c>
+      <c r="I13" s="3">
+        <f t="shared" si="0"/>
+        <v>860</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K13" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L13" s="3" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>351</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>352</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>353</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="G14" s="7">
+        <v>1775</v>
+      </c>
+      <c r="H14" s="7">
+        <v>35</v>
+      </c>
+      <c r="I14" s="7">
+        <f t="shared" si="0"/>
+        <v>1740</v>
+      </c>
+      <c r="J14" s="7" t="s">
+        <v>318</v>
+      </c>
+      <c r="K14" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L14" s="7" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>354</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>355</v>
+      </c>
+      <c r="E15" s="9" t="s">
+        <v>356</v>
+      </c>
+      <c r="F15" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="G15" s="9">
+        <v>885</v>
+      </c>
+      <c r="H15" s="9">
+        <v>25</v>
+      </c>
+      <c r="I15" s="9">
+        <f t="shared" si="0"/>
+        <v>860</v>
+      </c>
+      <c r="J15" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="K15" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L15" s="9" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>357</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>358</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>359</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="G16" s="5">
+        <v>690</v>
+      </c>
+      <c r="H16" s="5">
+        <v>30</v>
+      </c>
+      <c r="I16" s="5">
+        <f t="shared" si="0"/>
+        <v>660</v>
+      </c>
+      <c r="J16" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="K16" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L16" s="5" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="17" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="G17" s="3">
+        <v>685</v>
+      </c>
+      <c r="H17" s="3">
+        <v>25</v>
+      </c>
+      <c r="I17" s="3">
+        <f t="shared" si="0"/>
+        <v>660</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L17" s="3" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="18" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="G18" s="3">
+        <v>0</v>
+      </c>
+      <c r="H18" s="3">
+        <v>25</v>
+      </c>
+      <c r="I18" s="3">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L18" s="3" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="19" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="G19" s="3">
+        <v>870</v>
+      </c>
+      <c r="H19" s="3">
+        <v>30</v>
+      </c>
+      <c r="I19" s="3">
+        <f t="shared" si="0"/>
+        <v>840</v>
+      </c>
+      <c r="J19" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K19" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L19" s="3" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="20" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="G20" s="3">
+        <v>2370</v>
+      </c>
+      <c r="H20" s="3">
+        <v>25</v>
+      </c>
+      <c r="I20" s="3">
+        <f t="shared" si="0"/>
+        <v>2345</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L20" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="M20" s="3" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="21" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G21" s="3">
+        <v>910</v>
+      </c>
+      <c r="H21" s="3">
+        <v>20</v>
+      </c>
+      <c r="I21" s="3">
+        <f t="shared" si="0"/>
+        <v>890</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K21" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L21" s="3" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="22" spans="2:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C22" s="9" t="s">
+        <v>376</v>
+      </c>
+      <c r="D22" s="9" t="s">
+        <v>377</v>
+      </c>
+      <c r="E22" s="9" t="s">
+        <v>378</v>
+      </c>
+      <c r="F22" s="10" t="s">
+        <v>379</v>
+      </c>
+      <c r="G22" s="9">
+        <v>375</v>
+      </c>
+      <c r="H22" s="9">
+        <v>25</v>
+      </c>
+      <c r="I22" s="9">
+        <f t="shared" si="0"/>
+        <v>350</v>
+      </c>
+      <c r="J22" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="K22" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L22" s="9" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="23" spans="2:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>380</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>381</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>382</v>
+      </c>
+      <c r="F23" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="G23" s="7">
+        <v>720</v>
+      </c>
+      <c r="H23" s="7">
+        <v>30</v>
+      </c>
+      <c r="I23" s="7">
+        <f t="shared" si="0"/>
+        <v>690</v>
+      </c>
+      <c r="J23" s="7" t="s">
+        <v>318</v>
+      </c>
+      <c r="K23" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L23" s="7" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="24" spans="2:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>383</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>384</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>385</v>
+      </c>
+      <c r="F24" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="G24" s="7">
+        <v>690</v>
+      </c>
+      <c r="H24" s="7">
+        <v>30</v>
+      </c>
+      <c r="I24" s="7">
+        <f t="shared" si="0"/>
+        <v>660</v>
+      </c>
+      <c r="J24" s="7" t="s">
+        <v>318</v>
+      </c>
+      <c r="K24" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L24" s="7" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="25" spans="2:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>386</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>387</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>388</v>
+      </c>
+      <c r="F25" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="G25" s="7">
+        <v>0</v>
+      </c>
+      <c r="H25" s="7">
+        <v>30</v>
+      </c>
+      <c r="I25" s="7">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J25" s="7" t="s">
+        <v>318</v>
+      </c>
+      <c r="K25" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L25" s="7" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="26" spans="2:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C26" s="9" t="s">
+        <v>389</v>
+      </c>
+      <c r="D26" s="9" t="s">
+        <v>390</v>
+      </c>
+      <c r="E26" s="9" t="s">
+        <v>391</v>
+      </c>
+      <c r="F26" s="10" t="s">
+        <v>135</v>
+      </c>
+      <c r="G26" s="9">
+        <v>815</v>
+      </c>
+      <c r="H26" s="9">
+        <v>25</v>
+      </c>
+      <c r="I26" s="9">
+        <f t="shared" si="0"/>
+        <v>790</v>
+      </c>
+      <c r="J26" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="K26" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L26" s="9" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="27" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="G27" s="3">
+        <v>0</v>
+      </c>
+      <c r="H27" s="3">
+        <v>30</v>
+      </c>
+      <c r="I27" s="3">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K27" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L27" s="3" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="28" spans="2:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C28" s="9" t="s">
+        <v>395</v>
+      </c>
+      <c r="D28" s="9" t="s">
+        <v>396</v>
+      </c>
+      <c r="E28" s="9" t="s">
+        <v>397</v>
+      </c>
+      <c r="F28" s="10" t="s">
+        <v>379</v>
+      </c>
+      <c r="G28" s="9">
+        <v>775</v>
+      </c>
+      <c r="H28" s="9">
+        <v>25</v>
+      </c>
+      <c r="I28" s="9">
+        <f t="shared" si="0"/>
+        <v>750</v>
+      </c>
+      <c r="J28" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="K28" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L28" s="9" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="29" spans="2:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>398</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>399</v>
+      </c>
+      <c r="E29" s="7" t="s">
+        <v>400</v>
+      </c>
+      <c r="F29" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="G29" s="7">
+        <v>820</v>
+      </c>
+      <c r="H29" s="7">
+        <v>30</v>
+      </c>
+      <c r="I29" s="7">
+        <f t="shared" si="0"/>
+        <v>790</v>
+      </c>
+      <c r="J29" s="7" t="s">
+        <v>318</v>
+      </c>
+      <c r="K29" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L29" s="7" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="30" spans="2:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C30" s="7" t="s">
+        <v>401</v>
+      </c>
+      <c r="D30" s="7" t="s">
+        <v>402</v>
+      </c>
+      <c r="E30" s="7" t="s">
+        <v>403</v>
+      </c>
+      <c r="F30" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G30" s="7">
+        <v>690</v>
+      </c>
+      <c r="H30" s="7">
+        <v>30</v>
+      </c>
+      <c r="I30" s="7">
+        <f t="shared" si="0"/>
+        <v>660</v>
+      </c>
+      <c r="J30" s="7" t="s">
+        <v>318</v>
+      </c>
+      <c r="K30" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L30" s="7" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="31" spans="2:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B31" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C31" s="9" t="s">
+        <v>404</v>
+      </c>
+      <c r="D31" s="9" t="s">
+        <v>405</v>
+      </c>
+      <c r="E31" s="9" t="s">
+        <v>406</v>
+      </c>
+      <c r="F31" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="G31" s="9">
+        <v>885</v>
+      </c>
+      <c r="H31" s="9">
+        <v>25</v>
+      </c>
+      <c r="I31" s="9">
+        <f t="shared" si="0"/>
+        <v>860</v>
+      </c>
+      <c r="J31" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="K31" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L31" s="9" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="32" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B32" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G32" s="3">
+        <v>680</v>
+      </c>
+      <c r="H32" s="3">
+        <v>20</v>
+      </c>
+      <c r="I32" s="3">
+        <f t="shared" si="0"/>
+        <v>660</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K32" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L32" s="3" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="33" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B33" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="F33" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G33" s="3">
+        <v>840</v>
+      </c>
+      <c r="H33" s="3">
+        <v>20</v>
+      </c>
+      <c r="I33" s="3">
+        <f t="shared" si="0"/>
+        <v>820</v>
+      </c>
+      <c r="J33" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K33" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L33" s="3" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="34" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B34" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="F34" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="G34" s="3">
+        <v>0</v>
+      </c>
+      <c r="H34" s="3">
+        <v>25</v>
+      </c>
+      <c r="I34" s="3">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J34" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K34" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L34" s="3" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="35" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B35" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="F35" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="G35" s="3">
+        <v>0</v>
+      </c>
+      <c r="H35" s="3">
+        <v>40</v>
+      </c>
+      <c r="I35" s="3">
+        <f t="shared" si="0"/>
+        <v>-40</v>
+      </c>
+      <c r="J35" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K35" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L35" s="3" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="36" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B36" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C36" s="9" t="s">
+        <v>419</v>
+      </c>
+      <c r="D36" s="9" t="s">
+        <v>420</v>
+      </c>
+      <c r="E36" s="9" t="s">
+        <v>421</v>
+      </c>
+      <c r="F36" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="G36" s="9">
+        <v>680</v>
+      </c>
+      <c r="H36" s="9">
+        <v>20</v>
+      </c>
+      <c r="I36" s="9">
+        <f t="shared" si="0"/>
+        <v>660</v>
+      </c>
+      <c r="J36" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="K36" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L36" s="9" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="37" spans="1:17" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B37" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C37" s="7" t="s">
+        <v>422</v>
+      </c>
+      <c r="D37" s="7" t="s">
+        <v>423</v>
+      </c>
+      <c r="E37" s="7" t="s">
+        <v>424</v>
+      </c>
+      <c r="F37" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="G37" s="7">
+        <v>715</v>
+      </c>
+      <c r="H37" s="7">
+        <v>25</v>
+      </c>
+      <c r="I37" s="7">
+        <f t="shared" si="0"/>
+        <v>690</v>
+      </c>
+      <c r="J37" s="7" t="s">
+        <v>318</v>
+      </c>
+      <c r="K37" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L37" s="7" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="38" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B38" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C38" s="9" t="s">
+        <v>425</v>
+      </c>
+      <c r="D38" s="9" t="s">
+        <v>426</v>
+      </c>
+      <c r="E38" s="9" t="s">
+        <v>427</v>
+      </c>
+      <c r="F38" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="G38" s="9">
+        <v>0</v>
+      </c>
+      <c r="H38" s="9">
+        <v>25</v>
+      </c>
+      <c r="I38" s="9">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J38" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="K38" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L38" s="9" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="39" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="B39" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C39" s="9" t="s">
+        <v>428</v>
+      </c>
+      <c r="E39" s="9" t="s">
+        <v>429</v>
+      </c>
+      <c r="F39" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="G39" s="9">
+        <v>30</v>
+      </c>
+      <c r="H39" s="9">
+        <v>30</v>
+      </c>
+      <c r="I39" s="9">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J39" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="K39" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L39" s="9" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="40" spans="1:17" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="B40" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C40" s="7" t="s">
+        <v>430</v>
+      </c>
+      <c r="E40" s="7" t="s">
+        <v>431</v>
+      </c>
+      <c r="F40" s="8" t="s">
+        <v>218</v>
+      </c>
+      <c r="G40" s="7">
+        <v>30</v>
+      </c>
+      <c r="H40" s="7">
+        <v>30</v>
+      </c>
+      <c r="I40" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J40" s="7" t="s">
+        <v>318</v>
+      </c>
+      <c r="K40" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L40" s="7" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="41" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C41" s="5" t="s">
+        <v>432</v>
+      </c>
+      <c r="E41" s="5" t="s">
+        <v>433</v>
+      </c>
+      <c r="F41" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="G41" s="5">
+        <v>35</v>
+      </c>
+      <c r="H41" s="5">
+        <v>35</v>
+      </c>
+      <c r="I41" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J41" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="K41" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L41" s="5" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="42" spans="1:17" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="B42" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C42" s="7" t="s">
+        <v>434</v>
+      </c>
+      <c r="E42" s="7" t="s">
+        <v>435</v>
+      </c>
+      <c r="F42" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G42" s="7">
+        <v>40</v>
+      </c>
+      <c r="H42" s="7">
+        <v>40</v>
+      </c>
+      <c r="I42" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J42" s="7" t="s">
+        <v>318</v>
+      </c>
+      <c r="K42" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L42" s="7" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="43" spans="1:17" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B43" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="C43" s="11" t="s">
+        <v>436</v>
+      </c>
+      <c r="D43" s="11" t="s">
+        <v>437</v>
+      </c>
+      <c r="E43" s="11" t="s">
+        <v>438</v>
+      </c>
+      <c r="F43" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="G43" s="11">
+        <v>370</v>
+      </c>
+      <c r="H43" s="11">
+        <v>20</v>
+      </c>
+      <c r="I43" s="11">
+        <v>350</v>
+      </c>
+      <c r="J43" s="11" t="s">
+        <v>439</v>
+      </c>
+      <c r="K43" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="L43" s="11" t="s">
+        <v>440</v>
+      </c>
+      <c r="M43" s="11" t="s">
+        <v>441</v>
+      </c>
+      <c r="N43" s="11" t="s">
+        <v>442</v>
+      </c>
+      <c r="O43" s="11" t="s">
+        <v>442</v>
+      </c>
+      <c r="P43" s="11" t="s">
+        <v>443</v>
+      </c>
+      <c r="Q43" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:17" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B44" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="C44" s="11" t="s">
+        <v>142</v>
+      </c>
+      <c r="D44" s="11" t="s">
+        <v>143</v>
+      </c>
+      <c r="E44" s="11" t="s">
+        <v>144</v>
+      </c>
+      <c r="F44" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="G44" s="11">
+        <v>650</v>
+      </c>
+      <c r="H44" s="11">
+        <v>30</v>
+      </c>
+      <c r="I44" s="11">
+        <v>620</v>
+      </c>
+      <c r="J44" s="11" t="s">
+        <v>439</v>
+      </c>
+      <c r="K44" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="L44" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="M44" s="11" t="s">
+        <v>441</v>
+      </c>
+      <c r="N44" s="11" t="s">
+        <v>442</v>
+      </c>
+      <c r="O44" s="11" t="s">
+        <v>442</v>
+      </c>
+      <c r="P44" s="11" t="s">
+        <v>443</v>
+      </c>
+      <c r="Q44" s="11">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A1:Q55"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="12.7109375" customWidth="1"/>
+    <col min="2" max="2" width="17.7109375" customWidth="1"/>
+    <col min="3" max="3" width="34.42578125" customWidth="1"/>
+    <col min="4" max="4" width="9.85546875" customWidth="1"/>
+    <col min="5" max="5" width="61.85546875" customWidth="1"/>
+    <col min="6" max="6" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.5703125" customWidth="1"/>
+    <col min="9" max="9" width="10.5703125" customWidth="1"/>
+    <col min="10" max="10" width="9.7109375" customWidth="1"/>
+    <col min="11" max="11" width="10.85546875" customWidth="1"/>
+    <col min="12" max="12" width="10.42578125" customWidth="1"/>
+    <col min="13" max="13" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.7109375" customWidth="1"/>
+    <col min="15" max="15" width="13" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="7" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B1" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>446</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>447</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>448</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="G3" s="12">
+        <v>2390</v>
+      </c>
+      <c r="H3" s="12">
+        <v>30</v>
+      </c>
+      <c r="I3" s="12">
+        <f t="shared" ref="I3:I54" si="0">G3-H3</f>
+        <v>2360</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="Q3" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>450</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>451</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>545</v>
+      </c>
+      <c r="F4" s="8">
+        <v>7</v>
+      </c>
+      <c r="G4" s="13">
+        <v>470</v>
+      </c>
+      <c r="H4" s="13">
+        <v>30</v>
+      </c>
+      <c r="I4" s="13">
+        <f t="shared" si="0"/>
+        <v>440</v>
+      </c>
+      <c r="J4" s="7" t="s">
+        <v>452</v>
+      </c>
+      <c r="K4" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L4" s="7" t="s">
+        <v>449</v>
+      </c>
+      <c r="Q4" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>453</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>454</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>546</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="G5" s="12">
+        <v>1710</v>
+      </c>
+      <c r="H5" s="12">
+        <v>30</v>
+      </c>
+      <c r="I5" s="12">
+        <f t="shared" si="0"/>
+        <v>1680</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="Q5" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>455</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>547</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>548</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G6" s="13">
+        <v>820</v>
+      </c>
+      <c r="H6" s="13">
+        <v>30</v>
+      </c>
+      <c r="I6" s="13">
+        <f t="shared" si="0"/>
+        <v>790</v>
+      </c>
+      <c r="J6" s="7" t="s">
+        <v>452</v>
+      </c>
+      <c r="K6" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L6" s="7" t="s">
+        <v>449</v>
+      </c>
+      <c r="Q6" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>456</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>457</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>458</v>
+      </c>
+      <c r="F7" s="8">
+        <v>8</v>
+      </c>
+      <c r="G7" s="13">
+        <v>0</v>
+      </c>
+      <c r="H7" s="13">
+        <v>25</v>
+      </c>
+      <c r="I7" s="13">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J7" s="7" t="s">
+        <v>452</v>
+      </c>
+      <c r="K7" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L7" s="7" t="s">
+        <v>449</v>
+      </c>
+      <c r="Q7" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>549</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>459</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>550</v>
+      </c>
+      <c r="F8" s="8">
+        <v>6</v>
+      </c>
+      <c r="G8" s="13">
+        <v>1515</v>
+      </c>
+      <c r="H8" s="13">
+        <v>25</v>
+      </c>
+      <c r="I8" s="13">
+        <f t="shared" si="0"/>
+        <v>1490</v>
+      </c>
+      <c r="J8" s="7" t="s">
+        <v>452</v>
+      </c>
+      <c r="K8" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L8" s="7" t="s">
+        <v>449</v>
+      </c>
+      <c r="Q8" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>460</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>461</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>551</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G9" s="13">
+        <v>890</v>
+      </c>
+      <c r="H9" s="13">
+        <v>30</v>
+      </c>
+      <c r="I9" s="13">
+        <f t="shared" si="0"/>
+        <v>860</v>
+      </c>
+      <c r="J9" s="7" t="s">
+        <v>452</v>
+      </c>
+      <c r="K9" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L9" s="7" t="s">
+        <v>449</v>
+      </c>
+      <c r="Q9" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>462</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>463</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>464</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G10" s="13">
+        <v>470</v>
+      </c>
+      <c r="H10" s="13">
+        <v>30</v>
+      </c>
+      <c r="I10" s="13">
+        <f t="shared" si="0"/>
+        <v>440</v>
+      </c>
+      <c r="J10" s="7" t="s">
+        <v>452</v>
+      </c>
+      <c r="K10" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L10" s="7" t="s">
+        <v>449</v>
+      </c>
+      <c r="Q10" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>465</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>466</v>
+      </c>
+      <c r="E11" s="9" t="s">
+        <v>467</v>
+      </c>
+      <c r="F11" s="10">
+        <v>10</v>
+      </c>
+      <c r="G11" s="14">
+        <v>1505</v>
+      </c>
+      <c r="H11" s="14">
+        <v>25</v>
+      </c>
+      <c r="I11" s="14">
+        <f t="shared" si="0"/>
+        <v>1480</v>
+      </c>
+      <c r="J11" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="K11" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L11" s="9" t="s">
+        <v>449</v>
+      </c>
+      <c r="Q11" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>468</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>469</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>552</v>
+      </c>
+      <c r="F12" s="10">
+        <v>4</v>
+      </c>
+      <c r="G12" s="14">
+        <v>815</v>
+      </c>
+      <c r="H12" s="14">
+        <v>25</v>
+      </c>
+      <c r="I12" s="14">
+        <f t="shared" si="0"/>
+        <v>790</v>
+      </c>
+      <c r="J12" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="K12" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L12" s="9" t="s">
+        <v>449</v>
+      </c>
+      <c r="Q12" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>470</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>553</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="G13" s="12">
+        <v>1510</v>
+      </c>
+      <c r="H13" s="12">
+        <v>30</v>
+      </c>
+      <c r="I13" s="12">
+        <f t="shared" si="0"/>
+        <v>1480</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K13" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L13" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="Q13" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>472</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>473</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>474</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G14" s="13">
+        <v>920</v>
+      </c>
+      <c r="H14" s="13">
+        <v>30</v>
+      </c>
+      <c r="I14" s="13">
+        <f t="shared" si="0"/>
+        <v>890</v>
+      </c>
+      <c r="J14" s="7" t="s">
+        <v>452</v>
+      </c>
+      <c r="K14" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L14" s="7" t="s">
+        <v>449</v>
+      </c>
+      <c r="Q14" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>475</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G15" s="12">
+        <v>680</v>
+      </c>
+      <c r="H15" s="12">
+        <v>20</v>
+      </c>
+      <c r="I15" s="12">
+        <f t="shared" si="0"/>
+        <v>660</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L15" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="Q15" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>476</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>477</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>554</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="G16" s="12">
+        <v>1020</v>
+      </c>
+      <c r="H16" s="12">
+        <v>30</v>
+      </c>
+      <c r="I16" s="12">
+        <f t="shared" si="0"/>
+        <v>990</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K16" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L16" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="Q16" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="2:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>555</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>478</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>479</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="G17" s="12">
+        <v>0</v>
+      </c>
+      <c r="H17" s="12">
+        <v>30</v>
+      </c>
+      <c r="I17" s="12">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L17" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="Q17" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="2:17" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>556</v>
+      </c>
+      <c r="D18" s="9" t="s">
+        <v>480</v>
+      </c>
+      <c r="E18" s="9" t="s">
+        <v>557</v>
+      </c>
+      <c r="F18" s="10">
+        <v>8</v>
+      </c>
+      <c r="G18" s="14">
+        <v>820</v>
+      </c>
+      <c r="H18" s="14">
+        <v>30</v>
+      </c>
+      <c r="I18" s="14">
+        <f t="shared" si="0"/>
+        <v>790</v>
+      </c>
+      <c r="J18" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="K18" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L18" s="9" t="s">
+        <v>449</v>
+      </c>
+      <c r="Q18" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="2:17" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>481</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>482</v>
+      </c>
+      <c r="E19" s="9" t="s">
+        <v>558</v>
+      </c>
+      <c r="F19" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="G19" s="14">
+        <v>845</v>
+      </c>
+      <c r="H19" s="14">
+        <v>25</v>
+      </c>
+      <c r="I19" s="14">
+        <f t="shared" si="0"/>
+        <v>820</v>
+      </c>
+      <c r="J19" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="K19" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L19" s="9" t="s">
+        <v>449</v>
+      </c>
+      <c r="Q19" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="2:17" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>483</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>484</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>559</v>
+      </c>
+      <c r="F20" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="G20" s="13">
+        <v>695</v>
+      </c>
+      <c r="H20" s="13">
+        <v>25</v>
+      </c>
+      <c r="I20" s="13">
+        <f t="shared" si="0"/>
+        <v>670</v>
+      </c>
+      <c r="J20" s="7" t="s">
+        <v>452</v>
+      </c>
+      <c r="K20" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L20" s="7" t="s">
+        <v>449</v>
+      </c>
+      <c r="Q20" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="2:17" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>485</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>486</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>560</v>
+      </c>
+      <c r="F21" s="8">
+        <v>7</v>
+      </c>
+      <c r="G21" s="13">
+        <v>700</v>
+      </c>
+      <c r="H21" s="13">
+        <v>30</v>
+      </c>
+      <c r="I21" s="13">
+        <f t="shared" si="0"/>
+        <v>670</v>
+      </c>
+      <c r="J21" s="7" t="s">
+        <v>452</v>
+      </c>
+      <c r="K21" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L21" s="7" t="s">
+        <v>449</v>
+      </c>
+      <c r="Q21" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="2:17" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C22" s="9" t="s">
+        <v>487</v>
+      </c>
+      <c r="D22" s="9" t="s">
+        <v>488</v>
+      </c>
+      <c r="E22" s="9" t="s">
+        <v>561</v>
+      </c>
+      <c r="F22" s="10">
+        <v>4</v>
+      </c>
+      <c r="G22" s="14">
+        <v>735</v>
+      </c>
+      <c r="H22" s="14">
+        <v>25</v>
+      </c>
+      <c r="I22" s="14">
+        <f t="shared" si="0"/>
+        <v>710</v>
+      </c>
+      <c r="J22" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="K22" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L22" s="9" t="s">
+        <v>449</v>
+      </c>
+      <c r="Q22" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="2:17" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C23" s="9" t="s">
+        <v>489</v>
+      </c>
+      <c r="D23" s="9" t="s">
+        <v>490</v>
+      </c>
+      <c r="E23" s="9" t="s">
+        <v>562</v>
+      </c>
+      <c r="F23" s="10">
+        <v>4</v>
+      </c>
+      <c r="G23" s="14">
+        <v>75</v>
+      </c>
+      <c r="H23" s="14">
+        <v>25</v>
+      </c>
+      <c r="I23" s="14">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+      <c r="J23" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="K23" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L23" s="9" t="s">
+        <v>449</v>
+      </c>
+      <c r="M23" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="Q23" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="2:17" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>491</v>
+      </c>
+      <c r="D24" s="9" t="s">
+        <v>492</v>
+      </c>
+      <c r="E24" s="9" t="s">
+        <v>493</v>
+      </c>
+      <c r="F24" s="10">
+        <v>4</v>
+      </c>
+      <c r="G24" s="14">
+        <v>715</v>
+      </c>
+      <c r="H24" s="14">
+        <v>25</v>
+      </c>
+      <c r="I24" s="14">
+        <f t="shared" si="0"/>
+        <v>690</v>
+      </c>
+      <c r="J24" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="K24" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L24" s="9" t="s">
+        <v>449</v>
+      </c>
+      <c r="Q24" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="2:17" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>494</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>495</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>563</v>
+      </c>
+      <c r="F25" s="8">
+        <v>7</v>
+      </c>
+      <c r="G25" s="13">
+        <v>0</v>
+      </c>
+      <c r="H25" s="13">
+        <v>30</v>
+      </c>
+      <c r="I25" s="13">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J25" s="7" t="s">
+        <v>452</v>
+      </c>
+      <c r="K25" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L25" s="7" t="s">
+        <v>449</v>
+      </c>
+      <c r="Q25" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="2:17" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C26" s="9" t="s">
+        <v>496</v>
+      </c>
+      <c r="D26" s="9" t="s">
+        <v>497</v>
+      </c>
+      <c r="E26" s="9" t="s">
+        <v>564</v>
+      </c>
+      <c r="F26" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="G26" s="14">
+        <v>685</v>
+      </c>
+      <c r="H26" s="14">
+        <v>25</v>
+      </c>
+      <c r="I26" s="14">
+        <f t="shared" si="0"/>
+        <v>660</v>
+      </c>
+      <c r="J26" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="K26" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L26" s="9" t="s">
+        <v>449</v>
+      </c>
+      <c r="Q26" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="2:17" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>565</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>498</v>
+      </c>
+      <c r="E27" s="7" t="s">
+        <v>566</v>
+      </c>
+      <c r="F27" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G27" s="13">
+        <v>1020</v>
+      </c>
+      <c r="H27" s="13">
+        <v>30</v>
+      </c>
+      <c r="I27" s="13">
+        <f t="shared" si="0"/>
+        <v>990</v>
+      </c>
+      <c r="J27" s="7" t="s">
+        <v>452</v>
+      </c>
+      <c r="K27" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L27" s="7" t="s">
+        <v>449</v>
+      </c>
+      <c r="Q27" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="2:17" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C28" s="9" t="s">
+        <v>499</v>
+      </c>
+      <c r="D28" s="9" t="s">
+        <v>500</v>
+      </c>
+      <c r="E28" s="9" t="s">
+        <v>501</v>
+      </c>
+      <c r="F28" s="10">
+        <v>5</v>
+      </c>
+      <c r="G28" s="14">
+        <v>1185</v>
+      </c>
+      <c r="H28" s="14">
+        <v>25</v>
+      </c>
+      <c r="I28" s="14">
+        <f t="shared" si="0"/>
+        <v>1160</v>
+      </c>
+      <c r="J28" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="K28" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L28" s="9" t="s">
+        <v>449</v>
+      </c>
+      <c r="Q28" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="2:17" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C29" s="9" t="s">
+        <v>502</v>
+      </c>
+      <c r="D29" s="9" t="s">
+        <v>503</v>
+      </c>
+      <c r="E29" s="9" t="s">
+        <v>504</v>
+      </c>
+      <c r="F29" s="10">
+        <v>1</v>
+      </c>
+      <c r="G29" s="14">
+        <v>745</v>
+      </c>
+      <c r="H29" s="14">
+        <v>25</v>
+      </c>
+      <c r="I29" s="14">
+        <f t="shared" si="0"/>
+        <v>720</v>
+      </c>
+      <c r="J29" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="K29" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L29" s="9" t="s">
+        <v>449</v>
+      </c>
+      <c r="Q29" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="2:17" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C30" s="9" t="s">
+        <v>505</v>
+      </c>
+      <c r="D30" s="9" t="s">
+        <v>506</v>
+      </c>
+      <c r="E30" s="9" t="s">
+        <v>507</v>
+      </c>
+      <c r="F30" s="10">
+        <v>10</v>
+      </c>
+      <c r="G30" s="14">
+        <v>1255</v>
+      </c>
+      <c r="H30" s="14">
+        <v>25</v>
+      </c>
+      <c r="I30" s="14">
+        <f t="shared" si="0"/>
+        <v>1230</v>
+      </c>
+      <c r="J30" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="K30" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L30" s="9" t="s">
+        <v>449</v>
+      </c>
+      <c r="Q30" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="2:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B31" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>508</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>509</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>567</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="G31" s="12">
+        <v>0</v>
+      </c>
+      <c r="H31" s="12">
+        <v>25</v>
+      </c>
+      <c r="I31" s="12">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J31" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K31" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L31" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="Q31" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="2:17" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B32" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C32" s="9" t="s">
+        <v>436</v>
+      </c>
+      <c r="D32" s="9" t="s">
+        <v>437</v>
+      </c>
+      <c r="E32" s="9" t="s">
+        <v>438</v>
+      </c>
+      <c r="F32" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="G32" s="14">
+        <v>370</v>
+      </c>
+      <c r="H32" s="14">
+        <v>20</v>
+      </c>
+      <c r="I32" s="14">
+        <f t="shared" si="0"/>
+        <v>350</v>
+      </c>
+      <c r="J32" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="K32" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L32" s="9" t="s">
+        <v>449</v>
+      </c>
+      <c r="Q32" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B33" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C33" s="9" t="s">
+        <v>568</v>
+      </c>
+      <c r="D33" s="9" t="s">
+        <v>510</v>
+      </c>
+      <c r="E33" s="9" t="s">
+        <v>569</v>
+      </c>
+      <c r="F33" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="G33" s="14">
+        <v>915</v>
+      </c>
+      <c r="H33" s="14">
+        <v>25</v>
+      </c>
+      <c r="I33" s="14">
+        <f t="shared" si="0"/>
+        <v>890</v>
+      </c>
+      <c r="J33" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="K33" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L33" s="9" t="s">
+        <v>449</v>
+      </c>
+      <c r="Q33" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B34" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C34" s="9" t="s">
+        <v>511</v>
+      </c>
+      <c r="D34" s="9" t="s">
+        <v>512</v>
+      </c>
+      <c r="E34" s="9" t="s">
+        <v>513</v>
+      </c>
+      <c r="F34" s="10">
+        <v>1</v>
+      </c>
+      <c r="G34" s="14">
+        <v>1635</v>
+      </c>
+      <c r="H34" s="14">
+        <v>25</v>
+      </c>
+      <c r="I34" s="14">
+        <f t="shared" si="0"/>
+        <v>1610</v>
+      </c>
+      <c r="J34" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="K34" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L34" s="9" t="s">
+        <v>449</v>
+      </c>
+      <c r="Q34" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:17" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B35" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>514</v>
+      </c>
+      <c r="D35" s="7" t="s">
+        <v>515</v>
+      </c>
+      <c r="E35" s="7" t="s">
+        <v>570</v>
+      </c>
+      <c r="F35" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="G35" s="13">
+        <v>475</v>
+      </c>
+      <c r="H35" s="13">
+        <v>35</v>
+      </c>
+      <c r="I35" s="13">
+        <f t="shared" si="0"/>
+        <v>440</v>
+      </c>
+      <c r="J35" s="7" t="s">
+        <v>452</v>
+      </c>
+      <c r="K35" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L35" s="7" t="s">
+        <v>449</v>
+      </c>
+      <c r="Q35" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B36" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>516</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>517</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>518</v>
+      </c>
+      <c r="F36" s="4">
+        <v>2</v>
+      </c>
+      <c r="G36" s="12">
+        <v>820</v>
+      </c>
+      <c r="H36" s="12">
+        <v>30</v>
+      </c>
+      <c r="I36" s="12">
+        <f t="shared" si="0"/>
+        <v>790</v>
+      </c>
+      <c r="J36" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K36" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L36" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="Q36" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B37" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C37" s="9" t="s">
+        <v>519</v>
+      </c>
+      <c r="D37" s="9" t="s">
+        <v>520</v>
+      </c>
+      <c r="E37" s="9" t="s">
+        <v>571</v>
+      </c>
+      <c r="F37" s="10">
+        <v>10</v>
+      </c>
+      <c r="G37" s="14">
+        <v>465</v>
+      </c>
+      <c r="H37" s="14">
+        <v>25</v>
+      </c>
+      <c r="I37" s="14">
+        <f t="shared" si="0"/>
+        <v>440</v>
+      </c>
+      <c r="J37" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="K37" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L37" s="9" t="s">
+        <v>449</v>
+      </c>
+      <c r="Q37" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:17" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B38" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C38" s="7" t="s">
+        <v>521</v>
+      </c>
+      <c r="D38" s="7" t="s">
+        <v>522</v>
+      </c>
+      <c r="E38" s="7" t="s">
+        <v>523</v>
+      </c>
+      <c r="F38" s="8">
+        <v>6</v>
+      </c>
+      <c r="G38" s="13">
+        <v>2220</v>
+      </c>
+      <c r="H38" s="13">
+        <v>30</v>
+      </c>
+      <c r="I38" s="13">
+        <f t="shared" si="0"/>
+        <v>2190</v>
+      </c>
+      <c r="J38" s="7" t="s">
+        <v>452</v>
+      </c>
+      <c r="K38" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L38" s="7" t="s">
+        <v>449</v>
+      </c>
+      <c r="M38" s="7" t="s">
+        <v>372</v>
+      </c>
+      <c r="Q38" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B39" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>524</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>572</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>573</v>
+      </c>
+      <c r="F39" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="G39" s="12">
+        <v>0</v>
+      </c>
+      <c r="H39" s="12">
+        <v>25</v>
+      </c>
+      <c r="I39" s="12">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J39" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K39" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L39" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="Q39" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B40" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C40" s="9" t="s">
+        <v>525</v>
+      </c>
+      <c r="D40" s="9" t="s">
+        <v>526</v>
+      </c>
+      <c r="E40" s="9" t="s">
+        <v>527</v>
+      </c>
+      <c r="F40" s="10">
+        <v>4</v>
+      </c>
+      <c r="G40" s="14">
+        <v>0</v>
+      </c>
+      <c r="H40" s="14">
+        <v>25</v>
+      </c>
+      <c r="I40" s="14">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J40" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="K40" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L40" s="9" t="s">
+        <v>449</v>
+      </c>
+      <c r="Q40" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:17" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B41" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C41" s="7" t="s">
+        <v>574</v>
+      </c>
+      <c r="D41" s="7" t="s">
+        <v>575</v>
+      </c>
+      <c r="E41" s="7" t="s">
+        <v>403</v>
+      </c>
+      <c r="F41" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G41" s="13">
+        <v>720</v>
+      </c>
+      <c r="H41" s="13">
+        <v>30</v>
+      </c>
+      <c r="I41" s="13">
+        <f t="shared" si="0"/>
+        <v>690</v>
+      </c>
+      <c r="J41" s="7" t="s">
+        <v>452</v>
+      </c>
+      <c r="K41" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L41" s="7" t="s">
+        <v>449</v>
+      </c>
+      <c r="Q41" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:17" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B42" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C42" s="7" t="s">
+        <v>528</v>
+      </c>
+      <c r="D42" s="7" t="s">
+        <v>529</v>
+      </c>
+      <c r="E42" s="7" t="s">
+        <v>530</v>
+      </c>
+      <c r="F42" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G42" s="13">
+        <v>750</v>
+      </c>
+      <c r="H42" s="13">
+        <v>30</v>
+      </c>
+      <c r="I42" s="13">
+        <f t="shared" si="0"/>
+        <v>720</v>
+      </c>
+      <c r="J42" s="7" t="s">
+        <v>452</v>
+      </c>
+      <c r="K42" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L42" s="7" t="s">
+        <v>449</v>
+      </c>
+      <c r="Q42" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:17" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B43" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C43" s="7" t="s">
+        <v>531</v>
+      </c>
+      <c r="D43" s="7" t="s">
+        <v>576</v>
+      </c>
+      <c r="E43" s="7" t="s">
+        <v>532</v>
+      </c>
+      <c r="F43" s="8">
+        <v>8</v>
+      </c>
+      <c r="G43" s="13">
+        <v>390</v>
+      </c>
+      <c r="H43" s="13">
+        <v>30</v>
+      </c>
+      <c r="I43" s="13">
+        <f t="shared" si="0"/>
+        <v>360</v>
+      </c>
+      <c r="J43" s="7" t="s">
+        <v>452</v>
+      </c>
+      <c r="K43" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L43" s="7" t="s">
+        <v>449</v>
+      </c>
+      <c r="Q43" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B44" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>533</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>534</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>535</v>
+      </c>
+      <c r="F44" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="G44" s="12">
+        <v>1020</v>
+      </c>
+      <c r="H44" s="12">
+        <v>30</v>
+      </c>
+      <c r="I44" s="12">
+        <f t="shared" si="0"/>
+        <v>990</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K44" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L44" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="Q44" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B45" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>536</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>537</v>
+      </c>
+      <c r="F45" s="4">
+        <v>2</v>
+      </c>
+      <c r="G45" s="12">
+        <v>380</v>
+      </c>
+      <c r="H45" s="12">
+        <v>30</v>
+      </c>
+      <c r="I45" s="12">
+        <f t="shared" si="0"/>
+        <v>350</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K45" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L45" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="Q45" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B46" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>577</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>538</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>578</v>
+      </c>
+      <c r="F46" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="G46" s="12">
+        <v>1020</v>
+      </c>
+      <c r="H46" s="12">
+        <v>30</v>
+      </c>
+      <c r="I46" s="12">
+        <f t="shared" si="0"/>
+        <v>990</v>
+      </c>
+      <c r="J46" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K46" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L46" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="Q46" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:17" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B47" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C47" s="7" t="s">
+        <v>579</v>
+      </c>
+      <c r="D47" s="7" t="s">
+        <v>539</v>
+      </c>
+      <c r="E47" s="7" t="s">
+        <v>580</v>
+      </c>
+      <c r="F47" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G47" s="13">
+        <v>820</v>
+      </c>
+      <c r="H47" s="13">
+        <v>30</v>
+      </c>
+      <c r="I47" s="13">
+        <f t="shared" si="0"/>
+        <v>790</v>
+      </c>
+      <c r="J47" s="7" t="s">
+        <v>452</v>
+      </c>
+      <c r="K47" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L47" s="7" t="s">
+        <v>449</v>
+      </c>
+      <c r="Q47" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>540</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>581</v>
+      </c>
+      <c r="F48" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="G48" s="12">
+        <v>30</v>
+      </c>
+      <c r="H48" s="12">
+        <v>30</v>
+      </c>
+      <c r="I48" s="12">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J48" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K48" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L48" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="Q48" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="B49" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C49" s="9" t="s">
+        <v>541</v>
+      </c>
+      <c r="E49" s="9" t="s">
+        <v>542</v>
+      </c>
+      <c r="F49" s="10">
+        <v>4</v>
+      </c>
+      <c r="G49" s="14">
+        <v>30</v>
+      </c>
+      <c r="H49" s="14">
+        <v>30</v>
+      </c>
+      <c r="I49" s="14">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J49" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="K49" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L49" s="9" t="s">
+        <v>449</v>
+      </c>
+      <c r="Q49" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>582</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>543</v>
+      </c>
+      <c r="F50" s="4">
+        <v>12</v>
+      </c>
+      <c r="G50" s="12">
+        <v>0</v>
+      </c>
+      <c r="H50" s="12">
+        <v>35</v>
+      </c>
+      <c r="I50" s="12">
+        <f t="shared" si="0"/>
+        <v>-35</v>
+      </c>
+      <c r="J50" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K50" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L50" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="Q50" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:17" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="B51" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C51" s="7" t="s">
+        <v>583</v>
+      </c>
+      <c r="E51" s="7" t="s">
+        <v>584</v>
+      </c>
+      <c r="F51" s="8" t="s">
+        <v>218</v>
+      </c>
+      <c r="G51" s="13">
+        <v>30</v>
+      </c>
+      <c r="H51" s="13">
+        <v>30</v>
+      </c>
+      <c r="I51" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J51" s="7" t="s">
+        <v>452</v>
+      </c>
+      <c r="K51" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L51" s="7" t="s">
+        <v>449</v>
+      </c>
+      <c r="Q51" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:17" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="B52" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C52" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="E52" s="7" t="s">
+        <v>585</v>
+      </c>
+      <c r="F52" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="G52" s="13">
+        <v>30</v>
+      </c>
+      <c r="H52" s="13">
+        <v>30</v>
+      </c>
+      <c r="I52" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J52" s="7" t="s">
+        <v>452</v>
+      </c>
+      <c r="K52" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L52" s="7" t="s">
+        <v>449</v>
+      </c>
+      <c r="Q52" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="E53" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="F53" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="G53" s="12">
+        <v>30</v>
+      </c>
+      <c r="H53" s="12">
+        <v>30</v>
+      </c>
+      <c r="I53" s="12">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J53" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K53" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L53" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="Q53" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>544</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>586</v>
+      </c>
+      <c r="F54" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="G54" s="12">
+        <v>1015</v>
+      </c>
+      <c r="H54" s="12">
+        <v>35</v>
+      </c>
+      <c r="I54" s="12">
+        <f t="shared" si="0"/>
+        <v>980</v>
+      </c>
+      <c r="J54" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K54" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L54" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="Q54" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A55" s="11"/>
+      <c r="B55" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="C55" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="D55" s="11" t="s">
+        <v>355</v>
+      </c>
+      <c r="E55" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="F55" s="11">
+        <v>1</v>
+      </c>
+      <c r="G55" s="11">
+        <v>885</v>
+      </c>
+      <c r="H55" s="11">
+        <v>25</v>
+      </c>
+      <c r="I55" s="11">
+        <v>860</v>
+      </c>
+      <c r="J55" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="K55" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="L55" s="15" t="s">
+        <v>319</v>
+      </c>
+      <c r="M55" s="11" t="s">
+        <v>441</v>
+      </c>
+      <c r="N55" s="11" t="s">
+        <v>442</v>
+      </c>
+      <c r="O55" s="11" t="s">
+        <v>442</v>
+      </c>
+      <c r="P55" s="11" t="s">
+        <v>443</v>
+      </c>
+      <c r="Q55" s="11">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+</worksheet>
 </file>
--- a/data/Apr/Data.xlsx
+++ b/data/Apr/Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Freelance\TextInputter\data\Apr\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7F9556D-7094-44D0-9DB0-45E229EB2302}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5E0F714-C889-4EB2-8141-178BF9C8F181}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01-04" sheetId="4" r:id="rId1"/>
@@ -18,6 +18,7 @@
     <sheet name="03-04" sheetId="7" r:id="rId3"/>
     <sheet name="04-04" sheetId="8" r:id="rId4"/>
     <sheet name="06-04" sheetId="9" r:id="rId5"/>
+    <sheet name="07-04" sheetId="10" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1603" uniqueCount="587">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1821" uniqueCount="657">
   <si>
     <t>THU 4</t>
   </si>
@@ -1398,6 +1399,9 @@
     <t>HD008240</t>
   </si>
   <si>
+    <t>108 đường 85 tân hưng</t>
+  </si>
+  <si>
     <t>AT 06-04</t>
   </si>
   <si>
@@ -1407,9 +1411,18 @@
     <t>HD008286</t>
   </si>
   <si>
+    <t>225/4a đường tam bình phường tam phú</t>
+  </si>
+  <si>
     <t>Thúy Duy</t>
   </si>
   <si>
+    <t>HD008205</t>
+  </si>
+  <si>
+    <t>539/22 hương lộ 3 phường bình hưng hòa</t>
+  </si>
+  <si>
     <t>Bùi Vĩ Thương</t>
   </si>
   <si>
@@ -1419,15 +1432,24 @@
     <t>3273 phạm thế hiển, p7</t>
   </si>
   <si>
+    <t>Thi Thi</t>
+  </si>
+  <si>
     <t>HD008072</t>
   </si>
   <si>
+    <t>15 lô c cư xá phủ lâm D phường 10</t>
+  </si>
+  <si>
     <t>Ngọc Diệu</t>
   </si>
   <si>
     <t>HD008453</t>
   </si>
   <si>
+    <t>132 Le van quoi p bình hưng hòa a</t>
+  </si>
+  <si>
     <t>Hạnh Huỳnh</t>
   </si>
   <si>
@@ -1452,12 +1474,18 @@
     <t>HD008283</t>
   </si>
   <si>
+    <t>Saigon Royal Residences, Nguyễn Trường Tộ, phường 13</t>
+  </si>
+  <si>
     <t>Ngo Thuy Linh</t>
   </si>
   <si>
     <t>HD008187</t>
   </si>
   <si>
+    <t>37 nguyễn văn hưởng thảo điền</t>
+  </si>
+  <si>
     <t>Hồng Ngọc</t>
   </si>
   <si>
@@ -1476,45 +1504,72 @@
     <t>HD008440</t>
   </si>
   <si>
+    <t>310 tô ngọc vân -tam phú</t>
+  </si>
+  <si>
+    <t>Thúy Ly</t>
+  </si>
+  <si>
     <t>HD008413</t>
   </si>
   <si>
     <t>chung cư linh trung đường 16 linh trung</t>
   </si>
   <si>
+    <t>Phương Thao</t>
+  </si>
+  <si>
     <t>HD008275</t>
   </si>
   <si>
+    <t>137/18 âu dương lân</t>
+  </si>
+  <si>
     <t>Trần Ngọc Bích.</t>
   </si>
   <si>
     <t>HD008448</t>
   </si>
   <si>
+    <t>43/3 Cửu Long p2</t>
+  </si>
+  <si>
     <t>Lê Huyền Trang</t>
   </si>
   <si>
     <t>HD007992</t>
   </si>
   <si>
+    <t>737-739 hồng bàng, phường bình tây</t>
+  </si>
+  <si>
     <t>Huỳnh Huỳnh Như</t>
   </si>
   <si>
     <t>HD008318</t>
   </si>
   <si>
+    <t>Đường số 15, Phường Tân Phú The Peak Midtown Phú Mỹ Hưng</t>
+  </si>
+  <si>
     <t>Hiền</t>
   </si>
   <si>
     <t>HD008424</t>
   </si>
   <si>
+    <t>180 nguyễn tất thành</t>
+  </si>
+  <si>
     <t>Shin</t>
   </si>
   <si>
     <t>HD008285</t>
   </si>
   <si>
+    <t>278-283 chung cư grand riverside đường Bến Vân Đồn, phường 2</t>
+  </si>
+  <si>
     <t>chị Vân - fb Nguyễn Linh</t>
   </si>
   <si>
@@ -1530,15 +1585,27 @@
     <t>HD008237</t>
   </si>
   <si>
+    <t>56 đường số 1 khu dân cư hirnlam Tân Hưng</t>
+  </si>
+  <si>
     <t>Miêu Trần</t>
   </si>
   <si>
     <t>HD007974</t>
   </si>
   <si>
+    <t>Số 6 nguyễn biểu.P1</t>
+  </si>
+  <si>
+    <t>Huỳnh Quế Trinh</t>
+  </si>
+  <si>
     <t>HD008460</t>
   </si>
   <si>
+    <t>166 đường số 1, khu phố 25, phường Bình Hưng Hòa</t>
+  </si>
+  <si>
     <t>Elly Nguyễn</t>
   </si>
   <si>
@@ -1572,9 +1639,18 @@
     <t>HD007961</t>
   </si>
   <si>
+    <t>Số 5a, Tống Văn Hên, phường 15</t>
+  </si>
+  <si>
+    <t>Nguyễn Tiên</t>
+  </si>
+  <si>
     <t>HD008114</t>
   </si>
   <si>
+    <t>326 trần quang khải tân định</t>
+  </si>
+  <si>
     <t>Trà An</t>
   </si>
   <si>
@@ -1590,6 +1666,9 @@
     <t>HD008139</t>
   </si>
   <si>
+    <t>F4/19 ấp 6c đường liên ấp 2/6, Xã Vĩnh Lộc A</t>
+  </si>
+  <si>
     <t>Ngô Bích Hợp</t>
   </si>
   <si>
@@ -1605,6 +1684,9 @@
     <t>HD008126</t>
   </si>
   <si>
+    <t>200 đường 3/2 phường Hoà Hưng Chưng cư Hà Đô, Toà Iris 4</t>
+  </si>
+  <si>
     <t>Ngọc Dung</t>
   </si>
   <si>
@@ -1617,6 +1699,12 @@
     <t>Van Huynh ft Trương Mỹ Linh</t>
   </si>
   <si>
+    <t>HD008396</t>
+  </si>
+  <si>
+    <t>130/21 trần thị trọng. P15</t>
+  </si>
+  <si>
     <t>Anna Le</t>
   </si>
   <si>
@@ -1626,6 +1714,12 @@
     <t>112 bến vân đồn, phường 9</t>
   </si>
   <si>
+    <t>Note : Bống Kẹo</t>
+  </si>
+  <si>
+    <t>HD007921</t>
+  </si>
+  <si>
     <t>Nguyên Nguyễn</t>
   </si>
   <si>
@@ -1638,6 +1732,9 @@
     <t>Vy Lê</t>
   </si>
   <si>
+    <t>HX008403</t>
+  </si>
+  <si>
     <t>119F/31b đặng chất p.chánh hưng</t>
   </si>
   <si>
@@ -1656,151 +1753,265 @@
     <t>192 Nguyễn văn hưởng thảo điền</t>
   </si>
   <si>
+    <t>Lâm Oanh</t>
+  </si>
+  <si>
     <t>HD008229</t>
   </si>
   <si>
+    <t>102 phan văn hớn</t>
+  </si>
+  <si>
+    <t>Người Nhận : FB HUYEN VUONG</t>
+  </si>
+  <si>
     <t>HD008127</t>
   </si>
   <si>
+    <t>Số 78 Đường Số 7, P. Bình Hưng Hòa</t>
+  </si>
+  <si>
     <t>NANA CHONG</t>
   </si>
   <si>
+    <t>535/59/4C THỐNG NHẤT P16</t>
+  </si>
+  <si>
     <t>NGUYÊN NGUYÊN</t>
   </si>
   <si>
     <t>12 TÔN ĐẢN P13</t>
   </si>
   <si>
+    <t>WIND XPRESS</t>
+  </si>
+  <si>
     <t>375 tân thới hiệp 21, Tổ 3,Kp3</t>
   </si>
   <si>
+    <t>Thanh Hằng (Vivi Kosalim)</t>
+  </si>
+  <si>
+    <t>605 Âu Cơ, Phường Phú Trung</t>
+  </si>
+  <si>
+    <t>66 đường 17 p10</t>
+  </si>
+  <si>
     <t>BOS BMB</t>
   </si>
   <si>
-    <t>108 đường 85 tân hưng</t>
-  </si>
-  <si>
-    <t>225/4a đường tam bình phường tam phú</t>
-  </si>
-  <si>
-    <t>HD008205</t>
-  </si>
-  <si>
-    <t>539/22 hương lộ 3 phường bình hưng hòa</t>
-  </si>
-  <si>
-    <t>Thi Thi</t>
-  </si>
-  <si>
-    <t>15 lô c cư xá phủ lâm D phường 10</t>
-  </si>
-  <si>
-    <t>132 Le van quoi p bình hưng hòa a</t>
-  </si>
-  <si>
-    <t>Saigon Royal Residences, Nguyễn Trường Tộ, phường 13</t>
-  </si>
-  <si>
-    <t>37 nguyễn văn hưởng thảo điền</t>
-  </si>
-  <si>
-    <t>310 tô ngọc vân -tam phú</t>
-  </si>
-  <si>
-    <t>Thúy Ly</t>
-  </si>
-  <si>
-    <t>Phương Thao</t>
-  </si>
-  <si>
-    <t>137/18 âu dương lân</t>
-  </si>
-  <si>
-    <t>43/3 Cửu Long p2</t>
-  </si>
-  <si>
-    <t>737-739 hồng bàng, phường bình tây</t>
-  </si>
-  <si>
-    <t>Đường số 15, Phường Tân Phú The Peak Midtown Phú Mỹ Hưng</t>
-  </si>
-  <si>
-    <t>180 nguyễn tất thành</t>
-  </si>
-  <si>
-    <t>278-283 chung cư grand riverside đường Bến Vân Đồn, phường 2</t>
-  </si>
-  <si>
-    <t>56 đường số 1 khu dân cư hirnlam Tân Hưng</t>
-  </si>
-  <si>
-    <t>Số 6 nguyễn biểu.P1</t>
-  </si>
-  <si>
-    <t>Huỳnh Quế Trinh</t>
-  </si>
-  <si>
-    <t>166 đường số 1, khu phố 25, phường Bình Hưng Hòa</t>
-  </si>
-  <si>
-    <t>Số 5a, Tống Văn Hên, phường 15</t>
-  </si>
-  <si>
-    <t>Nguyễn Tiên</t>
-  </si>
-  <si>
-    <t>326 trần quang khải tân định</t>
-  </si>
-  <si>
-    <t>F4/19 ấp 6c đường liên ấp 2/6, Xã Vĩnh Lộc A</t>
-  </si>
-  <si>
-    <t>200 đường 3/2 phường Hoà Hưng Chưng cư Hà Đô, Toà Iris 4</t>
-  </si>
-  <si>
-    <t>HD008396</t>
-  </si>
-  <si>
-    <t>130/21 trần thị trọng. P15</t>
-  </si>
-  <si>
-    <t>Note : Bống Kẹo</t>
-  </si>
-  <si>
-    <t>HD007921</t>
-  </si>
-  <si>
-    <t>HX008403</t>
-  </si>
-  <si>
-    <t>Lâm Oanh</t>
-  </si>
-  <si>
-    <t>102 phan văn hớn</t>
-  </si>
-  <si>
-    <t>Người Nhận : FB HUYEN VUONG</t>
-  </si>
-  <si>
-    <t>Số 78 Đường Số 7, P. Bình Hưng Hòa</t>
-  </si>
-  <si>
-    <t>535/59/4C THỐNG NHẤT P16</t>
-  </si>
-  <si>
-    <t>WIND XPRESS</t>
-  </si>
-  <si>
-    <t>Thanh Hằng (Vivi Kosalim)</t>
-  </si>
-  <si>
-    <t>605 Âu Cơ, Phường Phú Trung</t>
-  </si>
-  <si>
-    <t>66 đường 17 p10</t>
-  </si>
-  <si>
     <t>119 hoàng diệu 2 linh trung</t>
+  </si>
+  <si>
+    <t>THU 3</t>
+  </si>
+  <si>
+    <t>NGAY 7-4</t>
+  </si>
+  <si>
+    <t>Hồng Hoa</t>
+  </si>
+  <si>
+    <t>HD008716</t>
+  </si>
+  <si>
+    <t>chung cư Feliz en vista số 1 lệ hiến mai p thạnh mỹ lợi</t>
+  </si>
+  <si>
+    <t>07-04-2026</t>
+  </si>
+  <si>
+    <t>Thỏ Bunny</t>
+  </si>
+  <si>
+    <t>HD007988</t>
+  </si>
+  <si>
+    <t>HD008429</t>
+  </si>
+  <si>
+    <t>AT 07-04</t>
+  </si>
+  <si>
+    <t>Tracyy An</t>
+  </si>
+  <si>
+    <t>HD008658</t>
+  </si>
+  <si>
+    <t>226 gò dưa tam bình</t>
+  </si>
+  <si>
+    <t>Trần Hy Kim Ngân</t>
+  </si>
+  <si>
+    <t>HD008694</t>
+  </si>
+  <si>
+    <t>125/16/33 bùi đình tuy phường 14</t>
+  </si>
+  <si>
+    <t>Phan Nhi</t>
+  </si>
+  <si>
+    <t>HD008516</t>
+  </si>
+  <si>
+    <t>107/189 quang trung, f.10</t>
+  </si>
+  <si>
+    <t>Vy Nguyên</t>
+  </si>
+  <si>
+    <t>HD008724</t>
+  </si>
+  <si>
+    <t>101 đường cn 11, phường sơn kỳ</t>
+  </si>
+  <si>
+    <t>Nany Nany</t>
+  </si>
+  <si>
+    <t>HD008494</t>
+  </si>
+  <si>
+    <t>phuong phuong (inst bedaunee)</t>
+  </si>
+  <si>
+    <t>HD008639</t>
+  </si>
+  <si>
+    <t>HD008644</t>
+  </si>
+  <si>
+    <t>Ivy Dao</t>
+  </si>
+  <si>
+    <t>HD008553</t>
+  </si>
+  <si>
+    <t>Lam Nguyên</t>
+  </si>
+  <si>
+    <t>HD008721</t>
+  </si>
+  <si>
+    <t>Jessie Beauty</t>
+  </si>
+  <si>
+    <t>HD008545</t>
+  </si>
+  <si>
+    <t>HD008482</t>
+  </si>
+  <si>
+    <t>Châu Phạm</t>
+  </si>
+  <si>
+    <t>HD008691</t>
+  </si>
+  <si>
+    <t>HD008669</t>
+  </si>
+  <si>
+    <t>Đào Hạnh nhận hộ An Hy</t>
+  </si>
+  <si>
+    <t>HD008648</t>
+  </si>
+  <si>
+    <t>24 Yên Thế, Phường 2</t>
+  </si>
+  <si>
+    <t>Võ Diễm My</t>
+  </si>
+  <si>
+    <t>HD008657</t>
+  </si>
+  <si>
+    <t>Nhung Lê</t>
+  </si>
+  <si>
+    <t>HD008600</t>
+  </si>
+  <si>
+    <t>NGÂN HÀ</t>
+  </si>
+  <si>
+    <t>40 đường 53 p10</t>
+  </si>
+  <si>
+    <t>UYÊN MI</t>
+  </si>
+  <si>
+    <t>jenny bouti</t>
+  </si>
+  <si>
+    <t>401 Quang trung f10</t>
+  </si>
+  <si>
+    <t>238/3 trường chinh, đông hưng thuận</t>
+  </si>
+  <si>
+    <t>Pachara (BN6994) hạnh Narin</t>
+  </si>
+  <si>
+    <t>14 Lam Thi Ho, Tan Chanh Hiep Ward</t>
+  </si>
+  <si>
+    <t>HCM warehouse address</t>
+  </si>
+  <si>
+    <t>188/15 đường số 4 phường 16</t>
+  </si>
+  <si>
+    <t>121 hiệp bình - p hiệp bình chánh</t>
+  </si>
+  <si>
+    <t>93/1 Nguyễn Chí Thanh P9</t>
+  </si>
+  <si>
+    <t>tran Bảo Châu</t>
+  </si>
+  <si>
+    <t>654/6 lạc long quân p9</t>
+  </si>
+  <si>
+    <t>Winnie</t>
+  </si>
+  <si>
+    <t>79/27 Trần Văn Đang, P. Nhiêu Lộc</t>
+  </si>
+  <si>
+    <t>71/2/13 Nguyễn Bặc, Phường 3</t>
+  </si>
+  <si>
+    <t>Vinhomes Golden River - Aqua 2, Ton Duc Thang, ward Ben Nghe</t>
+  </si>
+  <si>
+    <t>A nam</t>
+  </si>
+  <si>
+    <t>40/11B ấp 42 xã bà điểm</t>
+  </si>
+  <si>
+    <t>479 trần xuân soạn, phường tân kiểng</t>
+  </si>
+  <si>
+    <t>Minh Hải zalo cẩm ngân</t>
+  </si>
+  <si>
+    <t>17 Đường Số 13 Phường Bình Hưng Hòa</t>
+  </si>
+  <si>
+    <t>2050 phạm thể hiển p6</t>
+  </si>
+  <si>
+    <t>M37/15 Cư Xá Phú Lâm A Phường 12</t>
+  </si>
+  <si>
+    <t>616/5/6 lê trọng tấn phường Bình Hưng Hòa</t>
   </si>
 </sst>
 </file>
@@ -1901,7 +2112,7 @@
     <xf numFmtId="3" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="3" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="3" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5144,7 +5355,7 @@
         <v>25</v>
       </c>
       <c r="I35" s="7">
-        <f t="shared" ref="I35:I53" si="1">G35-H35</f>
+        <f t="shared" ref="I35:I66" si="1">G35-H35</f>
         <v>790</v>
       </c>
       <c r="J35" s="7" t="s">
@@ -7455,6 +7666,7 @@
     <col min="4" max="4" width="9.85546875" customWidth="1"/>
     <col min="5" max="5" width="61.85546875" customWidth="1"/>
     <col min="6" max="6" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.140625" customWidth="1"/>
     <col min="8" max="8" width="9.5703125" customWidth="1"/>
     <col min="9" max="9" width="10.5703125" customWidth="1"/>
     <col min="10" max="10" width="9.7109375" customWidth="1"/>
@@ -7547,7 +7759,7 @@
         <v>30</v>
       </c>
       <c r="I3" s="12">
-        <f t="shared" ref="I3:I54" si="0">G3-H3</f>
+        <f t="shared" ref="I3:I34" si="0">G3-H3</f>
         <v>2360</v>
       </c>
       <c r="J3" s="3" t="s">
@@ -7577,7 +7789,7 @@
         <v>451</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>545</v>
+        <v>452</v>
       </c>
       <c r="F4" s="8">
         <v>7</v>
@@ -7593,7 +7805,7 @@
         <v>440</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="K4" s="7" t="s">
         <v>24</v>
@@ -7610,13 +7822,13 @@
         <v>18</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>546</v>
+        <v>456</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>123</v>
@@ -7649,13 +7861,13 @@
         <v>18</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>547</v>
+        <v>458</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>548</v>
+        <v>459</v>
       </c>
       <c r="F6" s="8" t="s">
         <v>22</v>
@@ -7671,7 +7883,7 @@
         <v>790</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="K6" s="7" t="s">
         <v>24</v>
@@ -7688,13 +7900,13 @@
         <v>18</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="F7" s="8">
         <v>8</v>
@@ -7710,7 +7922,7 @@
         <v>-25</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="K7" s="7" t="s">
         <v>24</v>
@@ -7727,13 +7939,13 @@
         <v>18</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>549</v>
+        <v>463</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>550</v>
+        <v>465</v>
       </c>
       <c r="F8" s="8">
         <v>6</v>
@@ -7749,7 +7961,7 @@
         <v>1490</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="K8" s="7" t="s">
         <v>24</v>
@@ -7766,13 +7978,13 @@
         <v>18</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>460</v>
+        <v>466</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>461</v>
+        <v>467</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>551</v>
+        <v>468</v>
       </c>
       <c r="F9" s="8" t="s">
         <v>22</v>
@@ -7788,7 +8000,7 @@
         <v>860</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="K9" s="7" t="s">
         <v>24</v>
@@ -7805,13 +8017,13 @@
         <v>18</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>462</v>
+        <v>469</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>463</v>
+        <v>470</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>464</v>
+        <v>471</v>
       </c>
       <c r="F10" s="8" t="s">
         <v>22</v>
@@ -7827,7 +8039,7 @@
         <v>440</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="K10" s="7" t="s">
         <v>24</v>
@@ -7844,13 +8056,13 @@
         <v>18</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>465</v>
+        <v>472</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>466</v>
+        <v>473</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>467</v>
+        <v>474</v>
       </c>
       <c r="F11" s="10">
         <v>10</v>
@@ -7883,13 +8095,13 @@
         <v>18</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>468</v>
+        <v>475</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>469</v>
+        <v>476</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>552</v>
+        <v>477</v>
       </c>
       <c r="F12" s="10">
         <v>4</v>
@@ -7922,13 +8134,13 @@
         <v>18</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>470</v>
+        <v>478</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>471</v>
+        <v>479</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>553</v>
+        <v>480</v>
       </c>
       <c r="F13" s="4" t="s">
         <v>179</v>
@@ -7961,13 +8173,13 @@
         <v>18</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>472</v>
+        <v>481</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>473</v>
+        <v>482</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>474</v>
+        <v>483</v>
       </c>
       <c r="F14" s="8" t="s">
         <v>22</v>
@@ -7983,7 +8195,7 @@
         <v>890</v>
       </c>
       <c r="J14" s="7" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="K14" s="7" t="s">
         <v>24</v>
@@ -8003,7 +8215,7 @@
         <v>112</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>475</v>
+        <v>484</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>114</v>
@@ -8039,13 +8251,13 @@
         <v>18</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>476</v>
+        <v>485</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>477</v>
+        <v>486</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>554</v>
+        <v>487</v>
       </c>
       <c r="F16" s="4" t="s">
         <v>123</v>
@@ -8078,13 +8290,13 @@
         <v>18</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>555</v>
+        <v>488</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>478</v>
+        <v>489</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>479</v>
+        <v>490</v>
       </c>
       <c r="F17" s="4" t="s">
         <v>123</v>
@@ -8117,13 +8329,13 @@
         <v>18</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>556</v>
+        <v>491</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>480</v>
+        <v>492</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>557</v>
+        <v>493</v>
       </c>
       <c r="F18" s="10">
         <v>8</v>
@@ -8156,13 +8368,13 @@
         <v>18</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>481</v>
+        <v>494</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>482</v>
+        <v>495</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>558</v>
+        <v>496</v>
       </c>
       <c r="F19" s="10" t="s">
         <v>94</v>
@@ -8195,13 +8407,13 @@
         <v>18</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>483</v>
+        <v>497</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>484</v>
+        <v>498</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>559</v>
+        <v>499</v>
       </c>
       <c r="F20" s="8" t="s">
         <v>97</v>
@@ -8217,7 +8429,7 @@
         <v>670</v>
       </c>
       <c r="J20" s="7" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="K20" s="7" t="s">
         <v>24</v>
@@ -8234,13 +8446,13 @@
         <v>18</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>485</v>
+        <v>500</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>486</v>
+        <v>501</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>560</v>
+        <v>502</v>
       </c>
       <c r="F21" s="8">
         <v>7</v>
@@ -8256,7 +8468,7 @@
         <v>670</v>
       </c>
       <c r="J21" s="7" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="K21" s="7" t="s">
         <v>24</v>
@@ -8273,13 +8485,13 @@
         <v>18</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>487</v>
+        <v>503</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>488</v>
+        <v>504</v>
       </c>
       <c r="E22" s="9" t="s">
-        <v>561</v>
+        <v>505</v>
       </c>
       <c r="F22" s="10">
         <v>4</v>
@@ -8312,13 +8524,13 @@
         <v>18</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>489</v>
+        <v>506</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>490</v>
+        <v>507</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>562</v>
+        <v>508</v>
       </c>
       <c r="F23" s="10">
         <v>4</v>
@@ -8354,13 +8566,13 @@
         <v>18</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>491</v>
+        <v>509</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>492</v>
+        <v>510</v>
       </c>
       <c r="E24" s="9" t="s">
-        <v>493</v>
+        <v>511</v>
       </c>
       <c r="F24" s="10">
         <v>4</v>
@@ -8393,13 +8605,13 @@
         <v>18</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>494</v>
+        <v>512</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>495</v>
+        <v>513</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>563</v>
+        <v>514</v>
       </c>
       <c r="F25" s="8">
         <v>7</v>
@@ -8415,7 +8627,7 @@
         <v>-30</v>
       </c>
       <c r="J25" s="7" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="K25" s="7" t="s">
         <v>24</v>
@@ -8432,13 +8644,13 @@
         <v>18</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>496</v>
+        <v>515</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>497</v>
+        <v>516</v>
       </c>
       <c r="E26" s="9" t="s">
-        <v>564</v>
+        <v>517</v>
       </c>
       <c r="F26" s="10" t="s">
         <v>186</v>
@@ -8471,13 +8683,13 @@
         <v>18</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>565</v>
+        <v>518</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>498</v>
+        <v>519</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>566</v>
+        <v>520</v>
       </c>
       <c r="F27" s="8" t="s">
         <v>22</v>
@@ -8493,7 +8705,7 @@
         <v>990</v>
       </c>
       <c r="J27" s="7" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="K27" s="7" t="s">
         <v>24</v>
@@ -8510,13 +8722,13 @@
         <v>18</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>499</v>
+        <v>521</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>500</v>
+        <v>522</v>
       </c>
       <c r="E28" s="9" t="s">
-        <v>501</v>
+        <v>523</v>
       </c>
       <c r="F28" s="10">
         <v>5</v>
@@ -8549,13 +8761,13 @@
         <v>18</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>502</v>
+        <v>524</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>503</v>
+        <v>525</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>504</v>
+        <v>526</v>
       </c>
       <c r="F29" s="10">
         <v>1</v>
@@ -8588,13 +8800,13 @@
         <v>18</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>505</v>
+        <v>527</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>506</v>
+        <v>528</v>
       </c>
       <c r="E30" s="9" t="s">
-        <v>507</v>
+        <v>529</v>
       </c>
       <c r="F30" s="10">
         <v>10</v>
@@ -8627,13 +8839,13 @@
         <v>18</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>508</v>
+        <v>530</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>509</v>
+        <v>531</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>567</v>
+        <v>532</v>
       </c>
       <c r="F31" s="4" t="s">
         <v>94</v>
@@ -8705,13 +8917,13 @@
         <v>18</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>568</v>
+        <v>533</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>510</v>
+        <v>534</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>569</v>
+        <v>535</v>
       </c>
       <c r="F33" s="10" t="s">
         <v>60</v>
@@ -8744,13 +8956,13 @@
         <v>18</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>511</v>
+        <v>536</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>512</v>
+        <v>537</v>
       </c>
       <c r="E34" s="9" t="s">
-        <v>513</v>
+        <v>538</v>
       </c>
       <c r="F34" s="10">
         <v>1</v>
@@ -8783,13 +8995,13 @@
         <v>18</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>514</v>
+        <v>539</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>515</v>
+        <v>540</v>
       </c>
       <c r="E35" s="7" t="s">
-        <v>570</v>
+        <v>541</v>
       </c>
       <c r="F35" s="8" t="s">
         <v>151</v>
@@ -8801,11 +9013,11 @@
         <v>35</v>
       </c>
       <c r="I35" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="I35:I66" si="1">G35-H35</f>
         <v>440</v>
       </c>
       <c r="J35" s="7" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="K35" s="7" t="s">
         <v>24</v>
@@ -8822,13 +9034,13 @@
         <v>18</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>516</v>
+        <v>542</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>517</v>
+        <v>543</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>518</v>
+        <v>544</v>
       </c>
       <c r="F36" s="4">
         <v>2</v>
@@ -8840,7 +9052,7 @@
         <v>30</v>
       </c>
       <c r="I36" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>790</v>
       </c>
       <c r="J36" s="3" t="s">
@@ -8861,13 +9073,13 @@
         <v>18</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>519</v>
+        <v>545</v>
       </c>
       <c r="D37" s="9" t="s">
-        <v>520</v>
+        <v>546</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>571</v>
+        <v>547</v>
       </c>
       <c r="F37" s="10">
         <v>10</v>
@@ -8879,7 +9091,7 @@
         <v>25</v>
       </c>
       <c r="I37" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>440</v>
       </c>
       <c r="J37" s="9" t="s">
@@ -8900,13 +9112,13 @@
         <v>18</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>521</v>
+        <v>548</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>522</v>
+        <v>549</v>
       </c>
       <c r="E38" s="7" t="s">
-        <v>523</v>
+        <v>550</v>
       </c>
       <c r="F38" s="8">
         <v>6</v>
@@ -8918,11 +9130,11 @@
         <v>30</v>
       </c>
       <c r="I38" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2190</v>
       </c>
       <c r="J38" s="7" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="K38" s="7" t="s">
         <v>24</v>
@@ -8942,13 +9154,13 @@
         <v>18</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>524</v>
+        <v>551</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>572</v>
+        <v>552</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>573</v>
+        <v>553</v>
       </c>
       <c r="F39" s="4" t="s">
         <v>94</v>
@@ -8960,7 +9172,7 @@
         <v>25</v>
       </c>
       <c r="I39" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-25</v>
       </c>
       <c r="J39" s="3" t="s">
@@ -8981,13 +9193,13 @@
         <v>18</v>
       </c>
       <c r="C40" s="9" t="s">
-        <v>525</v>
+        <v>554</v>
       </c>
       <c r="D40" s="9" t="s">
-        <v>526</v>
+        <v>555</v>
       </c>
       <c r="E40" s="9" t="s">
-        <v>527</v>
+        <v>556</v>
       </c>
       <c r="F40" s="10">
         <v>4</v>
@@ -8999,7 +9211,7 @@
         <v>25</v>
       </c>
       <c r="I40" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-25</v>
       </c>
       <c r="J40" s="9" t="s">
@@ -9020,10 +9232,10 @@
         <v>18</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>574</v>
+        <v>557</v>
       </c>
       <c r="D41" s="7" t="s">
-        <v>575</v>
+        <v>558</v>
       </c>
       <c r="E41" s="7" t="s">
         <v>403</v>
@@ -9038,11 +9250,11 @@
         <v>30</v>
       </c>
       <c r="I41" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>690</v>
       </c>
       <c r="J41" s="7" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="K41" s="7" t="s">
         <v>24</v>
@@ -9059,13 +9271,13 @@
         <v>18</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>528</v>
+        <v>559</v>
       </c>
       <c r="D42" s="7" t="s">
-        <v>529</v>
+        <v>560</v>
       </c>
       <c r="E42" s="7" t="s">
-        <v>530</v>
+        <v>561</v>
       </c>
       <c r="F42" s="8" t="s">
         <v>22</v>
@@ -9077,11 +9289,11 @@
         <v>30</v>
       </c>
       <c r="I42" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>720</v>
       </c>
       <c r="J42" s="7" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="K42" s="7" t="s">
         <v>24</v>
@@ -9098,13 +9310,13 @@
         <v>18</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>531</v>
+        <v>562</v>
       </c>
       <c r="D43" s="7" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="E43" s="7" t="s">
-        <v>532</v>
+        <v>564</v>
       </c>
       <c r="F43" s="8">
         <v>8</v>
@@ -9116,11 +9328,11 @@
         <v>30</v>
       </c>
       <c r="I43" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>360</v>
       </c>
       <c r="J43" s="7" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="K43" s="7" t="s">
         <v>24</v>
@@ -9137,13 +9349,13 @@
         <v>18</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>533</v>
+        <v>565</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>534</v>
+        <v>566</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>535</v>
+        <v>567</v>
       </c>
       <c r="F44" s="4" t="s">
         <v>179</v>
@@ -9155,7 +9367,7 @@
         <v>30</v>
       </c>
       <c r="I44" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>990</v>
       </c>
       <c r="J44" s="3" t="s">
@@ -9179,10 +9391,10 @@
         <v>320</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>536</v>
+        <v>568</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>537</v>
+        <v>569</v>
       </c>
       <c r="F45" s="4">
         <v>2</v>
@@ -9194,7 +9406,7 @@
         <v>30</v>
       </c>
       <c r="I45" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>350</v>
       </c>
       <c r="J45" s="3" t="s">
@@ -9215,13 +9427,13 @@
         <v>18</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>577</v>
+        <v>570</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>538</v>
+        <v>571</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>578</v>
+        <v>572</v>
       </c>
       <c r="F46" s="4" t="s">
         <v>64</v>
@@ -9233,7 +9445,7 @@
         <v>30</v>
       </c>
       <c r="I46" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>990</v>
       </c>
       <c r="J46" s="3" t="s">
@@ -9254,13 +9466,13 @@
         <v>18</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>579</v>
+        <v>573</v>
       </c>
       <c r="D47" s="7" t="s">
-        <v>539</v>
+        <v>574</v>
       </c>
       <c r="E47" s="7" t="s">
-        <v>580</v>
+        <v>575</v>
       </c>
       <c r="F47" s="8" t="s">
         <v>22</v>
@@ -9272,11 +9484,11 @@
         <v>30</v>
       </c>
       <c r="I47" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>790</v>
       </c>
       <c r="J47" s="7" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="K47" s="7" t="s">
         <v>24</v>
@@ -9296,10 +9508,10 @@
         <v>18</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>540</v>
+        <v>576</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>581</v>
+        <v>577</v>
       </c>
       <c r="F48" s="4" t="s">
         <v>49</v>
@@ -9311,7 +9523,7 @@
         <v>30</v>
       </c>
       <c r="I48" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J48" s="3" t="s">
@@ -9335,10 +9547,10 @@
         <v>18</v>
       </c>
       <c r="C49" s="9" t="s">
-        <v>541</v>
+        <v>578</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>542</v>
+        <v>579</v>
       </c>
       <c r="F49" s="10">
         <v>4</v>
@@ -9350,7 +9562,7 @@
         <v>30</v>
       </c>
       <c r="I49" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J49" s="9" t="s">
@@ -9374,10 +9586,10 @@
         <v>18</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>543</v>
+        <v>581</v>
       </c>
       <c r="F50" s="4">
         <v>12</v>
@@ -9389,7 +9601,7 @@
         <v>35</v>
       </c>
       <c r="I50" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-35</v>
       </c>
       <c r="J50" s="3" t="s">
@@ -9413,10 +9625,10 @@
         <v>18</v>
       </c>
       <c r="C51" s="7" t="s">
+        <v>582</v>
+      </c>
+      <c r="E51" s="7" t="s">
         <v>583</v>
-      </c>
-      <c r="E51" s="7" t="s">
-        <v>584</v>
       </c>
       <c r="F51" s="8" t="s">
         <v>218</v>
@@ -9428,11 +9640,11 @@
         <v>30</v>
       </c>
       <c r="I51" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J51" s="7" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="K51" s="7" t="s">
         <v>24</v>
@@ -9455,7 +9667,7 @@
         <v>308</v>
       </c>
       <c r="E52" s="7" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="F52" s="8" t="s">
         <v>97</v>
@@ -9467,11 +9679,11 @@
         <v>30</v>
       </c>
       <c r="I52" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J52" s="7" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="K52" s="7" t="s">
         <v>24</v>
@@ -9506,7 +9718,7 @@
         <v>30</v>
       </c>
       <c r="I53" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J53" s="3" t="s">
@@ -9530,7 +9742,7 @@
         <v>18</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>544</v>
+        <v>585</v>
       </c>
       <c r="E54" s="3" t="s">
         <v>586</v>
@@ -9545,7 +9757,7 @@
         <v>35</v>
       </c>
       <c r="I54" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>980</v>
       </c>
       <c r="J54" s="3" t="s">
@@ -9616,4 +9828,984 @@
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <dimension ref="A1:P27"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="30.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="80.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B1" s="1" t="s">
+        <v>587</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>589</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>590</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>591</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="G3" s="3">
+        <v>850</v>
+      </c>
+      <c r="H3" s="3">
+        <v>30</v>
+      </c>
+      <c r="I3" s="3">
+        <f t="shared" ref="I3:I27" si="0">G3-H3</f>
+        <v>820</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>593</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>594</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>648</v>
+      </c>
+      <c r="F4" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="G4" s="9">
+        <v>745</v>
+      </c>
+      <c r="H4" s="9">
+        <v>25</v>
+      </c>
+      <c r="I4" s="9">
+        <f t="shared" si="0"/>
+        <v>720</v>
+      </c>
+      <c r="J4" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="K4" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L4" s="9" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>645</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>595</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>646</v>
+      </c>
+      <c r="F5" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="G5" s="9">
+        <v>1025</v>
+      </c>
+      <c r="H5" s="9">
+        <v>25</v>
+      </c>
+      <c r="I5" s="9">
+        <f t="shared" si="0"/>
+        <v>1000</v>
+      </c>
+      <c r="J5" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="K5" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L5" s="9" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>597</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>598</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>599</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="G6" s="3">
+        <v>1840</v>
+      </c>
+      <c r="H6" s="3">
+        <v>30</v>
+      </c>
+      <c r="I6" s="3">
+        <f t="shared" si="0"/>
+        <v>1810</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L6" s="3" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>600</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>601</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>602</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G7" s="3">
+        <v>815</v>
+      </c>
+      <c r="H7" s="3">
+        <v>25</v>
+      </c>
+      <c r="I7" s="3">
+        <f t="shared" si="0"/>
+        <v>790</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L7" s="3" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>603</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>604</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>605</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="G8" s="3">
+        <v>815</v>
+      </c>
+      <c r="H8" s="3">
+        <v>25</v>
+      </c>
+      <c r="I8" s="3">
+        <f t="shared" si="0"/>
+        <v>790</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>606</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>607</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>608</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>218</v>
+      </c>
+      <c r="G9" s="7">
+        <v>1035</v>
+      </c>
+      <c r="H9" s="7">
+        <v>25</v>
+      </c>
+      <c r="I9" s="7">
+        <f t="shared" si="0"/>
+        <v>1010</v>
+      </c>
+      <c r="J9" s="7" t="s">
+        <v>596</v>
+      </c>
+      <c r="K9" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L9" s="7" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>609</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>610</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>656</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G10" s="7">
+        <v>820</v>
+      </c>
+      <c r="H10" s="7">
+        <v>30</v>
+      </c>
+      <c r="I10" s="7">
+        <f t="shared" si="0"/>
+        <v>790</v>
+      </c>
+      <c r="J10" s="7" t="s">
+        <v>596</v>
+      </c>
+      <c r="K10" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L10" s="7" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>611</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>612</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>651</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="G11" s="7">
+        <v>780</v>
+      </c>
+      <c r="H11" s="7">
+        <v>30</v>
+      </c>
+      <c r="I11" s="7">
+        <f t="shared" si="0"/>
+        <v>750</v>
+      </c>
+      <c r="J11" s="7" t="s">
+        <v>596</v>
+      </c>
+      <c r="K11" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L11" s="7" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>652</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>613</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>653</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G12" s="7">
+        <v>2500</v>
+      </c>
+      <c r="H12" s="7">
+        <v>35</v>
+      </c>
+      <c r="I12" s="7">
+        <f t="shared" si="0"/>
+        <v>2465</v>
+      </c>
+      <c r="J12" s="7" t="s">
+        <v>596</v>
+      </c>
+      <c r="K12" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L12" s="7" t="s">
+        <v>592</v>
+      </c>
+      <c r="M12" s="7" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>614</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>615</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>636</v>
+      </c>
+      <c r="F13" s="4">
+        <v>12</v>
+      </c>
+      <c r="G13" s="3">
+        <v>0</v>
+      </c>
+      <c r="H13" s="3">
+        <v>30</v>
+      </c>
+      <c r="I13" s="3">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K13" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L13" s="3" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>616</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>617</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>655</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="G14" s="7">
+        <v>845</v>
+      </c>
+      <c r="H14" s="7">
+        <v>25</v>
+      </c>
+      <c r="I14" s="7">
+        <f t="shared" si="0"/>
+        <v>820</v>
+      </c>
+      <c r="J14" s="7" t="s">
+        <v>596</v>
+      </c>
+      <c r="K14" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L14" s="7" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>618</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>619</v>
+      </c>
+      <c r="E15" s="9" t="s">
+        <v>647</v>
+      </c>
+      <c r="F15" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="G15" s="9">
+        <v>115</v>
+      </c>
+      <c r="H15" s="9">
+        <v>25</v>
+      </c>
+      <c r="I15" s="9">
+        <f t="shared" si="0"/>
+        <v>90</v>
+      </c>
+      <c r="J15" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="K15" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L15" s="9" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>643</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>620</v>
+      </c>
+      <c r="E16" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="F16" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="G16" s="9">
+        <v>1325</v>
+      </c>
+      <c r="H16" s="9">
+        <v>25</v>
+      </c>
+      <c r="I16" s="9">
+        <f t="shared" si="0"/>
+        <v>1300</v>
+      </c>
+      <c r="J16" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="K16" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L16" s="9" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>621</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>622</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>654</v>
+      </c>
+      <c r="F17" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="G17" s="7">
+        <v>620</v>
+      </c>
+      <c r="H17" s="7">
+        <v>30</v>
+      </c>
+      <c r="I17" s="7">
+        <f t="shared" si="0"/>
+        <v>590</v>
+      </c>
+      <c r="J17" s="7" t="s">
+        <v>596</v>
+      </c>
+      <c r="K17" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L17" s="7" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>623</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="F18" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="G18" s="7">
+        <v>820</v>
+      </c>
+      <c r="H18" s="7">
+        <v>30</v>
+      </c>
+      <c r="I18" s="7">
+        <f t="shared" si="0"/>
+        <v>790</v>
+      </c>
+      <c r="J18" s="7" t="s">
+        <v>596</v>
+      </c>
+      <c r="K18" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L18" s="7" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>624</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>625</v>
+      </c>
+      <c r="E19" s="9" t="s">
+        <v>626</v>
+      </c>
+      <c r="F19" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="G19" s="9">
+        <v>765</v>
+      </c>
+      <c r="H19" s="9">
+        <v>25</v>
+      </c>
+      <c r="I19" s="9">
+        <f t="shared" si="0"/>
+        <v>740</v>
+      </c>
+      <c r="J19" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="K19" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L19" s="9" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>627</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>628</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>641</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3">
+        <v>30</v>
+      </c>
+      <c r="I20" s="3">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L20" s="3" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>629</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>630</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>640</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="G21" s="3">
+        <v>695</v>
+      </c>
+      <c r="H21" s="3">
+        <v>25</v>
+      </c>
+      <c r="I21" s="3">
+        <f t="shared" si="0"/>
+        <v>670</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K21" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L21" s="3" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>631</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>632</v>
+      </c>
+      <c r="F22" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="G22" s="7">
+        <v>1110</v>
+      </c>
+      <c r="H22" s="7">
+        <v>30</v>
+      </c>
+      <c r="I22" s="7">
+        <f t="shared" si="0"/>
+        <v>1080</v>
+      </c>
+      <c r="J22" s="7" t="s">
+        <v>596</v>
+      </c>
+      <c r="K22" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L22" s="7" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="B23" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C23" s="9" t="s">
+        <v>633</v>
+      </c>
+      <c r="E23" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="F23" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="G23" s="9">
+        <v>30</v>
+      </c>
+      <c r="H23" s="9">
+        <v>30</v>
+      </c>
+      <c r="I23" s="9">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J23" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="K23" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L23" s="9" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>649</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>650</v>
+      </c>
+      <c r="F24" s="8" t="s">
+        <v>297</v>
+      </c>
+      <c r="G24" s="7">
+        <v>45</v>
+      </c>
+      <c r="H24" s="7">
+        <v>45</v>
+      </c>
+      <c r="I24" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J24" s="7" t="s">
+        <v>596</v>
+      </c>
+      <c r="K24" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L24" s="7" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>634</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>635</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="G25" s="3">
+        <v>4895</v>
+      </c>
+      <c r="H25" s="3">
+        <v>35</v>
+      </c>
+      <c r="I25" s="3">
+        <f t="shared" si="0"/>
+        <v>4860</v>
+      </c>
+      <c r="J25" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K25" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L25" s="3" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>639</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>638</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="G26" s="3">
+        <v>0</v>
+      </c>
+      <c r="H26" s="3">
+        <v>35</v>
+      </c>
+      <c r="I26" s="3">
+        <f t="shared" si="0"/>
+        <v>-35</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K26" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L26" s="3" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>637</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="G27" s="3">
+        <v>0</v>
+      </c>
+      <c r="H27" s="3">
+        <v>35</v>
+      </c>
+      <c r="I27" s="3">
+        <f t="shared" si="0"/>
+        <v>-35</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K27" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L27" s="3" t="s">
+        <v>592</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/data/Apr/Data.xlsx
+++ b/data/Apr/Data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Freelance\TextInputter\data\Apr\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\TextExtractorTool\data\Apr\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3454F365-8E38-47E6-93B7-39359D1CE440}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79C841FD-2A31-4F42-9F2F-41CB83C05019}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-150" windowWidth="29040" windowHeight="15720" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01-04" sheetId="4" r:id="rId1"/>
@@ -22,6 +22,7 @@
     <sheet name="08-04" sheetId="11" r:id="rId7"/>
     <sheet name="09-04" sheetId="12" r:id="rId8"/>
     <sheet name="10-04" sheetId="13" r:id="rId9"/>
+    <sheet name="11-04" sheetId="14" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -44,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2835" uniqueCount="1007">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3181" uniqueCount="1125">
   <si>
     <t>THU 4</t>
   </si>
@@ -2674,12 +2675,27 @@
     <t>10-04-2026</t>
   </si>
   <si>
+    <t>Mr Thế</t>
+  </si>
+  <si>
     <t>27/5 Quách Văn Tuấn, F12</t>
   </si>
   <si>
     <t>TRANG LÊ</t>
   </si>
   <si>
+    <t>78 nguyễn duy trinh, P. Bình Trưng</t>
+  </si>
+  <si>
+    <t>107/189 Quang Trung</t>
+  </si>
+  <si>
+    <t>Mien Tran</t>
+  </si>
+  <si>
+    <t>Ngọc Hà</t>
+  </si>
+  <si>
     <t>HD009697</t>
   </si>
   <si>
@@ -2692,24 +2708,33 @@
     <t>HD009406</t>
   </si>
   <si>
+    <t>Toà Bora Bora, Diamond Island (Đảo Kim Cương), đường Trần Quý Kiên, Phường Bình Trưng</t>
+  </si>
+  <si>
+    <t>suzy fb Bei Bei</t>
+  </si>
+  <si>
+    <t>HD009942</t>
+  </si>
+  <si>
+    <t>256-258 Lý thường kiệt p14 ( chung cư xi grani) Lock A2</t>
+  </si>
+  <si>
+    <t>HD009826</t>
+  </si>
+  <si>
+    <t>Nguyễn Thị Kiều Hạnh</t>
+  </si>
+  <si>
+    <t>HD009945</t>
+  </si>
+  <si>
+    <t>606/7/12/18 hồ ngọc lãm bình trị đông b</t>
+  </si>
+  <si>
     <t>AT 10-04</t>
   </si>
   <si>
-    <t>suzy fb Bei Bei</t>
-  </si>
-  <si>
-    <t>HD009942</t>
-  </si>
-  <si>
-    <t>256-258 Lý thường kiệt p14 ( chung cư xi grani) Lock A2</t>
-  </si>
-  <si>
-    <t>Nguyễn Thị Kiều Hạnh</t>
-  </si>
-  <si>
-    <t>HD009945</t>
-  </si>
-  <si>
     <t>My My</t>
   </si>
   <si>
@@ -2725,6 +2750,9 @@
     <t>HD009753</t>
   </si>
   <si>
+    <t>Toà nhà lux 6...Vinhomes Golden River ( Bason), 2 Nguyễn Hữu Cảnh, P. Bến Nghé</t>
+  </si>
+  <si>
     <t>Trang Lê</t>
   </si>
   <si>
@@ -2740,6 +2768,12 @@
     <t>HD009818</t>
   </si>
   <si>
+    <t>416/4 Trường Sa, p2</t>
+  </si>
+  <si>
+    <t>My Ngô</t>
+  </si>
+  <si>
     <t>HD009834</t>
   </si>
   <si>
@@ -2773,12 +2807,18 @@
     <t>HD009606</t>
   </si>
   <si>
+    <t>270B, Lý Thường Kiệt, Khu Phố 1, Phường 6</t>
+  </si>
+  <si>
     <t>Linh Yên Nguyễn</t>
   </si>
   <si>
     <t>HD009817</t>
   </si>
   <si>
+    <t>22 phan sao nam p11</t>
+  </si>
+  <si>
     <t>Tiên Tiên</t>
   </si>
   <si>
@@ -2803,6 +2843,9 @@
     <t>HD009642</t>
   </si>
   <si>
+    <t>2 tân mỹ phường tân phú</t>
+  </si>
+  <si>
     <t>Kim Khánh</t>
   </si>
   <si>
@@ -2818,6 +2861,9 @@
     <t>HD010009</t>
   </si>
   <si>
+    <t>Nhà thuốc pharmacity số 10 thảo điền Thiện Phường thảo điền</t>
+  </si>
+  <si>
     <t>Alina Phạm</t>
   </si>
   <si>
@@ -2833,6 +2879,9 @@
     <t>HD009811</t>
   </si>
   <si>
+    <t>52 Phan Bá Vành, Cát Lái</t>
+  </si>
+  <si>
     <t>Nguyễn An Bình</t>
   </si>
   <si>
@@ -2848,6 +2897,9 @@
     <t>HD009943</t>
   </si>
   <si>
+    <t>765 Hồng bàng chung cư dhome</t>
+  </si>
+  <si>
     <t>Nguyễn Lê</t>
   </si>
   <si>
@@ -2863,6 +2915,12 @@
     <t>HD009398</t>
   </si>
   <si>
+    <t>Block A chung cư centana thủ thiêm 36 mai chí thọ phường an phú</t>
+  </si>
+  <si>
+    <t>Quyên</t>
+  </si>
+  <si>
     <t>HD009764</t>
   </si>
   <si>
@@ -2875,6 +2933,12 @@
     <t>HD010024</t>
   </si>
   <si>
+    <t>LD cc lenxington 67 mai chí thọ, an phú</t>
+  </si>
+  <si>
+    <t>HẬU (summer)</t>
+  </si>
+  <si>
     <t>HD009569</t>
   </si>
   <si>
@@ -2887,31 +2951,49 @@
     <t>HD009849</t>
   </si>
   <si>
+    <t>15/32/2 võ duy trinh</t>
+  </si>
+  <si>
     <t>Bông Bông</t>
   </si>
   <si>
     <t>HD009763</t>
   </si>
   <si>
+    <t>Sai gon riverside complex (block C1) Số 4 đảo trí phú thuận</t>
+  </si>
+  <si>
     <t>HD009882</t>
   </si>
   <si>
+    <t>131/12 bình trị đông phường bình trị đông</t>
+  </si>
+  <si>
     <t>C Hằng</t>
   </si>
   <si>
     <t>HD009870</t>
   </si>
   <si>
+    <t>9 Nguyễn Thị Minh Khai, p Sài Gòn (Ngay Đài truyền hình --TV)</t>
+  </si>
+  <si>
+    <t>CUS One Seven Eight Zero Zero- CUS17800 - insta socheatahun</t>
+  </si>
+  <si>
     <t>HD009716</t>
   </si>
   <si>
+    <t>270B Lý thường kiệt, khu phố 1, Phường 6</t>
+  </si>
+  <si>
     <t>Thy Mai</t>
   </si>
   <si>
     <t>HD009729</t>
   </si>
   <si>
-    <t>My Ngô</t>
+    <t>2 nguyên văn tưởng, phường tân phú . , chung cư the view revieta point</t>
   </si>
   <si>
     <t>HD009831</t>
@@ -2926,21 +3008,36 @@
     <t>HD009722</t>
   </si>
   <si>
+    <t>Chung cư kingdom 101 block c 334 tô hiến thành</t>
+  </si>
+  <si>
     <t>Hồ Hương</t>
   </si>
   <si>
     <t>HD009996</t>
   </si>
   <si>
+    <t>244/11 hong lac f11</t>
+  </si>
+  <si>
+    <t>Đinh Thiên Kim</t>
+  </si>
+  <si>
     <t>HD009727</t>
   </si>
   <si>
+    <t>55/10 đường 18D phường bình hưng hòa a</t>
+  </si>
+  <si>
     <t>Tâm</t>
   </si>
   <si>
     <t>HD009619</t>
   </si>
   <si>
+    <t>76 lạc long quân p3</t>
+  </si>
+  <si>
     <t>11</t>
   </si>
   <si>
@@ -2959,66 +3056,6 @@
     <t>HD009580</t>
   </si>
   <si>
-    <t>Mien Tran</t>
-  </si>
-  <si>
-    <t>Block A chung cư centana thủ thiêm 36 mai chí thọ phường an phú</t>
-  </si>
-  <si>
-    <t>107/189 Quang Trung</t>
-  </si>
-  <si>
-    <t>HẬU (summer)</t>
-  </si>
-  <si>
-    <t>15/32/2 võ duy trinh</t>
-  </si>
-  <si>
-    <t>Ngọc Hà</t>
-  </si>
-  <si>
-    <t>78 nguyễn duy trinh, P. Bình Trưng</t>
-  </si>
-  <si>
-    <t>52 Phan Bá Vành, Cát Lái</t>
-  </si>
-  <si>
-    <t>LD cc lenxington 67 mai chí thọ, an phú</t>
-  </si>
-  <si>
-    <t>HD009826</t>
-  </si>
-  <si>
-    <t>Mr Thế</t>
-  </si>
-  <si>
-    <t>Toà Bora Bora, Diamond Island (Đảo Kim Cương), đường Trần Quý Kiên, Phường Bình Trưng</t>
-  </si>
-  <si>
-    <t>Nhà thuốc pharmacity số 10 thảo điền Thiện Phường thảo điền</t>
-  </si>
-  <si>
-    <t>CUS One Seven Eight Zero Zero- CUS17800 - insta socheatahun</t>
-  </si>
-  <si>
-    <t>270B Lý thường kiệt, khu phố 1, Phường 6</t>
-  </si>
-  <si>
-    <t>9 Nguyễn Thị Minh Khai, p Sài Gòn (Ngay Đài truyền hình --TV)</t>
-  </si>
-  <si>
-    <t>270B, Lý Thường Kiệt, Khu Phố 1, Phường 6</t>
-  </si>
-  <si>
-    <t>416/4 Trường Sa, p2</t>
-  </si>
-  <si>
-    <t>Toà nhà lux 6...Vinhomes Golden River ( Bason), 2 Nguyễn Hữu Cảnh, P. Bến Nghé</t>
-  </si>
-  <si>
-    <t>Chung cư kingdom 101 block c 334 tô hiến thành</t>
-  </si>
-  <si>
     <t>284 nguyễn thiện thuật phường bàn cờ</t>
   </si>
   <si>
@@ -3031,40 +3068,358 @@
     <t>181 đường 79 tân quy</t>
   </si>
   <si>
-    <t>606/7/12/18 hồ ngọc lãm bình trị đông b</t>
-  </si>
-  <si>
-    <t>2 tân mỹ phường tân phú</t>
-  </si>
-  <si>
-    <t>Đinh Thiên Kim</t>
-  </si>
-  <si>
-    <t>55/10 đường 18D phường bình hưng hòa a</t>
-  </si>
-  <si>
-    <t>2 nguyên văn tưởng, phường tân phú . , chung cư the view revieta point</t>
-  </si>
-  <si>
-    <t>244/11 hong lac f11</t>
-  </si>
-  <si>
-    <t>765 Hồng bàng chung cư dhome</t>
-  </si>
-  <si>
-    <t>76 lạc long quân p3</t>
-  </si>
-  <si>
-    <t>22 phan sao nam p11</t>
-  </si>
-  <si>
-    <t>Sai gon riverside complex (block C1) Số 4 đảo trí phú thuận</t>
-  </si>
-  <si>
-    <t>131/12 bình trị đông phường bình trị đông</t>
-  </si>
-  <si>
-    <t>Quyên</t>
+    <t>NGAY 11-4</t>
+  </si>
+  <si>
+    <t>78 nguyen duy trinh, p Binh Trung</t>
+  </si>
+  <si>
+    <t>11-04-2026</t>
+  </si>
+  <si>
+    <t>HD010230</t>
+  </si>
+  <si>
+    <t>AT 11-04</t>
+  </si>
+  <si>
+    <t>chị my</t>
+  </si>
+  <si>
+    <t>HD010271</t>
+  </si>
+  <si>
+    <t>21/8 ly chinh thang</t>
+  </si>
+  <si>
+    <t>Minh fb Kim Hoa</t>
+  </si>
+  <si>
+    <t>HD010343</t>
+  </si>
+  <si>
+    <t>339/69 le van sỹ phương nhiêu Lộc</t>
+  </si>
+  <si>
+    <t>My Yên</t>
+  </si>
+  <si>
+    <t>HD010330</t>
+  </si>
+  <si>
+    <t>Thu Ly</t>
+  </si>
+  <si>
+    <t>HD010300</t>
+  </si>
+  <si>
+    <t>Mỹ Mỹ Mỹ</t>
+  </si>
+  <si>
+    <t>HD010212</t>
+  </si>
+  <si>
+    <t>Số 9 đường 5c bình hưng hoà a</t>
+  </si>
+  <si>
+    <t>Ruby Ha</t>
+  </si>
+  <si>
+    <t>HD010372</t>
+  </si>
+  <si>
+    <t>Nguyệt Quế</t>
+  </si>
+  <si>
+    <t>HD010075</t>
+  </si>
+  <si>
+    <t>Huyền beauty</t>
+  </si>
+  <si>
+    <t>HD010243</t>
+  </si>
+  <si>
+    <t>HD009949</t>
+  </si>
+  <si>
+    <t>NG Phúc</t>
+  </si>
+  <si>
+    <t>HD010229</t>
+  </si>
+  <si>
+    <t>12 Quốc Hương, Thảo Điền</t>
+  </si>
+  <si>
+    <t>Mỹ Phương</t>
+  </si>
+  <si>
+    <t>HDO10203</t>
+  </si>
+  <si>
+    <t>445 gia phú phường 1</t>
+  </si>
+  <si>
+    <t>Thi Thỏ</t>
+  </si>
+  <si>
+    <t>HD010074</t>
+  </si>
+  <si>
+    <t>338/5/7 Nguyễn Xí phường 13</t>
+  </si>
+  <si>
+    <t>Phiến Trương</t>
+  </si>
+  <si>
+    <t>HD010274</t>
+  </si>
+  <si>
+    <t>56/28b Thích quảng đức</t>
+  </si>
+  <si>
+    <t>Trần Mỹ Nhi</t>
+  </si>
+  <si>
+    <t>HD010278</t>
+  </si>
+  <si>
+    <t>408 nguyễn tri phương vườn lài</t>
+  </si>
+  <si>
+    <t>đức toàn fb hạ vi</t>
+  </si>
+  <si>
+    <t>HD010087</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>Hồng Diệu</t>
+  </si>
+  <si>
+    <t>HD010228</t>
+  </si>
+  <si>
+    <t>Saigon South Réidences Phước Kiểng</t>
+  </si>
+  <si>
+    <t>yumi kimthuy nguyễn fb kim hue</t>
+  </si>
+  <si>
+    <t>HD010051</t>
+  </si>
+  <si>
+    <t>125/12 lê văn phan phú thọ hòa</t>
+  </si>
+  <si>
+    <t>Tuyết Ngân</t>
+  </si>
+  <si>
+    <t>HD010385</t>
+  </si>
+  <si>
+    <t>la hồ biểu chánh phường 12</t>
+  </si>
+  <si>
+    <t>Lê thị giáng my</t>
+  </si>
+  <si>
+    <t>HD010076</t>
+  </si>
+  <si>
+    <t>Thảo Trần</t>
+  </si>
+  <si>
+    <t>HD010149</t>
+  </si>
+  <si>
+    <t>Anh Phượng</t>
+  </si>
+  <si>
+    <t>HD009656</t>
+  </si>
+  <si>
+    <t>248/27 p8 nguyễn văn khối</t>
+  </si>
+  <si>
+    <t>Thao My</t>
+  </si>
+  <si>
+    <t>HD009836</t>
+  </si>
+  <si>
+    <t>xiao yan</t>
+  </si>
+  <si>
+    <t>HD010007</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>Ms. Yến</t>
+  </si>
+  <si>
+    <t>HD009651</t>
+  </si>
+  <si>
+    <t>Phương Nhi</t>
+  </si>
+  <si>
+    <t>Linh - fb Nguyễn Anna</t>
+  </si>
+  <si>
+    <t>HD010124</t>
+  </si>
+  <si>
+    <t>Cherry Charm</t>
+  </si>
+  <si>
+    <t>HD010148</t>
+  </si>
+  <si>
+    <t>Hoàng Thu Thủy</t>
+  </si>
+  <si>
+    <t>HD010299</t>
+  </si>
+  <si>
+    <t>58B Nguyễn Thị Thập, phường Bình Thuận</t>
+  </si>
+  <si>
+    <t>Dung</t>
+  </si>
+  <si>
+    <t>HD010141</t>
+  </si>
+  <si>
+    <t>HD010143</t>
+  </si>
+  <si>
+    <t>Thu Hồng</t>
+  </si>
+  <si>
+    <t>HD010144</t>
+  </si>
+  <si>
+    <t>117/17 nguyễn hữu cảnh p thạnh mỹ tây</t>
+  </si>
+  <si>
+    <t>HD010269</t>
+  </si>
+  <si>
+    <t>53 Phan Đình Phùng, P.5</t>
+  </si>
+  <si>
+    <t>HD010055</t>
+  </si>
+  <si>
+    <t>HD010179</t>
+  </si>
+  <si>
+    <t>Châu Nhi</t>
+  </si>
+  <si>
+    <t>HD010342</t>
+  </si>
+  <si>
+    <t>92b/17/15 tôn thất thuyết p15</t>
+  </si>
+  <si>
+    <t>Tiên Nguyễn</t>
+  </si>
+  <si>
+    <t>HD009832</t>
+  </si>
+  <si>
+    <t>Sunrise City toà A 33 Nguyễn Hữu Thọ Tân Hưng</t>
+  </si>
+  <si>
+    <t>Chúc fb Shi HeBe</t>
+  </si>
+  <si>
+    <t>25 đường 61, Thạnh Mỹ Lợi</t>
+  </si>
+  <si>
+    <t>334/33/1C Chu văn an, phường 12</t>
+  </si>
+  <si>
+    <t>71 đường 44 tam bình, phường tam phú</t>
+  </si>
+  <si>
+    <t>Mỹ Hảo</t>
+  </si>
+  <si>
+    <t>145/9 đỗ xuân hợp phước long b</t>
+  </si>
+  <si>
+    <t>36/15 yên thế, phường tân sơn</t>
+  </si>
+  <si>
+    <t>346 Bến Vân đồn f1 Chung cư Gold View</t>
+  </si>
+  <si>
+    <t>Phòng khám thẩm mỹ 12Bis Phan kế Bính, Phường Dakao</t>
+  </si>
+  <si>
+    <t>số 15 lê trực bình tiên</t>
+  </si>
+  <si>
+    <t>160 Nam Kỳ Khởi Nghĩa, P. Xuân Hòa</t>
+  </si>
+  <si>
+    <t>346 bến vân đồn, phường vĩnh hội</t>
+  </si>
+  <si>
+    <t>134/1/4 bùi thị xuân p bến thành</t>
+  </si>
+  <si>
+    <t>HD010156</t>
+  </si>
+  <si>
+    <t>269 14/16 bà hom phường 13</t>
+  </si>
+  <si>
+    <t>749/14/3, Huỳnh Tấn Phát, Kp. 1, P. Phú Thuận</t>
+  </si>
+  <si>
+    <t>Bé Oanh</t>
+  </si>
+  <si>
+    <t>HD010381</t>
+  </si>
+  <si>
+    <t>841/4 quốc lộ 13 cũ hiệp bình trưng</t>
+  </si>
+  <si>
+    <t>114/4 Hương Lộ 80B, Khu Phố 7 Phường Hiệp Thành</t>
+  </si>
+  <si>
+    <t>HD010197</t>
+  </si>
+  <si>
+    <t>27duơng số 1 khu phố 5 tân tạo a</t>
+  </si>
+  <si>
+    <t>Tên Thúy Phượng</t>
+  </si>
+  <si>
+    <t>206/40 đồng đen F14</t>
+  </si>
+  <si>
+    <t>Oanh Trương</t>
+  </si>
+  <si>
+    <t>31 đường 6b khu trung sơn</t>
+  </si>
+  <si>
+    <t>sunrise wi, 25 nguyễn hữu thọ, tân hưng</t>
+  </si>
+  <si>
+    <t>22, ĐƯỜNG TÂN THỚI NHẤT 1B, Phường Đông Hưng Thuận</t>
   </si>
 </sst>
 </file>
@@ -3164,7 +3519,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -3186,6 +3541,7 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4315,6 +4671,1813 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
+  <dimension ref="A1:Q43"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="30.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="76.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B1" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1007</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A2" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="H2" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="I2" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J2" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="K2" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="L2" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="M2" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="N2" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="O2" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="P2" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q2" s="17"/>
+    </row>
+    <row r="3" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="18" t="s">
+        <v>85</v>
+      </c>
+      <c r="B3" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="18" t="s">
+        <v>878</v>
+      </c>
+      <c r="D3" s="18"/>
+      <c r="E3" s="18" t="s">
+        <v>1008</v>
+      </c>
+      <c r="F3" s="18">
+        <v>2</v>
+      </c>
+      <c r="G3" s="18">
+        <v>35</v>
+      </c>
+      <c r="H3" s="18">
+        <v>35</v>
+      </c>
+      <c r="I3" s="18">
+        <f t="shared" ref="I3:I43" si="0">G3-H3</f>
+        <v>0</v>
+      </c>
+      <c r="J3" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="K3" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="L3" s="18" t="s">
+        <v>1009</v>
+      </c>
+      <c r="M3" s="18"/>
+      <c r="N3" s="18"/>
+      <c r="O3" s="18"/>
+      <c r="P3" s="18"/>
+      <c r="Q3" s="18"/>
+    </row>
+    <row r="4" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="18" t="s">
+        <v>85</v>
+      </c>
+      <c r="B4" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="18" t="s">
+        <v>296</v>
+      </c>
+      <c r="D4" s="18"/>
+      <c r="E4" s="18" t="s">
+        <v>297</v>
+      </c>
+      <c r="F4" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="G4" s="18">
+        <v>30</v>
+      </c>
+      <c r="H4" s="18">
+        <v>30</v>
+      </c>
+      <c r="I4" s="18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J4" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="K4" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="L4" s="18" t="s">
+        <v>1009</v>
+      </c>
+      <c r="M4" s="18"/>
+      <c r="N4" s="18"/>
+      <c r="O4" s="18"/>
+      <c r="P4" s="18"/>
+      <c r="Q4" s="18"/>
+    </row>
+    <row r="5" spans="1:17" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="20"/>
+      <c r="B5" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="20" t="s">
+        <v>659</v>
+      </c>
+      <c r="D5" s="20" t="s">
+        <v>1010</v>
+      </c>
+      <c r="E5" s="20" t="s">
+        <v>661</v>
+      </c>
+      <c r="F5" s="20" t="s">
+        <v>763</v>
+      </c>
+      <c r="G5" s="20">
+        <v>0</v>
+      </c>
+      <c r="H5" s="20">
+        <v>25</v>
+      </c>
+      <c r="I5" s="20">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J5" s="20" t="s">
+        <v>1011</v>
+      </c>
+      <c r="K5" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="L5" s="20" t="s">
+        <v>1009</v>
+      </c>
+      <c r="M5" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="N5" s="20"/>
+      <c r="O5" s="20"/>
+      <c r="P5" s="20"/>
+      <c r="Q5" s="20"/>
+    </row>
+    <row r="6" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="19"/>
+      <c r="B6" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="19" t="s">
+        <v>1012</v>
+      </c>
+      <c r="D6" s="19" t="s">
+        <v>1013</v>
+      </c>
+      <c r="E6" s="19" t="s">
+        <v>1014</v>
+      </c>
+      <c r="F6" s="19" t="s">
+        <v>790</v>
+      </c>
+      <c r="G6" s="19">
+        <v>535</v>
+      </c>
+      <c r="H6" s="19">
+        <v>25</v>
+      </c>
+      <c r="I6" s="19">
+        <f t="shared" si="0"/>
+        <v>510</v>
+      </c>
+      <c r="J6" s="19" t="s">
+        <v>98</v>
+      </c>
+      <c r="K6" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="L6" s="19" t="s">
+        <v>1009</v>
+      </c>
+      <c r="M6" s="19"/>
+      <c r="N6" s="19"/>
+      <c r="O6" s="19"/>
+      <c r="P6" s="19"/>
+      <c r="Q6" s="19"/>
+    </row>
+    <row r="7" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="19"/>
+      <c r="B7" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="19" t="s">
+        <v>1015</v>
+      </c>
+      <c r="D7" s="19" t="s">
+        <v>1016</v>
+      </c>
+      <c r="E7" s="19" t="s">
+        <v>1017</v>
+      </c>
+      <c r="F7" s="19" t="s">
+        <v>790</v>
+      </c>
+      <c r="G7" s="19">
+        <v>1005</v>
+      </c>
+      <c r="H7" s="19">
+        <v>25</v>
+      </c>
+      <c r="I7" s="19">
+        <f t="shared" si="0"/>
+        <v>980</v>
+      </c>
+      <c r="J7" s="19" t="s">
+        <v>98</v>
+      </c>
+      <c r="K7" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="L7" s="19" t="s">
+        <v>1009</v>
+      </c>
+      <c r="M7" s="19"/>
+      <c r="N7" s="19"/>
+      <c r="O7" s="19"/>
+      <c r="P7" s="19"/>
+      <c r="Q7" s="19"/>
+    </row>
+    <row r="8" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="18"/>
+      <c r="B8" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="18" t="s">
+        <v>1018</v>
+      </c>
+      <c r="D8" s="18" t="s">
+        <v>1019</v>
+      </c>
+      <c r="E8" s="18" t="s">
+        <v>1099</v>
+      </c>
+      <c r="F8" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="G8" s="18">
+        <v>510</v>
+      </c>
+      <c r="H8" s="18">
+        <v>20</v>
+      </c>
+      <c r="I8" s="18">
+        <f t="shared" si="0"/>
+        <v>490</v>
+      </c>
+      <c r="J8" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="K8" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="L8" s="18" t="s">
+        <v>1009</v>
+      </c>
+      <c r="M8" s="18"/>
+      <c r="N8" s="18"/>
+      <c r="O8" s="18"/>
+      <c r="P8" s="18"/>
+      <c r="Q8" s="18"/>
+    </row>
+    <row r="9" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="19"/>
+      <c r="B9" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="19" t="s">
+        <v>1020</v>
+      </c>
+      <c r="D9" s="19" t="s">
+        <v>1021</v>
+      </c>
+      <c r="E9" s="19" t="s">
+        <v>1109</v>
+      </c>
+      <c r="F9" s="19" t="s">
+        <v>807</v>
+      </c>
+      <c r="G9" s="19">
+        <v>375</v>
+      </c>
+      <c r="H9" s="19">
+        <v>25</v>
+      </c>
+      <c r="I9" s="19">
+        <f t="shared" si="0"/>
+        <v>350</v>
+      </c>
+      <c r="J9" s="19" t="s">
+        <v>98</v>
+      </c>
+      <c r="K9" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="L9" s="19" t="s">
+        <v>1009</v>
+      </c>
+      <c r="M9" s="19"/>
+      <c r="N9" s="19"/>
+      <c r="O9" s="19"/>
+      <c r="P9" s="19"/>
+      <c r="Q9" s="19"/>
+    </row>
+    <row r="10" spans="1:17" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="20"/>
+      <c r="B10" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="20" t="s">
+        <v>1022</v>
+      </c>
+      <c r="D10" s="20" t="s">
+        <v>1023</v>
+      </c>
+      <c r="E10" s="20" t="s">
+        <v>1024</v>
+      </c>
+      <c r="F10" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="G10" s="20">
+        <v>390</v>
+      </c>
+      <c r="H10" s="20">
+        <v>30</v>
+      </c>
+      <c r="I10" s="20">
+        <f t="shared" si="0"/>
+        <v>360</v>
+      </c>
+      <c r="J10" s="20" t="s">
+        <v>1011</v>
+      </c>
+      <c r="K10" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="L10" s="20" t="s">
+        <v>1009</v>
+      </c>
+      <c r="M10" s="20"/>
+      <c r="N10" s="20"/>
+      <c r="O10" s="20"/>
+      <c r="P10" s="20"/>
+      <c r="Q10" s="20"/>
+    </row>
+    <row r="11" spans="1:17" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="20"/>
+      <c r="B11" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="20" t="s">
+        <v>1025</v>
+      </c>
+      <c r="D11" s="20" t="s">
+        <v>1026</v>
+      </c>
+      <c r="E11" s="20" t="s">
+        <v>1112</v>
+      </c>
+      <c r="F11" s="20">
+        <v>7</v>
+      </c>
+      <c r="G11" s="20">
+        <v>0</v>
+      </c>
+      <c r="H11" s="20">
+        <v>30</v>
+      </c>
+      <c r="I11" s="20">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J11" s="20" t="s">
+        <v>1011</v>
+      </c>
+      <c r="K11" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="L11" s="20" t="s">
+        <v>1009</v>
+      </c>
+      <c r="M11" s="20"/>
+      <c r="N11" s="20"/>
+      <c r="O11" s="20"/>
+      <c r="P11" s="20"/>
+      <c r="Q11" s="20"/>
+    </row>
+    <row r="12" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="19"/>
+      <c r="B12" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" s="19" t="s">
+        <v>1027</v>
+      </c>
+      <c r="D12" s="19" t="s">
+        <v>1028</v>
+      </c>
+      <c r="E12" s="19" t="s">
+        <v>1108</v>
+      </c>
+      <c r="F12" s="19" t="s">
+        <v>811</v>
+      </c>
+      <c r="G12" s="19">
+        <v>845</v>
+      </c>
+      <c r="H12" s="19">
+        <v>25</v>
+      </c>
+      <c r="I12" s="19">
+        <f t="shared" si="0"/>
+        <v>820</v>
+      </c>
+      <c r="J12" s="19" t="s">
+        <v>98</v>
+      </c>
+      <c r="K12" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="L12" s="19" t="s">
+        <v>1009</v>
+      </c>
+      <c r="M12" s="19"/>
+      <c r="N12" s="19"/>
+      <c r="O12" s="19"/>
+      <c r="P12" s="19"/>
+      <c r="Q12" s="19"/>
+    </row>
+    <row r="13" spans="1:17" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="20"/>
+      <c r="B13" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" s="20" t="s">
+        <v>1113</v>
+      </c>
+      <c r="D13" s="20" t="s">
+        <v>1114</v>
+      </c>
+      <c r="E13" s="20" t="s">
+        <v>1115</v>
+      </c>
+      <c r="F13" s="20" t="s">
+        <v>116</v>
+      </c>
+      <c r="G13" s="20">
+        <v>0</v>
+      </c>
+      <c r="H13" s="20">
+        <v>30</v>
+      </c>
+      <c r="I13" s="20">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J13" s="20" t="s">
+        <v>1011</v>
+      </c>
+      <c r="K13" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="L13" s="20" t="s">
+        <v>1009</v>
+      </c>
+      <c r="M13" s="20"/>
+      <c r="N13" s="20"/>
+      <c r="O13" s="20"/>
+      <c r="P13" s="20"/>
+      <c r="Q13" s="20"/>
+    </row>
+    <row r="14" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="19"/>
+      <c r="B14" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" s="19" t="s">
+        <v>1029</v>
+      </c>
+      <c r="D14" s="19" t="s">
+        <v>1030</v>
+      </c>
+      <c r="E14" s="19" t="s">
+        <v>1103</v>
+      </c>
+      <c r="F14" s="19" t="s">
+        <v>88</v>
+      </c>
+      <c r="G14" s="19">
+        <v>0</v>
+      </c>
+      <c r="H14" s="19">
+        <v>25</v>
+      </c>
+      <c r="I14" s="19">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J14" s="19" t="s">
+        <v>98</v>
+      </c>
+      <c r="K14" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="L14" s="19" t="s">
+        <v>1009</v>
+      </c>
+      <c r="M14" s="19"/>
+      <c r="N14" s="19"/>
+      <c r="O14" s="19"/>
+      <c r="P14" s="19"/>
+      <c r="Q14" s="19"/>
+    </row>
+    <row r="15" spans="1:17" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="20"/>
+      <c r="B15" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" s="20" t="s">
+        <v>1119</v>
+      </c>
+      <c r="D15" s="20" t="s">
+        <v>1031</v>
+      </c>
+      <c r="E15" s="20" t="s">
+        <v>1120</v>
+      </c>
+      <c r="F15" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="G15" s="20">
+        <v>0</v>
+      </c>
+      <c r="H15" s="20">
+        <v>25</v>
+      </c>
+      <c r="I15" s="20">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J15" s="20" t="s">
+        <v>1011</v>
+      </c>
+      <c r="K15" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="L15" s="20" t="s">
+        <v>1009</v>
+      </c>
+      <c r="M15" s="20"/>
+      <c r="N15" s="20"/>
+      <c r="O15" s="20"/>
+      <c r="P15" s="20"/>
+      <c r="Q15" s="20"/>
+    </row>
+    <row r="16" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="18"/>
+      <c r="B16" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="C16" s="18" t="s">
+        <v>1032</v>
+      </c>
+      <c r="D16" s="18" t="s">
+        <v>1033</v>
+      </c>
+      <c r="E16" s="18" t="s">
+        <v>1034</v>
+      </c>
+      <c r="F16" s="18" t="s">
+        <v>768</v>
+      </c>
+      <c r="G16" s="18">
+        <v>520</v>
+      </c>
+      <c r="H16" s="18">
+        <v>30</v>
+      </c>
+      <c r="I16" s="18">
+        <f t="shared" si="0"/>
+        <v>490</v>
+      </c>
+      <c r="J16" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="K16" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="L16" s="18" t="s">
+        <v>1009</v>
+      </c>
+      <c r="M16" s="18"/>
+      <c r="N16" s="18"/>
+      <c r="O16" s="18"/>
+      <c r="P16" s="18"/>
+      <c r="Q16" s="18"/>
+    </row>
+    <row r="17" spans="1:17" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="20"/>
+      <c r="B17" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" s="20" t="s">
+        <v>1035</v>
+      </c>
+      <c r="D17" s="20" t="s">
+        <v>1036</v>
+      </c>
+      <c r="E17" s="20" t="s">
+        <v>1037</v>
+      </c>
+      <c r="F17" s="20" t="s">
+        <v>763</v>
+      </c>
+      <c r="G17" s="20">
+        <v>915</v>
+      </c>
+      <c r="H17" s="20">
+        <v>25</v>
+      </c>
+      <c r="I17" s="20">
+        <f t="shared" si="0"/>
+        <v>890</v>
+      </c>
+      <c r="J17" s="20" t="s">
+        <v>1011</v>
+      </c>
+      <c r="K17" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="L17" s="20" t="s">
+        <v>1009</v>
+      </c>
+      <c r="M17" s="20"/>
+      <c r="N17" s="20"/>
+      <c r="O17" s="20"/>
+      <c r="P17" s="20"/>
+      <c r="Q17" s="20"/>
+    </row>
+    <row r="18" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="18"/>
+      <c r="B18" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="C18" s="18" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D18" s="18" t="s">
+        <v>1039</v>
+      </c>
+      <c r="E18" s="18" t="s">
+        <v>1040</v>
+      </c>
+      <c r="F18" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="G18" s="18">
+        <v>510</v>
+      </c>
+      <c r="H18" s="18">
+        <v>20</v>
+      </c>
+      <c r="I18" s="18">
+        <f t="shared" si="0"/>
+        <v>490</v>
+      </c>
+      <c r="J18" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="K18" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="L18" s="18" t="s">
+        <v>1009</v>
+      </c>
+      <c r="M18" s="18"/>
+      <c r="N18" s="18"/>
+      <c r="O18" s="18"/>
+      <c r="P18" s="18"/>
+      <c r="Q18" s="18"/>
+    </row>
+    <row r="19" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="19"/>
+      <c r="B19" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="C19" s="19" t="s">
+        <v>1041</v>
+      </c>
+      <c r="D19" s="19" t="s">
+        <v>1042</v>
+      </c>
+      <c r="E19" s="19" t="s">
+        <v>1043</v>
+      </c>
+      <c r="F19" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="G19" s="19">
+        <v>560</v>
+      </c>
+      <c r="H19" s="19">
+        <v>20</v>
+      </c>
+      <c r="I19" s="19">
+        <f t="shared" si="0"/>
+        <v>540</v>
+      </c>
+      <c r="J19" s="19" t="s">
+        <v>98</v>
+      </c>
+      <c r="K19" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="L19" s="19" t="s">
+        <v>1009</v>
+      </c>
+      <c r="M19" s="19"/>
+      <c r="N19" s="19"/>
+      <c r="O19" s="19"/>
+      <c r="P19" s="19"/>
+      <c r="Q19" s="19"/>
+    </row>
+    <row r="20" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="19"/>
+      <c r="B20" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="C20" s="19" t="s">
+        <v>1044</v>
+      </c>
+      <c r="D20" s="19" t="s">
+        <v>1045</v>
+      </c>
+      <c r="E20" s="19" t="s">
+        <v>1046</v>
+      </c>
+      <c r="F20" s="19" t="s">
+        <v>824</v>
+      </c>
+      <c r="G20" s="19">
+        <v>445</v>
+      </c>
+      <c r="H20" s="19">
+        <v>25</v>
+      </c>
+      <c r="I20" s="19">
+        <f t="shared" si="0"/>
+        <v>420</v>
+      </c>
+      <c r="J20" s="19" t="s">
+        <v>98</v>
+      </c>
+      <c r="K20" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="L20" s="19" t="s">
+        <v>1009</v>
+      </c>
+      <c r="M20" s="19" t="s">
+        <v>68</v>
+      </c>
+      <c r="N20" s="19"/>
+      <c r="O20" s="19"/>
+      <c r="P20" s="19"/>
+      <c r="Q20" s="19"/>
+    </row>
+    <row r="21" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="19"/>
+      <c r="B21" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="C21" s="19" t="s">
+        <v>1047</v>
+      </c>
+      <c r="D21" s="19" t="s">
+        <v>1048</v>
+      </c>
+      <c r="E21" s="19" t="s">
+        <v>1106</v>
+      </c>
+      <c r="F21" s="19" t="s">
+        <v>1049</v>
+      </c>
+      <c r="G21" s="19">
+        <v>515</v>
+      </c>
+      <c r="H21" s="19">
+        <v>25</v>
+      </c>
+      <c r="I21" s="19">
+        <f t="shared" si="0"/>
+        <v>490</v>
+      </c>
+      <c r="J21" s="19" t="s">
+        <v>98</v>
+      </c>
+      <c r="K21" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="L21" s="19" t="s">
+        <v>1009</v>
+      </c>
+      <c r="M21" s="19"/>
+      <c r="N21" s="19"/>
+      <c r="O21" s="19"/>
+      <c r="P21" s="19"/>
+      <c r="Q21" s="19"/>
+    </row>
+    <row r="22" spans="1:17" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="20"/>
+      <c r="B22" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="C22" s="20" t="s">
+        <v>1050</v>
+      </c>
+      <c r="D22" s="20" t="s">
+        <v>1051</v>
+      </c>
+      <c r="E22" s="20" t="s">
+        <v>1052</v>
+      </c>
+      <c r="F22" s="20" t="s">
+        <v>111</v>
+      </c>
+      <c r="G22" s="20">
+        <v>1365</v>
+      </c>
+      <c r="H22" s="20">
+        <v>35</v>
+      </c>
+      <c r="I22" s="20">
+        <f t="shared" si="0"/>
+        <v>1330</v>
+      </c>
+      <c r="J22" s="20" t="s">
+        <v>1011</v>
+      </c>
+      <c r="K22" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="L22" s="20" t="s">
+        <v>1009</v>
+      </c>
+      <c r="M22" s="20"/>
+      <c r="N22" s="20"/>
+      <c r="O22" s="20"/>
+      <c r="P22" s="20"/>
+      <c r="Q22" s="20"/>
+    </row>
+    <row r="23" spans="1:17" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="20"/>
+      <c r="B23" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="C23" s="20" t="s">
+        <v>1053</v>
+      </c>
+      <c r="D23" s="20" t="s">
+        <v>1054</v>
+      </c>
+      <c r="E23" s="20" t="s">
+        <v>1055</v>
+      </c>
+      <c r="F23" s="20" t="s">
+        <v>208</v>
+      </c>
+      <c r="G23" s="20">
+        <v>2970</v>
+      </c>
+      <c r="H23" s="20">
+        <v>30</v>
+      </c>
+      <c r="I23" s="20">
+        <f t="shared" si="0"/>
+        <v>2940</v>
+      </c>
+      <c r="J23" s="20" t="s">
+        <v>1011</v>
+      </c>
+      <c r="K23" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="L23" s="20" t="s">
+        <v>1009</v>
+      </c>
+      <c r="M23" s="20" t="s">
+        <v>361</v>
+      </c>
+      <c r="N23" s="20"/>
+      <c r="O23" s="20"/>
+      <c r="P23" s="20"/>
+      <c r="Q23" s="20"/>
+    </row>
+    <row r="24" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="19"/>
+      <c r="B24" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="C24" s="19" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D24" s="19" t="s">
+        <v>1057</v>
+      </c>
+      <c r="E24" s="19" t="s">
+        <v>1058</v>
+      </c>
+      <c r="F24" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="G24" s="19">
+        <v>1350</v>
+      </c>
+      <c r="H24" s="19">
+        <v>20</v>
+      </c>
+      <c r="I24" s="19">
+        <f t="shared" si="0"/>
+        <v>1330</v>
+      </c>
+      <c r="J24" s="19" t="s">
+        <v>98</v>
+      </c>
+      <c r="K24" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="L24" s="19" t="s">
+        <v>1009</v>
+      </c>
+      <c r="M24" s="19"/>
+      <c r="N24" s="19"/>
+      <c r="O24" s="19"/>
+      <c r="P24" s="19"/>
+      <c r="Q24" s="19"/>
+    </row>
+    <row r="25" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="18"/>
+      <c r="B25" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="C25" s="18" t="s">
+        <v>1059</v>
+      </c>
+      <c r="D25" s="18" t="s">
+        <v>1060</v>
+      </c>
+      <c r="E25" s="18" t="s">
+        <v>1100</v>
+      </c>
+      <c r="F25" s="18" t="s">
+        <v>116</v>
+      </c>
+      <c r="G25" s="18">
+        <v>470</v>
+      </c>
+      <c r="H25" s="18">
+        <v>30</v>
+      </c>
+      <c r="I25" s="18">
+        <f t="shared" si="0"/>
+        <v>440</v>
+      </c>
+      <c r="J25" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="K25" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="L25" s="18" t="s">
+        <v>1009</v>
+      </c>
+      <c r="M25" s="18"/>
+      <c r="N25" s="18"/>
+      <c r="O25" s="18"/>
+      <c r="P25" s="18"/>
+      <c r="Q25" s="18"/>
+    </row>
+    <row r="26" spans="1:17" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="20"/>
+      <c r="B26" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="C26" s="20" t="s">
+        <v>1061</v>
+      </c>
+      <c r="D26" s="20" t="s">
+        <v>1062</v>
+      </c>
+      <c r="E26" s="20" t="s">
+        <v>1123</v>
+      </c>
+      <c r="F26" s="20" t="s">
+        <v>800</v>
+      </c>
+      <c r="G26" s="20">
+        <v>1390</v>
+      </c>
+      <c r="H26" s="20">
+        <v>30</v>
+      </c>
+      <c r="I26" s="20">
+        <f t="shared" si="0"/>
+        <v>1360</v>
+      </c>
+      <c r="J26" s="20" t="s">
+        <v>1011</v>
+      </c>
+      <c r="K26" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="L26" s="20" t="s">
+        <v>1009</v>
+      </c>
+      <c r="M26" s="20"/>
+      <c r="N26" s="20"/>
+      <c r="O26" s="20"/>
+      <c r="P26" s="20"/>
+      <c r="Q26" s="20"/>
+    </row>
+    <row r="27" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="18"/>
+      <c r="B27" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="C27" s="18" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D27" s="18" t="s">
+        <v>1064</v>
+      </c>
+      <c r="E27" s="18" t="s">
+        <v>1065</v>
+      </c>
+      <c r="F27" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="G27" s="18">
+        <v>0</v>
+      </c>
+      <c r="H27" s="18">
+        <v>25</v>
+      </c>
+      <c r="I27" s="18">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J27" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="K27" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="L27" s="18" t="s">
+        <v>1009</v>
+      </c>
+      <c r="M27" s="18"/>
+      <c r="N27" s="18"/>
+      <c r="O27" s="18"/>
+      <c r="P27" s="18"/>
+      <c r="Q27" s="18"/>
+    </row>
+    <row r="28" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="19"/>
+      <c r="B28" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="C28" s="19" t="s">
+        <v>1066</v>
+      </c>
+      <c r="D28" s="19" t="s">
+        <v>1067</v>
+      </c>
+      <c r="E28" s="19" t="s">
+        <v>1104</v>
+      </c>
+      <c r="F28" s="19" t="s">
+        <v>811</v>
+      </c>
+      <c r="G28" s="19">
+        <v>785</v>
+      </c>
+      <c r="H28" s="19">
+        <v>25</v>
+      </c>
+      <c r="I28" s="19">
+        <f t="shared" si="0"/>
+        <v>760</v>
+      </c>
+      <c r="J28" s="19" t="s">
+        <v>98</v>
+      </c>
+      <c r="K28" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="L28" s="19" t="s">
+        <v>1009</v>
+      </c>
+      <c r="M28" s="19"/>
+      <c r="N28" s="19"/>
+      <c r="O28" s="19"/>
+      <c r="P28" s="19"/>
+      <c r="Q28" s="19"/>
+    </row>
+    <row r="29" spans="1:17" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="20"/>
+      <c r="B29" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="C29" s="20" t="s">
+        <v>1068</v>
+      </c>
+      <c r="D29" s="20" t="s">
+        <v>1069</v>
+      </c>
+      <c r="E29" s="20" t="s">
+        <v>1124</v>
+      </c>
+      <c r="F29" s="20" t="s">
+        <v>1070</v>
+      </c>
+      <c r="G29" s="20">
+        <v>890</v>
+      </c>
+      <c r="H29" s="20">
+        <v>30</v>
+      </c>
+      <c r="I29" s="20">
+        <f t="shared" si="0"/>
+        <v>860</v>
+      </c>
+      <c r="J29" s="20" t="s">
+        <v>1011</v>
+      </c>
+      <c r="K29" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="L29" s="20" t="s">
+        <v>1009</v>
+      </c>
+      <c r="M29" s="20"/>
+      <c r="N29" s="20"/>
+      <c r="O29" s="20"/>
+      <c r="P29" s="20"/>
+      <c r="Q29" s="20"/>
+    </row>
+    <row r="30" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="18"/>
+      <c r="B30" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="C30" s="18" t="s">
+        <v>1071</v>
+      </c>
+      <c r="D30" s="18" t="s">
+        <v>1072</v>
+      </c>
+      <c r="E30" s="18" t="s">
+        <v>1098</v>
+      </c>
+      <c r="F30" s="18" t="s">
+        <v>768</v>
+      </c>
+      <c r="G30" s="18">
+        <v>790</v>
+      </c>
+      <c r="H30" s="18">
+        <v>30</v>
+      </c>
+      <c r="I30" s="18">
+        <f t="shared" si="0"/>
+        <v>760</v>
+      </c>
+      <c r="J30" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="K30" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="L30" s="18" t="s">
+        <v>1009</v>
+      </c>
+      <c r="M30" s="18"/>
+      <c r="N30" s="18"/>
+      <c r="O30" s="18"/>
+      <c r="P30" s="18"/>
+      <c r="Q30" s="18"/>
+    </row>
+    <row r="31" spans="1:17" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="20"/>
+      <c r="B31" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="C31" s="20" t="s">
+        <v>1073</v>
+      </c>
+      <c r="D31" s="20" t="s">
+        <v>1117</v>
+      </c>
+      <c r="E31" s="20" t="s">
+        <v>1118</v>
+      </c>
+      <c r="F31" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="G31" s="20">
+        <v>1450</v>
+      </c>
+      <c r="H31" s="20">
+        <v>30</v>
+      </c>
+      <c r="I31" s="20">
+        <f t="shared" si="0"/>
+        <v>1420</v>
+      </c>
+      <c r="J31" s="20" t="s">
+        <v>1011</v>
+      </c>
+      <c r="K31" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="L31" s="20" t="s">
+        <v>1009</v>
+      </c>
+      <c r="M31" s="20"/>
+      <c r="N31" s="20"/>
+      <c r="O31" s="20"/>
+      <c r="P31" s="20"/>
+      <c r="Q31" s="20"/>
+    </row>
+    <row r="32" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="19"/>
+      <c r="B32" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="C32" s="19" t="s">
+        <v>1074</v>
+      </c>
+      <c r="D32" s="19" t="s">
+        <v>1075</v>
+      </c>
+      <c r="E32" s="19" t="s">
+        <v>1105</v>
+      </c>
+      <c r="F32" s="19" t="s">
+        <v>807</v>
+      </c>
+      <c r="G32" s="19">
+        <v>515</v>
+      </c>
+      <c r="H32" s="19">
+        <v>25</v>
+      </c>
+      <c r="I32" s="19">
+        <f t="shared" si="0"/>
+        <v>490</v>
+      </c>
+      <c r="J32" s="19" t="s">
+        <v>98</v>
+      </c>
+      <c r="K32" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="L32" s="19" t="s">
+        <v>1009</v>
+      </c>
+      <c r="M32" s="19"/>
+      <c r="N32" s="19"/>
+      <c r="O32" s="19"/>
+      <c r="P32" s="19"/>
+      <c r="Q32" s="19"/>
+    </row>
+    <row r="33" spans="1:17" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="20"/>
+      <c r="B33" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="C33" s="20" t="s">
+        <v>1076</v>
+      </c>
+      <c r="D33" s="20" t="s">
+        <v>1077</v>
+      </c>
+      <c r="E33" s="20" t="s">
+        <v>1116</v>
+      </c>
+      <c r="F33" s="20" t="s">
+        <v>1070</v>
+      </c>
+      <c r="G33" s="20">
+        <v>0</v>
+      </c>
+      <c r="H33" s="20">
+        <v>30</v>
+      </c>
+      <c r="I33" s="20">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J33" s="20" t="s">
+        <v>1011</v>
+      </c>
+      <c r="K33" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="L33" s="20" t="s">
+        <v>1009</v>
+      </c>
+      <c r="M33" s="20"/>
+      <c r="N33" s="20"/>
+      <c r="O33" s="20"/>
+      <c r="P33" s="20"/>
+      <c r="Q33" s="20"/>
+    </row>
+    <row r="34" spans="1:17" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="20"/>
+      <c r="B34" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="C34" s="20" t="s">
+        <v>1078</v>
+      </c>
+      <c r="D34" s="20" t="s">
+        <v>1079</v>
+      </c>
+      <c r="E34" s="20" t="s">
+        <v>1080</v>
+      </c>
+      <c r="F34" s="20" t="s">
+        <v>800</v>
+      </c>
+      <c r="G34" s="20">
+        <v>1120</v>
+      </c>
+      <c r="H34" s="20">
+        <v>30</v>
+      </c>
+      <c r="I34" s="20">
+        <f t="shared" si="0"/>
+        <v>1090</v>
+      </c>
+      <c r="J34" s="20" t="s">
+        <v>1011</v>
+      </c>
+      <c r="K34" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="L34" s="20" t="s">
+        <v>1009</v>
+      </c>
+      <c r="M34" s="20"/>
+      <c r="N34" s="20"/>
+      <c r="O34" s="20"/>
+      <c r="P34" s="20"/>
+      <c r="Q34" s="20"/>
+    </row>
+    <row r="35" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="19"/>
+      <c r="B35" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="C35" s="19" t="s">
+        <v>1081</v>
+      </c>
+      <c r="D35" s="19" t="s">
+        <v>1082</v>
+      </c>
+      <c r="E35" s="19" t="s">
+        <v>1107</v>
+      </c>
+      <c r="F35" s="19">
+        <v>3</v>
+      </c>
+      <c r="G35" s="19">
+        <v>0</v>
+      </c>
+      <c r="H35" s="19">
+        <v>25</v>
+      </c>
+      <c r="I35" s="19">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J35" s="19" t="s">
+        <v>98</v>
+      </c>
+      <c r="K35" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="L35" s="19" t="s">
+        <v>1009</v>
+      </c>
+      <c r="M35" s="19"/>
+      <c r="N35" s="19"/>
+      <c r="O35" s="19"/>
+      <c r="P35" s="19"/>
+      <c r="Q35" s="19"/>
+    </row>
+    <row r="36" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="21"/>
+      <c r="B36" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="C36" s="21" t="s">
+        <v>1101</v>
+      </c>
+      <c r="D36" s="21" t="s">
+        <v>1083</v>
+      </c>
+      <c r="E36" s="21" t="s">
+        <v>1102</v>
+      </c>
+      <c r="F36" s="21">
+        <v>9</v>
+      </c>
+      <c r="G36" s="21">
+        <v>1520</v>
+      </c>
+      <c r="H36" s="21">
+        <v>30</v>
+      </c>
+      <c r="I36" s="21">
+        <f t="shared" si="0"/>
+        <v>1490</v>
+      </c>
+      <c r="J36" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="K36" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="L36" s="21" t="s">
+        <v>1009</v>
+      </c>
+      <c r="M36" s="21"/>
+      <c r="N36" s="21"/>
+      <c r="O36" s="21"/>
+      <c r="P36" s="21"/>
+      <c r="Q36" s="21"/>
+    </row>
+    <row r="37" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="18"/>
+      <c r="B37" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="C37" s="18" t="s">
+        <v>1084</v>
+      </c>
+      <c r="D37" s="18" t="s">
+        <v>1085</v>
+      </c>
+      <c r="E37" s="18" t="s">
+        <v>1086</v>
+      </c>
+      <c r="F37" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="G37" s="18">
+        <v>910</v>
+      </c>
+      <c r="H37" s="18">
+        <v>20</v>
+      </c>
+      <c r="I37" s="18">
+        <f t="shared" si="0"/>
+        <v>890</v>
+      </c>
+      <c r="J37" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="K37" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="L37" s="18" t="s">
+        <v>1009</v>
+      </c>
+      <c r="M37" s="18"/>
+      <c r="N37" s="18"/>
+      <c r="O37" s="18"/>
+      <c r="P37" s="18"/>
+      <c r="Q37" s="18"/>
+    </row>
+    <row r="38" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="19"/>
+      <c r="B38" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="C38" s="19" t="s">
+        <v>896</v>
+      </c>
+      <c r="D38" s="19" t="s">
+        <v>1087</v>
+      </c>
+      <c r="E38" s="19" t="s">
+        <v>1088</v>
+      </c>
+      <c r="F38" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="G38" s="19">
+        <v>1110</v>
+      </c>
+      <c r="H38" s="19">
+        <v>20</v>
+      </c>
+      <c r="I38" s="19">
+        <f t="shared" si="0"/>
+        <v>1090</v>
+      </c>
+      <c r="J38" s="19" t="s">
+        <v>98</v>
+      </c>
+      <c r="K38" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="L38" s="19" t="s">
+        <v>1009</v>
+      </c>
+      <c r="M38" s="19"/>
+      <c r="N38" s="19"/>
+      <c r="O38" s="19"/>
+      <c r="P38" s="19"/>
+      <c r="Q38" s="19"/>
+    </row>
+    <row r="39" spans="1:17" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="20"/>
+      <c r="B39" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="C39" s="20" t="s">
+        <v>1121</v>
+      </c>
+      <c r="D39" s="20" t="s">
+        <v>1089</v>
+      </c>
+      <c r="E39" s="20" t="s">
+        <v>1122</v>
+      </c>
+      <c r="F39" s="20" t="s">
+        <v>143</v>
+      </c>
+      <c r="G39" s="20">
+        <v>925</v>
+      </c>
+      <c r="H39" s="20">
+        <v>35</v>
+      </c>
+      <c r="I39" s="20">
+        <f t="shared" si="0"/>
+        <v>890</v>
+      </c>
+      <c r="J39" s="20" t="s">
+        <v>1011</v>
+      </c>
+      <c r="K39" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="L39" s="20" t="s">
+        <v>1009</v>
+      </c>
+      <c r="M39" s="20"/>
+      <c r="N39" s="20"/>
+      <c r="O39" s="20"/>
+      <c r="P39" s="20"/>
+      <c r="Q39" s="20"/>
+    </row>
+    <row r="40" spans="1:17" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="20"/>
+      <c r="B40" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="C40" s="20" t="s">
+        <v>271</v>
+      </c>
+      <c r="D40" s="20" t="s">
+        <v>1090</v>
+      </c>
+      <c r="E40" s="20" t="s">
+        <v>973</v>
+      </c>
+      <c r="F40" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="G40" s="20">
+        <v>3250</v>
+      </c>
+      <c r="H40" s="20">
+        <v>35</v>
+      </c>
+      <c r="I40" s="20">
+        <f t="shared" si="0"/>
+        <v>3215</v>
+      </c>
+      <c r="J40" s="20" t="s">
+        <v>1011</v>
+      </c>
+      <c r="K40" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="L40" s="20" t="s">
+        <v>1009</v>
+      </c>
+      <c r="M40" s="20" t="s">
+        <v>361</v>
+      </c>
+      <c r="N40" s="20"/>
+      <c r="O40" s="20"/>
+      <c r="P40" s="20"/>
+      <c r="Q40" s="20"/>
+    </row>
+    <row r="41" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="19"/>
+      <c r="B41" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="C41" s="19" t="s">
+        <v>1091</v>
+      </c>
+      <c r="D41" s="19" t="s">
+        <v>1092</v>
+      </c>
+      <c r="E41" s="19" t="s">
+        <v>1093</v>
+      </c>
+      <c r="F41" s="19" t="s">
+        <v>811</v>
+      </c>
+      <c r="G41" s="19">
+        <v>715</v>
+      </c>
+      <c r="H41" s="19">
+        <v>25</v>
+      </c>
+      <c r="I41" s="19">
+        <f t="shared" si="0"/>
+        <v>690</v>
+      </c>
+      <c r="J41" s="19" t="s">
+        <v>98</v>
+      </c>
+      <c r="K41" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="L41" s="19" t="s">
+        <v>1009</v>
+      </c>
+      <c r="M41" s="19"/>
+      <c r="N41" s="19"/>
+      <c r="O41" s="19"/>
+      <c r="P41" s="19"/>
+      <c r="Q41" s="19"/>
+    </row>
+    <row r="42" spans="1:17" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="20"/>
+      <c r="B42" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="C42" s="20" t="s">
+        <v>1094</v>
+      </c>
+      <c r="D42" s="20" t="s">
+        <v>1095</v>
+      </c>
+      <c r="E42" s="20" t="s">
+        <v>1096</v>
+      </c>
+      <c r="F42" s="20" t="s">
+        <v>800</v>
+      </c>
+      <c r="G42" s="20">
+        <v>380</v>
+      </c>
+      <c r="H42" s="20">
+        <v>30</v>
+      </c>
+      <c r="I42" s="20">
+        <f t="shared" si="0"/>
+        <v>350</v>
+      </c>
+      <c r="J42" s="20" t="s">
+        <v>1011</v>
+      </c>
+      <c r="K42" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="L42" s="20" t="s">
+        <v>1009</v>
+      </c>
+      <c r="M42" s="20"/>
+      <c r="N42" s="20"/>
+      <c r="O42" s="20"/>
+      <c r="P42" s="20"/>
+      <c r="Q42" s="20"/>
+    </row>
+    <row r="43" spans="1:17" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="20"/>
+      <c r="B43" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="C43" s="20" t="s">
+        <v>1097</v>
+      </c>
+      <c r="D43" s="20" t="s">
+        <v>1110</v>
+      </c>
+      <c r="E43" s="20" t="s">
+        <v>1111</v>
+      </c>
+      <c r="F43" s="20" t="s">
+        <v>763</v>
+      </c>
+      <c r="G43" s="20">
+        <v>815</v>
+      </c>
+      <c r="H43" s="20">
+        <v>25</v>
+      </c>
+      <c r="I43" s="20">
+        <f t="shared" si="0"/>
+        <v>790</v>
+      </c>
+      <c r="J43" s="20" t="s">
+        <v>1011</v>
+      </c>
+      <c r="K43" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="L43" s="20" t="s">
+        <v>1009</v>
+      </c>
+      <c r="M43" s="20"/>
+      <c r="N43" s="20"/>
+      <c r="O43" s="20"/>
+      <c r="P43" s="20"/>
+      <c r="Q43" s="20"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CCBE8099-4F3D-4B80-A775-7DFD50F2A00C}">
   <dimension ref="A1:P25"/>
@@ -6426,7 +8589,7 @@
         <v>25</v>
       </c>
       <c r="I35" s="7">
-        <f t="shared" ref="I35:I66" si="1">G35-H35</f>
+        <f t="shared" ref="I35:I53" si="1">G35-H35</f>
         <v>660</v>
       </c>
       <c r="J35" s="7" t="s">
@@ -10110,7 +12273,7 @@
         <v>25</v>
       </c>
       <c r="I35" s="13">
-        <f t="shared" ref="I35:I66" si="1">G35-H35</f>
+        <f t="shared" ref="I35:I54" si="1">G35-H35</f>
         <v>1610</v>
       </c>
       <c r="J35" s="7" t="s">
@@ -15078,10 +17241,12 @@
   <dimension ref="A1:Q53"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="1" max="2" width="9.140625" customWidth="1"/>
     <col min="3" max="3" width="56.85546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.5703125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="112.7109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11.5703125" customWidth="1"/>
+    <col min="7" max="11" width="9.140625" customWidth="1"/>
     <col min="12" max="12" width="10.42578125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="13.7109375" bestFit="1" customWidth="1"/>
   </cols>
@@ -15169,7 +17334,7 @@
         <v>30</v>
       </c>
       <c r="I3" s="19">
-        <f>G3-H3</f>
+        <f t="shared" ref="I3:I34" si="0">G3-H3</f>
         <v>0</v>
       </c>
       <c r="J3" s="19" t="s">
@@ -15195,11 +17360,11 @@
         <v>18</v>
       </c>
       <c r="C4" s="18" t="s">
-        <v>981</v>
+        <v>876</v>
       </c>
       <c r="D4" s="18"/>
       <c r="E4" s="18" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="F4" s="18" t="s">
         <v>88</v>
@@ -15211,7 +17376,7 @@
         <v>30</v>
       </c>
       <c r="I4" s="18">
-        <f t="shared" ref="I4:I52" si="0">G4-H4</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J4" s="18" t="s">
@@ -15279,11 +17444,11 @@
         <v>18</v>
       </c>
       <c r="C6" s="18" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="D6" s="18"/>
       <c r="E6" s="18" t="s">
-        <v>977</v>
+        <v>879</v>
       </c>
       <c r="F6" s="18">
         <v>2</v>
@@ -15325,7 +17490,7 @@
       </c>
       <c r="D7" s="18"/>
       <c r="E7" s="18" t="s">
-        <v>973</v>
+        <v>880</v>
       </c>
       <c r="F7" s="18" t="s">
         <v>46</v>
@@ -15337,7 +17502,7 @@
         <v>25</v>
       </c>
       <c r="I7" s="18">
-        <f t="shared" ref="I7" si="1">G7-H7</f>
+        <f t="shared" si="0"/>
         <v>820</v>
       </c>
       <c r="J7" s="18" t="s">
@@ -15363,7 +17528,7 @@
         <v>18</v>
       </c>
       <c r="C8" s="18" t="s">
-        <v>971</v>
+        <v>881</v>
       </c>
       <c r="D8" s="18"/>
       <c r="E8" s="18" t="s">
@@ -15403,13 +17568,13 @@
         <v>18</v>
       </c>
       <c r="C9" s="18" t="s">
-        <v>976</v>
+        <v>882</v>
       </c>
       <c r="D9" s="18" t="s">
-        <v>878</v>
+        <v>883</v>
       </c>
       <c r="E9" s="18" t="s">
-        <v>879</v>
+        <v>884</v>
       </c>
       <c r="F9" s="18" t="s">
         <v>38</v>
@@ -15445,13 +17610,13 @@
         <v>18</v>
       </c>
       <c r="C10" s="18" t="s">
-        <v>880</v>
+        <v>885</v>
       </c>
       <c r="D10" s="18" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="E10" s="18" t="s">
-        <v>982</v>
+        <v>887</v>
       </c>
       <c r="F10" s="18">
         <v>2</v>
@@ -15487,13 +17652,13 @@
         <v>18</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>883</v>
+        <v>888</v>
       </c>
       <c r="D11" s="19" t="s">
-        <v>884</v>
+        <v>889</v>
       </c>
       <c r="E11" s="19" t="s">
-        <v>885</v>
+        <v>890</v>
       </c>
       <c r="F11" s="19" t="s">
         <v>824</v>
@@ -15532,7 +17697,7 @@
         <v>846</v>
       </c>
       <c r="D12" s="18" t="s">
-        <v>980</v>
+        <v>891</v>
       </c>
       <c r="E12" s="18" t="s">
         <v>848</v>
@@ -15571,13 +17736,13 @@
         <v>18</v>
       </c>
       <c r="C13" s="20" t="s">
-        <v>886</v>
+        <v>892</v>
       </c>
       <c r="D13" s="20" t="s">
-        <v>887</v>
+        <v>893</v>
       </c>
       <c r="E13" s="20" t="s">
-        <v>995</v>
+        <v>894</v>
       </c>
       <c r="F13" s="20" t="s">
         <v>22</v>
@@ -15593,7 +17758,7 @@
         <v>690</v>
       </c>
       <c r="J13" s="20" t="s">
-        <v>882</v>
+        <v>895</v>
       </c>
       <c r="K13" s="20" t="s">
         <v>24</v>
@@ -15613,13 +17778,13 @@
         <v>18</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>888</v>
+        <v>896</v>
       </c>
       <c r="D14" s="19" t="s">
-        <v>889</v>
+        <v>897</v>
       </c>
       <c r="E14" s="19" t="s">
-        <v>890</v>
+        <v>898</v>
       </c>
       <c r="F14" s="19" t="s">
         <v>81</v>
@@ -15655,13 +17820,13 @@
         <v>18</v>
       </c>
       <c r="C15" s="19" t="s">
-        <v>891</v>
+        <v>899</v>
       </c>
       <c r="D15" s="19" t="s">
-        <v>892</v>
+        <v>900</v>
       </c>
       <c r="E15" s="19" t="s">
-        <v>989</v>
+        <v>901</v>
       </c>
       <c r="F15" s="19">
         <v>1</v>
@@ -15697,13 +17862,13 @@
         <v>18</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>893</v>
+        <v>902</v>
       </c>
       <c r="D16" s="19" t="s">
-        <v>894</v>
+        <v>903</v>
       </c>
       <c r="E16" s="19" t="s">
-        <v>895</v>
+        <v>904</v>
       </c>
       <c r="F16" s="19" t="s">
         <v>88</v>
@@ -15739,13 +17904,13 @@
         <v>18</v>
       </c>
       <c r="C17" s="19" t="s">
-        <v>896</v>
+        <v>905</v>
       </c>
       <c r="D17" s="19" t="s">
-        <v>897</v>
+        <v>906</v>
       </c>
       <c r="E17" s="19" t="s">
-        <v>988</v>
+        <v>907</v>
       </c>
       <c r="F17" s="19" t="s">
         <v>81</v>
@@ -15781,13 +17946,13 @@
         <v>18</v>
       </c>
       <c r="C18" s="19" t="s">
-        <v>955</v>
+        <v>908</v>
       </c>
       <c r="D18" s="19" t="s">
-        <v>898</v>
+        <v>909</v>
       </c>
       <c r="E18" s="19" t="s">
-        <v>899</v>
+        <v>910</v>
       </c>
       <c r="F18" s="19" t="s">
         <v>807</v>
@@ -15825,13 +17990,13 @@
         <v>18</v>
       </c>
       <c r="C19" s="20" t="s">
-        <v>900</v>
+        <v>911</v>
       </c>
       <c r="D19" s="20" t="s">
-        <v>901</v>
+        <v>912</v>
       </c>
       <c r="E19" s="20" t="s">
-        <v>902</v>
+        <v>913</v>
       </c>
       <c r="F19" s="20" t="s">
         <v>763</v>
@@ -15847,7 +18012,7 @@
         <v>890</v>
       </c>
       <c r="J19" s="20" t="s">
-        <v>882</v>
+        <v>895</v>
       </c>
       <c r="K19" s="20" t="s">
         <v>24</v>
@@ -15870,7 +18035,7 @@
         <v>105</v>
       </c>
       <c r="D20" s="18" t="s">
-        <v>903</v>
+        <v>914</v>
       </c>
       <c r="E20" s="18" t="s">
         <v>107</v>
@@ -15914,7 +18079,7 @@
         <v>322</v>
       </c>
       <c r="D21" s="19" t="s">
-        <v>904</v>
+        <v>915</v>
       </c>
       <c r="E21" s="19" t="s">
         <v>324</v>
@@ -15956,10 +18121,10 @@
         <v>340</v>
       </c>
       <c r="D22" s="18" t="s">
-        <v>905</v>
+        <v>916</v>
       </c>
       <c r="E22" s="18" t="s">
-        <v>906</v>
+        <v>917</v>
       </c>
       <c r="F22" s="18" t="s">
         <v>46</v>
@@ -15995,13 +18160,13 @@
         <v>18</v>
       </c>
       <c r="C23" s="19" t="s">
-        <v>907</v>
+        <v>918</v>
       </c>
       <c r="D23" s="19" t="s">
-        <v>908</v>
+        <v>919</v>
       </c>
       <c r="E23" s="19" t="s">
-        <v>987</v>
+        <v>920</v>
       </c>
       <c r="F23" s="19" t="s">
         <v>88</v>
@@ -16037,13 +18202,13 @@
         <v>18</v>
       </c>
       <c r="C24" s="20" t="s">
-        <v>909</v>
+        <v>921</v>
       </c>
       <c r="D24" s="20" t="s">
-        <v>910</v>
+        <v>922</v>
       </c>
       <c r="E24" s="20" t="s">
-        <v>1003</v>
+        <v>923</v>
       </c>
       <c r="F24" s="20" t="s">
         <v>88</v>
@@ -16059,7 +18224,7 @@
         <v>0</v>
       </c>
       <c r="J24" s="20" t="s">
-        <v>882</v>
+        <v>895</v>
       </c>
       <c r="K24" s="20" t="s">
         <v>24</v>
@@ -16079,13 +18244,13 @@
         <v>18</v>
       </c>
       <c r="C25" s="20" t="s">
-        <v>911</v>
+        <v>924</v>
       </c>
       <c r="D25" s="20" t="s">
-        <v>912</v>
+        <v>925</v>
       </c>
       <c r="E25" s="20" t="s">
-        <v>913</v>
+        <v>926</v>
       </c>
       <c r="F25" s="20" t="s">
         <v>775</v>
@@ -16101,7 +18266,7 @@
         <v>2260</v>
       </c>
       <c r="J25" s="20" t="s">
-        <v>882</v>
+        <v>895</v>
       </c>
       <c r="K25" s="20" t="s">
         <v>24</v>
@@ -16121,13 +18286,13 @@
         <v>18</v>
       </c>
       <c r="C26" s="19" t="s">
-        <v>914</v>
+        <v>927</v>
       </c>
       <c r="D26" s="19" t="s">
-        <v>915</v>
+        <v>928</v>
       </c>
       <c r="E26" s="19" t="s">
-        <v>916</v>
+        <v>929</v>
       </c>
       <c r="F26" s="19" t="s">
         <v>790</v>
@@ -16163,13 +18328,13 @@
         <v>18</v>
       </c>
       <c r="C27" s="20" t="s">
-        <v>917</v>
+        <v>930</v>
       </c>
       <c r="D27" s="20" t="s">
-        <v>918</v>
+        <v>931</v>
       </c>
       <c r="E27" s="20" t="s">
-        <v>996</v>
+        <v>932</v>
       </c>
       <c r="F27" s="20" t="s">
         <v>800</v>
@@ -16185,7 +18350,7 @@
         <v>4090</v>
       </c>
       <c r="J27" s="20" t="s">
-        <v>882</v>
+        <v>895</v>
       </c>
       <c r="K27" s="20" t="s">
         <v>24</v>
@@ -16207,13 +18372,13 @@
         <v>18</v>
       </c>
       <c r="C28" s="18" t="s">
-        <v>919</v>
+        <v>933</v>
       </c>
       <c r="D28" s="18" t="s">
-        <v>920</v>
+        <v>934</v>
       </c>
       <c r="E28" s="18" t="s">
-        <v>921</v>
+        <v>935</v>
       </c>
       <c r="F28" s="18" t="s">
         <v>46</v>
@@ -16249,13 +18414,13 @@
         <v>18</v>
       </c>
       <c r="C29" s="18" t="s">
-        <v>922</v>
+        <v>936</v>
       </c>
       <c r="D29" s="18" t="s">
-        <v>923</v>
+        <v>937</v>
       </c>
       <c r="E29" s="18" t="s">
-        <v>983</v>
+        <v>938</v>
       </c>
       <c r="F29" s="18">
         <v>2</v>
@@ -16291,13 +18456,13 @@
         <v>18</v>
       </c>
       <c r="C30" s="19" t="s">
-        <v>924</v>
+        <v>939</v>
       </c>
       <c r="D30" s="19" t="s">
-        <v>925</v>
+        <v>940</v>
       </c>
       <c r="E30" s="19" t="s">
-        <v>926</v>
+        <v>941</v>
       </c>
       <c r="F30" s="19" t="s">
         <v>790</v>
@@ -16333,13 +18498,13 @@
         <v>18</v>
       </c>
       <c r="C31" s="18" t="s">
-        <v>927</v>
+        <v>942</v>
       </c>
       <c r="D31" s="18" t="s">
-        <v>928</v>
+        <v>943</v>
       </c>
       <c r="E31" s="18" t="s">
-        <v>978</v>
+        <v>944</v>
       </c>
       <c r="F31" s="18" t="s">
         <v>768</v>
@@ -16375,13 +18540,13 @@
         <v>18</v>
       </c>
       <c r="C32" s="18" t="s">
-        <v>929</v>
+        <v>945</v>
       </c>
       <c r="D32" s="18" t="s">
-        <v>930</v>
+        <v>946</v>
       </c>
       <c r="E32" s="18" t="s">
-        <v>931</v>
+        <v>947</v>
       </c>
       <c r="F32" s="18" t="s">
         <v>768</v>
@@ -16417,13 +18582,13 @@
         <v>18</v>
       </c>
       <c r="C33" s="20" t="s">
-        <v>932</v>
+        <v>948</v>
       </c>
       <c r="D33" s="20" t="s">
-        <v>933</v>
+        <v>949</v>
       </c>
       <c r="E33" s="20" t="s">
-        <v>1001</v>
+        <v>950</v>
       </c>
       <c r="F33" s="20" t="s">
         <v>763</v>
@@ -16439,7 +18604,7 @@
         <v>540</v>
       </c>
       <c r="J33" s="20" t="s">
-        <v>882</v>
+        <v>895</v>
       </c>
       <c r="K33" s="20" t="s">
         <v>24</v>
@@ -16459,13 +18624,13 @@
         <v>18</v>
       </c>
       <c r="C34" s="20" t="s">
-        <v>934</v>
+        <v>951</v>
       </c>
       <c r="D34" s="20" t="s">
-        <v>935</v>
+        <v>952</v>
       </c>
       <c r="E34" s="20" t="s">
-        <v>936</v>
+        <v>953</v>
       </c>
       <c r="F34" s="20" t="s">
         <v>208</v>
@@ -16481,7 +18646,7 @@
         <v>1510</v>
       </c>
       <c r="J34" s="20" t="s">
-        <v>882</v>
+        <v>895</v>
       </c>
       <c r="K34" s="20" t="s">
         <v>24</v>
@@ -16501,13 +18666,13 @@
         <v>18</v>
       </c>
       <c r="C35" s="18" t="s">
-        <v>937</v>
+        <v>954</v>
       </c>
       <c r="D35" s="18" t="s">
-        <v>938</v>
+        <v>955</v>
       </c>
       <c r="E35" s="18" t="s">
-        <v>972</v>
+        <v>956</v>
       </c>
       <c r="F35" s="18" t="s">
         <v>768</v>
@@ -16519,7 +18684,7 @@
         <v>30</v>
       </c>
       <c r="I35" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="I35:I53" si="1">G35-H35</f>
         <v>860</v>
       </c>
       <c r="J35" s="18" t="s">
@@ -16543,13 +18708,13 @@
         <v>18</v>
       </c>
       <c r="C36" s="18" t="s">
-        <v>1006</v>
+        <v>957</v>
       </c>
       <c r="D36" s="18" t="s">
-        <v>939</v>
+        <v>958</v>
       </c>
       <c r="E36" s="18" t="s">
-        <v>940</v>
+        <v>959</v>
       </c>
       <c r="F36" s="18" t="s">
         <v>88</v>
@@ -16561,7 +18726,7 @@
         <v>25</v>
       </c>
       <c r="I36" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>820</v>
       </c>
       <c r="J36" s="18" t="s">
@@ -16585,13 +18750,13 @@
         <v>18</v>
       </c>
       <c r="C37" s="18" t="s">
-        <v>941</v>
+        <v>960</v>
       </c>
       <c r="D37" s="18" t="s">
-        <v>942</v>
+        <v>961</v>
       </c>
       <c r="E37" s="18" t="s">
-        <v>979</v>
+        <v>962</v>
       </c>
       <c r="F37" s="18" t="s">
         <v>768</v>
@@ -16603,7 +18768,7 @@
         <v>30</v>
       </c>
       <c r="I37" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>670</v>
       </c>
       <c r="J37" s="18" t="s">
@@ -16627,13 +18792,13 @@
         <v>18</v>
       </c>
       <c r="C38" s="18" t="s">
-        <v>974</v>
+        <v>963</v>
       </c>
       <c r="D38" s="18" t="s">
-        <v>943</v>
+        <v>964</v>
       </c>
       <c r="E38" s="18" t="s">
-        <v>944</v>
+        <v>965</v>
       </c>
       <c r="F38" s="18" t="s">
         <v>46</v>
@@ -16645,7 +18810,7 @@
         <v>20</v>
       </c>
       <c r="I38" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1840</v>
       </c>
       <c r="J38" s="18" t="s">
@@ -16669,13 +18834,13 @@
         <v>18</v>
       </c>
       <c r="C39" s="18" t="s">
-        <v>945</v>
+        <v>966</v>
       </c>
       <c r="D39" s="18" t="s">
-        <v>946</v>
+        <v>967</v>
       </c>
       <c r="E39" s="18" t="s">
-        <v>975</v>
+        <v>968</v>
       </c>
       <c r="F39" s="18" t="s">
         <v>38</v>
@@ -16687,7 +18852,7 @@
         <v>20</v>
       </c>
       <c r="I39" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-20</v>
       </c>
       <c r="J39" s="18" t="s">
@@ -16711,13 +18876,13 @@
         <v>18</v>
       </c>
       <c r="C40" s="20" t="s">
-        <v>947</v>
+        <v>969</v>
       </c>
       <c r="D40" s="20" t="s">
-        <v>948</v>
+        <v>970</v>
       </c>
       <c r="E40" s="20" t="s">
-        <v>1004</v>
+        <v>971</v>
       </c>
       <c r="F40" s="20" t="s">
         <v>800</v>
@@ -16729,11 +18894,11 @@
         <v>30</v>
       </c>
       <c r="I40" s="20">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1880</v>
       </c>
       <c r="J40" s="20" t="s">
-        <v>882</v>
+        <v>895</v>
       </c>
       <c r="K40" s="20" t="s">
         <v>24</v>
@@ -16756,10 +18921,10 @@
         <v>271</v>
       </c>
       <c r="D41" s="20" t="s">
-        <v>949</v>
+        <v>972</v>
       </c>
       <c r="E41" s="20" t="s">
-        <v>1005</v>
+        <v>973</v>
       </c>
       <c r="F41" s="20" t="s">
         <v>22</v>
@@ -16771,11 +18936,11 @@
         <v>30</v>
       </c>
       <c r="I41" s="20">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>790</v>
       </c>
       <c r="J41" s="20" t="s">
-        <v>882</v>
+        <v>895</v>
       </c>
       <c r="K41" s="20" t="s">
         <v>24</v>
@@ -16795,13 +18960,13 @@
         <v>18</v>
       </c>
       <c r="C42" s="19" t="s">
-        <v>950</v>
+        <v>974</v>
       </c>
       <c r="D42" s="19" t="s">
-        <v>951</v>
+        <v>975</v>
       </c>
       <c r="E42" s="19" t="s">
-        <v>986</v>
+        <v>976</v>
       </c>
       <c r="F42" s="19">
         <v>1</v>
@@ -16813,7 +18978,7 @@
         <v>25</v>
       </c>
       <c r="I42" s="19">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-25</v>
       </c>
       <c r="J42" s="19" t="s">
@@ -16837,13 +19002,13 @@
         <v>18</v>
       </c>
       <c r="C43" s="19" t="s">
-        <v>984</v>
+        <v>977</v>
       </c>
       <c r="D43" s="19" t="s">
-        <v>952</v>
+        <v>978</v>
       </c>
       <c r="E43" s="19" t="s">
-        <v>985</v>
+        <v>979</v>
       </c>
       <c r="F43" s="19" t="s">
         <v>88</v>
@@ -16855,7 +19020,7 @@
         <v>25</v>
       </c>
       <c r="I43" s="19">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>820</v>
       </c>
       <c r="J43" s="19" t="s">
@@ -16879,13 +19044,13 @@
         <v>18</v>
       </c>
       <c r="C44" s="20" t="s">
-        <v>953</v>
+        <v>980</v>
       </c>
       <c r="D44" s="20" t="s">
-        <v>954</v>
+        <v>981</v>
       </c>
       <c r="E44" s="20" t="s">
-        <v>999</v>
+        <v>982</v>
       </c>
       <c r="F44" s="20" t="s">
         <v>800</v>
@@ -16897,11 +19062,11 @@
         <v>30</v>
       </c>
       <c r="I44" s="20">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>760</v>
       </c>
       <c r="J44" s="20" t="s">
-        <v>882</v>
+        <v>895</v>
       </c>
       <c r="K44" s="20" t="s">
         <v>24</v>
@@ -16921,13 +19086,13 @@
         <v>18</v>
       </c>
       <c r="C45" s="19" t="s">
-        <v>955</v>
+        <v>908</v>
       </c>
       <c r="D45" s="19" t="s">
-        <v>956</v>
+        <v>983</v>
       </c>
       <c r="E45" s="19" t="s">
-        <v>899</v>
+        <v>910</v>
       </c>
       <c r="F45" s="19" t="s">
         <v>807</v>
@@ -16939,7 +19104,7 @@
         <v>0</v>
       </c>
       <c r="I45" s="19">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1330</v>
       </c>
       <c r="J45" s="19" t="s">
@@ -16965,13 +19130,13 @@
         <v>18</v>
       </c>
       <c r="C46" s="19" t="s">
-        <v>893</v>
+        <v>902</v>
       </c>
       <c r="D46" s="19" t="s">
-        <v>957</v>
+        <v>984</v>
       </c>
       <c r="E46" s="19" t="s">
-        <v>895</v>
+        <v>904</v>
       </c>
       <c r="F46" s="19" t="s">
         <v>88</v>
@@ -16983,7 +19148,7 @@
         <v>25</v>
       </c>
       <c r="I46" s="19">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>760</v>
       </c>
       <c r="J46" s="19" t="s">
@@ -17007,13 +19172,13 @@
         <v>18</v>
       </c>
       <c r="C47" s="19" t="s">
-        <v>958</v>
+        <v>985</v>
       </c>
       <c r="D47" s="19" t="s">
-        <v>959</v>
+        <v>986</v>
       </c>
       <c r="E47" s="19" t="s">
-        <v>990</v>
+        <v>987</v>
       </c>
       <c r="F47" s="19" t="s">
         <v>824</v>
@@ -17025,7 +19190,7 @@
         <v>25</v>
       </c>
       <c r="I47" s="19">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>820</v>
       </c>
       <c r="J47" s="19" t="s">
@@ -17049,13 +19214,13 @@
         <v>18</v>
       </c>
       <c r="C48" s="20" t="s">
-        <v>960</v>
+        <v>988</v>
       </c>
       <c r="D48" s="20" t="s">
-        <v>961</v>
+        <v>989</v>
       </c>
       <c r="E48" s="20" t="s">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="F48" s="20" t="s">
         <v>88</v>
@@ -17067,11 +19232,11 @@
         <v>25</v>
       </c>
       <c r="I48" s="20">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>680</v>
       </c>
       <c r="J48" s="20" t="s">
-        <v>882</v>
+        <v>895</v>
       </c>
       <c r="K48" s="20" t="s">
         <v>24</v>
@@ -17091,13 +19256,13 @@
         <v>18</v>
       </c>
       <c r="C49" s="20" t="s">
-        <v>997</v>
+        <v>991</v>
       </c>
       <c r="D49" s="20" t="s">
-        <v>962</v>
+        <v>992</v>
       </c>
       <c r="E49" s="20" t="s">
-        <v>998</v>
+        <v>993</v>
       </c>
       <c r="F49" s="20" t="s">
         <v>22</v>
@@ -17109,11 +19274,11 @@
         <v>30</v>
       </c>
       <c r="I49" s="20">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>820</v>
       </c>
       <c r="J49" s="20" t="s">
-        <v>882</v>
+        <v>895</v>
       </c>
       <c r="K49" s="20" t="s">
         <v>24</v>
@@ -17133,16 +19298,16 @@
         <v>18</v>
       </c>
       <c r="C50" s="20" t="s">
-        <v>963</v>
+        <v>994</v>
       </c>
       <c r="D50" s="20" t="s">
-        <v>964</v>
+        <v>995</v>
       </c>
       <c r="E50" s="20" t="s">
-        <v>1002</v>
+        <v>996</v>
       </c>
       <c r="F50" s="20" t="s">
-        <v>965</v>
+        <v>997</v>
       </c>
       <c r="G50" s="20">
         <v>385</v>
@@ -17151,11 +19316,11 @@
         <v>25</v>
       </c>
       <c r="I50" s="20">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>360</v>
       </c>
       <c r="J50" s="20" t="s">
-        <v>882</v>
+        <v>895</v>
       </c>
       <c r="K50" s="20" t="s">
         <v>24</v>
@@ -17175,13 +19340,13 @@
         <v>18</v>
       </c>
       <c r="C51" s="18" t="s">
-        <v>966</v>
+        <v>998</v>
       </c>
       <c r="D51" s="18" t="s">
-        <v>967</v>
+        <v>999</v>
       </c>
       <c r="E51" s="18" t="s">
-        <v>968</v>
+        <v>1000</v>
       </c>
       <c r="F51" s="18" t="s">
         <v>88</v>
@@ -17193,7 +19358,7 @@
         <v>30</v>
       </c>
       <c r="I51" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2000</v>
       </c>
       <c r="J51" s="18" t="s">
@@ -17219,13 +19384,13 @@
         <v>18</v>
       </c>
       <c r="C52" s="19" t="s">
-        <v>969</v>
+        <v>1001</v>
       </c>
       <c r="D52" s="19" t="s">
-        <v>970</v>
+        <v>1002</v>
       </c>
       <c r="E52" s="19" t="s">
-        <v>991</v>
+        <v>1003</v>
       </c>
       <c r="F52" s="19">
         <v>3</v>
@@ -17237,7 +19402,7 @@
         <v>25</v>
       </c>
       <c r="I52" s="19">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>490</v>
       </c>
       <c r="J52" s="19" t="s">
@@ -17261,13 +19426,13 @@
         <v>18</v>
       </c>
       <c r="C53" s="20" t="s">
-        <v>992</v>
+        <v>1004</v>
       </c>
       <c r="D53" s="20" t="s">
-        <v>993</v>
+        <v>1005</v>
       </c>
       <c r="E53" s="20" t="s">
-        <v>994</v>
+        <v>1006</v>
       </c>
       <c r="F53" s="20">
         <v>7</v>
@@ -17279,11 +19444,11 @@
         <v>30</v>
       </c>
       <c r="I53" s="20">
-        <f t="shared" ref="I53" si="2">G53-H53</f>
+        <f t="shared" si="1"/>
         <v>790</v>
       </c>
       <c r="J53" s="20" t="s">
-        <v>882</v>
+        <v>895</v>
       </c>
       <c r="K53" s="20" t="s">
         <v>24</v>

--- a/data/Apr/Data.xlsx
+++ b/data/Apr/Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Freelance\TextInputter\data\Apr\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA85FAEC-EED7-4BA3-8EA7-28C0782D9BB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{855A097B-C30E-466F-949D-4A02803C5171}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01-04" sheetId="4" r:id="rId1"/>
@@ -26,6 +26,8 @@
     <sheet name="13-04" sheetId="15" r:id="rId11"/>
     <sheet name="14-04" sheetId="16" r:id="rId12"/>
     <sheet name="15-04" sheetId="17" r:id="rId13"/>
+    <sheet name="16-04" sheetId="18" r:id="rId14"/>
+    <sheet name="17-04" sheetId="19" r:id="rId15"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -48,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4212" uniqueCount="1422">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5064" uniqueCount="1677">
   <si>
     <t>THU 4</t>
   </si>
@@ -4133,12 +4135,18 @@
     <t>HD011460</t>
   </si>
   <si>
+    <t>103/23 cô giang phường cô giang</t>
+  </si>
+  <si>
     <t>Nguyễn Nhi</t>
   </si>
   <si>
     <t>HD011396</t>
   </si>
   <si>
+    <t>Vinhomes - phường long thạnh mỹ</t>
+  </si>
+  <si>
     <t>HD011457</t>
   </si>
   <si>
@@ -4175,6 +4183,9 @@
     <t>HD011625</t>
   </si>
   <si>
+    <t>16 kim ngân, khu dân cư phong phú 4, xã phong phú</t>
+  </si>
+  <si>
     <t>BN182 miki</t>
   </si>
   <si>
@@ -4220,6 +4231,9 @@
     <t>81/5B ấp Tam đông 3 xã thới tam thôn</t>
   </si>
   <si>
+    <t>Cẩm tú</t>
+  </si>
+  <si>
     <t>HD011498</t>
   </si>
   <si>
@@ -4253,15 +4267,24 @@
     <t>357/3 Trần Phú Phường 7</t>
   </si>
   <si>
+    <t>Thanh CU Hoàng</t>
+  </si>
+  <si>
     <t>HD011388</t>
   </si>
   <si>
+    <t>158/12 Trần Huy Liệu phường cầu kiệu</t>
+  </si>
+  <si>
     <t>Hs Út Hằng</t>
   </si>
   <si>
     <t>HD011539</t>
   </si>
   <si>
+    <t>28/1 nguyễn tri phương</t>
+  </si>
+  <si>
     <t>Nam Diep Hung Tue</t>
   </si>
   <si>
@@ -4274,53 +4297,797 @@
     <t>HD011391</t>
   </si>
   <si>
+    <t>189/46a Bạch Đằng, phường Hạnh Thông</t>
+  </si>
+  <si>
+    <t>linh sỉ lee</t>
+  </si>
+  <si>
+    <t>Số nhà 97A, đường 22, phường phước long</t>
+  </si>
+  <si>
+    <t>Ngọc</t>
+  </si>
+  <si>
+    <t>120/6 Lê Bình, phường Tân Sơn Nhất</t>
+  </si>
+  <si>
+    <t>Nguyễn Đắc Hội</t>
+  </si>
+  <si>
     <t>127/17 bình lợi p13</t>
   </si>
   <si>
-    <t>189/46a Bạch Đằng, phường Hạnh Thông</t>
-  </si>
-  <si>
-    <t>Nguyễn Đắc Hội</t>
-  </si>
-  <si>
-    <t>28/1 nguyễn tri phương</t>
-  </si>
-  <si>
-    <t>Thanh CU Hoàng</t>
-  </si>
-  <si>
-    <t>158/12 Trần Huy Liệu phường cầu kiệu</t>
-  </si>
-  <si>
-    <t>Ngọc</t>
-  </si>
-  <si>
-    <t>120/6 Lê Bình, phường Tân Sơn Nhất</t>
-  </si>
-  <si>
-    <t>103/23 cô giang phường cô giang</t>
-  </si>
-  <si>
-    <t>linh sỉ lee</t>
-  </si>
-  <si>
-    <t>Số nhà 97A, đường 22, phường phước long</t>
-  </si>
-  <si>
-    <t>Vinhomes - phường long thạnh mỹ</t>
-  </si>
-  <si>
-    <t>16 kim ngân, khu dân cư phong phú 4, xã phong phú</t>
-  </si>
-  <si>
-    <t>Cẩm tú</t>
+    <t>NGAY 16-4</t>
+  </si>
+  <si>
+    <t>Yin Nguyễn</t>
+  </si>
+  <si>
+    <t>HD011874</t>
+  </si>
+  <si>
+    <t>1164 đường số 16 p tân quy</t>
+  </si>
+  <si>
+    <t>AT 16-04</t>
+  </si>
+  <si>
+    <t>16-04-2026</t>
+  </si>
+  <si>
+    <t>Linh Đan</t>
+  </si>
+  <si>
+    <t>HD011649</t>
+  </si>
+  <si>
+    <t>107 nguyễn văn linh p tân thuận tây(cc eco green block D)</t>
+  </si>
+  <si>
+    <t>HD011796</t>
+  </si>
+  <si>
+    <t>Chị Ngân</t>
+  </si>
+  <si>
+    <t>HD011462</t>
+  </si>
+  <si>
+    <t>72 Lê Thánh Tôn</t>
+  </si>
+  <si>
+    <t>Ngọc Nguyễn</t>
+  </si>
+  <si>
+    <t>HD011701</t>
+  </si>
+  <si>
+    <t>132-134 Nguyễn Gia Trí, phường 25</t>
+  </si>
+  <si>
+    <t>Hỷ Hỷ</t>
+  </si>
+  <si>
+    <t>HD011465</t>
+  </si>
+  <si>
+    <t>42A mã lò bình trị đông A</t>
+  </si>
+  <si>
+    <t>Trang Nhã</t>
+  </si>
+  <si>
+    <t>HD011728</t>
+  </si>
+  <si>
+    <t>149A đường số 79 p Tân Quy</t>
+  </si>
+  <si>
+    <t>HD011711</t>
+  </si>
+  <si>
+    <t>B2 lý phục man phường bình thuận</t>
+  </si>
+  <si>
+    <t>ambodian Monyrothna Leng TKK 067234568 Postal code: 7</t>
+  </si>
+  <si>
+    <t>HD011629</t>
+  </si>
+  <si>
+    <t>154 tuệ tĩnh p12</t>
+  </si>
+  <si>
+    <t>Ai Quyên Mai ( QUANG)</t>
+  </si>
+  <si>
+    <t>HD011737</t>
+  </si>
+  <si>
+    <t>1/18 Nguyễn Văn Vĩnh, Phường 4</t>
+  </si>
+  <si>
+    <t>Hàn Bảo Xuyên</t>
+  </si>
+  <si>
+    <t>HD011745</t>
+  </si>
+  <si>
+    <t>2a đường 79 phường tân quy Spa HaiX</t>
+  </si>
+  <si>
+    <t>Trần Thương</t>
+  </si>
+  <si>
+    <t>HD011719</t>
+  </si>
+  <si>
+    <t>187/1 trần phú, phường chợ quán</t>
+  </si>
+  <si>
+    <t>HD011683</t>
+  </si>
+  <si>
+    <t>HD011875</t>
+  </si>
+  <si>
+    <t>169 Nguyễn thái học phường bến thành</t>
+  </si>
+  <si>
+    <t>Thu Huong</t>
+  </si>
+  <si>
+    <t>HD011944</t>
+  </si>
+  <si>
+    <t>cổng1 chung cư Emeral 1 Số 2- N4 Tân Sơn Nhì</t>
+  </si>
+  <si>
+    <t>Người nhận: Fb Phương Mai</t>
+  </si>
+  <si>
+    <t>HD011829</t>
+  </si>
+  <si>
+    <t>433/11/2 Lê Đức Thọ, Phường 17</t>
+  </si>
+  <si>
+    <t>HD011909</t>
+  </si>
+  <si>
+    <t>114/4 Hương Lộ 30B, khu phố 7, P. Hiệp Thành</t>
+  </si>
+  <si>
+    <t>siêng fb Nguyễn Đức Hùng</t>
+  </si>
+  <si>
+    <t>HD011883</t>
+  </si>
+  <si>
+    <t>Trung tâm trợ thính hearLIFE MEDEL: 476-478 Sư Vạn Hạnh, Phường 9</t>
+  </si>
+  <si>
+    <t>Minh Thơ</t>
+  </si>
+  <si>
+    <t>HD011741</t>
+  </si>
+  <si>
+    <t>12 đường số 41, bình thuận</t>
+  </si>
+  <si>
+    <t>My Tú</t>
+  </si>
+  <si>
+    <t>HD011740</t>
+  </si>
+  <si>
+    <t>130/4 gò dưa tam bình</t>
+  </si>
+  <si>
+    <t>Nguyễn thị nhung fb Yuna Tasaki</t>
+  </si>
+  <si>
+    <t>HD011754</t>
+  </si>
+  <si>
+    <t>21 lê văn lương Chung cư golden palm nhe Nguyễn thị nhung</t>
+  </si>
+  <si>
+    <t>tinh</t>
+  </si>
+  <si>
+    <t>hàng tỉnh</t>
+  </si>
+  <si>
+    <t>HD011877</t>
+  </si>
+  <si>
+    <t>Phạm Đào Ngọc Hà</t>
+  </si>
+  <si>
+    <t>HD011926</t>
+  </si>
+  <si>
+    <t>Nhà h15 kdc park riverside đường bưng ông thoàn phường phước long trường</t>
+  </si>
+  <si>
+    <t>Phuong Tram Ho</t>
+  </si>
+  <si>
+    <t>HD011766</t>
+  </si>
+  <si>
+    <t>Chung cư Empire city thủ thiêm, toà Tilia, đường D11</t>
+  </si>
+  <si>
+    <t>Nguyen Thuy Linh</t>
+  </si>
+  <si>
+    <t>HD011734</t>
+  </si>
+  <si>
+    <t>56 bến vân đồn, p13</t>
+  </si>
+  <si>
+    <t>Liên Hà</t>
+  </si>
+  <si>
+    <t>HD011950</t>
+  </si>
+  <si>
+    <t>92-94 nam kỳ khởi nghĩa- bến nghé</t>
+  </si>
+  <si>
+    <t>HD011720</t>
+  </si>
+  <si>
+    <t>Yến Như</t>
+  </si>
+  <si>
+    <t>HD011735</t>
+  </si>
+  <si>
+    <t>213 Bưng Ông Thoàn, Tăng Nhơn Phú B</t>
+  </si>
+  <si>
+    <t>Trang ( Nabi )</t>
+  </si>
+  <si>
+    <t>HD011951</t>
+  </si>
+  <si>
+    <t>262/57 Phan anh, Hiệp Tân</t>
+  </si>
+  <si>
+    <t>Phụng Phụng</t>
+  </si>
+  <si>
+    <t>HD011918</t>
+  </si>
+  <si>
+    <t>58/22/73 phan chu trinh p24</t>
+  </si>
+  <si>
+    <t>HD011824</t>
+  </si>
+  <si>
+    <t>thùy linh ALLINA</t>
+  </si>
+  <si>
+    <t>HD011925</t>
+  </si>
+  <si>
+    <t>276/169 thống nhất an hội đông</t>
+  </si>
+  <si>
+    <t>Mai Dinh</t>
+  </si>
+  <si>
+    <t>HD011635</t>
+  </si>
+  <si>
+    <t>165 cư xá PHÚ BÌNH, đường Lạc Long Quân, P5</t>
+  </si>
+  <si>
+    <t>Đoàn Ngọc</t>
+  </si>
+  <si>
+    <t>HD011937</t>
+  </si>
+  <si>
+    <t>nha khoa tâm đức 66/16 bình thành bình hưng hòa</t>
+  </si>
+  <si>
+    <t>(SS623- Meskill) SS Carg Shipping</t>
+  </si>
+  <si>
+    <t>HD011626</t>
+  </si>
+  <si>
+    <t>674 đường số 2, Phường 13</t>
+  </si>
+  <si>
+    <t>Choo You</t>
+  </si>
+  <si>
+    <t>HD011931</t>
+  </si>
+  <si>
+    <t>48/8/7 Ung Văn Khiêm, phường Thạnh Mỹ Tây</t>
+  </si>
+  <si>
+    <t>giao đồ cho hoa</t>
+  </si>
+  <si>
+    <t>HD011790</t>
+  </si>
+  <si>
+    <t>49/32/8a đường 51 p.14</t>
+  </si>
+  <si>
+    <t>Nguyễn Hân</t>
+  </si>
+  <si>
+    <t>HD011913</t>
+  </si>
+  <si>
+    <t>1069, lê đức anh, bình trị đông a</t>
+  </si>
+  <si>
+    <t>lindsiepham</t>
+  </si>
+  <si>
+    <t>HD011656</t>
+  </si>
+  <si>
+    <t>landmark 5b vinhomes central park</t>
+  </si>
+  <si>
+    <t>Nhật Lệ</t>
+  </si>
+  <si>
+    <t>HD011930</t>
+  </si>
+  <si>
+    <t>Block D, chung cư him lam phú an, 39 thuỷ lợi, phường Phước Long A</t>
+  </si>
+  <si>
+    <t>HD011705</t>
+  </si>
+  <si>
+    <t>Lan Anh Nguyen</t>
+  </si>
+  <si>
+    <t>HD011857</t>
+  </si>
+  <si>
+    <t>400/6 Ung Văn Khiêm, P25</t>
+  </si>
+  <si>
+    <t>Mỹ hảo</t>
+  </si>
+  <si>
+    <t>145/9 Đỗ Xuân Hợp Khu nhà trọ Phước Long B</t>
+  </si>
+  <si>
+    <t>KIỀU MY</t>
+  </si>
+  <si>
+    <t>27/10/3 đường 17, kp46, p. hiệp bình</t>
+  </si>
+  <si>
+    <t>Nguyễn Minh Hải</t>
+  </si>
+  <si>
+    <t>17 Đường Số 13 Bình Hưng Hoà</t>
+  </si>
+  <si>
+    <t>NOTE GỬI CHO SU ANH</t>
+  </si>
+  <si>
+    <t>119 Hoàng Diệu 2 linh trung</t>
+  </si>
+  <si>
+    <t>Quy</t>
+  </si>
+  <si>
+    <t>HD012000</t>
+  </si>
+  <si>
+    <t>S5.02 Vinhome Grandpark, Đường Nguyễn Xiển, phường Long Thạnh Mỹ</t>
+  </si>
+  <si>
+    <t>đơn cũ ck</t>
+  </si>
+  <si>
+    <t>NGAY 17-4</t>
+  </si>
+  <si>
+    <t>HD012112</t>
+  </si>
+  <si>
+    <t>Tháp B cc godview p1</t>
+  </si>
+  <si>
+    <t>17-04-2026</t>
+  </si>
+  <si>
+    <t>HD011758</t>
+  </si>
+  <si>
+    <t>66/12/6 phan huy ích p tân sơn</t>
+  </si>
+  <si>
+    <t>Yen Thi Kim Le</t>
+  </si>
+  <si>
+    <t>HD012249</t>
+  </si>
+  <si>
+    <t>549 Điện Biên Phủ bàn cờ</t>
+  </si>
+  <si>
+    <t>Phạm Thị Diễm Trinh</t>
+  </si>
+  <si>
+    <t>HD012321</t>
+  </si>
+  <si>
+    <t>AT 17-04</t>
+  </si>
+  <si>
+    <t>Thụy Hãn</t>
+  </si>
+  <si>
+    <t>HD012255</t>
+  </si>
+  <si>
+    <t>người nhận Tâm mini</t>
+  </si>
+  <si>
+    <t>HD012094</t>
+  </si>
+  <si>
+    <t>Lê Thị Thùy Hương</t>
+  </si>
+  <si>
+    <t>HD011985</t>
+  </si>
+  <si>
+    <t>15/40 ao đôi, p bình trị đông A</t>
+  </si>
+  <si>
+    <t>HD012087</t>
+  </si>
+  <si>
+    <t>Giang Phạm</t>
+  </si>
+  <si>
+    <t>HD012035</t>
+  </si>
+  <si>
+    <t>52 nguyễn văn trỗi p15</t>
+  </si>
+  <si>
+    <t>Thu Anh</t>
+  </si>
+  <si>
+    <t>HD012105</t>
+  </si>
+  <si>
+    <t>ksan hoàng tây phường 12</t>
+  </si>
+  <si>
+    <t>Ngô Thị Lài</t>
+  </si>
+  <si>
+    <t>HD012037</t>
+  </si>
+  <si>
+    <t>584 Bà Hạt P6</t>
+  </si>
+  <si>
+    <t>ZALLO KELLY</t>
+  </si>
+  <si>
+    <t>HD012336</t>
+  </si>
+  <si>
+    <t>Ng nhận Jen</t>
+  </si>
+  <si>
+    <t>HD012102</t>
+  </si>
+  <si>
+    <t>189/46a bạch đằng p3</t>
+  </si>
+  <si>
+    <t>Thu Thuỷ (Kim Ngân)</t>
+  </si>
+  <si>
+    <t>HD012209</t>
+  </si>
+  <si>
+    <t>Công ty đà nẵng Post Địa chỉ: B106 Bạch Đằng, Phường 2</t>
+  </si>
+  <si>
+    <t>Tuyet Nhung Nguyen</t>
+  </si>
+  <si>
+    <t>HD012341</t>
+  </si>
+  <si>
+    <t>HD012038</t>
+  </si>
+  <si>
+    <t>Trang lê</t>
+  </si>
+  <si>
+    <t>HD012347</t>
+  </si>
+  <si>
+    <t>BA Sông Thương P2</t>
+  </si>
+  <si>
+    <t>Tuyết Hoàng</t>
+  </si>
+  <si>
+    <t>HD012350</t>
+  </si>
+  <si>
+    <t>31 lê duẩn, bến nghé</t>
+  </si>
+  <si>
+    <t>Tường Vi</t>
+  </si>
+  <si>
+    <t>HD012273</t>
+  </si>
+  <si>
+    <t>325 phan xích long</t>
+  </si>
+  <si>
+    <t>Bella Ngọc</t>
+  </si>
+  <si>
+    <t>HD012121</t>
+  </si>
+  <si>
+    <t>133/3 hoà hưng p12</t>
+  </si>
+  <si>
+    <t>Mai Anh</t>
+  </si>
+  <si>
+    <t>HD012018</t>
+  </si>
+  <si>
+    <t>109/22/14 Dương Bá Trạc p1</t>
+  </si>
+  <si>
+    <t>HD012274</t>
+  </si>
+  <si>
+    <t>Tú Như Lê Nguyễn</t>
+  </si>
+  <si>
+    <t>HD012014</t>
+  </si>
+  <si>
+    <t>Paul (sumthingtopasabuy) - IG sumthingtopasabuy</t>
+  </si>
+  <si>
+    <t>HD012288</t>
+  </si>
+  <si>
+    <t>Lana Nguyễn</t>
+  </si>
+  <si>
+    <t>HD012053</t>
+  </si>
+  <si>
+    <t>Quỳnh Nami</t>
+  </si>
+  <si>
+    <t>HD012351</t>
+  </si>
+  <si>
+    <t>Như Quỳnh</t>
+  </si>
+  <si>
+    <t>khả my</t>
+  </si>
+  <si>
+    <t>HD012319</t>
+  </si>
+  <si>
+    <t>chung cư opal garden đường 20 hiệp bình</t>
+  </si>
+  <si>
+    <t>Ngọc Hân Nghiêm</t>
+  </si>
+  <si>
+    <t>HD012338</t>
+  </si>
+  <si>
+    <t>Tuyết Nhung ( Vy Vy - VY VY LE YUAN)</t>
+  </si>
+  <si>
+    <t>HD012354</t>
+  </si>
+  <si>
+    <t>66 đường số 17, phường 10</t>
+  </si>
+  <si>
+    <t>HD012364</t>
+  </si>
+  <si>
+    <t>Thudena Nguyên</t>
+  </si>
+  <si>
+    <t>HD012120</t>
+  </si>
+  <si>
+    <t>54/24 đường 281 lý thường kiệt p15</t>
+  </si>
+  <si>
+    <t>Khả Hân</t>
+  </si>
+  <si>
+    <t>HD012265</t>
+  </si>
+  <si>
+    <t>HD012357</t>
+  </si>
+  <si>
+    <t>HD011639</t>
+  </si>
+  <si>
+    <t>Mỹ Ngọc</t>
+  </si>
+  <si>
+    <t>HD012340</t>
+  </si>
+  <si>
+    <t>HD012139</t>
+  </si>
+  <si>
+    <t>Mát Mát</t>
+  </si>
+  <si>
+    <t>HD012263</t>
+  </si>
+  <si>
+    <t>HD012352</t>
+  </si>
+  <si>
+    <t>HD012080</t>
+  </si>
+  <si>
+    <t>BN6352</t>
+  </si>
+  <si>
+    <t>HD012154</t>
+  </si>
+  <si>
+    <t>Phạm Yến</t>
+  </si>
+  <si>
+    <t>HD012084</t>
+  </si>
+  <si>
+    <t>64b đường số 32 bình trị đông b</t>
+  </si>
+  <si>
+    <t>Name-Isabella</t>
+  </si>
+  <si>
+    <t>Ruby VO</t>
+  </si>
+  <si>
+    <t>Mr Thế minh tuệ</t>
+  </si>
+  <si>
+    <t>242 nguyễn oanh, phường gò vấp</t>
+  </si>
+  <si>
+    <t>61/31 đường 19 p8</t>
+  </si>
+  <si>
+    <t>1007, Topaz 1, Saigon Pearl, 92 Nguyễn Hữu Cảnh, P Thạnh Mỹ Tây</t>
+  </si>
+  <si>
+    <t>494/1/12 Le Quang Dinh, P1</t>
+  </si>
+  <si>
+    <t>Phuong truong</t>
+  </si>
+  <si>
+    <t>TRANG TRẦN 2</t>
+  </si>
+  <si>
+    <t>1122/23/7 quang trung phường 8</t>
+  </si>
+  <si>
+    <t>khả trinh</t>
+  </si>
+  <si>
+    <t>82/17/20đinh tiên hoàng p1</t>
+  </si>
+  <si>
+    <t>T4 masteri thảo điền, 159 võ nguyên giáp, phường An Khánh</t>
+  </si>
+  <si>
+    <t>Sảnh S10.06 đường Nguyễn Xiển, phường Long Bình (vinhomes grand park)</t>
+  </si>
+  <si>
+    <t>chung cư Flora Kikyo Phú Hữu</t>
+  </si>
+  <si>
+    <t>Toa BE2 The Beverly Vinhomes Grand Park Long Binh</t>
+  </si>
+  <si>
+    <t>Yuri what's app</t>
+  </si>
+  <si>
+    <t>2/13 Nguyễn Bặc, Phường 3</t>
+  </si>
+  <si>
+    <t>28 Cù lao p. Cầu kiệu</t>
+  </si>
+  <si>
+    <t>anh phước (đồ của chị yến)</t>
+  </si>
+  <si>
+    <t>241 lên thánh tôn, p bến thành</t>
+  </si>
+  <si>
+    <t>HD012264</t>
+  </si>
+  <si>
+    <t>195 Hùng Vương, P.An Đông (Q.5 cũ)</t>
+  </si>
+  <si>
+    <t>258/23 Bông Sao Phường 5</t>
+  </si>
+  <si>
+    <t>ANDY OANH</t>
+  </si>
+  <si>
+    <t>108/89/33/3 trần văn quang phường 10</t>
+  </si>
+  <si>
+    <t>Số 17 Đường số 13, p. Bình Hưng Hòa</t>
+  </si>
+  <si>
+    <t>HD012360</t>
+  </si>
+  <si>
+    <t>Cc cardinal tower B phường Tân Phú</t>
+  </si>
+  <si>
+    <t>35 Duy Tân phường 8</t>
+  </si>
+  <si>
+    <t>688/23/1C HƯƠNG LỘ 2 phường BÌNH TRỊ ĐÔNG A</t>
+  </si>
+  <si>
+    <t>1107/36 dương bạch mai p5</t>
+  </si>
+  <si>
+    <t>Khách sạn Hoa Hướng Dương số 57C Tô Hiệu</t>
+  </si>
+  <si>
+    <t>124 đường số 9 KDC Bình Hưng, Bình Hưng</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4347,12 +5114,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="8">
@@ -4425,7 +5186,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -4449,15 +5210,14 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="49" fontId="2" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="49" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5547,7 +6307,7 @@
       <c r="E23" t="s">
         <v>90</v>
       </c>
-      <c r="F23" s="31">
+      <c r="F23" s="28">
         <v>6</v>
       </c>
       <c r="G23">
@@ -5662,7 +6422,7 @@
       <c r="E3" s="18" t="s">
         <v>1008</v>
       </c>
-      <c r="F3" s="27">
+      <c r="F3" s="24">
         <v>2</v>
       </c>
       <c r="G3" s="18">
@@ -5704,7 +6464,7 @@
       <c r="E4" s="18" t="s">
         <v>297</v>
       </c>
-      <c r="F4" s="27" t="s">
+      <c r="F4" s="24" t="s">
         <v>46</v>
       </c>
       <c r="G4" s="18">
@@ -5746,7 +6506,7 @@
       <c r="E5" s="20" t="s">
         <v>661</v>
       </c>
-      <c r="F5" s="28" t="s">
+      <c r="F5" s="25" t="s">
         <v>763</v>
       </c>
       <c r="G5" s="20">
@@ -5790,7 +6550,7 @@
       <c r="E6" s="19" t="s">
         <v>1014</v>
       </c>
-      <c r="F6" s="29" t="s">
+      <c r="F6" s="26" t="s">
         <v>790</v>
       </c>
       <c r="G6" s="19">
@@ -5832,7 +6592,7 @@
       <c r="E7" s="19" t="s">
         <v>1017</v>
       </c>
-      <c r="F7" s="29" t="s">
+      <c r="F7" s="26" t="s">
         <v>790</v>
       </c>
       <c r="G7" s="19">
@@ -5874,7 +6634,7 @@
       <c r="E8" s="18" t="s">
         <v>1020</v>
       </c>
-      <c r="F8" s="27" t="s">
+      <c r="F8" s="24" t="s">
         <v>38</v>
       </c>
       <c r="G8" s="18">
@@ -5916,7 +6676,7 @@
       <c r="E9" s="19" t="s">
         <v>1023</v>
       </c>
-      <c r="F9" s="29" t="s">
+      <c r="F9" s="26" t="s">
         <v>807</v>
       </c>
       <c r="G9" s="19">
@@ -5958,7 +6718,7 @@
       <c r="E10" s="20" t="s">
         <v>1026</v>
       </c>
-      <c r="F10" s="28" t="s">
+      <c r="F10" s="25" t="s">
         <v>22</v>
       </c>
       <c r="G10" s="20">
@@ -6000,7 +6760,7 @@
       <c r="E11" s="20" t="s">
         <v>1029</v>
       </c>
-      <c r="F11" s="28">
+      <c r="F11" s="25">
         <v>7</v>
       </c>
       <c r="G11" s="20">
@@ -6042,7 +6802,7 @@
       <c r="E12" s="19" t="s">
         <v>1032</v>
       </c>
-      <c r="F12" s="29" t="s">
+      <c r="F12" s="26" t="s">
         <v>811</v>
       </c>
       <c r="G12" s="19">
@@ -6084,7 +6844,7 @@
       <c r="E13" s="20" t="s">
         <v>1035</v>
       </c>
-      <c r="F13" s="28" t="s">
+      <c r="F13" s="25" t="s">
         <v>116</v>
       </c>
       <c r="G13" s="20">
@@ -6126,7 +6886,7 @@
       <c r="E14" s="19" t="s">
         <v>1038</v>
       </c>
-      <c r="F14" s="29" t="s">
+      <c r="F14" s="26" t="s">
         <v>88</v>
       </c>
       <c r="G14" s="19">
@@ -6168,7 +6928,7 @@
       <c r="E15" s="20" t="s">
         <v>1041</v>
       </c>
-      <c r="F15" s="28" t="s">
+      <c r="F15" s="25" t="s">
         <v>88</v>
       </c>
       <c r="G15" s="20">
@@ -6210,7 +6970,7 @@
       <c r="E16" s="18" t="s">
         <v>1044</v>
       </c>
-      <c r="F16" s="27" t="s">
+      <c r="F16" s="24" t="s">
         <v>768</v>
       </c>
       <c r="G16" s="18">
@@ -6252,7 +7012,7 @@
       <c r="E17" s="20" t="s">
         <v>1047</v>
       </c>
-      <c r="F17" s="28" t="s">
+      <c r="F17" s="25" t="s">
         <v>763</v>
       </c>
       <c r="G17" s="20">
@@ -6294,7 +7054,7 @@
       <c r="E18" s="18" t="s">
         <v>1050</v>
       </c>
-      <c r="F18" s="27" t="s">
+      <c r="F18" s="24" t="s">
         <v>38</v>
       </c>
       <c r="G18" s="18">
@@ -6336,7 +7096,7 @@
       <c r="E19" s="19" t="s">
         <v>1053</v>
       </c>
-      <c r="F19" s="29" t="s">
+      <c r="F19" s="26" t="s">
         <v>81</v>
       </c>
       <c r="G19" s="19">
@@ -6378,7 +7138,7 @@
       <c r="E20" s="19" t="s">
         <v>1056</v>
       </c>
-      <c r="F20" s="29" t="s">
+      <c r="F20" s="26" t="s">
         <v>824</v>
       </c>
       <c r="G20" s="19">
@@ -6422,7 +7182,7 @@
       <c r="E21" s="19" t="s">
         <v>1059</v>
       </c>
-      <c r="F21" s="29" t="s">
+      <c r="F21" s="26" t="s">
         <v>1060</v>
       </c>
       <c r="G21" s="19">
@@ -6464,7 +7224,7 @@
       <c r="E22" s="20" t="s">
         <v>1063</v>
       </c>
-      <c r="F22" s="28" t="s">
+      <c r="F22" s="25" t="s">
         <v>111</v>
       </c>
       <c r="G22" s="20">
@@ -6506,7 +7266,7 @@
       <c r="E23" s="20" t="s">
         <v>1066</v>
       </c>
-      <c r="F23" s="28" t="s">
+      <c r="F23" s="25" t="s">
         <v>208</v>
       </c>
       <c r="G23" s="20">
@@ -6550,7 +7310,7 @@
       <c r="E24" s="19" t="s">
         <v>1069</v>
       </c>
-      <c r="F24" s="29" t="s">
+      <c r="F24" s="26" t="s">
         <v>81</v>
       </c>
       <c r="G24" s="19">
@@ -6592,7 +7352,7 @@
       <c r="E25" s="18" t="s">
         <v>1072</v>
       </c>
-      <c r="F25" s="27" t="s">
+      <c r="F25" s="24" t="s">
         <v>116</v>
       </c>
       <c r="G25" s="18">
@@ -6634,7 +7394,7 @@
       <c r="E26" s="20" t="s">
         <v>1075</v>
       </c>
-      <c r="F26" s="28" t="s">
+      <c r="F26" s="25" t="s">
         <v>800</v>
       </c>
       <c r="G26" s="20">
@@ -6676,7 +7436,7 @@
       <c r="E27" s="18" t="s">
         <v>1078</v>
       </c>
-      <c r="F27" s="27" t="s">
+      <c r="F27" s="24" t="s">
         <v>46</v>
       </c>
       <c r="G27" s="18">
@@ -6718,7 +7478,7 @@
       <c r="E28" s="19" t="s">
         <v>1081</v>
       </c>
-      <c r="F28" s="29" t="s">
+      <c r="F28" s="26" t="s">
         <v>811</v>
       </c>
       <c r="G28" s="19">
@@ -6760,7 +7520,7 @@
       <c r="E29" s="20" t="s">
         <v>1084</v>
       </c>
-      <c r="F29" s="28" t="s">
+      <c r="F29" s="25" t="s">
         <v>1085</v>
       </c>
       <c r="G29" s="20">
@@ -6802,7 +7562,7 @@
       <c r="E30" s="18" t="s">
         <v>1088</v>
       </c>
-      <c r="F30" s="27" t="s">
+      <c r="F30" s="24" t="s">
         <v>768</v>
       </c>
       <c r="G30" s="18">
@@ -6844,7 +7604,7 @@
       <c r="E31" s="20" t="s">
         <v>1091</v>
       </c>
-      <c r="F31" s="28" t="s">
+      <c r="F31" s="25" t="s">
         <v>22</v>
       </c>
       <c r="G31" s="20">
@@ -6886,7 +7646,7 @@
       <c r="E32" s="19" t="s">
         <v>1094</v>
       </c>
-      <c r="F32" s="29" t="s">
+      <c r="F32" s="26" t="s">
         <v>807</v>
       </c>
       <c r="G32" s="19">
@@ -6928,7 +7688,7 @@
       <c r="E33" s="20" t="s">
         <v>1097</v>
       </c>
-      <c r="F33" s="28" t="s">
+      <c r="F33" s="25" t="s">
         <v>1085</v>
       </c>
       <c r="G33" s="20">
@@ -6970,7 +7730,7 @@
       <c r="E34" s="20" t="s">
         <v>1100</v>
       </c>
-      <c r="F34" s="28" t="s">
+      <c r="F34" s="25" t="s">
         <v>800</v>
       </c>
       <c r="G34" s="20">
@@ -7012,7 +7772,7 @@
       <c r="E35" s="19" t="s">
         <v>1103</v>
       </c>
-      <c r="F35" s="29">
+      <c r="F35" s="26">
         <v>3</v>
       </c>
       <c r="G35" s="19">
@@ -7054,7 +7814,7 @@
       <c r="E36" s="21" t="s">
         <v>1106</v>
       </c>
-      <c r="F36" s="30">
+      <c r="F36" s="27">
         <v>9</v>
       </c>
       <c r="G36" s="21">
@@ -7096,7 +7856,7 @@
       <c r="E37" s="18" t="s">
         <v>1109</v>
       </c>
-      <c r="F37" s="27" t="s">
+      <c r="F37" s="24" t="s">
         <v>38</v>
       </c>
       <c r="G37" s="18">
@@ -7138,7 +7898,7 @@
       <c r="E38" s="19" t="s">
         <v>1111</v>
       </c>
-      <c r="F38" s="29" t="s">
+      <c r="F38" s="26" t="s">
         <v>81</v>
       </c>
       <c r="G38" s="19">
@@ -7180,7 +7940,7 @@
       <c r="E39" s="20" t="s">
         <v>1114</v>
       </c>
-      <c r="F39" s="28" t="s">
+      <c r="F39" s="25" t="s">
         <v>143</v>
       </c>
       <c r="G39" s="20">
@@ -7222,7 +7982,7 @@
       <c r="E40" s="20" t="s">
         <v>973</v>
       </c>
-      <c r="F40" s="28" t="s">
+      <c r="F40" s="25" t="s">
         <v>22</v>
       </c>
       <c r="G40" s="20">
@@ -7266,7 +8026,7 @@
       <c r="E41" s="19" t="s">
         <v>1118</v>
       </c>
-      <c r="F41" s="29" t="s">
+      <c r="F41" s="26" t="s">
         <v>811</v>
       </c>
       <c r="G41" s="19">
@@ -7308,7 +8068,7 @@
       <c r="E42" s="20" t="s">
         <v>1121</v>
       </c>
-      <c r="F42" s="28" t="s">
+      <c r="F42" s="25" t="s">
         <v>800</v>
       </c>
       <c r="G42" s="20">
@@ -7350,7 +8110,7 @@
       <c r="E43" s="20" t="s">
         <v>1124</v>
       </c>
-      <c r="F43" s="28" t="s">
+      <c r="F43" s="25" t="s">
         <v>763</v>
       </c>
       <c r="G43" s="20">
@@ -9178,7 +9938,7 @@
       <c r="E50" s="22" t="s">
         <v>910</v>
       </c>
-      <c r="F50" s="26" t="s">
+      <c r="F50" s="23" t="s">
         <v>807</v>
       </c>
       <c r="G50" s="22">
@@ -10808,11 +11568,14 @@
   <dimension ref="A1:Q35"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="1" max="2" width="9.140625" customWidth="1"/>
     <col min="3" max="3" width="24.28515625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9.5703125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="57.140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="9" width="9.140625" customWidth="1"/>
     <col min="10" max="10" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.140625" customWidth="1"/>
     <col min="12" max="12" width="10.42578125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="13.7109375" bestFit="1" customWidth="1"/>
   </cols>
@@ -10898,7 +11661,7 @@
         <v>25</v>
       </c>
       <c r="I3" s="9">
-        <f t="shared" ref="I3:I34" si="0">G3-H3</f>
+        <f t="shared" ref="I3:I35" si="0">G3-H3</f>
         <v>-25</v>
       </c>
       <c r="J3" s="9" t="s">
@@ -10958,7 +11721,7 @@
         <v>1360</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>1416</v>
+        <v>1361</v>
       </c>
       <c r="F5" s="10" t="s">
         <v>807</v>
@@ -10988,13 +11751,13 @@
         <v>18</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>1361</v>
+        <v>1362</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>1362</v>
+        <v>1363</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>1419</v>
+        <v>1364</v>
       </c>
       <c r="F6" s="6" t="s">
         <v>1199</v>
@@ -11027,10 +11790,10 @@
         <v>117</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>1363</v>
+        <v>1365</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>1364</v>
+        <v>1366</v>
       </c>
       <c r="F7" s="8" t="s">
         <v>22</v>
@@ -11063,13 +11826,13 @@
         <v>18</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>1365</v>
+        <v>1367</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>1366</v>
+        <v>1368</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>1367</v>
+        <v>1369</v>
       </c>
       <c r="F8" s="8" t="s">
         <v>763</v>
@@ -11099,10 +11862,10 @@
         <v>18</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>1368</v>
+        <v>1370</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>1369</v>
+        <v>1371</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>820</v>
@@ -11135,13 +11898,13 @@
         <v>18</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>1370</v>
+        <v>1372</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>1371</v>
+        <v>1373</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>1372</v>
+        <v>1374</v>
       </c>
       <c r="F10" s="4" t="s">
         <v>116</v>
@@ -11171,13 +11934,13 @@
         <v>18</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>1373</v>
+        <v>1375</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>1374</v>
+        <v>1376</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>1420</v>
+        <v>1377</v>
       </c>
       <c r="F11" s="8" t="s">
         <v>143</v>
@@ -11207,10 +11970,10 @@
         <v>18</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>1375</v>
+        <v>1378</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>1376</v>
+        <v>1379</v>
       </c>
       <c r="E12" s="7" t="s">
         <v>406</v>
@@ -11246,7 +12009,7 @@
         <v>678</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>1377</v>
+        <v>1380</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>680</v>
@@ -11279,13 +12042,13 @@
         <v>18</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>1378</v>
+        <v>1381</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>1379</v>
+        <v>1382</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>1380</v>
+        <v>1383</v>
       </c>
       <c r="F14" s="4" t="s">
         <v>116</v>
@@ -11315,13 +12078,13 @@
         <v>18</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>1381</v>
+        <v>1384</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>1382</v>
+        <v>1385</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>1383</v>
+        <v>1386</v>
       </c>
       <c r="F15" s="4" t="s">
         <v>88</v>
@@ -11351,13 +12114,13 @@
         <v>18</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>1384</v>
+        <v>1387</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>1385</v>
+        <v>1388</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>1386</v>
+        <v>1389</v>
       </c>
       <c r="F16" s="10" t="s">
         <v>1060</v>
@@ -11387,13 +12150,13 @@
         <v>18</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>1387</v>
+        <v>1390</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>1388</v>
+        <v>1391</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>1389</v>
+        <v>1392</v>
       </c>
       <c r="F17" s="8" t="s">
         <v>287</v>
@@ -11423,13 +12186,13 @@
         <v>18</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>1421</v>
+        <v>1393</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>1390</v>
+        <v>1394</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>1391</v>
+        <v>1395</v>
       </c>
       <c r="F18" s="8" t="s">
         <v>775</v>
@@ -11459,13 +12222,13 @@
         <v>18</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>1392</v>
+        <v>1396</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>1393</v>
+        <v>1397</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>1394</v>
+        <v>1398</v>
       </c>
       <c r="F19" s="8" t="s">
         <v>775</v>
@@ -11495,13 +12258,13 @@
         <v>18</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>1396</v>
+        <v>1400</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>1397</v>
+        <v>1401</v>
       </c>
       <c r="F20" s="10" t="s">
         <v>807</v>
@@ -11531,13 +12294,13 @@
         <v>18</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>1398</v>
+        <v>1402</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>1399</v>
+        <v>1403</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>1400</v>
+        <v>1404</v>
       </c>
       <c r="F21" s="10" t="s">
         <v>1060</v>
@@ -11603,13 +12366,13 @@
         <v>18</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>1412</v>
+        <v>1405</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>1401</v>
+        <v>1406</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>1413</v>
+        <v>1407</v>
       </c>
       <c r="F23" s="10" t="s">
         <v>81</v>
@@ -11639,13 +12402,13 @@
         <v>18</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>1402</v>
+        <v>1408</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>1403</v>
+        <v>1409</v>
       </c>
       <c r="E24" s="9" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="F24" s="10" t="s">
         <v>824</v>
@@ -11675,13 +12438,13 @@
         <v>18</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>1404</v>
+        <v>1411</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>1405</v>
+        <v>1412</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>1406</v>
+        <v>1413</v>
       </c>
       <c r="F25" s="8" t="s">
         <v>208</v>
@@ -11714,7 +12477,7 @@
         <v>593</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>1407</v>
+        <v>1414</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>595</v>
@@ -11753,7 +12516,7 @@
         <v>101</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>1409</v>
+        <v>1415</v>
       </c>
       <c r="F27" s="4" t="s">
         <v>46</v>
@@ -11822,10 +12585,10 @@
         <v>18</v>
       </c>
       <c r="C29" s="5" t="s">
+        <v>1416</v>
+      </c>
+      <c r="E29" s="5" t="s">
         <v>1417</v>
-      </c>
-      <c r="E29" s="5" t="s">
-        <v>1418</v>
       </c>
       <c r="F29" s="6">
         <v>9</v>
@@ -11930,10 +12693,10 @@
         <v>18</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>1414</v>
+        <v>1418</v>
       </c>
       <c r="E32" s="9" t="s">
-        <v>1415</v>
+        <v>1419</v>
       </c>
       <c r="F32" s="10" t="s">
         <v>88</v>
@@ -12002,10 +12765,10 @@
         <v>18</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>1410</v>
+        <v>1420</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>1408</v>
+        <v>1421</v>
       </c>
       <c r="F34" s="4" t="s">
         <v>38</v>
@@ -12031,53 +12794,3875 @@
       </c>
     </row>
     <row r="35" spans="1:17" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="23"/>
-      <c r="B35" s="23" t="s">
-        <v>18</v>
-      </c>
-      <c r="C35" s="23" t="s">
+      <c r="B35" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="C35" s="11" t="s">
         <v>1262</v>
       </c>
-      <c r="D35" s="23" t="s">
+      <c r="D35" s="11" t="s">
         <v>1263</v>
       </c>
-      <c r="E35" s="23" t="s">
+      <c r="E35" s="11" t="s">
         <v>1264</v>
       </c>
-      <c r="F35" s="25">
+      <c r="F35" s="15">
         <v>12</v>
       </c>
-      <c r="G35" s="24">
+      <c r="G35" s="29">
         <v>870</v>
       </c>
-      <c r="H35" s="24">
+      <c r="H35" s="29">
         <v>0</v>
       </c>
-      <c r="I35" s="24">
-        <f>G35-H35</f>
+      <c r="I35" s="29">
+        <f t="shared" si="0"/>
         <v>870</v>
       </c>
-      <c r="J35" s="23" t="s">
+      <c r="J35" s="11" t="s">
         <v>427</v>
       </c>
-      <c r="K35" s="23" t="s">
-        <v>24</v>
-      </c>
-      <c r="L35" s="23" t="s">
+      <c r="K35" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="L35" s="11" t="s">
         <v>1130</v>
       </c>
-      <c r="M35" s="23"/>
-      <c r="N35" s="23" t="s">
+      <c r="N35" s="11" t="s">
         <v>430</v>
       </c>
-      <c r="O35" s="23" t="s">
+      <c r="O35" s="11" t="s">
         <v>430</v>
       </c>
-      <c r="P35" s="23" t="s">
+      <c r="P35" s="11" t="s">
         <v>431</v>
       </c>
       <c r="Q35" s="11">
         <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
+  <dimension ref="A1:Q52"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="9.140625" customWidth="1"/>
+    <col min="2" max="2" width="18" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="52.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="70.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.42578125" customWidth="1"/>
+    <col min="7" max="11" width="9.140625" customWidth="1"/>
+    <col min="12" max="12" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B1" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1422</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>1423</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>1424</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>1425</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>800</v>
+      </c>
+      <c r="G3" s="7">
+        <v>950</v>
+      </c>
+      <c r="H3" s="7">
+        <v>30</v>
+      </c>
+      <c r="I3" s="7">
+        <f t="shared" ref="I3:I34" si="0">G3-H3</f>
+        <v>920</v>
+      </c>
+      <c r="J3" s="7" t="s">
+        <v>1426</v>
+      </c>
+      <c r="K3" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L3" s="7" t="s">
+        <v>1427</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>1428</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>1429</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>1430</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>800</v>
+      </c>
+      <c r="G4" s="7">
+        <v>670</v>
+      </c>
+      <c r="H4" s="7">
+        <v>30</v>
+      </c>
+      <c r="I4" s="7">
+        <f t="shared" si="0"/>
+        <v>640</v>
+      </c>
+      <c r="J4" s="7" t="s">
+        <v>1426</v>
+      </c>
+      <c r="K4" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L4" s="7" t="s">
+        <v>1427</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>615</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>1431</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>617</v>
+      </c>
+      <c r="F5" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="G5" s="9">
+        <v>945</v>
+      </c>
+      <c r="H5" s="9">
+        <v>25</v>
+      </c>
+      <c r="I5" s="9">
+        <f t="shared" si="0"/>
+        <v>920</v>
+      </c>
+      <c r="J5" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="K5" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L5" s="9" t="s">
+        <v>1427</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>1432</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>1433</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>1434</v>
+      </c>
+      <c r="F6" s="10" t="s">
+        <v>807</v>
+      </c>
+      <c r="G6" s="9">
+        <v>725</v>
+      </c>
+      <c r="H6" s="9">
+        <v>25</v>
+      </c>
+      <c r="I6" s="9">
+        <f t="shared" si="0"/>
+        <v>700</v>
+      </c>
+      <c r="J6" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="K6" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L6" s="9" t="s">
+        <v>1427</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>1435</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>1436</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>1437</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="G7" s="3">
+        <v>460</v>
+      </c>
+      <c r="H7" s="3">
+        <v>20</v>
+      </c>
+      <c r="I7" s="3">
+        <f t="shared" si="0"/>
+        <v>440</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L7" s="3" t="s">
+        <v>1427</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>1438</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>1439</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>1440</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G8" s="7">
+        <v>780</v>
+      </c>
+      <c r="H8" s="7">
+        <v>30</v>
+      </c>
+      <c r="I8" s="7">
+        <f t="shared" si="0"/>
+        <v>750</v>
+      </c>
+      <c r="J8" s="7" t="s">
+        <v>1426</v>
+      </c>
+      <c r="K8" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L8" s="7" t="s">
+        <v>1427</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>1441</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>1442</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>1443</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>800</v>
+      </c>
+      <c r="G9" s="7">
+        <v>850</v>
+      </c>
+      <c r="H9" s="7">
+        <v>30</v>
+      </c>
+      <c r="I9" s="7">
+        <f t="shared" si="0"/>
+        <v>820</v>
+      </c>
+      <c r="J9" s="7" t="s">
+        <v>1426</v>
+      </c>
+      <c r="K9" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L9" s="7" t="s">
+        <v>1427</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>1153</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>1444</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>1445</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>800</v>
+      </c>
+      <c r="G10" s="7">
+        <v>520</v>
+      </c>
+      <c r="H10" s="7">
+        <v>30</v>
+      </c>
+      <c r="I10" s="7">
+        <f t="shared" si="0"/>
+        <v>490</v>
+      </c>
+      <c r="J10" s="7" t="s">
+        <v>1426</v>
+      </c>
+      <c r="K10" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L10" s="7" t="s">
+        <v>1427</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>1446</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>1447</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>1448</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>997</v>
+      </c>
+      <c r="G11" s="7">
+        <v>0</v>
+      </c>
+      <c r="H11" s="7">
+        <v>25</v>
+      </c>
+      <c r="I11" s="7">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J11" s="7" t="s">
+        <v>1426</v>
+      </c>
+      <c r="K11" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L11" s="7" t="s">
+        <v>1427</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>1449</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>1450</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>1451</v>
+      </c>
+      <c r="F12" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="G12" s="9">
+        <v>0</v>
+      </c>
+      <c r="H12" s="9">
+        <v>25</v>
+      </c>
+      <c r="I12" s="9">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J12" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="K12" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L12" s="9" t="s">
+        <v>1427</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>1452</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>1453</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>1454</v>
+      </c>
+      <c r="F13" s="8" t="s">
+        <v>800</v>
+      </c>
+      <c r="G13" s="7">
+        <v>30</v>
+      </c>
+      <c r="H13" s="7">
+        <v>30</v>
+      </c>
+      <c r="I13" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J13" s="7" t="s">
+        <v>1426</v>
+      </c>
+      <c r="K13" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L13" s="7" t="s">
+        <v>1427</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>1455</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>1456</v>
+      </c>
+      <c r="E14" s="9" t="s">
+        <v>1457</v>
+      </c>
+      <c r="F14" s="10" t="s">
+        <v>1060</v>
+      </c>
+      <c r="G14" s="9">
+        <v>0</v>
+      </c>
+      <c r="H14" s="9">
+        <v>25</v>
+      </c>
+      <c r="I14" s="9">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J14" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="K14" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L14" s="9" t="s">
+        <v>1427</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>902</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>1458</v>
+      </c>
+      <c r="E15" s="9" t="s">
+        <v>904</v>
+      </c>
+      <c r="F15" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="G15" s="9">
+        <v>975</v>
+      </c>
+      <c r="H15" s="9">
+        <v>25</v>
+      </c>
+      <c r="I15" s="9">
+        <f t="shared" si="0"/>
+        <v>950</v>
+      </c>
+      <c r="J15" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="K15" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L15" s="9" t="s">
+        <v>1427</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>747</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>1459</v>
+      </c>
+      <c r="E16" s="9" t="s">
+        <v>1460</v>
+      </c>
+      <c r="F16" s="10" t="s">
+        <v>807</v>
+      </c>
+      <c r="G16" s="9">
+        <v>0</v>
+      </c>
+      <c r="H16" s="9">
+        <v>25</v>
+      </c>
+      <c r="I16" s="9">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J16" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="K16" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L16" s="9" t="s">
+        <v>1427</v>
+      </c>
+    </row>
+    <row r="17" spans="2:16" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>1461</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>1462</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>1463</v>
+      </c>
+      <c r="F17" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="G17" s="7">
+        <v>1015</v>
+      </c>
+      <c r="H17" s="7">
+        <v>25</v>
+      </c>
+      <c r="I17" s="7">
+        <f t="shared" si="0"/>
+        <v>990</v>
+      </c>
+      <c r="J17" s="7" t="s">
+        <v>1426</v>
+      </c>
+      <c r="K17" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L17" s="7" t="s">
+        <v>1427</v>
+      </c>
+    </row>
+    <row r="18" spans="2:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>1464</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>1465</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>1466</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="G18" s="3">
+        <v>1855</v>
+      </c>
+      <c r="H18" s="3">
+        <v>25</v>
+      </c>
+      <c r="I18" s="3">
+        <f t="shared" si="0"/>
+        <v>1830</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L18" s="3" t="s">
+        <v>1427</v>
+      </c>
+    </row>
+    <row r="19" spans="2:16" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>812</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>1467</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>1468</v>
+      </c>
+      <c r="F19" s="8" t="s">
+        <v>1085</v>
+      </c>
+      <c r="G19" s="7">
+        <v>0</v>
+      </c>
+      <c r="H19" s="7">
+        <v>30</v>
+      </c>
+      <c r="I19" s="7">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J19" s="7" t="s">
+        <v>1426</v>
+      </c>
+      <c r="K19" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L19" s="7" t="s">
+        <v>1427</v>
+      </c>
+    </row>
+    <row r="20" spans="2:16" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>1469</v>
+      </c>
+      <c r="D20" s="9" t="s">
+        <v>1470</v>
+      </c>
+      <c r="E20" s="9" t="s">
+        <v>1471</v>
+      </c>
+      <c r="F20" s="10" t="s">
+        <v>824</v>
+      </c>
+      <c r="G20" s="9">
+        <v>835</v>
+      </c>
+      <c r="H20" s="9">
+        <v>25</v>
+      </c>
+      <c r="I20" s="9">
+        <f t="shared" si="0"/>
+        <v>810</v>
+      </c>
+      <c r="J20" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="K20" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L20" s="9" t="s">
+        <v>1427</v>
+      </c>
+    </row>
+    <row r="21" spans="2:16" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>1472</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>1473</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>1474</v>
+      </c>
+      <c r="F21" s="8" t="s">
+        <v>800</v>
+      </c>
+      <c r="G21" s="7">
+        <v>390</v>
+      </c>
+      <c r="H21" s="7">
+        <v>30</v>
+      </c>
+      <c r="I21" s="7">
+        <f t="shared" si="0"/>
+        <v>360</v>
+      </c>
+      <c r="J21" s="7" t="s">
+        <v>1426</v>
+      </c>
+      <c r="K21" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L21" s="7" t="s">
+        <v>1427</v>
+      </c>
+    </row>
+    <row r="22" spans="2:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>1475</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>1476</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>1477</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="G22" s="3">
+        <v>960</v>
+      </c>
+      <c r="H22" s="3">
+        <v>30</v>
+      </c>
+      <c r="I22" s="3">
+        <f t="shared" si="0"/>
+        <v>930</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L22" s="3" t="s">
+        <v>1427</v>
+      </c>
+    </row>
+    <row r="23" spans="2:16" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="C23" s="11" t="s">
+        <v>1478</v>
+      </c>
+      <c r="D23" s="11" t="s">
+        <v>1479</v>
+      </c>
+      <c r="E23" s="11" t="s">
+        <v>1480</v>
+      </c>
+      <c r="F23" s="15" t="s">
+        <v>1481</v>
+      </c>
+      <c r="G23" s="11">
+        <v>2040</v>
+      </c>
+      <c r="H23" s="11">
+        <v>0</v>
+      </c>
+      <c r="I23" s="11">
+        <f t="shared" si="0"/>
+        <v>2040</v>
+      </c>
+      <c r="J23" s="11" t="s">
+        <v>427</v>
+      </c>
+      <c r="K23" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="L23" s="11" t="s">
+        <v>1427</v>
+      </c>
+      <c r="M23" s="30" t="s">
+        <v>1482</v>
+      </c>
+      <c r="N23" s="11" t="s">
+        <v>430</v>
+      </c>
+      <c r="P23" s="11" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="24" spans="2:16" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>448</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>1483</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>450</v>
+      </c>
+      <c r="F24" s="8" t="s">
+        <v>775</v>
+      </c>
+      <c r="G24" s="7">
+        <v>1300</v>
+      </c>
+      <c r="H24" s="7">
+        <v>30</v>
+      </c>
+      <c r="I24" s="7">
+        <f t="shared" si="0"/>
+        <v>1270</v>
+      </c>
+      <c r="J24" s="7" t="s">
+        <v>1426</v>
+      </c>
+      <c r="K24" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L24" s="7" t="s">
+        <v>1427</v>
+      </c>
+    </row>
+    <row r="25" spans="2:16" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>1484</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>1485</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>1486</v>
+      </c>
+      <c r="F25" s="6" t="s">
+        <v>1199</v>
+      </c>
+      <c r="G25" s="5">
+        <v>1420</v>
+      </c>
+      <c r="H25" s="5">
+        <v>30</v>
+      </c>
+      <c r="I25" s="5">
+        <f t="shared" si="0"/>
+        <v>1390</v>
+      </c>
+      <c r="J25" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="K25" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L25" s="5" t="s">
+        <v>1427</v>
+      </c>
+    </row>
+    <row r="26" spans="2:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>1487</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>1488</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>1489</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>768</v>
+      </c>
+      <c r="G26" s="3">
+        <v>600</v>
+      </c>
+      <c r="H26" s="3">
+        <v>30</v>
+      </c>
+      <c r="I26" s="3">
+        <f t="shared" si="0"/>
+        <v>570</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K26" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L26" s="3" t="s">
+        <v>1427</v>
+      </c>
+    </row>
+    <row r="27" spans="2:16" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C27" s="9" t="s">
+        <v>1490</v>
+      </c>
+      <c r="D27" s="9" t="s">
+        <v>1491</v>
+      </c>
+      <c r="E27" s="9" t="s">
+        <v>1492</v>
+      </c>
+      <c r="F27" s="10" t="s">
+        <v>811</v>
+      </c>
+      <c r="G27" s="9">
+        <v>955</v>
+      </c>
+      <c r="H27" s="9">
+        <v>25</v>
+      </c>
+      <c r="I27" s="9">
+        <f t="shared" si="0"/>
+        <v>930</v>
+      </c>
+      <c r="J27" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="K27" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L27" s="9" t="s">
+        <v>1427</v>
+      </c>
+    </row>
+    <row r="28" spans="2:16" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C28" s="9" t="s">
+        <v>1493</v>
+      </c>
+      <c r="D28" s="9" t="s">
+        <v>1494</v>
+      </c>
+      <c r="E28" s="9" t="s">
+        <v>1495</v>
+      </c>
+      <c r="F28" s="10" t="s">
+        <v>807</v>
+      </c>
+      <c r="G28" s="9">
+        <v>0</v>
+      </c>
+      <c r="H28" s="9">
+        <v>25</v>
+      </c>
+      <c r="I28" s="9">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J28" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="K28" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L28" s="9" t="s">
+        <v>1427</v>
+      </c>
+    </row>
+    <row r="29" spans="2:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>1496</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="G29" s="3">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3">
+        <v>20</v>
+      </c>
+      <c r="I29" s="3">
+        <f t="shared" si="0"/>
+        <v>-20</v>
+      </c>
+      <c r="J29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L29" s="3" t="s">
+        <v>1427</v>
+      </c>
+    </row>
+    <row r="30" spans="2:16" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>1497</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>1498</v>
+      </c>
+      <c r="E30" s="5" t="s">
+        <v>1499</v>
+      </c>
+      <c r="F30" s="6" t="s">
+        <v>1199</v>
+      </c>
+      <c r="G30" s="5">
+        <v>1170</v>
+      </c>
+      <c r="H30" s="5">
+        <v>30</v>
+      </c>
+      <c r="I30" s="5">
+        <f t="shared" si="0"/>
+        <v>1140</v>
+      </c>
+      <c r="J30" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="K30" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L30" s="5" t="s">
+        <v>1427</v>
+      </c>
+    </row>
+    <row r="31" spans="2:16" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B31" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>1500</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>1501</v>
+      </c>
+      <c r="E31" s="7" t="s">
+        <v>1502</v>
+      </c>
+      <c r="F31" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="G31" s="7">
+        <v>0</v>
+      </c>
+      <c r="H31" s="7">
+        <v>25</v>
+      </c>
+      <c r="I31" s="7">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J31" s="7" t="s">
+        <v>1426</v>
+      </c>
+      <c r="K31" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L31" s="7" t="s">
+        <v>1427</v>
+      </c>
+    </row>
+    <row r="32" spans="2:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B32" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>1503</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>1504</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>1505</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="G32" s="3">
+        <v>840</v>
+      </c>
+      <c r="H32" s="3">
+        <v>20</v>
+      </c>
+      <c r="I32" s="3">
+        <f t="shared" si="0"/>
+        <v>820</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K32" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L32" s="3" t="s">
+        <v>1427</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B33" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C33" s="9" t="s">
+        <v>1243</v>
+      </c>
+      <c r="D33" s="9" t="s">
+        <v>1506</v>
+      </c>
+      <c r="E33" s="9" t="s">
+        <v>1245</v>
+      </c>
+      <c r="F33" s="10" t="s">
+        <v>824</v>
+      </c>
+      <c r="G33" s="9">
+        <v>975</v>
+      </c>
+      <c r="H33" s="9">
+        <v>25</v>
+      </c>
+      <c r="I33" s="9">
+        <f t="shared" si="0"/>
+        <v>950</v>
+      </c>
+      <c r="J33" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="K33" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L33" s="9" t="s">
+        <v>1427</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B34" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>1507</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>1508</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>1509</v>
+      </c>
+      <c r="F34" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="G34" s="3">
+        <v>0</v>
+      </c>
+      <c r="H34" s="3">
+        <v>25</v>
+      </c>
+      <c r="I34" s="3">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J34" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K34" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L34" s="3" t="s">
+        <v>1427</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B35" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>1510</v>
+      </c>
+      <c r="D35" s="7" t="s">
+        <v>1511</v>
+      </c>
+      <c r="E35" s="7" t="s">
+        <v>1512</v>
+      </c>
+      <c r="F35" s="8" t="s">
+        <v>997</v>
+      </c>
+      <c r="G35" s="7">
+        <v>0</v>
+      </c>
+      <c r="H35" s="7">
+        <v>25</v>
+      </c>
+      <c r="I35" s="7">
+        <f t="shared" ref="I35:I66" si="1">G35-H35</f>
+        <v>-25</v>
+      </c>
+      <c r="J35" s="7" t="s">
+        <v>1426</v>
+      </c>
+      <c r="K35" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L35" s="7" t="s">
+        <v>1427</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B36" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C36" s="7" t="s">
+        <v>1513</v>
+      </c>
+      <c r="D36" s="7" t="s">
+        <v>1514</v>
+      </c>
+      <c r="E36" s="7" t="s">
+        <v>1515</v>
+      </c>
+      <c r="F36" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G36" s="7">
+        <v>900</v>
+      </c>
+      <c r="H36" s="7">
+        <v>30</v>
+      </c>
+      <c r="I36" s="7">
+        <f t="shared" si="1"/>
+        <v>870</v>
+      </c>
+      <c r="J36" s="7" t="s">
+        <v>1426</v>
+      </c>
+      <c r="K36" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L36" s="7" t="s">
+        <v>1427</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B37" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C37" s="7" t="s">
+        <v>1516</v>
+      </c>
+      <c r="D37" s="7" t="s">
+        <v>1517</v>
+      </c>
+      <c r="E37" s="7" t="s">
+        <v>1518</v>
+      </c>
+      <c r="F37" s="8" t="s">
+        <v>763</v>
+      </c>
+      <c r="G37" s="7">
+        <v>0</v>
+      </c>
+      <c r="H37" s="7">
+        <v>25</v>
+      </c>
+      <c r="I37" s="7">
+        <f t="shared" si="1"/>
+        <v>-25</v>
+      </c>
+      <c r="J37" s="7" t="s">
+        <v>1426</v>
+      </c>
+      <c r="K37" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L37" s="7" t="s">
+        <v>1427</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B38" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>1519</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>1520</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>1521</v>
+      </c>
+      <c r="F38" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="G38" s="3">
+        <v>970</v>
+      </c>
+      <c r="H38" s="3">
+        <v>20</v>
+      </c>
+      <c r="I38" s="3">
+        <f t="shared" si="1"/>
+        <v>950</v>
+      </c>
+      <c r="J38" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K38" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L38" s="3" t="s">
+        <v>1427</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B39" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>1522</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>1523</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>1524</v>
+      </c>
+      <c r="F39" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="G39" s="3">
+        <v>0</v>
+      </c>
+      <c r="H39" s="3">
+        <v>25</v>
+      </c>
+      <c r="I39" s="3">
+        <f t="shared" si="1"/>
+        <v>-25</v>
+      </c>
+      <c r="J39" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K39" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L39" s="3" t="s">
+        <v>1427</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B40" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C40" s="7" t="s">
+        <v>1525</v>
+      </c>
+      <c r="D40" s="7" t="s">
+        <v>1526</v>
+      </c>
+      <c r="E40" s="7" t="s">
+        <v>1527</v>
+      </c>
+      <c r="F40" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G40" s="7">
+        <v>30</v>
+      </c>
+      <c r="H40" s="7">
+        <v>30</v>
+      </c>
+      <c r="I40" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J40" s="7" t="s">
+        <v>1426</v>
+      </c>
+      <c r="K40" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L40" s="7" t="s">
+        <v>1427</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B41" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>1528</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>1529</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>1530</v>
+      </c>
+      <c r="F41" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="G41" s="3">
+        <v>810</v>
+      </c>
+      <c r="H41" s="3">
+        <v>20</v>
+      </c>
+      <c r="I41" s="3">
+        <f t="shared" si="1"/>
+        <v>790</v>
+      </c>
+      <c r="J41" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K41" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L41" s="3" t="s">
+        <v>1427</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B42" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C42" s="5" t="s">
+        <v>1531</v>
+      </c>
+      <c r="D42" s="5" t="s">
+        <v>1532</v>
+      </c>
+      <c r="E42" s="5" t="s">
+        <v>1533</v>
+      </c>
+      <c r="F42" s="6">
+        <v>9</v>
+      </c>
+      <c r="G42" s="5">
+        <v>1910</v>
+      </c>
+      <c r="H42" s="5">
+        <v>30</v>
+      </c>
+      <c r="I42" s="5">
+        <f t="shared" si="1"/>
+        <v>1880</v>
+      </c>
+      <c r="J42" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="K42" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L42" s="5" t="s">
+        <v>1427</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B43" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C43" s="5" t="s">
+        <v>346</v>
+      </c>
+      <c r="D43" s="5" t="s">
+        <v>1534</v>
+      </c>
+      <c r="E43" s="5" t="s">
+        <v>348</v>
+      </c>
+      <c r="F43" s="6" t="s">
+        <v>1199</v>
+      </c>
+      <c r="G43" s="5">
+        <v>380</v>
+      </c>
+      <c r="H43" s="5">
+        <v>30</v>
+      </c>
+      <c r="I43" s="5">
+        <f t="shared" si="1"/>
+        <v>350</v>
+      </c>
+      <c r="J43" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="K43" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L43" s="5" t="s">
+        <v>1427</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B44" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>1535</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>1536</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>1537</v>
+      </c>
+      <c r="F44" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="G44" s="3">
+        <v>810</v>
+      </c>
+      <c r="H44" s="3">
+        <v>20</v>
+      </c>
+      <c r="I44" s="3">
+        <f t="shared" si="1"/>
+        <v>790</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K44" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L44" s="3" t="s">
+        <v>1427</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C45" s="5" t="s">
+        <v>1538</v>
+      </c>
+      <c r="E45" s="5" t="s">
+        <v>1539</v>
+      </c>
+      <c r="F45" s="6" t="s">
+        <v>1199</v>
+      </c>
+      <c r="G45" s="5">
+        <v>0</v>
+      </c>
+      <c r="H45" s="5">
+        <v>35</v>
+      </c>
+      <c r="I45" s="5">
+        <f t="shared" si="1"/>
+        <v>-35</v>
+      </c>
+      <c r="J45" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="K45" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L45" s="5" t="s">
+        <v>1427</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>1540</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>1541</v>
+      </c>
+      <c r="F46" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="G46" s="3">
+        <v>35</v>
+      </c>
+      <c r="H46" s="3">
+        <v>35</v>
+      </c>
+      <c r="I46" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J46" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K46" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L46" s="3" t="s">
+        <v>1427</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="B47" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C47" s="7" t="s">
+        <v>1542</v>
+      </c>
+      <c r="E47" s="7" t="s">
+        <v>1543</v>
+      </c>
+      <c r="F47" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G47" s="7">
+        <v>40</v>
+      </c>
+      <c r="H47" s="7">
+        <v>40</v>
+      </c>
+      <c r="I47" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J47" s="7" t="s">
+        <v>1426</v>
+      </c>
+      <c r="K47" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L47" s="7" t="s">
+        <v>1427</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="B48" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C48" s="9" t="s">
+        <v>566</v>
+      </c>
+      <c r="E48" s="9" t="s">
+        <v>567</v>
+      </c>
+      <c r="F48" s="10" t="s">
+        <v>811</v>
+      </c>
+      <c r="G48" s="9">
+        <v>30</v>
+      </c>
+      <c r="H48" s="9">
+        <v>30</v>
+      </c>
+      <c r="I48" s="9">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J48" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="K48" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L48" s="9" t="s">
+        <v>1427</v>
+      </c>
+    </row>
+    <row r="49" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="B49" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C49" s="9" t="s">
+        <v>1544</v>
+      </c>
+      <c r="E49" s="9" t="s">
+        <v>417</v>
+      </c>
+      <c r="F49" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="G49" s="9">
+        <v>0</v>
+      </c>
+      <c r="H49" s="9">
+        <v>30</v>
+      </c>
+      <c r="I49" s="9">
+        <f t="shared" si="1"/>
+        <v>-30</v>
+      </c>
+      <c r="J49" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="K49" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L49" s="9" t="s">
+        <v>1427</v>
+      </c>
+    </row>
+    <row r="50" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>573</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>1545</v>
+      </c>
+      <c r="F50" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="G50" s="3">
+        <v>1175</v>
+      </c>
+      <c r="H50" s="3">
+        <v>35</v>
+      </c>
+      <c r="I50" s="3">
+        <f t="shared" si="1"/>
+        <v>1140</v>
+      </c>
+      <c r="J50" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K50" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L50" s="3" t="s">
+        <v>1427</v>
+      </c>
+    </row>
+    <row r="51" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B51" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C51" s="5" t="s">
+        <v>1546</v>
+      </c>
+      <c r="D51" s="5" t="s">
+        <v>1547</v>
+      </c>
+      <c r="E51" s="5" t="s">
+        <v>1548</v>
+      </c>
+      <c r="F51" s="6" t="s">
+        <v>1199</v>
+      </c>
+      <c r="G51" s="5">
+        <v>1120</v>
+      </c>
+      <c r="H51" s="5">
+        <v>30</v>
+      </c>
+      <c r="I51" s="5">
+        <f t="shared" si="1"/>
+        <v>1090</v>
+      </c>
+      <c r="J51" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="K51" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L51" s="5" t="s">
+        <v>1427</v>
+      </c>
+    </row>
+    <row r="52" spans="1:17" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B52" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="C52" s="11" t="s">
+        <v>1313</v>
+      </c>
+      <c r="D52" s="11" t="s">
+        <v>1314</v>
+      </c>
+      <c r="E52" s="11" t="s">
+        <v>1315</v>
+      </c>
+      <c r="F52" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="G52" s="11">
+        <v>1115</v>
+      </c>
+      <c r="H52" s="11">
+        <v>0</v>
+      </c>
+      <c r="I52" s="11">
+        <f t="shared" si="1"/>
+        <v>1115</v>
+      </c>
+      <c r="J52" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="K52" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="L52" s="11" t="s">
+        <v>1294</v>
+      </c>
+      <c r="M52" s="11" t="s">
+        <v>1549</v>
+      </c>
+      <c r="N52" s="11" t="s">
+        <v>430</v>
+      </c>
+      <c r="O52" s="11" t="s">
+        <v>430</v>
+      </c>
+      <c r="P52" s="11" t="s">
+        <v>431</v>
+      </c>
+      <c r="Q52" s="11">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
+  <dimension ref="A1:P53"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="46.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="62" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.5703125" customWidth="1"/>
+    <col min="12" max="12" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B1" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1550</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>383</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>1551</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>1552</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>811</v>
+      </c>
+      <c r="G3" s="9">
+        <v>775</v>
+      </c>
+      <c r="H3" s="9">
+        <v>25</v>
+      </c>
+      <c r="I3" s="9">
+        <f t="shared" ref="I3:I34" si="0">G3-H3</f>
+        <v>750</v>
+      </c>
+      <c r="J3" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="K3" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L3" s="9" t="s">
+        <v>1553</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>1554</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>1555</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="G4" s="3">
+        <v>975</v>
+      </c>
+      <c r="H4" s="3">
+        <v>25</v>
+      </c>
+      <c r="I4" s="3">
+        <f t="shared" si="0"/>
+        <v>950</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>1553</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>1556</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>1557</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>1558</v>
+      </c>
+      <c r="F5" s="10" t="s">
+        <v>790</v>
+      </c>
+      <c r="G5" s="9">
+        <v>775</v>
+      </c>
+      <c r="H5" s="9">
+        <v>25</v>
+      </c>
+      <c r="I5" s="9">
+        <f t="shared" si="0"/>
+        <v>750</v>
+      </c>
+      <c r="J5" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="K5" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L5" s="9" t="s">
+        <v>1553</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>1559</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>1560</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>1656</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>1199</v>
+      </c>
+      <c r="G6" s="5">
+        <v>820</v>
+      </c>
+      <c r="H6" s="5">
+        <v>30</v>
+      </c>
+      <c r="I6" s="5">
+        <f t="shared" si="0"/>
+        <v>790</v>
+      </c>
+      <c r="J6" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="K6" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L6" s="5" t="s">
+        <v>1553</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>1562</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>1563</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>1674</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>775</v>
+      </c>
+      <c r="G7" s="7">
+        <v>870</v>
+      </c>
+      <c r="H7" s="7">
+        <v>30</v>
+      </c>
+      <c r="I7" s="7">
+        <f t="shared" si="0"/>
+        <v>840</v>
+      </c>
+      <c r="J7" s="7" t="s">
+        <v>1561</v>
+      </c>
+      <c r="K7" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L7" s="7" t="s">
+        <v>1553</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>1564</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>1565</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>1669</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G8" s="7">
+        <v>980</v>
+      </c>
+      <c r="H8" s="7">
+        <v>30</v>
+      </c>
+      <c r="I8" s="7">
+        <f t="shared" si="0"/>
+        <v>950</v>
+      </c>
+      <c r="J8" s="7" t="s">
+        <v>1561</v>
+      </c>
+      <c r="K8" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L8" s="7" t="s">
+        <v>1553</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>1566</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>1567</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>1568</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G9" s="7">
+        <v>1440</v>
+      </c>
+      <c r="H9" s="7">
+        <v>30</v>
+      </c>
+      <c r="I9" s="7">
+        <f t="shared" si="0"/>
+        <v>1410</v>
+      </c>
+      <c r="J9" s="7" t="s">
+        <v>1561</v>
+      </c>
+      <c r="K9" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L9" s="7" t="s">
+        <v>1553</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>687</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>1569</v>
+      </c>
+      <c r="E10" s="9" t="s">
+        <v>1361</v>
+      </c>
+      <c r="F10" s="10" t="s">
+        <v>807</v>
+      </c>
+      <c r="G10" s="9">
+        <v>895</v>
+      </c>
+      <c r="H10" s="9">
+        <v>25</v>
+      </c>
+      <c r="I10" s="9">
+        <f t="shared" si="0"/>
+        <v>870</v>
+      </c>
+      <c r="J10" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="K10" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L10" s="9" t="s">
+        <v>1553</v>
+      </c>
+      <c r="M10" s="9" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>1570</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>1571</v>
+      </c>
+      <c r="E11" s="9" t="s">
+        <v>1572</v>
+      </c>
+      <c r="F11" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="G11" s="9">
+        <v>590</v>
+      </c>
+      <c r="H11" s="9">
+        <v>20</v>
+      </c>
+      <c r="I11" s="9">
+        <f t="shared" si="0"/>
+        <v>570</v>
+      </c>
+      <c r="J11" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="K11" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L11" s="9" t="s">
+        <v>1553</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>1573</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>1574</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>1575</v>
+      </c>
+      <c r="F12" s="10" t="s">
+        <v>824</v>
+      </c>
+      <c r="G12" s="9">
+        <v>845</v>
+      </c>
+      <c r="H12" s="9">
+        <v>25</v>
+      </c>
+      <c r="I12" s="9">
+        <f t="shared" si="0"/>
+        <v>820</v>
+      </c>
+      <c r="J12" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="K12" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L12" s="9" t="s">
+        <v>1553</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>1576</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>1577</v>
+      </c>
+      <c r="E13" s="9" t="s">
+        <v>1578</v>
+      </c>
+      <c r="F13" s="10" t="s">
+        <v>824</v>
+      </c>
+      <c r="G13" s="9">
+        <v>0</v>
+      </c>
+      <c r="H13" s="9">
+        <v>25</v>
+      </c>
+      <c r="I13" s="9">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J13" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="K13" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L13" s="9" t="s">
+        <v>1553</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>1579</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>1580</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>1673</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G14" s="7">
+        <v>1780</v>
+      </c>
+      <c r="H14" s="7">
+        <v>30</v>
+      </c>
+      <c r="I14" s="7">
+        <f t="shared" si="0"/>
+        <v>1750</v>
+      </c>
+      <c r="J14" s="7" t="s">
+        <v>1561</v>
+      </c>
+      <c r="K14" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L14" s="7" t="s">
+        <v>1553</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>1581</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>1582</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>1583</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="G15" s="3">
+        <v>0</v>
+      </c>
+      <c r="H15" s="3">
+        <v>25</v>
+      </c>
+      <c r="I15" s="3">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L15" s="3" t="s">
+        <v>1553</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>1584</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>1585</v>
+      </c>
+      <c r="E16" s="9" t="s">
+        <v>1586</v>
+      </c>
+      <c r="F16" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="G16" s="9">
+        <v>1515</v>
+      </c>
+      <c r="H16" s="9">
+        <v>25</v>
+      </c>
+      <c r="I16" s="9">
+        <f t="shared" si="0"/>
+        <v>1490</v>
+      </c>
+      <c r="J16" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="K16" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L16" s="9" t="s">
+        <v>1553</v>
+      </c>
+    </row>
+    <row r="17" spans="2:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>1587</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>1588</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>1672</v>
+      </c>
+      <c r="F17" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="G17" s="7">
+        <v>915</v>
+      </c>
+      <c r="H17" s="7">
+        <v>25</v>
+      </c>
+      <c r="I17" s="7">
+        <f t="shared" si="0"/>
+        <v>890</v>
+      </c>
+      <c r="J17" s="7" t="s">
+        <v>1561</v>
+      </c>
+      <c r="K17" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L17" s="7" t="s">
+        <v>1553</v>
+      </c>
+    </row>
+    <row r="18" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>974</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>1589</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>1648</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="G18" s="3">
+        <v>0</v>
+      </c>
+      <c r="H18" s="3">
+        <v>20</v>
+      </c>
+      <c r="I18" s="3">
+        <f t="shared" si="0"/>
+        <v>-20</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L18" s="3" t="s">
+        <v>1553</v>
+      </c>
+    </row>
+    <row r="19" spans="2:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>1590</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>1591</v>
+      </c>
+      <c r="E19" s="9" t="s">
+        <v>1592</v>
+      </c>
+      <c r="F19" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="G19" s="9">
+        <v>915</v>
+      </c>
+      <c r="H19" s="9">
+        <v>25</v>
+      </c>
+      <c r="I19" s="9">
+        <f t="shared" si="0"/>
+        <v>890</v>
+      </c>
+      <c r="J19" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="K19" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L19" s="9" t="s">
+        <v>1553</v>
+      </c>
+    </row>
+    <row r="20" spans="2:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>1593</v>
+      </c>
+      <c r="D20" s="9" t="s">
+        <v>1594</v>
+      </c>
+      <c r="E20" s="9" t="s">
+        <v>1595</v>
+      </c>
+      <c r="F20" s="10" t="s">
+        <v>807</v>
+      </c>
+      <c r="G20" s="9">
+        <v>725</v>
+      </c>
+      <c r="H20" s="9">
+        <v>25</v>
+      </c>
+      <c r="I20" s="9">
+        <f t="shared" si="0"/>
+        <v>700</v>
+      </c>
+      <c r="J20" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="K20" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L20" s="9" t="s">
+        <v>1553</v>
+      </c>
+    </row>
+    <row r="21" spans="2:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C21" s="9" t="s">
+        <v>1596</v>
+      </c>
+      <c r="D21" s="9" t="s">
+        <v>1597</v>
+      </c>
+      <c r="E21" s="9" t="s">
+        <v>1598</v>
+      </c>
+      <c r="F21" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="G21" s="9">
+        <v>690</v>
+      </c>
+      <c r="H21" s="9">
+        <v>20</v>
+      </c>
+      <c r="I21" s="9">
+        <f t="shared" si="0"/>
+        <v>670</v>
+      </c>
+      <c r="J21" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="K21" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L21" s="9" t="s">
+        <v>1553</v>
+      </c>
+    </row>
+    <row r="22" spans="2:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C22" s="9" t="s">
+        <v>1599</v>
+      </c>
+      <c r="D22" s="9" t="s">
+        <v>1600</v>
+      </c>
+      <c r="E22" s="9" t="s">
+        <v>1601</v>
+      </c>
+      <c r="F22" s="10" t="s">
+        <v>824</v>
+      </c>
+      <c r="G22" s="9">
+        <v>845</v>
+      </c>
+      <c r="H22" s="9">
+        <v>25</v>
+      </c>
+      <c r="I22" s="9">
+        <f t="shared" si="0"/>
+        <v>820</v>
+      </c>
+      <c r="J22" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="K22" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L22" s="9" t="s">
+        <v>1553</v>
+      </c>
+    </row>
+    <row r="23" spans="2:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>1602</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>1603</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>1604</v>
+      </c>
+      <c r="F23" s="8" t="s">
+        <v>775</v>
+      </c>
+      <c r="G23" s="7">
+        <v>0</v>
+      </c>
+      <c r="H23" s="7">
+        <v>25</v>
+      </c>
+      <c r="I23" s="7">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J23" s="7" t="s">
+        <v>1561</v>
+      </c>
+      <c r="K23" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L23" s="7" t="s">
+        <v>1553</v>
+      </c>
+    </row>
+    <row r="24" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>1653</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>1605</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>1654</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="G24" s="3">
+        <v>1700</v>
+      </c>
+      <c r="H24" s="3">
+        <v>20</v>
+      </c>
+      <c r="I24" s="3">
+        <f t="shared" si="0"/>
+        <v>1680</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K24" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L24" s="3" t="s">
+        <v>1553</v>
+      </c>
+    </row>
+    <row r="25" spans="2:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>1606</v>
+      </c>
+      <c r="D25" s="9" t="s">
+        <v>1664</v>
+      </c>
+      <c r="E25" s="9" t="s">
+        <v>1665</v>
+      </c>
+      <c r="F25" s="10" t="s">
+        <v>1060</v>
+      </c>
+      <c r="G25" s="9">
+        <v>595</v>
+      </c>
+      <c r="H25" s="9">
+        <v>25</v>
+      </c>
+      <c r="I25" s="9">
+        <f t="shared" si="0"/>
+        <v>570</v>
+      </c>
+      <c r="J25" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="K25" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L25" s="9" t="s">
+        <v>1553</v>
+      </c>
+    </row>
+    <row r="26" spans="2:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C26" s="9" t="s">
+        <v>687</v>
+      </c>
+      <c r="D26" s="9" t="s">
+        <v>1607</v>
+      </c>
+      <c r="E26" s="9" t="s">
+        <v>1361</v>
+      </c>
+      <c r="F26" s="10" t="s">
+        <v>807</v>
+      </c>
+      <c r="G26" s="9">
+        <v>890</v>
+      </c>
+      <c r="H26" s="9">
+        <v>0</v>
+      </c>
+      <c r="I26" s="9">
+        <f t="shared" si="0"/>
+        <v>890</v>
+      </c>
+      <c r="J26" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="K26" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L26" s="9" t="s">
+        <v>1553</v>
+      </c>
+      <c r="M26" s="9" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="27" spans="2:13" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>1608</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>1609</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>1658</v>
+      </c>
+      <c r="F27" s="6" t="s">
+        <v>1199</v>
+      </c>
+      <c r="G27" s="5">
+        <v>0</v>
+      </c>
+      <c r="H27" s="5">
+        <v>30</v>
+      </c>
+      <c r="I27" s="5">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J27" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="K27" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L27" s="5" t="s">
+        <v>1553</v>
+      </c>
+    </row>
+    <row r="28" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>1610</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>1611</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>1655</v>
+      </c>
+      <c r="F28" s="4">
+        <v>2</v>
+      </c>
+      <c r="G28" s="3">
+        <v>820</v>
+      </c>
+      <c r="H28" s="3">
+        <v>30</v>
+      </c>
+      <c r="I28" s="3">
+        <f t="shared" si="0"/>
+        <v>790</v>
+      </c>
+      <c r="J28" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K28" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L28" s="3" t="s">
+        <v>1553</v>
+      </c>
+    </row>
+    <row r="29" spans="2:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>1612</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>1613</v>
+      </c>
+      <c r="E29" s="7" t="s">
+        <v>1675</v>
+      </c>
+      <c r="F29" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="G29" s="7">
+        <v>955</v>
+      </c>
+      <c r="H29" s="7">
+        <v>25</v>
+      </c>
+      <c r="I29" s="7">
+        <f t="shared" si="0"/>
+        <v>930</v>
+      </c>
+      <c r="J29" s="7" t="s">
+        <v>1561</v>
+      </c>
+      <c r="K29" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L29" s="7" t="s">
+        <v>1553</v>
+      </c>
+    </row>
+    <row r="30" spans="2:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C30" s="7" t="s">
+        <v>1614</v>
+      </c>
+      <c r="D30" s="7" t="s">
+        <v>1670</v>
+      </c>
+      <c r="E30" s="7" t="s">
+        <v>1671</v>
+      </c>
+      <c r="F30" s="8" t="s">
+        <v>800</v>
+      </c>
+      <c r="G30" s="7">
+        <v>0</v>
+      </c>
+      <c r="H30" s="7">
+        <v>30</v>
+      </c>
+      <c r="I30" s="7">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J30" s="7" t="s">
+        <v>1561</v>
+      </c>
+      <c r="K30" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L30" s="7" t="s">
+        <v>1553</v>
+      </c>
+    </row>
+    <row r="31" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B31" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>1615</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>1616</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>1617</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="G31" s="3">
+        <v>1960</v>
+      </c>
+      <c r="H31" s="3">
+        <v>30</v>
+      </c>
+      <c r="I31" s="3">
+        <f t="shared" si="0"/>
+        <v>1930</v>
+      </c>
+      <c r="J31" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K31" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L31" s="3" t="s">
+        <v>1553</v>
+      </c>
+      <c r="M31" s="3" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="32" spans="2:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B32" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C32" s="7" t="s">
+        <v>1618</v>
+      </c>
+      <c r="D32" s="7" t="s">
+        <v>1619</v>
+      </c>
+      <c r="E32" s="7" t="s">
+        <v>1676</v>
+      </c>
+      <c r="F32" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="G32" s="7">
+        <v>0</v>
+      </c>
+      <c r="H32" s="7">
+        <v>35</v>
+      </c>
+      <c r="I32" s="7">
+        <f t="shared" si="0"/>
+        <v>-35</v>
+      </c>
+      <c r="J32" s="7" t="s">
+        <v>1561</v>
+      </c>
+      <c r="K32" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L32" s="7" t="s">
+        <v>1553</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B33" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>1620</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>1621</v>
+      </c>
+      <c r="E33" s="7" t="s">
+        <v>1622</v>
+      </c>
+      <c r="F33" s="8" t="s">
+        <v>763</v>
+      </c>
+      <c r="G33" s="7">
+        <v>0</v>
+      </c>
+      <c r="H33" s="7">
+        <v>25</v>
+      </c>
+      <c r="I33" s="7">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J33" s="7" t="s">
+        <v>1561</v>
+      </c>
+      <c r="K33" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L33" s="7" t="s">
+        <v>1553</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B34" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C34" s="9" t="s">
+        <v>463</v>
+      </c>
+      <c r="D34" s="9" t="s">
+        <v>1623</v>
+      </c>
+      <c r="E34" s="9" t="s">
+        <v>465</v>
+      </c>
+      <c r="F34" s="10" t="s">
+        <v>811</v>
+      </c>
+      <c r="G34" s="9">
+        <v>1015</v>
+      </c>
+      <c r="H34" s="9">
+        <v>25</v>
+      </c>
+      <c r="I34" s="9">
+        <f t="shared" si="0"/>
+        <v>990</v>
+      </c>
+      <c r="J34" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="K34" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L34" s="9" t="s">
+        <v>1553</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B35" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>1624</v>
+      </c>
+      <c r="D35" s="7" t="s">
+        <v>1625</v>
+      </c>
+      <c r="E35" s="7" t="s">
+        <v>1626</v>
+      </c>
+      <c r="F35" s="8" t="s">
+        <v>997</v>
+      </c>
+      <c r="G35" s="7">
+        <v>785</v>
+      </c>
+      <c r="H35" s="7">
+        <v>25</v>
+      </c>
+      <c r="I35" s="7">
+        <f t="shared" ref="I35:I66" si="1">G35-H35</f>
+        <v>760</v>
+      </c>
+      <c r="J35" s="7" t="s">
+        <v>1561</v>
+      </c>
+      <c r="K35" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L35" s="7" t="s">
+        <v>1553</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B36" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>1627</v>
+      </c>
+      <c r="D36" s="5" t="s">
+        <v>1628</v>
+      </c>
+      <c r="E36" s="5" t="s">
+        <v>1657</v>
+      </c>
+      <c r="F36" s="6" t="s">
+        <v>1199</v>
+      </c>
+      <c r="G36" s="5">
+        <v>750</v>
+      </c>
+      <c r="H36" s="5">
+        <v>30</v>
+      </c>
+      <c r="I36" s="5">
+        <f t="shared" si="1"/>
+        <v>720</v>
+      </c>
+      <c r="J36" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="K36" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L36" s="5" t="s">
+        <v>1553</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B37" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C37" s="9" t="s">
+        <v>684</v>
+      </c>
+      <c r="D37" s="9" t="s">
+        <v>1629</v>
+      </c>
+      <c r="E37" s="9" t="s">
+        <v>1661</v>
+      </c>
+      <c r="F37" s="10" t="s">
+        <v>807</v>
+      </c>
+      <c r="G37" s="9">
+        <v>400</v>
+      </c>
+      <c r="H37" s="9">
+        <v>20</v>
+      </c>
+      <c r="I37" s="9">
+        <f t="shared" si="1"/>
+        <v>380</v>
+      </c>
+      <c r="J37" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="K37" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L37" s="9" t="s">
+        <v>1553</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B38" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C38" s="7" t="s">
+        <v>1348</v>
+      </c>
+      <c r="D38" s="7" t="s">
+        <v>1630</v>
+      </c>
+      <c r="E38" s="7" t="s">
+        <v>1350</v>
+      </c>
+      <c r="F38" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="G38" s="7">
+        <v>745</v>
+      </c>
+      <c r="H38" s="7">
+        <v>35</v>
+      </c>
+      <c r="I38" s="7">
+        <f t="shared" si="1"/>
+        <v>710</v>
+      </c>
+      <c r="J38" s="7" t="s">
+        <v>1561</v>
+      </c>
+      <c r="K38" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L38" s="7" t="s">
+        <v>1553</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B39" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>1631</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>1632</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>1646</v>
+      </c>
+      <c r="F39" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="G39" s="3">
+        <v>475</v>
+      </c>
+      <c r="H39" s="3">
+        <v>25</v>
+      </c>
+      <c r="I39" s="3">
+        <f t="shared" si="1"/>
+        <v>450</v>
+      </c>
+      <c r="J39" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K39" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L39" s="3" t="s">
+        <v>1553</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B40" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>1633</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="F40" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="G40" s="3">
+        <v>0</v>
+      </c>
+      <c r="H40" s="3">
+        <v>20</v>
+      </c>
+      <c r="I40" s="3">
+        <f t="shared" si="1"/>
+        <v>-20</v>
+      </c>
+      <c r="J40" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K40" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L40" s="3" t="s">
+        <v>1553</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B41" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>1634</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>1635</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>1647</v>
+      </c>
+      <c r="F41" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="G41" s="3">
+        <v>745</v>
+      </c>
+      <c r="H41" s="3">
+        <v>25</v>
+      </c>
+      <c r="I41" s="3">
+        <f t="shared" si="1"/>
+        <v>720</v>
+      </c>
+      <c r="J41" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K41" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L41" s="3" t="s">
+        <v>1553</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B42" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C42" s="9" t="s">
+        <v>615</v>
+      </c>
+      <c r="D42" s="9" t="s">
+        <v>1636</v>
+      </c>
+      <c r="E42" s="9" t="s">
+        <v>617</v>
+      </c>
+      <c r="F42" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="G42" s="9">
+        <v>875</v>
+      </c>
+      <c r="H42" s="9">
+        <v>25</v>
+      </c>
+      <c r="I42" s="9">
+        <f t="shared" si="1"/>
+        <v>850</v>
+      </c>
+      <c r="J42" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="K42" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L42" s="9" t="s">
+        <v>1553</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B43" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C43" s="9" t="s">
+        <v>1662</v>
+      </c>
+      <c r="D43" s="9" t="s">
+        <v>1637</v>
+      </c>
+      <c r="E43" s="9" t="s">
+        <v>1663</v>
+      </c>
+      <c r="F43" s="10" t="s">
+        <v>807</v>
+      </c>
+      <c r="G43" s="9">
+        <v>1665</v>
+      </c>
+      <c r="H43" s="9">
+        <v>25</v>
+      </c>
+      <c r="I43" s="9">
+        <f t="shared" si="1"/>
+        <v>1640</v>
+      </c>
+      <c r="J43" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="K43" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L43" s="9" t="s">
+        <v>1553</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B44" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>1638</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>1639</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="F44" s="4" t="s">
+        <v>1085</v>
+      </c>
+      <c r="G44" s="3">
+        <v>0</v>
+      </c>
+      <c r="H44" s="3">
+        <v>30</v>
+      </c>
+      <c r="I44" s="3">
+        <f t="shared" si="1"/>
+        <v>-30</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K44" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L44" s="3" t="s">
+        <v>1553</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B45" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C45" s="7" t="s">
+        <v>1640</v>
+      </c>
+      <c r="D45" s="7" t="s">
+        <v>1641</v>
+      </c>
+      <c r="E45" s="7" t="s">
+        <v>1642</v>
+      </c>
+      <c r="F45" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G45" s="7">
+        <v>920</v>
+      </c>
+      <c r="H45" s="7">
+        <v>30</v>
+      </c>
+      <c r="I45" s="7">
+        <f t="shared" si="1"/>
+        <v>890</v>
+      </c>
+      <c r="J45" s="7" t="s">
+        <v>1561</v>
+      </c>
+      <c r="K45" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L45" s="7" t="s">
+        <v>1553</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>1643</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>1649</v>
+      </c>
+      <c r="F46" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="G46" s="3">
+        <v>0</v>
+      </c>
+      <c r="H46" s="3">
+        <v>30</v>
+      </c>
+      <c r="I46" s="3">
+        <f t="shared" si="1"/>
+        <v>-30</v>
+      </c>
+      <c r="J46" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K46" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L46" s="3" t="s">
+        <v>1553</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>1650</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="F47" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="G47" s="3">
+        <v>970</v>
+      </c>
+      <c r="H47" s="3">
+        <v>30</v>
+      </c>
+      <c r="I47" s="3">
+        <f t="shared" si="1"/>
+        <v>940</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K47" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L47" s="3" t="s">
+        <v>1553</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>1651</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>1652</v>
+      </c>
+      <c r="F48" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="G48" s="3">
+        <v>30</v>
+      </c>
+      <c r="H48" s="3">
+        <v>30</v>
+      </c>
+      <c r="I48" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J48" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K48" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L48" s="3" t="s">
+        <v>1553</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="B49" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C49" s="7" t="s">
+        <v>1644</v>
+      </c>
+      <c r="E49" s="7" t="s">
+        <v>1666</v>
+      </c>
+      <c r="F49" s="8" t="s">
+        <v>775</v>
+      </c>
+      <c r="G49" s="7">
+        <v>40</v>
+      </c>
+      <c r="H49" s="7">
+        <v>40</v>
+      </c>
+      <c r="I49" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J49" s="7" t="s">
+        <v>1561</v>
+      </c>
+      <c r="K49" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L49" s="7" t="s">
+        <v>1553</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="B50" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C50" s="7" t="s">
+        <v>1667</v>
+      </c>
+      <c r="E50" s="7" t="s">
+        <v>1668</v>
+      </c>
+      <c r="F50" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="G50" s="7">
+        <v>30</v>
+      </c>
+      <c r="H50" s="7">
+        <v>30</v>
+      </c>
+      <c r="I50" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J50" s="7" t="s">
+        <v>1561</v>
+      </c>
+      <c r="K50" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L50" s="7" t="s">
+        <v>1553</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="B51" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C51" s="9" t="s">
+        <v>1659</v>
+      </c>
+      <c r="E51" s="9" t="s">
+        <v>1660</v>
+      </c>
+      <c r="F51" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="G51" s="9">
+        <v>35</v>
+      </c>
+      <c r="H51" s="9">
+        <v>35</v>
+      </c>
+      <c r="I51" s="9">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J51" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="K51" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L51" s="9" t="s">
+        <v>1553</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>1645</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>877</v>
+      </c>
+      <c r="F52" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="G52" s="3">
+        <v>30</v>
+      </c>
+      <c r="H52" s="3">
+        <v>30</v>
+      </c>
+      <c r="I52" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K52" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L52" s="3" t="s">
+        <v>1553</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>564</v>
+      </c>
+      <c r="E53" s="3" t="s">
+        <v>565</v>
+      </c>
+      <c r="F53" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="G53" s="3">
+        <v>30</v>
+      </c>
+      <c r="H53" s="3">
+        <v>30</v>
+      </c>
+      <c r="I53" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J53" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K53" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L53" s="3" t="s">
+        <v>1553</v>
       </c>
     </row>
   </sheetData>
@@ -12929,7 +17514,7 @@
       <c r="E24" t="s">
         <v>158</v>
       </c>
-      <c r="F24" s="31" t="s">
+      <c r="F24" s="28" t="s">
         <v>38</v>
       </c>
       <c r="G24">
@@ -13051,7 +17636,7 @@
         <v>20</v>
       </c>
       <c r="I3" s="3">
-        <f t="shared" ref="I3:I33" si="0">G3-H3</f>
+        <f t="shared" ref="I3:I34" si="0">G3-H3</f>
         <v>660</v>
       </c>
       <c r="J3" s="3" t="s">
@@ -14170,7 +18755,7 @@
         <v>25</v>
       </c>
       <c r="I34" s="7">
-        <f t="shared" ref="I34:I52" si="1">G34-H34</f>
+        <f t="shared" si="0"/>
         <v>660</v>
       </c>
       <c r="J34" s="7" t="s">
@@ -14209,7 +18794,7 @@
         <v>25</v>
       </c>
       <c r="I35" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="I35:I66" si="1">G35-H35</f>
         <v>790</v>
       </c>
       <c r="J35" s="3" t="s">
@@ -14856,7 +19441,7 @@
       <c r="E53" t="s">
         <v>303</v>
       </c>
-      <c r="F53" s="31">
+      <c r="F53" s="28">
         <v>6</v>
       </c>
       <c r="G53">
@@ -16465,7 +21050,7 @@
       <c r="E44" t="s">
         <v>136</v>
       </c>
-      <c r="F44" s="31">
+      <c r="F44" s="28">
         <v>7</v>
       </c>
       <c r="G44">
@@ -16611,7 +21196,7 @@
         <v>30</v>
       </c>
       <c r="I3" s="13">
-        <f t="shared" ref="I3:I33" si="0">G3-H3</f>
+        <f t="shared" ref="I3:I34" si="0">G3-H3</f>
         <v>2360</v>
       </c>
       <c r="J3" s="7" t="s">
@@ -17826,7 +22411,7 @@
         <v>25</v>
       </c>
       <c r="I34" s="13">
-        <f t="shared" ref="I34:I53" si="1">G34-H34</f>
+        <f t="shared" si="0"/>
         <v>1610</v>
       </c>
       <c r="J34" s="7" t="s">
@@ -17865,7 +22450,7 @@
         <v>35</v>
       </c>
       <c r="I35" s="12">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="I35:I66" si="1">G35-H35</f>
         <v>440</v>
       </c>
       <c r="J35" s="3" t="s">
@@ -18642,7 +23227,7 @@
       <c r="E55" t="s">
         <v>345</v>
       </c>
-      <c r="F55" s="31">
+      <c r="F55" s="28">
         <v>1</v>
       </c>
       <c r="G55">
@@ -19651,7 +24236,7 @@
       <c r="E28" t="s">
         <v>406</v>
       </c>
-      <c r="F28" s="31">
+      <c r="F28" s="28">
         <v>12</v>
       </c>
       <c r="G28">
@@ -22877,7 +27462,7 @@
       <c r="E3" s="19" t="s">
         <v>567</v>
       </c>
-      <c r="F3" s="29" t="s">
+      <c r="F3" s="26" t="s">
         <v>811</v>
       </c>
       <c r="G3" s="19">
@@ -22919,7 +27504,7 @@
       <c r="E4" s="18" t="s">
         <v>877</v>
       </c>
-      <c r="F4" s="27" t="s">
+      <c r="F4" s="24" t="s">
         <v>88</v>
       </c>
       <c r="G4" s="18">
@@ -22961,7 +27546,7 @@
       <c r="E5" s="18" t="s">
         <v>641</v>
       </c>
-      <c r="F5" s="27" t="s">
+      <c r="F5" s="24" t="s">
         <v>46</v>
       </c>
       <c r="G5" s="18">
@@ -23003,7 +27588,7 @@
       <c r="E6" s="18" t="s">
         <v>879</v>
       </c>
-      <c r="F6" s="27">
+      <c r="F6" s="24">
         <v>2</v>
       </c>
       <c r="G6" s="18">
@@ -23045,7 +27630,7 @@
       <c r="E7" s="18" t="s">
         <v>880</v>
       </c>
-      <c r="F7" s="27" t="s">
+      <c r="F7" s="24" t="s">
         <v>46</v>
       </c>
       <c r="G7" s="18">
@@ -23087,7 +27672,7 @@
       <c r="E8" s="18" t="s">
         <v>643</v>
       </c>
-      <c r="F8" s="27">
+      <c r="F8" s="24">
         <v>12</v>
       </c>
       <c r="G8" s="18">
@@ -23129,7 +27714,7 @@
       <c r="E9" s="18" t="s">
         <v>884</v>
       </c>
-      <c r="F9" s="27" t="s">
+      <c r="F9" s="24" t="s">
         <v>38</v>
       </c>
       <c r="G9" s="18">
@@ -23171,7 +27756,7 @@
       <c r="E10" s="18" t="s">
         <v>887</v>
       </c>
-      <c r="F10" s="27">
+      <c r="F10" s="24">
         <v>2</v>
       </c>
       <c r="G10" s="18">
@@ -23213,7 +27798,7 @@
       <c r="E11" s="19" t="s">
         <v>890</v>
       </c>
-      <c r="F11" s="29" t="s">
+      <c r="F11" s="26" t="s">
         <v>824</v>
       </c>
       <c r="G11" s="19">
@@ -23255,7 +27840,7 @@
       <c r="E12" s="18" t="s">
         <v>848</v>
       </c>
-      <c r="F12" s="27" t="s">
+      <c r="F12" s="24" t="s">
         <v>768</v>
       </c>
       <c r="G12" s="18">
@@ -23297,7 +27882,7 @@
       <c r="E13" s="20" t="s">
         <v>894</v>
       </c>
-      <c r="F13" s="28" t="s">
+      <c r="F13" s="25" t="s">
         <v>22</v>
       </c>
       <c r="G13" s="20">
@@ -23339,7 +27924,7 @@
       <c r="E14" s="19" t="s">
         <v>898</v>
       </c>
-      <c r="F14" s="29" t="s">
+      <c r="F14" s="26" t="s">
         <v>81</v>
       </c>
       <c r="G14" s="19">
@@ -23381,7 +27966,7 @@
       <c r="E15" s="19" t="s">
         <v>901</v>
       </c>
-      <c r="F15" s="29">
+      <c r="F15" s="26">
         <v>1</v>
       </c>
       <c r="G15" s="19">
@@ -23423,7 +28008,7 @@
       <c r="E16" s="19" t="s">
         <v>904</v>
       </c>
-      <c r="F16" s="29" t="s">
+      <c r="F16" s="26" t="s">
         <v>88</v>
       </c>
       <c r="G16" s="19">
@@ -23465,7 +28050,7 @@
       <c r="E17" s="19" t="s">
         <v>907</v>
       </c>
-      <c r="F17" s="29" t="s">
+      <c r="F17" s="26" t="s">
         <v>81</v>
       </c>
       <c r="G17" s="19">
@@ -23507,7 +28092,7 @@
       <c r="E18" s="19" t="s">
         <v>910</v>
       </c>
-      <c r="F18" s="29" t="s">
+      <c r="F18" s="26" t="s">
         <v>807</v>
       </c>
       <c r="G18" s="19">
@@ -23551,7 +28136,7 @@
       <c r="E19" s="20" t="s">
         <v>913</v>
       </c>
-      <c r="F19" s="28" t="s">
+      <c r="F19" s="25" t="s">
         <v>763</v>
       </c>
       <c r="G19" s="20">
@@ -23593,7 +28178,7 @@
       <c r="E20" s="18" t="s">
         <v>107</v>
       </c>
-      <c r="F20" s="27" t="s">
+      <c r="F20" s="24" t="s">
         <v>38</v>
       </c>
       <c r="G20" s="18">
@@ -23637,7 +28222,7 @@
       <c r="E21" s="19" t="s">
         <v>324</v>
       </c>
-      <c r="F21" s="29" t="s">
+      <c r="F21" s="26" t="s">
         <v>790</v>
       </c>
       <c r="G21" s="19">
@@ -23679,7 +28264,7 @@
       <c r="E22" s="18" t="s">
         <v>917</v>
       </c>
-      <c r="F22" s="27" t="s">
+      <c r="F22" s="24" t="s">
         <v>46</v>
       </c>
       <c r="G22" s="18">
@@ -23721,7 +28306,7 @@
       <c r="E23" s="19" t="s">
         <v>920</v>
       </c>
-      <c r="F23" s="29" t="s">
+      <c r="F23" s="26" t="s">
         <v>88</v>
       </c>
       <c r="G23" s="19">
@@ -23763,7 +28348,7 @@
       <c r="E24" s="20" t="s">
         <v>923</v>
       </c>
-      <c r="F24" s="28" t="s">
+      <c r="F24" s="25" t="s">
         <v>88</v>
       </c>
       <c r="G24" s="20">
@@ -23805,7 +28390,7 @@
       <c r="E25" s="20" t="s">
         <v>926</v>
       </c>
-      <c r="F25" s="28" t="s">
+      <c r="F25" s="25" t="s">
         <v>775</v>
       </c>
       <c r="G25" s="20">
@@ -23847,7 +28432,7 @@
       <c r="E26" s="19" t="s">
         <v>929</v>
       </c>
-      <c r="F26" s="29" t="s">
+      <c r="F26" s="26" t="s">
         <v>790</v>
       </c>
       <c r="G26" s="19">
@@ -23889,7 +28474,7 @@
       <c r="E27" s="20" t="s">
         <v>932</v>
       </c>
-      <c r="F27" s="28" t="s">
+      <c r="F27" s="25" t="s">
         <v>800</v>
       </c>
       <c r="G27" s="20">
@@ -23933,7 +28518,7 @@
       <c r="E28" s="18" t="s">
         <v>935</v>
       </c>
-      <c r="F28" s="27" t="s">
+      <c r="F28" s="24" t="s">
         <v>46</v>
       </c>
       <c r="G28" s="18">
@@ -23975,7 +28560,7 @@
       <c r="E29" s="18" t="s">
         <v>938</v>
       </c>
-      <c r="F29" s="27">
+      <c r="F29" s="24">
         <v>2</v>
       </c>
       <c r="G29" s="18">
@@ -24017,7 +28602,7 @@
       <c r="E30" s="19" t="s">
         <v>941</v>
       </c>
-      <c r="F30" s="29" t="s">
+      <c r="F30" s="26" t="s">
         <v>790</v>
       </c>
       <c r="G30" s="19">
@@ -24059,7 +28644,7 @@
       <c r="E31" s="18" t="s">
         <v>944</v>
       </c>
-      <c r="F31" s="27" t="s">
+      <c r="F31" s="24" t="s">
         <v>768</v>
       </c>
       <c r="G31" s="18">
@@ -24101,7 +28686,7 @@
       <c r="E32" s="18" t="s">
         <v>947</v>
       </c>
-      <c r="F32" s="27" t="s">
+      <c r="F32" s="24" t="s">
         <v>768</v>
       </c>
       <c r="G32" s="18">
@@ -24143,7 +28728,7 @@
       <c r="E33" s="20" t="s">
         <v>950</v>
       </c>
-      <c r="F33" s="28" t="s">
+      <c r="F33" s="25" t="s">
         <v>763</v>
       </c>
       <c r="G33" s="20">
@@ -24185,7 +28770,7 @@
       <c r="E34" s="20" t="s">
         <v>953</v>
       </c>
-      <c r="F34" s="28" t="s">
+      <c r="F34" s="25" t="s">
         <v>208</v>
       </c>
       <c r="G34" s="20">
@@ -24227,7 +28812,7 @@
       <c r="E35" s="18" t="s">
         <v>956</v>
       </c>
-      <c r="F35" s="27" t="s">
+      <c r="F35" s="24" t="s">
         <v>768</v>
       </c>
       <c r="G35" s="18">
@@ -24237,7 +28822,7 @@
         <v>30</v>
       </c>
       <c r="I35" s="18">
-        <f t="shared" ref="I35:I53" si="1">G35-H35</f>
+        <f t="shared" ref="I35:I66" si="1">G35-H35</f>
         <v>860</v>
       </c>
       <c r="J35" s="18" t="s">
@@ -24269,7 +28854,7 @@
       <c r="E36" s="18" t="s">
         <v>959</v>
       </c>
-      <c r="F36" s="27" t="s">
+      <c r="F36" s="24" t="s">
         <v>88</v>
       </c>
       <c r="G36" s="18">
@@ -24311,7 +28896,7 @@
       <c r="E37" s="18" t="s">
         <v>962</v>
       </c>
-      <c r="F37" s="27" t="s">
+      <c r="F37" s="24" t="s">
         <v>768</v>
       </c>
       <c r="G37" s="18">
@@ -24353,7 +28938,7 @@
       <c r="E38" s="18" t="s">
         <v>965</v>
       </c>
-      <c r="F38" s="27" t="s">
+      <c r="F38" s="24" t="s">
         <v>46</v>
       </c>
       <c r="G38" s="18">
@@ -24395,7 +28980,7 @@
       <c r="E39" s="18" t="s">
         <v>968</v>
       </c>
-      <c r="F39" s="27" t="s">
+      <c r="F39" s="24" t="s">
         <v>38</v>
       </c>
       <c r="G39" s="18">
@@ -24437,7 +29022,7 @@
       <c r="E40" s="20" t="s">
         <v>971</v>
       </c>
-      <c r="F40" s="28" t="s">
+      <c r="F40" s="25" t="s">
         <v>800</v>
       </c>
       <c r="G40" s="20">
@@ -24479,7 +29064,7 @@
       <c r="E41" s="20" t="s">
         <v>973</v>
       </c>
-      <c r="F41" s="28" t="s">
+      <c r="F41" s="25" t="s">
         <v>22</v>
       </c>
       <c r="G41" s="20">
@@ -24521,7 +29106,7 @@
       <c r="E42" s="19" t="s">
         <v>976</v>
       </c>
-      <c r="F42" s="29">
+      <c r="F42" s="26">
         <v>1</v>
       </c>
       <c r="G42" s="19">
@@ -24563,7 +29148,7 @@
       <c r="E43" s="19" t="s">
         <v>979</v>
       </c>
-      <c r="F43" s="29" t="s">
+      <c r="F43" s="26" t="s">
         <v>88</v>
       </c>
       <c r="G43" s="19">
@@ -24605,7 +29190,7 @@
       <c r="E44" s="20" t="s">
         <v>982</v>
       </c>
-      <c r="F44" s="28" t="s">
+      <c r="F44" s="25" t="s">
         <v>800</v>
       </c>
       <c r="G44" s="20">
@@ -24647,7 +29232,7 @@
       <c r="E45" s="19" t="s">
         <v>910</v>
       </c>
-      <c r="F45" s="29" t="s">
+      <c r="F45" s="26" t="s">
         <v>807</v>
       </c>
       <c r="G45" s="19">
@@ -24691,7 +29276,7 @@
       <c r="E46" s="19" t="s">
         <v>904</v>
       </c>
-      <c r="F46" s="29" t="s">
+      <c r="F46" s="26" t="s">
         <v>88</v>
       </c>
       <c r="G46" s="19">
@@ -24733,7 +29318,7 @@
       <c r="E47" s="19" t="s">
         <v>987</v>
       </c>
-      <c r="F47" s="29" t="s">
+      <c r="F47" s="26" t="s">
         <v>824</v>
       </c>
       <c r="G47" s="19">
@@ -24775,7 +29360,7 @@
       <c r="E48" s="20" t="s">
         <v>990</v>
       </c>
-      <c r="F48" s="28" t="s">
+      <c r="F48" s="25" t="s">
         <v>88</v>
       </c>
       <c r="G48" s="20">
@@ -24817,7 +29402,7 @@
       <c r="E49" s="20" t="s">
         <v>993</v>
       </c>
-      <c r="F49" s="28" t="s">
+      <c r="F49" s="25" t="s">
         <v>22</v>
       </c>
       <c r="G49" s="20">
@@ -24859,7 +29444,7 @@
       <c r="E50" s="20" t="s">
         <v>996</v>
       </c>
-      <c r="F50" s="28" t="s">
+      <c r="F50" s="25" t="s">
         <v>997</v>
       </c>
       <c r="G50" s="20">
@@ -24901,7 +29486,7 @@
       <c r="E51" s="18" t="s">
         <v>1000</v>
       </c>
-      <c r="F51" s="27" t="s">
+      <c r="F51" s="24" t="s">
         <v>88</v>
       </c>
       <c r="G51" s="18">
@@ -24945,7 +29530,7 @@
       <c r="E52" s="19" t="s">
         <v>1003</v>
       </c>
-      <c r="F52" s="29">
+      <c r="F52" s="26">
         <v>3</v>
       </c>
       <c r="G52" s="19">
@@ -24987,7 +29572,7 @@
       <c r="E53" s="20" t="s">
         <v>1006</v>
       </c>
-      <c r="F53" s="28">
+      <c r="F53" s="25">
         <v>7</v>
       </c>
       <c r="G53" s="20">

--- a/data/Apr/Data.xlsx
+++ b/data/Apr/Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Freelance\TextInputter\data\Apr\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD803C71-00D5-48A2-9A86-1A39A223C7A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{675B32BF-AB00-481C-B155-1FA53D6D4AF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="3" activeTab="17" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="5" activeTab="19" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01-04" sheetId="4" r:id="rId1"/>
@@ -31,6 +31,8 @@
     <sheet name="18-04" sheetId="20" r:id="rId16"/>
     <sheet name="20-04" sheetId="21" r:id="rId17"/>
     <sheet name="21-04" sheetId="22" r:id="rId18"/>
+    <sheet name="22-04" sheetId="23" r:id="rId19"/>
+    <sheet name="23-04" sheetId="24" r:id="rId20"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -53,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6505" uniqueCount="2127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7442" uniqueCount="2407">
   <si>
     <t>THU 4</t>
   </si>
@@ -6434,6 +6436,846 @@
   </si>
   <si>
     <t>181/12 Tam Châu tam bình</t>
+  </si>
+  <si>
+    <t>NGAY 22-4</t>
+  </si>
+  <si>
+    <t>Gia Anh</t>
+  </si>
+  <si>
+    <t>HD014090</t>
+  </si>
+  <si>
+    <t>Landmark Plus - Vinhome Central Park, Số 720, Điện Biên Phủ, Phường 22</t>
+  </si>
+  <si>
+    <t>22-04-2026</t>
+  </si>
+  <si>
+    <t>HD013970</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>VERISKA (YAYANG) - ROOM 104</t>
+  </si>
+  <si>
+    <t>HD014162</t>
+  </si>
+  <si>
+    <t>Saigon Europe Hotel, Số 207 đường Đề Thám, phường bến Thành</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>Quỳnh Vi</t>
+  </si>
+  <si>
+    <t>HD014111</t>
+  </si>
+  <si>
+    <t>40/4 nguyễn văn đậu p5</t>
+  </si>
+  <si>
+    <t>Danh Híi</t>
+  </si>
+  <si>
+    <t>HD014321</t>
+  </si>
+  <si>
+    <t>33 đường D32 - Phước Long B</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>Thiên Nga</t>
+  </si>
+  <si>
+    <t>HD014188</t>
+  </si>
+  <si>
+    <t>S5.02 Vinhomes grand park, Nguyễn Xiển, Long Mỹ</t>
+  </si>
+  <si>
+    <t>Sam Meo</t>
+  </si>
+  <si>
+    <t>HD014212</t>
+  </si>
+  <si>
+    <t>81 Tân Sơn hòa p2</t>
+  </si>
+  <si>
+    <t>CUS19950/pepanhaketya</t>
+  </si>
+  <si>
+    <t>HD014360</t>
+  </si>
+  <si>
+    <t>Ánh Vy</t>
+  </si>
+  <si>
+    <t>HD013979</t>
+  </si>
+  <si>
+    <t>688/23/12 Hương Lộ 2, P. Bình Trị Đông A</t>
+  </si>
+  <si>
+    <t>AT 22-04</t>
+  </si>
+  <si>
+    <t>KIM YẾN ( mụi mụi)</t>
+  </si>
+  <si>
+    <t>HD013983</t>
+  </si>
+  <si>
+    <t>Tk24c/16 Nguyễn cảnh chân thường cầu ông lãnh</t>
+  </si>
+  <si>
+    <t>Kim Ju CUS One Eight Zero Six Seven</t>
+  </si>
+  <si>
+    <t>HD014008</t>
+  </si>
+  <si>
+    <t>HD014053</t>
+  </si>
+  <si>
+    <t>Nguyễn Thư</t>
+  </si>
+  <si>
+    <t>HD014056</t>
+  </si>
+  <si>
+    <t>39 hồ hảo hớn, P. Cô Giang</t>
+  </si>
+  <si>
+    <t>Nguyễn Minh Anhh</t>
+  </si>
+  <si>
+    <t>HD014302</t>
+  </si>
+  <si>
+    <t>385b3 nguyen trai</t>
+  </si>
+  <si>
+    <t>HD014084</t>
+  </si>
+  <si>
+    <t>Tô Tô</t>
+  </si>
+  <si>
+    <t>HD013964</t>
+  </si>
+  <si>
+    <t>46 Lê Thị Riêng, phường Bến Thành</t>
+  </si>
+  <si>
+    <t>Ngân Kim Lê</t>
+  </si>
+  <si>
+    <t>HD013991</t>
+  </si>
+  <si>
+    <t>90 trần đình xu, phường Cầu Ông Lãnh</t>
+  </si>
+  <si>
+    <t>Thảo Nguyên Sarah</t>
+  </si>
+  <si>
+    <t>HD014051</t>
+  </si>
+  <si>
+    <t>199/57A1 lê quang định p7</t>
+  </si>
+  <si>
+    <t>HD013961</t>
+  </si>
+  <si>
+    <t>HD014178</t>
+  </si>
+  <si>
+    <t>Somas dothing (insta soma_clothing21)</t>
+  </si>
+  <si>
+    <t>HD014291</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>Bùi Khánh Ngọc</t>
+  </si>
+  <si>
+    <t>HD014022</t>
+  </si>
+  <si>
+    <t>Cc River Panorama 20 Lê Thị Chợ phường Phú Thuận</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>HD014272</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>Nguyễn Thuỳ Linh</t>
+  </si>
+  <si>
+    <t>HD014325</t>
+  </si>
+  <si>
+    <t>Nắng spa sảnh S803, vinhome grand park, p. Long Thạnh Mỹ</t>
+  </si>
+  <si>
+    <t>HD014224</t>
+  </si>
+  <si>
+    <t>69 phổ tiểu nam, p. Tân Phú</t>
+  </si>
+  <si>
+    <t>HD013989</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>Miko fb Giàu Ngọc</t>
+  </si>
+  <si>
+    <t>HD013962</t>
+  </si>
+  <si>
+    <t>841/4 quốc lộ 13 hiệp bình phước</t>
+  </si>
+  <si>
+    <t>Hoa Cây Cà</t>
+  </si>
+  <si>
+    <t>HD014107</t>
+  </si>
+  <si>
+    <t>36 đường 40 kết vạn phúc, hiệp bình phước</t>
+  </si>
+  <si>
+    <t>HD014007</t>
+  </si>
+  <si>
+    <t>thảo - fb Hang Bui</t>
+  </si>
+  <si>
+    <t>HD014323</t>
+  </si>
+  <si>
+    <t>36/42/2 đường số 4, kp6, hiệp bình phước</t>
+  </si>
+  <si>
+    <t>Nguyễn Vi</t>
+  </si>
+  <si>
+    <t>HD013674</t>
+  </si>
+  <si>
+    <t>L21 Park riverside, đường bưng ông thoàn Phường phú hữu (long trường)</t>
+  </si>
+  <si>
+    <t>HD014195</t>
+  </si>
+  <si>
+    <t>chung cư flora novia, block b phạm văn đồng, an bình</t>
+  </si>
+  <si>
+    <t>Nguyễn Duy</t>
+  </si>
+  <si>
+    <t>HD013999</t>
+  </si>
+  <si>
+    <t>99/13 trần bình trọng p1</t>
+  </si>
+  <si>
+    <t>HD014087</t>
+  </si>
+  <si>
+    <t>160/7 bùi đinh túy,p12</t>
+  </si>
+  <si>
+    <t>HD013988</t>
+  </si>
+  <si>
+    <t>765 Hồng bằng chung cư dhome</t>
+  </si>
+  <si>
+    <t>Đỗ Thảo</t>
+  </si>
+  <si>
+    <t>HD014221</t>
+  </si>
+  <si>
+    <t>80a bến vân đồn p9</t>
+  </si>
+  <si>
+    <t>Sokhavy Room 205</t>
+  </si>
+  <si>
+    <t>HD013992</t>
+  </si>
+  <si>
+    <t>A25 luxury hotel 277B Le Thanh Ton, Ben Thanh ward</t>
+  </si>
+  <si>
+    <t>Thanh Vy Le</t>
+  </si>
+  <si>
+    <t>HD014227</t>
+  </si>
+  <si>
+    <t>42/10 Tôn Thất Thiệp, phường Bến Nghé</t>
+  </si>
+  <si>
+    <t>TRÚC ST034</t>
+  </si>
+  <si>
+    <t>HD014057</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>Đặng Phạm Hương Giang</t>
+  </si>
+  <si>
+    <t>HD014112</t>
+  </si>
+  <si>
+    <t>128/18 lê đức thọ, phường an nhơn</t>
+  </si>
+  <si>
+    <t>Ngan Huyen</t>
+  </si>
+  <si>
+    <t>HD014211</t>
+  </si>
+  <si>
+    <t>F5/29D vĩnh lộc A</t>
+  </si>
+  <si>
+    <t>HD014092</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>Thùy Dung</t>
+  </si>
+  <si>
+    <t>HD014274</t>
+  </si>
+  <si>
+    <t>Chung cư Hà Đô iris3, đường 3/2, phường 12</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>Ngọc Huyền</t>
+  </si>
+  <si>
+    <t>HD013956</t>
+  </si>
+  <si>
+    <t>vinhome grand park - khu rain bow - sảnh s1.06 nguyễn xiển, p long bình</t>
+  </si>
+  <si>
+    <t>Ín Nile</t>
+  </si>
+  <si>
+    <t>HD014086</t>
+  </si>
+  <si>
+    <t>429/1 nguyễn kiệm p9</t>
+  </si>
+  <si>
+    <t>Nguyễn Uyên</t>
+  </si>
+  <si>
+    <t>HD014061</t>
+  </si>
+  <si>
+    <t>525/44 tô hiến thành p diên hồng</t>
+  </si>
+  <si>
+    <t>Hạ Mi</t>
+  </si>
+  <si>
+    <t>HD014049</t>
+  </si>
+  <si>
+    <t>Sunrise Riverside block C Phước Kiển</t>
+  </si>
+  <si>
+    <t>Thu Thuỷ</t>
+  </si>
+  <si>
+    <t>HD014059</t>
+  </si>
+  <si>
+    <t>TOM AG</t>
+  </si>
+  <si>
+    <t>12 HỒ VĂN HUÊ PHƯỜNG 9</t>
+  </si>
+  <si>
+    <t>CHEATA</t>
+  </si>
+  <si>
+    <t>CHÀNH XE PHY PHY</t>
+  </si>
+  <si>
+    <t>NABY 22</t>
+  </si>
+  <si>
+    <t>90/35 Trần Văn Ơn, phường Tân Sơn Nhì</t>
+  </si>
+  <si>
+    <t>NGAY 23-4</t>
+  </si>
+  <si>
+    <t>Ái</t>
+  </si>
+  <si>
+    <t>HD014697</t>
+  </si>
+  <si>
+    <t>265 lý tự trọng</t>
+  </si>
+  <si>
+    <t>23-04-2026</t>
+  </si>
+  <si>
+    <t>AT 23-04</t>
+  </si>
+  <si>
+    <t>HD014739</t>
+  </si>
+  <si>
+    <t>HD014714</t>
+  </si>
+  <si>
+    <t>Xuân Anh</t>
+  </si>
+  <si>
+    <t>HD014688</t>
+  </si>
+  <si>
+    <t>18/23 đường 266 Bùi Minh Trực P6</t>
+  </si>
+  <si>
+    <t>Trúc Phương</t>
+  </si>
+  <si>
+    <t>HD014191</t>
+  </si>
+  <si>
+    <t>Pidor 012736103</t>
+  </si>
+  <si>
+    <t>HD013727</t>
+  </si>
+  <si>
+    <t>NHÀ XE KHẢI NAM</t>
+  </si>
+  <si>
+    <t>W3235</t>
+  </si>
+  <si>
+    <t>HD014695</t>
+  </si>
+  <si>
+    <t>688/23/1C hương lộ 2, phường bình trị đông A</t>
+  </si>
+  <si>
+    <t>HD014415</t>
+  </si>
+  <si>
+    <t>Thanh Trần</t>
+  </si>
+  <si>
+    <t>HD014525</t>
+  </si>
+  <si>
+    <t>23 Đ. Phú Thuận, Phú Thuận , hcm Sunshine Sky City sảnh A1</t>
+  </si>
+  <si>
+    <t>HD014666</t>
+  </si>
+  <si>
+    <t>HD000100</t>
+  </si>
+  <si>
+    <t>Như Hảo</t>
+  </si>
+  <si>
+    <t>HD014400</t>
+  </si>
+  <si>
+    <t>15 dương 26 linh đông</t>
+  </si>
+  <si>
+    <t>Linh Phạm</t>
+  </si>
+  <si>
+    <t>HD014734</t>
+  </si>
+  <si>
+    <t>304/66/3E bùi đình tuý, p12</t>
+  </si>
+  <si>
+    <t>HD014529</t>
+  </si>
+  <si>
+    <t>HD014448</t>
+  </si>
+  <si>
+    <t>Tên Nhi fb Kim Khoa</t>
+  </si>
+  <si>
+    <t>HD014404</t>
+  </si>
+  <si>
+    <t>Phẩm Huỳnh</t>
+  </si>
+  <si>
+    <t>HD014565</t>
+  </si>
+  <si>
+    <t>Ngân</t>
+  </si>
+  <si>
+    <t>HD014686</t>
+  </si>
+  <si>
+    <t>Trang Lâm</t>
+  </si>
+  <si>
+    <t>HD014526</t>
+  </si>
+  <si>
+    <t>HD014094</t>
+  </si>
+  <si>
+    <t>HD014694</t>
+  </si>
+  <si>
+    <t>Thu Hà</t>
+  </si>
+  <si>
+    <t>HD014340</t>
+  </si>
+  <si>
+    <t>61/8 đường 23 hiệp bình Chánh</t>
+  </si>
+  <si>
+    <t>Tran Huyen Thuong</t>
+  </si>
+  <si>
+    <t>HD014171</t>
+  </si>
+  <si>
+    <t>422 đào trí shunshine diamond</t>
+  </si>
+  <si>
+    <t>HD014399</t>
+  </si>
+  <si>
+    <t>36/18 dương đức thiền tây thạnh</t>
+  </si>
+  <si>
+    <t>HD014661</t>
+  </si>
+  <si>
+    <t>86/36/3 PHỔ QUANG, PHƯỜNG TÂN SƠN HOÀ</t>
+  </si>
+  <si>
+    <t>chip chip</t>
+  </si>
+  <si>
+    <t>HD014665</t>
+  </si>
+  <si>
+    <t>Hoài An ft Ann Nguyen</t>
+  </si>
+  <si>
+    <t>HD014716</t>
+  </si>
+  <si>
+    <t>Mỹ Hạnh</t>
+  </si>
+  <si>
+    <t>HD014717</t>
+  </si>
+  <si>
+    <t>HD014669</t>
+  </si>
+  <si>
+    <t>Saigon Royal Res cences,Nguyễn Trường Tộ, phường 13</t>
+  </si>
+  <si>
+    <t>Ngọc fb Nga Nguyenn</t>
+  </si>
+  <si>
+    <t>434/20/14 Phạm Văn Chiêu Phường 9</t>
+  </si>
+  <si>
+    <t>Châu Trần</t>
+  </si>
+  <si>
+    <t>HD014449</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>HD014600</t>
+  </si>
+  <si>
+    <t>HD014497</t>
+  </si>
+  <si>
+    <t>Phương Linh fb Lê Hoàng Sang</t>
+  </si>
+  <si>
+    <t>HD014346</t>
+  </si>
+  <si>
+    <t>Trần Phượng Liên</t>
+  </si>
+  <si>
+    <t>HD014498</t>
+  </si>
+  <si>
+    <t>Kim Anh Phạm Nguyễn</t>
+  </si>
+  <si>
+    <t>240/38/4 Tô ngọc vân, phường Thạnh Xuân</t>
+  </si>
+  <si>
+    <t>Ngọc Vinh</t>
+  </si>
+  <si>
+    <t>HD014488</t>
+  </si>
+  <si>
+    <t>17-19 Trường Sơn P4</t>
+  </si>
+  <si>
+    <t>Huong, A20.08</t>
+  </si>
+  <si>
+    <t>HD014420</t>
+  </si>
+  <si>
+    <t>CC Tân Phước lỗ a 153 Lý Thường Kiệt, Phường 7</t>
+  </si>
+  <si>
+    <t>NG MY</t>
+  </si>
+  <si>
+    <t>HD014515</t>
+  </si>
+  <si>
+    <t>5 đương số 8 bình thuận</t>
+  </si>
+  <si>
+    <t>Van Anh</t>
+  </si>
+  <si>
+    <t>HD014468</t>
+  </si>
+  <si>
+    <t>HD014726</t>
+  </si>
+  <si>
+    <t>Vy - hàng của hồng</t>
+  </si>
+  <si>
+    <t>HD014730</t>
+  </si>
+  <si>
+    <t>Carol Phuong Trinh</t>
+  </si>
+  <si>
+    <t>HD014685</t>
+  </si>
+  <si>
+    <t>Người nhận chuột</t>
+  </si>
+  <si>
+    <t>Hoàng An</t>
+  </si>
+  <si>
+    <t>HD014684</t>
+  </si>
+  <si>
+    <t>Cuc Nguyen</t>
+  </si>
+  <si>
+    <t>HD014696</t>
+  </si>
+  <si>
+    <t>BN8823</t>
+  </si>
+  <si>
+    <t>HD014668</t>
+  </si>
+  <si>
+    <t>Thị Bi</t>
+  </si>
+  <si>
+    <t>HD014615</t>
+  </si>
+  <si>
+    <t>Chung cư Citiesto, cát lái</t>
+  </si>
+  <si>
+    <t>Charli (inst char importshop )-BN2441</t>
+  </si>
+  <si>
+    <t>207/9 nguyễn văn khôi p8</t>
+  </si>
+  <si>
+    <t>448/65/2 Phan Huy Ích P.12</t>
+  </si>
+  <si>
+    <t>HD014524</t>
+  </si>
+  <si>
+    <t>47/3 trần bình trọng</t>
+  </si>
+  <si>
+    <t>Block b, 102 đặng văn bi, bình thọ</t>
+  </si>
+  <si>
+    <t>Landmark Plus, 208 Nguyễn Hữu Cảnh, phường 22</t>
+  </si>
+  <si>
+    <t>29/7 Yên Thế, Phường 2</t>
+  </si>
+  <si>
+    <t>Hong Nho+Nguyễn Thị Diễm Chi</t>
+  </si>
+  <si>
+    <t>HD014374</t>
+  </si>
+  <si>
+    <t>482/10/26 nơ trang Long, p13</t>
+  </si>
+  <si>
+    <t>Xiabao</t>
+  </si>
+  <si>
+    <t>375 Tân thới hiệp 21, Tổ 3</t>
+  </si>
+  <si>
+    <t>Toà S5, chung cư the Sun Avenue 28 Mai Chí Thọ, P.Bình Trưng</t>
+  </si>
+  <si>
+    <t>amy doan</t>
+  </si>
+  <si>
+    <t>HD014381</t>
+  </si>
+  <si>
+    <t>8y Lạc Long Quân, P. Hòa Bình</t>
+  </si>
+  <si>
+    <t>Hoàng Thanh Hiền</t>
+  </si>
+  <si>
+    <t>HD014608</t>
+  </si>
+  <si>
+    <t>Huyền Trinh</t>
+  </si>
+  <si>
+    <t>69 phố tiểu nam, phường tân phú</t>
+  </si>
+  <si>
+    <t>fb Thuyền Quyên</t>
+  </si>
+  <si>
+    <t>275A phạm ngũ lão phường phạm ngũ lão</t>
+  </si>
+  <si>
+    <t>Nhận hàng giúp chị phương (ở Úc) fb Phương My</t>
+  </si>
+  <si>
+    <t>Chung cư Tecco, block C, đường Nguyễn Cửu Phủ, phường Tân Tạo</t>
+  </si>
+  <si>
+    <t>182 phú thọ hoa phường phú thọ hoa</t>
+  </si>
+  <si>
+    <t>84 phạm Hồng thái phường bến thành</t>
+  </si>
+  <si>
+    <t>1806/45/20/10 huỳnh tấn phát</t>
+  </si>
+  <si>
+    <t>22-24 Thi Sách, Bến Nghế</t>
+  </si>
+  <si>
+    <t>số 3 hoà bình phường bình thới</t>
+  </si>
+  <si>
+    <t>HD014594</t>
+  </si>
+  <si>
+    <t>2/1a quốc lộ 1a, tân chánh hiệp</t>
+  </si>
+  <si>
+    <t>HD014672</t>
+  </si>
+  <si>
+    <t>Thu Tài Trần - Phù Thỉ</t>
+  </si>
+  <si>
+    <t>71/16 thới an 16</t>
+  </si>
+  <si>
+    <t>156/3 Nguyễn Văn Linh phường Tân Thuận Tây</t>
+  </si>
+  <si>
+    <t>HD014543</t>
+  </si>
+  <si>
+    <t>Quế Anh Đỗ</t>
+  </si>
+  <si>
+    <t>HD014655</t>
+  </si>
+  <si>
+    <t>chung cư de la sol</t>
+  </si>
+  <si>
+    <t>Bs16a The oasis Vinhomes grand park ( Phước Thiện Long Bình)</t>
+  </si>
+  <si>
+    <t>Anie Nguyen</t>
+  </si>
+  <si>
+    <t>HD014598</t>
+  </si>
+  <si>
+    <t>C3B/124 ấp 3B Vĩnh Lộc B, hẻm Tiến Long chạy vào quẹo hẻm 2 tay phải, xã Vĩnh Lộc B</t>
   </si>
 </sst>
 </file>
@@ -23256,7 +24098,7 @@
         <v>30</v>
       </c>
       <c r="I3" s="5">
-        <f t="shared" ref="I3:I33" si="0">G3-H3</f>
+        <f t="shared" ref="I3:I34" si="0">G3-H3</f>
         <v>-30</v>
       </c>
       <c r="J3" s="5" t="s">
@@ -24384,7 +25226,7 @@
         <v>25</v>
       </c>
       <c r="I34" s="3">
-        <f t="shared" ref="I34:I59" si="1">G34-H34</f>
+        <f t="shared" si="0"/>
         <v>1975</v>
       </c>
       <c r="J34" s="3" t="s">
@@ -24423,7 +25265,7 @@
         <v>25</v>
       </c>
       <c r="I35" s="7">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="I35:I66" si="1">G35-H35</f>
         <v>530</v>
       </c>
       <c r="J35" s="7" t="s">
@@ -25534,6 +26376,2056 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
+  <dimension ref="A1:P56"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="2" width="9.140625" customWidth="1"/>
+    <col min="3" max="3" width="36.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="78.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.28515625" customWidth="1"/>
+    <col min="7" max="11" width="9.140625" customWidth="1"/>
+    <col min="12" max="12" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2127</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>2128</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>2129</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>2130</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="G3" s="3">
+        <v>470</v>
+      </c>
+      <c r="H3" s="3">
+        <v>20</v>
+      </c>
+      <c r="I3" s="3">
+        <f t="shared" ref="I3:I34" si="0">G3-H3</f>
+        <v>450</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>2131</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>1840</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>2132</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>1842</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>2133</v>
+      </c>
+      <c r="G4" s="3">
+        <v>1490</v>
+      </c>
+      <c r="H4" s="3">
+        <v>30</v>
+      </c>
+      <c r="I4" s="3">
+        <f t="shared" si="0"/>
+        <v>1460</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>2131</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>2134</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>2135</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>2136</v>
+      </c>
+      <c r="F5" s="10" t="s">
+        <v>2137</v>
+      </c>
+      <c r="G5" s="9">
+        <v>0</v>
+      </c>
+      <c r="H5" s="9">
+        <v>25</v>
+      </c>
+      <c r="I5" s="9">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J5" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="K5" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L5" s="9" t="s">
+        <v>2131</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>2138</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>2139</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>2140</v>
+      </c>
+      <c r="F6" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="G6" s="9">
+        <v>470</v>
+      </c>
+      <c r="H6" s="9">
+        <v>20</v>
+      </c>
+      <c r="I6" s="9">
+        <f t="shared" si="0"/>
+        <v>450</v>
+      </c>
+      <c r="J6" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="K6" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L6" s="9" t="s">
+        <v>2131</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>2141</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>2142</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>2143</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>2144</v>
+      </c>
+      <c r="G7" s="5">
+        <v>0</v>
+      </c>
+      <c r="H7" s="5">
+        <v>30</v>
+      </c>
+      <c r="I7" s="5">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J7" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="K7" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L7" s="5" t="s">
+        <v>2131</v>
+      </c>
+      <c r="M7" s="5" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>2145</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>2146</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>2147</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>2144</v>
+      </c>
+      <c r="G8" s="5">
+        <v>480</v>
+      </c>
+      <c r="H8" s="5">
+        <v>30</v>
+      </c>
+      <c r="I8" s="5">
+        <f t="shared" si="0"/>
+        <v>450</v>
+      </c>
+      <c r="J8" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="K8" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L8" s="5" t="s">
+        <v>2131</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>2148</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>2149</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>2150</v>
+      </c>
+      <c r="F9" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="G9" s="9">
+        <v>865</v>
+      </c>
+      <c r="H9" s="9">
+        <v>25</v>
+      </c>
+      <c r="I9" s="9">
+        <f t="shared" si="0"/>
+        <v>840</v>
+      </c>
+      <c r="J9" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="K9" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L9" s="9" t="s">
+        <v>2131</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>2151</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>2152</v>
+      </c>
+      <c r="E10" s="9" t="s">
+        <v>971</v>
+      </c>
+      <c r="F10" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="G10" s="9">
+        <v>0</v>
+      </c>
+      <c r="H10" s="9">
+        <v>25</v>
+      </c>
+      <c r="I10" s="9">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J10" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="K10" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L10" s="9" t="s">
+        <v>2131</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>2153</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>2154</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>2155</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G11" s="7">
+        <v>0</v>
+      </c>
+      <c r="H11" s="7">
+        <v>30</v>
+      </c>
+      <c r="I11" s="7">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J11" s="7" t="s">
+        <v>2156</v>
+      </c>
+      <c r="K11" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L11" s="7" t="s">
+        <v>2131</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>2157</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>2158</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>2159</v>
+      </c>
+      <c r="F12" s="10" t="s">
+        <v>2137</v>
+      </c>
+      <c r="G12" s="9">
+        <v>475</v>
+      </c>
+      <c r="H12" s="9">
+        <v>25</v>
+      </c>
+      <c r="I12" s="9">
+        <f t="shared" si="0"/>
+        <v>450</v>
+      </c>
+      <c r="J12" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="K12" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L12" s="9" t="s">
+        <v>2131</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>2160</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>2161</v>
+      </c>
+      <c r="E13" s="9" t="s">
+        <v>971</v>
+      </c>
+      <c r="F13" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="G13" s="9">
+        <v>0</v>
+      </c>
+      <c r="H13" s="9">
+        <v>25</v>
+      </c>
+      <c r="I13" s="9">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J13" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="K13" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L13" s="9" t="s">
+        <v>2131</v>
+      </c>
+      <c r="M13" s="9" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>1452</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>2162</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>1454</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="G14" s="3">
+        <v>2020</v>
+      </c>
+      <c r="H14" s="3">
+        <v>30</v>
+      </c>
+      <c r="I14" s="3">
+        <f t="shared" si="0"/>
+        <v>1990</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>2131</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>2163</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>2164</v>
+      </c>
+      <c r="E15" s="9" t="s">
+        <v>2165</v>
+      </c>
+      <c r="F15" s="10" t="s">
+        <v>2137</v>
+      </c>
+      <c r="G15" s="9">
+        <v>405</v>
+      </c>
+      <c r="H15" s="9">
+        <v>25</v>
+      </c>
+      <c r="I15" s="9">
+        <f t="shared" si="0"/>
+        <v>380</v>
+      </c>
+      <c r="J15" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="K15" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L15" s="9" t="s">
+        <v>2131</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>2166</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>2167</v>
+      </c>
+      <c r="E16" s="9" t="s">
+        <v>2168</v>
+      </c>
+      <c r="F16" s="10" t="s">
+        <v>2137</v>
+      </c>
+      <c r="G16" s="9">
+        <v>685</v>
+      </c>
+      <c r="H16" s="9">
+        <v>25</v>
+      </c>
+      <c r="I16" s="9">
+        <f t="shared" si="0"/>
+        <v>660</v>
+      </c>
+      <c r="J16" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="K16" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L16" s="9" t="s">
+        <v>2131</v>
+      </c>
+    </row>
+    <row r="17" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>2082</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>2169</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>2084</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="G17" s="3">
+        <v>20</v>
+      </c>
+      <c r="H17" s="3">
+        <v>20</v>
+      </c>
+      <c r="I17" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L17" s="3" t="s">
+        <v>2131</v>
+      </c>
+      <c r="M17" s="3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="18" spans="2:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>2170</v>
+      </c>
+      <c r="D18" s="9" t="s">
+        <v>2171</v>
+      </c>
+      <c r="E18" s="9" t="s">
+        <v>2172</v>
+      </c>
+      <c r="F18" s="10" t="s">
+        <v>2137</v>
+      </c>
+      <c r="G18" s="9">
+        <v>795</v>
+      </c>
+      <c r="H18" s="9">
+        <v>25</v>
+      </c>
+      <c r="I18" s="9">
+        <f t="shared" si="0"/>
+        <v>770</v>
+      </c>
+      <c r="J18" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="K18" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L18" s="9" t="s">
+        <v>2131</v>
+      </c>
+    </row>
+    <row r="19" spans="2:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>2173</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>2174</v>
+      </c>
+      <c r="E19" s="9" t="s">
+        <v>2175</v>
+      </c>
+      <c r="F19" s="10">
+        <v>1</v>
+      </c>
+      <c r="G19" s="9">
+        <v>515</v>
+      </c>
+      <c r="H19" s="9">
+        <v>25</v>
+      </c>
+      <c r="I19" s="9">
+        <f t="shared" si="0"/>
+        <v>490</v>
+      </c>
+      <c r="J19" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="K19" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L19" s="9" t="s">
+        <v>2131</v>
+      </c>
+    </row>
+    <row r="20" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>2176</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>2177</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>2178</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="G20" s="3">
+        <v>860</v>
+      </c>
+      <c r="H20" s="3">
+        <v>20</v>
+      </c>
+      <c r="I20" s="3">
+        <f t="shared" si="0"/>
+        <v>840</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L20" s="3" t="s">
+        <v>2131</v>
+      </c>
+    </row>
+    <row r="21" spans="2:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>1928</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>2179</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>1930</v>
+      </c>
+      <c r="F21" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="G21" s="7">
+        <v>0</v>
+      </c>
+      <c r="H21" s="7">
+        <v>25</v>
+      </c>
+      <c r="I21" s="7">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J21" s="7" t="s">
+        <v>2156</v>
+      </c>
+      <c r="K21" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L21" s="7" t="s">
+        <v>2131</v>
+      </c>
+      <c r="M21" s="7" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="22" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>1573</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>2180</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>1575</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="G22" s="3">
+        <v>475</v>
+      </c>
+      <c r="H22" s="3">
+        <v>25</v>
+      </c>
+      <c r="I22" s="3">
+        <f t="shared" si="0"/>
+        <v>450</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L22" s="3" t="s">
+        <v>2131</v>
+      </c>
+    </row>
+    <row r="23" spans="2:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C23" s="9" t="s">
+        <v>2181</v>
+      </c>
+      <c r="D23" s="9" t="s">
+        <v>2182</v>
+      </c>
+      <c r="E23" s="9" t="s">
+        <v>2061</v>
+      </c>
+      <c r="F23" s="10" t="s">
+        <v>2183</v>
+      </c>
+      <c r="G23" s="9">
+        <v>0</v>
+      </c>
+      <c r="H23" s="9">
+        <v>25</v>
+      </c>
+      <c r="I23" s="9">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J23" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="K23" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L23" s="9" t="s">
+        <v>2131</v>
+      </c>
+    </row>
+    <row r="24" spans="2:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>2184</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>2185</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>2186</v>
+      </c>
+      <c r="F24" s="8" t="s">
+        <v>2187</v>
+      </c>
+      <c r="G24" s="7">
+        <v>1380</v>
+      </c>
+      <c r="H24" s="7">
+        <v>30</v>
+      </c>
+      <c r="I24" s="7">
+        <f t="shared" si="0"/>
+        <v>1350</v>
+      </c>
+      <c r="J24" s="7" t="s">
+        <v>2156</v>
+      </c>
+      <c r="K24" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L24" s="7" t="s">
+        <v>2131</v>
+      </c>
+    </row>
+    <row r="25" spans="2:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>2040</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>2188</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>2042</v>
+      </c>
+      <c r="F25" s="8" t="s">
+        <v>2189</v>
+      </c>
+      <c r="G25" s="7">
+        <v>30</v>
+      </c>
+      <c r="H25" s="7">
+        <v>30</v>
+      </c>
+      <c r="I25" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J25" s="7" t="s">
+        <v>2156</v>
+      </c>
+      <c r="K25" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L25" s="7" t="s">
+        <v>2131</v>
+      </c>
+      <c r="M25" s="7" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="26" spans="2:13" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>2190</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>2191</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>2192</v>
+      </c>
+      <c r="F26" s="6" t="s">
+        <v>2144</v>
+      </c>
+      <c r="G26" s="5">
+        <v>520</v>
+      </c>
+      <c r="H26" s="5">
+        <v>30</v>
+      </c>
+      <c r="I26" s="5">
+        <f t="shared" si="0"/>
+        <v>490</v>
+      </c>
+      <c r="J26" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="K26" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L26" s="5" t="s">
+        <v>2131</v>
+      </c>
+    </row>
+    <row r="27" spans="2:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>2193</v>
+      </c>
+      <c r="E27" s="7" t="s">
+        <v>2194</v>
+      </c>
+      <c r="F27" s="8" t="s">
+        <v>2187</v>
+      </c>
+      <c r="G27" s="7">
+        <v>1220</v>
+      </c>
+      <c r="H27" s="7">
+        <v>30</v>
+      </c>
+      <c r="I27" s="7">
+        <f t="shared" si="0"/>
+        <v>1190</v>
+      </c>
+      <c r="J27" s="7" t="s">
+        <v>2156</v>
+      </c>
+      <c r="K27" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L27" s="7" t="s">
+        <v>2131</v>
+      </c>
+    </row>
+    <row r="28" spans="2:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C28" s="9" t="s">
+        <v>1105</v>
+      </c>
+      <c r="D28" s="9" t="s">
+        <v>2195</v>
+      </c>
+      <c r="E28" s="9" t="s">
+        <v>1107</v>
+      </c>
+      <c r="F28" s="10" t="s">
+        <v>2196</v>
+      </c>
+      <c r="G28" s="9">
+        <v>685</v>
+      </c>
+      <c r="H28" s="9">
+        <v>25</v>
+      </c>
+      <c r="I28" s="9">
+        <f t="shared" si="0"/>
+        <v>660</v>
+      </c>
+      <c r="J28" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="K28" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L28" s="9" t="s">
+        <v>2131</v>
+      </c>
+    </row>
+    <row r="29" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>2197</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>2198</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>2199</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="G29" s="3">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3">
+        <v>30</v>
+      </c>
+      <c r="I29" s="3">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L29" s="3" t="s">
+        <v>2131</v>
+      </c>
+    </row>
+    <row r="30" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>2200</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>2201</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>2202</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="G30" s="3">
+        <v>890</v>
+      </c>
+      <c r="H30" s="3">
+        <v>30</v>
+      </c>
+      <c r="I30" s="3">
+        <f t="shared" si="0"/>
+        <v>860</v>
+      </c>
+      <c r="J30" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K30" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L30" s="3" t="s">
+        <v>2131</v>
+      </c>
+    </row>
+    <row r="31" spans="2:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B31" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C31" s="9" t="s">
+        <v>2160</v>
+      </c>
+      <c r="D31" s="9" t="s">
+        <v>2203</v>
+      </c>
+      <c r="E31" s="9" t="s">
+        <v>971</v>
+      </c>
+      <c r="F31" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="G31" s="9">
+        <v>0</v>
+      </c>
+      <c r="H31" s="9">
+        <v>0</v>
+      </c>
+      <c r="I31" s="9">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J31" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="K31" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L31" s="9" t="s">
+        <v>2131</v>
+      </c>
+      <c r="M31" s="9" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="32" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B32" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>2204</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>2205</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>2206</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="G32" s="3">
+        <v>2290</v>
+      </c>
+      <c r="H32" s="3">
+        <v>35</v>
+      </c>
+      <c r="I32" s="3">
+        <f t="shared" si="0"/>
+        <v>2255</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K32" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L32" s="3" t="s">
+        <v>2131</v>
+      </c>
+      <c r="M32" s="3" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="33" spans="2:12" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B33" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>2207</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>2208</v>
+      </c>
+      <c r="E33" s="5" t="s">
+        <v>2209</v>
+      </c>
+      <c r="F33" s="6" t="s">
+        <v>2144</v>
+      </c>
+      <c r="G33" s="5">
+        <v>890</v>
+      </c>
+      <c r="H33" s="5">
+        <v>30</v>
+      </c>
+      <c r="I33" s="5">
+        <f t="shared" si="0"/>
+        <v>860</v>
+      </c>
+      <c r="J33" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="K33" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L33" s="5" t="s">
+        <v>2131</v>
+      </c>
+    </row>
+    <row r="34" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B34" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>2210</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>2211</v>
+      </c>
+      <c r="F34" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="G34" s="3">
+        <v>0</v>
+      </c>
+      <c r="H34" s="3">
+        <v>30</v>
+      </c>
+      <c r="I34" s="3">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J34" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K34" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L34" s="3" t="s">
+        <v>2131</v>
+      </c>
+    </row>
+    <row r="35" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B35" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>2212</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>2213</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>2214</v>
+      </c>
+      <c r="F35" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="G35" s="3">
+        <v>0</v>
+      </c>
+      <c r="H35" s="3">
+        <v>25</v>
+      </c>
+      <c r="I35" s="3">
+        <f t="shared" ref="I35:I66" si="1">G35-H35</f>
+        <v>-25</v>
+      </c>
+      <c r="J35" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K35" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L35" s="3" t="s">
+        <v>2131</v>
+      </c>
+    </row>
+    <row r="36" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B36" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>2215</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>2216</v>
+      </c>
+      <c r="F36" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="G36" s="3">
+        <v>1140</v>
+      </c>
+      <c r="H36" s="3">
+        <v>20</v>
+      </c>
+      <c r="I36" s="3">
+        <f t="shared" si="1"/>
+        <v>1120</v>
+      </c>
+      <c r="J36" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K36" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L36" s="3" t="s">
+        <v>2131</v>
+      </c>
+    </row>
+    <row r="37" spans="2:12" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B37" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C37" s="7" t="s">
+        <v>940</v>
+      </c>
+      <c r="D37" s="7" t="s">
+        <v>2217</v>
+      </c>
+      <c r="E37" s="7" t="s">
+        <v>2218</v>
+      </c>
+      <c r="F37" s="8" t="s">
+        <v>2183</v>
+      </c>
+      <c r="G37" s="7">
+        <v>595</v>
+      </c>
+      <c r="H37" s="7">
+        <v>25</v>
+      </c>
+      <c r="I37" s="7">
+        <f t="shared" si="1"/>
+        <v>570</v>
+      </c>
+      <c r="J37" s="7" t="s">
+        <v>2156</v>
+      </c>
+      <c r="K37" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L37" s="7" t="s">
+        <v>2131</v>
+      </c>
+    </row>
+    <row r="38" spans="2:12" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B38" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C38" s="9" t="s">
+        <v>2219</v>
+      </c>
+      <c r="D38" s="9" t="s">
+        <v>2220</v>
+      </c>
+      <c r="E38" s="9" t="s">
+        <v>2221</v>
+      </c>
+      <c r="F38" s="10" t="s">
+        <v>2196</v>
+      </c>
+      <c r="G38" s="9">
+        <v>1145</v>
+      </c>
+      <c r="H38" s="9">
+        <v>25</v>
+      </c>
+      <c r="I38" s="9">
+        <f t="shared" si="1"/>
+        <v>1120</v>
+      </c>
+      <c r="J38" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="K38" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L38" s="9" t="s">
+        <v>2131</v>
+      </c>
+    </row>
+    <row r="39" spans="2:12" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B39" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C39" s="9" t="s">
+        <v>2222</v>
+      </c>
+      <c r="D39" s="9" t="s">
+        <v>2223</v>
+      </c>
+      <c r="E39" s="9" t="s">
+        <v>2224</v>
+      </c>
+      <c r="F39" s="10" t="s">
+        <v>2137</v>
+      </c>
+      <c r="G39" s="9">
+        <v>475</v>
+      </c>
+      <c r="H39" s="9">
+        <v>25</v>
+      </c>
+      <c r="I39" s="9">
+        <f t="shared" si="1"/>
+        <v>450</v>
+      </c>
+      <c r="J39" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="K39" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L39" s="9" t="s">
+        <v>2131</v>
+      </c>
+    </row>
+    <row r="40" spans="2:12" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B40" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C40" s="9" t="s">
+        <v>2225</v>
+      </c>
+      <c r="D40" s="9" t="s">
+        <v>2226</v>
+      </c>
+      <c r="E40" s="9" t="s">
+        <v>2227</v>
+      </c>
+      <c r="F40" s="10" t="s">
+        <v>2137</v>
+      </c>
+      <c r="G40" s="9">
+        <v>595</v>
+      </c>
+      <c r="H40" s="9">
+        <v>25</v>
+      </c>
+      <c r="I40" s="9">
+        <f t="shared" si="1"/>
+        <v>570</v>
+      </c>
+      <c r="J40" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="K40" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L40" s="9" t="s">
+        <v>2131</v>
+      </c>
+    </row>
+    <row r="41" spans="2:12" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B41" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C41" s="7" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D41" s="7" t="s">
+        <v>2229</v>
+      </c>
+      <c r="E41" s="7" t="s">
+        <v>1506</v>
+      </c>
+      <c r="F41" s="8" t="s">
+        <v>2230</v>
+      </c>
+      <c r="G41" s="7">
+        <v>405</v>
+      </c>
+      <c r="H41" s="7">
+        <v>25</v>
+      </c>
+      <c r="I41" s="7">
+        <f t="shared" si="1"/>
+        <v>380</v>
+      </c>
+      <c r="J41" s="7" t="s">
+        <v>2156</v>
+      </c>
+      <c r="K41" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L41" s="7" t="s">
+        <v>2131</v>
+      </c>
+    </row>
+    <row r="42" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B42" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>2231</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>2232</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>2233</v>
+      </c>
+      <c r="F42" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="G42" s="3">
+        <v>885</v>
+      </c>
+      <c r="H42" s="3">
+        <v>25</v>
+      </c>
+      <c r="I42" s="3">
+        <f t="shared" si="1"/>
+        <v>860</v>
+      </c>
+      <c r="J42" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K42" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L42" s="3" t="s">
+        <v>2131</v>
+      </c>
+    </row>
+    <row r="43" spans="2:12" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B43" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C43" s="7" t="s">
+        <v>2234</v>
+      </c>
+      <c r="D43" s="7" t="s">
+        <v>2235</v>
+      </c>
+      <c r="E43" s="7" t="s">
+        <v>2236</v>
+      </c>
+      <c r="F43" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="G43" s="7">
+        <v>485</v>
+      </c>
+      <c r="H43" s="7">
+        <v>35</v>
+      </c>
+      <c r="I43" s="7">
+        <f t="shared" si="1"/>
+        <v>450</v>
+      </c>
+      <c r="J43" s="7" t="s">
+        <v>2156</v>
+      </c>
+      <c r="K43" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L43" s="7" t="s">
+        <v>2131</v>
+      </c>
+    </row>
+    <row r="44" spans="2:12" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B44" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C44" s="7" t="s">
+        <v>219</v>
+      </c>
+      <c r="D44" s="7" t="s">
+        <v>2237</v>
+      </c>
+      <c r="E44" s="7" t="s">
+        <v>221</v>
+      </c>
+      <c r="F44" s="8" t="s">
+        <v>2238</v>
+      </c>
+      <c r="G44" s="7">
+        <v>0</v>
+      </c>
+      <c r="H44" s="7">
+        <v>25</v>
+      </c>
+      <c r="I44" s="7">
+        <f t="shared" si="1"/>
+        <v>-25</v>
+      </c>
+      <c r="J44" s="7" t="s">
+        <v>2156</v>
+      </c>
+      <c r="K44" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L44" s="7" t="s">
+        <v>2131</v>
+      </c>
+    </row>
+    <row r="45" spans="2:12" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B45" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C45" s="9" t="s">
+        <v>2239</v>
+      </c>
+      <c r="D45" s="9" t="s">
+        <v>2240</v>
+      </c>
+      <c r="E45" s="9" t="s">
+        <v>2241</v>
+      </c>
+      <c r="F45" s="10" t="s">
+        <v>2242</v>
+      </c>
+      <c r="G45" s="9">
+        <v>685</v>
+      </c>
+      <c r="H45" s="9">
+        <v>25</v>
+      </c>
+      <c r="I45" s="9">
+        <f t="shared" si="1"/>
+        <v>660</v>
+      </c>
+      <c r="J45" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="K45" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L45" s="9" t="s">
+        <v>2131</v>
+      </c>
+    </row>
+    <row r="46" spans="2:12" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B46" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C46" s="5" t="s">
+        <v>2243</v>
+      </c>
+      <c r="D46" s="5" t="s">
+        <v>2244</v>
+      </c>
+      <c r="E46" s="5" t="s">
+        <v>2245</v>
+      </c>
+      <c r="F46" s="6" t="s">
+        <v>2144</v>
+      </c>
+      <c r="G46" s="5">
+        <v>690</v>
+      </c>
+      <c r="H46" s="5">
+        <v>30</v>
+      </c>
+      <c r="I46" s="5">
+        <f t="shared" si="1"/>
+        <v>660</v>
+      </c>
+      <c r="J46" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="K46" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L46" s="5" t="s">
+        <v>2131</v>
+      </c>
+    </row>
+    <row r="47" spans="2:12" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B47" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C47" s="9" t="s">
+        <v>2246</v>
+      </c>
+      <c r="D47" s="9" t="s">
+        <v>2247</v>
+      </c>
+      <c r="E47" s="9" t="s">
+        <v>2248</v>
+      </c>
+      <c r="F47" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="G47" s="9">
+        <v>1140</v>
+      </c>
+      <c r="H47" s="9">
+        <v>20</v>
+      </c>
+      <c r="I47" s="9">
+        <f t="shared" si="1"/>
+        <v>1120</v>
+      </c>
+      <c r="J47" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="K47" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L47" s="9" t="s">
+        <v>2131</v>
+      </c>
+    </row>
+    <row r="48" spans="2:12" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B48" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C48" s="9" t="s">
+        <v>2249</v>
+      </c>
+      <c r="D48" s="9" t="s">
+        <v>2250</v>
+      </c>
+      <c r="E48" s="9" t="s">
+        <v>2251</v>
+      </c>
+      <c r="F48" s="10" t="s">
+        <v>2242</v>
+      </c>
+      <c r="G48" s="9">
+        <v>1145</v>
+      </c>
+      <c r="H48" s="9">
+        <v>25</v>
+      </c>
+      <c r="I48" s="9">
+        <f t="shared" si="1"/>
+        <v>1120</v>
+      </c>
+      <c r="J48" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="K48" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L48" s="9" t="s">
+        <v>2131</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B49" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C49" s="7" t="s">
+        <v>2252</v>
+      </c>
+      <c r="D49" s="7" t="s">
+        <v>2253</v>
+      </c>
+      <c r="E49" s="7" t="s">
+        <v>2254</v>
+      </c>
+      <c r="F49" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="G49" s="7">
+        <v>745</v>
+      </c>
+      <c r="H49" s="7">
+        <v>35</v>
+      </c>
+      <c r="I49" s="7">
+        <f t="shared" si="1"/>
+        <v>710</v>
+      </c>
+      <c r="J49" s="7" t="s">
+        <v>2156</v>
+      </c>
+      <c r="K49" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L49" s="7" t="s">
+        <v>2131</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B50" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C50" s="7" t="s">
+        <v>2255</v>
+      </c>
+      <c r="D50" s="7" t="s">
+        <v>2256</v>
+      </c>
+      <c r="E50" s="7" t="s">
+        <v>997</v>
+      </c>
+      <c r="F50" s="8" t="s">
+        <v>2187</v>
+      </c>
+      <c r="G50" s="7">
+        <v>900</v>
+      </c>
+      <c r="H50" s="7">
+        <v>30</v>
+      </c>
+      <c r="I50" s="7">
+        <f t="shared" si="1"/>
+        <v>870</v>
+      </c>
+      <c r="J50" s="7" t="s">
+        <v>2156</v>
+      </c>
+      <c r="K50" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L50" s="7" t="s">
+        <v>2131</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="B51" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C51" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="E51" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="F51" s="8" t="s">
+        <v>2230</v>
+      </c>
+      <c r="G51" s="7">
+        <v>0</v>
+      </c>
+      <c r="H51" s="7">
+        <v>30</v>
+      </c>
+      <c r="I51" s="7">
+        <f t="shared" si="1"/>
+        <v>-30</v>
+      </c>
+      <c r="J51" s="7" t="s">
+        <v>2156</v>
+      </c>
+      <c r="K51" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L51" s="7" t="s">
+        <v>2131</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="B52" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C52" s="9" t="s">
+        <v>2257</v>
+      </c>
+      <c r="E52" s="9" t="s">
+        <v>2258</v>
+      </c>
+      <c r="F52" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="G52" s="9">
+        <v>30</v>
+      </c>
+      <c r="H52" s="9">
+        <v>30</v>
+      </c>
+      <c r="I52" s="9">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J52" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="K52" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L52" s="9" t="s">
+        <v>2131</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="E53" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="F53" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="G53" s="3">
+        <v>0</v>
+      </c>
+      <c r="H53" s="3">
+        <v>30</v>
+      </c>
+      <c r="I53" s="3">
+        <f t="shared" si="1"/>
+        <v>-30</v>
+      </c>
+      <c r="J53" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K53" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L53" s="3" t="s">
+        <v>2131</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="B54" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C54" s="7" t="s">
+        <v>2259</v>
+      </c>
+      <c r="E54" s="7" t="s">
+        <v>2260</v>
+      </c>
+      <c r="F54" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="G54" s="7">
+        <v>0</v>
+      </c>
+      <c r="H54" s="7">
+        <v>30</v>
+      </c>
+      <c r="I54" s="7">
+        <f t="shared" si="1"/>
+        <v>-30</v>
+      </c>
+      <c r="J54" s="7" t="s">
+        <v>2156</v>
+      </c>
+      <c r="K54" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L54" s="7" t="s">
+        <v>2131</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>1653</v>
+      </c>
+      <c r="E55" s="3" t="s">
+        <v>1654</v>
+      </c>
+      <c r="F55" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="G55" s="3">
+        <v>0</v>
+      </c>
+      <c r="H55" s="3">
+        <v>30</v>
+      </c>
+      <c r="I55" s="3">
+        <f t="shared" si="1"/>
+        <v>-30</v>
+      </c>
+      <c r="J55" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K55" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L55" s="3" t="s">
+        <v>2131</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>2261</v>
+      </c>
+      <c r="E56" s="3" t="s">
+        <v>2262</v>
+      </c>
+      <c r="F56" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="G56" s="3">
+        <v>23400</v>
+      </c>
+      <c r="H56" s="3">
+        <v>135</v>
+      </c>
+      <c r="I56" s="3">
+        <f t="shared" si="1"/>
+        <v>23265</v>
+      </c>
+      <c r="J56" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K56" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L56" s="3" t="s">
+        <v>2131</v>
+      </c>
+      <c r="M56" s="3" t="s">
+        <v>361</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -26413,6 +29305,2172 @@
       </c>
       <c r="L25" t="s">
         <v>95</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1300-000000000000}">
+  <dimension ref="A1:P60"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="45" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="76.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B1" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2263</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>2264</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>2265</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>2266</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>2137</v>
+      </c>
+      <c r="G3" s="7">
+        <v>1145</v>
+      </c>
+      <c r="H3" s="7">
+        <v>25</v>
+      </c>
+      <c r="I3" s="7">
+        <f t="shared" ref="I3:I33" si="0">G3-H3</f>
+        <v>1120</v>
+      </c>
+      <c r="J3" s="7" t="s">
+        <v>2268</v>
+      </c>
+      <c r="K3" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L3" s="7" t="s">
+        <v>2267</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>1219</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>2399</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>1221</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G4" s="7">
+        <v>0</v>
+      </c>
+      <c r="H4" s="7">
+        <v>30</v>
+      </c>
+      <c r="I4" s="7">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J4" s="7" t="s">
+        <v>2268</v>
+      </c>
+      <c r="K4" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L4" s="7" t="s">
+        <v>2267</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>2382</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>2269</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>2383</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>2187</v>
+      </c>
+      <c r="G5" s="7">
+        <v>470</v>
+      </c>
+      <c r="H5" s="7">
+        <v>30</v>
+      </c>
+      <c r="I5" s="7">
+        <f t="shared" si="0"/>
+        <v>440</v>
+      </c>
+      <c r="J5" s="7" t="s">
+        <v>2268</v>
+      </c>
+      <c r="K5" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L5" s="7" t="s">
+        <v>2267</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>884</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>2270</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>886</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G6" s="7">
+        <v>380</v>
+      </c>
+      <c r="H6" s="7">
+        <v>30</v>
+      </c>
+      <c r="I6" s="7">
+        <f t="shared" si="0"/>
+        <v>350</v>
+      </c>
+      <c r="J6" s="7" t="s">
+        <v>2268</v>
+      </c>
+      <c r="K6" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L6" s="7" t="s">
+        <v>2267</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>2271</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>2272</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>2273</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>2238</v>
+      </c>
+      <c r="G7" s="7">
+        <v>560</v>
+      </c>
+      <c r="H7" s="7">
+        <v>30</v>
+      </c>
+      <c r="I7" s="7">
+        <f t="shared" si="0"/>
+        <v>530</v>
+      </c>
+      <c r="J7" s="7" t="s">
+        <v>2268</v>
+      </c>
+      <c r="K7" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L7" s="7" t="s">
+        <v>2267</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>2274</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>2275</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>2362</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>2133</v>
+      </c>
+      <c r="G8" s="3">
+        <v>690</v>
+      </c>
+      <c r="H8" s="3">
+        <v>30</v>
+      </c>
+      <c r="I8" s="3">
+        <f t="shared" si="0"/>
+        <v>660</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>2267</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>2276</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>2277</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>2278</v>
+      </c>
+      <c r="F9" s="9">
+        <v>5</v>
+      </c>
+      <c r="G9" s="9">
+        <v>0</v>
+      </c>
+      <c r="H9" s="9">
+        <v>25</v>
+      </c>
+      <c r="I9" s="9">
+        <v>-25</v>
+      </c>
+      <c r="J9" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="K9" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L9" s="9" t="s">
+        <v>2267</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>2279</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>2372</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>569</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>2189</v>
+      </c>
+      <c r="G10" s="3">
+        <v>0</v>
+      </c>
+      <c r="H10" s="3">
+        <v>30</v>
+      </c>
+      <c r="I10" s="3">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L10" s="3" t="s">
+        <v>2267</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>2384</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>2280</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>2281</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G11" s="7">
+        <v>0</v>
+      </c>
+      <c r="H11" s="7">
+        <v>30</v>
+      </c>
+      <c r="I11" s="7">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J11" s="7" t="s">
+        <v>2268</v>
+      </c>
+      <c r="K11" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L11" s="7" t="s">
+        <v>2267</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>596</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>2282</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>598</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="G12" s="7">
+        <v>525</v>
+      </c>
+      <c r="H12" s="7">
+        <v>25</v>
+      </c>
+      <c r="I12" s="7">
+        <f t="shared" si="0"/>
+        <v>500</v>
+      </c>
+      <c r="J12" s="7" t="s">
+        <v>2268</v>
+      </c>
+      <c r="K12" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L12" s="7" t="s">
+        <v>2267</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>2283</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>2284</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>2285</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>2187</v>
+      </c>
+      <c r="G13" s="7">
+        <v>690</v>
+      </c>
+      <c r="H13" s="7">
+        <v>30</v>
+      </c>
+      <c r="I13" s="7">
+        <f t="shared" si="0"/>
+        <v>660</v>
+      </c>
+      <c r="J13" s="7" t="s">
+        <v>2268</v>
+      </c>
+      <c r="K13" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L13" s="7" t="s">
+        <v>2267</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>750</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>2286</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>752</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>2230</v>
+      </c>
+      <c r="G14" s="7">
+        <v>475</v>
+      </c>
+      <c r="H14" s="7">
+        <v>25</v>
+      </c>
+      <c r="I14" s="7">
+        <f t="shared" si="0"/>
+        <v>450</v>
+      </c>
+      <c r="J14" s="7" t="s">
+        <v>2268</v>
+      </c>
+      <c r="K14" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L14" s="7" t="s">
+        <v>2267</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>2023</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>2287</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>2387</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="G15" s="7">
+        <v>480</v>
+      </c>
+      <c r="H15" s="7">
+        <v>30</v>
+      </c>
+      <c r="I15" s="7">
+        <f t="shared" si="0"/>
+        <v>450</v>
+      </c>
+      <c r="J15" s="7" t="s">
+        <v>2268</v>
+      </c>
+      <c r="K15" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L15" s="7" t="s">
+        <v>2267</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>2400</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>2401</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>2402</v>
+      </c>
+      <c r="F16" s="8">
+        <v>4</v>
+      </c>
+      <c r="G16" s="7">
+        <v>685</v>
+      </c>
+      <c r="H16" s="7">
+        <v>25</v>
+      </c>
+      <c r="I16" s="7">
+        <f t="shared" si="0"/>
+        <v>660</v>
+      </c>
+      <c r="J16" s="7" t="s">
+        <v>2268</v>
+      </c>
+      <c r="K16" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L16" s="7" t="s">
+        <v>2267</v>
+      </c>
+    </row>
+    <row r="17" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>2288</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>2289</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>2290</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="G17" s="3">
+        <v>480</v>
+      </c>
+      <c r="H17" s="3">
+        <v>30</v>
+      </c>
+      <c r="I17" s="3">
+        <f t="shared" si="0"/>
+        <v>450</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L17" s="3" t="s">
+        <v>2267</v>
+      </c>
+    </row>
+    <row r="18" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>2291</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>2292</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>2293</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="G18" s="3">
+        <v>1140</v>
+      </c>
+      <c r="H18" s="3">
+        <v>20</v>
+      </c>
+      <c r="I18" s="3">
+        <f t="shared" si="0"/>
+        <v>1120</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L18" s="3" t="s">
+        <v>2267</v>
+      </c>
+    </row>
+    <row r="19" spans="2:12" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>1108</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>2294</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>2403</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>2144</v>
+      </c>
+      <c r="G19" s="5">
+        <v>50</v>
+      </c>
+      <c r="H19" s="5">
+        <v>20</v>
+      </c>
+      <c r="I19" s="5">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="J19" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="K19" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L19" s="5" t="s">
+        <v>2267</v>
+      </c>
+    </row>
+    <row r="20" spans="2:12" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>2386</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>2295</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>1796</v>
+      </c>
+      <c r="F20" s="7" t="s">
+        <v>287</v>
+      </c>
+      <c r="G20" s="7">
+        <v>0</v>
+      </c>
+      <c r="H20" s="7">
+        <v>35</v>
+      </c>
+      <c r="I20" s="7">
+        <f t="shared" si="0"/>
+        <v>-35</v>
+      </c>
+      <c r="J20" s="7" t="s">
+        <v>2268</v>
+      </c>
+      <c r="K20" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L20" s="7" t="s">
+        <v>2267</v>
+      </c>
+    </row>
+    <row r="21" spans="2:12" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>2296</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>2297</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>2385</v>
+      </c>
+      <c r="F21" s="7" t="s">
+        <v>2137</v>
+      </c>
+      <c r="G21" s="7">
+        <v>865</v>
+      </c>
+      <c r="H21" s="7">
+        <v>25</v>
+      </c>
+      <c r="I21" s="7">
+        <f t="shared" si="0"/>
+        <v>840</v>
+      </c>
+      <c r="J21" s="7" t="s">
+        <v>2268</v>
+      </c>
+      <c r="K21" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L21" s="7" t="s">
+        <v>2267</v>
+      </c>
+    </row>
+    <row r="22" spans="2:12" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>2298</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>2299</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>2389</v>
+      </c>
+      <c r="F22" s="7" t="s">
+        <v>2137</v>
+      </c>
+      <c r="G22" s="7">
+        <v>1915</v>
+      </c>
+      <c r="H22" s="7">
+        <v>25</v>
+      </c>
+      <c r="I22" s="7">
+        <f t="shared" si="0"/>
+        <v>1890</v>
+      </c>
+      <c r="J22" s="7" t="s">
+        <v>2268</v>
+      </c>
+      <c r="K22" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L22" s="7" t="s">
+        <v>2267</v>
+      </c>
+    </row>
+    <row r="23" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>2300</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>2301</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>2369</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="G23" s="3">
+        <v>0</v>
+      </c>
+      <c r="H23" s="3">
+        <v>20</v>
+      </c>
+      <c r="I23" s="3">
+        <f t="shared" si="0"/>
+        <v>-20</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K23" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L23" s="3" t="s">
+        <v>2267</v>
+      </c>
+    </row>
+    <row r="24" spans="2:12" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>2302</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>2303</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>2390</v>
+      </c>
+      <c r="F24" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="G24" s="7">
+        <v>1355</v>
+      </c>
+      <c r="H24" s="7">
+        <v>35</v>
+      </c>
+      <c r="I24" s="7">
+        <f t="shared" si="0"/>
+        <v>1320</v>
+      </c>
+      <c r="J24" s="7" t="s">
+        <v>2268</v>
+      </c>
+      <c r="K24" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L24" s="7" t="s">
+        <v>2267</v>
+      </c>
+    </row>
+    <row r="25" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>2374</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>2304</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>2375</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>2189</v>
+      </c>
+      <c r="G25" s="3">
+        <v>0</v>
+      </c>
+      <c r="H25" s="3">
+        <v>30</v>
+      </c>
+      <c r="I25" s="3">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J25" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K25" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L25" s="3" t="s">
+        <v>2267</v>
+      </c>
+    </row>
+    <row r="26" spans="2:12" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>2305</v>
+      </c>
+      <c r="E26" s="7" t="s">
+        <v>1189</v>
+      </c>
+      <c r="F26" s="7" t="s">
+        <v>2187</v>
+      </c>
+      <c r="G26" s="7">
+        <v>880</v>
+      </c>
+      <c r="H26" s="7">
+        <v>30</v>
+      </c>
+      <c r="I26" s="7">
+        <f t="shared" si="0"/>
+        <v>850</v>
+      </c>
+      <c r="J26" s="7" t="s">
+        <v>2268</v>
+      </c>
+      <c r="K26" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L26" s="7" t="s">
+        <v>2267</v>
+      </c>
+    </row>
+    <row r="27" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>2306</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>2307</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>2308</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="G27" s="3">
+        <v>890</v>
+      </c>
+      <c r="H27" s="3">
+        <v>30</v>
+      </c>
+      <c r="I27" s="3">
+        <f t="shared" si="0"/>
+        <v>860</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K27" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L27" s="3" t="s">
+        <v>2267</v>
+      </c>
+    </row>
+    <row r="28" spans="2:12" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>2309</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>2310</v>
+      </c>
+      <c r="E28" s="7" t="s">
+        <v>2311</v>
+      </c>
+      <c r="F28" s="7" t="s">
+        <v>2187</v>
+      </c>
+      <c r="G28" s="7">
+        <v>1990</v>
+      </c>
+      <c r="H28" s="7">
+        <v>30</v>
+      </c>
+      <c r="I28" s="7">
+        <f t="shared" si="0"/>
+        <v>1960</v>
+      </c>
+      <c r="J28" s="7" t="s">
+        <v>2268</v>
+      </c>
+      <c r="K28" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L28" s="7" t="s">
+        <v>2267</v>
+      </c>
+    </row>
+    <row r="29" spans="2:12" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>2404</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>2405</v>
+      </c>
+      <c r="E29" s="7" t="s">
+        <v>2406</v>
+      </c>
+      <c r="F29" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="G29" s="7">
+        <v>0</v>
+      </c>
+      <c r="H29" s="7">
+        <v>35</v>
+      </c>
+      <c r="I29" s="7">
+        <f t="shared" si="0"/>
+        <v>-35</v>
+      </c>
+      <c r="J29" s="7" t="s">
+        <v>2268</v>
+      </c>
+      <c r="K29" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L29" s="7" t="s">
+        <v>2267</v>
+      </c>
+    </row>
+    <row r="30" spans="2:12" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C30" s="7" t="s">
+        <v>2377</v>
+      </c>
+      <c r="D30" s="7" t="s">
+        <v>2312</v>
+      </c>
+      <c r="E30" s="7" t="s">
+        <v>2313</v>
+      </c>
+      <c r="F30" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="G30" s="7">
+        <v>1545</v>
+      </c>
+      <c r="H30" s="7">
+        <v>25</v>
+      </c>
+      <c r="I30" s="7">
+        <f t="shared" si="0"/>
+        <v>1520</v>
+      </c>
+      <c r="J30" s="7" t="s">
+        <v>2268</v>
+      </c>
+      <c r="K30" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L30" s="7" t="s">
+        <v>2267</v>
+      </c>
+    </row>
+    <row r="31" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B31" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>2363</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>2314</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>1730</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>2189</v>
+      </c>
+      <c r="G31" s="3">
+        <v>0</v>
+      </c>
+      <c r="H31" s="3">
+        <v>30</v>
+      </c>
+      <c r="I31" s="3">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J31" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K31" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L31" s="3" t="s">
+        <v>2267</v>
+      </c>
+    </row>
+    <row r="32" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B32" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>2360</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>2361</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>2315</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="G32" s="3">
+        <v>1245</v>
+      </c>
+      <c r="H32" s="3">
+        <v>25</v>
+      </c>
+      <c r="I32" s="3">
+        <f t="shared" si="0"/>
+        <v>1220</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K32" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L32" s="3" t="s">
+        <v>2267</v>
+      </c>
+    </row>
+    <row r="33" spans="2:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B33" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>2316</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>2317</v>
+      </c>
+      <c r="E33" s="7" t="s">
+        <v>2397</v>
+      </c>
+      <c r="F33" s="7" t="s">
+        <v>2189</v>
+      </c>
+      <c r="G33" s="7">
+        <v>920</v>
+      </c>
+      <c r="H33" s="7">
+        <v>30</v>
+      </c>
+      <c r="I33" s="7">
+        <f t="shared" si="0"/>
+        <v>890</v>
+      </c>
+      <c r="J33" s="7" t="s">
+        <v>2268</v>
+      </c>
+      <c r="K33" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L33" s="7" t="s">
+        <v>2267</v>
+      </c>
+    </row>
+    <row r="34" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B34" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>2318</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>2319</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>2376</v>
+      </c>
+      <c r="F34" s="4">
+        <v>2</v>
+      </c>
+      <c r="G34" s="3">
+        <v>0</v>
+      </c>
+      <c r="H34" s="3">
+        <v>30</v>
+      </c>
+      <c r="I34" s="3">
+        <f t="shared" ref="I34:I65" si="1">G34-H34</f>
+        <v>-30</v>
+      </c>
+      <c r="J34" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K34" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L34" s="3" t="s">
+        <v>2267</v>
+      </c>
+    </row>
+    <row r="35" spans="2:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B35" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>2115</v>
+      </c>
+      <c r="D35" s="7" t="s">
+        <v>2393</v>
+      </c>
+      <c r="E35" s="7" t="s">
+        <v>2117</v>
+      </c>
+      <c r="F35" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="G35" s="7">
+        <v>0</v>
+      </c>
+      <c r="H35" s="7">
+        <v>25</v>
+      </c>
+      <c r="I35" s="7">
+        <f t="shared" si="1"/>
+        <v>-25</v>
+      </c>
+      <c r="J35" s="7" t="s">
+        <v>2268</v>
+      </c>
+      <c r="K35" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L35" s="7" t="s">
+        <v>2267</v>
+      </c>
+    </row>
+    <row r="36" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B36" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>2320</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>2321</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>2365</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="G36" s="3">
+        <v>0</v>
+      </c>
+      <c r="H36" s="3">
+        <v>25</v>
+      </c>
+      <c r="I36" s="3">
+        <f t="shared" si="1"/>
+        <v>-25</v>
+      </c>
+      <c r="J36" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K36" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L36" s="3" t="s">
+        <v>2267</v>
+      </c>
+    </row>
+    <row r="37" spans="2:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B37" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C37" s="7" t="s">
+        <v>463</v>
+      </c>
+      <c r="D37" s="7" t="s">
+        <v>2322</v>
+      </c>
+      <c r="E37" s="7" t="s">
+        <v>2323</v>
+      </c>
+      <c r="F37" s="7" t="s">
+        <v>2196</v>
+      </c>
+      <c r="G37" s="7">
+        <v>915</v>
+      </c>
+      <c r="H37" s="7">
+        <v>25</v>
+      </c>
+      <c r="I37" s="7">
+        <f t="shared" si="1"/>
+        <v>890</v>
+      </c>
+      <c r="J37" s="7" t="s">
+        <v>2268</v>
+      </c>
+      <c r="K37" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L37" s="7" t="s">
+        <v>2267</v>
+      </c>
+    </row>
+    <row r="38" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B38" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>2324</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>2359</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>2325</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="G38" s="3">
+        <v>915</v>
+      </c>
+      <c r="H38" s="3">
+        <v>25</v>
+      </c>
+      <c r="I38" s="3">
+        <f t="shared" si="1"/>
+        <v>890</v>
+      </c>
+      <c r="J38" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K38" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L38" s="3" t="s">
+        <v>2267</v>
+      </c>
+    </row>
+    <row r="39" spans="2:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B39" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C39" s="7" t="s">
+        <v>2326</v>
+      </c>
+      <c r="D39" s="7" t="s">
+        <v>2327</v>
+      </c>
+      <c r="E39" s="7" t="s">
+        <v>2392</v>
+      </c>
+      <c r="F39" s="7" t="s">
+        <v>2328</v>
+      </c>
+      <c r="G39" s="7">
+        <v>1175</v>
+      </c>
+      <c r="H39" s="7">
+        <v>25</v>
+      </c>
+      <c r="I39" s="7">
+        <f t="shared" si="1"/>
+        <v>1150</v>
+      </c>
+      <c r="J39" s="7" t="s">
+        <v>2268</v>
+      </c>
+      <c r="K39" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L39" s="7" t="s">
+        <v>2267</v>
+      </c>
+    </row>
+    <row r="40" spans="2:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B40" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C40" s="7" t="s">
+        <v>1693</v>
+      </c>
+      <c r="D40" s="7" t="s">
+        <v>2329</v>
+      </c>
+      <c r="E40" s="7" t="s">
+        <v>1695</v>
+      </c>
+      <c r="F40" s="7" t="s">
+        <v>2187</v>
+      </c>
+      <c r="G40" s="7">
+        <v>390</v>
+      </c>
+      <c r="H40" s="7">
+        <v>30</v>
+      </c>
+      <c r="I40" s="7">
+        <f t="shared" si="1"/>
+        <v>360</v>
+      </c>
+      <c r="J40" s="7" t="s">
+        <v>2268</v>
+      </c>
+      <c r="K40" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L40" s="7" t="s">
+        <v>2267</v>
+      </c>
+    </row>
+    <row r="41" spans="2:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B41" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C41" s="7" t="s">
+        <v>900</v>
+      </c>
+      <c r="D41" s="7" t="s">
+        <v>2330</v>
+      </c>
+      <c r="E41" s="7" t="s">
+        <v>902</v>
+      </c>
+      <c r="F41" s="7" t="s">
+        <v>2137</v>
+      </c>
+      <c r="G41" s="7">
+        <v>65</v>
+      </c>
+      <c r="H41" s="7">
+        <v>25</v>
+      </c>
+      <c r="I41" s="7">
+        <f t="shared" si="1"/>
+        <v>40</v>
+      </c>
+      <c r="J41" s="7" t="s">
+        <v>2268</v>
+      </c>
+      <c r="K41" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L41" s="7" t="s">
+        <v>2267</v>
+      </c>
+      <c r="M41" s="7" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="42" spans="2:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B42" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C42" s="7" t="s">
+        <v>2331</v>
+      </c>
+      <c r="D42" s="7" t="s">
+        <v>2332</v>
+      </c>
+      <c r="E42" s="7" t="s">
+        <v>2391</v>
+      </c>
+      <c r="F42" s="7" t="s">
+        <v>2137</v>
+      </c>
+      <c r="G42" s="7">
+        <v>685</v>
+      </c>
+      <c r="H42" s="7">
+        <v>25</v>
+      </c>
+      <c r="I42" s="7">
+        <f t="shared" si="1"/>
+        <v>660</v>
+      </c>
+      <c r="J42" s="7" t="s">
+        <v>2268</v>
+      </c>
+      <c r="K42" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L42" s="7" t="s">
+        <v>2267</v>
+      </c>
+    </row>
+    <row r="43" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B43" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>2333</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>2334</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>2364</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="G43" s="3">
+        <v>875</v>
+      </c>
+      <c r="H43" s="3">
+        <v>25</v>
+      </c>
+      <c r="I43" s="3">
+        <f t="shared" si="1"/>
+        <v>850</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K43" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L43" s="3" t="s">
+        <v>2267</v>
+      </c>
+    </row>
+    <row r="44" spans="2:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B44" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C44" s="7" t="s">
+        <v>2335</v>
+      </c>
+      <c r="D44" s="7" t="s">
+        <v>2378</v>
+      </c>
+      <c r="E44" s="7" t="s">
+        <v>2336</v>
+      </c>
+      <c r="F44" s="7" t="s">
+        <v>2189</v>
+      </c>
+      <c r="G44" s="7">
+        <v>1670</v>
+      </c>
+      <c r="H44" s="7">
+        <v>30</v>
+      </c>
+      <c r="I44" s="7">
+        <f t="shared" si="1"/>
+        <v>1640</v>
+      </c>
+      <c r="J44" s="7" t="s">
+        <v>2268</v>
+      </c>
+      <c r="K44" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L44" s="7" t="s">
+        <v>2267</v>
+      </c>
+    </row>
+    <row r="45" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B45" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>2337</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>2338</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>2339</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="G45" s="3">
+        <v>1555</v>
+      </c>
+      <c r="H45" s="3">
+        <v>25</v>
+      </c>
+      <c r="I45" s="3">
+        <f t="shared" si="1"/>
+        <v>1530</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K45" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L45" s="3" t="s">
+        <v>2267</v>
+      </c>
+    </row>
+    <row r="46" spans="2:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B46" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C46" s="7" t="s">
+        <v>2340</v>
+      </c>
+      <c r="D46" s="7" t="s">
+        <v>2341</v>
+      </c>
+      <c r="E46" s="7" t="s">
+        <v>2342</v>
+      </c>
+      <c r="F46" s="7" t="s">
+        <v>2328</v>
+      </c>
+      <c r="G46" s="7">
+        <v>0</v>
+      </c>
+      <c r="H46" s="7">
+        <v>25</v>
+      </c>
+      <c r="I46" s="7">
+        <f t="shared" si="1"/>
+        <v>-25</v>
+      </c>
+      <c r="J46" s="7" t="s">
+        <v>2268</v>
+      </c>
+      <c r="K46" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L46" s="7" t="s">
+        <v>2267</v>
+      </c>
+    </row>
+    <row r="47" spans="2:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B47" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C47" s="7" t="s">
+        <v>2343</v>
+      </c>
+      <c r="D47" s="7" t="s">
+        <v>2344</v>
+      </c>
+      <c r="E47" s="7" t="s">
+        <v>2388</v>
+      </c>
+      <c r="F47" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="G47" s="7">
+        <v>685</v>
+      </c>
+      <c r="H47" s="7">
+        <v>25</v>
+      </c>
+      <c r="I47" s="7">
+        <f t="shared" si="1"/>
+        <v>660</v>
+      </c>
+      <c r="J47" s="7" t="s">
+        <v>2268</v>
+      </c>
+      <c r="K47" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L47" s="7" t="s">
+        <v>2267</v>
+      </c>
+    </row>
+    <row r="48" spans="2:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B48" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C48" s="7" t="s">
+        <v>2380</v>
+      </c>
+      <c r="D48" s="7" t="s">
+        <v>2381</v>
+      </c>
+      <c r="E48" s="7" t="s">
+        <v>2345</v>
+      </c>
+      <c r="F48" s="7" t="s">
+        <v>2187</v>
+      </c>
+      <c r="G48" s="7">
+        <v>1530</v>
+      </c>
+      <c r="H48" s="7">
+        <v>30</v>
+      </c>
+      <c r="I48" s="7">
+        <f t="shared" si="1"/>
+        <v>1500</v>
+      </c>
+      <c r="J48" s="7" t="s">
+        <v>2268</v>
+      </c>
+      <c r="K48" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L48" s="7" t="s">
+        <v>2267</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B49" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C49" s="7" t="s">
+        <v>2346</v>
+      </c>
+      <c r="D49" s="7" t="s">
+        <v>2347</v>
+      </c>
+      <c r="E49" s="7" t="s">
+        <v>2394</v>
+      </c>
+      <c r="F49" s="7" t="s">
+        <v>2189</v>
+      </c>
+      <c r="G49" s="7">
+        <v>0</v>
+      </c>
+      <c r="H49" s="7">
+        <v>35</v>
+      </c>
+      <c r="I49" s="7">
+        <f t="shared" si="1"/>
+        <v>-35</v>
+      </c>
+      <c r="J49" s="7" t="s">
+        <v>2268</v>
+      </c>
+      <c r="K49" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L49" s="7" t="s">
+        <v>2267</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B50" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C50" s="7" t="s">
+        <v>894</v>
+      </c>
+      <c r="D50" s="7" t="s">
+        <v>2348</v>
+      </c>
+      <c r="E50" s="7" t="s">
+        <v>896</v>
+      </c>
+      <c r="F50" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="G50" s="7">
+        <v>915</v>
+      </c>
+      <c r="H50" s="7">
+        <v>25</v>
+      </c>
+      <c r="I50" s="7">
+        <f t="shared" si="1"/>
+        <v>890</v>
+      </c>
+      <c r="J50" s="7" t="s">
+        <v>2268</v>
+      </c>
+      <c r="K50" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L50" s="7" t="s">
+        <v>2267</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B51" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C51" s="7" t="s">
+        <v>2349</v>
+      </c>
+      <c r="D51" s="7" t="s">
+        <v>2350</v>
+      </c>
+      <c r="E51" s="7" t="s">
+        <v>2379</v>
+      </c>
+      <c r="F51" s="8">
+        <v>11</v>
+      </c>
+      <c r="G51" s="7">
+        <v>855</v>
+      </c>
+      <c r="H51" s="7">
+        <v>25</v>
+      </c>
+      <c r="I51" s="7">
+        <f t="shared" si="1"/>
+        <v>830</v>
+      </c>
+      <c r="J51" s="7" t="s">
+        <v>2268</v>
+      </c>
+      <c r="K51" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L51" s="7" t="s">
+        <v>2267</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B52" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C52" s="7" t="s">
+        <v>2351</v>
+      </c>
+      <c r="D52" s="7" t="s">
+        <v>2352</v>
+      </c>
+      <c r="E52" s="7" t="s">
+        <v>2398</v>
+      </c>
+      <c r="F52" s="7" t="s">
+        <v>2187</v>
+      </c>
+      <c r="G52" s="7">
+        <v>1860</v>
+      </c>
+      <c r="H52" s="7">
+        <v>30</v>
+      </c>
+      <c r="I52" s="7">
+        <f t="shared" si="1"/>
+        <v>1830</v>
+      </c>
+      <c r="J52" s="7" t="s">
+        <v>2268</v>
+      </c>
+      <c r="K52" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L52" s="7" t="s">
+        <v>2267</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B53" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C53" s="7" t="s">
+        <v>2353</v>
+      </c>
+      <c r="D53" s="7" t="s">
+        <v>2395</v>
+      </c>
+      <c r="E53" s="7" t="s">
+        <v>698</v>
+      </c>
+      <c r="F53" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="G53" s="7">
+        <v>685</v>
+      </c>
+      <c r="H53" s="7">
+        <v>25</v>
+      </c>
+      <c r="I53" s="7">
+        <f t="shared" si="1"/>
+        <v>660</v>
+      </c>
+      <c r="J53" s="7" t="s">
+        <v>2268</v>
+      </c>
+      <c r="K53" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L53" s="7" t="s">
+        <v>2267</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B54" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>2354</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>2366</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>2367</v>
+      </c>
+      <c r="F54" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="G54" s="3">
+        <v>690</v>
+      </c>
+      <c r="H54" s="3">
+        <v>20</v>
+      </c>
+      <c r="I54" s="3">
+        <f t="shared" si="1"/>
+        <v>670</v>
+      </c>
+      <c r="J54" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K54" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L54" s="3" t="s">
+        <v>2267</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B55" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C55" s="7" t="s">
+        <v>2396</v>
+      </c>
+      <c r="D55" s="7" t="s">
+        <v>2355</v>
+      </c>
+      <c r="E55" s="7" t="s">
+        <v>1866</v>
+      </c>
+      <c r="F55" s="7" t="s">
+        <v>2137</v>
+      </c>
+      <c r="G55" s="7">
+        <v>685</v>
+      </c>
+      <c r="H55" s="7">
+        <v>25</v>
+      </c>
+      <c r="I55" s="7">
+        <f t="shared" si="1"/>
+        <v>660</v>
+      </c>
+      <c r="J55" s="7" t="s">
+        <v>2268</v>
+      </c>
+      <c r="K55" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L55" s="7" t="s">
+        <v>2267</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B56" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>2356</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>2357</v>
+      </c>
+      <c r="E56" s="3" t="s">
+        <v>2368</v>
+      </c>
+      <c r="F56" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="G56" s="3">
+        <v>480</v>
+      </c>
+      <c r="H56" s="3">
+        <v>30</v>
+      </c>
+      <c r="I56" s="3">
+        <f t="shared" si="1"/>
+        <v>450</v>
+      </c>
+      <c r="J56" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K56" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L56" s="3" t="s">
+        <v>2267</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>2371</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>2370</v>
+      </c>
+      <c r="F57" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="G57" s="3">
+        <v>30</v>
+      </c>
+      <c r="H57" s="3">
+        <v>30</v>
+      </c>
+      <c r="I57" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J57" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K57" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L57" s="3" t="s">
+        <v>2267</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>2358</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>1730</v>
+      </c>
+      <c r="F58" s="3" t="s">
+        <v>2189</v>
+      </c>
+      <c r="G58" s="3">
+        <v>0</v>
+      </c>
+      <c r="H58" s="3">
+        <v>35</v>
+      </c>
+      <c r="I58" s="3">
+        <f t="shared" si="1"/>
+        <v>-35</v>
+      </c>
+      <c r="J58" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K58" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L58" s="3" t="s">
+        <v>2267</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>1761</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>2373</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="G59" s="3">
+        <v>275</v>
+      </c>
+      <c r="H59" s="3">
+        <v>25</v>
+      </c>
+      <c r="I59" s="3">
+        <f t="shared" si="1"/>
+        <v>250</v>
+      </c>
+      <c r="J59" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K59" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L59" s="3" t="s">
+        <v>2267</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="F60" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="G60" s="3">
+        <v>30</v>
+      </c>
+      <c r="H60" s="3">
+        <v>30</v>
+      </c>
+      <c r="I60" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J60" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K60" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L60" s="3" t="s">
+        <v>2267</v>
       </c>
     </row>
   </sheetData>

--- a/data/Apr/Data.xlsx
+++ b/data/Apr/Data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Freelance\TextInputter\data\Apr\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{675B32BF-AB00-481C-B155-1FA53D6D4AF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F482066E-E455-47D4-B642-74C4DC57EED2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="5" activeTab="19" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="6" activeTab="20" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01-04" sheetId="4" r:id="rId1"/>
@@ -33,6 +33,7 @@
     <sheet name="21-04" sheetId="22" r:id="rId18"/>
     <sheet name="22-04" sheetId="23" r:id="rId19"/>
     <sheet name="23-04" sheetId="24" r:id="rId20"/>
+    <sheet name="24-04" sheetId="25" r:id="rId21"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -55,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7442" uniqueCount="2407">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7980" uniqueCount="2554">
   <si>
     <t>THU 4</t>
   </si>
@@ -6858,15 +6859,24 @@
     <t>265 lý tự trọng</t>
   </si>
   <si>
+    <t>AT 23-04</t>
+  </si>
+  <si>
     <t>23-04-2026</t>
   </si>
   <si>
-    <t>AT 23-04</t>
+    <t>HD014543</t>
+  </si>
+  <si>
+    <t>Huyền Trinh</t>
   </si>
   <si>
     <t>HD014739</t>
   </si>
   <si>
+    <t>69 phố tiểu nam, phường tân phú</t>
+  </si>
+  <si>
     <t>HD014714</t>
   </si>
   <si>
@@ -6885,6 +6895,9 @@
     <t>HD014191</t>
   </si>
   <si>
+    <t>Chung cư Citiesto, cát lái</t>
+  </si>
+  <si>
     <t>Pidor 012736103</t>
   </si>
   <si>
@@ -6897,6 +6910,12 @@
     <t>W3235</t>
   </si>
   <si>
+    <t>HD014374</t>
+  </si>
+  <si>
+    <t>fb Thuyền Quyên</t>
+  </si>
+  <si>
     <t>HD014695</t>
   </si>
   <si>
@@ -6921,6 +6940,18 @@
     <t>HD000100</t>
   </si>
   <si>
+    <t>Chung cư Tecco, block C, đường Nguyễn Cửu Phủ, phường Tân Tạo</t>
+  </si>
+  <si>
+    <t>Quế Anh Đỗ</t>
+  </si>
+  <si>
+    <t>HD014655</t>
+  </si>
+  <si>
+    <t>chung cư de la sol</t>
+  </si>
+  <si>
     <t>Như Hảo</t>
   </si>
   <si>
@@ -6942,6 +6973,12 @@
     <t>HD014529</t>
   </si>
   <si>
+    <t>Bs16a The oasis Vinhomes grand park ( Phước Thiện Long Bình)</t>
+  </si>
+  <si>
+    <t>Nhận hàng giúp chị phương (ở Úc) fb Phương My</t>
+  </si>
+  <si>
     <t>HD014448</t>
   </si>
   <si>
@@ -6951,27 +6988,45 @@
     <t>HD014404</t>
   </si>
   <si>
+    <t>275A phạm ngũ lão phường phạm ngũ lão</t>
+  </si>
+  <si>
     <t>Phẩm Huỳnh</t>
   </si>
   <si>
     <t>HD014565</t>
   </si>
   <si>
+    <t>84 phạm Hồng thái phường bến thành</t>
+  </si>
+  <si>
     <t>Ngân</t>
   </si>
   <si>
     <t>HD014686</t>
   </si>
   <si>
+    <t>Landmark Plus, 208 Nguyễn Hữu Cảnh, phường 22</t>
+  </si>
+  <si>
     <t>Trang Lâm</t>
   </si>
   <si>
     <t>HD014526</t>
   </si>
   <si>
+    <t>1806/45/20/10 huỳnh tấn phát</t>
+  </si>
+  <si>
+    <t>Xiabao</t>
+  </si>
+  <si>
     <t>HD014094</t>
   </si>
   <si>
+    <t>375 Tân thới hiệp 21, Tổ 3</t>
+  </si>
+  <si>
     <t>HD014694</t>
   </si>
   <si>
@@ -6993,15 +7048,36 @@
     <t>422 đào trí shunshine diamond</t>
   </si>
   <si>
+    <t>Anie Nguyen</t>
+  </si>
+  <si>
+    <t>HD014598</t>
+  </si>
+  <si>
+    <t>C3B/124 ấp 3B Vĩnh Lộc B, hẻm Tiến Long chạy vào quẹo hẻm 2 tay phải, xã Vĩnh Lộc B</t>
+  </si>
+  <si>
+    <t>amy doan</t>
+  </si>
+  <si>
     <t>HD014399</t>
   </si>
   <si>
     <t>36/18 dương đức thiền tây thạnh</t>
   </si>
   <si>
+    <t>Charli (inst char importshop )-BN2441</t>
+  </si>
+  <si>
     <t>HD014661</t>
   </si>
   <si>
+    <t>Thị Bi</t>
+  </si>
+  <si>
+    <t>HD014615</t>
+  </si>
+  <si>
     <t>86/36/3 PHỔ QUANG, PHƯỜNG TÂN SƠN HOÀ</t>
   </si>
   <si>
@@ -7011,18 +7087,30 @@
     <t>HD014665</t>
   </si>
   <si>
+    <t>71/16 thới an 16</t>
+  </si>
+  <si>
     <t>Hoài An ft Ann Nguyen</t>
   </si>
   <si>
     <t>HD014716</t>
   </si>
   <si>
+    <t>Toà S5, chung cư the Sun Avenue 28 Mai Chí Thọ, P.Bình Trưng</t>
+  </si>
+  <si>
+    <t>HD014594</t>
+  </si>
+  <si>
     <t>Mỹ Hạnh</t>
   </si>
   <si>
     <t>HD014717</t>
   </si>
   <si>
+    <t>448/65/2 Phan Huy Ích P.12</t>
+  </si>
+  <si>
     <t>HD014669</t>
   </si>
   <si>
@@ -7032,6 +7120,9 @@
     <t>Ngọc fb Nga Nguyenn</t>
   </si>
   <si>
+    <t>HD014668</t>
+  </si>
+  <si>
     <t>434/20/14 Phạm Văn Chiêu Phường 9</t>
   </si>
   <si>
@@ -7041,6 +7132,9 @@
     <t>HD014449</t>
   </si>
   <si>
+    <t>số 3 hoà bình phường bình thới</t>
+  </si>
+  <si>
     <t>11</t>
   </si>
   <si>
@@ -7056,15 +7150,24 @@
     <t>HD014346</t>
   </si>
   <si>
+    <t>22-24 Thi Sách, Bến Nghế</t>
+  </si>
+  <si>
     <t>Trần Phượng Liên</t>
   </si>
   <si>
     <t>HD014498</t>
   </si>
   <si>
+    <t>207/9 nguyễn văn khôi p8</t>
+  </si>
+  <si>
     <t>Kim Anh Phạm Nguyễn</t>
   </si>
   <si>
+    <t>HD014381</t>
+  </si>
+  <si>
     <t>240/38/4 Tô ngọc vân, phường Thạnh Xuân</t>
   </si>
   <si>
@@ -7092,6 +7195,15 @@
     <t>HD014515</t>
   </si>
   <si>
+    <t>182 phú thọ hoa phường phú thọ hoa</t>
+  </si>
+  <si>
+    <t>Hoàng Thanh Hiền</t>
+  </si>
+  <si>
+    <t>HD014608</t>
+  </si>
+  <si>
     <t>5 đương số 8 bình thuận</t>
   </si>
   <si>
@@ -7101,6 +7213,9 @@
     <t>HD014468</t>
   </si>
   <si>
+    <t>2/1a quốc lộ 1a, tân chánh hiệp</t>
+  </si>
+  <si>
     <t>HD014726</t>
   </si>
   <si>
@@ -7110,18 +7225,36 @@
     <t>HD014730</t>
   </si>
   <si>
+    <t>8y Lạc Long Quân, P. Hòa Bình</t>
+  </si>
+  <si>
     <t>Carol Phuong Trinh</t>
   </si>
   <si>
     <t>HD014685</t>
   </si>
   <si>
+    <t>156/3 Nguyễn Văn Linh phường Tân Thuận Tây</t>
+  </si>
+  <si>
     <t>Người nhận chuột</t>
   </si>
   <si>
+    <t>HD014672</t>
+  </si>
+  <si>
     <t>Hoàng An</t>
   </si>
   <si>
+    <t>HD014524</t>
+  </si>
+  <si>
+    <t>47/3 trần bình trọng</t>
+  </si>
+  <si>
+    <t>Thu Tài Trần - Phù Thỉ</t>
+  </si>
+  <si>
     <t>HD014684</t>
   </si>
   <si>
@@ -7131,151 +7264,460 @@
     <t>HD014696</t>
   </si>
   <si>
+    <t>Block b, 102 đặng văn bi, bình thọ</t>
+  </si>
+  <si>
+    <t>Hong Nho+Nguyễn Thị Diễm Chi</t>
+  </si>
+  <si>
+    <t>29/7 Yên Thế, Phường 2</t>
+  </si>
+  <si>
     <t>BN8823</t>
   </si>
   <si>
-    <t>HD014668</t>
-  </si>
-  <si>
-    <t>Thị Bi</t>
-  </si>
-  <si>
-    <t>HD014615</t>
-  </si>
-  <si>
-    <t>Chung cư Citiesto, cát lái</t>
-  </si>
-  <si>
-    <t>Charli (inst char importshop )-BN2441</t>
-  </si>
-  <si>
-    <t>207/9 nguyễn văn khôi p8</t>
-  </si>
-  <si>
-    <t>448/65/2 Phan Huy Ích P.12</t>
-  </si>
-  <si>
-    <t>HD014524</t>
-  </si>
-  <si>
-    <t>47/3 trần bình trọng</t>
-  </si>
-  <si>
-    <t>Block b, 102 đặng văn bi, bình thọ</t>
-  </si>
-  <si>
-    <t>Landmark Plus, 208 Nguyễn Hữu Cảnh, phường 22</t>
-  </si>
-  <si>
-    <t>29/7 Yên Thế, Phường 2</t>
-  </si>
-  <si>
-    <t>Hong Nho+Nguyễn Thị Diễm Chi</t>
-  </si>
-  <si>
-    <t>HD014374</t>
-  </si>
-  <si>
     <t>482/10/26 nơ trang Long, p13</t>
   </si>
   <si>
-    <t>Xiabao</t>
-  </si>
-  <si>
-    <t>375 Tân thới hiệp 21, Tổ 3</t>
-  </si>
-  <si>
-    <t>Toà S5, chung cư the Sun Avenue 28 Mai Chí Thọ, P.Bình Trưng</t>
-  </si>
-  <si>
-    <t>amy doan</t>
-  </si>
-  <si>
-    <t>HD014381</t>
-  </si>
-  <si>
-    <t>8y Lạc Long Quân, P. Hòa Bình</t>
-  </si>
-  <si>
-    <t>Hoàng Thanh Hiền</t>
-  </si>
-  <si>
-    <t>HD014608</t>
-  </si>
-  <si>
-    <t>Huyền Trinh</t>
-  </si>
-  <si>
-    <t>69 phố tiểu nam, phường tân phú</t>
-  </si>
-  <si>
-    <t>fb Thuyền Quyên</t>
-  </si>
-  <si>
-    <t>275A phạm ngũ lão phường phạm ngũ lão</t>
-  </si>
-  <si>
-    <t>Nhận hàng giúp chị phương (ở Úc) fb Phương My</t>
-  </si>
-  <si>
-    <t>Chung cư Tecco, block C, đường Nguyễn Cửu Phủ, phường Tân Tạo</t>
-  </si>
-  <si>
-    <t>182 phú thọ hoa phường phú thọ hoa</t>
-  </si>
-  <si>
-    <t>84 phạm Hồng thái phường bến thành</t>
-  </si>
-  <si>
-    <t>1806/45/20/10 huỳnh tấn phát</t>
-  </si>
-  <si>
-    <t>22-24 Thi Sách, Bến Nghế</t>
-  </si>
-  <si>
-    <t>số 3 hoà bình phường bình thới</t>
-  </si>
-  <si>
-    <t>HD014594</t>
-  </si>
-  <si>
-    <t>2/1a quốc lộ 1a, tân chánh hiệp</t>
-  </si>
-  <si>
-    <t>HD014672</t>
-  </si>
-  <si>
-    <t>Thu Tài Trần - Phù Thỉ</t>
-  </si>
-  <si>
-    <t>71/16 thới an 16</t>
-  </si>
-  <si>
-    <t>156/3 Nguyễn Văn Linh phường Tân Thuận Tây</t>
-  </si>
-  <si>
-    <t>HD014543</t>
-  </si>
-  <si>
-    <t>Quế Anh Đỗ</t>
-  </si>
-  <si>
-    <t>HD014655</t>
-  </si>
-  <si>
-    <t>chung cư de la sol</t>
-  </si>
-  <si>
-    <t>Bs16a The oasis Vinhomes grand park ( Phước Thiện Long Bình)</t>
-  </si>
-  <si>
-    <t>Anie Nguyen</t>
-  </si>
-  <si>
-    <t>HD014598</t>
-  </si>
-  <si>
-    <t>C3B/124 ấp 3B Vĩnh Lộc B, hẻm Tiến Long chạy vào quẹo hẻm 2 tay phải, xã Vĩnh Lộc B</t>
+    <t>NGAY 24-4</t>
+  </si>
+  <si>
+    <t>Ngọc Hồng Thương</t>
+  </si>
+  <si>
+    <t>HD014885</t>
+  </si>
+  <si>
+    <t>51 đường 81 tân quy</t>
+  </si>
+  <si>
+    <t>AT 24-04</t>
+  </si>
+  <si>
+    <t>24-04-2026</t>
+  </si>
+  <si>
+    <t>Nguyễn Kim Hằng,</t>
+  </si>
+  <si>
+    <t>HD015065</t>
+  </si>
+  <si>
+    <t>Họ Yen</t>
+  </si>
+  <si>
+    <t>HD014983</t>
+  </si>
+  <si>
+    <t>HD015027</t>
+  </si>
+  <si>
+    <t>36 đường 40 kdt vạn phúc, hiệp bình phước</t>
+  </si>
+  <si>
+    <t>Hiền Hoàng</t>
+  </si>
+  <si>
+    <t>HD015189</t>
+  </si>
+  <si>
+    <t>HD015129</t>
+  </si>
+  <si>
+    <t>Thủy Ngọc Võ</t>
+  </si>
+  <si>
+    <t>HD015166</t>
+  </si>
+  <si>
+    <t>Thuương</t>
+  </si>
+  <si>
+    <t>HD014951</t>
+  </si>
+  <si>
+    <t>32/50 đường số 5, Bình Hưng Hoà</t>
+  </si>
+  <si>
+    <t>HD014899</t>
+  </si>
+  <si>
+    <t>HD014866</t>
+  </si>
+  <si>
+    <t>Thơm Thơm</t>
+  </si>
+  <si>
+    <t>HD015104</t>
+  </si>
+  <si>
+    <t>Tu Chi Tien</t>
+  </si>
+  <si>
+    <t>HD015173</t>
+  </si>
+  <si>
+    <t>41 trần quy khoách tân định</t>
+  </si>
+  <si>
+    <t>Phạm T.Thảo</t>
+  </si>
+  <si>
+    <t>HD015179</t>
+  </si>
+  <si>
+    <t>63 dương bá trạc p.rạch ông</t>
+  </si>
+  <si>
+    <t>HD014919</t>
+  </si>
+  <si>
+    <t>Hằng Nhi</t>
+  </si>
+  <si>
+    <t>HD014563</t>
+  </si>
+  <si>
+    <t>HD015199</t>
+  </si>
+  <si>
+    <t>HD015161</t>
+  </si>
+  <si>
+    <t>Lê Tuyết Nhi</t>
+  </si>
+  <si>
+    <t>HD015201</t>
+  </si>
+  <si>
+    <t>An Vi</t>
+  </si>
+  <si>
+    <t>HD014867</t>
+  </si>
+  <si>
+    <t>Hải Dương</t>
+  </si>
+  <si>
+    <t>HD014950</t>
+  </si>
+  <si>
+    <t>CUS19950/pe panhaketya</t>
+  </si>
+  <si>
+    <t>HD015159</t>
+  </si>
+  <si>
+    <t>HD015214</t>
+  </si>
+  <si>
+    <t>Nguyễn Thị Bích Huyền</t>
+  </si>
+  <si>
+    <t>HD015022</t>
+  </si>
+  <si>
+    <t>Nguyen Thi Thu Trang</t>
+  </si>
+  <si>
+    <t>HD014831</t>
+  </si>
+  <si>
+    <t>bảo bảo fb Phương Phương</t>
+  </si>
+  <si>
+    <t>HD015165</t>
+  </si>
+  <si>
+    <t>HD015008</t>
+  </si>
+  <si>
+    <t>HD014870</t>
+  </si>
+  <si>
+    <t>306 Nguyễn thiện thuật phường 3</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>Trần Lê Trâm Anh</t>
+  </si>
+  <si>
+    <t>HD015267</t>
+  </si>
+  <si>
+    <t>179/13A hoà bình</t>
+  </si>
+  <si>
+    <t>HD015068</t>
+  </si>
+  <si>
+    <t>Phương Quỳnh</t>
+  </si>
+  <si>
+    <t>HD014884</t>
+  </si>
+  <si>
+    <t>6D đường số 2B, Khu Phố 9, Bình Hưng Hòa A</t>
+  </si>
+  <si>
+    <t>HD014965</t>
+  </si>
+  <si>
+    <t>Hà Gia Mẫn</t>
+  </si>
+  <si>
+    <t>HD015024</t>
+  </si>
+  <si>
+    <t>Tk22/26 Nguyễn cảnh chân- cầu ông lãnh</t>
+  </si>
+  <si>
+    <t>Nhớ Nhớ</t>
+  </si>
+  <si>
+    <t>HD015170</t>
+  </si>
+  <si>
+    <t>HD015010</t>
+  </si>
+  <si>
+    <t>The Sun Avenue S3-Mai Chí thọ</t>
+  </si>
+  <si>
+    <t>HD015082</t>
+  </si>
+  <si>
+    <t>Nhã Phương</t>
+  </si>
+  <si>
+    <t>HD015029</t>
+  </si>
+  <si>
+    <t>Tuyết Nhi</t>
+  </si>
+  <si>
+    <t>HD014894</t>
+  </si>
+  <si>
+    <t>HD014972</t>
+  </si>
+  <si>
+    <t>HD015158</t>
+  </si>
+  <si>
+    <t>Ngọc Phượng</t>
+  </si>
+  <si>
+    <t>HD014928</t>
+  </si>
+  <si>
+    <t>HD015089</t>
+  </si>
+  <si>
+    <t>HD014764</t>
+  </si>
+  <si>
+    <t>116a đường số 16 p tân quy</t>
+  </si>
+  <si>
+    <t>Thanh Hà Phạm</t>
+  </si>
+  <si>
+    <t>HD015051</t>
+  </si>
+  <si>
+    <t>29/15 yên thế, p2</t>
+  </si>
+  <si>
+    <t>Yen Nguyen</t>
+  </si>
+  <si>
+    <t>HD015181</t>
+  </si>
+  <si>
+    <t>92g nguyễn hữu cảnh, phường 22</t>
+  </si>
+  <si>
+    <t>HD015080</t>
+  </si>
+  <si>
+    <t>Trang Nhung</t>
+  </si>
+  <si>
+    <t>HD015083</t>
+  </si>
+  <si>
+    <t>Chung cư Hà độ toà orchid 2</t>
+  </si>
+  <si>
+    <t>Nguyễn Hồng Nga</t>
+  </si>
+  <si>
+    <t>HD014904</t>
+  </si>
+  <si>
+    <t>HD015264</t>
+  </si>
+  <si>
+    <t>Nguyễn Hương Giang</t>
+  </si>
+  <si>
+    <t>HD015198</t>
+  </si>
+  <si>
+    <t>1702 Quang Trung, P.10</t>
+  </si>
+  <si>
+    <t>Nguyễn Kim Ngân</t>
+  </si>
+  <si>
+    <t>HD014871</t>
+  </si>
+  <si>
+    <t>Lavida Plus, Nguyễn Văi Linh, Tân Phong</t>
+  </si>
+  <si>
+    <t>Ny</t>
+  </si>
+  <si>
+    <t>HD015044</t>
+  </si>
+  <si>
+    <t>301 Phuong Pham Ngu Lao Street, District 1</t>
+  </si>
+  <si>
+    <t>HD015180</t>
+  </si>
+  <si>
+    <t>HD014918</t>
+  </si>
+  <si>
+    <t>HD015247</t>
+  </si>
+  <si>
+    <t>HD015072</t>
+  </si>
+  <si>
+    <t>Trần Hương</t>
+  </si>
+  <si>
+    <t>HD015100</t>
+  </si>
+  <si>
+    <t>Lê Thị Tuyết Trâm</t>
+  </si>
+  <si>
+    <t>HD015167</t>
+  </si>
+  <si>
+    <t>HD015077</t>
+  </si>
+  <si>
+    <t>208 nguyễn hữu cảnh p22 - landmark 3</t>
+  </si>
+  <si>
+    <t>104/12 Nguyễn Trọng Tuyển, P15</t>
+  </si>
+  <si>
+    <t>Toà Central 2, Vinhomes Central Park, số 208 Nguyễn Hữu Cảnh, phường 22</t>
+  </si>
+  <si>
+    <t>fb Trang Nguyen</t>
+  </si>
+  <si>
+    <t>452/ G33 Phan Văn trị phường 7 Công ty chuyển phát nhanh quốc tế Bm ViNa</t>
+  </si>
+  <si>
+    <t>82/17/20 đinh tiên hoàng p1</t>
+  </si>
+  <si>
+    <t>chung cư terrace 21 võ trường toản</t>
+  </si>
+  <si>
+    <t>119 nguyễn văn công p. Hạnh Thông</t>
+  </si>
+  <si>
+    <t>26/2 đường 59 p14</t>
+  </si>
+  <si>
+    <t>đường số 104 brillant tower 3 1206 cc đảo kim cương bình trưng tây</t>
+  </si>
+  <si>
+    <t>MINZZY</t>
+  </si>
+  <si>
+    <t>XE TOÀN THẮNG</t>
+  </si>
+  <si>
+    <t>mai chí thọ phường an phú Cc lexington block B</t>
+  </si>
+  <si>
+    <t>13 đường số 3, Khu dân cư phước kiển A, Lê Văn Lương</t>
+  </si>
+  <si>
+    <t>179/13A hoà bình Phường Hiệp Tân</t>
+  </si>
+  <si>
+    <t>8/14 Trịnh Đình Thảo, Hoà Thạnh</t>
+  </si>
+  <si>
+    <t>Chung Cư số 1 Tôn Thất Thuyết Lô M1.613</t>
+  </si>
+  <si>
+    <t>Xuân Phát tiktok @xuanphat94</t>
+  </si>
+  <si>
+    <t>HD015085</t>
+  </si>
+  <si>
+    <t>B214bis đường đông hưng thuận 1, phường đông hưng thuận</t>
+  </si>
+  <si>
+    <t>132 bến vân đồn p9</t>
+  </si>
+  <si>
+    <t>Thý An</t>
+  </si>
+  <si>
+    <t>Block d2, chung cư sài gòn riverside (số 4 đào trí, phú thuận)</t>
+  </si>
+  <si>
+    <t>The grand midtown m5 đường số 16 p. Tân Phú</t>
+  </si>
+  <si>
+    <t>139/1 dạ nam phường 3</t>
+  </si>
+  <si>
+    <t>Sunrise lô D Nguyễn hữa thọ, Xã Phước Kiển</t>
+  </si>
+  <si>
+    <t>132 bến vân đồn p6</t>
+  </si>
+  <si>
+    <t>Nguyễn Thùy Vi</t>
+  </si>
+  <si>
+    <t>The Tresor,39-39b bến vân đồn</t>
+  </si>
+  <si>
+    <t>339 lê văn quới phường bình trị đông A</t>
+  </si>
+  <si>
+    <t>A22/5 phạm thế hiển p3</t>
+  </si>
+  <si>
+    <t>Sài gòn Mia block A đường 9a khu trung sơn bình hưng</t>
+  </si>
+  <si>
+    <t>HD014837</t>
+  </si>
+  <si>
+    <t>90/11 dương bá trạc phương rạch ông</t>
+  </si>
+  <si>
+    <t>gộp, kh ck shop 865k</t>
   </si>
 </sst>
 </file>
@@ -7317,7 +7759,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -7370,6 +7812,12 @@
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -7398,7 +7846,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -7435,6 +7883,7 @@
     <xf numFmtId="49" fontId="2" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -16366,7 +16815,7 @@
         <v>25</v>
       </c>
       <c r="I35" s="7">
-        <f t="shared" ref="I35:I66" si="1">G35-H35</f>
+        <f t="shared" ref="I35:I52" si="1">G35-H35</f>
         <v>-25</v>
       </c>
       <c r="J35" s="7" t="s">
@@ -18280,7 +18729,7 @@
         <v>25</v>
       </c>
       <c r="I35" s="7">
-        <f t="shared" ref="I35:I66" si="1">G35-H35</f>
+        <f t="shared" ref="I35:I53" si="1">G35-H35</f>
         <v>990</v>
       </c>
       <c r="J35" s="7" t="s">
@@ -22850,7 +23299,7 @@
         <v>25</v>
       </c>
       <c r="I67" s="3">
-        <f t="shared" ref="I67:I98" si="2">G67-H67</f>
+        <f t="shared" ref="I67:I97" si="2">G67-H67</f>
         <v>-25</v>
       </c>
       <c r="J67" s="3" t="s">
@@ -25265,7 +25714,7 @@
         <v>25</v>
       </c>
       <c r="I35" s="7">
-        <f t="shared" ref="I35:I66" si="1">G35-H35</f>
+        <f t="shared" ref="I35:I59" si="1">G35-H35</f>
         <v>530</v>
       </c>
       <c r="J35" s="7" t="s">
@@ -27651,7 +28100,7 @@
         <v>25</v>
       </c>
       <c r="I35" s="3">
-        <f t="shared" ref="I35:I66" si="1">G35-H35</f>
+        <f t="shared" ref="I35:I56" si="1">G35-H35</f>
         <v>-25</v>
       </c>
       <c r="J35" s="3" t="s">
@@ -29317,11 +29766,14 @@
   <dimension ref="A1:P60"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="1" max="2" width="9.140625" customWidth="1"/>
     <col min="3" max="3" width="45" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9.5703125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="76.140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="9" width="9.140625" customWidth="1"/>
     <col min="10" max="10" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.140625" customWidth="1"/>
     <col min="12" max="12" width="10.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -29406,17 +29858,17 @@
         <v>25</v>
       </c>
       <c r="I3" s="7">
-        <f t="shared" ref="I3:I33" si="0">G3-H3</f>
+        <f t="shared" ref="I3:I8" si="0">G3-H3</f>
         <v>1120</v>
       </c>
       <c r="J3" s="7" t="s">
+        <v>2267</v>
+      </c>
+      <c r="K3" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L3" s="7" t="s">
         <v>2268</v>
-      </c>
-      <c r="K3" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="L3" s="7" t="s">
-        <v>2267</v>
       </c>
     </row>
     <row r="4" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -29427,7 +29879,7 @@
         <v>1219</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>2399</v>
+        <v>2269</v>
       </c>
       <c r="E4" s="7" t="s">
         <v>1221</v>
@@ -29446,13 +29898,13 @@
         <v>-30</v>
       </c>
       <c r="J4" s="7" t="s">
+        <v>2267</v>
+      </c>
+      <c r="K4" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L4" s="7" t="s">
         <v>2268</v>
-      </c>
-      <c r="K4" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="L4" s="7" t="s">
-        <v>2267</v>
       </c>
     </row>
     <row r="5" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -29460,13 +29912,13 @@
         <v>18</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>2382</v>
+        <v>2270</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>2269</v>
+        <v>2271</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>2383</v>
+        <v>2272</v>
       </c>
       <c r="F5" s="7" t="s">
         <v>2187</v>
@@ -29482,13 +29934,13 @@
         <v>440</v>
       </c>
       <c r="J5" s="7" t="s">
+        <v>2267</v>
+      </c>
+      <c r="K5" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L5" s="7" t="s">
         <v>2268</v>
-      </c>
-      <c r="K5" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="L5" s="7" t="s">
-        <v>2267</v>
       </c>
     </row>
     <row r="6" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -29499,7 +29951,7 @@
         <v>884</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>2270</v>
+        <v>2273</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>886</v>
@@ -29518,13 +29970,13 @@
         <v>350</v>
       </c>
       <c r="J6" s="7" t="s">
+        <v>2267</v>
+      </c>
+      <c r="K6" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L6" s="7" t="s">
         <v>2268</v>
-      </c>
-      <c r="K6" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="L6" s="7" t="s">
-        <v>2267</v>
       </c>
     </row>
     <row r="7" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -29532,13 +29984,13 @@
         <v>18</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>2271</v>
+        <v>2274</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>2272</v>
+        <v>2275</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>2273</v>
+        <v>2276</v>
       </c>
       <c r="F7" s="7" t="s">
         <v>2238</v>
@@ -29554,13 +30006,13 @@
         <v>530</v>
       </c>
       <c r="J7" s="7" t="s">
+        <v>2267</v>
+      </c>
+      <c r="K7" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L7" s="7" t="s">
         <v>2268</v>
-      </c>
-      <c r="K7" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="L7" s="7" t="s">
-        <v>2267</v>
       </c>
     </row>
     <row r="8" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -29568,13 +30020,13 @@
         <v>18</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>2274</v>
+        <v>2277</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>2275</v>
+        <v>2278</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>2362</v>
+        <v>2279</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>2133</v>
@@ -29596,7 +30048,7 @@
         <v>24</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>2267</v>
+        <v>2268</v>
       </c>
     </row>
     <row r="9" spans="1:16" s="9" customFormat="1" x14ac:dyDescent="0.25">
@@ -29604,13 +30056,13 @@
         <v>18</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>2276</v>
+        <v>2280</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>2277</v>
+        <v>2281</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>2278</v>
+        <v>2282</v>
       </c>
       <c r="F9" s="9">
         <v>5</v>
@@ -29631,7 +30083,7 @@
         <v>24</v>
       </c>
       <c r="L9" s="9" t="s">
-        <v>2267</v>
+        <v>2268</v>
       </c>
     </row>
     <row r="10" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -29639,10 +30091,10 @@
         <v>18</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>2279</v>
+        <v>2283</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>2372</v>
+        <v>2284</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>569</v>
@@ -29657,7 +30109,7 @@
         <v>30</v>
       </c>
       <c r="I10" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="I10:I41" si="1">G10-H10</f>
         <v>-30</v>
       </c>
       <c r="J10" s="3" t="s">
@@ -29667,7 +30119,7 @@
         <v>24</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>2267</v>
+        <v>2268</v>
       </c>
     </row>
     <row r="11" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -29675,13 +30127,13 @@
         <v>18</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>2384</v>
+        <v>2285</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>2280</v>
+        <v>2286</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>2281</v>
+        <v>2287</v>
       </c>
       <c r="F11" s="7" t="s">
         <v>22</v>
@@ -29693,17 +30145,17 @@
         <v>30</v>
       </c>
       <c r="I11" s="7">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-30</v>
       </c>
       <c r="J11" s="7" t="s">
+        <v>2267</v>
+      </c>
+      <c r="K11" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L11" s="7" t="s">
         <v>2268</v>
-      </c>
-      <c r="K11" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="L11" s="7" t="s">
-        <v>2267</v>
       </c>
     </row>
     <row r="12" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -29714,7 +30166,7 @@
         <v>596</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>2282</v>
+        <v>2288</v>
       </c>
       <c r="E12" s="7" t="s">
         <v>598</v>
@@ -29729,17 +30181,17 @@
         <v>25</v>
       </c>
       <c r="I12" s="7">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>500</v>
       </c>
       <c r="J12" s="7" t="s">
+        <v>2267</v>
+      </c>
+      <c r="K12" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L12" s="7" t="s">
         <v>2268</v>
-      </c>
-      <c r="K12" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="L12" s="7" t="s">
-        <v>2267</v>
       </c>
     </row>
     <row r="13" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -29747,13 +30199,13 @@
         <v>18</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>2283</v>
+        <v>2289</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>2284</v>
+        <v>2290</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>2285</v>
+        <v>2291</v>
       </c>
       <c r="F13" s="7" t="s">
         <v>2187</v>
@@ -29765,17 +30217,17 @@
         <v>30</v>
       </c>
       <c r="I13" s="7">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>660</v>
       </c>
       <c r="J13" s="7" t="s">
+        <v>2267</v>
+      </c>
+      <c r="K13" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L13" s="7" t="s">
         <v>2268</v>
-      </c>
-      <c r="K13" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="L13" s="7" t="s">
-        <v>2267</v>
       </c>
     </row>
     <row r="14" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -29786,7 +30238,7 @@
         <v>750</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>2286</v>
+        <v>2292</v>
       </c>
       <c r="E14" s="7" t="s">
         <v>752</v>
@@ -29801,17 +30253,17 @@
         <v>25</v>
       </c>
       <c r="I14" s="7">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>450</v>
       </c>
       <c r="J14" s="7" t="s">
+        <v>2267</v>
+      </c>
+      <c r="K14" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L14" s="7" t="s">
         <v>2268</v>
-      </c>
-      <c r="K14" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="L14" s="7" t="s">
-        <v>2267</v>
       </c>
     </row>
     <row r="15" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -29822,10 +30274,10 @@
         <v>2023</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>2287</v>
+        <v>2293</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>2387</v>
+        <v>2294</v>
       </c>
       <c r="F15" s="7" t="s">
         <v>88</v>
@@ -29837,17 +30289,17 @@
         <v>30</v>
       </c>
       <c r="I15" s="7">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>450</v>
       </c>
       <c r="J15" s="7" t="s">
+        <v>2267</v>
+      </c>
+      <c r="K15" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L15" s="7" t="s">
         <v>2268</v>
-      </c>
-      <c r="K15" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="L15" s="7" t="s">
-        <v>2267</v>
       </c>
     </row>
     <row r="16" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -29855,13 +30307,13 @@
         <v>18</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>2400</v>
+        <v>2295</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>2401</v>
+        <v>2296</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>2402</v>
+        <v>2297</v>
       </c>
       <c r="F16" s="8">
         <v>4</v>
@@ -29873,17 +30325,17 @@
         <v>25</v>
       </c>
       <c r="I16" s="7">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>660</v>
       </c>
       <c r="J16" s="7" t="s">
+        <v>2267</v>
+      </c>
+      <c r="K16" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L16" s="7" t="s">
         <v>2268</v>
-      </c>
-      <c r="K16" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="L16" s="7" t="s">
-        <v>2267</v>
       </c>
     </row>
     <row r="17" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -29891,13 +30343,13 @@
         <v>18</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>2288</v>
+        <v>2298</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>2289</v>
+        <v>2299</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>2290</v>
+        <v>2300</v>
       </c>
       <c r="F17" s="3" t="s">
         <v>116</v>
@@ -29909,7 +30361,7 @@
         <v>30</v>
       </c>
       <c r="I17" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>450</v>
       </c>
       <c r="J17" s="3" t="s">
@@ -29919,7 +30371,7 @@
         <v>24</v>
       </c>
       <c r="L17" s="3" t="s">
-        <v>2267</v>
+        <v>2268</v>
       </c>
     </row>
     <row r="18" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -29927,13 +30379,13 @@
         <v>18</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>2291</v>
+        <v>2301</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>2292</v>
+        <v>2302</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>2293</v>
+        <v>2303</v>
       </c>
       <c r="F18" s="3" t="s">
         <v>38</v>
@@ -29945,7 +30397,7 @@
         <v>20</v>
       </c>
       <c r="I18" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1120</v>
       </c>
       <c r="J18" s="3" t="s">
@@ -29955,7 +30407,7 @@
         <v>24</v>
       </c>
       <c r="L18" s="3" t="s">
-        <v>2267</v>
+        <v>2268</v>
       </c>
     </row>
     <row r="19" spans="2:12" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -29966,10 +30418,10 @@
         <v>1108</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>2294</v>
+        <v>2304</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>2403</v>
+        <v>2305</v>
       </c>
       <c r="F19" s="5" t="s">
         <v>2144</v>
@@ -29981,7 +30433,7 @@
         <v>20</v>
       </c>
       <c r="I19" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>30</v>
       </c>
       <c r="J19" s="5" t="s">
@@ -29991,7 +30443,7 @@
         <v>24</v>
       </c>
       <c r="L19" s="5" t="s">
-        <v>2267</v>
+        <v>2268</v>
       </c>
     </row>
     <row r="20" spans="2:12" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -29999,10 +30451,10 @@
         <v>18</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>2386</v>
+        <v>2306</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>2295</v>
+        <v>2307</v>
       </c>
       <c r="E20" s="7" t="s">
         <v>1796</v>
@@ -30017,17 +30469,17 @@
         <v>35</v>
       </c>
       <c r="I20" s="7">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-35</v>
       </c>
       <c r="J20" s="7" t="s">
+        <v>2267</v>
+      </c>
+      <c r="K20" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L20" s="7" t="s">
         <v>2268</v>
-      </c>
-      <c r="K20" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="L20" s="7" t="s">
-        <v>2267</v>
       </c>
     </row>
     <row r="21" spans="2:12" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -30035,13 +30487,13 @@
         <v>18</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>2296</v>
+        <v>2308</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>2297</v>
+        <v>2309</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>2385</v>
+        <v>2310</v>
       </c>
       <c r="F21" s="7" t="s">
         <v>2137</v>
@@ -30053,17 +30505,17 @@
         <v>25</v>
       </c>
       <c r="I21" s="7">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>840</v>
       </c>
       <c r="J21" s="7" t="s">
+        <v>2267</v>
+      </c>
+      <c r="K21" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L21" s="7" t="s">
         <v>2268</v>
-      </c>
-      <c r="K21" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="L21" s="7" t="s">
-        <v>2267</v>
       </c>
     </row>
     <row r="22" spans="2:12" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -30071,13 +30523,13 @@
         <v>18</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>2298</v>
+        <v>2311</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>2299</v>
+        <v>2312</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>2389</v>
+        <v>2313</v>
       </c>
       <c r="F22" s="7" t="s">
         <v>2137</v>
@@ -30089,17 +30541,17 @@
         <v>25</v>
       </c>
       <c r="I22" s="7">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1890</v>
       </c>
       <c r="J22" s="7" t="s">
+        <v>2267</v>
+      </c>
+      <c r="K22" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L22" s="7" t="s">
         <v>2268</v>
-      </c>
-      <c r="K22" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="L22" s="7" t="s">
-        <v>2267</v>
       </c>
     </row>
     <row r="23" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -30107,13 +30559,13 @@
         <v>18</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>2300</v>
+        <v>2314</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>2301</v>
+        <v>2315</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>2369</v>
+        <v>2316</v>
       </c>
       <c r="F23" s="3" t="s">
         <v>38</v>
@@ -30125,7 +30577,7 @@
         <v>20</v>
       </c>
       <c r="I23" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-20</v>
       </c>
       <c r="J23" s="3" t="s">
@@ -30135,7 +30587,7 @@
         <v>24</v>
       </c>
       <c r="L23" s="3" t="s">
-        <v>2267</v>
+        <v>2268</v>
       </c>
     </row>
     <row r="24" spans="2:12" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -30143,13 +30595,13 @@
         <v>18</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>2302</v>
+        <v>2317</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>2303</v>
+        <v>2318</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>2390</v>
+        <v>2319</v>
       </c>
       <c r="F24" s="7" t="s">
         <v>111</v>
@@ -30161,17 +30613,17 @@
         <v>35</v>
       </c>
       <c r="I24" s="7">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1320</v>
       </c>
       <c r="J24" s="7" t="s">
+        <v>2267</v>
+      </c>
+      <c r="K24" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L24" s="7" t="s">
         <v>2268</v>
-      </c>
-      <c r="K24" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="L24" s="7" t="s">
-        <v>2267</v>
       </c>
     </row>
     <row r="25" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -30179,13 +30631,13 @@
         <v>18</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>2374</v>
+        <v>2320</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>2304</v>
+        <v>2321</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>2375</v>
+        <v>2322</v>
       </c>
       <c r="F25" s="3" t="s">
         <v>2189</v>
@@ -30197,7 +30649,7 @@
         <v>30</v>
       </c>
       <c r="I25" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-30</v>
       </c>
       <c r="J25" s="3" t="s">
@@ -30207,7 +30659,7 @@
         <v>24</v>
       </c>
       <c r="L25" s="3" t="s">
-        <v>2267</v>
+        <v>2268</v>
       </c>
     </row>
     <row r="26" spans="2:12" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -30218,7 +30670,7 @@
         <v>1063</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>2305</v>
+        <v>2323</v>
       </c>
       <c r="E26" s="7" t="s">
         <v>1189</v>
@@ -30233,17 +30685,17 @@
         <v>30</v>
       </c>
       <c r="I26" s="7">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>850</v>
       </c>
       <c r="J26" s="7" t="s">
+        <v>2267</v>
+      </c>
+      <c r="K26" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L26" s="7" t="s">
         <v>2268</v>
-      </c>
-      <c r="K26" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="L26" s="7" t="s">
-        <v>2267</v>
       </c>
     </row>
     <row r="27" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -30251,13 +30703,13 @@
         <v>18</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>2306</v>
+        <v>2324</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>2307</v>
+        <v>2325</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>2308</v>
+        <v>2326</v>
       </c>
       <c r="F27" s="3" t="s">
         <v>116</v>
@@ -30269,7 +30721,7 @@
         <v>30</v>
       </c>
       <c r="I27" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>860</v>
       </c>
       <c r="J27" s="3" t="s">
@@ -30279,7 +30731,7 @@
         <v>24</v>
       </c>
       <c r="L27" s="3" t="s">
-        <v>2267</v>
+        <v>2268</v>
       </c>
     </row>
     <row r="28" spans="2:12" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -30287,13 +30739,13 @@
         <v>18</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>2309</v>
+        <v>2327</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>2310</v>
+        <v>2328</v>
       </c>
       <c r="E28" s="7" t="s">
-        <v>2311</v>
+        <v>2329</v>
       </c>
       <c r="F28" s="7" t="s">
         <v>2187</v>
@@ -30305,17 +30757,17 @@
         <v>30</v>
       </c>
       <c r="I28" s="7">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1960</v>
       </c>
       <c r="J28" s="7" t="s">
+        <v>2267</v>
+      </c>
+      <c r="K28" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L28" s="7" t="s">
         <v>2268</v>
-      </c>
-      <c r="K28" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="L28" s="7" t="s">
-        <v>2267</v>
       </c>
     </row>
     <row r="29" spans="2:12" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -30323,13 +30775,13 @@
         <v>18</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>2404</v>
+        <v>2330</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>2405</v>
+        <v>2331</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>2406</v>
+        <v>2332</v>
       </c>
       <c r="F29" s="7" t="s">
         <v>143</v>
@@ -30341,17 +30793,17 @@
         <v>35</v>
       </c>
       <c r="I29" s="7">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-35</v>
       </c>
       <c r="J29" s="7" t="s">
+        <v>2267</v>
+      </c>
+      <c r="K29" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L29" s="7" t="s">
         <v>2268</v>
-      </c>
-      <c r="K29" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="L29" s="7" t="s">
-        <v>2267</v>
       </c>
     </row>
     <row r="30" spans="2:12" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -30359,13 +30811,13 @@
         <v>18</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>2377</v>
+        <v>2333</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>2312</v>
+        <v>2334</v>
       </c>
       <c r="E30" s="7" t="s">
-        <v>2313</v>
+        <v>2335</v>
       </c>
       <c r="F30" s="7" t="s">
         <v>208</v>
@@ -30377,17 +30829,17 @@
         <v>25</v>
       </c>
       <c r="I30" s="7">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1520</v>
       </c>
       <c r="J30" s="7" t="s">
+        <v>2267</v>
+      </c>
+      <c r="K30" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L30" s="7" t="s">
         <v>2268</v>
-      </c>
-      <c r="K30" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="L30" s="7" t="s">
-        <v>2267</v>
       </c>
     </row>
     <row r="31" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -30395,10 +30847,10 @@
         <v>18</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>2363</v>
+        <v>2336</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>2314</v>
+        <v>2337</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>1730</v>
@@ -30413,7 +30865,7 @@
         <v>30</v>
       </c>
       <c r="I31" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-30</v>
       </c>
       <c r="J31" s="3" t="s">
@@ -30423,7 +30875,7 @@
         <v>24</v>
       </c>
       <c r="L31" s="3" t="s">
-        <v>2267</v>
+        <v>2268</v>
       </c>
     </row>
     <row r="32" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -30431,13 +30883,13 @@
         <v>18</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>2360</v>
+        <v>2338</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>2361</v>
+        <v>2339</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>2315</v>
+        <v>2340</v>
       </c>
       <c r="F32" s="3" t="s">
         <v>88</v>
@@ -30449,7 +30901,7 @@
         <v>25</v>
       </c>
       <c r="I32" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1220</v>
       </c>
       <c r="J32" s="3" t="s">
@@ -30459,7 +30911,7 @@
         <v>24</v>
       </c>
       <c r="L32" s="3" t="s">
-        <v>2267</v>
+        <v>2268</v>
       </c>
     </row>
     <row r="33" spans="2:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -30467,13 +30919,13 @@
         <v>18</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>2316</v>
+        <v>2341</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>2317</v>
+        <v>2342</v>
       </c>
       <c r="E33" s="7" t="s">
-        <v>2397</v>
+        <v>2343</v>
       </c>
       <c r="F33" s="7" t="s">
         <v>2189</v>
@@ -30485,17 +30937,17 @@
         <v>30</v>
       </c>
       <c r="I33" s="7">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>890</v>
       </c>
       <c r="J33" s="7" t="s">
+        <v>2267</v>
+      </c>
+      <c r="K33" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L33" s="7" t="s">
         <v>2268</v>
-      </c>
-      <c r="K33" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="L33" s="7" t="s">
-        <v>2267</v>
       </c>
     </row>
     <row r="34" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -30503,13 +30955,13 @@
         <v>18</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>2318</v>
+        <v>2344</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>2319</v>
+        <v>2345</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>2376</v>
+        <v>2346</v>
       </c>
       <c r="F34" s="4">
         <v>2</v>
@@ -30521,7 +30973,7 @@
         <v>30</v>
       </c>
       <c r="I34" s="3">
-        <f t="shared" ref="I34:I65" si="1">G34-H34</f>
+        <f t="shared" si="1"/>
         <v>-30</v>
       </c>
       <c r="J34" s="3" t="s">
@@ -30531,7 +30983,7 @@
         <v>24</v>
       </c>
       <c r="L34" s="3" t="s">
-        <v>2267</v>
+        <v>2268</v>
       </c>
     </row>
     <row r="35" spans="2:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -30542,7 +30994,7 @@
         <v>2115</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>2393</v>
+        <v>2347</v>
       </c>
       <c r="E35" s="7" t="s">
         <v>2117</v>
@@ -30561,13 +31013,13 @@
         <v>-25</v>
       </c>
       <c r="J35" s="7" t="s">
+        <v>2267</v>
+      </c>
+      <c r="K35" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L35" s="7" t="s">
         <v>2268</v>
-      </c>
-      <c r="K35" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="L35" s="7" t="s">
-        <v>2267</v>
       </c>
     </row>
     <row r="36" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -30575,13 +31027,13 @@
         <v>18</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>2320</v>
+        <v>2348</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>2321</v>
+        <v>2349</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>2365</v>
+        <v>2350</v>
       </c>
       <c r="F36" s="3" t="s">
         <v>46</v>
@@ -30603,7 +31055,7 @@
         <v>24</v>
       </c>
       <c r="L36" s="3" t="s">
-        <v>2267</v>
+        <v>2268</v>
       </c>
     </row>
     <row r="37" spans="2:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -30614,10 +31066,10 @@
         <v>463</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>2322</v>
+        <v>2351</v>
       </c>
       <c r="E37" s="7" t="s">
-        <v>2323</v>
+        <v>2352</v>
       </c>
       <c r="F37" s="7" t="s">
         <v>2196</v>
@@ -30633,13 +31085,13 @@
         <v>890</v>
       </c>
       <c r="J37" s="7" t="s">
+        <v>2267</v>
+      </c>
+      <c r="K37" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L37" s="7" t="s">
         <v>2268</v>
-      </c>
-      <c r="K37" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="L37" s="7" t="s">
-        <v>2267</v>
       </c>
     </row>
     <row r="38" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -30647,13 +31099,13 @@
         <v>18</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>2324</v>
+        <v>2353</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>2359</v>
+        <v>2354</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>2325</v>
+        <v>2355</v>
       </c>
       <c r="F38" s="3" t="s">
         <v>46</v>
@@ -30675,7 +31127,7 @@
         <v>24</v>
       </c>
       <c r="L38" s="3" t="s">
-        <v>2267</v>
+        <v>2268</v>
       </c>
     </row>
     <row r="39" spans="2:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -30683,16 +31135,16 @@
         <v>18</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>2326</v>
+        <v>2356</v>
       </c>
       <c r="D39" s="7" t="s">
-        <v>2327</v>
+        <v>2357</v>
       </c>
       <c r="E39" s="7" t="s">
-        <v>2392</v>
+        <v>2358</v>
       </c>
       <c r="F39" s="7" t="s">
-        <v>2328</v>
+        <v>2359</v>
       </c>
       <c r="G39" s="7">
         <v>1175</v>
@@ -30705,13 +31157,13 @@
         <v>1150</v>
       </c>
       <c r="J39" s="7" t="s">
+        <v>2267</v>
+      </c>
+      <c r="K39" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L39" s="7" t="s">
         <v>2268</v>
-      </c>
-      <c r="K39" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="L39" s="7" t="s">
-        <v>2267</v>
       </c>
     </row>
     <row r="40" spans="2:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -30722,7 +31174,7 @@
         <v>1693</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>2329</v>
+        <v>2360</v>
       </c>
       <c r="E40" s="7" t="s">
         <v>1695</v>
@@ -30741,13 +31193,13 @@
         <v>360</v>
       </c>
       <c r="J40" s="7" t="s">
+        <v>2267</v>
+      </c>
+      <c r="K40" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L40" s="7" t="s">
         <v>2268</v>
-      </c>
-      <c r="K40" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="L40" s="7" t="s">
-        <v>2267</v>
       </c>
     </row>
     <row r="41" spans="2:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -30758,7 +31210,7 @@
         <v>900</v>
       </c>
       <c r="D41" s="7" t="s">
-        <v>2330</v>
+        <v>2361</v>
       </c>
       <c r="E41" s="7" t="s">
         <v>902</v>
@@ -30777,13 +31229,13 @@
         <v>40</v>
       </c>
       <c r="J41" s="7" t="s">
+        <v>2267</v>
+      </c>
+      <c r="K41" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L41" s="7" t="s">
         <v>2268</v>
-      </c>
-      <c r="K41" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="L41" s="7" t="s">
-        <v>2267</v>
       </c>
       <c r="M41" s="7" t="s">
         <v>68</v>
@@ -30794,13 +31246,13 @@
         <v>18</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>2331</v>
+        <v>2362</v>
       </c>
       <c r="D42" s="7" t="s">
-        <v>2332</v>
+        <v>2363</v>
       </c>
       <c r="E42" s="7" t="s">
-        <v>2391</v>
+        <v>2364</v>
       </c>
       <c r="F42" s="7" t="s">
         <v>2137</v>
@@ -30812,17 +31264,17 @@
         <v>25</v>
       </c>
       <c r="I42" s="7">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="I42:I60" si="2">G42-H42</f>
         <v>660</v>
       </c>
       <c r="J42" s="7" t="s">
+        <v>2267</v>
+      </c>
+      <c r="K42" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L42" s="7" t="s">
         <v>2268</v>
-      </c>
-      <c r="K42" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="L42" s="7" t="s">
-        <v>2267</v>
       </c>
     </row>
     <row r="43" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -30830,13 +31282,13 @@
         <v>18</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>2333</v>
+        <v>2365</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>2334</v>
+        <v>2366</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>2364</v>
+        <v>2367</v>
       </c>
       <c r="F43" s="3" t="s">
         <v>46</v>
@@ -30848,7 +31300,7 @@
         <v>25</v>
       </c>
       <c r="I43" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>850</v>
       </c>
       <c r="J43" s="3" t="s">
@@ -30858,7 +31310,7 @@
         <v>24</v>
       </c>
       <c r="L43" s="3" t="s">
-        <v>2267</v>
+        <v>2268</v>
       </c>
     </row>
     <row r="44" spans="2:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -30866,13 +31318,13 @@
         <v>18</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>2335</v>
+        <v>2368</v>
       </c>
       <c r="D44" s="7" t="s">
-        <v>2378</v>
+        <v>2369</v>
       </c>
       <c r="E44" s="7" t="s">
-        <v>2336</v>
+        <v>2370</v>
       </c>
       <c r="F44" s="7" t="s">
         <v>2189</v>
@@ -30884,17 +31336,17 @@
         <v>30</v>
       </c>
       <c r="I44" s="7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1640</v>
       </c>
       <c r="J44" s="7" t="s">
+        <v>2267</v>
+      </c>
+      <c r="K44" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L44" s="7" t="s">
         <v>2268</v>
-      </c>
-      <c r="K44" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="L44" s="7" t="s">
-        <v>2267</v>
       </c>
     </row>
     <row r="45" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -30902,13 +31354,13 @@
         <v>18</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>2337</v>
+        <v>2371</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>2338</v>
+        <v>2372</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>2339</v>
+        <v>2373</v>
       </c>
       <c r="F45" s="3" t="s">
         <v>88</v>
@@ -30920,7 +31372,7 @@
         <v>25</v>
       </c>
       <c r="I45" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1530</v>
       </c>
       <c r="J45" s="3" t="s">
@@ -30930,7 +31382,7 @@
         <v>24</v>
       </c>
       <c r="L45" s="3" t="s">
-        <v>2267</v>
+        <v>2268</v>
       </c>
     </row>
     <row r="46" spans="2:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -30938,16 +31390,16 @@
         <v>18</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>2340</v>
+        <v>2374</v>
       </c>
       <c r="D46" s="7" t="s">
-        <v>2341</v>
+        <v>2375</v>
       </c>
       <c r="E46" s="7" t="s">
-        <v>2342</v>
+        <v>2376</v>
       </c>
       <c r="F46" s="7" t="s">
-        <v>2328</v>
+        <v>2359</v>
       </c>
       <c r="G46" s="7">
         <v>0</v>
@@ -30956,17 +31408,17 @@
         <v>25</v>
       </c>
       <c r="I46" s="7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-25</v>
       </c>
       <c r="J46" s="7" t="s">
+        <v>2267</v>
+      </c>
+      <c r="K46" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L46" s="7" t="s">
         <v>2268</v>
-      </c>
-      <c r="K46" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="L46" s="7" t="s">
-        <v>2267</v>
       </c>
     </row>
     <row r="47" spans="2:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -30974,13 +31426,13 @@
         <v>18</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>2343</v>
+        <v>2377</v>
       </c>
       <c r="D47" s="7" t="s">
-        <v>2344</v>
+        <v>2378</v>
       </c>
       <c r="E47" s="7" t="s">
-        <v>2388</v>
+        <v>2379</v>
       </c>
       <c r="F47" s="7" t="s">
         <v>208</v>
@@ -30992,17 +31444,17 @@
         <v>25</v>
       </c>
       <c r="I47" s="7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>660</v>
       </c>
       <c r="J47" s="7" t="s">
+        <v>2267</v>
+      </c>
+      <c r="K47" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L47" s="7" t="s">
         <v>2268</v>
-      </c>
-      <c r="K47" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="L47" s="7" t="s">
-        <v>2267</v>
       </c>
     </row>
     <row r="48" spans="2:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -31016,7 +31468,7 @@
         <v>2381</v>
       </c>
       <c r="E48" s="7" t="s">
-        <v>2345</v>
+        <v>2382</v>
       </c>
       <c r="F48" s="7" t="s">
         <v>2187</v>
@@ -31028,17 +31480,17 @@
         <v>30</v>
       </c>
       <c r="I48" s="7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1500</v>
       </c>
       <c r="J48" s="7" t="s">
+        <v>2267</v>
+      </c>
+      <c r="K48" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L48" s="7" t="s">
         <v>2268</v>
-      </c>
-      <c r="K48" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="L48" s="7" t="s">
-        <v>2267</v>
       </c>
     </row>
     <row r="49" spans="1:12" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -31046,13 +31498,13 @@
         <v>18</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>2346</v>
+        <v>2383</v>
       </c>
       <c r="D49" s="7" t="s">
-        <v>2347</v>
+        <v>2384</v>
       </c>
       <c r="E49" s="7" t="s">
-        <v>2394</v>
+        <v>2385</v>
       </c>
       <c r="F49" s="7" t="s">
         <v>2189</v>
@@ -31064,17 +31516,17 @@
         <v>35</v>
       </c>
       <c r="I49" s="7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-35</v>
       </c>
       <c r="J49" s="7" t="s">
+        <v>2267</v>
+      </c>
+      <c r="K49" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L49" s="7" t="s">
         <v>2268</v>
-      </c>
-      <c r="K49" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="L49" s="7" t="s">
-        <v>2267</v>
       </c>
     </row>
     <row r="50" spans="1:12" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -31085,7 +31537,7 @@
         <v>894</v>
       </c>
       <c r="D50" s="7" t="s">
-        <v>2348</v>
+        <v>2386</v>
       </c>
       <c r="E50" s="7" t="s">
         <v>896</v>
@@ -31100,17 +31552,17 @@
         <v>25</v>
       </c>
       <c r="I50" s="7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>890</v>
       </c>
       <c r="J50" s="7" t="s">
+        <v>2267</v>
+      </c>
+      <c r="K50" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L50" s="7" t="s">
         <v>2268</v>
-      </c>
-      <c r="K50" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="L50" s="7" t="s">
-        <v>2267</v>
       </c>
     </row>
     <row r="51" spans="1:12" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -31118,13 +31570,13 @@
         <v>18</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>2349</v>
+        <v>2387</v>
       </c>
       <c r="D51" s="7" t="s">
-        <v>2350</v>
+        <v>2388</v>
       </c>
       <c r="E51" s="7" t="s">
-        <v>2379</v>
+        <v>2389</v>
       </c>
       <c r="F51" s="8">
         <v>11</v>
@@ -31136,17 +31588,17 @@
         <v>25</v>
       </c>
       <c r="I51" s="7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>830</v>
       </c>
       <c r="J51" s="7" t="s">
+        <v>2267</v>
+      </c>
+      <c r="K51" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L51" s="7" t="s">
         <v>2268</v>
-      </c>
-      <c r="K51" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="L51" s="7" t="s">
-        <v>2267</v>
       </c>
     </row>
     <row r="52" spans="1:12" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -31154,13 +31606,13 @@
         <v>18</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>2351</v>
+        <v>2390</v>
       </c>
       <c r="D52" s="7" t="s">
-        <v>2352</v>
+        <v>2391</v>
       </c>
       <c r="E52" s="7" t="s">
-        <v>2398</v>
+        <v>2392</v>
       </c>
       <c r="F52" s="7" t="s">
         <v>2187</v>
@@ -31172,17 +31624,17 @@
         <v>30</v>
       </c>
       <c r="I52" s="7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1830</v>
       </c>
       <c r="J52" s="7" t="s">
+        <v>2267</v>
+      </c>
+      <c r="K52" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L52" s="7" t="s">
         <v>2268</v>
-      </c>
-      <c r="K52" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="L52" s="7" t="s">
-        <v>2267</v>
       </c>
     </row>
     <row r="53" spans="1:12" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -31190,10 +31642,10 @@
         <v>18</v>
       </c>
       <c r="C53" s="7" t="s">
-        <v>2353</v>
+        <v>2393</v>
       </c>
       <c r="D53" s="7" t="s">
-        <v>2395</v>
+        <v>2394</v>
       </c>
       <c r="E53" s="7" t="s">
         <v>698</v>
@@ -31208,17 +31660,17 @@
         <v>25</v>
       </c>
       <c r="I53" s="7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>660</v>
       </c>
       <c r="J53" s="7" t="s">
+        <v>2267</v>
+      </c>
+      <c r="K53" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L53" s="7" t="s">
         <v>2268</v>
-      </c>
-      <c r="K53" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="L53" s="7" t="s">
-        <v>2267</v>
       </c>
     </row>
     <row r="54" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -31226,13 +31678,13 @@
         <v>18</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>2354</v>
+        <v>2395</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>2366</v>
+        <v>2396</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>2367</v>
+        <v>2397</v>
       </c>
       <c r="F54" s="3" t="s">
         <v>38</v>
@@ -31244,7 +31696,7 @@
         <v>20</v>
       </c>
       <c r="I54" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>670</v>
       </c>
       <c r="J54" s="3" t="s">
@@ -31254,7 +31706,7 @@
         <v>24</v>
       </c>
       <c r="L54" s="3" t="s">
-        <v>2267</v>
+        <v>2268</v>
       </c>
     </row>
     <row r="55" spans="1:12" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -31262,10 +31714,10 @@
         <v>18</v>
       </c>
       <c r="C55" s="7" t="s">
-        <v>2396</v>
+        <v>2398</v>
       </c>
       <c r="D55" s="7" t="s">
-        <v>2355</v>
+        <v>2399</v>
       </c>
       <c r="E55" s="7" t="s">
         <v>1866</v>
@@ -31280,17 +31732,17 @@
         <v>25</v>
       </c>
       <c r="I55" s="7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>660</v>
       </c>
       <c r="J55" s="7" t="s">
+        <v>2267</v>
+      </c>
+      <c r="K55" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L55" s="7" t="s">
         <v>2268</v>
-      </c>
-      <c r="K55" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="L55" s="7" t="s">
-        <v>2267</v>
       </c>
     </row>
     <row r="56" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -31298,13 +31750,13 @@
         <v>18</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>2356</v>
+        <v>2400</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>2357</v>
+        <v>2401</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>2368</v>
+        <v>2402</v>
       </c>
       <c r="F56" s="3" t="s">
         <v>116</v>
@@ -31316,7 +31768,7 @@
         <v>30</v>
       </c>
       <c r="I56" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>450</v>
       </c>
       <c r="J56" s="3" t="s">
@@ -31326,7 +31778,7 @@
         <v>24</v>
       </c>
       <c r="L56" s="3" t="s">
-        <v>2267</v>
+        <v>2268</v>
       </c>
     </row>
     <row r="57" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -31337,10 +31789,10 @@
         <v>18</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>2371</v>
+        <v>2403</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>2370</v>
+        <v>2404</v>
       </c>
       <c r="F57" s="3" t="s">
         <v>88</v>
@@ -31352,7 +31804,7 @@
         <v>30</v>
       </c>
       <c r="I57" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="J57" s="3" t="s">
@@ -31362,7 +31814,7 @@
         <v>24</v>
       </c>
       <c r="L57" s="3" t="s">
-        <v>2267</v>
+        <v>2268</v>
       </c>
     </row>
     <row r="58" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -31373,7 +31825,7 @@
         <v>18</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>2358</v>
+        <v>2405</v>
       </c>
       <c r="E58" s="3" t="s">
         <v>1730</v>
@@ -31388,7 +31840,7 @@
         <v>35</v>
       </c>
       <c r="I58" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-35</v>
       </c>
       <c r="J58" s="3" t="s">
@@ -31398,7 +31850,7 @@
         <v>24</v>
       </c>
       <c r="L58" s="3" t="s">
-        <v>2267</v>
+        <v>2268</v>
       </c>
     </row>
     <row r="59" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -31412,7 +31864,7 @@
         <v>1761</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>2373</v>
+        <v>2406</v>
       </c>
       <c r="F59" s="3" t="s">
         <v>38</v>
@@ -31424,7 +31876,7 @@
         <v>25</v>
       </c>
       <c r="I59" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>250</v>
       </c>
       <c r="J59" s="3" t="s">
@@ -31434,7 +31886,7 @@
         <v>24</v>
       </c>
       <c r="L59" s="3" t="s">
-        <v>2267</v>
+        <v>2268</v>
       </c>
     </row>
     <row r="60" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -31460,17 +31912,2418 @@
         <v>30</v>
       </c>
       <c r="I60" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J60" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K60" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L60" s="3" t="s">
+        <v>2268</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1400-000000000000}">
+  <dimension ref="A1:P66"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="27.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="75.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.7109375" customWidth="1"/>
+    <col min="12" max="12" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="19.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B1" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2407</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>2408</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>2409</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>2410</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>2187</v>
+      </c>
+      <c r="G3" s="7">
+        <v>0</v>
+      </c>
+      <c r="H3" s="7">
+        <v>30</v>
+      </c>
+      <c r="I3" s="7">
+        <f t="shared" ref="I3:I34" si="0">G3-H3</f>
+        <v>-30</v>
+      </c>
+      <c r="J3" s="7" t="s">
+        <v>2411</v>
+      </c>
+      <c r="K3" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L3" s="7" t="s">
+        <v>2412</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>2413</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>2414</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>2549</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>2238</v>
+      </c>
+      <c r="G4" s="7">
+        <v>690</v>
+      </c>
+      <c r="H4" s="7">
+        <v>30</v>
+      </c>
+      <c r="I4" s="7">
+        <f t="shared" si="0"/>
+        <v>660</v>
+      </c>
+      <c r="J4" s="7" t="s">
+        <v>2411</v>
+      </c>
+      <c r="K4" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L4" s="7" t="s">
+        <v>2412</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>2415</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>2416</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>2521</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="G5" s="3">
+        <v>0</v>
+      </c>
+      <c r="H5" s="3">
+        <v>20</v>
+      </c>
+      <c r="I5" s="3">
+        <f t="shared" si="0"/>
+        <v>-20</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>2412</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>2200</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>2417</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>2418</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="G6" s="3">
+        <v>30</v>
+      </c>
+      <c r="H6" s="3">
+        <v>30</v>
+      </c>
+      <c r="I6" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L6" s="3" t="s">
+        <v>2412</v>
+      </c>
+      <c r="M6" s="3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>2419</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>2420</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>2519</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="G7" s="3">
+        <v>810</v>
+      </c>
+      <c r="H7" s="3">
+        <v>20</v>
+      </c>
+      <c r="I7" s="3">
+        <f t="shared" si="0"/>
+        <v>790</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L7" s="3" t="s">
+        <v>2412</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>1219</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>2421</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>1221</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G8" s="7">
+        <v>0</v>
+      </c>
+      <c r="H8" s="7">
+        <v>30</v>
+      </c>
+      <c r="I8" s="7">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J8" s="7" t="s">
+        <v>2411</v>
+      </c>
+      <c r="K8" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L8" s="7" t="s">
+        <v>2412</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>2422</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>2423</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>718</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>2137</v>
+      </c>
+      <c r="G9" s="3">
+        <v>815</v>
+      </c>
+      <c r="H9" s="3">
+        <v>25</v>
+      </c>
+      <c r="I9" s="3">
+        <f t="shared" si="0"/>
+        <v>790</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L9" s="3" t="s">
+        <v>2412</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>2424</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>2425</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>2426</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G10" s="7">
+        <v>820</v>
+      </c>
+      <c r="H10" s="7">
+        <v>30</v>
+      </c>
+      <c r="I10" s="7">
+        <f t="shared" si="0"/>
+        <v>790</v>
+      </c>
+      <c r="J10" s="7" t="s">
+        <v>2411</v>
+      </c>
+      <c r="K10" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L10" s="7" t="s">
+        <v>2412</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>1429</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>2427</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>1431</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>2187</v>
+      </c>
+      <c r="G11" s="7">
+        <v>950</v>
+      </c>
+      <c r="H11" s="7">
+        <v>30</v>
+      </c>
+      <c r="I11" s="7">
+        <f t="shared" si="0"/>
+        <v>920</v>
+      </c>
+      <c r="J11" s="7" t="s">
+        <v>2411</v>
+      </c>
+      <c r="K11" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L11" s="7" t="s">
+        <v>2412</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>678</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>2428</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>2539</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>2196</v>
+      </c>
+      <c r="G12" s="7">
+        <v>715</v>
+      </c>
+      <c r="H12" s="7">
+        <v>25</v>
+      </c>
+      <c r="I12" s="7">
+        <f t="shared" si="0"/>
+        <v>690</v>
+      </c>
+      <c r="J12" s="7" t="s">
+        <v>2411</v>
+      </c>
+      <c r="K12" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L12" s="7" t="s">
+        <v>2412</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>2429</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>2430</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>2526</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="G13" s="3">
+        <v>1795</v>
+      </c>
+      <c r="H13" s="3">
+        <v>25</v>
+      </c>
+      <c r="I13" s="3">
+        <f t="shared" si="0"/>
+        <v>1770</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K13" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L13" s="3" t="s">
+        <v>2412</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>2431</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>2432</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>2433</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>2137</v>
+      </c>
+      <c r="G14" s="3">
+        <v>2050</v>
+      </c>
+      <c r="H14" s="3">
+        <v>25</v>
+      </c>
+      <c r="I14" s="3">
+        <f t="shared" si="0"/>
+        <v>2025</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>2412</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>2434</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>2435</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>2436</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>2238</v>
+      </c>
+      <c r="G15" s="7">
+        <v>600</v>
+      </c>
+      <c r="H15" s="7">
+        <v>30</v>
+      </c>
+      <c r="I15" s="7">
+        <f t="shared" si="0"/>
+        <v>570</v>
+      </c>
+      <c r="J15" s="7" t="s">
+        <v>2411</v>
+      </c>
+      <c r="K15" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L15" s="7" t="s">
+        <v>2412</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>2437</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>909</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="G16" s="3">
+        <v>1215</v>
+      </c>
+      <c r="H16" s="3">
+        <v>25</v>
+      </c>
+      <c r="I16" s="3">
+        <f t="shared" si="0"/>
+        <v>1190</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K16" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L16" s="3" t="s">
+        <v>2412</v>
+      </c>
+    </row>
+    <row r="17" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>2438</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>2439</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>2528</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>2133</v>
+      </c>
+      <c r="G17" s="3">
+        <v>0</v>
+      </c>
+      <c r="H17" s="3">
+        <v>30</v>
+      </c>
+      <c r="I17" s="3">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L17" s="3" t="s">
+        <v>2412</v>
+      </c>
+    </row>
+    <row r="18" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>894</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>2440</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>896</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="G18" s="3">
+        <v>1345</v>
+      </c>
+      <c r="H18" s="3">
+        <v>25</v>
+      </c>
+      <c r="I18" s="3">
+        <f t="shared" si="0"/>
+        <v>1320</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L18" s="3" t="s">
+        <v>2412</v>
+      </c>
+    </row>
+    <row r="19" spans="2:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>2398</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>2441</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>1866</v>
+      </c>
+      <c r="F19" s="7" t="s">
+        <v>2137</v>
+      </c>
+      <c r="G19" s="7">
+        <v>765</v>
+      </c>
+      <c r="H19" s="7">
+        <v>25</v>
+      </c>
+      <c r="I19" s="7">
+        <f t="shared" si="0"/>
+        <v>740</v>
+      </c>
+      <c r="J19" s="7" t="s">
+        <v>2411</v>
+      </c>
+      <c r="K19" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L19" s="7" t="s">
+        <v>2412</v>
+      </c>
+    </row>
+    <row r="20" spans="2:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>2442</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>2443</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>2534</v>
+      </c>
+      <c r="F20" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="G20" s="7">
+        <v>865</v>
+      </c>
+      <c r="H20" s="7">
+        <v>25</v>
+      </c>
+      <c r="I20" s="7">
+        <f t="shared" si="0"/>
+        <v>840</v>
+      </c>
+      <c r="J20" s="7" t="s">
+        <v>2411</v>
+      </c>
+      <c r="K20" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L20" s="7" t="s">
+        <v>2412</v>
+      </c>
+    </row>
+    <row r="21" spans="2:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>2444</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>2445</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>2543</v>
+      </c>
+      <c r="F21" s="7" t="s">
+        <v>2238</v>
+      </c>
+      <c r="G21" s="7">
+        <v>720</v>
+      </c>
+      <c r="H21" s="7">
+        <v>30</v>
+      </c>
+      <c r="I21" s="7">
+        <f t="shared" si="0"/>
+        <v>690</v>
+      </c>
+      <c r="J21" s="7" t="s">
+        <v>2411</v>
+      </c>
+      <c r="K21" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L21" s="7" t="s">
+        <v>2412</v>
+      </c>
+    </row>
+    <row r="22" spans="2:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>2446</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>2447</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>2535</v>
+      </c>
+      <c r="F22" s="7" t="s">
+        <v>2196</v>
+      </c>
+      <c r="G22" s="7">
+        <v>0</v>
+      </c>
+      <c r="H22" s="7">
+        <v>25</v>
+      </c>
+      <c r="I22" s="7">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J22" s="7" t="s">
+        <v>2411</v>
+      </c>
+      <c r="K22" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L22" s="7" t="s">
+        <v>2412</v>
+      </c>
+    </row>
+    <row r="23" spans="2:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>2448</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>2449</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>971</v>
+      </c>
+      <c r="F23" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="G23" s="7">
+        <v>0</v>
+      </c>
+      <c r="H23" s="7">
+        <v>25</v>
+      </c>
+      <c r="I23" s="7">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J23" s="7" t="s">
+        <v>2411</v>
+      </c>
+      <c r="K23" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L23" s="7" t="s">
+        <v>2412</v>
+      </c>
+    </row>
+    <row r="24" spans="2:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>1481</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>2450</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>1483</v>
+      </c>
+      <c r="F24" s="7" t="s">
+        <v>2137</v>
+      </c>
+      <c r="G24" s="7">
+        <v>775</v>
+      </c>
+      <c r="H24" s="7">
+        <v>25</v>
+      </c>
+      <c r="I24" s="7">
+        <f t="shared" si="0"/>
+        <v>750</v>
+      </c>
+      <c r="J24" s="7" t="s">
+        <v>2411</v>
+      </c>
+      <c r="K24" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L24" s="7" t="s">
+        <v>2412</v>
+      </c>
+    </row>
+    <row r="25" spans="2:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>2451</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>2452</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>2544</v>
+      </c>
+      <c r="F25" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="G25" s="7">
+        <v>695</v>
+      </c>
+      <c r="H25" s="7">
+        <v>35</v>
+      </c>
+      <c r="I25" s="7">
+        <f t="shared" si="0"/>
+        <v>660</v>
+      </c>
+      <c r="J25" s="7" t="s">
+        <v>2411</v>
+      </c>
+      <c r="K25" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L25" s="7" t="s">
+        <v>2412</v>
+      </c>
+    </row>
+    <row r="26" spans="2:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>2453</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>2454</v>
+      </c>
+      <c r="E26" s="7" t="s">
+        <v>2532</v>
+      </c>
+      <c r="F26" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="G26" s="7">
+        <v>0</v>
+      </c>
+      <c r="H26" s="7">
+        <v>0</v>
+      </c>
+      <c r="I26" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J26" s="7" t="s">
+        <v>2411</v>
+      </c>
+      <c r="K26" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L26" s="7" t="s">
+        <v>2412</v>
+      </c>
+      <c r="M26" s="7" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="27" spans="2:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>2455</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>2456</v>
+      </c>
+      <c r="E27" s="7" t="s">
+        <v>2545</v>
+      </c>
+      <c r="F27" s="7" t="s">
+        <v>2196</v>
+      </c>
+      <c r="G27" s="7">
+        <v>815</v>
+      </c>
+      <c r="H27" s="7">
+        <v>25</v>
+      </c>
+      <c r="I27" s="7">
+        <f t="shared" si="0"/>
+        <v>790</v>
+      </c>
+      <c r="J27" s="7" t="s">
+        <v>2411</v>
+      </c>
+      <c r="K27" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L27" s="7" t="s">
+        <v>2412</v>
+      </c>
+    </row>
+    <row r="28" spans="2:13" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>1683</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>2457</v>
+      </c>
+      <c r="E28" s="5" t="s">
+        <v>1685</v>
+      </c>
+      <c r="F28" s="5" t="s">
+        <v>2144</v>
+      </c>
+      <c r="G28" s="5">
+        <v>0</v>
+      </c>
+      <c r="H28" s="5">
+        <v>30</v>
+      </c>
+      <c r="I28" s="5">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J28" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="K28" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L28" s="5" t="s">
+        <v>2412</v>
+      </c>
+    </row>
+    <row r="29" spans="2:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>2540</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>2458</v>
+      </c>
+      <c r="E29" s="7" t="s">
+        <v>2459</v>
+      </c>
+      <c r="F29" s="7" t="s">
+        <v>2460</v>
+      </c>
+      <c r="G29" s="7">
+        <v>685</v>
+      </c>
+      <c r="H29" s="7">
+        <v>25</v>
+      </c>
+      <c r="I29" s="7">
+        <f t="shared" si="0"/>
+        <v>660</v>
+      </c>
+      <c r="J29" s="7" t="s">
+        <v>2411</v>
+      </c>
+      <c r="K29" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L29" s="7" t="s">
+        <v>2412</v>
+      </c>
+    </row>
+    <row r="30" spans="2:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C30" s="7" t="s">
+        <v>2461</v>
+      </c>
+      <c r="D30" s="7" t="s">
+        <v>2462</v>
+      </c>
+      <c r="E30" s="7" t="s">
+        <v>2533</v>
+      </c>
+      <c r="F30" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="G30" s="7">
+        <v>1635</v>
+      </c>
+      <c r="H30" s="7">
+        <v>25</v>
+      </c>
+      <c r="I30" s="7">
+        <f t="shared" si="0"/>
+        <v>1610</v>
+      </c>
+      <c r="J30" s="7" t="s">
+        <v>2411</v>
+      </c>
+      <c r="K30" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L30" s="7" t="s">
+        <v>2412</v>
+      </c>
+      <c r="M30" s="7" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="31" spans="2:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B31" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>2536</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>2537</v>
+      </c>
+      <c r="E31" s="7" t="s">
+        <v>2538</v>
+      </c>
+      <c r="F31" s="8">
+        <v>12</v>
+      </c>
+      <c r="G31" s="7">
+        <v>980</v>
+      </c>
+      <c r="H31" s="7">
+        <v>30</v>
+      </c>
+      <c r="I31" s="7">
+        <f t="shared" si="0"/>
+        <v>950</v>
+      </c>
+      <c r="J31" s="7" t="s">
+        <v>2411</v>
+      </c>
+      <c r="K31" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L31" s="7" t="s">
+        <v>2412</v>
+      </c>
+    </row>
+    <row r="32" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B32" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>2464</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="G32" s="3">
+        <v>710</v>
+      </c>
+      <c r="H32" s="3">
+        <v>20</v>
+      </c>
+      <c r="I32" s="3">
+        <f t="shared" si="0"/>
+        <v>690</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K32" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L32" s="3" t="s">
+        <v>2412</v>
+      </c>
+    </row>
+    <row r="33" spans="2:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B33" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>2465</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>2466</v>
+      </c>
+      <c r="E33" s="7" t="s">
+        <v>2467</v>
+      </c>
+      <c r="F33" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G33" s="7">
+        <v>820</v>
+      </c>
+      <c r="H33" s="7">
+        <v>30</v>
+      </c>
+      <c r="I33" s="7">
+        <f t="shared" si="0"/>
+        <v>790</v>
+      </c>
+      <c r="J33" s="7" t="s">
+        <v>2411</v>
+      </c>
+      <c r="K33" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L33" s="7" t="s">
+        <v>2412</v>
+      </c>
+    </row>
+    <row r="34" spans="2:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B34" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C34" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D34" s="7" t="s">
+        <v>2468</v>
+      </c>
+      <c r="E34" s="7" t="s">
+        <v>1203</v>
+      </c>
+      <c r="F34" s="7" t="s">
+        <v>2187</v>
+      </c>
+      <c r="G34" s="7">
+        <v>1090</v>
+      </c>
+      <c r="H34" s="7">
+        <v>30</v>
+      </c>
+      <c r="I34" s="7">
+        <f t="shared" si="0"/>
+        <v>1060</v>
+      </c>
+      <c r="J34" s="7" t="s">
+        <v>2411</v>
+      </c>
+      <c r="K34" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L34" s="7" t="s">
+        <v>2412</v>
+      </c>
+    </row>
+    <row r="35" spans="2:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B35" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>2469</v>
+      </c>
+      <c r="D35" s="7" t="s">
+        <v>2470</v>
+      </c>
+      <c r="E35" s="7" t="s">
+        <v>2471</v>
+      </c>
+      <c r="F35" s="7" t="s">
+        <v>2137</v>
+      </c>
+      <c r="G35" s="7">
+        <v>815</v>
+      </c>
+      <c r="H35" s="7">
+        <v>25</v>
+      </c>
+      <c r="I35" s="7">
+        <f t="shared" ref="I35:I63" si="1">G35-H35</f>
+        <v>790</v>
+      </c>
+      <c r="J35" s="7" t="s">
+        <v>2411</v>
+      </c>
+      <c r="K35" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L35" s="7" t="s">
+        <v>2412</v>
+      </c>
+    </row>
+    <row r="36" spans="2:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B36" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C36" s="7" t="s">
+        <v>2472</v>
+      </c>
+      <c r="D36" s="7" t="s">
+        <v>2473</v>
+      </c>
+      <c r="E36" s="7" t="s">
+        <v>2550</v>
+      </c>
+      <c r="F36" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="G36" s="7">
+        <v>985</v>
+      </c>
+      <c r="H36" s="7">
+        <v>35</v>
+      </c>
+      <c r="I36" s="7">
+        <f t="shared" si="1"/>
+        <v>950</v>
+      </c>
+      <c r="J36" s="7" t="s">
+        <v>2411</v>
+      </c>
+      <c r="K36" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L36" s="7" t="s">
+        <v>2412</v>
+      </c>
+    </row>
+    <row r="37" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B37" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>1519</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>2474</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>2475</v>
+      </c>
+      <c r="F37" s="4" t="s">
+        <v>2133</v>
+      </c>
+      <c r="G37" s="3">
+        <v>920</v>
+      </c>
+      <c r="H37" s="3">
+        <v>30</v>
+      </c>
+      <c r="I37" s="3">
+        <f t="shared" si="1"/>
+        <v>890</v>
+      </c>
+      <c r="J37" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K37" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L37" s="3" t="s">
+        <v>2412</v>
+      </c>
+    </row>
+    <row r="38" spans="2:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B38" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C38" s="7" t="s">
+        <v>2453</v>
+      </c>
+      <c r="D38" s="7" t="s">
+        <v>2476</v>
+      </c>
+      <c r="E38" s="7" t="s">
+        <v>2532</v>
+      </c>
+      <c r="F38" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="G38" s="7">
+        <v>0</v>
+      </c>
+      <c r="H38" s="7">
+        <v>35</v>
+      </c>
+      <c r="I38" s="7">
+        <f t="shared" si="1"/>
+        <v>-35</v>
+      </c>
+      <c r="J38" s="7" t="s">
+        <v>2411</v>
+      </c>
+      <c r="K38" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L38" s="7" t="s">
+        <v>2412</v>
+      </c>
+      <c r="M38" s="7" t="s">
+        <v>2553</v>
+      </c>
+    </row>
+    <row r="39" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B39" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>2477</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>2478</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>2527</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="G39" s="3">
+        <v>865</v>
+      </c>
+      <c r="H39" s="3">
+        <v>25</v>
+      </c>
+      <c r="I39" s="3">
+        <f t="shared" si="1"/>
+        <v>840</v>
+      </c>
+      <c r="J39" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K39" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L39" s="3" t="s">
+        <v>2412</v>
+      </c>
+    </row>
+    <row r="40" spans="2:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B40" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C40" s="7" t="s">
+        <v>2479</v>
+      </c>
+      <c r="D40" s="7" t="s">
+        <v>2480</v>
+      </c>
+      <c r="E40" s="7" t="s">
+        <v>2541</v>
+      </c>
+      <c r="F40" s="7" t="s">
+        <v>2187</v>
+      </c>
+      <c r="G40" s="7">
+        <v>720</v>
+      </c>
+      <c r="H40" s="7">
+        <v>30</v>
+      </c>
+      <c r="I40" s="7">
+        <f t="shared" si="1"/>
+        <v>690</v>
+      </c>
+      <c r="J40" s="7" t="s">
+        <v>2411</v>
+      </c>
+      <c r="K40" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L40" s="7" t="s">
+        <v>2412</v>
+      </c>
+    </row>
+    <row r="41" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B41" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>593</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>2481</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>595</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="G41" s="3">
+        <v>1835</v>
+      </c>
+      <c r="H41" s="3">
+        <v>25</v>
+      </c>
+      <c r="I41" s="3">
+        <f t="shared" si="1"/>
+        <v>1810</v>
+      </c>
+      <c r="J41" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K41" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L41" s="3" t="s">
+        <v>2412</v>
+      </c>
+    </row>
+    <row r="42" spans="2:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B42" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C42" s="7" t="s">
+        <v>900</v>
+      </c>
+      <c r="D42" s="7" t="s">
+        <v>2482</v>
+      </c>
+      <c r="E42" s="7" t="s">
+        <v>902</v>
+      </c>
+      <c r="F42" s="7" t="s">
+        <v>2137</v>
+      </c>
+      <c r="G42" s="7">
+        <v>0</v>
+      </c>
+      <c r="H42" s="7">
+        <v>25</v>
+      </c>
+      <c r="I42" s="7">
+        <f t="shared" si="1"/>
+        <v>-25</v>
+      </c>
+      <c r="J42" s="7" t="s">
+        <v>2411</v>
+      </c>
+      <c r="K42" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L42" s="7" t="s">
+        <v>2412</v>
+      </c>
+      <c r="M42" s="7" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="43" spans="2:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B43" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C43" s="7" t="s">
+        <v>2483</v>
+      </c>
+      <c r="D43" s="7" t="s">
+        <v>2484</v>
+      </c>
+      <c r="E43" s="7" t="s">
+        <v>2542</v>
+      </c>
+      <c r="F43" s="7" t="s">
+        <v>2187</v>
+      </c>
+      <c r="G43" s="7">
+        <v>870</v>
+      </c>
+      <c r="H43" s="7">
+        <v>30</v>
+      </c>
+      <c r="I43" s="7">
+        <f t="shared" si="1"/>
+        <v>840</v>
+      </c>
+      <c r="J43" s="7" t="s">
+        <v>2411</v>
+      </c>
+      <c r="K43" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L43" s="7" t="s">
+        <v>2412</v>
+      </c>
+    </row>
+    <row r="44" spans="2:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B44" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C44" s="7" t="s">
+        <v>271</v>
+      </c>
+      <c r="D44" s="7" t="s">
+        <v>2485</v>
+      </c>
+      <c r="E44" s="7" t="s">
+        <v>273</v>
+      </c>
+      <c r="F44" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="G44" s="7">
+        <v>885</v>
+      </c>
+      <c r="H44" s="7">
+        <v>35</v>
+      </c>
+      <c r="I44" s="7">
+        <f t="shared" si="1"/>
+        <v>850</v>
+      </c>
+      <c r="J44" s="7" t="s">
+        <v>2411</v>
+      </c>
+      <c r="K44" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L44" s="7" t="s">
+        <v>2412</v>
+      </c>
+    </row>
+    <row r="45" spans="2:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B45" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C45" s="7" t="s">
+        <v>1411</v>
+      </c>
+      <c r="D45" s="7" t="s">
+        <v>2486</v>
+      </c>
+      <c r="E45" s="7" t="s">
+        <v>2487</v>
+      </c>
+      <c r="F45" s="7" t="s">
+        <v>2187</v>
+      </c>
+      <c r="G45" s="7">
+        <v>1610</v>
+      </c>
+      <c r="H45" s="7">
+        <v>30</v>
+      </c>
+      <c r="I45" s="7">
+        <f t="shared" si="1"/>
+        <v>1580</v>
+      </c>
+      <c r="J45" s="7" t="s">
+        <v>2411</v>
+      </c>
+      <c r="K45" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L45" s="7" t="s">
+        <v>2412</v>
+      </c>
+    </row>
+    <row r="46" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B46" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>2488</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>2489</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>2490</v>
+      </c>
+      <c r="F46" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="G46" s="3">
+        <v>715</v>
+      </c>
+      <c r="H46" s="3">
+        <v>25</v>
+      </c>
+      <c r="I46" s="3">
+        <f t="shared" si="1"/>
+        <v>690</v>
+      </c>
+      <c r="J46" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K46" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L46" s="3" t="s">
+        <v>2412</v>
+      </c>
+    </row>
+    <row r="47" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B47" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>2491</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>2492</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>2493</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="G47" s="3">
+        <v>680</v>
+      </c>
+      <c r="H47" s="3">
+        <v>20</v>
+      </c>
+      <c r="I47" s="3">
+        <f t="shared" si="1"/>
+        <v>660</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K47" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L47" s="3" t="s">
+        <v>2412</v>
+      </c>
+    </row>
+    <row r="48" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B48" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>2522</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>2494</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>2523</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="G48" s="3">
+        <v>0</v>
+      </c>
+      <c r="H48" s="3">
+        <v>25</v>
+      </c>
+      <c r="I48" s="3">
+        <f t="shared" si="1"/>
+        <v>-25</v>
+      </c>
+      <c r="J48" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K48" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L48" s="3" t="s">
+        <v>2412</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B49" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C49" s="7" t="s">
+        <v>2495</v>
+      </c>
+      <c r="D49" s="7" t="s">
+        <v>2496</v>
+      </c>
+      <c r="E49" s="7" t="s">
+        <v>2497</v>
+      </c>
+      <c r="F49" s="8" t="s">
+        <v>2242</v>
+      </c>
+      <c r="G49" s="7">
+        <v>815</v>
+      </c>
+      <c r="H49" s="7">
+        <v>25</v>
+      </c>
+      <c r="I49" s="7">
+        <f t="shared" si="1"/>
+        <v>790</v>
+      </c>
+      <c r="J49" s="7" t="s">
+        <v>2411</v>
+      </c>
+      <c r="K49" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L49" s="7" t="s">
+        <v>2412</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B50" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>2498</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>2499</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>2520</v>
+      </c>
+      <c r="F50" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="G50" s="3">
+        <v>710</v>
+      </c>
+      <c r="H50" s="3">
+        <v>20</v>
+      </c>
+      <c r="I50" s="3">
+        <f t="shared" si="1"/>
+        <v>690</v>
+      </c>
+      <c r="J50" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K50" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L50" s="3" t="s">
+        <v>2412</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B51" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C51" s="7" t="s">
+        <v>2461</v>
+      </c>
+      <c r="D51" s="7" t="s">
+        <v>2500</v>
+      </c>
+      <c r="E51" s="7" t="s">
+        <v>2463</v>
+      </c>
+      <c r="F51" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="G51" s="7">
+        <v>0</v>
+      </c>
+      <c r="H51" s="7">
+        <v>0</v>
+      </c>
+      <c r="I51" s="7">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J60" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="K60" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="L60" s="3" t="s">
-        <v>2267</v>
+      <c r="J51" s="7" t="s">
+        <v>2411</v>
+      </c>
+      <c r="K51" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L51" s="7" t="s">
+        <v>2412</v>
+      </c>
+      <c r="M51" s="7" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B52" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>2501</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>2502</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>2503</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="G52" s="3">
+        <v>1145</v>
+      </c>
+      <c r="H52" s="3">
+        <v>25</v>
+      </c>
+      <c r="I52" s="3">
+        <f t="shared" si="1"/>
+        <v>1120</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K52" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L52" s="3" t="s">
+        <v>2412</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B53" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C53" s="7" t="s">
+        <v>2504</v>
+      </c>
+      <c r="D53" s="7" t="s">
+        <v>2505</v>
+      </c>
+      <c r="E53" s="7" t="s">
+        <v>2506</v>
+      </c>
+      <c r="F53" s="7" t="s">
+        <v>2187</v>
+      </c>
+      <c r="G53" s="7">
+        <v>1610</v>
+      </c>
+      <c r="H53" s="7">
+        <v>30</v>
+      </c>
+      <c r="I53" s="7">
+        <f t="shared" si="1"/>
+        <v>1580</v>
+      </c>
+      <c r="J53" s="7" t="s">
+        <v>2411</v>
+      </c>
+      <c r="K53" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L53" s="7" t="s">
+        <v>2412</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B54" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C54" s="7" t="s">
+        <v>2507</v>
+      </c>
+      <c r="D54" s="7" t="s">
+        <v>2508</v>
+      </c>
+      <c r="E54" s="7" t="s">
+        <v>2509</v>
+      </c>
+      <c r="F54" s="7" t="s">
+        <v>2137</v>
+      </c>
+      <c r="G54" s="7">
+        <v>0</v>
+      </c>
+      <c r="H54" s="7">
+        <v>25</v>
+      </c>
+      <c r="I54" s="7">
+        <f t="shared" si="1"/>
+        <v>-25</v>
+      </c>
+      <c r="J54" s="7" t="s">
+        <v>2411</v>
+      </c>
+      <c r="K54" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L54" s="7" t="s">
+        <v>2412</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B55" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>1689</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>2510</v>
+      </c>
+      <c r="E55" s="3" t="s">
+        <v>1454</v>
+      </c>
+      <c r="F55" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="G55" s="3">
+        <v>765</v>
+      </c>
+      <c r="H55" s="3">
+        <v>25</v>
+      </c>
+      <c r="I55" s="3">
+        <f t="shared" si="1"/>
+        <v>740</v>
+      </c>
+      <c r="J55" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K55" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L55" s="3" t="s">
+        <v>2412</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B56" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>2511</v>
+      </c>
+      <c r="E56" s="3" t="s">
+        <v>2531</v>
+      </c>
+      <c r="F56" s="3" t="s">
+        <v>2133</v>
+      </c>
+      <c r="G56" s="3">
+        <v>1460</v>
+      </c>
+      <c r="H56" s="3">
+        <v>30</v>
+      </c>
+      <c r="I56" s="3">
+        <f t="shared" si="1"/>
+        <v>1430</v>
+      </c>
+      <c r="J56" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K56" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L56" s="3" t="s">
+        <v>2412</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B57" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>1599</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>2512</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>2524</v>
+      </c>
+      <c r="F57" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="G57" s="3">
+        <v>680</v>
+      </c>
+      <c r="H57" s="3">
+        <v>20</v>
+      </c>
+      <c r="I57" s="3">
+        <f t="shared" si="1"/>
+        <v>660</v>
+      </c>
+      <c r="J57" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K57" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L57" s="3" t="s">
+        <v>2412</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B58" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C58" s="7" t="s">
+        <v>1834</v>
+      </c>
+      <c r="D58" s="7" t="s">
+        <v>2513</v>
+      </c>
+      <c r="E58" s="7" t="s">
+        <v>1836</v>
+      </c>
+      <c r="F58" s="7" t="s">
+        <v>2187</v>
+      </c>
+      <c r="G58" s="7">
+        <v>150</v>
+      </c>
+      <c r="H58" s="7">
+        <v>30</v>
+      </c>
+      <c r="I58" s="7">
+        <f t="shared" si="1"/>
+        <v>120</v>
+      </c>
+      <c r="J58" s="7" t="s">
+        <v>2411</v>
+      </c>
+      <c r="K58" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L58" s="7" t="s">
+        <v>2412</v>
+      </c>
+      <c r="M58" s="7" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B59" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C59" s="7" t="s">
+        <v>2514</v>
+      </c>
+      <c r="D59" s="7" t="s">
+        <v>2515</v>
+      </c>
+      <c r="E59" s="7" t="s">
+        <v>2548</v>
+      </c>
+      <c r="F59" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G59" s="7">
+        <v>840</v>
+      </c>
+      <c r="H59" s="7">
+        <v>30</v>
+      </c>
+      <c r="I59" s="7">
+        <f t="shared" si="1"/>
+        <v>810</v>
+      </c>
+      <c r="J59" s="7" t="s">
+        <v>2411</v>
+      </c>
+      <c r="K59" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L59" s="7" t="s">
+        <v>2412</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B60" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C60" s="7" t="s">
+        <v>2516</v>
+      </c>
+      <c r="D60" s="7" t="s">
+        <v>2551</v>
+      </c>
+      <c r="E60" s="7" t="s">
+        <v>2552</v>
+      </c>
+      <c r="F60" s="7" t="s">
+        <v>2238</v>
+      </c>
+      <c r="G60" s="7">
+        <v>0</v>
+      </c>
+      <c r="H60" s="7">
+        <v>25</v>
+      </c>
+      <c r="I60" s="7">
+        <f t="shared" si="1"/>
+        <v>-25</v>
+      </c>
+      <c r="J60" s="7" t="s">
+        <v>2411</v>
+      </c>
+      <c r="K60" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L60" s="7" t="s">
+        <v>2412</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B61" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>2517</v>
+      </c>
+      <c r="E61" s="3" t="s">
+        <v>2525</v>
+      </c>
+      <c r="F61" s="3" t="s">
+        <v>2133</v>
+      </c>
+      <c r="G61" s="3">
+        <v>1050</v>
+      </c>
+      <c r="H61" s="3">
+        <v>30</v>
+      </c>
+      <c r="I61" s="3">
+        <f t="shared" si="1"/>
+        <v>1020</v>
+      </c>
+      <c r="J61" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K61" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L61" s="3" t="s">
+        <v>2412</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B62" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C62" s="7" t="s">
+        <v>2546</v>
+      </c>
+      <c r="D62" s="7" t="s">
+        <v>2518</v>
+      </c>
+      <c r="E62" s="7" t="s">
+        <v>2547</v>
+      </c>
+      <c r="F62" s="7" t="s">
+        <v>2196</v>
+      </c>
+      <c r="G62" s="7">
+        <v>2410</v>
+      </c>
+      <c r="H62" s="7">
+        <v>25</v>
+      </c>
+      <c r="I62" s="7">
+        <f t="shared" si="1"/>
+        <v>2385</v>
+      </c>
+      <c r="J62" s="7" t="s">
+        <v>2156</v>
+      </c>
+      <c r="K62" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L62" s="7" t="s">
+        <v>2412</v>
+      </c>
+      <c r="M62" s="7" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>640</v>
+      </c>
+      <c r="E63" s="3" t="s">
+        <v>1275</v>
+      </c>
+      <c r="F63" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="G63" s="3">
+        <v>7240</v>
+      </c>
+      <c r="H63" s="3">
+        <v>45</v>
+      </c>
+      <c r="I63" s="3">
+        <f t="shared" si="1"/>
+        <v>7195</v>
+      </c>
+      <c r="J63" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K63" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L63" s="3" t="s">
+        <v>2412</v>
+      </c>
+      <c r="M63" s="3" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>1656</v>
+      </c>
+      <c r="E64" s="3" t="s">
+        <v>1657</v>
+      </c>
+      <c r="F64" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="G64" s="3">
+        <v>40</v>
+      </c>
+      <c r="H64" s="3">
+        <v>40</v>
+      </c>
+      <c r="I64" s="3">
+        <f t="shared" ref="I64" si="2">G64-H64</f>
+        <v>0</v>
+      </c>
+      <c r="J64" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K64" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L64" s="3" t="s">
+        <v>2412</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12" s="36" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="36" t="s">
+        <v>85</v>
+      </c>
+      <c r="B65" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="C65" s="36" t="s">
+        <v>2529</v>
+      </c>
+      <c r="E65" s="36" t="s">
+        <v>2530</v>
+      </c>
+      <c r="I65" s="36">
+        <f t="shared" ref="I65:I66" si="3">G65-H65</f>
+        <v>0</v>
+      </c>
+      <c r="J65" s="36" t="s">
+        <v>24</v>
+      </c>
+      <c r="K65" s="36" t="s">
+        <v>24</v>
+      </c>
+      <c r="L65" s="36" t="s">
+        <v>2412</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="B66" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C66" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="E66" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="F66" s="8" t="s">
+        <v>2230</v>
+      </c>
+      <c r="G66" s="7">
+        <v>0</v>
+      </c>
+      <c r="H66" s="7">
+        <v>30</v>
+      </c>
+      <c r="I66" s="7">
+        <f t="shared" si="3"/>
+        <v>-30</v>
+      </c>
+      <c r="J66" s="7" t="s">
+        <v>2156</v>
+      </c>
+      <c r="K66" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L66" s="7" t="s">
+        <v>2412</v>
       </c>
     </row>
   </sheetData>
@@ -32705,7 +35558,7 @@
         <v>25</v>
       </c>
       <c r="I35" s="3">
-        <f t="shared" ref="I35:I66" si="1">G35-H35</f>
+        <f t="shared" ref="I35:I52" si="1">G35-H35</f>
         <v>660</v>
       </c>
       <c r="J35" s="3" t="s">
@@ -36387,7 +39240,7 @@
         <v>25</v>
       </c>
       <c r="I35" s="12">
-        <f t="shared" ref="I35:I66" si="1">G35-H35</f>
+        <f t="shared" ref="I35:I53" si="1">G35-H35</f>
         <v>1610</v>
       </c>
       <c r="J35" s="3" t="s">
@@ -42817,7 +45670,7 @@
         <v>25</v>
       </c>
       <c r="I35" s="18">
-        <f t="shared" ref="I35:I66" si="1">G35-H35</f>
+        <f t="shared" ref="I35:I53" si="1">G35-H35</f>
         <v>1510</v>
       </c>
       <c r="J35" s="18" t="s">

--- a/data/Apr/Data.xlsx
+++ b/data/Apr/Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Freelance\TextInputter\data\Apr\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F482066E-E455-47D4-B642-74C4DC57EED2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1E36D81-E9C5-4D27-B3F1-4146E2CB238F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="6" activeTab="20" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="7" activeTab="21" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01-04" sheetId="4" r:id="rId1"/>
@@ -34,6 +34,7 @@
     <sheet name="22-04" sheetId="23" r:id="rId19"/>
     <sheet name="23-04" sheetId="24" r:id="rId20"/>
     <sheet name="24-04" sheetId="25" r:id="rId21"/>
+    <sheet name="25-04" sheetId="26" r:id="rId22"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -56,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7980" uniqueCount="2554">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8421" uniqueCount="2674">
   <si>
     <t>THU 4</t>
   </si>
@@ -7303,12 +7304,18 @@
     <t>HD015065</t>
   </si>
   <si>
+    <t>A22/5 phạm thế hiển p3</t>
+  </si>
+  <si>
     <t>Họ Yen</t>
   </si>
   <si>
     <t>HD014983</t>
   </si>
   <si>
+    <t>Toà Central 2, Vinhomes Central Park, số 208 Nguyễn Hữu Cảnh, phường 22</t>
+  </si>
+  <si>
     <t>HD015027</t>
   </si>
   <si>
@@ -7321,6 +7328,9 @@
     <t>HD015189</t>
   </si>
   <si>
+    <t>208 nguyễn hữu cảnh p22 - landmark 3</t>
+  </si>
+  <si>
     <t>HD015129</t>
   </si>
   <si>
@@ -7345,12 +7355,18 @@
     <t>HD014866</t>
   </si>
   <si>
+    <t>132 bến vân đồn p9</t>
+  </si>
+  <si>
     <t>Thơm Thơm</t>
   </si>
   <si>
     <t>HD015104</t>
   </si>
   <si>
+    <t>119 nguyễn văn công p. Hạnh Thông</t>
+  </si>
+  <si>
     <t>Tu Chi Tien</t>
   </si>
   <si>
@@ -7378,6 +7394,9 @@
     <t>HD014563</t>
   </si>
   <si>
+    <t>đường số 104 brillant tower 3 1206 cc đảo kim cương bình trưng tây</t>
+  </si>
+  <si>
     <t>HD015199</t>
   </si>
   <si>
@@ -7390,18 +7409,27 @@
     <t>HD015201</t>
   </si>
   <si>
+    <t>8/14 Trịnh Đình Thảo, Hoà Thạnh</t>
+  </si>
+  <si>
     <t>An Vi</t>
   </si>
   <si>
     <t>HD014867</t>
   </si>
   <si>
+    <t>139/1 dạ nam phường 3</t>
+  </si>
+  <si>
     <t>Hải Dương</t>
   </si>
   <si>
     <t>HD014950</t>
   </si>
   <si>
+    <t>Chung Cư số 1 Tôn Thất Thuyết Lô M1.613</t>
+  </si>
+  <si>
     <t>CUS19950/pe panhaketya</t>
   </si>
   <si>
@@ -7417,21 +7445,33 @@
     <t>HD015022</t>
   </si>
   <si>
+    <t>Sunrise lô D Nguyễn hữa thọ, Xã Phước Kiển</t>
+  </si>
+  <si>
     <t>Nguyen Thi Thu Trang</t>
   </si>
   <si>
     <t>HD014831</t>
   </si>
   <si>
+    <t>13 đường số 3, Khu dân cư phước kiển A, Lê Văn Lương</t>
+  </si>
+  <si>
     <t>bảo bảo fb Phương Phương</t>
   </si>
   <si>
     <t>HD015165</t>
   </si>
   <si>
+    <t>132 bến vân đồn p6</t>
+  </si>
+  <si>
     <t>HD015008</t>
   </si>
   <si>
+    <t>Thý An</t>
+  </si>
+  <si>
     <t>HD014870</t>
   </si>
   <si>
@@ -7447,120 +7487,156 @@
     <t>HD015267</t>
   </si>
   <si>
+    <t>179/13A hoà bình Phường Hiệp Tân</t>
+  </si>
+  <si>
+    <t>Xuân Phát tiktok @xuanphat94</t>
+  </si>
+  <si>
+    <t>HD015085</t>
+  </si>
+  <si>
+    <t>B214bis đường đông hưng thuận 1, phường đông hưng thuận</t>
+  </si>
+  <si>
+    <t>HD015068</t>
+  </si>
+  <si>
+    <t>Phương Quỳnh</t>
+  </si>
+  <si>
+    <t>HD014884</t>
+  </si>
+  <si>
+    <t>6D đường số 2B, Khu Phố 9, Bình Hưng Hòa A</t>
+  </si>
+  <si>
+    <t>HD014965</t>
+  </si>
+  <si>
+    <t>Hà Gia Mẫn</t>
+  </si>
+  <si>
+    <t>HD015024</t>
+  </si>
+  <si>
+    <t>Tk22/26 Nguyễn cảnh chân- cầu ông lãnh</t>
+  </si>
+  <si>
+    <t>Nhớ Nhớ</t>
+  </si>
+  <si>
+    <t>HD015170</t>
+  </si>
+  <si>
+    <t>Sài gòn Mia block A đường 9a khu trung sơn bình hưng</t>
+  </si>
+  <si>
+    <t>HD015010</t>
+  </si>
+  <si>
+    <t>The Sun Avenue S3-Mai Chí thọ</t>
+  </si>
+  <si>
+    <t>HD015082</t>
+  </si>
+  <si>
+    <t>gộp, kh ck shop 865k</t>
+  </si>
+  <si>
+    <t>Nhã Phương</t>
+  </si>
+  <si>
+    <t>HD015029</t>
+  </si>
+  <si>
+    <t>26/2 đường 59 p14</t>
+  </si>
+  <si>
+    <t>Tuyết Nhi</t>
+  </si>
+  <si>
+    <t>HD014894</t>
+  </si>
+  <si>
+    <t>Block d2, chung cư sài gòn riverside (số 4 đào trí, phú thuận)</t>
+  </si>
+  <si>
+    <t>HD014972</t>
+  </si>
+  <si>
+    <t>HD015158</t>
+  </si>
+  <si>
+    <t>Ngọc Phượng</t>
+  </si>
+  <si>
+    <t>HD014928</t>
+  </si>
+  <si>
+    <t>The grand midtown m5 đường số 16 p. Tân Phú</t>
+  </si>
+  <si>
+    <t>HD015089</t>
+  </si>
+  <si>
+    <t>HD014764</t>
+  </si>
+  <si>
+    <t>116a đường số 16 p tân quy</t>
+  </si>
+  <si>
+    <t>Thanh Hà Phạm</t>
+  </si>
+  <si>
+    <t>HD015051</t>
+  </si>
+  <si>
+    <t>29/15 yên thế, p2</t>
+  </si>
+  <si>
+    <t>Yen Nguyen</t>
+  </si>
+  <si>
+    <t>HD015181</t>
+  </si>
+  <si>
+    <t>92g nguyễn hữu cảnh, phường 22</t>
+  </si>
+  <si>
+    <t>fb Trang Nguyen</t>
+  </si>
+  <si>
+    <t>HD015080</t>
+  </si>
+  <si>
+    <t>452/ G33 Phan Văn trị phường 7 Công ty chuyển phát nhanh quốc tế Bm ViNa</t>
+  </si>
+  <si>
+    <t>Trang Nhung</t>
+  </si>
+  <si>
+    <t>HD015083</t>
+  </si>
+  <si>
+    <t>Chung cư Hà độ toà orchid 2</t>
+  </si>
+  <si>
+    <t>Nguyễn Hồng Nga</t>
+  </si>
+  <si>
+    <t>HD014904</t>
+  </si>
+  <si>
+    <t>104/12 Nguyễn Trọng Tuyển, P15</t>
+  </si>
+  <si>
+    <t>HD015264</t>
+  </si>
+  <si>
     <t>179/13A hoà bình</t>
   </si>
   <si>
-    <t>HD015068</t>
-  </si>
-  <si>
-    <t>Phương Quỳnh</t>
-  </si>
-  <si>
-    <t>HD014884</t>
-  </si>
-  <si>
-    <t>6D đường số 2B, Khu Phố 9, Bình Hưng Hòa A</t>
-  </si>
-  <si>
-    <t>HD014965</t>
-  </si>
-  <si>
-    <t>Hà Gia Mẫn</t>
-  </si>
-  <si>
-    <t>HD015024</t>
-  </si>
-  <si>
-    <t>Tk22/26 Nguyễn cảnh chân- cầu ông lãnh</t>
-  </si>
-  <si>
-    <t>Nhớ Nhớ</t>
-  </si>
-  <si>
-    <t>HD015170</t>
-  </si>
-  <si>
-    <t>HD015010</t>
-  </si>
-  <si>
-    <t>The Sun Avenue S3-Mai Chí thọ</t>
-  </si>
-  <si>
-    <t>HD015082</t>
-  </si>
-  <si>
-    <t>Nhã Phương</t>
-  </si>
-  <si>
-    <t>HD015029</t>
-  </si>
-  <si>
-    <t>Tuyết Nhi</t>
-  </si>
-  <si>
-    <t>HD014894</t>
-  </si>
-  <si>
-    <t>HD014972</t>
-  </si>
-  <si>
-    <t>HD015158</t>
-  </si>
-  <si>
-    <t>Ngọc Phượng</t>
-  </si>
-  <si>
-    <t>HD014928</t>
-  </si>
-  <si>
-    <t>HD015089</t>
-  </si>
-  <si>
-    <t>HD014764</t>
-  </si>
-  <si>
-    <t>116a đường số 16 p tân quy</t>
-  </si>
-  <si>
-    <t>Thanh Hà Phạm</t>
-  </si>
-  <si>
-    <t>HD015051</t>
-  </si>
-  <si>
-    <t>29/15 yên thế, p2</t>
-  </si>
-  <si>
-    <t>Yen Nguyen</t>
-  </si>
-  <si>
-    <t>HD015181</t>
-  </si>
-  <si>
-    <t>92g nguyễn hữu cảnh, phường 22</t>
-  </si>
-  <si>
-    <t>HD015080</t>
-  </si>
-  <si>
-    <t>Trang Nhung</t>
-  </si>
-  <si>
-    <t>HD015083</t>
-  </si>
-  <si>
-    <t>Chung cư Hà độ toà orchid 2</t>
-  </si>
-  <si>
-    <t>Nguyễn Hồng Nga</t>
-  </si>
-  <si>
-    <t>HD014904</t>
-  </si>
-  <si>
-    <t>HD015264</t>
-  </si>
-  <si>
     <t>Nguyễn Hương Giang</t>
   </si>
   <si>
@@ -7594,9 +7670,15 @@
     <t>HD014918</t>
   </si>
   <si>
+    <t>mai chí thọ phường an phú Cc lexington block B</t>
+  </si>
+  <si>
     <t>HD015247</t>
   </si>
   <si>
+    <t>82/17/20 đinh tiên hoàng p1</t>
+  </si>
+  <si>
     <t>HD015072</t>
   </si>
   <si>
@@ -7606,43 +7688,31 @@
     <t>HD015100</t>
   </si>
   <si>
+    <t>339 lê văn quới phường bình trị đông A</t>
+  </si>
+  <si>
     <t>Lê Thị Tuyết Trâm</t>
   </si>
   <si>
+    <t>HD014837</t>
+  </si>
+  <si>
+    <t>90/11 dương bá trạc phương rạch ông</t>
+  </si>
+  <si>
     <t>HD015167</t>
   </si>
   <si>
+    <t>chung cư terrace 21 võ trường toản</t>
+  </si>
+  <si>
+    <t>Nguyễn Thùy Vi</t>
+  </si>
+  <si>
     <t>HD015077</t>
   </si>
   <si>
-    <t>208 nguyễn hữu cảnh p22 - landmark 3</t>
-  </si>
-  <si>
-    <t>104/12 Nguyễn Trọng Tuyển, P15</t>
-  </si>
-  <si>
-    <t>Toà Central 2, Vinhomes Central Park, số 208 Nguyễn Hữu Cảnh, phường 22</t>
-  </si>
-  <si>
-    <t>fb Trang Nguyen</t>
-  </si>
-  <si>
-    <t>452/ G33 Phan Văn trị phường 7 Công ty chuyển phát nhanh quốc tế Bm ViNa</t>
-  </si>
-  <si>
-    <t>82/17/20 đinh tiên hoàng p1</t>
-  </si>
-  <si>
-    <t>chung cư terrace 21 võ trường toản</t>
-  </si>
-  <si>
-    <t>119 nguyễn văn công p. Hạnh Thông</t>
-  </si>
-  <si>
-    <t>26/2 đường 59 p14</t>
-  </si>
-  <si>
-    <t>đường số 104 brillant tower 3 1206 cc đảo kim cương bình trưng tây</t>
+    <t>The Tresor,39-39b bến vân đồn</t>
   </si>
   <si>
     <t>MINZZY</t>
@@ -7651,73 +7721,364 @@
     <t>XE TOÀN THẮNG</t>
   </si>
   <si>
-    <t>mai chí thọ phường an phú Cc lexington block B</t>
-  </si>
-  <si>
-    <t>13 đường số 3, Khu dân cư phước kiển A, Lê Văn Lương</t>
-  </si>
-  <si>
-    <t>179/13A hoà bình Phường Hiệp Tân</t>
-  </si>
-  <si>
-    <t>8/14 Trịnh Đình Thảo, Hoà Thạnh</t>
-  </si>
-  <si>
-    <t>Chung Cư số 1 Tôn Thất Thuyết Lô M1.613</t>
-  </si>
-  <si>
-    <t>Xuân Phát tiktok @xuanphat94</t>
-  </si>
-  <si>
-    <t>HD015085</t>
-  </si>
-  <si>
-    <t>B214bis đường đông hưng thuận 1, phường đông hưng thuận</t>
-  </si>
-  <si>
-    <t>132 bến vân đồn p9</t>
-  </si>
-  <si>
-    <t>Thý An</t>
-  </si>
-  <si>
-    <t>Block d2, chung cư sài gòn riverside (số 4 đào trí, phú thuận)</t>
-  </si>
-  <si>
-    <t>The grand midtown m5 đường số 16 p. Tân Phú</t>
-  </si>
-  <si>
-    <t>139/1 dạ nam phường 3</t>
-  </si>
-  <si>
-    <t>Sunrise lô D Nguyễn hữa thọ, Xã Phước Kiển</t>
-  </si>
-  <si>
-    <t>132 bến vân đồn p6</t>
-  </si>
-  <si>
-    <t>Nguyễn Thùy Vi</t>
-  </si>
-  <si>
-    <t>The Tresor,39-39b bến vân đồn</t>
-  </si>
-  <si>
-    <t>339 lê văn quới phường bình trị đông A</t>
-  </si>
-  <si>
-    <t>A22/5 phạm thế hiển p3</t>
-  </si>
-  <si>
-    <t>Sài gòn Mia block A đường 9a khu trung sơn bình hưng</t>
-  </si>
-  <si>
-    <t>HD014837</t>
-  </si>
-  <si>
-    <t>90/11 dương bá trạc phương rạch ông</t>
-  </si>
-  <si>
-    <t>gộp, kh ck shop 865k</t>
+    <t>NGAY 25-4</t>
+  </si>
+  <si>
+    <t>HD015763</t>
+  </si>
+  <si>
+    <t>AT 25-04</t>
+  </si>
+  <si>
+    <t>25-04-2026</t>
+  </si>
+  <si>
+    <t>HD015672</t>
+  </si>
+  <si>
+    <t>Loan Tran</t>
+  </si>
+  <si>
+    <t>HD015680</t>
+  </si>
+  <si>
+    <t>Hằng Nguyễn</t>
+  </si>
+  <si>
+    <t>HD015363</t>
+  </si>
+  <si>
+    <t>HD015600</t>
+  </si>
+  <si>
+    <t>99 đương số 9 KDC bình hưng</t>
+  </si>
+  <si>
+    <t>HD015565</t>
+  </si>
+  <si>
+    <t>Lotus Tram</t>
+  </si>
+  <si>
+    <t>HD015505</t>
+  </si>
+  <si>
+    <t>HD015602</t>
+  </si>
+  <si>
+    <t>thu đuc</t>
+  </si>
+  <si>
+    <t>Nguyễn Hải Phụng</t>
+  </si>
+  <si>
+    <t>HD015693</t>
+  </si>
+  <si>
+    <t>Thuy Trang</t>
+  </si>
+  <si>
+    <t>HD015739</t>
+  </si>
+  <si>
+    <t>A3 Chung cư The Gold View 346 Bến Vân Đồn - P.1</t>
+  </si>
+  <si>
+    <t>HD015528</t>
+  </si>
+  <si>
+    <t>HD015502</t>
+  </si>
+  <si>
+    <t>HĐ015764</t>
+  </si>
+  <si>
+    <t>HD015726</t>
+  </si>
+  <si>
+    <t>HD015418</t>
+  </si>
+  <si>
+    <t>số 13 đường số 9, P13</t>
+  </si>
+  <si>
+    <t>HD015588</t>
+  </si>
+  <si>
+    <t>HD015392</t>
+  </si>
+  <si>
+    <t>MỸ HUYỀN - giữ đơn</t>
+  </si>
+  <si>
+    <t>HD014566</t>
+  </si>
+  <si>
+    <t>HD015574</t>
+  </si>
+  <si>
+    <t>Vũ Duy Tâm - fb Ngoc Nga</t>
+  </si>
+  <si>
+    <t>HD015761</t>
+  </si>
+  <si>
+    <t>HD015334</t>
+  </si>
+  <si>
+    <t>HD015581</t>
+  </si>
+  <si>
+    <t>HD015372</t>
+  </si>
+  <si>
+    <t>Nguyễn Kim Hồng</t>
+  </si>
+  <si>
+    <t>HD015760</t>
+  </si>
+  <si>
+    <t>Minh Trang</t>
+  </si>
+  <si>
+    <t>HD015370</t>
+  </si>
+  <si>
+    <t>Emily Le</t>
+  </si>
+  <si>
+    <t>HD015400</t>
+  </si>
+  <si>
+    <t>281/36 Lê Văn Sỹ P1</t>
+  </si>
+  <si>
+    <t>HD015483</t>
+  </si>
+  <si>
+    <t>Chung cư Hà đô toà orchid 2</t>
+  </si>
+  <si>
+    <t>HD015678</t>
+  </si>
+  <si>
+    <t>Lucie Huỳnh</t>
+  </si>
+  <si>
+    <t>HD015492</t>
+  </si>
+  <si>
+    <t>HD015705</t>
+  </si>
+  <si>
+    <t>Chan Vin</t>
+  </si>
+  <si>
+    <t>HD015702</t>
+  </si>
+  <si>
+    <t>LIBERTY CENTRAL SAIGON RIVERSIDE HOTEL - 17 Ton Duc Thang St</t>
+  </si>
+  <si>
+    <t>HD015571</t>
+  </si>
+  <si>
+    <t>336/43/5e nguyễn văn luôn p12</t>
+  </si>
+  <si>
+    <t>Ngân Hà</t>
+  </si>
+  <si>
+    <t>HD015652</t>
+  </si>
+  <si>
+    <t>Cc dream home 2, lô B, đường 59, p14</t>
+  </si>
+  <si>
+    <t>HD015424</t>
+  </si>
+  <si>
+    <t>Vân Vân</t>
+  </si>
+  <si>
+    <t>HD015567</t>
+  </si>
+  <si>
+    <t>86/36/3 phổ quang, tân sơn hòa</t>
+  </si>
+  <si>
+    <t>HD015527</t>
+  </si>
+  <si>
+    <t>Thuỷ Trúc</t>
+  </si>
+  <si>
+    <t>HD015561</t>
+  </si>
+  <si>
+    <t>Nguyễn Như Ý</t>
+  </si>
+  <si>
+    <t>HD015595</t>
+  </si>
+  <si>
+    <t>HD015736</t>
+  </si>
+  <si>
+    <t>Lê Ngọc Diễm</t>
+  </si>
+  <si>
+    <t>HD015562</t>
+  </si>
+  <si>
+    <t>HD015601</t>
+  </si>
+  <si>
+    <t>980/4b là gốm p8</t>
+  </si>
+  <si>
+    <t>Hoàng Thuý Liên</t>
+  </si>
+  <si>
+    <t>HD015756</t>
+  </si>
+  <si>
+    <t>119 hoàng diệu 2</t>
+  </si>
+  <si>
+    <t>HD015737</t>
+  </si>
+  <si>
+    <t>Dang Thuy Trang</t>
+  </si>
+  <si>
+    <t>Tòa landmark3, vinhome tân cang</t>
+  </si>
+  <si>
+    <t>Nguyễn Hoài An</t>
+  </si>
+  <si>
+    <t>HD015748</t>
+  </si>
+  <si>
+    <t>15 đặng thai mai p7</t>
+  </si>
+  <si>
+    <t>686 Tô Ngọc Vân, P. Tam Bình</t>
+  </si>
+  <si>
+    <t>685 Tân Sơn phường 12</t>
+  </si>
+  <si>
+    <t>Số 3, đường 37,khu dân cư vạn phúc?phường hiệp bình phước</t>
+  </si>
+  <si>
+    <t>29 Tran thi nghĩ p7</t>
+  </si>
+  <si>
+    <t>47 hiệp bình, hiệp bình chánh</t>
+  </si>
+  <si>
+    <t>107/189 Quang Trung P10</t>
+  </si>
+  <si>
+    <t>trâm fb Anne Ng</t>
+  </si>
+  <si>
+    <t>294/22/53 xô viết nghệ tinh,khu phố 21 phường thạnh mỹ tây</t>
+  </si>
+  <si>
+    <t>kh ck shop 685k</t>
+  </si>
+  <si>
+    <t>kh ck shop 730k</t>
+  </si>
+  <si>
+    <t>kh ck shop 1895k</t>
+  </si>
+  <si>
+    <t>tòa B chung cư 9 view phường phước long</t>
+  </si>
+  <si>
+    <t>36 bờ bao tận trắng P. Sơn Kỳ (chung cư celedon cổng diamond brilliant block B2)</t>
+  </si>
+  <si>
+    <t>Chung cư tara. Phường 6. Block B2 tòa khải hoàn</t>
+  </si>
+  <si>
+    <t>TRINH fb Nguyễn --oben</t>
+  </si>
+  <si>
+    <t>Ms Thuyên Tổ Như ari</t>
+  </si>
+  <si>
+    <t>HD015674</t>
+  </si>
+  <si>
+    <t>Chung cư starlight riverside phường bình phú</t>
+  </si>
+  <si>
+    <t>18/10 kdc bảo anh kp40 đường TL26 phường an phú đông</t>
+  </si>
+  <si>
+    <t>28/13 Trần Thiện Chánh p12</t>
+  </si>
+  <si>
+    <t>346 bến vân đồn, P1</t>
+  </si>
+  <si>
+    <t>290 an dương vương phường chợ quán</t>
+  </si>
+  <si>
+    <t>Chung Cư Diamond Brilliant Số 3 Đường N1 phường Tân Sơn Nhì Sảnh B1</t>
+  </si>
+  <si>
+    <t>A22/6 phạm thể hiển p3</t>
+  </si>
+  <si>
+    <t>206/26/10 Lê văn quới, kp4, bình trị đông</t>
+  </si>
+  <si>
+    <t>Eco green sài gòn, đường nguyễn văn linh, phường tân thuận tân Block B</t>
+  </si>
+  <si>
+    <t>Cc cardinal tower B Phường Tân Phú B908</t>
+  </si>
+  <si>
+    <t>NHƯ Ý LÊ</t>
+  </si>
+  <si>
+    <t>Chung cư Callagarden, kdc Greenlife 13C, Đ. Nguyễn Văn Linh, X. Phong Phú</t>
+  </si>
+  <si>
+    <t>YU MY</t>
+  </si>
+  <si>
+    <t>coca kẹ</t>
+  </si>
+  <si>
+    <t>HD015733</t>
+  </si>
+  <si>
+    <t>532/3/93 Kinh Dương Vương. Phường An Lạc</t>
+  </si>
+  <si>
+    <t>Thuy An Dao</t>
+  </si>
+  <si>
+    <t>Sảnh B2 chung cư Emerald phường Sơn Kỳ</t>
+  </si>
+  <si>
+    <t>17 Bùi Thế Mỹ P. Bảy Hiền</t>
+  </si>
+  <si>
+    <t>Thảo Quyên người nhận tên Thuỳ Minh</t>
+  </si>
+  <si>
+    <t>169 Kênh Trung Ương, Ấp 50, Xã Xuân Thới Thượng</t>
+  </si>
+  <si>
+    <t>HD015427</t>
   </si>
 </sst>
 </file>
@@ -31935,10 +32296,12 @@
   <dimension ref="A1:P66"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="1" max="2" width="9.140625" customWidth="1"/>
     <col min="3" max="3" width="27.5703125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9.5703125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="75.7109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.7109375" customWidth="1"/>
+    <col min="7" max="11" width="9.140625" customWidth="1"/>
     <col min="12" max="12" width="10.42578125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="19.140625" bestFit="1" customWidth="1"/>
   </cols>
@@ -32048,7 +32411,7 @@
         <v>2414</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>2549</v>
+        <v>2415</v>
       </c>
       <c r="F4" s="8" t="s">
         <v>2238</v>
@@ -32078,13 +32441,13 @@
         <v>18</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>2415</v>
+        <v>2416</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>2416</v>
+        <v>2417</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>2521</v>
+        <v>2418</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>38</v>
@@ -32117,10 +32480,10 @@
         <v>2200</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>2417</v>
+        <v>2419</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>2418</v>
+        <v>2420</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>116</v>
@@ -32153,13 +32516,13 @@
         <v>18</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>2419</v>
+        <v>2421</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>2420</v>
+        <v>2422</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>2519</v>
+        <v>2423</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>38</v>
@@ -32192,7 +32555,7 @@
         <v>1219</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>2421</v>
+        <v>2424</v>
       </c>
       <c r="E8" s="7" t="s">
         <v>1221</v>
@@ -32225,10 +32588,10 @@
         <v>18</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>2422</v>
+        <v>2425</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>2423</v>
+        <v>2426</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>718</v>
@@ -32261,13 +32624,13 @@
         <v>18</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>2424</v>
+        <v>2427</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>2425</v>
+        <v>2428</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>2426</v>
+        <v>2429</v>
       </c>
       <c r="F10" s="7" t="s">
         <v>22</v>
@@ -32300,7 +32663,7 @@
         <v>1429</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>2427</v>
+        <v>2430</v>
       </c>
       <c r="E11" s="7" t="s">
         <v>1431</v>
@@ -32336,10 +32699,10 @@
         <v>678</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>2428</v>
+        <v>2431</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>2539</v>
+        <v>2432</v>
       </c>
       <c r="F12" s="8" t="s">
         <v>2196</v>
@@ -32369,13 +32732,13 @@
         <v>18</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>2429</v>
+        <v>2433</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>2430</v>
+        <v>2434</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>2526</v>
+        <v>2435</v>
       </c>
       <c r="F13" s="3" t="s">
         <v>46</v>
@@ -32405,13 +32768,13 @@
         <v>18</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>2431</v>
+        <v>2436</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>2432</v>
+        <v>2437</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>2433</v>
+        <v>2438</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>2137</v>
@@ -32444,13 +32807,13 @@
         <v>18</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>2434</v>
+        <v>2439</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>2435</v>
+        <v>2440</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>2436</v>
+        <v>2441</v>
       </c>
       <c r="F15" s="7" t="s">
         <v>2238</v>
@@ -32483,7 +32846,7 @@
         <v>340</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>2437</v>
+        <v>2442</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>909</v>
@@ -32516,13 +32879,13 @@
         <v>18</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>2438</v>
+        <v>2443</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>2439</v>
+        <v>2444</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>2528</v>
+        <v>2445</v>
       </c>
       <c r="F17" s="4" t="s">
         <v>2133</v>
@@ -32555,7 +32918,7 @@
         <v>894</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>2440</v>
+        <v>2446</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>896</v>
@@ -32591,7 +32954,7 @@
         <v>2398</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>2441</v>
+        <v>2447</v>
       </c>
       <c r="E19" s="7" t="s">
         <v>1866</v>
@@ -32624,13 +32987,13 @@
         <v>18</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>2442</v>
+        <v>2448</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>2443</v>
+        <v>2449</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>2534</v>
+        <v>2450</v>
       </c>
       <c r="F20" s="7" t="s">
         <v>208</v>
@@ -32660,13 +33023,13 @@
         <v>18</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>2444</v>
+        <v>2451</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>2445</v>
+        <v>2452</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>2543</v>
+        <v>2453</v>
       </c>
       <c r="F21" s="7" t="s">
         <v>2238</v>
@@ -32696,13 +33059,13 @@
         <v>18</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>2446</v>
+        <v>2454</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>2447</v>
+        <v>2455</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>2535</v>
+        <v>2456</v>
       </c>
       <c r="F22" s="7" t="s">
         <v>2196</v>
@@ -32732,10 +33095,10 @@
         <v>18</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>2448</v>
+        <v>2457</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>2449</v>
+        <v>2458</v>
       </c>
       <c r="E23" s="7" t="s">
         <v>971</v>
@@ -32771,7 +33134,7 @@
         <v>1481</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>2450</v>
+        <v>2459</v>
       </c>
       <c r="E24" s="7" t="s">
         <v>1483</v>
@@ -32804,13 +33167,13 @@
         <v>18</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>2451</v>
+        <v>2460</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>2452</v>
+        <v>2461</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>2544</v>
+        <v>2462</v>
       </c>
       <c r="F25" s="7" t="s">
         <v>111</v>
@@ -32840,13 +33203,13 @@
         <v>18</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>2453</v>
+        <v>2463</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>2454</v>
+        <v>2464</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>2532</v>
+        <v>2465</v>
       </c>
       <c r="F26" s="7" t="s">
         <v>111</v>
@@ -32879,13 +33242,13 @@
         <v>18</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>2455</v>
+        <v>2466</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>2456</v>
+        <v>2467</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>2545</v>
+        <v>2468</v>
       </c>
       <c r="F27" s="7" t="s">
         <v>2196</v>
@@ -32918,7 +33281,7 @@
         <v>1683</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>2457</v>
+        <v>2469</v>
       </c>
       <c r="E28" s="5" t="s">
         <v>1685</v>
@@ -32951,16 +33314,16 @@
         <v>18</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>2540</v>
+        <v>2470</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>2458</v>
+        <v>2471</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>2459</v>
+        <v>2472</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>2460</v>
+        <v>2473</v>
       </c>
       <c r="G29" s="7">
         <v>685</v>
@@ -32987,13 +33350,13 @@
         <v>18</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>2461</v>
+        <v>2474</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>2462</v>
+        <v>2475</v>
       </c>
       <c r="E30" s="7" t="s">
-        <v>2533</v>
+        <v>2476</v>
       </c>
       <c r="F30" s="7" t="s">
         <v>208</v>
@@ -33026,13 +33389,13 @@
         <v>18</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>2536</v>
+        <v>2477</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>2537</v>
+        <v>2478</v>
       </c>
       <c r="E31" s="7" t="s">
-        <v>2538</v>
+        <v>2479</v>
       </c>
       <c r="F31" s="8">
         <v>12</v>
@@ -33065,7 +33428,7 @@
         <v>161</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>2464</v>
+        <v>2480</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>163</v>
@@ -33098,13 +33461,13 @@
         <v>18</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>2465</v>
+        <v>2481</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>2466</v>
+        <v>2482</v>
       </c>
       <c r="E33" s="7" t="s">
-        <v>2467</v>
+        <v>2483</v>
       </c>
       <c r="F33" s="7" t="s">
         <v>22</v>
@@ -33137,7 +33500,7 @@
         <v>65</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>2468</v>
+        <v>2484</v>
       </c>
       <c r="E34" s="7" t="s">
         <v>1203</v>
@@ -33170,13 +33533,13 @@
         <v>18</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>2469</v>
+        <v>2485</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>2470</v>
+        <v>2486</v>
       </c>
       <c r="E35" s="7" t="s">
-        <v>2471</v>
+        <v>2487</v>
       </c>
       <c r="F35" s="7" t="s">
         <v>2137</v>
@@ -33188,7 +33551,7 @@
         <v>25</v>
       </c>
       <c r="I35" s="7">
-        <f t="shared" ref="I35:I63" si="1">G35-H35</f>
+        <f t="shared" ref="I35:I66" si="1">G35-H35</f>
         <v>790</v>
       </c>
       <c r="J35" s="7" t="s">
@@ -33206,13 +33569,13 @@
         <v>18</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>2472</v>
+        <v>2488</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>2473</v>
+        <v>2489</v>
       </c>
       <c r="E36" s="7" t="s">
-        <v>2550</v>
+        <v>2490</v>
       </c>
       <c r="F36" s="7" t="s">
         <v>143</v>
@@ -33245,10 +33608,10 @@
         <v>1519</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>2474</v>
+        <v>2491</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>2475</v>
+        <v>2492</v>
       </c>
       <c r="F37" s="4" t="s">
         <v>2133</v>
@@ -33278,13 +33641,13 @@
         <v>18</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>2453</v>
+        <v>2463</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>2476</v>
+        <v>2493</v>
       </c>
       <c r="E38" s="7" t="s">
-        <v>2532</v>
+        <v>2465</v>
       </c>
       <c r="F38" s="7" t="s">
         <v>111</v>
@@ -33309,7 +33672,7 @@
         <v>2412</v>
       </c>
       <c r="M38" s="7" t="s">
-        <v>2553</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="39" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -33317,13 +33680,13 @@
         <v>18</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>2477</v>
+        <v>2495</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>2478</v>
+        <v>2496</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>2527</v>
+        <v>2497</v>
       </c>
       <c r="F39" s="3" t="s">
         <v>46</v>
@@ -33353,13 +33716,13 @@
         <v>18</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>2479</v>
+        <v>2498</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>2480</v>
+        <v>2499</v>
       </c>
       <c r="E40" s="7" t="s">
-        <v>2541</v>
+        <v>2500</v>
       </c>
       <c r="F40" s="7" t="s">
         <v>2187</v>
@@ -33392,7 +33755,7 @@
         <v>593</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>2481</v>
+        <v>2501</v>
       </c>
       <c r="E41" s="3" t="s">
         <v>595</v>
@@ -33428,7 +33791,7 @@
         <v>900</v>
       </c>
       <c r="D42" s="7" t="s">
-        <v>2482</v>
+        <v>2502</v>
       </c>
       <c r="E42" s="7" t="s">
         <v>902</v>
@@ -33464,13 +33827,13 @@
         <v>18</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>2483</v>
+        <v>2503</v>
       </c>
       <c r="D43" s="7" t="s">
-        <v>2484</v>
+        <v>2504</v>
       </c>
       <c r="E43" s="7" t="s">
-        <v>2542</v>
+        <v>2505</v>
       </c>
       <c r="F43" s="7" t="s">
         <v>2187</v>
@@ -33503,7 +33866,7 @@
         <v>271</v>
       </c>
       <c r="D44" s="7" t="s">
-        <v>2485</v>
+        <v>2506</v>
       </c>
       <c r="E44" s="7" t="s">
         <v>273</v>
@@ -33539,10 +33902,10 @@
         <v>1411</v>
       </c>
       <c r="D45" s="7" t="s">
-        <v>2486</v>
+        <v>2507</v>
       </c>
       <c r="E45" s="7" t="s">
-        <v>2487</v>
+        <v>2508</v>
       </c>
       <c r="F45" s="7" t="s">
         <v>2187</v>
@@ -33572,13 +33935,13 @@
         <v>18</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>2488</v>
+        <v>2509</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>2489</v>
+        <v>2510</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>2490</v>
+        <v>2511</v>
       </c>
       <c r="F46" s="3" t="s">
         <v>88</v>
@@ -33608,13 +33971,13 @@
         <v>18</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>2491</v>
+        <v>2512</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>2492</v>
+        <v>2513</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>2493</v>
+        <v>2514</v>
       </c>
       <c r="F47" s="3" t="s">
         <v>38</v>
@@ -33644,13 +34007,13 @@
         <v>18</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>2522</v>
+        <v>2515</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>2494</v>
+        <v>2516</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>2523</v>
+        <v>2517</v>
       </c>
       <c r="F48" s="3" t="s">
         <v>46</v>
@@ -33680,13 +34043,13 @@
         <v>18</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>2495</v>
+        <v>2518</v>
       </c>
       <c r="D49" s="7" t="s">
-        <v>2496</v>
+        <v>2519</v>
       </c>
       <c r="E49" s="7" t="s">
-        <v>2497</v>
+        <v>2520</v>
       </c>
       <c r="F49" s="8" t="s">
         <v>2242</v>
@@ -33716,13 +34079,13 @@
         <v>18</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>2498</v>
+        <v>2521</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>2499</v>
+        <v>2522</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>2520</v>
+        <v>2523</v>
       </c>
       <c r="F50" s="3" t="s">
         <v>81</v>
@@ -33752,13 +34115,13 @@
         <v>18</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>2461</v>
+        <v>2474</v>
       </c>
       <c r="D51" s="7" t="s">
-        <v>2500</v>
+        <v>2524</v>
       </c>
       <c r="E51" s="7" t="s">
-        <v>2463</v>
+        <v>2525</v>
       </c>
       <c r="F51" s="7" t="s">
         <v>208</v>
@@ -33791,13 +34154,13 @@
         <v>18</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>2501</v>
+        <v>2526</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>2502</v>
+        <v>2527</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>2503</v>
+        <v>2528</v>
       </c>
       <c r="F52" s="3" t="s">
         <v>46</v>
@@ -33827,13 +34190,13 @@
         <v>18</v>
       </c>
       <c r="C53" s="7" t="s">
-        <v>2504</v>
+        <v>2529</v>
       </c>
       <c r="D53" s="7" t="s">
-        <v>2505</v>
+        <v>2530</v>
       </c>
       <c r="E53" s="7" t="s">
-        <v>2506</v>
+        <v>2531</v>
       </c>
       <c r="F53" s="7" t="s">
         <v>2187</v>
@@ -33863,13 +34226,13 @@
         <v>18</v>
       </c>
       <c r="C54" s="7" t="s">
-        <v>2507</v>
+        <v>2532</v>
       </c>
       <c r="D54" s="7" t="s">
-        <v>2508</v>
+        <v>2533</v>
       </c>
       <c r="E54" s="7" t="s">
-        <v>2509</v>
+        <v>2534</v>
       </c>
       <c r="F54" s="7" t="s">
         <v>2137</v>
@@ -33902,7 +34265,7 @@
         <v>1689</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>2510</v>
+        <v>2535</v>
       </c>
       <c r="E55" s="3" t="s">
         <v>1454</v>
@@ -33938,10 +34301,10 @@
         <v>216</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>2511</v>
+        <v>2536</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>2531</v>
+        <v>2537</v>
       </c>
       <c r="F56" s="3" t="s">
         <v>2133</v>
@@ -33974,10 +34337,10 @@
         <v>1599</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>2512</v>
+        <v>2538</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>2524</v>
+        <v>2539</v>
       </c>
       <c r="F57" s="3" t="s">
         <v>38</v>
@@ -34010,7 +34373,7 @@
         <v>1834</v>
       </c>
       <c r="D58" s="7" t="s">
-        <v>2513</v>
+        <v>2540</v>
       </c>
       <c r="E58" s="7" t="s">
         <v>1836</v>
@@ -34046,13 +34409,13 @@
         <v>18</v>
       </c>
       <c r="C59" s="7" t="s">
-        <v>2514</v>
+        <v>2541</v>
       </c>
       <c r="D59" s="7" t="s">
-        <v>2515</v>
+        <v>2542</v>
       </c>
       <c r="E59" s="7" t="s">
-        <v>2548</v>
+        <v>2543</v>
       </c>
       <c r="F59" s="7" t="s">
         <v>22</v>
@@ -34082,13 +34445,13 @@
         <v>18</v>
       </c>
       <c r="C60" s="7" t="s">
-        <v>2516</v>
+        <v>2544</v>
       </c>
       <c r="D60" s="7" t="s">
-        <v>2551</v>
+        <v>2545</v>
       </c>
       <c r="E60" s="7" t="s">
-        <v>2552</v>
+        <v>2546</v>
       </c>
       <c r="F60" s="7" t="s">
         <v>2238</v>
@@ -34121,10 +34484,10 @@
         <v>140</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>2517</v>
+        <v>2547</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>2525</v>
+        <v>2548</v>
       </c>
       <c r="F61" s="3" t="s">
         <v>2133</v>
@@ -34154,13 +34517,13 @@
         <v>18</v>
       </c>
       <c r="C62" s="7" t="s">
-        <v>2546</v>
+        <v>2549</v>
       </c>
       <c r="D62" s="7" t="s">
-        <v>2518</v>
+        <v>2550</v>
       </c>
       <c r="E62" s="7" t="s">
-        <v>2547</v>
+        <v>2551</v>
       </c>
       <c r="F62" s="7" t="s">
         <v>2196</v>
@@ -34250,7 +34613,7 @@
         <v>40</v>
       </c>
       <c r="I64" s="3">
-        <f t="shared" ref="I64" si="2">G64-H64</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J64" s="3" t="s">
@@ -34271,13 +34634,13 @@
         <v>18</v>
       </c>
       <c r="C65" s="36" t="s">
-        <v>2529</v>
+        <v>2552</v>
       </c>
       <c r="E65" s="36" t="s">
-        <v>2530</v>
+        <v>2553</v>
       </c>
       <c r="I65" s="36">
-        <f t="shared" ref="I65:I66" si="3">G65-H65</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J65" s="36" t="s">
@@ -34313,7 +34676,7 @@
         <v>30</v>
       </c>
       <c r="I66" s="7">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>-30</v>
       </c>
       <c r="J66" s="7" t="s">
@@ -34324,6 +34687,1963 @@
       </c>
       <c r="L66" s="7" t="s">
         <v>2412</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1500-000000000000}">
+  <dimension ref="A1:P53"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="36.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="80" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B1" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2554</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>750</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>2555</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>752</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>2230</v>
+      </c>
+      <c r="G3" s="7">
+        <v>785</v>
+      </c>
+      <c r="H3" s="7">
+        <v>25</v>
+      </c>
+      <c r="I3" s="7">
+        <f t="shared" ref="I3:I35" si="0">G3-H3</f>
+        <v>760</v>
+      </c>
+      <c r="J3" s="7" t="s">
+        <v>2556</v>
+      </c>
+      <c r="K3" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L3" s="7" t="s">
+        <v>2557</v>
+      </c>
+      <c r="M3" s="7" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>2668</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>2558</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>2669</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="G4" s="7">
+        <v>775</v>
+      </c>
+      <c r="H4" s="7">
+        <v>25</v>
+      </c>
+      <c r="I4" s="7">
+        <f t="shared" si="0"/>
+        <v>750</v>
+      </c>
+      <c r="J4" s="7" t="s">
+        <v>2556</v>
+      </c>
+      <c r="K4" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L4" s="7" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>2559</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>2560</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>2657</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="G5" s="7">
+        <v>375</v>
+      </c>
+      <c r="H5" s="7">
+        <v>25</v>
+      </c>
+      <c r="I5" s="7">
+        <f t="shared" si="0"/>
+        <v>350</v>
+      </c>
+      <c r="J5" s="7" t="s">
+        <v>2556</v>
+      </c>
+      <c r="K5" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L5" s="7" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>2561</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>2562</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>2635</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="G6" s="3">
+        <v>690</v>
+      </c>
+      <c r="H6" s="3">
+        <v>30</v>
+      </c>
+      <c r="I6" s="3">
+        <f t="shared" si="0"/>
+        <v>660</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L6" s="3" t="s">
+        <v>2557</v>
+      </c>
+      <c r="M6" s="3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>2585</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>2659</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G7" s="7">
+        <v>750</v>
+      </c>
+      <c r="H7" s="7">
+        <v>30</v>
+      </c>
+      <c r="I7" s="7">
+        <f t="shared" ref="I7" si="1">G7-H7</f>
+        <v>720</v>
+      </c>
+      <c r="J7" s="7" t="s">
+        <v>2556</v>
+      </c>
+      <c r="K7" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L7" s="7" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>2664</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>2563</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>2564</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="G8" s="7">
+        <v>775</v>
+      </c>
+      <c r="H8" s="7">
+        <v>35</v>
+      </c>
+      <c r="I8" s="7">
+        <f t="shared" si="0"/>
+        <v>740</v>
+      </c>
+      <c r="J8" s="7" t="s">
+        <v>2556</v>
+      </c>
+      <c r="K8" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L8" s="7" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>952</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>2565</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>2638</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="G9" s="3">
+        <v>0</v>
+      </c>
+      <c r="H9" s="3">
+        <v>25</v>
+      </c>
+      <c r="I9" s="3">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L9" s="3" t="s">
+        <v>2557</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>2643</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>2566</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>2567</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>2637</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="G10" s="3">
+        <v>820</v>
+      </c>
+      <c r="H10" s="3">
+        <v>30</v>
+      </c>
+      <c r="I10" s="3">
+        <f t="shared" si="0"/>
+        <v>790</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L10" s="3" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>699</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>2568</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>2653</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>2189</v>
+      </c>
+      <c r="G11" s="7">
+        <v>690</v>
+      </c>
+      <c r="H11" s="7">
+        <v>30</v>
+      </c>
+      <c r="I11" s="7">
+        <f t="shared" si="0"/>
+        <v>660</v>
+      </c>
+      <c r="J11" s="7" t="s">
+        <v>2556</v>
+      </c>
+      <c r="K11" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L11" s="7" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>2570</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>2571</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>2647</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="G12" s="7">
+        <v>1455</v>
+      </c>
+      <c r="H12" s="7">
+        <v>25</v>
+      </c>
+      <c r="I12" s="7">
+        <f t="shared" si="0"/>
+        <v>1430</v>
+      </c>
+      <c r="J12" s="7" t="s">
+        <v>2556</v>
+      </c>
+      <c r="K12" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L12" s="7" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>2572</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>2573</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>2574</v>
+      </c>
+      <c r="F13" s="8" t="s">
+        <v>2196</v>
+      </c>
+      <c r="G13" s="7">
+        <v>0</v>
+      </c>
+      <c r="H13" s="7">
+        <v>25</v>
+      </c>
+      <c r="I13" s="7">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J13" s="7" t="s">
+        <v>2556</v>
+      </c>
+      <c r="K13" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L13" s="7" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>1142</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>2575</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>1781</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>2187</v>
+      </c>
+      <c r="G14" s="7">
+        <v>0</v>
+      </c>
+      <c r="H14" s="7">
+        <v>30</v>
+      </c>
+      <c r="I14" s="7">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J14" s="7" t="s">
+        <v>2556</v>
+      </c>
+      <c r="K14" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L14" s="7" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>2004</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>2576</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>2646</v>
+      </c>
+      <c r="F15" s="6" t="s">
+        <v>2144</v>
+      </c>
+      <c r="G15" s="5">
+        <v>0</v>
+      </c>
+      <c r="H15" s="5">
+        <v>30</v>
+      </c>
+      <c r="I15" s="5">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J15" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="K15" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L15" s="5" t="s">
+        <v>2557</v>
+      </c>
+      <c r="M15" s="5" t="s">
+        <v>2644</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>687</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>2577</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>2639</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="G16" s="3">
+        <v>770</v>
+      </c>
+      <c r="H16" s="3">
+        <v>30</v>
+      </c>
+      <c r="I16" s="3">
+        <f t="shared" si="0"/>
+        <v>740</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K16" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L16" s="3" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="17" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>2630</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>2578</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>2631</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="G17" s="3">
+        <v>550</v>
+      </c>
+      <c r="H17" s="3">
+        <v>20</v>
+      </c>
+      <c r="I17" s="3">
+        <f t="shared" si="0"/>
+        <v>530</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L17" s="3" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="18" spans="2:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>2662</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>2579</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>2580</v>
+      </c>
+      <c r="F18" s="8" t="s">
+        <v>2230</v>
+      </c>
+      <c r="G18" s="7">
+        <v>0</v>
+      </c>
+      <c r="H18" s="7">
+        <v>25</v>
+      </c>
+      <c r="I18" s="7">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J18" s="7" t="s">
+        <v>2556</v>
+      </c>
+      <c r="K18" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L18" s="7" t="s">
+        <v>2557</v>
+      </c>
+      <c r="M18" s="7" t="s">
+        <v>2645</v>
+      </c>
+    </row>
+    <row r="19" spans="2:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>1481</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>2581</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>1483</v>
+      </c>
+      <c r="F19" s="8" t="s">
+        <v>2137</v>
+      </c>
+      <c r="G19" s="7">
+        <v>685</v>
+      </c>
+      <c r="H19" s="7">
+        <v>25</v>
+      </c>
+      <c r="I19" s="7">
+        <f t="shared" si="0"/>
+        <v>660</v>
+      </c>
+      <c r="J19" s="7" t="s">
+        <v>2556</v>
+      </c>
+      <c r="K19" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L19" s="7" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="20" spans="2:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>1478</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>2582</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>1480</v>
+      </c>
+      <c r="F20" s="8" t="s">
+        <v>2196</v>
+      </c>
+      <c r="G20" s="7">
+        <v>745</v>
+      </c>
+      <c r="H20" s="7">
+        <v>25</v>
+      </c>
+      <c r="I20" s="7">
+        <f t="shared" si="0"/>
+        <v>720</v>
+      </c>
+      <c r="J20" s="7" t="s">
+        <v>2556</v>
+      </c>
+      <c r="K20" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L20" s="7" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="21" spans="2:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>1237</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>2673</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>1239</v>
+      </c>
+      <c r="F21" s="8" t="s">
+        <v>2183</v>
+      </c>
+      <c r="G21" s="7">
+        <v>0</v>
+      </c>
+      <c r="H21" s="7">
+        <v>25</v>
+      </c>
+      <c r="I21" s="7">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J21" s="7" t="s">
+        <v>2556</v>
+      </c>
+      <c r="K21" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L21" s="7" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="22" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>1689</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>2629</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>1454</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="G22" s="3">
+        <v>1455</v>
+      </c>
+      <c r="H22" s="3">
+        <v>25</v>
+      </c>
+      <c r="I22" s="3">
+        <f t="shared" si="0"/>
+        <v>1430</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L22" s="3" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="23" spans="2:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>2583</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>2584</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>2670</v>
+      </c>
+      <c r="F23" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="G23" s="7">
+        <v>25</v>
+      </c>
+      <c r="H23" s="7">
+        <v>25</v>
+      </c>
+      <c r="I23" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J23" s="7" t="s">
+        <v>2556</v>
+      </c>
+      <c r="K23" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L23" s="7" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="24" spans="2:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>2650</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>2651</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>1252</v>
+      </c>
+      <c r="F24" s="8" t="s">
+        <v>2189</v>
+      </c>
+      <c r="G24" s="7">
+        <v>0</v>
+      </c>
+      <c r="H24" s="7">
+        <v>30</v>
+      </c>
+      <c r="I24" s="7">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J24" s="7" t="s">
+        <v>2556</v>
+      </c>
+      <c r="K24" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L24" s="7" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="25" spans="2:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>2586</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>2587</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>2672</v>
+      </c>
+      <c r="F25" s="8" t="s">
+        <v>287</v>
+      </c>
+      <c r="G25" s="7">
+        <v>1915</v>
+      </c>
+      <c r="H25" s="7">
+        <v>35</v>
+      </c>
+      <c r="I25" s="7">
+        <f t="shared" si="0"/>
+        <v>1880</v>
+      </c>
+      <c r="J25" s="7" t="s">
+        <v>2556</v>
+      </c>
+      <c r="K25" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L25" s="7" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="26" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>2588</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="G26" s="3">
+        <v>0</v>
+      </c>
+      <c r="H26" s="3">
+        <v>20</v>
+      </c>
+      <c r="I26" s="3">
+        <f t="shared" si="0"/>
+        <v>-20</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K26" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L26" s="3" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="27" spans="2:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>1222</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>2589</v>
+      </c>
+      <c r="E27" s="7" t="s">
+        <v>2655</v>
+      </c>
+      <c r="F27" s="8" t="s">
+        <v>2196</v>
+      </c>
+      <c r="G27" s="7">
+        <v>685</v>
+      </c>
+      <c r="H27" s="7">
+        <v>25</v>
+      </c>
+      <c r="I27" s="7">
+        <f t="shared" si="0"/>
+        <v>660</v>
+      </c>
+      <c r="J27" s="7" t="s">
+        <v>2556</v>
+      </c>
+      <c r="K27" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L27" s="7" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="28" spans="2:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>1615</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>2590</v>
+      </c>
+      <c r="E28" s="7" t="s">
+        <v>2661</v>
+      </c>
+      <c r="F28" s="8" t="s">
+        <v>2187</v>
+      </c>
+      <c r="G28" s="7">
+        <v>1810</v>
+      </c>
+      <c r="H28" s="7">
+        <v>30</v>
+      </c>
+      <c r="I28" s="7">
+        <f t="shared" si="0"/>
+        <v>1780</v>
+      </c>
+      <c r="J28" s="7" t="s">
+        <v>2556</v>
+      </c>
+      <c r="K28" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L28" s="7" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="29" spans="2:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>2591</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>2592</v>
+      </c>
+      <c r="E29" s="7" t="s">
+        <v>2658</v>
+      </c>
+      <c r="F29" s="8" t="s">
+        <v>2238</v>
+      </c>
+      <c r="G29" s="7">
+        <v>690</v>
+      </c>
+      <c r="H29" s="7">
+        <v>30</v>
+      </c>
+      <c r="I29" s="7">
+        <f t="shared" si="0"/>
+        <v>660</v>
+      </c>
+      <c r="J29" s="7" t="s">
+        <v>2556</v>
+      </c>
+      <c r="K29" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L29" s="7" t="s">
+        <v>2557</v>
+      </c>
+      <c r="M29" s="7" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="30" spans="2:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C30" s="7" t="s">
+        <v>2593</v>
+      </c>
+      <c r="D30" s="7" t="s">
+        <v>2594</v>
+      </c>
+      <c r="E30" s="7" t="s">
+        <v>2660</v>
+      </c>
+      <c r="F30" s="8" t="s">
+        <v>2187</v>
+      </c>
+      <c r="G30" s="7">
+        <v>980</v>
+      </c>
+      <c r="H30" s="7">
+        <v>30</v>
+      </c>
+      <c r="I30" s="7">
+        <f t="shared" si="0"/>
+        <v>950</v>
+      </c>
+      <c r="J30" s="7" t="s">
+        <v>2556</v>
+      </c>
+      <c r="K30" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L30" s="7" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="31" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B31" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>2595</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>2596</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>2597</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="G31" s="3">
+        <v>715</v>
+      </c>
+      <c r="H31" s="3">
+        <v>25</v>
+      </c>
+      <c r="I31" s="3">
+        <f t="shared" si="0"/>
+        <v>690</v>
+      </c>
+      <c r="J31" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K31" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L31" s="3" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="32" spans="2:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B32" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C32" s="7" t="s">
+        <v>2518</v>
+      </c>
+      <c r="D32" s="7" t="s">
+        <v>2598</v>
+      </c>
+      <c r="E32" s="7" t="s">
+        <v>2599</v>
+      </c>
+      <c r="F32" s="8" t="s">
+        <v>2242</v>
+      </c>
+      <c r="G32" s="7">
+        <v>0</v>
+      </c>
+      <c r="H32" s="7">
+        <v>25</v>
+      </c>
+      <c r="I32" s="7">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J32" s="7" t="s">
+        <v>2556</v>
+      </c>
+      <c r="K32" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L32" s="7" t="s">
+        <v>2557</v>
+      </c>
+      <c r="M32" s="7" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="33" spans="2:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B33" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>2234</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>2600</v>
+      </c>
+      <c r="E33" s="7" t="s">
+        <v>2236</v>
+      </c>
+      <c r="F33" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="G33" s="7">
+        <v>35</v>
+      </c>
+      <c r="H33" s="7">
+        <v>35</v>
+      </c>
+      <c r="I33" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J33" s="7" t="s">
+        <v>2556</v>
+      </c>
+      <c r="K33" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L33" s="7" t="s">
+        <v>2557</v>
+      </c>
+      <c r="M33" s="7" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="34" spans="2:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B34" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C34" s="7" t="s">
+        <v>2601</v>
+      </c>
+      <c r="D34" s="7" t="s">
+        <v>2602</v>
+      </c>
+      <c r="E34" s="7" t="s">
+        <v>2652</v>
+      </c>
+      <c r="F34" s="8" t="s">
+        <v>2230</v>
+      </c>
+      <c r="G34" s="7">
+        <v>815</v>
+      </c>
+      <c r="H34" s="7">
+        <v>25</v>
+      </c>
+      <c r="I34" s="7">
+        <f t="shared" si="0"/>
+        <v>790</v>
+      </c>
+      <c r="J34" s="7" t="s">
+        <v>2556</v>
+      </c>
+      <c r="K34" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L34" s="7" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="35" spans="2:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B35" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>488</v>
+      </c>
+      <c r="D35" s="7" t="s">
+        <v>2603</v>
+      </c>
+      <c r="E35" s="7" t="s">
+        <v>490</v>
+      </c>
+      <c r="F35" s="8" t="s">
+        <v>2187</v>
+      </c>
+      <c r="G35" s="7">
+        <v>690</v>
+      </c>
+      <c r="H35" s="7">
+        <v>30</v>
+      </c>
+      <c r="I35" s="7">
+        <f t="shared" si="0"/>
+        <v>660</v>
+      </c>
+      <c r="J35" s="7" t="s">
+        <v>2556</v>
+      </c>
+      <c r="K35" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L35" s="7" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="36" spans="2:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B36" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C36" s="7" t="s">
+        <v>2604</v>
+      </c>
+      <c r="D36" s="7" t="s">
+        <v>2605</v>
+      </c>
+      <c r="E36" s="7" t="s">
+        <v>2606</v>
+      </c>
+      <c r="F36" s="8" t="s">
+        <v>2137</v>
+      </c>
+      <c r="G36" s="7">
+        <v>695</v>
+      </c>
+      <c r="H36" s="7">
+        <v>25</v>
+      </c>
+      <c r="I36" s="7">
+        <f t="shared" ref="I36:I52" si="2">G36-H36</f>
+        <v>670</v>
+      </c>
+      <c r="J36" s="7" t="s">
+        <v>2556</v>
+      </c>
+      <c r="K36" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L36" s="7" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="37" spans="2:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B37" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C37" s="7" t="s">
+        <v>2671</v>
+      </c>
+      <c r="D37" s="7" t="s">
+        <v>2607</v>
+      </c>
+      <c r="E37" s="7" t="s">
+        <v>2608</v>
+      </c>
+      <c r="F37" s="8" t="s">
+        <v>2230</v>
+      </c>
+      <c r="G37" s="7">
+        <v>815</v>
+      </c>
+      <c r="H37" s="7">
+        <v>25</v>
+      </c>
+      <c r="I37" s="7">
+        <f t="shared" si="2"/>
+        <v>790</v>
+      </c>
+      <c r="J37" s="7" t="s">
+        <v>2556</v>
+      </c>
+      <c r="K37" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L37" s="7" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="38" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B38" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>2609</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>2610</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>2611</v>
+      </c>
+      <c r="F38" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="G38" s="3">
+        <v>685</v>
+      </c>
+      <c r="H38" s="3">
+        <v>25</v>
+      </c>
+      <c r="I38" s="3">
+        <f t="shared" si="2"/>
+        <v>660</v>
+      </c>
+      <c r="J38" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K38" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L38" s="3" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="39" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B39" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>2632</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>2633</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>2634</v>
+      </c>
+      <c r="F39" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="G39" s="3">
+        <v>680</v>
+      </c>
+      <c r="H39" s="3">
+        <v>20</v>
+      </c>
+      <c r="I39" s="3">
+        <f t="shared" si="2"/>
+        <v>660</v>
+      </c>
+      <c r="J39" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K39" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L39" s="3" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="40" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B40" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>593</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>2612</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>2640</v>
+      </c>
+      <c r="F40" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="G40" s="3">
+        <v>720</v>
+      </c>
+      <c r="H40" s="3">
+        <v>25</v>
+      </c>
+      <c r="I40" s="3">
+        <f t="shared" si="2"/>
+        <v>695</v>
+      </c>
+      <c r="J40" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K40" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L40" s="3" t="s">
+        <v>2557</v>
+      </c>
+      <c r="M40" s="3" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="41" spans="2:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B41" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C41" s="7" t="s">
+        <v>2665</v>
+      </c>
+      <c r="D41" s="7" t="s">
+        <v>2666</v>
+      </c>
+      <c r="E41" s="7" t="s">
+        <v>2667</v>
+      </c>
+      <c r="F41" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G41" s="7">
+        <v>690</v>
+      </c>
+      <c r="H41" s="7">
+        <v>30</v>
+      </c>
+      <c r="I41" s="7">
+        <f t="shared" si="2"/>
+        <v>660</v>
+      </c>
+      <c r="J41" s="7" t="s">
+        <v>2556</v>
+      </c>
+      <c r="K41" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L41" s="7" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="42" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B42" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>2613</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>2614</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>2615</v>
+      </c>
+      <c r="F42" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="G42" s="3">
+        <v>685</v>
+      </c>
+      <c r="H42" s="3">
+        <v>25</v>
+      </c>
+      <c r="I42" s="3">
+        <f t="shared" si="2"/>
+        <v>660</v>
+      </c>
+      <c r="J42" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K42" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L42" s="3" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="43" spans="2:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B43" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C43" s="7" t="s">
+        <v>2649</v>
+      </c>
+      <c r="D43" s="7" t="s">
+        <v>2616</v>
+      </c>
+      <c r="E43" s="7" t="s">
+        <v>789</v>
+      </c>
+      <c r="F43" s="8" t="s">
+        <v>2230</v>
+      </c>
+      <c r="G43" s="7">
+        <v>815</v>
+      </c>
+      <c r="H43" s="7">
+        <v>25</v>
+      </c>
+      <c r="I43" s="7">
+        <f t="shared" si="2"/>
+        <v>790</v>
+      </c>
+      <c r="J43" s="7" t="s">
+        <v>2556</v>
+      </c>
+      <c r="K43" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L43" s="7" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="44" spans="2:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B44" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C44" s="7" t="s">
+        <v>2617</v>
+      </c>
+      <c r="D44" s="7" t="s">
+        <v>2618</v>
+      </c>
+      <c r="E44" s="7" t="s">
+        <v>2663</v>
+      </c>
+      <c r="F44" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="G44" s="7">
+        <v>345</v>
+      </c>
+      <c r="H44" s="7">
+        <v>35</v>
+      </c>
+      <c r="I44" s="7">
+        <f t="shared" si="2"/>
+        <v>310</v>
+      </c>
+      <c r="J44" s="7" t="s">
+        <v>2556</v>
+      </c>
+      <c r="K44" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L44" s="7" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="45" spans="2:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B45" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C45" s="7" t="s">
+        <v>2619</v>
+      </c>
+      <c r="D45" s="7" t="s">
+        <v>2620</v>
+      </c>
+      <c r="E45" s="7" t="s">
+        <v>2654</v>
+      </c>
+      <c r="F45" s="8" t="s">
+        <v>2242</v>
+      </c>
+      <c r="G45" s="7">
+        <v>875</v>
+      </c>
+      <c r="H45" s="7">
+        <v>25</v>
+      </c>
+      <c r="I45" s="7">
+        <f t="shared" si="2"/>
+        <v>850</v>
+      </c>
+      <c r="J45" s="7" t="s">
+        <v>2556</v>
+      </c>
+      <c r="K45" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L45" s="7" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="46" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B46" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>2641</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>2621</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>2642</v>
+      </c>
+      <c r="F46" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="G46" s="3">
+        <v>2260</v>
+      </c>
+      <c r="H46" s="3">
+        <v>20</v>
+      </c>
+      <c r="I46" s="3">
+        <f t="shared" si="2"/>
+        <v>2240</v>
+      </c>
+      <c r="J46" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K46" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L46" s="3" t="s">
+        <v>2557</v>
+      </c>
+      <c r="M46" s="3" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="47" spans="2:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B47" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C47" s="7" t="s">
+        <v>2622</v>
+      </c>
+      <c r="D47" s="7" t="s">
+        <v>2623</v>
+      </c>
+      <c r="E47" s="7" t="s">
+        <v>2648</v>
+      </c>
+      <c r="F47" s="8" t="s">
+        <v>2238</v>
+      </c>
+      <c r="G47" s="7">
+        <v>690</v>
+      </c>
+      <c r="H47" s="7">
+        <v>30</v>
+      </c>
+      <c r="I47" s="7">
+        <f t="shared" si="2"/>
+        <v>660</v>
+      </c>
+      <c r="J47" s="7" t="s">
+        <v>2556</v>
+      </c>
+      <c r="K47" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L47" s="7" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="48" spans="2:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B48" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C48" s="7" t="s">
+        <v>750</v>
+      </c>
+      <c r="D48" s="7" t="s">
+        <v>2624</v>
+      </c>
+      <c r="E48" s="7" t="s">
+        <v>2625</v>
+      </c>
+      <c r="F48" s="8" t="s">
+        <v>2230</v>
+      </c>
+      <c r="G48" s="7">
+        <v>0</v>
+      </c>
+      <c r="H48" s="7">
+        <v>0</v>
+      </c>
+      <c r="I48" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J48" s="7" t="s">
+        <v>2556</v>
+      </c>
+      <c r="K48" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L48" s="7" t="s">
+        <v>2557</v>
+      </c>
+      <c r="M48" s="7" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="49" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B49" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C49" s="7" t="s">
+        <v>2626</v>
+      </c>
+      <c r="D49" s="7" t="s">
+        <v>2627</v>
+      </c>
+      <c r="E49" s="7" t="s">
+        <v>2656</v>
+      </c>
+      <c r="F49" s="8" t="s">
+        <v>2183</v>
+      </c>
+      <c r="G49" s="7">
+        <v>925</v>
+      </c>
+      <c r="H49" s="7">
+        <v>25</v>
+      </c>
+      <c r="I49" s="7">
+        <f t="shared" si="2"/>
+        <v>900</v>
+      </c>
+      <c r="J49" s="7" t="s">
+        <v>2556</v>
+      </c>
+      <c r="K49" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L49" s="7" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="50" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>640</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>641</v>
+      </c>
+      <c r="F50" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="G50" s="3">
+        <v>3955</v>
+      </c>
+      <c r="H50" s="3">
+        <v>35</v>
+      </c>
+      <c r="I50" s="3">
+        <f t="shared" si="2"/>
+        <v>3920</v>
+      </c>
+      <c r="J50" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K50" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L50" s="3" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="51" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>573</v>
+      </c>
+      <c r="E51" s="3" t="s">
+        <v>2628</v>
+      </c>
+      <c r="F51" s="4" t="s">
+        <v>2569</v>
+      </c>
+      <c r="G51" s="3">
+        <v>1415</v>
+      </c>
+      <c r="H51" s="3">
+        <v>35</v>
+      </c>
+      <c r="I51" s="3">
+        <f t="shared" si="2"/>
+        <v>1380</v>
+      </c>
+      <c r="J51" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K51" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L51" s="3" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="52" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>2636</v>
+      </c>
+      <c r="F52" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="G52" s="3">
+        <v>30</v>
+      </c>
+      <c r="H52" s="3">
+        <v>30</v>
+      </c>
+      <c r="I52" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K52" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L52" s="3" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="53" spans="1:16" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B53" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="C53" s="11" t="s">
+        <v>1689</v>
+      </c>
+      <c r="D53" s="11" t="s">
+        <v>2535</v>
+      </c>
+      <c r="E53" s="11" t="s">
+        <v>1454</v>
+      </c>
+      <c r="F53" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="G53" s="11">
+        <v>765</v>
+      </c>
+      <c r="H53" s="11">
+        <v>0</v>
+      </c>
+      <c r="I53" s="11">
+        <f>G53-H53</f>
+        <v>765</v>
+      </c>
+      <c r="J53" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="K53" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="L53" s="11" t="s">
+        <v>2412</v>
+      </c>
+      <c r="M53" s="11" t="s">
+        <v>429</v>
+      </c>
+      <c r="N53" s="11" t="s">
+        <v>430</v>
+      </c>
+      <c r="O53" s="11" t="s">
+        <v>430</v>
+      </c>
+      <c r="P53" s="11" t="s">
+        <v>431</v>
       </c>
     </row>
   </sheetData>

--- a/data/Apr/Data.xlsx
+++ b/data/Apr/Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Freelance\TextInputter\data\Apr\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1E36D81-E9C5-4D27-B3F1-4146E2CB238F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10B71B07-6EFE-4FC8-B717-11C035502575}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="7" activeTab="21" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="9" activeTab="23" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01-04" sheetId="4" r:id="rId1"/>
@@ -35,6 +35,8 @@
     <sheet name="23-04" sheetId="24" r:id="rId20"/>
     <sheet name="24-04" sheetId="25" r:id="rId21"/>
     <sheet name="25-04" sheetId="26" r:id="rId22"/>
+    <sheet name="27-04" sheetId="27" r:id="rId23"/>
+    <sheet name="28-04" sheetId="28" r:id="rId24"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -57,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8421" uniqueCount="2674">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9861" uniqueCount="3067">
   <si>
     <t>THU 4</t>
   </si>
@@ -7733,21 +7735,42 @@
     <t>25-04-2026</t>
   </si>
   <si>
+    <t>Thuy An Dao</t>
+  </si>
+  <si>
     <t>HD015672</t>
   </si>
   <si>
+    <t>Sảnh B2 chung cư Emerald phường Sơn Kỳ</t>
+  </si>
+  <si>
     <t>Loan Tran</t>
   </si>
   <si>
     <t>HD015680</t>
   </si>
   <si>
+    <t>Chung Cư Diamond Brilliant Số 3 Đường N1 phường Tân Sơn Nhì Sảnh B1</t>
+  </si>
+  <si>
     <t>Hằng Nguyễn</t>
   </si>
   <si>
     <t>HD015363</t>
   </si>
   <si>
+    <t>686 Tô Ngọc Vân, P. Tam Bình</t>
+  </si>
+  <si>
+    <t>HD015574</t>
+  </si>
+  <si>
+    <t>206/26/10 Lê văn quới, kp4, bình trị đông</t>
+  </si>
+  <si>
+    <t>YU MY</t>
+  </si>
+  <si>
     <t>HD015600</t>
   </si>
   <si>
@@ -7757,328 +7780,1486 @@
     <t>HD015565</t>
   </si>
   <si>
+    <t>29 Tran thi nghĩ p7</t>
+  </si>
+  <si>
+    <t>kh ck shop 685k</t>
+  </si>
+  <si>
     <t>Lotus Tram</t>
   </si>
   <si>
     <t>HD015505</t>
   </si>
   <si>
+    <t>Số 3, đường 37,khu dân cư vạn phúc?phường hiệp bình phước</t>
+  </si>
+  <si>
     <t>HD015602</t>
   </si>
   <si>
+    <t>18/10 kdc bảo anh kp40 đường TL26 phường an phú đông</t>
+  </si>
+  <si>
+    <t>Nguyễn Hải Phụng</t>
+  </si>
+  <si>
+    <t>HD015693</t>
+  </si>
+  <si>
+    <t>36 bờ bao tận trắng P. Sơn Kỳ (chung cư celedon cổng diamond brilliant block B2)</t>
+  </si>
+  <si>
+    <t>Thuy Trang</t>
+  </si>
+  <si>
+    <t>HD015739</t>
+  </si>
+  <si>
+    <t>A3 Chung cư The Gold View 346 Bến Vân Đồn - P.1</t>
+  </si>
+  <si>
+    <t>HD015528</t>
+  </si>
+  <si>
+    <t>HD015502</t>
+  </si>
+  <si>
+    <t>tòa B chung cư 9 view phường phước long</t>
+  </si>
+  <si>
+    <t>kh ck shop 730k</t>
+  </si>
+  <si>
+    <t>HĐ015764</t>
+  </si>
+  <si>
+    <t>47 hiệp bình, hiệp bình chánh</t>
+  </si>
+  <si>
+    <t>Dang Thuy Trang</t>
+  </si>
+  <si>
+    <t>HD015726</t>
+  </si>
+  <si>
+    <t>Tòa landmark3, vinhome tân cang</t>
+  </si>
+  <si>
+    <t>NHƯ Ý LÊ</t>
+  </si>
+  <si>
+    <t>HD015418</t>
+  </si>
+  <si>
+    <t>số 13 đường số 9, P13</t>
+  </si>
+  <si>
+    <t>kh ck shop 1895k</t>
+  </si>
+  <si>
+    <t>HD015588</t>
+  </si>
+  <si>
+    <t>HD015392</t>
+  </si>
+  <si>
+    <t>HD015427</t>
+  </si>
+  <si>
+    <t>HD015737</t>
+  </si>
+  <si>
+    <t>MỸ HUYỀN - giữ đơn</t>
+  </si>
+  <si>
+    <t>HD014566</t>
+  </si>
+  <si>
+    <t>17 Bùi Thế Mỹ P. Bảy Hiền</t>
+  </si>
+  <si>
+    <t>Ms Thuyên Tổ Như ari</t>
+  </si>
+  <si>
+    <t>HD015674</t>
+  </si>
+  <si>
+    <t>Vũ Duy Tâm - fb Ngoc Nga</t>
+  </si>
+  <si>
+    <t>HD015761</t>
+  </si>
+  <si>
+    <t>169 Kênh Trung Ương, Ấp 50, Xã Xuân Thới Thượng</t>
+  </si>
+  <si>
+    <t>HD015334</t>
+  </si>
+  <si>
+    <t>HD015581</t>
+  </si>
+  <si>
+    <t>346 bến vân đồn, P1</t>
+  </si>
+  <si>
+    <t>HD015372</t>
+  </si>
+  <si>
+    <t>Cc cardinal tower B Phường Tân Phú B908</t>
+  </si>
+  <si>
+    <t>Nguyễn Kim Hồng</t>
+  </si>
+  <si>
+    <t>HD015760</t>
+  </si>
+  <si>
+    <t>A22/6 phạm thể hiển p3</t>
+  </si>
+  <si>
+    <t>Minh Trang</t>
+  </si>
+  <si>
+    <t>HD015370</t>
+  </si>
+  <si>
+    <t>Eco green sài gòn, đường nguyễn văn linh, phường tân thuận tân Block B</t>
+  </si>
+  <si>
+    <t>Emily Le</t>
+  </si>
+  <si>
+    <t>HD015400</t>
+  </si>
+  <si>
+    <t>281/36 Lê Văn Sỹ P1</t>
+  </si>
+  <si>
+    <t>HD015483</t>
+  </si>
+  <si>
+    <t>Chung cư Hà đô toà orchid 2</t>
+  </si>
+  <si>
+    <t>HD015678</t>
+  </si>
+  <si>
+    <t>Lucie Huỳnh</t>
+  </si>
+  <si>
+    <t>HD015492</t>
+  </si>
+  <si>
+    <t>Chung cư starlight riverside phường bình phú</t>
+  </si>
+  <si>
+    <t>HD015705</t>
+  </si>
+  <si>
+    <t>Chan Vin</t>
+  </si>
+  <si>
+    <t>HD015702</t>
+  </si>
+  <si>
+    <t>LIBERTY CENTRAL SAIGON RIVERSIDE HOTEL - 17 Ton Duc Thang St</t>
+  </si>
+  <si>
+    <t>Thảo Quyên người nhận tên Thuỳ Minh</t>
+  </si>
+  <si>
+    <t>HD015571</t>
+  </si>
+  <si>
+    <t>336/43/5e nguyễn văn luôn p12</t>
+  </si>
+  <si>
+    <t>Ngân Hà</t>
+  </si>
+  <si>
+    <t>HD015652</t>
+  </si>
+  <si>
+    <t>Cc dream home 2, lô B, đường 59, p14</t>
+  </si>
+  <si>
+    <t>Nguyễn Hoài An</t>
+  </si>
+  <si>
+    <t>HD015748</t>
+  </si>
+  <si>
+    <t>15 đặng thai mai p7</t>
+  </si>
+  <si>
+    <t>HD015424</t>
+  </si>
+  <si>
+    <t>107/189 Quang Trung P10</t>
+  </si>
+  <si>
+    <t>coca kẹ</t>
+  </si>
+  <si>
+    <t>HD015733</t>
+  </si>
+  <si>
+    <t>532/3/93 Kinh Dương Vương. Phường An Lạc</t>
+  </si>
+  <si>
+    <t>Vân Vân</t>
+  </si>
+  <si>
+    <t>HD015567</t>
+  </si>
+  <si>
+    <t>86/36/3 phổ quang, tân sơn hòa</t>
+  </si>
+  <si>
+    <t>TRINH fb Nguyễn --oben</t>
+  </si>
+  <si>
+    <t>HD015527</t>
+  </si>
+  <si>
+    <t>Thuỷ Trúc</t>
+  </si>
+  <si>
+    <t>HD015561</t>
+  </si>
+  <si>
+    <t>Chung cư Callagarden, kdc Greenlife 13C, Đ. Nguyễn Văn Linh, X. Phong Phú</t>
+  </si>
+  <si>
+    <t>Nguyễn Như Ý</t>
+  </si>
+  <si>
+    <t>HD015595</t>
+  </si>
+  <si>
+    <t>28/13 Trần Thiện Chánh p12</t>
+  </si>
+  <si>
+    <t>trâm fb Anne Ng</t>
+  </si>
+  <si>
+    <t>HD015736</t>
+  </si>
+  <si>
+    <t>294/22/53 xô viết nghệ tinh,khu phố 21 phường thạnh mỹ tây</t>
+  </si>
+  <si>
+    <t>Lê Ngọc Diễm</t>
+  </si>
+  <si>
+    <t>HD015562</t>
+  </si>
+  <si>
+    <t>Chung cư tara. Phường 6. Block B2 tòa khải hoàn</t>
+  </si>
+  <si>
+    <t>HD015601</t>
+  </si>
+  <si>
+    <t>980/4b là gốm p8</t>
+  </si>
+  <si>
+    <t>Hoàng Thuý Liên</t>
+  </si>
+  <si>
+    <t>HD015756</t>
+  </si>
+  <si>
+    <t>290 an dương vương phường chợ quán</t>
+  </si>
+  <si>
+    <t>119 hoàng diệu 2</t>
+  </si>
+  <si>
     <t>thu đuc</t>
   </si>
   <si>
-    <t>Nguyễn Hải Phụng</t>
-  </si>
-  <si>
-    <t>HD015693</t>
-  </si>
-  <si>
-    <t>Thuy Trang</t>
-  </si>
-  <si>
-    <t>HD015739</t>
-  </si>
-  <si>
-    <t>A3 Chung cư The Gold View 346 Bến Vân Đồn - P.1</t>
-  </si>
-  <si>
-    <t>HD015528</t>
-  </si>
-  <si>
-    <t>HD015502</t>
-  </si>
-  <si>
-    <t>HĐ015764</t>
-  </si>
-  <si>
-    <t>HD015726</t>
-  </si>
-  <si>
-    <t>HD015418</t>
-  </si>
-  <si>
-    <t>số 13 đường số 9, P13</t>
-  </si>
-  <si>
-    <t>HD015588</t>
-  </si>
-  <si>
-    <t>HD015392</t>
-  </si>
-  <si>
-    <t>MỸ HUYỀN - giữ đơn</t>
-  </si>
-  <si>
-    <t>HD014566</t>
-  </si>
-  <si>
-    <t>HD015574</t>
-  </si>
-  <si>
-    <t>Vũ Duy Tâm - fb Ngoc Nga</t>
-  </si>
-  <si>
-    <t>HD015761</t>
-  </si>
-  <si>
-    <t>HD015334</t>
-  </si>
-  <si>
-    <t>HD015581</t>
-  </si>
-  <si>
-    <t>HD015372</t>
-  </si>
-  <si>
-    <t>Nguyễn Kim Hồng</t>
-  </si>
-  <si>
-    <t>HD015760</t>
-  </si>
-  <si>
-    <t>Minh Trang</t>
-  </si>
-  <si>
-    <t>HD015370</t>
-  </si>
-  <si>
-    <t>Emily Le</t>
-  </si>
-  <si>
-    <t>HD015400</t>
-  </si>
-  <si>
-    <t>281/36 Lê Văn Sỹ P1</t>
-  </si>
-  <si>
-    <t>HD015483</t>
-  </si>
-  <si>
-    <t>Chung cư Hà đô toà orchid 2</t>
-  </si>
-  <si>
-    <t>HD015678</t>
-  </si>
-  <si>
-    <t>Lucie Huỳnh</t>
-  </si>
-  <si>
-    <t>HD015492</t>
-  </si>
-  <si>
-    <t>HD015705</t>
-  </si>
-  <si>
-    <t>Chan Vin</t>
-  </si>
-  <si>
-    <t>HD015702</t>
-  </si>
-  <si>
-    <t>LIBERTY CENTRAL SAIGON RIVERSIDE HOTEL - 17 Ton Duc Thang St</t>
-  </si>
-  <si>
-    <t>HD015571</t>
-  </si>
-  <si>
-    <t>336/43/5e nguyễn văn luôn p12</t>
-  </si>
-  <si>
-    <t>Ngân Hà</t>
-  </si>
-  <si>
-    <t>HD015652</t>
-  </si>
-  <si>
-    <t>Cc dream home 2, lô B, đường 59, p14</t>
-  </si>
-  <si>
-    <t>HD015424</t>
-  </si>
-  <si>
-    <t>Vân Vân</t>
-  </si>
-  <si>
-    <t>HD015567</t>
-  </si>
-  <si>
-    <t>86/36/3 phổ quang, tân sơn hòa</t>
-  </si>
-  <si>
-    <t>HD015527</t>
-  </si>
-  <si>
-    <t>Thuỷ Trúc</t>
-  </si>
-  <si>
-    <t>HD015561</t>
-  </si>
-  <si>
-    <t>Nguyễn Như Ý</t>
-  </si>
-  <si>
-    <t>HD015595</t>
-  </si>
-  <si>
-    <t>HD015736</t>
-  </si>
-  <si>
-    <t>Lê Ngọc Diễm</t>
-  </si>
-  <si>
-    <t>HD015562</t>
-  </si>
-  <si>
-    <t>HD015601</t>
-  </si>
-  <si>
-    <t>980/4b là gốm p8</t>
-  </si>
-  <si>
-    <t>Hoàng Thuý Liên</t>
-  </si>
-  <si>
-    <t>HD015756</t>
-  </si>
-  <si>
-    <t>119 hoàng diệu 2</t>
-  </si>
-  <si>
-    <t>HD015737</t>
-  </si>
-  <si>
-    <t>Dang Thuy Trang</t>
-  </si>
-  <si>
-    <t>Tòa landmark3, vinhome tân cang</t>
-  </si>
-  <si>
-    <t>Nguyễn Hoài An</t>
-  </si>
-  <si>
-    <t>HD015748</t>
-  </si>
-  <si>
-    <t>15 đặng thai mai p7</t>
-  </si>
-  <si>
-    <t>686 Tô Ngọc Vân, P. Tam Bình</t>
-  </si>
-  <si>
     <t>685 Tân Sơn phường 12</t>
   </si>
   <si>
-    <t>Số 3, đường 37,khu dân cư vạn phúc?phường hiệp bình phước</t>
-  </si>
-  <si>
-    <t>29 Tran thi nghĩ p7</t>
-  </si>
-  <si>
-    <t>47 hiệp bình, hiệp bình chánh</t>
-  </si>
-  <si>
-    <t>107/189 Quang Trung P10</t>
-  </si>
-  <si>
-    <t>trâm fb Anne Ng</t>
-  </si>
-  <si>
-    <t>294/22/53 xô viết nghệ tinh,khu phố 21 phường thạnh mỹ tây</t>
-  </si>
-  <si>
-    <t>kh ck shop 685k</t>
-  </si>
-  <si>
-    <t>kh ck shop 730k</t>
-  </si>
-  <si>
-    <t>kh ck shop 1895k</t>
-  </si>
-  <si>
-    <t>tòa B chung cư 9 view phường phước long</t>
-  </si>
-  <si>
-    <t>36 bờ bao tận trắng P. Sơn Kỳ (chung cư celedon cổng diamond brilliant block B2)</t>
-  </si>
-  <si>
-    <t>Chung cư tara. Phường 6. Block B2 tòa khải hoàn</t>
-  </si>
-  <si>
-    <t>TRINH fb Nguyễn --oben</t>
-  </si>
-  <si>
-    <t>Ms Thuyên Tổ Như ari</t>
-  </si>
-  <si>
-    <t>HD015674</t>
-  </si>
-  <si>
-    <t>Chung cư starlight riverside phường bình phú</t>
-  </si>
-  <si>
-    <t>18/10 kdc bảo anh kp40 đường TL26 phường an phú đông</t>
-  </si>
-  <si>
-    <t>28/13 Trần Thiện Chánh p12</t>
-  </si>
-  <si>
-    <t>346 bến vân đồn, P1</t>
-  </si>
-  <si>
-    <t>290 an dương vương phường chợ quán</t>
-  </si>
-  <si>
-    <t>Chung Cư Diamond Brilliant Số 3 Đường N1 phường Tân Sơn Nhì Sảnh B1</t>
-  </si>
-  <si>
-    <t>A22/6 phạm thể hiển p3</t>
-  </si>
-  <si>
-    <t>206/26/10 Lê văn quới, kp4, bình trị đông</t>
-  </si>
-  <si>
-    <t>Eco green sài gòn, đường nguyễn văn linh, phường tân thuận tân Block B</t>
-  </si>
-  <si>
-    <t>Cc cardinal tower B Phường Tân Phú B908</t>
-  </si>
-  <si>
-    <t>NHƯ Ý LÊ</t>
-  </si>
-  <si>
-    <t>Chung cư Callagarden, kdc Greenlife 13C, Đ. Nguyễn Văn Linh, X. Phong Phú</t>
-  </si>
-  <si>
-    <t>YU MY</t>
-  </si>
-  <si>
-    <t>coca kẹ</t>
-  </si>
-  <si>
-    <t>HD015733</t>
-  </si>
-  <si>
-    <t>532/3/93 Kinh Dương Vương. Phường An Lạc</t>
-  </si>
-  <si>
-    <t>Thuy An Dao</t>
-  </si>
-  <si>
-    <t>Sảnh B2 chung cư Emerald phường Sơn Kỳ</t>
-  </si>
-  <si>
-    <t>17 Bùi Thế Mỹ P. Bảy Hiền</t>
-  </si>
-  <si>
-    <t>Thảo Quyên người nhận tên Thuỳ Minh</t>
-  </si>
-  <si>
-    <t>169 Kênh Trung Ương, Ấp 50, Xã Xuân Thới Thượng</t>
-  </si>
-  <si>
-    <t>HD015427</t>
+    <t>NGAY 27-4</t>
+  </si>
+  <si>
+    <t>HD016292</t>
+  </si>
+  <si>
+    <t>27-04-2026</t>
+  </si>
+  <si>
+    <t>Bông Bong</t>
+  </si>
+  <si>
+    <t>HD016136</t>
+  </si>
+  <si>
+    <t>số 31 Lê Hồng Phong, p4</t>
+  </si>
+  <si>
+    <t>Trần Châu Yến Vy</t>
+  </si>
+  <si>
+    <t>HD016317</t>
+  </si>
+  <si>
+    <t>2B Mai Chí Thọ, Empire Tòa Tila</t>
+  </si>
+  <si>
+    <t>Nhật Lê Hin</t>
+  </si>
+  <si>
+    <t>HD016217</t>
+  </si>
+  <si>
+    <t>814 sư vạn hạnh</t>
+  </si>
+  <si>
+    <t>Lam</t>
+  </si>
+  <si>
+    <t>HD015857</t>
+  </si>
+  <si>
+    <t>168/50 nguyễn cư trinh phường nguyễn cư trinh</t>
+  </si>
+  <si>
+    <t>Hoàng THỊ Diễm Quỳnh</t>
+  </si>
+  <si>
+    <t>HD016105</t>
+  </si>
+  <si>
+    <t>Khu Holm căn 21 145 Nguyễn Và Hưởng</t>
+  </si>
+  <si>
+    <t>Hảo Ngọc</t>
+  </si>
+  <si>
+    <t>HD016263</t>
+  </si>
+  <si>
+    <t>220b lê văn lương, P. Tân Hưng</t>
+  </si>
+  <si>
+    <t>AT 27-04</t>
+  </si>
+  <si>
+    <t>Mỹ Mỹ</t>
+  </si>
+  <si>
+    <t>H0016352</t>
+  </si>
+  <si>
+    <t>135/2F đình phong phú</t>
+  </si>
+  <si>
+    <t>HD016276</t>
+  </si>
+  <si>
+    <t>Landmark plus. 720a điện biên phủ. Phường 22</t>
+  </si>
+  <si>
+    <t>HD016312</t>
+  </si>
+  <si>
+    <t>Chi Tel : 068968666 (inst -lefemaleboutique)</t>
+  </si>
+  <si>
+    <t>HD015894</t>
+  </si>
+  <si>
+    <t>nhà xe khải nam 367 hùng vương</t>
+  </si>
+  <si>
+    <t>Triệu Như Huyền</t>
+  </si>
+  <si>
+    <t>HD016038</t>
+  </si>
+  <si>
+    <t>39 bến vân đồn</t>
+  </si>
+  <si>
+    <t>Trần Thị Kim Giang</t>
+  </si>
+  <si>
+    <t>HD016266</t>
+  </si>
+  <si>
+    <t>234/674 lê đức thọ p6</t>
+  </si>
+  <si>
+    <t>Danh Hồng</t>
+  </si>
+  <si>
+    <t>HD016192</t>
+  </si>
+  <si>
+    <t>33 nguyễn văn giai p đakao</t>
+  </si>
+  <si>
+    <t>HD016010</t>
+  </si>
+  <si>
+    <t>Lê Thuỳ Tiên</t>
+  </si>
+  <si>
+    <t>HD016104</t>
+  </si>
+  <si>
+    <t>Suby Phạm</t>
+  </si>
+  <si>
+    <t>HD016415</t>
+  </si>
+  <si>
+    <t>16 đường 36 Tân quy</t>
+  </si>
+  <si>
+    <t>Tran Thanh (Sammy Mona)</t>
+  </si>
+  <si>
+    <t>HD015142</t>
+  </si>
+  <si>
+    <t>228/1/3 nguyễn thượng hiền, Phường 1</t>
+  </si>
+  <si>
+    <t>Lam Ngọc Tuyết</t>
+  </si>
+  <si>
+    <t>HD016416</t>
+  </si>
+  <si>
+    <t>25 Nguyễn bỉnh khiêm phường ben nghe</t>
+  </si>
+  <si>
+    <t>Minh Hà Hana</t>
+  </si>
+  <si>
+    <t>HD015716</t>
+  </si>
+  <si>
+    <t>So 1 võ trường toản</t>
+  </si>
+  <si>
+    <t>Kim Anh Phạm</t>
+  </si>
+  <si>
+    <t>HD015993</t>
+  </si>
+  <si>
+    <t>16 cư xá bình minh, đường dương bá trạc, phường 1</t>
+  </si>
+  <si>
+    <t>Shipping Mark PT: Srcyneth Min</t>
+  </si>
+  <si>
+    <t>HD016360</t>
+  </si>
+  <si>
+    <t>Nhà 39, Đường B4, Tây Thạnh, Tân Phú</t>
+  </si>
+  <si>
+    <t>HD016301</t>
+  </si>
+  <si>
+    <t>HD015955</t>
+  </si>
+  <si>
+    <t>Thanh</t>
+  </si>
+  <si>
+    <t>HD016208</t>
+  </si>
+  <si>
+    <t>63/5 Dương Đình Hội, Phường Phước Long</t>
+  </si>
+  <si>
+    <t>HD015903</t>
+  </si>
+  <si>
+    <t>6/24 tân chánh hiệp 36, P trung mỹ tây</t>
+  </si>
+  <si>
+    <t>Nina Châu</t>
+  </si>
+  <si>
+    <t>HD016235</t>
+  </si>
+  <si>
+    <t>88/10/5 trần văn quang p10</t>
+  </si>
+  <si>
+    <t>Sapphire Tran</t>
+  </si>
+  <si>
+    <t>HD016311</t>
+  </si>
+  <si>
+    <t>The standard bình dương-p.tân khánh-kp khánh hội</t>
+  </si>
+  <si>
+    <t>HD015889</t>
+  </si>
+  <si>
+    <t>em xíu shiiny</t>
+  </si>
+  <si>
+    <t>HD016293</t>
+  </si>
+  <si>
+    <t>số 217 Đường bùi thị xuân phường 1</t>
+  </si>
+  <si>
+    <t>Hoài Thanh</t>
+  </si>
+  <si>
+    <t>HD016113</t>
+  </si>
+  <si>
+    <t>108/10 đường ngô chí quốc, p tam bình</t>
+  </si>
+  <si>
+    <t>Vu Hao Nhi</t>
+  </si>
+  <si>
+    <t>HD016228</t>
+  </si>
+  <si>
+    <t>30/43 đoàn văn bơ p9</t>
+  </si>
+  <si>
+    <t>Mễ Mễ</t>
+  </si>
+  <si>
+    <t>HD016245</t>
+  </si>
+  <si>
+    <t>60b Nguyễn thông p9</t>
+  </si>
+  <si>
+    <t>Thúy Hằng Trương</t>
+  </si>
+  <si>
+    <t>HD016254</t>
+  </si>
+  <si>
+    <t>26 hoàng diệu 2 phường linh chiểu</t>
+  </si>
+  <si>
+    <t>Ái My</t>
+  </si>
+  <si>
+    <t>HD015320</t>
+  </si>
+  <si>
+    <t>82 bình long phường phú thạnh</t>
+  </si>
+  <si>
+    <t>HD016112</t>
+  </si>
+  <si>
+    <t>Trần Nguyễn Ánh Ngọc</t>
+  </si>
+  <si>
+    <t>HD016376</t>
+  </si>
+  <si>
+    <t>49 đương số 3 cư xá đô thành p4</t>
+  </si>
+  <si>
+    <t>Hùng fb Hini Bie</t>
+  </si>
+  <si>
+    <t>HD016199</t>
+  </si>
+  <si>
+    <t>1 đường số 1, Tân kiểng</t>
+  </si>
+  <si>
+    <t>Nguyễn Thị Trà My</t>
+  </si>
+  <si>
+    <t>HD016071</t>
+  </si>
+  <si>
+    <t>264 Võ Văn Hát Long Trường</t>
+  </si>
+  <si>
+    <t>Phan Thị Huyền My</t>
+  </si>
+  <si>
+    <t>HD016110</t>
+  </si>
+  <si>
+    <t>533/15 B lê đức thọ</t>
+  </si>
+  <si>
+    <t>C30ST (inst-sth3a)</t>
+  </si>
+  <si>
+    <t>HD016201</t>
+  </si>
+  <si>
+    <t>270B Đường Lý Thường Kiệt, Khu Phố 1 Phường 6</t>
+  </si>
+  <si>
+    <t>bé đầm fb Ngân Phạm</t>
+  </si>
+  <si>
+    <t>HD015858</t>
+  </si>
+  <si>
+    <t>7 đường số 13a.khu phố 7, bình hưng hòa a</t>
+  </si>
+  <si>
+    <t>Ngân Lê</t>
+  </si>
+  <si>
+    <t>HD016355</t>
+  </si>
+  <si>
+    <t>358/2/2 CMT8</t>
+  </si>
+  <si>
+    <t>Chị Vy - Ib Phạm Thị Hồng Ngọc</t>
+  </si>
+  <si>
+    <t>HD016018</t>
+  </si>
+  <si>
+    <t>109 Chu Văn An, Phường 26</t>
+  </si>
+  <si>
+    <t>Trân Trương</t>
+  </si>
+  <si>
+    <t>HD016368</t>
+  </si>
+  <si>
+    <t>511 trần xuân soạn phường tân kiểng</t>
+  </si>
+  <si>
+    <t>Lê Kim Khỏe</t>
+  </si>
+  <si>
+    <t>HD015848</t>
+  </si>
+  <si>
+    <t>block C, Chung cư Conic Đông Nam Á, đường số 2, Xã Bình Hưng (Xã Phong Phú cũ)</t>
+  </si>
+  <si>
+    <t>HIẾU (fb Huyen Nguyen}</t>
+  </si>
+  <si>
+    <t>HD015871</t>
+  </si>
+  <si>
+    <t>Hân Trương</t>
+  </si>
+  <si>
+    <t>HD016007</t>
+  </si>
+  <si>
+    <t>347/40B Minh Phụng, p2</t>
+  </si>
+  <si>
+    <t>Nguyen Vo Tuong Vyy</t>
+  </si>
+  <si>
+    <t>HD015830</t>
+  </si>
+  <si>
+    <t>Số 13 đường 126 ấp 12 phú hoà đông</t>
+  </si>
+  <si>
+    <t>cu chi</t>
+  </si>
+  <si>
+    <t>Nguyễn Trinh</t>
+  </si>
+  <si>
+    <t>HD016185</t>
+  </si>
+  <si>
+    <t>198/8 Dương Bá Trạc Phường Chánh Hưng</t>
+  </si>
+  <si>
+    <t>Mỹ Diện</t>
+  </si>
+  <si>
+    <t>HD016619</t>
+  </si>
+  <si>
+    <t>virhomes grand park tòa nhà s705 nguyễn xiển p long thạnh mỹ</t>
+  </si>
+  <si>
+    <t>Gia Huy nhận của ILIS NGUYỄN ( singapore)</t>
+  </si>
+  <si>
+    <t>HD016677</t>
+  </si>
+  <si>
+    <t>2/11 Đường Thiên Phước, Phường 9</t>
+  </si>
+  <si>
+    <t>Jenny Đoàn</t>
+  </si>
+  <si>
+    <t>HD016652</t>
+  </si>
+  <si>
+    <t>lô m3 chung cư tôn thất thuyết p1</t>
+  </si>
+  <si>
+    <t>HD016362</t>
+  </si>
+  <si>
+    <t>Võ Thu Hà</t>
+  </si>
+  <si>
+    <t>HD016679</t>
+  </si>
+  <si>
+    <t>262/15 lũy bán bích, hòa thạch</t>
+  </si>
+  <si>
+    <t>HD016331</t>
+  </si>
+  <si>
+    <t>Cc cardinal tower B Phường Tân Phú</t>
+  </si>
+  <si>
+    <t>Quynh Trang Hoang</t>
+  </si>
+  <si>
+    <t>HD016602</t>
+  </si>
+  <si>
+    <t>landmark 1- vinhome central park</t>
+  </si>
+  <si>
+    <t>Trường Quanh</t>
+  </si>
+  <si>
+    <t>HD016589</t>
+  </si>
+  <si>
+    <t>26 lê văn sỹ, phường 11</t>
+  </si>
+  <si>
+    <t>HD016636</t>
+  </si>
+  <si>
+    <t>Xuân Nghi</t>
+  </si>
+  <si>
+    <t>HD016401</t>
+  </si>
+  <si>
+    <t>116 lý chiêu hoàng, phường Bình Phú</t>
+  </si>
+  <si>
+    <t>Pinky Nguyễn</t>
+  </si>
+  <si>
+    <t>HD015827</t>
+  </si>
+  <si>
+    <t>278 Hoà Bình, hiệp tân</t>
+  </si>
+  <si>
+    <t>HD016687</t>
+  </si>
+  <si>
+    <t>W3320</t>
+  </si>
+  <si>
+    <t>HD016053</t>
+  </si>
+  <si>
+    <t>Kim Kim</t>
+  </si>
+  <si>
+    <t>HD016265</t>
+  </si>
+  <si>
+    <t>206 Tây Thạnh, P Tây Thạnh</t>
+  </si>
+  <si>
+    <t>Phuong Thao</t>
+  </si>
+  <si>
+    <t>HD016211</t>
+  </si>
+  <si>
+    <t>126/5h song hành tân hiệp</t>
+  </si>
+  <si>
+    <t>Trần Trang</t>
+  </si>
+  <si>
+    <t>HD016148</t>
+  </si>
+  <si>
+    <t>T1 08 02, Chung cư Palm Heights, phường Bình Trưng</t>
+  </si>
+  <si>
+    <t>HD016335</t>
+  </si>
+  <si>
+    <t>Mị Nương nguyễn</t>
+  </si>
+  <si>
+    <t>HD016064</t>
+  </si>
+  <si>
+    <t>16 nguyễn Văn kinh Thạnh Mỹ Lợi</t>
+  </si>
+  <si>
+    <t>HD016630</t>
+  </si>
+  <si>
+    <t>HD016476</t>
+  </si>
+  <si>
+    <t>Thu Hiền (Hòa)</t>
+  </si>
+  <si>
+    <t>HD016623</t>
+  </si>
+  <si>
+    <t>73/50 Đình Phong Phú, p. Tăng Nhơn Phú B</t>
+  </si>
+  <si>
+    <t>HD016597</t>
+  </si>
+  <si>
+    <t>Đặng ngọc thuỳ vân</t>
+  </si>
+  <si>
+    <t>HD015121</t>
+  </si>
+  <si>
+    <t>Chung cư an lộc1 p bình trưng</t>
+  </si>
+  <si>
+    <t>Huong Nguyễn</t>
+  </si>
+  <si>
+    <t>HD016369</t>
+  </si>
+  <si>
+    <t>182/9/5 đường 26/3 bình hưng hoà</t>
+  </si>
+  <si>
+    <t>HD015670</t>
+  </si>
+  <si>
+    <t>HD016058</t>
+  </si>
+  <si>
+    <t>Kim Sky</t>
+  </si>
+  <si>
+    <t>HD016086</t>
+  </si>
+  <si>
+    <t>17/8 Lê Thánh Tôn phường Bến Nghé</t>
+  </si>
+  <si>
+    <t>Hienn Nguyen</t>
+  </si>
+  <si>
+    <t>HD015994</t>
+  </si>
+  <si>
+    <t>Số 9, khu phố 1a, phường chánh phú hoà</t>
+  </si>
+  <si>
+    <t>Thu Trần</t>
+  </si>
+  <si>
+    <t>HD016454</t>
+  </si>
+  <si>
+    <t>Khách sạn The Blue Airport 2, 37 Phan Thúc Duyện, Phường 4</t>
+  </si>
+  <si>
+    <t>Mỹ Tâm</t>
+  </si>
+  <si>
+    <t>HD016571</t>
+  </si>
+  <si>
+    <t>342a cách mạng tháng tám</t>
+  </si>
+  <si>
+    <t>Mai Phuong Nguyen</t>
+  </si>
+  <si>
+    <t>HD016678</t>
+  </si>
+  <si>
+    <t>626 Phan Văn Trị, phường Gò Vấp</t>
+  </si>
+  <si>
+    <t>HD016550</t>
+  </si>
+  <si>
+    <t>Kim An</t>
+  </si>
+  <si>
+    <t>HD016560</t>
+  </si>
+  <si>
+    <t>14/27 Hoàng Dư Khương, phường 12</t>
+  </si>
+  <si>
+    <t>Tuyen Huynh</t>
+  </si>
+  <si>
+    <t>HD016287</t>
+  </si>
+  <si>
+    <t>185/9 nguyễn suý tân quý</t>
+  </si>
+  <si>
+    <t>____det____ insta Address: Phnom Penh NHÀ XE KHAI NAM</t>
+  </si>
+  <si>
+    <t>HD016353</t>
+  </si>
+  <si>
+    <t>HD016692</t>
+  </si>
+  <si>
+    <t>63/14 đường số 19 An Khánh</t>
+  </si>
+  <si>
+    <t>HD016643</t>
+  </si>
+  <si>
+    <t>623/43 CMT8 P15</t>
+  </si>
+  <si>
+    <t>Hoài Yên - fb Truc Nguyen</t>
+  </si>
+  <si>
+    <t>HD016102</t>
+  </si>
+  <si>
+    <t>55/24/11 Thành Mỹ, P. Tân Hòa</t>
+  </si>
+  <si>
+    <t>nguyễn ngân</t>
+  </si>
+  <si>
+    <t>HD016599</t>
+  </si>
+  <si>
+    <t>411/93 lê đức thọ p17</t>
+  </si>
+  <si>
+    <t>HD016290</t>
+  </si>
+  <si>
+    <t>Minh Hai ( Bobay Laddavanh )</t>
+  </si>
+  <si>
+    <t>HD016530</t>
+  </si>
+  <si>
+    <t>17, đường số 13, bình hưng hoà</t>
+  </si>
+  <si>
+    <t>kanchana Phnom Penh 017882879</t>
+  </si>
+  <si>
+    <t>HD016585</t>
+  </si>
+  <si>
+    <t>1610 võ văn kiệt bình tiền</t>
+  </si>
+  <si>
+    <t>HD016631</t>
+  </si>
+  <si>
+    <t>Bánh Mì</t>
+  </si>
+  <si>
+    <t>HD016473</t>
+  </si>
+  <si>
+    <t>193/12 bà hat p vườn lài</t>
+  </si>
+  <si>
+    <t>HD016264</t>
+  </si>
+  <si>
+    <t>Kennith Phe Loong Biau</t>
+  </si>
+  <si>
+    <t>HD016517</t>
+  </si>
+  <si>
+    <t>Kennith Phe Loong Biau B2 Duong Số 20, Trung My Tay Ward</t>
+  </si>
+  <si>
+    <t>Huế Vũ</t>
+  </si>
+  <si>
+    <t>HD016682</t>
+  </si>
+  <si>
+    <t>352/9 lê văn quới, phường bình hưng hòa</t>
+  </si>
+  <si>
+    <t>W3189</t>
+  </si>
+  <si>
+    <t>HD016463</t>
+  </si>
+  <si>
+    <t>Huỳnh Hương Nhi</t>
+  </si>
+  <si>
+    <t>HD016644</t>
+  </si>
+  <si>
+    <t>Số 17 đường số 13 phường bình hưng hoà</t>
+  </si>
+  <si>
+    <t>HD016608</t>
+  </si>
+  <si>
+    <t>Thao Doan</t>
+  </si>
+  <si>
+    <t>HD016691</t>
+  </si>
+  <si>
+    <t>81/64 Nguyễn Cửu Vân, p17</t>
+  </si>
+  <si>
+    <t>HD015560</t>
+  </si>
+  <si>
+    <t>29/08 nguyen van đậu. phuong binh loi trung</t>
+  </si>
+  <si>
+    <t>nhận hộ anna</t>
+  </si>
+  <si>
+    <t>HD016191</t>
+  </si>
+  <si>
+    <t>A5-09 THE SILVER STAR, 1564 NGUYỄN HỮU THỌ, PHƯỚC KIỂN</t>
+  </si>
+  <si>
+    <t>Nguyễn My</t>
+  </si>
+  <si>
+    <t>HD016488</t>
+  </si>
+  <si>
+    <t>Căn 1803 Lô A, Chung Cư An Khang, phường An Phú</t>
+  </si>
+  <si>
+    <t>Cẩm Hiền Nguyễn</t>
+  </si>
+  <si>
+    <t>HD016551</t>
+  </si>
+  <si>
+    <t>số 94/10, Trần Khắc Chân, Phường 9</t>
+  </si>
+  <si>
+    <t>HD016617</t>
+  </si>
+  <si>
+    <t>HD016466</t>
+  </si>
+  <si>
+    <t>Bùi Thị Cẩm Dung (inst: zunzung99)</t>
+  </si>
+  <si>
+    <t>HD016569</t>
+  </si>
+  <si>
+    <t>Dii da</t>
+  </si>
+  <si>
+    <t>HD016040</t>
+  </si>
+  <si>
+    <t>Nhà Xe khải nam</t>
+  </si>
+  <si>
+    <t>HD016108</t>
+  </si>
+  <si>
+    <t>240/38/4 Tô ngọc vân, phường Thanh Xuân</t>
+  </si>
+  <si>
+    <t>Khánh An Bùi</t>
+  </si>
+  <si>
+    <t>HD016618</t>
+  </si>
+  <si>
+    <t>64/18 ốp 2 đường Tân Liễu, xã Hưng Long</t>
+  </si>
+  <si>
+    <t>Hý Hý</t>
+  </si>
+  <si>
+    <t>HD016554</t>
+  </si>
+  <si>
+    <t>424 mã lò, Bình Trị Đông A</t>
+  </si>
+  <si>
+    <t>Nguyệt -Nancy truong</t>
+  </si>
+  <si>
+    <t>HD016556</t>
+  </si>
+  <si>
+    <t>57 Nguyễn Quang Bích phường 13</t>
+  </si>
+  <si>
+    <t>Charli ( Inst chari_Importshop )-EN2441</t>
+  </si>
+  <si>
+    <t>HD016215</t>
+  </si>
+  <si>
+    <t>163 Trương Thị Hoa, phương Tân Thới Hiệp</t>
+  </si>
+  <si>
+    <t>401 Quang Trung f10</t>
+  </si>
+  <si>
+    <t>DARAVIN</t>
+  </si>
+  <si>
+    <t>301 Phạm Ngũ Lão, phường Phạm Ngũ Lão</t>
+  </si>
+  <si>
+    <t>HD016319</t>
+  </si>
+  <si>
+    <t>FANG FANG</t>
+  </si>
+  <si>
+    <t>A75/6B/2 Bạch Đằng, Phường 2</t>
+  </si>
+  <si>
+    <t>NGAY 28-4</t>
+  </si>
+  <si>
+    <t>AT 28-04</t>
+  </si>
+  <si>
+    <t>28-04-2026</t>
+  </si>
+  <si>
+    <t>HƯƠNG TRẦN</t>
+  </si>
+  <si>
+    <t>Thanh Thanh Tô</t>
+  </si>
+  <si>
+    <t>HD017096</t>
+  </si>
+  <si>
+    <t>2/16 tân lập p8</t>
+  </si>
+  <si>
+    <t>HD016989</t>
+  </si>
+  <si>
+    <t>Lê Thảo</t>
+  </si>
+  <si>
+    <t>3 Đặng Dung, P Tân Định</t>
+  </si>
+  <si>
+    <t>Vy Nhật Hà note kh gọi được thì nhắn zalo</t>
+  </si>
+  <si>
+    <t>HD016775</t>
+  </si>
+  <si>
+    <t>1619/29 phạm thế hiển phường 6</t>
+  </si>
+  <si>
+    <t>Phương Phan</t>
+  </si>
+  <si>
+    <t>HD017091</t>
+  </si>
+  <si>
+    <t>D4/10 ấp 46, Tân Vĩnh Lộc</t>
+  </si>
+  <si>
+    <t>Thiên Thiên</t>
+  </si>
+  <si>
+    <t>huyền nguyễn</t>
+  </si>
+  <si>
+    <t>HD016308</t>
+  </si>
+  <si>
+    <t>Sunwah White House fb Mzzton</t>
+  </si>
+  <si>
+    <t>90 nguyễn hữu cảnh thạnh mỹ tây</t>
+  </si>
+  <si>
+    <t>Diệu Quyên</t>
+  </si>
+  <si>
+    <t>HD017101</t>
+  </si>
+  <si>
+    <t>242/20 phạm văn bạch p15</t>
+  </si>
+  <si>
+    <t>(Anna Hanh )</t>
+  </si>
+  <si>
+    <t>HD016907</t>
+  </si>
+  <si>
+    <t>HD017134</t>
+  </si>
+  <si>
+    <t>Diễm</t>
+  </si>
+  <si>
+    <t>HD016967</t>
+  </si>
+  <si>
+    <t>HD016592</t>
+  </si>
+  <si>
+    <t>Phạm Mỹ Tiên</t>
+  </si>
+  <si>
+    <t>HD017135</t>
+  </si>
+  <si>
+    <t>thảo fb Nguyễn Bình Phương Trinh</t>
+  </si>
+  <si>
+    <t>HD016407</t>
+  </si>
+  <si>
+    <t>232/111 Vĩnh Khánh f8</t>
+  </si>
+  <si>
+    <t>Nick Loan</t>
+  </si>
+  <si>
+    <t>HD016998</t>
+  </si>
+  <si>
+    <t>HD016824</t>
+  </si>
+  <si>
+    <t>Khánh Vy Đỗ</t>
+  </si>
+  <si>
+    <t>HD017102</t>
+  </si>
+  <si>
+    <t>Thảo Susi</t>
+  </si>
+  <si>
+    <t>HD016982</t>
+  </si>
+  <si>
+    <t>Lynn Pham</t>
+  </si>
+  <si>
+    <t>HD017066</t>
+  </si>
+  <si>
+    <t>2/11 thiên phước phường 9</t>
+  </si>
+  <si>
+    <t>Thanh Vy</t>
+  </si>
+  <si>
+    <t>HD017042</t>
+  </si>
+  <si>
+    <t>167 sư vạn hạnh p3</t>
+  </si>
+  <si>
+    <t>GIA HUY nhận hộ ELIS NGUYỄN ( singapore)</t>
+  </si>
+  <si>
+    <t>HD017110</t>
+  </si>
+  <si>
+    <t>Trang Nabie</t>
+  </si>
+  <si>
+    <t>HD016850</t>
+  </si>
+  <si>
+    <t>HD016826</t>
+  </si>
+  <si>
+    <t>Lê Ngọc Anh</t>
+  </si>
+  <si>
+    <t>HD016990</t>
+  </si>
+  <si>
+    <t>HD017081</t>
+  </si>
+  <si>
+    <t>HD017133</t>
+  </si>
+  <si>
+    <t>HD016798</t>
+  </si>
+  <si>
+    <t>HD017106</t>
+  </si>
+  <si>
+    <t>HD016728</t>
+  </si>
+  <si>
+    <t>HD016977</t>
+  </si>
+  <si>
+    <t>Duyên Huỳnh</t>
+  </si>
+  <si>
+    <t>HD016794</t>
+  </si>
+  <si>
+    <t>Cc tôn thất thuyết phường 1</t>
+  </si>
+  <si>
+    <t>Bé Bờm</t>
+  </si>
+  <si>
+    <t>HD017078</t>
+  </si>
+  <si>
+    <t>167/10 Đào Sư Tích, Phước Kiển</t>
+  </si>
+  <si>
+    <t>Trần Minh Thông</t>
+  </si>
+  <si>
+    <t>H0017097</t>
+  </si>
+  <si>
+    <t>người nhận nana - fb Oanh Tống</t>
+  </si>
+  <si>
+    <t>HD016818</t>
+  </si>
+  <si>
+    <t>24 đường số 6 - tam phú</t>
+  </si>
+  <si>
+    <t>261/26c chu văn an p12</t>
+  </si>
+  <si>
+    <t>22/31/4 đường số 21, Phường 8 (phường Thông Tây Hội mới)</t>
+  </si>
+  <si>
+    <t>HD017084</t>
+  </si>
+  <si>
+    <t>20 đường số 6, linh chiểu</t>
+  </si>
+  <si>
+    <t>HD017028</t>
+  </si>
+  <si>
+    <t>BN182</t>
+  </si>
+  <si>
+    <t>188 Nguyễn Văn Công, P.3</t>
+  </si>
+  <si>
+    <t>90/35 Trần Văn Ơn, Phường Tân Sơn Nhì</t>
+  </si>
+  <si>
+    <t>NGUYỄN MINH DUY</t>
+  </si>
+  <si>
+    <t>HD017045</t>
+  </si>
+  <si>
+    <t>Truc Trieu</t>
+  </si>
+  <si>
+    <t>Số nhà A6, Garden Home Thủ Đức, Đường số 3, QL13, Phường Hiệp Binh Phước</t>
+  </si>
+  <si>
+    <t>536/43/40 âu cơ p. bảy hiền</t>
+  </si>
+  <si>
+    <t>Landmark 1 vinhome central park p thạnh mỹ tây</t>
+  </si>
+  <si>
+    <t>Tòa S501, Vinhome grand park, long thạnh mỹ</t>
+  </si>
+  <si>
+    <t>THƯƠNG 1994</t>
+  </si>
+  <si>
+    <t>485 nguyễn đình chiểu</t>
+  </si>
+  <si>
+    <t>HD016900</t>
+  </si>
+  <si>
+    <t>220/18 Hồ Văn Huê, P.9</t>
+  </si>
+  <si>
+    <t>10/14 âu duong lân p3</t>
+  </si>
+  <si>
+    <t>10/16 đường số 8 phường Bình Hưng Hòa</t>
+  </si>
+  <si>
+    <t>chi - fb Mi Na</t>
+  </si>
+  <si>
+    <t>HD017060</t>
+  </si>
+  <si>
+    <t>V6, Sunrise city south tower 23 nguyễn hữu thọ, phường tân hưng</t>
+  </si>
+  <si>
+    <t>Vũ Thùy Dương</t>
+  </si>
+  <si>
+    <t>96/50/5 đường phạm đăng giảng, bình hưng hòa</t>
+  </si>
+  <si>
+    <t>1707 Phạm thế hiển phường bình đông</t>
+  </si>
+  <si>
+    <t>đơn chuyển AT 28-04</t>
   </si>
 </sst>
 </file>
@@ -8207,7 +9388,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -8245,6 +9426,7 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="49" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -17176,7 +18358,7 @@
         <v>25</v>
       </c>
       <c r="I35" s="7">
-        <f t="shared" ref="I35:I52" si="1">G35-H35</f>
+        <f t="shared" ref="I35:I66" si="1">G35-H35</f>
         <v>-25</v>
       </c>
       <c r="J35" s="7" t="s">
@@ -19090,7 +20272,7 @@
         <v>25</v>
       </c>
       <c r="I35" s="7">
-        <f t="shared" ref="I35:I53" si="1">G35-H35</f>
+        <f t="shared" ref="I35:I66" si="1">G35-H35</f>
         <v>990</v>
       </c>
       <c r="J35" s="7" t="s">
@@ -23660,7 +24842,7 @@
         <v>25</v>
       </c>
       <c r="I67" s="3">
-        <f t="shared" ref="I67:I97" si="2">G67-H67</f>
+        <f t="shared" ref="I67:I98" si="2">G67-H67</f>
         <v>-25</v>
       </c>
       <c r="J67" s="3" t="s">
@@ -26075,7 +27257,7 @@
         <v>25</v>
       </c>
       <c r="I35" s="7">
-        <f t="shared" ref="I35:I59" si="1">G35-H35</f>
+        <f t="shared" ref="I35:I66" si="1">G35-H35</f>
         <v>530</v>
       </c>
       <c r="J35" s="7" t="s">
@@ -28461,7 +29643,7 @@
         <v>25</v>
       </c>
       <c r="I35" s="3">
-        <f t="shared" ref="I35:I56" si="1">G35-H35</f>
+        <f t="shared" ref="I35:I66" si="1">G35-H35</f>
         <v>-25</v>
       </c>
       <c r="J35" s="3" t="s">
@@ -31625,7 +32807,7 @@
         <v>25</v>
       </c>
       <c r="I42" s="7">
-        <f t="shared" ref="I42:I60" si="2">G42-H42</f>
+        <f t="shared" ref="I42:I73" si="2">G42-H42</f>
         <v>660</v>
       </c>
       <c r="J42" s="7" t="s">
@@ -34699,10 +35881,12 @@
   <dimension ref="A1:P53"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="1" max="2" width="9.140625" customWidth="1"/>
     <col min="3" max="3" width="36.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9.5703125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="80" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="9.140625" customWidth="1"/>
     <col min="12" max="12" width="10.42578125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="14.7109375" bestFit="1" customWidth="1"/>
   </cols>
@@ -34788,7 +35972,7 @@
         <v>25</v>
       </c>
       <c r="I3" s="7">
-        <f t="shared" ref="I3:I35" si="0">G3-H3</f>
+        <f t="shared" ref="I3:I34" si="0">G3-H3</f>
         <v>760</v>
       </c>
       <c r="J3" s="7" t="s">
@@ -34809,13 +35993,13 @@
         <v>18</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>2668</v>
+        <v>2558</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>2558</v>
+        <v>2559</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>2669</v>
+        <v>2560</v>
       </c>
       <c r="F4" s="8" t="s">
         <v>208</v>
@@ -34845,13 +36029,13 @@
         <v>18</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>2559</v>
+        <v>2561</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>2560</v>
+        <v>2562</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>2657</v>
+        <v>2563</v>
       </c>
       <c r="F5" s="8" t="s">
         <v>208</v>
@@ -34881,13 +36065,13 @@
         <v>18</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>2561</v>
+        <v>2564</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>2562</v>
+        <v>2565</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>2635</v>
+        <v>2566</v>
       </c>
       <c r="F6" s="4" t="s">
         <v>116</v>
@@ -34923,10 +36107,10 @@
         <v>108</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>2585</v>
+        <v>2567</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>2659</v>
+        <v>2568</v>
       </c>
       <c r="F7" s="8" t="s">
         <v>22</v>
@@ -34938,7 +36122,7 @@
         <v>30</v>
       </c>
       <c r="I7" s="7">
-        <f t="shared" ref="I7" si="1">G7-H7</f>
+        <f t="shared" si="0"/>
         <v>720</v>
       </c>
       <c r="J7" s="7" t="s">
@@ -34956,13 +36140,13 @@
         <v>18</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>2664</v>
+        <v>2569</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>2563</v>
+        <v>2570</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>2564</v>
+        <v>2571</v>
       </c>
       <c r="F8" s="8" t="s">
         <v>143</v>
@@ -34995,10 +36179,10 @@
         <v>952</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>2565</v>
+        <v>2572</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>2638</v>
+        <v>2573</v>
       </c>
       <c r="F9" s="4" t="s">
         <v>46</v>
@@ -35023,7 +36207,7 @@
         <v>2557</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>2643</v>
+        <v>2574</v>
       </c>
     </row>
     <row r="10" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -35031,13 +36215,13 @@
         <v>18</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>2566</v>
+        <v>2575</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>2567</v>
+        <v>2576</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>2637</v>
+        <v>2577</v>
       </c>
       <c r="F10" s="4" t="s">
         <v>116</v>
@@ -35070,10 +36254,10 @@
         <v>699</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>2568</v>
+        <v>2578</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>2653</v>
+        <v>2579</v>
       </c>
       <c r="F11" s="8" t="s">
         <v>2189</v>
@@ -35103,13 +36287,13 @@
         <v>18</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>2570</v>
+        <v>2580</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>2571</v>
+        <v>2581</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>2647</v>
+        <v>2582</v>
       </c>
       <c r="F12" s="8" t="s">
         <v>208</v>
@@ -35139,13 +36323,13 @@
         <v>18</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>2572</v>
+        <v>2583</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>2573</v>
+        <v>2584</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>2574</v>
+        <v>2585</v>
       </c>
       <c r="F13" s="8" t="s">
         <v>2196</v>
@@ -35178,7 +36362,7 @@
         <v>1142</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>2575</v>
+        <v>2586</v>
       </c>
       <c r="E14" s="7" t="s">
         <v>1781</v>
@@ -35214,10 +36398,10 @@
         <v>2004</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>2576</v>
+        <v>2587</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>2646</v>
+        <v>2588</v>
       </c>
       <c r="F15" s="6" t="s">
         <v>2144</v>
@@ -35242,7 +36426,7 @@
         <v>2557</v>
       </c>
       <c r="M15" s="5" t="s">
-        <v>2644</v>
+        <v>2589</v>
       </c>
     </row>
     <row r="16" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -35253,10 +36437,10 @@
         <v>687</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>2577</v>
+        <v>2590</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>2639</v>
+        <v>2591</v>
       </c>
       <c r="F16" s="4" t="s">
         <v>116</v>
@@ -35286,13 +36470,13 @@
         <v>18</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>2630</v>
+        <v>2592</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>2578</v>
+        <v>2593</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>2631</v>
+        <v>2594</v>
       </c>
       <c r="F17" s="4" t="s">
         <v>38</v>
@@ -35322,13 +36506,13 @@
         <v>18</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>2662</v>
+        <v>2595</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>2579</v>
+        <v>2596</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>2580</v>
+        <v>2597</v>
       </c>
       <c r="F18" s="8" t="s">
         <v>2230</v>
@@ -35353,7 +36537,7 @@
         <v>2557</v>
       </c>
       <c r="M18" s="7" t="s">
-        <v>2645</v>
+        <v>2598</v>
       </c>
     </row>
     <row r="19" spans="2:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -35364,7 +36548,7 @@
         <v>1481</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>2581</v>
+        <v>2599</v>
       </c>
       <c r="E19" s="7" t="s">
         <v>1483</v>
@@ -35400,7 +36584,7 @@
         <v>1478</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>2582</v>
+        <v>2600</v>
       </c>
       <c r="E20" s="7" t="s">
         <v>1480</v>
@@ -35436,7 +36620,7 @@
         <v>1237</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>2673</v>
+        <v>2601</v>
       </c>
       <c r="E21" s="7" t="s">
         <v>1239</v>
@@ -35472,7 +36656,7 @@
         <v>1689</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>2629</v>
+        <v>2602</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>1454</v>
@@ -35505,13 +36689,13 @@
         <v>18</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>2583</v>
+        <v>2603</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>2584</v>
+        <v>2604</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>2670</v>
+        <v>2605</v>
       </c>
       <c r="F23" s="8" t="s">
         <v>88</v>
@@ -35541,10 +36725,10 @@
         <v>18</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>2650</v>
+        <v>2606</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>2651</v>
+        <v>2607</v>
       </c>
       <c r="E24" s="7" t="s">
         <v>1252</v>
@@ -35577,13 +36761,13 @@
         <v>18</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>2586</v>
+        <v>2608</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>2587</v>
+        <v>2609</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>2672</v>
+        <v>2610</v>
       </c>
       <c r="F25" s="8" t="s">
         <v>287</v>
@@ -35616,7 +36800,7 @@
         <v>131</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>2588</v>
+        <v>2611</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>133</v>
@@ -35652,10 +36836,10 @@
         <v>1222</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>2589</v>
+        <v>2612</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>2655</v>
+        <v>2613</v>
       </c>
       <c r="F27" s="8" t="s">
         <v>2196</v>
@@ -35688,10 +36872,10 @@
         <v>1615</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>2590</v>
+        <v>2614</v>
       </c>
       <c r="E28" s="7" t="s">
-        <v>2661</v>
+        <v>2615</v>
       </c>
       <c r="F28" s="8" t="s">
         <v>2187</v>
@@ -35721,13 +36905,13 @@
         <v>18</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>2591</v>
+        <v>2616</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>2592</v>
+        <v>2617</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>2658</v>
+        <v>2618</v>
       </c>
       <c r="F29" s="8" t="s">
         <v>2238</v>
@@ -35760,13 +36944,13 @@
         <v>18</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>2593</v>
+        <v>2619</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>2594</v>
+        <v>2620</v>
       </c>
       <c r="E30" s="7" t="s">
-        <v>2660</v>
+        <v>2621</v>
       </c>
       <c r="F30" s="8" t="s">
         <v>2187</v>
@@ -35796,13 +36980,13 @@
         <v>18</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>2595</v>
+        <v>2622</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>2596</v>
+        <v>2623</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>2597</v>
+        <v>2624</v>
       </c>
       <c r="F31" s="4" t="s">
         <v>88</v>
@@ -35835,10 +37019,10 @@
         <v>2518</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>2598</v>
+        <v>2625</v>
       </c>
       <c r="E32" s="7" t="s">
-        <v>2599</v>
+        <v>2626</v>
       </c>
       <c r="F32" s="8" t="s">
         <v>2242</v>
@@ -35874,7 +37058,7 @@
         <v>2234</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>2600</v>
+        <v>2627</v>
       </c>
       <c r="E33" s="7" t="s">
         <v>2236</v>
@@ -35910,13 +37094,13 @@
         <v>18</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>2601</v>
+        <v>2628</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>2602</v>
+        <v>2629</v>
       </c>
       <c r="E34" s="7" t="s">
-        <v>2652</v>
+        <v>2630</v>
       </c>
       <c r="F34" s="8" t="s">
         <v>2230</v>
@@ -35949,7 +37133,7 @@
         <v>488</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>2603</v>
+        <v>2631</v>
       </c>
       <c r="E35" s="7" t="s">
         <v>490</v>
@@ -35964,7 +37148,7 @@
         <v>30</v>
       </c>
       <c r="I35" s="7">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="I35:I66" si="1">G35-H35</f>
         <v>660</v>
       </c>
       <c r="J35" s="7" t="s">
@@ -35982,13 +37166,13 @@
         <v>18</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>2604</v>
+        <v>2632</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>2605</v>
+        <v>2633</v>
       </c>
       <c r="E36" s="7" t="s">
-        <v>2606</v>
+        <v>2634</v>
       </c>
       <c r="F36" s="8" t="s">
         <v>2137</v>
@@ -36000,7 +37184,7 @@
         <v>25</v>
       </c>
       <c r="I36" s="7">
-        <f t="shared" ref="I36:I52" si="2">G36-H36</f>
+        <f t="shared" si="1"/>
         <v>670</v>
       </c>
       <c r="J36" s="7" t="s">
@@ -36018,13 +37202,13 @@
         <v>18</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>2671</v>
+        <v>2635</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>2607</v>
+        <v>2636</v>
       </c>
       <c r="E37" s="7" t="s">
-        <v>2608</v>
+        <v>2637</v>
       </c>
       <c r="F37" s="8" t="s">
         <v>2230</v>
@@ -36036,7 +37220,7 @@
         <v>25</v>
       </c>
       <c r="I37" s="7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>790</v>
       </c>
       <c r="J37" s="7" t="s">
@@ -36054,13 +37238,13 @@
         <v>18</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>2609</v>
+        <v>2638</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>2610</v>
+        <v>2639</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>2611</v>
+        <v>2640</v>
       </c>
       <c r="F38" s="4" t="s">
         <v>46</v>
@@ -36072,7 +37256,7 @@
         <v>25</v>
       </c>
       <c r="I38" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>660</v>
       </c>
       <c r="J38" s="3" t="s">
@@ -36090,13 +37274,13 @@
         <v>18</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>2632</v>
+        <v>2641</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>2633</v>
+        <v>2642</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>2634</v>
+        <v>2643</v>
       </c>
       <c r="F39" s="4" t="s">
         <v>81</v>
@@ -36108,7 +37292,7 @@
         <v>20</v>
       </c>
       <c r="I39" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>660</v>
       </c>
       <c r="J39" s="3" t="s">
@@ -36129,10 +37313,10 @@
         <v>593</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>2612</v>
+        <v>2644</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>2640</v>
+        <v>2645</v>
       </c>
       <c r="F40" s="4" t="s">
         <v>46</v>
@@ -36144,7 +37328,7 @@
         <v>25</v>
       </c>
       <c r="I40" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>695</v>
       </c>
       <c r="J40" s="3" t="s">
@@ -36165,13 +37349,13 @@
         <v>18</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>2665</v>
+        <v>2646</v>
       </c>
       <c r="D41" s="7" t="s">
-        <v>2666</v>
+        <v>2647</v>
       </c>
       <c r="E41" s="7" t="s">
-        <v>2667</v>
+        <v>2648</v>
       </c>
       <c r="F41" s="8" t="s">
         <v>22</v>
@@ -36183,7 +37367,7 @@
         <v>30</v>
       </c>
       <c r="I41" s="7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>660</v>
       </c>
       <c r="J41" s="7" t="s">
@@ -36201,13 +37385,13 @@
         <v>18</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>2613</v>
+        <v>2649</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>2614</v>
+        <v>2650</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>2615</v>
+        <v>2651</v>
       </c>
       <c r="F42" s="4" t="s">
         <v>88</v>
@@ -36219,7 +37403,7 @@
         <v>25</v>
       </c>
       <c r="I42" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>660</v>
       </c>
       <c r="J42" s="3" t="s">
@@ -36237,10 +37421,10 @@
         <v>18</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>2649</v>
+        <v>2652</v>
       </c>
       <c r="D43" s="7" t="s">
-        <v>2616</v>
+        <v>2653</v>
       </c>
       <c r="E43" s="7" t="s">
         <v>789</v>
@@ -36255,7 +37439,7 @@
         <v>25</v>
       </c>
       <c r="I43" s="7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>790</v>
       </c>
       <c r="J43" s="7" t="s">
@@ -36273,13 +37457,13 @@
         <v>18</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>2617</v>
+        <v>2654</v>
       </c>
       <c r="D44" s="7" t="s">
-        <v>2618</v>
+        <v>2655</v>
       </c>
       <c r="E44" s="7" t="s">
-        <v>2663</v>
+        <v>2656</v>
       </c>
       <c r="F44" s="8" t="s">
         <v>143</v>
@@ -36291,7 +37475,7 @@
         <v>35</v>
       </c>
       <c r="I44" s="7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>310</v>
       </c>
       <c r="J44" s="7" t="s">
@@ -36309,13 +37493,13 @@
         <v>18</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>2619</v>
+        <v>2657</v>
       </c>
       <c r="D45" s="7" t="s">
-        <v>2620</v>
+        <v>2658</v>
       </c>
       <c r="E45" s="7" t="s">
-        <v>2654</v>
+        <v>2659</v>
       </c>
       <c r="F45" s="8" t="s">
         <v>2242</v>
@@ -36327,7 +37511,7 @@
         <v>25</v>
       </c>
       <c r="I45" s="7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>850</v>
       </c>
       <c r="J45" s="7" t="s">
@@ -36345,13 +37529,13 @@
         <v>18</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>2641</v>
+        <v>2660</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>2621</v>
+        <v>2661</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>2642</v>
+        <v>2662</v>
       </c>
       <c r="F46" s="4" t="s">
         <v>38</v>
@@ -36363,7 +37547,7 @@
         <v>20</v>
       </c>
       <c r="I46" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>2240</v>
       </c>
       <c r="J46" s="3" t="s">
@@ -36384,13 +37568,13 @@
         <v>18</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>2622</v>
+        <v>2663</v>
       </c>
       <c r="D47" s="7" t="s">
-        <v>2623</v>
+        <v>2664</v>
       </c>
       <c r="E47" s="7" t="s">
-        <v>2648</v>
+        <v>2665</v>
       </c>
       <c r="F47" s="8" t="s">
         <v>2238</v>
@@ -36402,7 +37586,7 @@
         <v>30</v>
       </c>
       <c r="I47" s="7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>660</v>
       </c>
       <c r="J47" s="7" t="s">
@@ -36423,10 +37607,10 @@
         <v>750</v>
       </c>
       <c r="D48" s="7" t="s">
-        <v>2624</v>
+        <v>2666</v>
       </c>
       <c r="E48" s="7" t="s">
-        <v>2625</v>
+        <v>2667</v>
       </c>
       <c r="F48" s="8" t="s">
         <v>2230</v>
@@ -36438,7 +37622,7 @@
         <v>0</v>
       </c>
       <c r="I48" s="7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J48" s="7" t="s">
@@ -36459,13 +37643,13 @@
         <v>18</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>2626</v>
+        <v>2668</v>
       </c>
       <c r="D49" s="7" t="s">
-        <v>2627</v>
+        <v>2669</v>
       </c>
       <c r="E49" s="7" t="s">
-        <v>2656</v>
+        <v>2670</v>
       </c>
       <c r="F49" s="8" t="s">
         <v>2183</v>
@@ -36477,7 +37661,7 @@
         <v>25</v>
       </c>
       <c r="I49" s="7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>900</v>
       </c>
       <c r="J49" s="7" t="s">
@@ -36513,7 +37697,7 @@
         <v>35</v>
       </c>
       <c r="I50" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>3920</v>
       </c>
       <c r="J50" s="3" t="s">
@@ -36537,10 +37721,10 @@
         <v>573</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>2628</v>
+        <v>2671</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>2569</v>
+        <v>2672</v>
       </c>
       <c r="G51" s="3">
         <v>1415</v>
@@ -36549,7 +37733,7 @@
         <v>35</v>
       </c>
       <c r="I51" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1380</v>
       </c>
       <c r="J51" s="3" t="s">
@@ -36573,7 +37757,7 @@
         <v>296</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>2636</v>
+        <v>2673</v>
       </c>
       <c r="F52" s="4" t="s">
         <v>46</v>
@@ -36585,65 +37769,6493 @@
         <v>30</v>
       </c>
       <c r="I52" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K52" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L52" s="3" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="53" spans="1:16" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B53" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="C53" s="11" t="s">
+        <v>1689</v>
+      </c>
+      <c r="D53" s="11" t="s">
+        <v>2535</v>
+      </c>
+      <c r="E53" s="11" t="s">
+        <v>1454</v>
+      </c>
+      <c r="F53" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="G53" s="11">
+        <v>765</v>
+      </c>
+      <c r="H53" s="11">
+        <v>0</v>
+      </c>
+      <c r="I53" s="11">
+        <f t="shared" si="1"/>
+        <v>765</v>
+      </c>
+      <c r="J53" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="K53" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="L53" s="11" t="s">
+        <v>2412</v>
+      </c>
+      <c r="M53" s="11" t="s">
+        <v>429</v>
+      </c>
+      <c r="N53" s="11" t="s">
+        <v>430</v>
+      </c>
+      <c r="O53" s="11" t="s">
+        <v>430</v>
+      </c>
+      <c r="P53" s="11" t="s">
+        <v>431</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1600-000000000000}">
+  <dimension ref="A1:Q126"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="2" width="9.140625" customWidth="1"/>
+    <col min="3" max="3" width="54.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="58.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
+    <col min="7" max="11" width="9.140625" customWidth="1"/>
+    <col min="12" max="12" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B1" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2674</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>259</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>2675</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>261</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>2242</v>
+      </c>
+      <c r="G3" s="9">
+        <v>885</v>
+      </c>
+      <c r="H3" s="9">
+        <v>25</v>
+      </c>
+      <c r="I3" s="9">
+        <f t="shared" ref="I3:I34" si="0">G3-H3</f>
+        <v>860</v>
+      </c>
+      <c r="J3" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="K3" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L3" s="9" t="s">
+        <v>2676</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>2677</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>2678</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>2679</v>
+      </c>
+      <c r="F4" s="10" t="s">
+        <v>2183</v>
+      </c>
+      <c r="G4" s="9">
+        <v>855</v>
+      </c>
+      <c r="H4" s="9">
+        <v>25</v>
+      </c>
+      <c r="I4" s="9">
+        <f t="shared" si="0"/>
+        <v>830</v>
+      </c>
+      <c r="J4" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="K4" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L4" s="9" t="s">
+        <v>2676</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>2680</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>2681</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>2682</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>2133</v>
+      </c>
+      <c r="G5" s="3">
+        <v>2190</v>
+      </c>
+      <c r="H5" s="3">
+        <v>30</v>
+      </c>
+      <c r="I5" s="3">
+        <f t="shared" si="0"/>
+        <v>2160</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>2676</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>2683</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>2684</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>2685</v>
+      </c>
+      <c r="F6" s="10" t="s">
+        <v>2242</v>
+      </c>
+      <c r="G6" s="9">
+        <v>685</v>
+      </c>
+      <c r="H6" s="9">
+        <v>25</v>
+      </c>
+      <c r="I6" s="9">
+        <f t="shared" si="0"/>
+        <v>660</v>
+      </c>
+      <c r="J6" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="K6" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L6" s="9" t="s">
+        <v>2676</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>2686</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>2687</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>2688</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>2137</v>
+      </c>
+      <c r="G7" s="9">
+        <v>0</v>
+      </c>
+      <c r="H7" s="9">
+        <v>25</v>
+      </c>
+      <c r="I7" s="9">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J7" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="K7" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L7" s="9" t="s">
+        <v>2676</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>2689</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>2690</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>2691</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>2133</v>
+      </c>
+      <c r="G8" s="3">
+        <v>1200</v>
+      </c>
+      <c r="H8" s="3">
+        <v>30</v>
+      </c>
+      <c r="I8" s="3">
+        <f t="shared" si="0"/>
+        <v>1170</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>2676</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>2692</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>2693</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>2694</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>2187</v>
+      </c>
+      <c r="G9" s="7">
+        <v>720</v>
+      </c>
+      <c r="H9" s="7">
+        <v>30</v>
+      </c>
+      <c r="I9" s="7">
+        <f t="shared" si="0"/>
+        <v>690</v>
+      </c>
+      <c r="J9" s="7" t="s">
+        <v>2695</v>
+      </c>
+      <c r="K9" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L9" s="7" t="s">
+        <v>2676</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>2696</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>2697</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>2698</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>2144</v>
+      </c>
+      <c r="G10" s="5">
+        <v>890</v>
+      </c>
+      <c r="H10" s="5">
+        <v>30</v>
+      </c>
+      <c r="I10" s="5">
+        <f t="shared" si="0"/>
+        <v>860</v>
+      </c>
+      <c r="J10" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="K10" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L10" s="5" t="s">
+        <v>2676</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>1782</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>2699</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>2700</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="G11" s="3">
+        <v>760</v>
+      </c>
+      <c r="H11" s="3">
+        <v>20</v>
+      </c>
+      <c r="I11" s="3">
+        <f t="shared" si="0"/>
+        <v>740</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K11" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L11" s="3" t="s">
+        <v>2676</v>
+      </c>
+      <c r="M11" s="3" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>1544</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>2701</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>1546</v>
+      </c>
+      <c r="F12" s="10" t="s">
+        <v>2473</v>
+      </c>
+      <c r="G12" s="9">
+        <v>915</v>
+      </c>
+      <c r="H12" s="9">
+        <v>25</v>
+      </c>
+      <c r="I12" s="9">
+        <f t="shared" si="0"/>
+        <v>890</v>
+      </c>
+      <c r="J12" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="K12" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L12" s="9" t="s">
+        <v>2676</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>2702</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>2703</v>
+      </c>
+      <c r="E13" s="9" t="s">
+        <v>2704</v>
+      </c>
+      <c r="F13" s="10" t="s">
+        <v>2183</v>
+      </c>
+      <c r="G13" s="9">
+        <v>0</v>
+      </c>
+      <c r="H13" s="9">
+        <v>25</v>
+      </c>
+      <c r="I13" s="9">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J13" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="K13" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L13" s="9" t="s">
+        <v>2676</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>2705</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>2706</v>
+      </c>
+      <c r="E14" s="9" t="s">
+        <v>2707</v>
+      </c>
+      <c r="F14" s="10" t="s">
+        <v>2137</v>
+      </c>
+      <c r="G14" s="9">
+        <v>815</v>
+      </c>
+      <c r="H14" s="9">
+        <v>25</v>
+      </c>
+      <c r="I14" s="9">
+        <f t="shared" si="0"/>
+        <v>790</v>
+      </c>
+      <c r="J14" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="K14" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L14" s="9" t="s">
+        <v>2676</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>2708</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>2709</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>2710</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="G15" s="3">
+        <v>765</v>
+      </c>
+      <c r="H15" s="3">
+        <v>25</v>
+      </c>
+      <c r="I15" s="3">
+        <f t="shared" si="0"/>
+        <v>740</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L15" s="3" t="s">
+        <v>2676</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>2711</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>2712</v>
+      </c>
+      <c r="E16" s="9" t="s">
+        <v>2713</v>
+      </c>
+      <c r="F16" s="10" t="s">
+        <v>2137</v>
+      </c>
+      <c r="G16" s="9">
+        <v>1475</v>
+      </c>
+      <c r="H16" s="9">
+        <v>25</v>
+      </c>
+      <c r="I16" s="9">
+        <f t="shared" si="0"/>
+        <v>1450</v>
+      </c>
+      <c r="J16" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="K16" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L16" s="9" t="s">
+        <v>2676</v>
+      </c>
+    </row>
+    <row r="17" spans="2:16" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>2635</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>2714</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>2637</v>
+      </c>
+      <c r="F17" s="8" t="s">
+        <v>2230</v>
+      </c>
+      <c r="G17" s="7">
+        <v>815</v>
+      </c>
+      <c r="H17" s="7">
+        <v>25</v>
+      </c>
+      <c r="I17" s="7">
+        <f t="shared" si="0"/>
+        <v>790</v>
+      </c>
+      <c r="J17" s="7" t="s">
+        <v>2695</v>
+      </c>
+      <c r="K17" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L17" s="7" t="s">
+        <v>2676</v>
+      </c>
+    </row>
+    <row r="18" spans="2:16" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>2715</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>2716</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>348</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>2144</v>
+      </c>
+      <c r="G18" s="5">
+        <v>820</v>
+      </c>
+      <c r="H18" s="5">
+        <v>30</v>
+      </c>
+      <c r="I18" s="5">
+        <f t="shared" si="0"/>
+        <v>790</v>
+      </c>
+      <c r="J18" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="K18" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L18" s="5" t="s">
+        <v>2676</v>
+      </c>
+    </row>
+    <row r="19" spans="2:16" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>2717</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>2718</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>2719</v>
+      </c>
+      <c r="F19" s="8" t="s">
+        <v>2187</v>
+      </c>
+      <c r="G19" s="7">
+        <v>770</v>
+      </c>
+      <c r="H19" s="7">
+        <v>30</v>
+      </c>
+      <c r="I19" s="7">
+        <f t="shared" si="0"/>
+        <v>740</v>
+      </c>
+      <c r="J19" s="7" t="s">
+        <v>2695</v>
+      </c>
+      <c r="K19" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L19" s="7" t="s">
+        <v>2676</v>
+      </c>
+    </row>
+    <row r="20" spans="2:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>2720</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>2721</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>2722</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3">
+        <v>25</v>
+      </c>
+      <c r="I20" s="3">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L20" s="3" t="s">
+        <v>2676</v>
+      </c>
+    </row>
+    <row r="21" spans="2:16" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C21" s="9" t="s">
+        <v>2723</v>
+      </c>
+      <c r="D21" s="9" t="s">
+        <v>2724</v>
+      </c>
+      <c r="E21" s="9" t="s">
+        <v>2725</v>
+      </c>
+      <c r="F21" s="10" t="s">
+        <v>2137</v>
+      </c>
+      <c r="G21" s="9">
+        <v>765</v>
+      </c>
+      <c r="H21" s="9">
+        <v>25</v>
+      </c>
+      <c r="I21" s="9">
+        <f t="shared" si="0"/>
+        <v>740</v>
+      </c>
+      <c r="J21" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="K21" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L21" s="9" t="s">
+        <v>2676</v>
+      </c>
+    </row>
+    <row r="22" spans="2:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>2726</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>2727</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>2728</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>2133</v>
+      </c>
+      <c r="G22" s="3">
+        <v>870</v>
+      </c>
+      <c r="H22" s="3">
+        <v>30</v>
+      </c>
+      <c r="I22" s="3">
+        <f t="shared" si="0"/>
+        <v>840</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L22" s="3" t="s">
+        <v>2676</v>
+      </c>
+    </row>
+    <row r="23" spans="2:16" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>2729</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>2730</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>2731</v>
+      </c>
+      <c r="F23" s="8" t="s">
+        <v>2238</v>
+      </c>
+      <c r="G23" s="7">
+        <v>480</v>
+      </c>
+      <c r="H23" s="7">
+        <v>30</v>
+      </c>
+      <c r="I23" s="7">
+        <f t="shared" si="0"/>
+        <v>450</v>
+      </c>
+      <c r="J23" s="7" t="s">
+        <v>2695</v>
+      </c>
+      <c r="K23" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L23" s="7" t="s">
+        <v>2676</v>
+      </c>
+      <c r="M23" s="7" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="24" spans="2:16" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>2732</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>2733</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>2734</v>
+      </c>
+      <c r="F24" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="G24" s="7">
+        <v>0</v>
+      </c>
+      <c r="H24" s="7">
+        <v>25</v>
+      </c>
+      <c r="I24" s="7">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J24" s="7" t="s">
+        <v>2695</v>
+      </c>
+      <c r="K24" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L24" s="7" t="s">
+        <v>2676</v>
+      </c>
+    </row>
+    <row r="25" spans="2:16" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>2481</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>2735</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>2483</v>
+      </c>
+      <c r="F25" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G25" s="7">
+        <v>780</v>
+      </c>
+      <c r="H25" s="7">
+        <v>30</v>
+      </c>
+      <c r="I25" s="7">
+        <f t="shared" si="0"/>
+        <v>750</v>
+      </c>
+      <c r="J25" s="7" t="s">
+        <v>2695</v>
+      </c>
+      <c r="K25" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L25" s="7" t="s">
+        <v>2676</v>
+      </c>
+    </row>
+    <row r="26" spans="2:16" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>1693</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>2736</v>
+      </c>
+      <c r="E26" s="7" t="s">
+        <v>1695</v>
+      </c>
+      <c r="F26" s="8" t="s">
+        <v>2187</v>
+      </c>
+      <c r="G26" s="7">
+        <v>690</v>
+      </c>
+      <c r="H26" s="7">
+        <v>30</v>
+      </c>
+      <c r="I26" s="7">
+        <f t="shared" si="0"/>
+        <v>660</v>
+      </c>
+      <c r="J26" s="7" t="s">
+        <v>2695</v>
+      </c>
+      <c r="K26" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L26" s="7" t="s">
+        <v>2676</v>
+      </c>
+    </row>
+    <row r="27" spans="2:16" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>2737</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>2738</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>2739</v>
+      </c>
+      <c r="F27" s="6" t="s">
+        <v>2144</v>
+      </c>
+      <c r="G27" s="5">
+        <v>0</v>
+      </c>
+      <c r="H27" s="5">
+        <v>30</v>
+      </c>
+      <c r="I27" s="5">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J27" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="K27" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L27" s="5" t="s">
+        <v>2676</v>
+      </c>
+    </row>
+    <row r="28" spans="2:16" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>2740</v>
+      </c>
+      <c r="E28" s="7" t="s">
+        <v>2741</v>
+      </c>
+      <c r="F28" s="8" t="s">
+        <v>2189</v>
+      </c>
+      <c r="G28" s="7">
+        <v>720</v>
+      </c>
+      <c r="H28" s="7">
+        <v>30</v>
+      </c>
+      <c r="I28" s="7">
+        <f t="shared" si="0"/>
+        <v>690</v>
+      </c>
+      <c r="J28" s="7" t="s">
+        <v>2695</v>
+      </c>
+      <c r="K28" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L28" s="7" t="s">
+        <v>2676</v>
+      </c>
+    </row>
+    <row r="29" spans="2:16" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C29" s="9" t="s">
+        <v>2742</v>
+      </c>
+      <c r="D29" s="9" t="s">
+        <v>2743</v>
+      </c>
+      <c r="E29" s="9" t="s">
+        <v>2744</v>
+      </c>
+      <c r="F29" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="G29" s="9">
+        <v>685</v>
+      </c>
+      <c r="H29" s="9">
+        <v>25</v>
+      </c>
+      <c r="I29" s="9">
+        <f t="shared" si="0"/>
+        <v>660</v>
+      </c>
+      <c r="J29" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="K29" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L29" s="9" t="s">
+        <v>2676</v>
+      </c>
+    </row>
+    <row r="30" spans="2:16" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="C30" s="11" t="s">
+        <v>2745</v>
+      </c>
+      <c r="D30" s="11" t="s">
+        <v>2746</v>
+      </c>
+      <c r="E30" s="11" t="s">
+        <v>2747</v>
+      </c>
+      <c r="F30" s="15" t="s">
+        <v>1469</v>
+      </c>
+      <c r="G30" s="11">
+        <v>1760</v>
+      </c>
+      <c r="H30" s="11">
+        <v>0</v>
+      </c>
+      <c r="I30" s="11">
+        <f t="shared" si="0"/>
+        <v>1760</v>
+      </c>
+      <c r="J30" s="11" t="s">
+        <v>427</v>
+      </c>
+      <c r="K30" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="L30" s="11" t="s">
+        <v>2676</v>
+      </c>
+      <c r="M30" s="11" t="s">
+        <v>1470</v>
+      </c>
+      <c r="N30" s="11" t="s">
+        <v>430</v>
+      </c>
+      <c r="P30" s="11" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="31" spans="2:16" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B31" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>1624</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>2748</v>
+      </c>
+      <c r="E31" s="7" t="s">
+        <v>1626</v>
+      </c>
+      <c r="F31" s="8" t="s">
+        <v>2230</v>
+      </c>
+      <c r="G31" s="7">
+        <v>0</v>
+      </c>
+      <c r="H31" s="7">
+        <v>25</v>
+      </c>
+      <c r="I31" s="7">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J31" s="7" t="s">
+        <v>2695</v>
+      </c>
+      <c r="K31" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L31" s="7" t="s">
+        <v>2676</v>
+      </c>
+    </row>
+    <row r="32" spans="2:16" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B32" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C32" s="9" t="s">
+        <v>2749</v>
+      </c>
+      <c r="D32" s="9" t="s">
+        <v>2750</v>
+      </c>
+      <c r="E32" s="9" t="s">
+        <v>2751</v>
+      </c>
+      <c r="F32" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="G32" s="9">
+        <v>765</v>
+      </c>
+      <c r="H32" s="9">
+        <v>25</v>
+      </c>
+      <c r="I32" s="9">
+        <f t="shared" si="0"/>
+        <v>740</v>
+      </c>
+      <c r="J32" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="K32" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L32" s="9" t="s">
+        <v>2676</v>
+      </c>
+    </row>
+    <row r="33" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B33" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>2752</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>2753</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>2754</v>
+      </c>
+      <c r="F33" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="G33" s="3">
+        <v>750</v>
+      </c>
+      <c r="H33" s="3">
+        <v>30</v>
+      </c>
+      <c r="I33" s="3">
+        <f t="shared" si="0"/>
+        <v>720</v>
+      </c>
+      <c r="J33" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K33" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L33" s="3" t="s">
+        <v>2676</v>
+      </c>
+    </row>
+    <row r="34" spans="2:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B34" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C34" s="9" t="s">
+        <v>2755</v>
+      </c>
+      <c r="D34" s="9" t="s">
+        <v>2756</v>
+      </c>
+      <c r="E34" s="9" t="s">
+        <v>2757</v>
+      </c>
+      <c r="F34" s="10" t="s">
+        <v>2196</v>
+      </c>
+      <c r="G34" s="9">
+        <v>765</v>
+      </c>
+      <c r="H34" s="9">
+        <v>25</v>
+      </c>
+      <c r="I34" s="9">
+        <f t="shared" si="0"/>
+        <v>740</v>
+      </c>
+      <c r="J34" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="K34" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L34" s="9" t="s">
+        <v>2676</v>
+      </c>
+    </row>
+    <row r="35" spans="2:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B35" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C35" s="9" t="s">
+        <v>2758</v>
+      </c>
+      <c r="D35" s="9" t="s">
+        <v>2759</v>
+      </c>
+      <c r="E35" s="9" t="s">
+        <v>2760</v>
+      </c>
+      <c r="F35" s="10" t="s">
+        <v>2473</v>
+      </c>
+      <c r="G35" s="9">
+        <v>375</v>
+      </c>
+      <c r="H35" s="9">
+        <v>25</v>
+      </c>
+      <c r="I35" s="9">
+        <f t="shared" ref="I35:I66" si="1">G35-H35</f>
+        <v>350</v>
+      </c>
+      <c r="J35" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="K35" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L35" s="9" t="s">
+        <v>2676</v>
+      </c>
+    </row>
+    <row r="36" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B36" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>2761</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>2762</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>2763</v>
+      </c>
+      <c r="F36" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="G36" s="3">
+        <v>690</v>
+      </c>
+      <c r="H36" s="3">
+        <v>30</v>
+      </c>
+      <c r="I36" s="3">
+        <f t="shared" si="1"/>
+        <v>660</v>
+      </c>
+      <c r="J36" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K36" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L36" s="3" t="s">
+        <v>2676</v>
+      </c>
+    </row>
+    <row r="37" spans="2:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B37" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C37" s="7" t="s">
+        <v>2764</v>
+      </c>
+      <c r="D37" s="7" t="s">
+        <v>2765</v>
+      </c>
+      <c r="E37" s="7" t="s">
+        <v>2766</v>
+      </c>
+      <c r="F37" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="G37" s="7">
+        <v>375</v>
+      </c>
+      <c r="H37" s="7">
+        <v>25</v>
+      </c>
+      <c r="I37" s="7">
+        <f t="shared" si="1"/>
+        <v>350</v>
+      </c>
+      <c r="J37" s="7" t="s">
+        <v>2695</v>
+      </c>
+      <c r="K37" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L37" s="7" t="s">
+        <v>2676</v>
+      </c>
+    </row>
+    <row r="38" spans="2:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B38" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C38" s="7" t="s">
+        <v>1201</v>
+      </c>
+      <c r="D38" s="7" t="s">
+        <v>2767</v>
+      </c>
+      <c r="E38" s="7" t="s">
+        <v>1203</v>
+      </c>
+      <c r="F38" s="8" t="s">
+        <v>2187</v>
+      </c>
+      <c r="G38" s="7">
+        <v>2110</v>
+      </c>
+      <c r="H38" s="7">
+        <v>35</v>
+      </c>
+      <c r="I38" s="7">
+        <f t="shared" si="1"/>
+        <v>2075</v>
+      </c>
+      <c r="J38" s="7" t="s">
+        <v>2695</v>
+      </c>
+      <c r="K38" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L38" s="7" t="s">
+        <v>2676</v>
+      </c>
+      <c r="M38" s="7" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="39" spans="2:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B39" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C39" s="9" t="s">
+        <v>2768</v>
+      </c>
+      <c r="D39" s="9" t="s">
+        <v>2769</v>
+      </c>
+      <c r="E39" s="9" t="s">
+        <v>2770</v>
+      </c>
+      <c r="F39" s="10" t="s">
+        <v>2473</v>
+      </c>
+      <c r="G39" s="9">
+        <v>1145</v>
+      </c>
+      <c r="H39" s="9">
+        <v>25</v>
+      </c>
+      <c r="I39" s="9">
+        <f t="shared" si="1"/>
+        <v>1120</v>
+      </c>
+      <c r="J39" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="K39" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L39" s="9" t="s">
+        <v>2676</v>
+      </c>
+    </row>
+    <row r="40" spans="2:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B40" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C40" s="7" t="s">
+        <v>2771</v>
+      </c>
+      <c r="D40" s="7" t="s">
+        <v>2772</v>
+      </c>
+      <c r="E40" s="7" t="s">
+        <v>2773</v>
+      </c>
+      <c r="F40" s="8" t="s">
+        <v>2187</v>
+      </c>
+      <c r="G40" s="7">
+        <v>0</v>
+      </c>
+      <c r="H40" s="7">
+        <v>30</v>
+      </c>
+      <c r="I40" s="7">
+        <f t="shared" si="1"/>
+        <v>-30</v>
+      </c>
+      <c r="J40" s="7" t="s">
+        <v>2695</v>
+      </c>
+      <c r="K40" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L40" s="7" t="s">
+        <v>2676</v>
+      </c>
+    </row>
+    <row r="41" spans="2:13" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B41" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C41" s="5" t="s">
+        <v>2774</v>
+      </c>
+      <c r="D41" s="5" t="s">
+        <v>2775</v>
+      </c>
+      <c r="E41" s="5" t="s">
+        <v>2776</v>
+      </c>
+      <c r="F41" s="6" t="s">
+        <v>2144</v>
+      </c>
+      <c r="G41" s="5">
+        <v>770</v>
+      </c>
+      <c r="H41" s="5">
+        <v>30</v>
+      </c>
+      <c r="I41" s="5">
+        <f t="shared" si="1"/>
+        <v>740</v>
+      </c>
+      <c r="J41" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="K41" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L41" s="5" t="s">
+        <v>2676</v>
+      </c>
+    </row>
+    <row r="42" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B42" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>2777</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>2778</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>2779</v>
+      </c>
+      <c r="F42" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="G42" s="3">
+        <v>715</v>
+      </c>
+      <c r="H42" s="3">
+        <v>25</v>
+      </c>
+      <c r="I42" s="3">
+        <f t="shared" si="1"/>
+        <v>690</v>
+      </c>
+      <c r="J42" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K42" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L42" s="3" t="s">
+        <v>2676</v>
+      </c>
+    </row>
+    <row r="43" spans="2:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B43" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C43" s="9" t="s">
+        <v>2780</v>
+      </c>
+      <c r="D43" s="9" t="s">
+        <v>2781</v>
+      </c>
+      <c r="E43" s="9" t="s">
+        <v>2782</v>
+      </c>
+      <c r="F43" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="G43" s="9">
+        <v>0</v>
+      </c>
+      <c r="H43" s="9">
+        <v>25</v>
+      </c>
+      <c r="I43" s="9">
+        <f t="shared" si="1"/>
+        <v>-25</v>
+      </c>
+      <c r="J43" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="K43" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L43" s="9" t="s">
+        <v>2676</v>
+      </c>
+    </row>
+    <row r="44" spans="2:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B44" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C44" s="7" t="s">
+        <v>2783</v>
+      </c>
+      <c r="D44" s="7" t="s">
+        <v>2784</v>
+      </c>
+      <c r="E44" s="7" t="s">
+        <v>2785</v>
+      </c>
+      <c r="F44" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G44" s="7">
+        <v>0</v>
+      </c>
+      <c r="H44" s="7">
+        <v>30</v>
+      </c>
+      <c r="I44" s="7">
+        <f t="shared" si="1"/>
+        <v>-30</v>
+      </c>
+      <c r="J44" s="7" t="s">
+        <v>2695</v>
+      </c>
+      <c r="K44" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L44" s="7" t="s">
+        <v>2676</v>
+      </c>
+    </row>
+    <row r="45" spans="2:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B45" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C45" s="9" t="s">
+        <v>2786</v>
+      </c>
+      <c r="D45" s="9" t="s">
+        <v>2787</v>
+      </c>
+      <c r="E45" s="9" t="s">
+        <v>2788</v>
+      </c>
+      <c r="F45" s="10" t="s">
+        <v>2473</v>
+      </c>
+      <c r="G45" s="9">
+        <v>885</v>
+      </c>
+      <c r="H45" s="9">
+        <v>25</v>
+      </c>
+      <c r="I45" s="9">
+        <f t="shared" si="1"/>
+        <v>860</v>
+      </c>
+      <c r="J45" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="K45" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L45" s="9" t="s">
+        <v>2676</v>
+      </c>
+    </row>
+    <row r="46" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B46" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>2789</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>2790</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>2791</v>
+      </c>
+      <c r="F46" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="G46" s="3">
+        <v>880</v>
+      </c>
+      <c r="H46" s="3">
+        <v>20</v>
+      </c>
+      <c r="I46" s="3">
+        <f t="shared" si="1"/>
+        <v>860</v>
+      </c>
+      <c r="J46" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K46" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L46" s="3" t="s">
+        <v>2676</v>
+      </c>
+    </row>
+    <row r="47" spans="2:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B47" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C47" s="7" t="s">
+        <v>2792</v>
+      </c>
+      <c r="D47" s="7" t="s">
+        <v>2793</v>
+      </c>
+      <c r="E47" s="7" t="s">
+        <v>2794</v>
+      </c>
+      <c r="F47" s="8" t="s">
+        <v>2187</v>
+      </c>
+      <c r="G47" s="7">
+        <v>820</v>
+      </c>
+      <c r="H47" s="7">
+        <v>30</v>
+      </c>
+      <c r="I47" s="7">
+        <f t="shared" si="1"/>
+        <v>790</v>
+      </c>
+      <c r="J47" s="7" t="s">
+        <v>2695</v>
+      </c>
+      <c r="K47" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L47" s="7" t="s">
+        <v>2676</v>
+      </c>
+    </row>
+    <row r="48" spans="2:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B48" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C48" s="7" t="s">
+        <v>2795</v>
+      </c>
+      <c r="D48" s="7" t="s">
+        <v>2796</v>
+      </c>
+      <c r="E48" s="7" t="s">
+        <v>2797</v>
+      </c>
+      <c r="F48" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="G48" s="7">
+        <v>965</v>
+      </c>
+      <c r="H48" s="7">
+        <v>35</v>
+      </c>
+      <c r="I48" s="7">
+        <f t="shared" si="1"/>
+        <v>930</v>
+      </c>
+      <c r="J48" s="7" t="s">
+        <v>2695</v>
+      </c>
+      <c r="K48" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L48" s="7" t="s">
+        <v>2676</v>
+      </c>
+    </row>
+    <row r="49" spans="2:16" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B49" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C49" s="9" t="s">
+        <v>2798</v>
+      </c>
+      <c r="D49" s="9" t="s">
+        <v>2799</v>
+      </c>
+      <c r="E49" s="9" t="s">
+        <v>1830</v>
+      </c>
+      <c r="F49" s="10" t="s">
+        <v>2242</v>
+      </c>
+      <c r="G49" s="9">
+        <v>1020</v>
+      </c>
+      <c r="H49" s="9">
+        <v>0</v>
+      </c>
+      <c r="I49" s="9">
+        <f t="shared" si="1"/>
+        <v>1020</v>
+      </c>
+      <c r="J49" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="K49" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L49" s="9" t="s">
+        <v>2676</v>
+      </c>
+      <c r="M49" s="9" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="50" spans="2:16" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B50" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C50" s="7" t="s">
+        <v>2800</v>
+      </c>
+      <c r="D50" s="7" t="s">
+        <v>2801</v>
+      </c>
+      <c r="E50" s="7" t="s">
+        <v>2802</v>
+      </c>
+      <c r="F50" s="8" t="s">
+        <v>2359</v>
+      </c>
+      <c r="G50" s="7">
+        <v>915</v>
+      </c>
+      <c r="H50" s="7">
+        <v>25</v>
+      </c>
+      <c r="I50" s="7">
+        <f t="shared" si="1"/>
+        <v>890</v>
+      </c>
+      <c r="J50" s="7" t="s">
+        <v>2695</v>
+      </c>
+      <c r="K50" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L50" s="7" t="s">
+        <v>2676</v>
+      </c>
+    </row>
+    <row r="51" spans="2:16" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B51" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="C51" s="11" t="s">
+        <v>2803</v>
+      </c>
+      <c r="D51" s="11" t="s">
+        <v>2804</v>
+      </c>
+      <c r="E51" s="11" t="s">
+        <v>2805</v>
+      </c>
+      <c r="F51" s="15" t="s">
+        <v>2806</v>
+      </c>
+      <c r="G51" s="11">
+        <v>490</v>
+      </c>
+      <c r="H51" s="11">
+        <v>0</v>
+      </c>
+      <c r="I51" s="11">
+        <f t="shared" si="1"/>
+        <v>490</v>
+      </c>
+      <c r="J51" s="11" t="s">
+        <v>427</v>
+      </c>
+      <c r="K51" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="L51" s="11" t="s">
+        <v>2676</v>
+      </c>
+      <c r="M51" s="11" t="s">
+        <v>1470</v>
+      </c>
+      <c r="N51" s="11" t="s">
+        <v>430</v>
+      </c>
+      <c r="P51" s="11" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="52" spans="2:16" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B52" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C52" s="7" t="s">
+        <v>2807</v>
+      </c>
+      <c r="D52" s="7" t="s">
+        <v>2808</v>
+      </c>
+      <c r="E52" s="7" t="s">
+        <v>2809</v>
+      </c>
+      <c r="F52" s="8" t="s">
+        <v>2238</v>
+      </c>
+      <c r="G52" s="7">
+        <v>0</v>
+      </c>
+      <c r="H52" s="7">
+        <v>35</v>
+      </c>
+      <c r="I52" s="7">
+        <f t="shared" si="1"/>
+        <v>-35</v>
+      </c>
+      <c r="J52" s="7" t="s">
+        <v>2695</v>
+      </c>
+      <c r="K52" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L52" s="7" t="s">
+        <v>2676</v>
+      </c>
+    </row>
+    <row r="53" spans="2:16" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B53" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C53" s="5" t="s">
+        <v>2810</v>
+      </c>
+      <c r="D53" s="5" t="s">
+        <v>2811</v>
+      </c>
+      <c r="E53" s="5" t="s">
+        <v>2812</v>
+      </c>
+      <c r="F53" s="6" t="s">
+        <v>2144</v>
+      </c>
+      <c r="G53" s="5">
+        <v>820</v>
+      </c>
+      <c r="H53" s="5">
+        <v>30</v>
+      </c>
+      <c r="I53" s="5">
+        <f t="shared" si="1"/>
+        <v>790</v>
+      </c>
+      <c r="J53" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="K53" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L53" s="5" t="s">
+        <v>2676</v>
+      </c>
+    </row>
+    <row r="54" spans="2:16" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B54" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C54" s="9" t="s">
+        <v>2813</v>
+      </c>
+      <c r="D54" s="9" t="s">
+        <v>2814</v>
+      </c>
+      <c r="E54" s="9" t="s">
+        <v>2815</v>
+      </c>
+      <c r="F54" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="G54" s="9">
+        <v>0</v>
+      </c>
+      <c r="H54" s="9">
+        <v>25</v>
+      </c>
+      <c r="I54" s="9">
+        <f t="shared" si="1"/>
+        <v>-25</v>
+      </c>
+      <c r="J54" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="K54" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L54" s="9" t="s">
+        <v>2676</v>
+      </c>
+    </row>
+    <row r="55" spans="2:16" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B55" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C55" s="9" t="s">
+        <v>2816</v>
+      </c>
+      <c r="D55" s="9" t="s">
+        <v>2817</v>
+      </c>
+      <c r="E55" s="9" t="s">
+        <v>2818</v>
+      </c>
+      <c r="F55" s="10" t="s">
+        <v>2196</v>
+      </c>
+      <c r="G55" s="9">
+        <v>885</v>
+      </c>
+      <c r="H55" s="9">
+        <v>25</v>
+      </c>
+      <c r="I55" s="9">
+        <f t="shared" si="1"/>
+        <v>860</v>
+      </c>
+      <c r="J55" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="K55" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L55" s="9" t="s">
+        <v>2676</v>
+      </c>
+    </row>
+    <row r="56" spans="2:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B56" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>1782</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>2819</v>
+      </c>
+      <c r="E56" s="3" t="s">
+        <v>2700</v>
+      </c>
+      <c r="F56" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="G56" s="3">
+        <v>440</v>
+      </c>
+      <c r="H56" s="3">
+        <v>0</v>
+      </c>
+      <c r="I56" s="3">
+        <f t="shared" si="1"/>
+        <v>440</v>
+      </c>
+      <c r="J56" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K56" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L56" s="3" t="s">
+        <v>2676</v>
+      </c>
+      <c r="M56" s="3" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="57" spans="2:16" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B57" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C57" s="7" t="s">
+        <v>2820</v>
+      </c>
+      <c r="D57" s="7" t="s">
+        <v>2821</v>
+      </c>
+      <c r="E57" s="7" t="s">
+        <v>2822</v>
+      </c>
+      <c r="F57" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="G57" s="7">
+        <v>1285</v>
+      </c>
+      <c r="H57" s="7">
+        <v>25</v>
+      </c>
+      <c r="I57" s="7">
+        <f t="shared" si="1"/>
+        <v>1260</v>
+      </c>
+      <c r="J57" s="7" t="s">
+        <v>2695</v>
+      </c>
+      <c r="K57" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L57" s="7" t="s">
+        <v>2676</v>
+      </c>
+    </row>
+    <row r="58" spans="2:16" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B58" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C58" s="7" t="s">
+        <v>1615</v>
+      </c>
+      <c r="D58" s="7" t="s">
+        <v>2823</v>
+      </c>
+      <c r="E58" s="7" t="s">
+        <v>2824</v>
+      </c>
+      <c r="F58" s="8" t="s">
+        <v>2187</v>
+      </c>
+      <c r="G58" s="7">
+        <v>30</v>
+      </c>
+      <c r="H58" s="7">
+        <v>30</v>
+      </c>
+      <c r="I58" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J58" s="7" t="s">
+        <v>2695</v>
+      </c>
+      <c r="K58" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L58" s="7" t="s">
+        <v>2676</v>
+      </c>
+      <c r="M58" s="7" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="59" spans="2:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B59" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>2825</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>2826</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>2827</v>
+      </c>
+      <c r="F59" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="G59" s="3">
+        <v>1830</v>
+      </c>
+      <c r="H59" s="3">
+        <v>20</v>
+      </c>
+      <c r="I59" s="3">
+        <f t="shared" si="1"/>
+        <v>1810</v>
+      </c>
+      <c r="J59" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K59" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L59" s="3" t="s">
+        <v>2676</v>
+      </c>
+    </row>
+    <row r="60" spans="2:16" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B60" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C60" s="9" t="s">
+        <v>2828</v>
+      </c>
+      <c r="D60" s="9" t="s">
+        <v>2829</v>
+      </c>
+      <c r="E60" s="9" t="s">
+        <v>2830</v>
+      </c>
+      <c r="F60" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="G60" s="9">
+        <v>710</v>
+      </c>
+      <c r="H60" s="9">
+        <v>20</v>
+      </c>
+      <c r="I60" s="9">
+        <f t="shared" si="1"/>
+        <v>690</v>
+      </c>
+      <c r="J60" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="K60" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L60" s="9" t="s">
+        <v>2676</v>
+      </c>
+    </row>
+    <row r="61" spans="2:16" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B61" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C61" s="7" t="s">
+        <v>1320</v>
+      </c>
+      <c r="D61" s="7" t="s">
+        <v>2831</v>
+      </c>
+      <c r="E61" s="7" t="s">
+        <v>1322</v>
+      </c>
+      <c r="F61" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="G61" s="7">
+        <v>825</v>
+      </c>
+      <c r="H61" s="7">
+        <v>35</v>
+      </c>
+      <c r="I61" s="7">
+        <f t="shared" si="1"/>
+        <v>790</v>
+      </c>
+      <c r="J61" s="7" t="s">
+        <v>2695</v>
+      </c>
+      <c r="K61" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L61" s="7" t="s">
+        <v>2676</v>
+      </c>
+    </row>
+    <row r="62" spans="2:16" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B62" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C62" s="7" t="s">
+        <v>2832</v>
+      </c>
+      <c r="D62" s="7" t="s">
+        <v>2833</v>
+      </c>
+      <c r="E62" s="7" t="s">
+        <v>2834</v>
+      </c>
+      <c r="F62" s="8" t="s">
+        <v>2230</v>
+      </c>
+      <c r="G62" s="7">
+        <v>30</v>
+      </c>
+      <c r="H62" s="7">
+        <v>30</v>
+      </c>
+      <c r="I62" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J62" s="7" t="s">
+        <v>2695</v>
+      </c>
+      <c r="K62" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L62" s="7" t="s">
+        <v>2676</v>
+      </c>
+    </row>
+    <row r="63" spans="2:16" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B63" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C63" s="7" t="s">
+        <v>2835</v>
+      </c>
+      <c r="D63" s="7" t="s">
+        <v>2836</v>
+      </c>
+      <c r="E63" s="7" t="s">
+        <v>2837</v>
+      </c>
+      <c r="F63" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="G63" s="7">
+        <v>715</v>
+      </c>
+      <c r="H63" s="7">
+        <v>25</v>
+      </c>
+      <c r="I63" s="7">
+        <f t="shared" si="1"/>
+        <v>690</v>
+      </c>
+      <c r="J63" s="7" t="s">
+        <v>2695</v>
+      </c>
+      <c r="K63" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L63" s="7" t="s">
+        <v>2676</v>
+      </c>
+    </row>
+    <row r="64" spans="2:16" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B64" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C64" s="7" t="s">
+        <v>274</v>
+      </c>
+      <c r="D64" s="7" t="s">
+        <v>2838</v>
+      </c>
+      <c r="E64" s="7" t="s">
+        <v>276</v>
+      </c>
+      <c r="F64" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G64" s="7">
+        <v>950</v>
+      </c>
+      <c r="H64" s="7">
+        <v>30</v>
+      </c>
+      <c r="I64" s="7">
+        <f t="shared" si="1"/>
+        <v>920</v>
+      </c>
+      <c r="J64" s="7" t="s">
+        <v>2695</v>
+      </c>
+      <c r="K64" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L64" s="7" t="s">
+        <v>2676</v>
+      </c>
+    </row>
+    <row r="65" spans="2:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B65" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>2839</v>
+      </c>
+      <c r="D65" s="3" t="s">
+        <v>2840</v>
+      </c>
+      <c r="E65" s="3" t="s">
+        <v>1122</v>
+      </c>
+      <c r="F65" s="4" t="s">
+        <v>2189</v>
+      </c>
+      <c r="G65" s="3">
+        <v>0</v>
+      </c>
+      <c r="H65" s="3">
+        <v>30</v>
+      </c>
+      <c r="I65" s="3">
+        <f t="shared" si="1"/>
+        <v>-30</v>
+      </c>
+      <c r="J65" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K65" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L65" s="3" t="s">
+        <v>2676</v>
+      </c>
+    </row>
+    <row r="66" spans="2:16" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B66" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C66" s="7" t="s">
+        <v>2841</v>
+      </c>
+      <c r="D66" s="7" t="s">
+        <v>2842</v>
+      </c>
+      <c r="E66" s="7" t="s">
+        <v>2843</v>
+      </c>
+      <c r="F66" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="G66" s="7">
+        <v>765</v>
+      </c>
+      <c r="H66" s="7">
+        <v>25</v>
+      </c>
+      <c r="I66" s="7">
+        <f t="shared" si="1"/>
+        <v>740</v>
+      </c>
+      <c r="J66" s="7" t="s">
+        <v>2695</v>
+      </c>
+      <c r="K66" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L66" s="7" t="s">
+        <v>2676</v>
+      </c>
+    </row>
+    <row r="67" spans="2:16" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B67" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C67" s="7" t="s">
+        <v>2844</v>
+      </c>
+      <c r="D67" s="7" t="s">
+        <v>2845</v>
+      </c>
+      <c r="E67" s="7" t="s">
+        <v>2846</v>
+      </c>
+      <c r="F67" s="8" t="s">
+        <v>287</v>
+      </c>
+      <c r="G67" s="7">
+        <v>2660</v>
+      </c>
+      <c r="H67" s="7">
+        <v>35</v>
+      </c>
+      <c r="I67" s="7">
+        <f t="shared" ref="I67:I98" si="2">G67-H67</f>
+        <v>2625</v>
+      </c>
+      <c r="J67" s="7" t="s">
+        <v>2695</v>
+      </c>
+      <c r="K67" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L67" s="7" t="s">
+        <v>2676</v>
+      </c>
+      <c r="M67" s="7" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="68" spans="2:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B68" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>2847</v>
+      </c>
+      <c r="D68" s="3" t="s">
+        <v>2848</v>
+      </c>
+      <c r="E68" s="3" t="s">
+        <v>2849</v>
+      </c>
+      <c r="F68" s="4" t="s">
+        <v>2133</v>
+      </c>
+      <c r="G68" s="3">
+        <v>930</v>
+      </c>
+      <c r="H68" s="3">
+        <v>30</v>
+      </c>
+      <c r="I68" s="3">
+        <f t="shared" si="2"/>
+        <v>900</v>
+      </c>
+      <c r="J68" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K68" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L68" s="3" t="s">
+        <v>2676</v>
+      </c>
+    </row>
+    <row r="69" spans="2:16" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B69" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C69" s="9" t="s">
+        <v>2509</v>
+      </c>
+      <c r="D69" s="9" t="s">
+        <v>2850</v>
+      </c>
+      <c r="E69" s="9" t="s">
+        <v>2511</v>
+      </c>
+      <c r="F69" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="G69" s="9">
+        <v>1625</v>
+      </c>
+      <c r="H69" s="9">
+        <v>25</v>
+      </c>
+      <c r="I69" s="9">
+        <f t="shared" si="2"/>
+        <v>1600</v>
+      </c>
+      <c r="J69" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="K69" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L69" s="9" t="s">
+        <v>2676</v>
+      </c>
+    </row>
+    <row r="70" spans="2:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B70" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>2851</v>
+      </c>
+      <c r="D70" s="3" t="s">
+        <v>2852</v>
+      </c>
+      <c r="E70" s="3" t="s">
+        <v>2853</v>
+      </c>
+      <c r="F70" s="4" t="s">
+        <v>2133</v>
+      </c>
+      <c r="G70" s="3">
+        <v>690</v>
+      </c>
+      <c r="H70" s="3">
+        <v>30</v>
+      </c>
+      <c r="I70" s="3">
+        <f t="shared" si="2"/>
+        <v>660</v>
+      </c>
+      <c r="J70" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K70" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L70" s="3" t="s">
+        <v>2676</v>
+      </c>
+    </row>
+    <row r="71" spans="2:16" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B71" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C71" s="7" t="s">
+        <v>2541</v>
+      </c>
+      <c r="D71" s="7" t="s">
+        <v>2854</v>
+      </c>
+      <c r="E71" s="7" t="s">
+        <v>2543</v>
+      </c>
+      <c r="F71" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G71" s="7">
+        <v>470</v>
+      </c>
+      <c r="H71" s="7">
+        <v>30</v>
+      </c>
+      <c r="I71" s="7">
+        <f t="shared" si="2"/>
+        <v>440</v>
+      </c>
+      <c r="J71" s="7" t="s">
+        <v>2695</v>
+      </c>
+      <c r="K71" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L71" s="7" t="s">
+        <v>2676</v>
+      </c>
+      <c r="M71" s="7" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="72" spans="2:16" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B72" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C72" s="7" t="s">
+        <v>2729</v>
+      </c>
+      <c r="D72" s="7" t="s">
+        <v>2855</v>
+      </c>
+      <c r="E72" s="7" t="s">
+        <v>2731</v>
+      </c>
+      <c r="F72" s="8" t="s">
+        <v>2238</v>
+      </c>
+      <c r="G72" s="7">
+        <v>370</v>
+      </c>
+      <c r="H72" s="7">
+        <v>0</v>
+      </c>
+      <c r="I72" s="7">
+        <f t="shared" si="2"/>
+        <v>370</v>
+      </c>
+      <c r="J72" s="7" t="s">
+        <v>2695</v>
+      </c>
+      <c r="K72" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L72" s="7" t="s">
+        <v>2676</v>
+      </c>
+      <c r="M72" s="7" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="73" spans="2:16" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B73" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C73" s="5" t="s">
+        <v>2856</v>
+      </c>
+      <c r="D73" s="5" t="s">
+        <v>2857</v>
+      </c>
+      <c r="E73" s="5" t="s">
+        <v>2858</v>
+      </c>
+      <c r="F73" s="6" t="s">
+        <v>2144</v>
+      </c>
+      <c r="G73" s="5">
+        <v>0</v>
+      </c>
+      <c r="H73" s="5">
+        <v>30</v>
+      </c>
+      <c r="I73" s="5">
+        <f t="shared" si="2"/>
+        <v>-30</v>
+      </c>
+      <c r="J73" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="K73" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L73" s="5" t="s">
+        <v>2676</v>
+      </c>
+    </row>
+    <row r="74" spans="2:16" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B74" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="C74" s="11" t="s">
+        <v>2745</v>
+      </c>
+      <c r="D74" s="11" t="s">
+        <v>2859</v>
+      </c>
+      <c r="E74" s="11" t="s">
+        <v>2747</v>
+      </c>
+      <c r="F74" s="15" t="s">
+        <v>1469</v>
+      </c>
+      <c r="G74" s="11">
+        <v>820</v>
+      </c>
+      <c r="H74" s="11">
+        <v>0</v>
+      </c>
+      <c r="I74" s="11">
+        <f t="shared" si="2"/>
+        <v>820</v>
+      </c>
+      <c r="J74" s="11" t="s">
+        <v>427</v>
+      </c>
+      <c r="K74" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="L74" s="11" t="s">
+        <v>2676</v>
+      </c>
+      <c r="M74" s="11" t="s">
+        <v>1470</v>
+      </c>
+      <c r="N74" s="11" t="s">
+        <v>430</v>
+      </c>
+      <c r="P74" s="11" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="75" spans="2:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B75" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>2860</v>
+      </c>
+      <c r="D75" s="3" t="s">
+        <v>2861</v>
+      </c>
+      <c r="E75" s="3" t="s">
+        <v>2862</v>
+      </c>
+      <c r="F75" s="4" t="s">
+        <v>2133</v>
+      </c>
+      <c r="G75" s="3">
+        <v>980</v>
+      </c>
+      <c r="H75" s="3">
+        <v>30</v>
+      </c>
+      <c r="I75" s="3">
+        <f t="shared" si="2"/>
+        <v>950</v>
+      </c>
+      <c r="J75" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K75" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L75" s="3" t="s">
+        <v>2676</v>
+      </c>
+    </row>
+    <row r="76" spans="2:16" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B76" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C76" s="7" t="s">
+        <v>2863</v>
+      </c>
+      <c r="D76" s="7" t="s">
+        <v>2864</v>
+      </c>
+      <c r="E76" s="7" t="s">
+        <v>2865</v>
+      </c>
+      <c r="F76" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G76" s="7">
+        <v>770</v>
+      </c>
+      <c r="H76" s="7">
+        <v>30</v>
+      </c>
+      <c r="I76" s="7">
+        <f t="shared" si="2"/>
+        <v>740</v>
+      </c>
+      <c r="J76" s="7" t="s">
+        <v>2695</v>
+      </c>
+      <c r="K76" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L76" s="7" t="s">
+        <v>2676</v>
+      </c>
+    </row>
+    <row r="77" spans="2:16" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B77" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C77" s="9" t="s">
+        <v>2518</v>
+      </c>
+      <c r="D77" s="9" t="s">
+        <v>2866</v>
+      </c>
+      <c r="E77" s="9" t="s">
+        <v>2626</v>
+      </c>
+      <c r="F77" s="10" t="s">
+        <v>2242</v>
+      </c>
+      <c r="G77" s="9">
+        <v>585</v>
+      </c>
+      <c r="H77" s="9">
+        <v>25</v>
+      </c>
+      <c r="I77" s="9">
+        <f t="shared" si="2"/>
+        <v>560</v>
+      </c>
+      <c r="J77" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="K77" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L77" s="9" t="s">
+        <v>2676</v>
+      </c>
+      <c r="M77" s="9" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="78" spans="2:16" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B78" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C78" s="9" t="s">
+        <v>581</v>
+      </c>
+      <c r="D78" s="9" t="s">
+        <v>2867</v>
+      </c>
+      <c r="E78" s="9" t="s">
+        <v>583</v>
+      </c>
+      <c r="F78" s="10" t="s">
+        <v>2137</v>
+      </c>
+      <c r="G78" s="9">
+        <v>465</v>
+      </c>
+      <c r="H78" s="9">
+        <v>25</v>
+      </c>
+      <c r="I78" s="9">
+        <f t="shared" si="2"/>
+        <v>440</v>
+      </c>
+      <c r="J78" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="K78" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L78" s="9" t="s">
+        <v>2676</v>
+      </c>
+    </row>
+    <row r="79" spans="2:16" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B79" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C79" s="9" t="s">
+        <v>2868</v>
+      </c>
+      <c r="D79" s="9" t="s">
+        <v>2869</v>
+      </c>
+      <c r="E79" s="9" t="s">
+        <v>2870</v>
+      </c>
+      <c r="F79" s="10" t="s">
+        <v>2137</v>
+      </c>
+      <c r="G79" s="9">
+        <v>685</v>
+      </c>
+      <c r="H79" s="9">
+        <v>25</v>
+      </c>
+      <c r="I79" s="9">
+        <f t="shared" si="2"/>
+        <v>660</v>
+      </c>
+      <c r="J79" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="K79" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L79" s="9" t="s">
+        <v>2676</v>
+      </c>
+    </row>
+    <row r="80" spans="2:16" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B80" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="C80" s="11" t="s">
+        <v>2871</v>
+      </c>
+      <c r="D80" s="11" t="s">
+        <v>2872</v>
+      </c>
+      <c r="E80" s="11" t="s">
+        <v>2873</v>
+      </c>
+      <c r="F80" s="23" t="s">
+        <v>1469</v>
+      </c>
+      <c r="G80" s="11">
+        <v>690</v>
+      </c>
+      <c r="H80" s="11">
+        <v>0</v>
+      </c>
+      <c r="I80" s="11">
+        <f t="shared" si="2"/>
+        <v>690</v>
+      </c>
+      <c r="J80" s="11" t="s">
+        <v>427</v>
+      </c>
+      <c r="K80" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="L80" s="11" t="s">
+        <v>2676</v>
+      </c>
+      <c r="M80" s="11" t="s">
+        <v>1470</v>
+      </c>
+      <c r="N80" s="11" t="s">
+        <v>430</v>
+      </c>
+      <c r="P80" s="11" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="81" spans="2:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B81" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C81" s="9" t="s">
+        <v>2874</v>
+      </c>
+      <c r="D81" s="9" t="s">
+        <v>2875</v>
+      </c>
+      <c r="E81" s="9" t="s">
+        <v>2876</v>
+      </c>
+      <c r="F81" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="G81" s="9">
+        <v>0</v>
+      </c>
+      <c r="H81" s="9">
+        <v>25</v>
+      </c>
+      <c r="I81" s="9">
+        <f t="shared" si="2"/>
+        <v>-25</v>
+      </c>
+      <c r="J81" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="K81" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L81" s="9" t="s">
+        <v>2676</v>
+      </c>
+    </row>
+    <row r="82" spans="2:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B82" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C82" s="9" t="s">
+        <v>2877</v>
+      </c>
+      <c r="D82" s="9" t="s">
+        <v>2878</v>
+      </c>
+      <c r="E82" s="9" t="s">
+        <v>2879</v>
+      </c>
+      <c r="F82" s="10" t="s">
+        <v>2473</v>
+      </c>
+      <c r="G82" s="9">
+        <v>1145</v>
+      </c>
+      <c r="H82" s="9">
+        <v>25</v>
+      </c>
+      <c r="I82" s="9">
+        <f t="shared" si="2"/>
+        <v>1120</v>
+      </c>
+      <c r="J82" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="K82" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L82" s="9" t="s">
+        <v>2676</v>
+      </c>
+    </row>
+    <row r="83" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B83" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>2880</v>
+      </c>
+      <c r="D83" s="3" t="s">
+        <v>2881</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>2882</v>
+      </c>
+      <c r="F83" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="G83" s="3">
+        <v>865</v>
+      </c>
+      <c r="H83" s="3">
+        <v>25</v>
+      </c>
+      <c r="I83" s="3">
+        <f t="shared" si="2"/>
+        <v>840</v>
+      </c>
+      <c r="J83" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K83" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L83" s="3" t="s">
+        <v>2676</v>
+      </c>
+    </row>
+    <row r="84" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B84" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>1599</v>
+      </c>
+      <c r="D84" s="3" t="s">
+        <v>2883</v>
+      </c>
+      <c r="E84" s="3" t="s">
+        <v>2539</v>
+      </c>
+      <c r="F84" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="G84" s="3">
+        <v>680</v>
+      </c>
+      <c r="H84" s="3">
+        <v>20</v>
+      </c>
+      <c r="I84" s="3">
+        <f t="shared" si="2"/>
+        <v>660</v>
+      </c>
+      <c r="J84" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K84" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L84" s="3" t="s">
+        <v>2676</v>
+      </c>
+    </row>
+    <row r="85" spans="2:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B85" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C85" s="9" t="s">
+        <v>2884</v>
+      </c>
+      <c r="D85" s="9" t="s">
+        <v>2885</v>
+      </c>
+      <c r="E85" s="9" t="s">
+        <v>2886</v>
+      </c>
+      <c r="F85" s="10" t="s">
+        <v>2242</v>
+      </c>
+      <c r="G85" s="9">
+        <v>765</v>
+      </c>
+      <c r="H85" s="9">
+        <v>25</v>
+      </c>
+      <c r="I85" s="9">
+        <f t="shared" si="2"/>
+        <v>740</v>
+      </c>
+      <c r="J85" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="K85" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L85" s="9" t="s">
+        <v>2676</v>
+      </c>
+    </row>
+    <row r="86" spans="2:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B86" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C86" s="7" t="s">
+        <v>2887</v>
+      </c>
+      <c r="D86" s="7" t="s">
+        <v>2888</v>
+      </c>
+      <c r="E86" s="7" t="s">
+        <v>2889</v>
+      </c>
+      <c r="F86" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="G86" s="7">
+        <v>2240</v>
+      </c>
+      <c r="H86" s="7">
+        <v>25</v>
+      </c>
+      <c r="I86" s="7">
+        <f t="shared" si="2"/>
+        <v>2215</v>
+      </c>
+      <c r="J86" s="7" t="s">
+        <v>2695</v>
+      </c>
+      <c r="K86" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L86" s="7" t="s">
+        <v>2676</v>
+      </c>
+      <c r="M86" s="7" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="87" spans="2:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B87" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C87" s="9" t="s">
+        <v>2890</v>
+      </c>
+      <c r="D87" s="9" t="s">
+        <v>2891</v>
+      </c>
+      <c r="E87" s="9" t="s">
+        <v>1306</v>
+      </c>
+      <c r="F87" s="10" t="s">
+        <v>2183</v>
+      </c>
+      <c r="G87" s="9">
+        <v>0</v>
+      </c>
+      <c r="H87" s="9">
+        <v>25</v>
+      </c>
+      <c r="I87" s="9">
+        <f t="shared" si="2"/>
+        <v>-25</v>
+      </c>
+      <c r="J87" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="K87" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L87" s="9" t="s">
+        <v>2676</v>
+      </c>
+    </row>
+    <row r="88" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B88" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="D88" s="3" t="s">
+        <v>2892</v>
+      </c>
+      <c r="E88" s="3" t="s">
+        <v>2893</v>
+      </c>
+      <c r="F88" s="4" t="s">
+        <v>2133</v>
+      </c>
+      <c r="G88" s="3">
+        <v>770</v>
+      </c>
+      <c r="H88" s="3">
+        <v>30</v>
+      </c>
+      <c r="I88" s="3">
+        <f t="shared" si="2"/>
+        <v>740</v>
+      </c>
+      <c r="J88" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K88" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L88" s="3" t="s">
+        <v>2676</v>
+      </c>
+    </row>
+    <row r="89" spans="2:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B89" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C89" s="9" t="s">
+        <v>1828</v>
+      </c>
+      <c r="D89" s="9" t="s">
+        <v>2894</v>
+      </c>
+      <c r="E89" s="9" t="s">
+        <v>2895</v>
+      </c>
+      <c r="F89" s="10" t="s">
+        <v>2242</v>
+      </c>
+      <c r="G89" s="9">
+        <v>1505</v>
+      </c>
+      <c r="H89" s="9">
+        <v>25</v>
+      </c>
+      <c r="I89" s="9">
+        <f t="shared" si="2"/>
+        <v>1480</v>
+      </c>
+      <c r="J89" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="K89" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L89" s="9" t="s">
+        <v>2676</v>
+      </c>
+      <c r="M89" s="9" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="90" spans="2:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B90" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C90" s="9" t="s">
+        <v>2896</v>
+      </c>
+      <c r="D90" s="9" t="s">
+        <v>2897</v>
+      </c>
+      <c r="E90" s="9" t="s">
+        <v>2898</v>
+      </c>
+      <c r="F90" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="G90" s="9">
+        <v>0</v>
+      </c>
+      <c r="H90" s="9">
+        <v>0</v>
+      </c>
+      <c r="I90" s="9">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J52" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="K52" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="L52" s="3" t="s">
-        <v>2557</v>
-      </c>
-    </row>
-    <row r="53" spans="1:16" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B53" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="C53" s="11" t="s">
-        <v>1689</v>
-      </c>
-      <c r="D53" s="11" t="s">
-        <v>2535</v>
-      </c>
-      <c r="E53" s="11" t="s">
-        <v>1454</v>
-      </c>
-      <c r="F53" s="15" t="s">
+      <c r="J90" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="K90" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L90" s="9" t="s">
+        <v>2676</v>
+      </c>
+      <c r="M90" s="9" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="91" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B91" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C91" s="3" t="s">
+        <v>2899</v>
+      </c>
+      <c r="D91" s="3" t="s">
+        <v>2900</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>2901</v>
+      </c>
+      <c r="F91" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="G53" s="11">
-        <v>765</v>
-      </c>
-      <c r="H53" s="11">
+      <c r="G91" s="3">
+        <v>3050</v>
+      </c>
+      <c r="H91" s="3">
+        <v>30</v>
+      </c>
+      <c r="I91" s="3">
+        <f t="shared" si="2"/>
+        <v>3020</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K91" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L91" s="3" t="s">
+        <v>2676</v>
+      </c>
+      <c r="M91" s="3" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="92" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B92" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C92" s="3" t="s">
+        <v>1366</v>
+      </c>
+      <c r="D92" s="3" t="s">
+        <v>2902</v>
+      </c>
+      <c r="E92" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="F92" s="4" t="s">
+        <v>2189</v>
+      </c>
+      <c r="G92" s="3">
         <v>0</v>
       </c>
-      <c r="I53" s="11">
-        <f>G53-H53</f>
-        <v>765</v>
-      </c>
-      <c r="J53" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="K53" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="L53" s="11" t="s">
-        <v>2412</v>
-      </c>
-      <c r="M53" s="11" t="s">
+      <c r="H92" s="3">
+        <v>30</v>
+      </c>
+      <c r="I92" s="3">
+        <f t="shared" si="2"/>
+        <v>-30</v>
+      </c>
+      <c r="J92" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K92" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L92" s="3" t="s">
+        <v>2676</v>
+      </c>
+    </row>
+    <row r="93" spans="2:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B93" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C93" s="7" t="s">
+        <v>2903</v>
+      </c>
+      <c r="D93" s="7" t="s">
+        <v>2904</v>
+      </c>
+      <c r="E93" s="7" t="s">
+        <v>2905</v>
+      </c>
+      <c r="F93" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G93" s="7">
+        <v>0</v>
+      </c>
+      <c r="H93" s="7">
+        <v>30</v>
+      </c>
+      <c r="I93" s="7">
+        <f t="shared" si="2"/>
+        <v>-30</v>
+      </c>
+      <c r="J93" s="7" t="s">
+        <v>2695</v>
+      </c>
+      <c r="K93" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L93" s="7" t="s">
+        <v>2676</v>
+      </c>
+    </row>
+    <row r="94" spans="2:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B94" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C94" s="7" t="s">
+        <v>2906</v>
+      </c>
+      <c r="D94" s="7" t="s">
+        <v>2907</v>
+      </c>
+      <c r="E94" s="7" t="s">
+        <v>2908</v>
+      </c>
+      <c r="F94" s="8" t="s">
+        <v>2230</v>
+      </c>
+      <c r="G94" s="7">
+        <v>0</v>
+      </c>
+      <c r="H94" s="7">
+        <v>25</v>
+      </c>
+      <c r="I94" s="7">
+        <f t="shared" si="2"/>
+        <v>-25</v>
+      </c>
+      <c r="J94" s="7" t="s">
+        <v>2695</v>
+      </c>
+      <c r="K94" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L94" s="7" t="s">
+        <v>2676</v>
+      </c>
+    </row>
+    <row r="95" spans="2:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B95" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C95" s="7" t="s">
+        <v>2541</v>
+      </c>
+      <c r="D95" s="7" t="s">
+        <v>2909</v>
+      </c>
+      <c r="E95" s="7" t="s">
+        <v>2543</v>
+      </c>
+      <c r="F95" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G95" s="7">
+        <v>360</v>
+      </c>
+      <c r="H95" s="7">
+        <v>0</v>
+      </c>
+      <c r="I95" s="7">
+        <f t="shared" si="2"/>
+        <v>360</v>
+      </c>
+      <c r="J95" s="7" t="s">
+        <v>2695</v>
+      </c>
+      <c r="K95" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L95" s="7" t="s">
+        <v>2676</v>
+      </c>
+      <c r="M95" s="7" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="96" spans="2:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B96" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C96" s="9" t="s">
+        <v>2910</v>
+      </c>
+      <c r="D96" s="9" t="s">
+        <v>2911</v>
+      </c>
+      <c r="E96" s="9" t="s">
+        <v>2912</v>
+      </c>
+      <c r="F96" s="10" t="s">
+        <v>2242</v>
+      </c>
+      <c r="G96" s="9">
+        <v>685</v>
+      </c>
+      <c r="H96" s="9">
+        <v>25</v>
+      </c>
+      <c r="I96" s="9">
+        <f t="shared" si="2"/>
+        <v>660</v>
+      </c>
+      <c r="J96" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="K96" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L96" s="9" t="s">
+        <v>2676</v>
+      </c>
+    </row>
+    <row r="97" spans="2:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B97" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C97" s="9" t="s">
+        <v>2466</v>
+      </c>
+      <c r="D97" s="9" t="s">
+        <v>2913</v>
+      </c>
+      <c r="E97" s="9" t="s">
+        <v>2468</v>
+      </c>
+      <c r="F97" s="10" t="s">
+        <v>2196</v>
+      </c>
+      <c r="G97" s="9">
+        <v>845</v>
+      </c>
+      <c r="H97" s="9">
+        <v>25</v>
+      </c>
+      <c r="I97" s="9">
+        <f t="shared" si="2"/>
+        <v>820</v>
+      </c>
+      <c r="J97" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="K97" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L97" s="9" t="s">
+        <v>2676</v>
+      </c>
+    </row>
+    <row r="98" spans="2:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B98" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C98" s="7" t="s">
+        <v>2914</v>
+      </c>
+      <c r="D98" s="7" t="s">
+        <v>2915</v>
+      </c>
+      <c r="E98" s="7" t="s">
+        <v>2916</v>
+      </c>
+      <c r="F98" s="8" t="s">
+        <v>2189</v>
+      </c>
+      <c r="G98" s="7">
+        <v>890</v>
+      </c>
+      <c r="H98" s="7">
+        <v>30</v>
+      </c>
+      <c r="I98" s="7">
+        <f t="shared" si="2"/>
+        <v>860</v>
+      </c>
+      <c r="J98" s="7" t="s">
+        <v>2695</v>
+      </c>
+      <c r="K98" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L98" s="7" t="s">
+        <v>2676</v>
+      </c>
+    </row>
+    <row r="99" spans="2:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B99" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C99" s="7" t="s">
+        <v>2917</v>
+      </c>
+      <c r="D99" s="7" t="s">
+        <v>2918</v>
+      </c>
+      <c r="E99" s="7" t="s">
+        <v>2919</v>
+      </c>
+      <c r="F99" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G99" s="7">
+        <v>0</v>
+      </c>
+      <c r="H99" s="7">
+        <v>30</v>
+      </c>
+      <c r="I99" s="7">
+        <f t="shared" ref="I99:I130" si="3">G99-H99</f>
+        <v>-30</v>
+      </c>
+      <c r="J99" s="7" t="s">
+        <v>2695</v>
+      </c>
+      <c r="K99" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L99" s="7" t="s">
+        <v>2676</v>
+      </c>
+    </row>
+    <row r="100" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B100" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C100" s="3" t="s">
+        <v>2920</v>
+      </c>
+      <c r="D100" s="3" t="s">
+        <v>2921</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>1122</v>
+      </c>
+      <c r="F100" s="4" t="s">
+        <v>2189</v>
+      </c>
+      <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
+        <v>30</v>
+      </c>
+      <c r="I100" s="3">
+        <f t="shared" si="3"/>
+        <v>-30</v>
+      </c>
+      <c r="J100" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K100" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L100" s="3" t="s">
+        <v>2676</v>
+      </c>
+    </row>
+    <row r="101" spans="2:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B101" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C101" s="7" t="s">
+        <v>2922</v>
+      </c>
+      <c r="D101" s="7" t="s">
+        <v>2923</v>
+      </c>
+      <c r="E101" s="7" t="s">
+        <v>2924</v>
+      </c>
+      <c r="F101" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G101" s="7">
+        <v>0</v>
+      </c>
+      <c r="H101" s="7">
+        <v>30</v>
+      </c>
+      <c r="I101" s="7">
+        <f t="shared" si="3"/>
+        <v>-30</v>
+      </c>
+      <c r="J101" s="7" t="s">
+        <v>2695</v>
+      </c>
+      <c r="K101" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L101" s="7" t="s">
+        <v>2676</v>
+      </c>
+    </row>
+    <row r="102" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B102" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C102" s="3" t="s">
+        <v>2575</v>
+      </c>
+      <c r="D102" s="3" t="s">
+        <v>2925</v>
+      </c>
+      <c r="E102" s="3" t="s">
+        <v>2577</v>
+      </c>
+      <c r="F102" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="G102" s="3">
+        <v>720</v>
+      </c>
+      <c r="H102" s="3">
+        <v>30</v>
+      </c>
+      <c r="I102" s="3">
+        <f t="shared" si="3"/>
+        <v>690</v>
+      </c>
+      <c r="J102" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K102" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L102" s="3" t="s">
+        <v>2676</v>
+      </c>
+    </row>
+    <row r="103" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B103" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C103" s="3" t="s">
+        <v>2926</v>
+      </c>
+      <c r="D103" s="3" t="s">
+        <v>2927</v>
+      </c>
+      <c r="E103" s="3" t="s">
+        <v>2928</v>
+      </c>
+      <c r="F103" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="G103" s="3">
+        <v>880</v>
+      </c>
+      <c r="H103" s="3">
+        <v>20</v>
+      </c>
+      <c r="I103" s="3">
+        <f t="shared" si="3"/>
+        <v>860</v>
+      </c>
+      <c r="J103" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K103" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L103" s="3" t="s">
+        <v>2676</v>
+      </c>
+    </row>
+    <row r="104" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B104" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C104" s="3" t="s">
+        <v>1791</v>
+      </c>
+      <c r="D104" s="3" t="s">
+        <v>2929</v>
+      </c>
+      <c r="E104" s="3" t="s">
+        <v>2930</v>
+      </c>
+      <c r="F104" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="G104" s="3">
+        <v>3310</v>
+      </c>
+      <c r="H104" s="3">
+        <v>25</v>
+      </c>
+      <c r="I104" s="3">
+        <f t="shared" si="3"/>
+        <v>3285</v>
+      </c>
+      <c r="J104" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K104" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L104" s="3" t="s">
+        <v>2676</v>
+      </c>
+      <c r="M104" s="3" t="s">
+        <v>1197</v>
+      </c>
+    </row>
+    <row r="105" spans="2:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B105" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C105" s="7" t="s">
+        <v>2931</v>
+      </c>
+      <c r="D105" s="7" t="s">
+        <v>2932</v>
+      </c>
+      <c r="E105" s="7" t="s">
+        <v>2933</v>
+      </c>
+      <c r="F105" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="G105" s="7">
+        <v>0</v>
+      </c>
+      <c r="H105" s="7">
+        <v>40</v>
+      </c>
+      <c r="I105" s="7">
+        <f t="shared" si="3"/>
+        <v>-40</v>
+      </c>
+      <c r="J105" s="7" t="s">
+        <v>2695</v>
+      </c>
+      <c r="K105" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L105" s="7" t="s">
+        <v>2676</v>
+      </c>
+    </row>
+    <row r="106" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B106" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C106" s="3" t="s">
+        <v>2934</v>
+      </c>
+      <c r="D106" s="3" t="s">
+        <v>2935</v>
+      </c>
+      <c r="E106" s="3" t="s">
+        <v>2936</v>
+      </c>
+      <c r="F106" s="4" t="s">
+        <v>2133</v>
+      </c>
+      <c r="G106" s="3">
+        <v>770</v>
+      </c>
+      <c r="H106" s="3">
+        <v>30</v>
+      </c>
+      <c r="I106" s="3">
+        <f t="shared" si="3"/>
+        <v>740</v>
+      </c>
+      <c r="J106" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K106" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L106" s="3" t="s">
+        <v>2676</v>
+      </c>
+    </row>
+    <row r="107" spans="2:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B107" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C107" s="9" t="s">
+        <v>2937</v>
+      </c>
+      <c r="D107" s="9" t="s">
+        <v>2938</v>
+      </c>
+      <c r="E107" s="9" t="s">
+        <v>2939</v>
+      </c>
+      <c r="F107" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="G107" s="9">
+        <v>710</v>
+      </c>
+      <c r="H107" s="9">
+        <v>20</v>
+      </c>
+      <c r="I107" s="9">
+        <f t="shared" si="3"/>
+        <v>690</v>
+      </c>
+      <c r="J107" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="K107" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L107" s="9" t="s">
+        <v>2676</v>
+      </c>
+    </row>
+    <row r="108" spans="2:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B108" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C108" s="9" t="s">
+        <v>2896</v>
+      </c>
+      <c r="D108" s="9" t="s">
+        <v>2940</v>
+      </c>
+      <c r="E108" s="9" t="s">
+        <v>2898</v>
+      </c>
+      <c r="F108" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="G108" s="9">
+        <v>2910</v>
+      </c>
+      <c r="H108" s="9">
+        <v>30</v>
+      </c>
+      <c r="I108" s="9">
+        <f t="shared" si="3"/>
+        <v>2880</v>
+      </c>
+      <c r="J108" s="9" t="s">
+        <v>2695</v>
+      </c>
+      <c r="K108" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L108" s="9" t="s">
+        <v>2676</v>
+      </c>
+      <c r="M108" s="9" t="s">
+        <v>1197</v>
+      </c>
+    </row>
+    <row r="109" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B109" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C109" s="3" t="s">
+        <v>1791</v>
+      </c>
+      <c r="D109" s="3" t="s">
+        <v>2941</v>
+      </c>
+      <c r="E109" s="3" t="s">
+        <v>2930</v>
+      </c>
+      <c r="F109" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="G109" s="3">
+        <v>1320</v>
+      </c>
+      <c r="H109" s="3">
+        <v>0</v>
+      </c>
+      <c r="I109" s="3">
+        <f t="shared" si="3"/>
+        <v>1320</v>
+      </c>
+      <c r="J109" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K109" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L109" s="3" t="s">
+        <v>2676</v>
+      </c>
+      <c r="M109" s="3" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="110" spans="2:13" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B110" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C110" s="5" t="s">
+        <v>2942</v>
+      </c>
+      <c r="D110" s="5" t="s">
+        <v>2943</v>
+      </c>
+      <c r="E110" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="F110" s="6" t="s">
+        <v>2144</v>
+      </c>
+      <c r="G110" s="5">
+        <v>1860</v>
+      </c>
+      <c r="H110" s="5">
+        <v>30</v>
+      </c>
+      <c r="I110" s="5">
+        <f t="shared" si="3"/>
+        <v>1830</v>
+      </c>
+      <c r="J110" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="K110" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L110" s="5" t="s">
+        <v>2676</v>
+      </c>
+    </row>
+    <row r="111" spans="2:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B111" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C111" s="9" t="s">
+        <v>2944</v>
+      </c>
+      <c r="D111" s="9" t="s">
+        <v>2945</v>
+      </c>
+      <c r="E111" s="9" t="s">
+        <v>2946</v>
+      </c>
+      <c r="F111" s="10" t="s">
+        <v>2183</v>
+      </c>
+      <c r="G111" s="9">
+        <v>0</v>
+      </c>
+      <c r="H111" s="9">
+        <v>25</v>
+      </c>
+      <c r="I111" s="9">
+        <f t="shared" si="3"/>
+        <v>-25</v>
+      </c>
+      <c r="J111" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="K111" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L111" s="9" t="s">
+        <v>2676</v>
+      </c>
+    </row>
+    <row r="112" spans="2:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B112" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C112" s="7" t="s">
+        <v>2368</v>
+      </c>
+      <c r="D112" s="7" t="s">
+        <v>2947</v>
+      </c>
+      <c r="E112" s="7" t="s">
+        <v>2948</v>
+      </c>
+      <c r="F112" s="8" t="s">
+        <v>2189</v>
+      </c>
+      <c r="G112" s="7">
+        <v>890</v>
+      </c>
+      <c r="H112" s="7">
+        <v>30</v>
+      </c>
+      <c r="I112" s="7">
+        <f t="shared" si="3"/>
+        <v>860</v>
+      </c>
+      <c r="J112" s="7" t="s">
+        <v>2695</v>
+      </c>
+      <c r="K112" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L112" s="7" t="s">
+        <v>2676</v>
+      </c>
+      <c r="M112" s="7" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="113" spans="1:17" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B113" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C113" s="7" t="s">
+        <v>2949</v>
+      </c>
+      <c r="D113" s="7" t="s">
+        <v>2950</v>
+      </c>
+      <c r="E113" s="7" t="s">
+        <v>2951</v>
+      </c>
+      <c r="F113" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="G113" s="7">
+        <v>825</v>
+      </c>
+      <c r="H113" s="7">
+        <v>35</v>
+      </c>
+      <c r="I113" s="7">
+        <f t="shared" si="3"/>
+        <v>790</v>
+      </c>
+      <c r="J113" s="7" t="s">
+        <v>2695</v>
+      </c>
+      <c r="K113" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L113" s="7" t="s">
+        <v>2676</v>
+      </c>
+    </row>
+    <row r="114" spans="1:17" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B114" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C114" s="7" t="s">
+        <v>2952</v>
+      </c>
+      <c r="D114" s="7" t="s">
+        <v>2953</v>
+      </c>
+      <c r="E114" s="7" t="s">
+        <v>2954</v>
+      </c>
+      <c r="F114" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G114" s="7">
+        <v>600</v>
+      </c>
+      <c r="H114" s="7">
+        <v>30</v>
+      </c>
+      <c r="I114" s="7">
+        <f t="shared" si="3"/>
+        <v>570</v>
+      </c>
+      <c r="J114" s="7" t="s">
+        <v>2695</v>
+      </c>
+      <c r="K114" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L114" s="7" t="s">
+        <v>2676</v>
+      </c>
+    </row>
+    <row r="115" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B115" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C115" s="3" t="s">
+        <v>2955</v>
+      </c>
+      <c r="D115" s="3" t="s">
+        <v>2956</v>
+      </c>
+      <c r="E115" s="3" t="s">
+        <v>2957</v>
+      </c>
+      <c r="F115" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="G115" s="3">
+        <v>0</v>
+      </c>
+      <c r="H115" s="3">
+        <v>30</v>
+      </c>
+      <c r="I115" s="3">
+        <f t="shared" si="3"/>
+        <v>-30</v>
+      </c>
+      <c r="J115" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K115" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L115" s="3" t="s">
+        <v>2676</v>
+      </c>
+    </row>
+    <row r="116" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B116" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C116" s="3" t="s">
+        <v>2958</v>
+      </c>
+      <c r="D116" s="3" t="s">
+        <v>2959</v>
+      </c>
+      <c r="E116" s="3" t="s">
+        <v>2960</v>
+      </c>
+      <c r="F116" s="4" t="s">
+        <v>2189</v>
+      </c>
+      <c r="G116" s="3">
+        <v>0</v>
+      </c>
+      <c r="H116" s="3">
+        <v>35</v>
+      </c>
+      <c r="I116" s="3">
+        <f t="shared" si="3"/>
+        <v>-35</v>
+      </c>
+      <c r="J116" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K116" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L116" s="3" t="s">
+        <v>2676</v>
+      </c>
+    </row>
+    <row r="117" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A117" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B117" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C117" s="3" t="s">
+        <v>640</v>
+      </c>
+      <c r="E117" s="3" t="s">
+        <v>2961</v>
+      </c>
+      <c r="F117" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="G117" s="3">
+        <v>2815</v>
+      </c>
+      <c r="H117" s="3">
+        <v>35</v>
+      </c>
+      <c r="I117" s="3">
+        <f t="shared" si="3"/>
+        <v>2780</v>
+      </c>
+      <c r="J117" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K117" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L117" s="3" t="s">
+        <v>2676</v>
+      </c>
+    </row>
+    <row r="118" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A118" s="11"/>
+      <c r="B118" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="C118" s="11" t="s">
+        <v>1699</v>
+      </c>
+      <c r="D118" s="11" t="s">
+        <v>1700</v>
+      </c>
+      <c r="E118" s="11" t="s">
+        <v>1701</v>
+      </c>
+      <c r="F118" s="15">
+        <v>12</v>
+      </c>
+      <c r="G118" s="11">
+        <v>700</v>
+      </c>
+      <c r="H118" s="11">
+        <v>30</v>
+      </c>
+      <c r="I118" s="11">
+        <f t="shared" si="3"/>
+        <v>670</v>
+      </c>
+      <c r="J118" s="11" t="s">
+        <v>1673</v>
+      </c>
+      <c r="K118" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="L118" s="11" t="s">
+        <v>1669</v>
+      </c>
+      <c r="M118" s="11" t="s">
         <v>429</v>
       </c>
-      <c r="N53" s="11" t="s">
+      <c r="N118" s="11" t="s">
         <v>430</v>
       </c>
-      <c r="O53" s="11" t="s">
+      <c r="O118" s="11" t="s">
         <v>430</v>
       </c>
-      <c r="P53" s="11" t="s">
+      <c r="P118" s="11" t="s">
         <v>431</v>
+      </c>
+      <c r="Q118" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="119" spans="1:17" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B119" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="C119" s="11" t="s">
+        <v>2012</v>
+      </c>
+      <c r="D119" s="11" t="s">
+        <v>2013</v>
+      </c>
+      <c r="E119" s="11" t="s">
+        <v>2014</v>
+      </c>
+      <c r="F119" s="15">
+        <v>12</v>
+      </c>
+      <c r="G119" s="11">
+        <v>600</v>
+      </c>
+      <c r="H119" s="11">
+        <v>30</v>
+      </c>
+      <c r="I119" s="11">
+        <f t="shared" si="3"/>
+        <v>570</v>
+      </c>
+      <c r="J119" s="11" t="s">
+        <v>1994</v>
+      </c>
+      <c r="K119" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="L119" s="11" t="s">
+        <v>1991</v>
+      </c>
+      <c r="M119" s="11" t="s">
+        <v>429</v>
+      </c>
+      <c r="N119" s="11" t="s">
+        <v>430</v>
+      </c>
+      <c r="O119" s="11" t="s">
+        <v>430</v>
+      </c>
+      <c r="P119" s="11" t="s">
+        <v>431</v>
+      </c>
+      <c r="Q119" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="120" spans="1:17" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B120" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="C120" s="11" t="s">
+        <v>1674</v>
+      </c>
+      <c r="D120" s="11" t="s">
+        <v>1675</v>
+      </c>
+      <c r="E120" s="11" t="s">
+        <v>1630</v>
+      </c>
+      <c r="F120" s="15">
+        <v>11</v>
+      </c>
+      <c r="G120" s="11">
+        <v>895</v>
+      </c>
+      <c r="H120" s="11">
+        <v>25</v>
+      </c>
+      <c r="I120" s="11">
+        <f t="shared" si="3"/>
+        <v>870</v>
+      </c>
+      <c r="J120" s="11" t="s">
+        <v>1673</v>
+      </c>
+      <c r="K120" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="L120" s="11" t="s">
+        <v>1669</v>
+      </c>
+      <c r="M120" s="11" t="s">
+        <v>429</v>
+      </c>
+      <c r="N120" s="11" t="s">
+        <v>430</v>
+      </c>
+      <c r="O120" s="11" t="s">
+        <v>430</v>
+      </c>
+      <c r="P120" s="11" t="s">
+        <v>431</v>
+      </c>
+      <c r="Q120" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="121" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A121" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="B121" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C121" s="9" t="s">
+        <v>416</v>
+      </c>
+      <c r="E121" s="9" t="s">
+        <v>417</v>
+      </c>
+      <c r="F121" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="G121" s="9">
+        <v>0</v>
+      </c>
+      <c r="H121" s="9">
+        <v>30</v>
+      </c>
+      <c r="I121" s="9">
+        <f t="shared" si="3"/>
+        <v>-30</v>
+      </c>
+      <c r="J121" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="K121" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L121" s="9" t="s">
+        <v>2676</v>
+      </c>
+    </row>
+    <row r="122" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A122" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="B122" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C122" s="9" t="s">
+        <v>2962</v>
+      </c>
+      <c r="E122" s="9" t="s">
+        <v>2963</v>
+      </c>
+      <c r="F122" s="10">
+        <v>1</v>
+      </c>
+      <c r="G122" s="9">
+        <v>0</v>
+      </c>
+      <c r="H122" s="9">
+        <v>30</v>
+      </c>
+      <c r="I122" s="9">
+        <f t="shared" si="3"/>
+        <v>-30</v>
+      </c>
+      <c r="J122" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="K122" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L122" s="9" t="s">
+        <v>2676</v>
+      </c>
+    </row>
+    <row r="123" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A123" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="B123" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C123" s="9" t="s">
+        <v>1764</v>
+      </c>
+      <c r="E123" s="9" t="s">
+        <v>1765</v>
+      </c>
+      <c r="F123" s="10" t="s">
+        <v>2183</v>
+      </c>
+      <c r="G123" s="9">
+        <v>2995</v>
+      </c>
+      <c r="H123" s="9">
+        <v>35</v>
+      </c>
+      <c r="I123" s="9">
+        <f t="shared" si="3"/>
+        <v>2960</v>
+      </c>
+      <c r="J123" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="K123" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L123" s="9" t="s">
+        <v>2676</v>
+      </c>
+    </row>
+    <row r="124" spans="1:17" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A124" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="B124" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C124" s="7" t="s">
+        <v>649</v>
+      </c>
+      <c r="E124" s="7" t="s">
+        <v>650</v>
+      </c>
+      <c r="F124" s="7" t="s">
+        <v>287</v>
+      </c>
+      <c r="G124" s="7">
+        <v>2460</v>
+      </c>
+      <c r="H124" s="7">
+        <v>40</v>
+      </c>
+      <c r="I124" s="7">
+        <f t="shared" si="3"/>
+        <v>2420</v>
+      </c>
+      <c r="J124" s="7" t="s">
+        <v>2695</v>
+      </c>
+      <c r="K124" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L124" s="7" t="s">
+        <v>2676</v>
+      </c>
+    </row>
+    <row r="125" spans="1:17" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B125" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C125" s="7" t="s">
+        <v>2368</v>
+      </c>
+      <c r="D125" s="7" t="s">
+        <v>2964</v>
+      </c>
+      <c r="E125" s="7" t="s">
+        <v>2948</v>
+      </c>
+      <c r="F125" s="8" t="s">
+        <v>2189</v>
+      </c>
+      <c r="G125" s="7">
+        <v>860</v>
+      </c>
+      <c r="H125" s="7">
+        <v>0</v>
+      </c>
+      <c r="I125" s="7">
+        <f t="shared" si="3"/>
+        <v>860</v>
+      </c>
+      <c r="J125" s="7" t="s">
+        <v>2695</v>
+      </c>
+      <c r="K125" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L125" s="7" t="s">
+        <v>2676</v>
+      </c>
+      <c r="M125" s="7" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="126" spans="1:17" s="34" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A126" s="34" t="s">
+        <v>85</v>
+      </c>
+      <c r="B126" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="C126" s="34" t="s">
+        <v>2965</v>
+      </c>
+      <c r="E126" s="34" t="s">
+        <v>2966</v>
+      </c>
+      <c r="F126" s="37" t="s">
+        <v>88</v>
+      </c>
+      <c r="G126" s="34">
+        <v>1300</v>
+      </c>
+      <c r="H126" s="34">
+        <v>30</v>
+      </c>
+      <c r="I126" s="34">
+        <f t="shared" si="3"/>
+        <v>1270</v>
+      </c>
+      <c r="K126" s="34" t="s">
+        <v>24</v>
+      </c>
+      <c r="L126" s="34" t="s">
+        <v>2676</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1700-000000000000}">
+  <dimension ref="A1:P48"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="39.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="71.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.5703125" customWidth="1"/>
+    <col min="12" max="12" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="19.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B1" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2967</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>3047</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>3046</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="G3" s="3">
+        <v>9030</v>
+      </c>
+      <c r="H3" s="3">
+        <v>50</v>
+      </c>
+      <c r="I3" s="3">
+        <f t="shared" ref="I3:I47" si="0">G3-H3</f>
+        <v>8980</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>2969</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>566</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>567</v>
+      </c>
+      <c r="F4" s="10" t="s">
+        <v>2196</v>
+      </c>
+      <c r="G4" s="9">
+        <v>30</v>
+      </c>
+      <c r="H4" s="9">
+        <v>30</v>
+      </c>
+      <c r="I4" s="9">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J4" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="K4" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L4" s="9" t="s">
+        <v>2969</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>416</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>417</v>
+      </c>
+      <c r="F5" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="G5" s="9">
+        <v>0</v>
+      </c>
+      <c r="H5" s="9">
+        <v>30</v>
+      </c>
+      <c r="I5" s="9">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J5" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="K5" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L5" s="9" t="s">
+        <v>2969</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>3054</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>3053</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>2672</v>
+      </c>
+      <c r="G6" s="5">
+        <v>35</v>
+      </c>
+      <c r="H6" s="5">
+        <v>35</v>
+      </c>
+      <c r="I6" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J6" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="K6" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L6" s="5" t="s">
+        <v>2969</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="G7" s="3">
+        <v>30</v>
+      </c>
+      <c r="H7" s="3">
+        <v>30</v>
+      </c>
+      <c r="I7" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L7" s="3" t="s">
+        <v>2969</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>2965</v>
+      </c>
+      <c r="E8" s="9" t="s">
+        <v>2966</v>
+      </c>
+      <c r="F8" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="G8" s="9">
+        <v>1300</v>
+      </c>
+      <c r="H8" s="9">
+        <v>30</v>
+      </c>
+      <c r="I8" s="9">
+        <f t="shared" si="0"/>
+        <v>1270</v>
+      </c>
+      <c r="J8" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="K8" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L8" s="9" t="s">
+        <v>2969</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>868</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>869</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="G9" s="3">
+        <v>30</v>
+      </c>
+      <c r="H9" s="3">
+        <v>30</v>
+      </c>
+      <c r="I9" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L9" s="3" t="s">
+        <v>2969</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>2970</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>3039</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="G10" s="3">
+        <v>1375</v>
+      </c>
+      <c r="H10" s="3">
+        <v>25</v>
+      </c>
+      <c r="I10" s="3">
+        <f t="shared" si="0"/>
+        <v>1350</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L10" s="3" t="s">
+        <v>2969</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>2971</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>2972</v>
+      </c>
+      <c r="E11" s="9" t="s">
+        <v>2973</v>
+      </c>
+      <c r="F11" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="G11" s="9">
+        <v>1375</v>
+      </c>
+      <c r="H11" s="9">
+        <v>25</v>
+      </c>
+      <c r="I11" s="9">
+        <f t="shared" si="0"/>
+        <v>1350</v>
+      </c>
+      <c r="J11" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="K11" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L11" s="9" t="s">
+        <v>2969</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>2974</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G12" s="7">
+        <v>910</v>
+      </c>
+      <c r="H12" s="7">
+        <v>30</v>
+      </c>
+      <c r="I12" s="7">
+        <f t="shared" si="0"/>
+        <v>880</v>
+      </c>
+      <c r="J12" s="7" t="s">
+        <v>2968</v>
+      </c>
+      <c r="K12" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L12" s="7" t="s">
+        <v>2969</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>2975</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>3056</v>
+      </c>
+      <c r="E13" s="9" t="s">
+        <v>2976</v>
+      </c>
+      <c r="F13" s="10" t="s">
+        <v>2137</v>
+      </c>
+      <c r="G13" s="9">
+        <v>981</v>
+      </c>
+      <c r="H13" s="9">
+        <v>25</v>
+      </c>
+      <c r="I13" s="9">
+        <f t="shared" si="0"/>
+        <v>956</v>
+      </c>
+      <c r="J13" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="K13" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L13" s="9" t="s">
+        <v>2969</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>2977</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>2978</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>3052</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="G14" s="3">
+        <v>1970</v>
+      </c>
+      <c r="H14" s="3">
+        <v>20</v>
+      </c>
+      <c r="I14" s="3">
+        <f t="shared" si="0"/>
+        <v>1950</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>2969</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>3060</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>3061</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>2979</v>
+      </c>
+      <c r="F15" s="8" t="s">
+        <v>2238</v>
+      </c>
+      <c r="G15" s="7">
+        <v>1580</v>
+      </c>
+      <c r="H15" s="7">
+        <v>30</v>
+      </c>
+      <c r="I15" s="7">
+        <f t="shared" si="0"/>
+        <v>1550</v>
+      </c>
+      <c r="J15" s="7" t="s">
+        <v>2968</v>
+      </c>
+      <c r="K15" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L15" s="7" t="s">
+        <v>2969</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>2980</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>2981</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>2982</v>
+      </c>
+      <c r="F16" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="G16" s="7">
+        <v>825</v>
+      </c>
+      <c r="H16" s="7">
+        <v>35</v>
+      </c>
+      <c r="I16" s="7">
+        <f t="shared" si="0"/>
+        <v>790</v>
+      </c>
+      <c r="J16" s="7" t="s">
+        <v>2968</v>
+      </c>
+      <c r="K16" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L16" s="7" t="s">
+        <v>2969</v>
+      </c>
+    </row>
+    <row r="17" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>2983</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>3041</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>3042</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="G17" s="3">
+        <v>490</v>
+      </c>
+      <c r="H17" s="3">
+        <v>30</v>
+      </c>
+      <c r="I17" s="3">
+        <f t="shared" si="0"/>
+        <v>460</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L17" s="3" t="s">
+        <v>2969</v>
+      </c>
+    </row>
+    <row r="18" spans="2:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>2984</v>
+      </c>
+      <c r="D18" s="9" t="s">
+        <v>2985</v>
+      </c>
+      <c r="E18" s="9" t="s">
+        <v>698</v>
+      </c>
+      <c r="F18" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="G18" s="9">
+        <v>2900</v>
+      </c>
+      <c r="H18" s="9">
+        <v>25</v>
+      </c>
+      <c r="I18" s="9">
+        <f t="shared" si="0"/>
+        <v>2875</v>
+      </c>
+      <c r="J18" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="K18" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L18" s="9" t="s">
+        <v>2969</v>
+      </c>
+      <c r="M18" s="9" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="19" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>2986</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>3048</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>2987</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="G19" s="3">
+        <v>0</v>
+      </c>
+      <c r="H19" s="3">
+        <v>20</v>
+      </c>
+      <c r="I19" s="3">
+        <f t="shared" si="0"/>
+        <v>-20</v>
+      </c>
+      <c r="J19" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K19" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L19" s="3" t="s">
+        <v>2969</v>
+      </c>
+    </row>
+    <row r="20" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>2988</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>2989</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>2990</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="G20" s="3">
+        <v>1805</v>
+      </c>
+      <c r="H20" s="3">
+        <v>25</v>
+      </c>
+      <c r="I20" s="3">
+        <f t="shared" si="0"/>
+        <v>1780</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L20" s="3" t="s">
+        <v>2969</v>
+      </c>
+    </row>
+    <row r="21" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>2991</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>2992</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>3045</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="G21" s="3">
+        <v>0</v>
+      </c>
+      <c r="H21" s="3">
+        <v>25</v>
+      </c>
+      <c r="I21" s="3">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K21" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L21" s="3" t="s">
+        <v>2969</v>
+      </c>
+      <c r="M21" s="3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="22" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>678</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>2993</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>680</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="G22" s="3">
+        <v>600</v>
+      </c>
+      <c r="H22" s="3">
+        <v>20</v>
+      </c>
+      <c r="I22" s="3">
+        <f t="shared" si="0"/>
+        <v>580</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L22" s="3" t="s">
+        <v>2969</v>
+      </c>
+    </row>
+    <row r="23" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>2994</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>2995</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>3040</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="G23" s="3">
+        <v>815</v>
+      </c>
+      <c r="H23" s="3">
+        <v>25</v>
+      </c>
+      <c r="I23" s="3">
+        <f t="shared" si="0"/>
+        <v>790</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K23" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L23" s="3" t="s">
+        <v>2969</v>
+      </c>
+    </row>
+    <row r="24" spans="2:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>2327</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>2996</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>2329</v>
+      </c>
+      <c r="F24" s="8" t="s">
+        <v>2187</v>
+      </c>
+      <c r="G24" s="7">
+        <v>130</v>
+      </c>
+      <c r="H24" s="7">
+        <v>30</v>
+      </c>
+      <c r="I24" s="7">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="J24" s="7" t="s">
+        <v>2968</v>
+      </c>
+      <c r="K24" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L24" s="7" t="s">
+        <v>2969</v>
+      </c>
+      <c r="M24" s="7" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="25" spans="2:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>2997</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>2998</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>3058</v>
+      </c>
+      <c r="F25" s="8" t="s">
+        <v>2238</v>
+      </c>
+      <c r="G25" s="7">
+        <v>1940</v>
+      </c>
+      <c r="H25" s="7">
+        <v>30</v>
+      </c>
+      <c r="I25" s="7">
+        <f t="shared" si="0"/>
+        <v>1910</v>
+      </c>
+      <c r="J25" s="7" t="s">
+        <v>2968</v>
+      </c>
+      <c r="K25" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L25" s="7" t="s">
+        <v>2969</v>
+      </c>
+    </row>
+    <row r="26" spans="2:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C26" s="9" t="s">
+        <v>2999</v>
+      </c>
+      <c r="D26" s="9" t="s">
+        <v>3000</v>
+      </c>
+      <c r="E26" s="9" t="s">
+        <v>3001</v>
+      </c>
+      <c r="F26" s="10" t="s">
+        <v>2196</v>
+      </c>
+      <c r="G26" s="9">
+        <v>0</v>
+      </c>
+      <c r="H26" s="9">
+        <v>25</v>
+      </c>
+      <c r="I26" s="9">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J26" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="K26" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L26" s="9" t="s">
+        <v>2969</v>
+      </c>
+    </row>
+    <row r="27" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>3002</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>3003</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>3051</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="G27" s="3">
+        <v>815</v>
+      </c>
+      <c r="H27" s="3">
+        <v>25</v>
+      </c>
+      <c r="I27" s="3">
+        <f t="shared" si="0"/>
+        <v>790</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K27" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L27" s="3" t="s">
+        <v>2969</v>
+      </c>
+    </row>
+    <row r="28" spans="2:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C28" s="9" t="s">
+        <v>1734</v>
+      </c>
+      <c r="D28" s="9" t="s">
+        <v>3004</v>
+      </c>
+      <c r="E28" s="9" t="s">
+        <v>3055</v>
+      </c>
+      <c r="F28" s="10" t="s">
+        <v>2473</v>
+      </c>
+      <c r="G28" s="9">
+        <v>1655</v>
+      </c>
+      <c r="H28" s="9">
+        <v>25</v>
+      </c>
+      <c r="I28" s="9">
+        <f t="shared" si="0"/>
+        <v>1630</v>
+      </c>
+      <c r="J28" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="K28" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L28" s="9" t="s">
+        <v>2969</v>
+      </c>
+    </row>
+    <row r="29" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>3005</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>3006</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>3038</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="G29" s="3">
+        <v>870</v>
+      </c>
+      <c r="H29" s="3">
+        <v>30</v>
+      </c>
+      <c r="I29" s="3">
+        <f t="shared" si="0"/>
+        <v>840</v>
+      </c>
+      <c r="J29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L29" s="3" t="s">
+        <v>2969</v>
+      </c>
+    </row>
+    <row r="30" spans="2:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C30" s="7" t="s">
+        <v>3007</v>
+      </c>
+      <c r="D30" s="7" t="s">
+        <v>3008</v>
+      </c>
+      <c r="E30" s="7" t="s">
+        <v>3059</v>
+      </c>
+      <c r="F30" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G30" s="7">
+        <v>1150</v>
+      </c>
+      <c r="H30" s="7">
+        <v>30</v>
+      </c>
+      <c r="I30" s="7">
+        <f t="shared" si="0"/>
+        <v>1120</v>
+      </c>
+      <c r="J30" s="7" t="s">
+        <v>2968</v>
+      </c>
+      <c r="K30" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L30" s="7" t="s">
+        <v>2969</v>
+      </c>
+    </row>
+    <row r="31" spans="2:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B31" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C31" s="9" t="s">
+        <v>3009</v>
+      </c>
+      <c r="D31" s="9" t="s">
+        <v>3010</v>
+      </c>
+      <c r="E31" s="9" t="s">
+        <v>3011</v>
+      </c>
+      <c r="F31" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="G31" s="9">
+        <v>0</v>
+      </c>
+      <c r="H31" s="9">
+        <v>25</v>
+      </c>
+      <c r="I31" s="9">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J31" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="K31" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L31" s="9" t="s">
+        <v>2969</v>
+      </c>
+    </row>
+    <row r="32" spans="2:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B32" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C32" s="9" t="s">
+        <v>3012</v>
+      </c>
+      <c r="D32" s="9" t="s">
+        <v>3013</v>
+      </c>
+      <c r="E32" s="9" t="s">
+        <v>3014</v>
+      </c>
+      <c r="F32" s="10" t="s">
+        <v>2242</v>
+      </c>
+      <c r="G32" s="9">
+        <v>715</v>
+      </c>
+      <c r="H32" s="9">
+        <v>25</v>
+      </c>
+      <c r="I32" s="9">
+        <f t="shared" si="0"/>
+        <v>690</v>
+      </c>
+      <c r="J32" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="K32" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L32" s="9" t="s">
+        <v>2969</v>
+      </c>
+    </row>
+    <row r="33" spans="2:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B33" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C33" s="9" t="s">
+        <v>3015</v>
+      </c>
+      <c r="D33" s="9" t="s">
+        <v>3016</v>
+      </c>
+      <c r="E33" s="9" t="s">
+        <v>2815</v>
+      </c>
+      <c r="F33" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="G33" s="9">
+        <v>0</v>
+      </c>
+      <c r="H33" s="9">
+        <v>25</v>
+      </c>
+      <c r="I33" s="9">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J33" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="K33" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L33" s="9" t="s">
+        <v>2969</v>
+      </c>
+    </row>
+    <row r="34" spans="2:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B34" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C34" s="7" t="s">
+        <v>3017</v>
+      </c>
+      <c r="D34" s="7" t="s">
+        <v>3018</v>
+      </c>
+      <c r="E34" s="7" t="s">
+        <v>3062</v>
+      </c>
+      <c r="F34" s="8" t="s">
+        <v>2187</v>
+      </c>
+      <c r="G34" s="7">
+        <v>570</v>
+      </c>
+      <c r="H34" s="7">
+        <v>30</v>
+      </c>
+      <c r="I34" s="7">
+        <f t="shared" si="0"/>
+        <v>540</v>
+      </c>
+      <c r="J34" s="7" t="s">
+        <v>2968</v>
+      </c>
+      <c r="K34" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L34" s="7" t="s">
+        <v>2969</v>
+      </c>
+    </row>
+    <row r="35" spans="2:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B35" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C35" s="9" t="s">
+        <v>910</v>
+      </c>
+      <c r="D35" s="9" t="s">
+        <v>3019</v>
+      </c>
+      <c r="E35" s="9" t="s">
+        <v>912</v>
+      </c>
+      <c r="F35" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="G35" s="9">
+        <v>0</v>
+      </c>
+      <c r="H35" s="9">
+        <v>25</v>
+      </c>
+      <c r="I35" s="9">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J35" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="K35" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L35" s="9" t="s">
+        <v>2969</v>
+      </c>
+    </row>
+    <row r="36" spans="2:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B36" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C36" s="9" t="s">
+        <v>3020</v>
+      </c>
+      <c r="D36" s="9" t="s">
+        <v>3021</v>
+      </c>
+      <c r="E36" s="9" t="s">
+        <v>3057</v>
+      </c>
+      <c r="F36" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="G36" s="9">
+        <v>770</v>
+      </c>
+      <c r="H36" s="9">
+        <v>20</v>
+      </c>
+      <c r="I36" s="9">
+        <f t="shared" si="0"/>
+        <v>750</v>
+      </c>
+      <c r="J36" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="K36" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L36" s="9" t="s">
+        <v>2969</v>
+      </c>
+    </row>
+    <row r="37" spans="2:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B37" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C37" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="D37" s="7" t="s">
+        <v>3022</v>
+      </c>
+      <c r="E37" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="F37" s="8" t="s">
+        <v>2189</v>
+      </c>
+      <c r="G37" s="7">
+        <v>800</v>
+      </c>
+      <c r="H37" s="7">
+        <v>30</v>
+      </c>
+      <c r="I37" s="7">
+        <f t="shared" si="0"/>
+        <v>770</v>
+      </c>
+      <c r="J37" s="7" t="s">
+        <v>2968</v>
+      </c>
+      <c r="K37" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L37" s="7" t="s">
+        <v>2969</v>
+      </c>
+    </row>
+    <row r="38" spans="2:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B38" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C38" s="7" t="s">
+        <v>1126</v>
+      </c>
+      <c r="D38" s="7" t="s">
+        <v>3023</v>
+      </c>
+      <c r="E38" s="7" t="s">
+        <v>1128</v>
+      </c>
+      <c r="F38" s="8" t="s">
+        <v>2187</v>
+      </c>
+      <c r="G38" s="7">
+        <v>0</v>
+      </c>
+      <c r="H38" s="7">
+        <v>30</v>
+      </c>
+      <c r="I38" s="7">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J38" s="7" t="s">
+        <v>2968</v>
+      </c>
+      <c r="K38" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L38" s="7" t="s">
+        <v>2969</v>
+      </c>
+    </row>
+    <row r="39" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B39" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>3044</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>3043</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>2008</v>
+      </c>
+      <c r="F39" s="4" t="s">
+        <v>2189</v>
+      </c>
+      <c r="G39" s="3">
+        <v>0</v>
+      </c>
+      <c r="H39" s="3">
+        <v>30</v>
+      </c>
+      <c r="I39" s="3">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J39" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K39" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L39" s="3" t="s">
+        <v>2969</v>
+      </c>
+    </row>
+    <row r="40" spans="2:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B40" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C40" s="9" t="s">
+        <v>900</v>
+      </c>
+      <c r="D40" s="9" t="s">
+        <v>3024</v>
+      </c>
+      <c r="E40" s="9" t="s">
+        <v>902</v>
+      </c>
+      <c r="F40" s="10" t="s">
+        <v>2137</v>
+      </c>
+      <c r="G40" s="9">
+        <v>405</v>
+      </c>
+      <c r="H40" s="9">
+        <v>25</v>
+      </c>
+      <c r="I40" s="9">
+        <f t="shared" si="0"/>
+        <v>380</v>
+      </c>
+      <c r="J40" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="K40" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L40" s="9" t="s">
+        <v>2969</v>
+      </c>
+    </row>
+    <row r="41" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B41" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>3049</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>3025</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>3050</v>
+      </c>
+      <c r="F41" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="G41" s="3">
+        <v>950</v>
+      </c>
+      <c r="H41" s="3">
+        <v>30</v>
+      </c>
+      <c r="I41" s="3">
+        <f t="shared" si="0"/>
+        <v>920</v>
+      </c>
+      <c r="J41" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K41" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L41" s="3" t="s">
+        <v>2969</v>
+      </c>
+    </row>
+    <row r="42" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B42" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>3036</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>3037</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>1409</v>
+      </c>
+      <c r="F42" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="G42" s="3">
+        <v>940</v>
+      </c>
+      <c r="H42" s="3">
+        <v>20</v>
+      </c>
+      <c r="I42" s="3">
+        <f t="shared" si="0"/>
+        <v>920</v>
+      </c>
+      <c r="J42" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K42" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L42" s="3" t="s">
+        <v>2969</v>
+      </c>
+    </row>
+    <row r="43" spans="2:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B43" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C43" s="9" t="s">
+        <v>1876</v>
+      </c>
+      <c r="D43" s="9" t="s">
+        <v>3026</v>
+      </c>
+      <c r="E43" s="9" t="s">
+        <v>1878</v>
+      </c>
+      <c r="F43" s="10" t="s">
+        <v>2242</v>
+      </c>
+      <c r="G43" s="9">
+        <v>0</v>
+      </c>
+      <c r="H43" s="9">
+        <v>25</v>
+      </c>
+      <c r="I43" s="9">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J43" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="K43" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L43" s="9" t="s">
+        <v>2969</v>
+      </c>
+    </row>
+    <row r="44" spans="2:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B44" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C44" s="7" t="s">
+        <v>3063</v>
+      </c>
+      <c r="D44" s="7" t="s">
+        <v>3027</v>
+      </c>
+      <c r="E44" s="7" t="s">
+        <v>3064</v>
+      </c>
+      <c r="F44" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G44" s="7">
+        <v>0</v>
+      </c>
+      <c r="H44" s="7">
+        <v>30</v>
+      </c>
+      <c r="I44" s="7">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J44" s="7" t="s">
+        <v>2968</v>
+      </c>
+      <c r="K44" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L44" s="7" t="s">
+        <v>2969</v>
+      </c>
+    </row>
+    <row r="45" spans="2:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B45" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C45" s="9" t="s">
+        <v>3028</v>
+      </c>
+      <c r="D45" s="9" t="s">
+        <v>3029</v>
+      </c>
+      <c r="E45" s="9" t="s">
+        <v>3030</v>
+      </c>
+      <c r="F45" s="10" t="s">
+        <v>2196</v>
+      </c>
+      <c r="G45" s="9">
+        <v>1565</v>
+      </c>
+      <c r="H45" s="9">
+        <v>25</v>
+      </c>
+      <c r="I45" s="9">
+        <f t="shared" si="0"/>
+        <v>1540</v>
+      </c>
+      <c r="J45" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="K45" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L45" s="9" t="s">
+        <v>2969</v>
+      </c>
+    </row>
+    <row r="46" spans="2:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B46" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C46" s="7" t="s">
+        <v>3031</v>
+      </c>
+      <c r="D46" s="7" t="s">
+        <v>3032</v>
+      </c>
+      <c r="E46" s="7" t="s">
+        <v>3033</v>
+      </c>
+      <c r="F46" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="G46" s="7">
+        <v>935</v>
+      </c>
+      <c r="H46" s="7">
+        <v>35</v>
+      </c>
+      <c r="I46" s="7">
+        <f t="shared" si="0"/>
+        <v>900</v>
+      </c>
+      <c r="J46" s="7" t="s">
+        <v>2968</v>
+      </c>
+      <c r="K46" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L46" s="7" t="s">
+        <v>2969</v>
+      </c>
+    </row>
+    <row r="47" spans="2:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B47" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C47" s="7" t="s">
+        <v>3034</v>
+      </c>
+      <c r="D47" s="7" t="s">
+        <v>3035</v>
+      </c>
+      <c r="E47" s="7" t="s">
+        <v>3065</v>
+      </c>
+      <c r="F47" s="8" t="s">
+        <v>2238</v>
+      </c>
+      <c r="G47" s="7">
+        <v>750</v>
+      </c>
+      <c r="H47" s="7">
+        <v>30</v>
+      </c>
+      <c r="I47" s="7">
+        <f t="shared" si="0"/>
+        <v>720</v>
+      </c>
+      <c r="J47" s="7" t="s">
+        <v>2968</v>
+      </c>
+      <c r="K47" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L47" s="7" t="s">
+        <v>2969</v>
+      </c>
+    </row>
+    <row r="48" spans="2:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B48" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C48" s="7" t="s">
+        <v>2157</v>
+      </c>
+      <c r="D48" s="7" t="s">
+        <v>2158</v>
+      </c>
+      <c r="E48" s="7" t="s">
+        <v>2159</v>
+      </c>
+      <c r="F48" s="7" t="s">
+        <v>2137</v>
+      </c>
+      <c r="G48" s="7">
+        <v>480</v>
+      </c>
+      <c r="H48" s="7">
+        <v>30</v>
+      </c>
+      <c r="I48" s="7">
+        <f>G48-H48</f>
+        <v>450</v>
+      </c>
+      <c r="J48" s="7" t="s">
+        <v>2968</v>
+      </c>
+      <c r="K48" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L48" s="7" t="s">
+        <v>2131</v>
+      </c>
+      <c r="M48" s="7" t="s">
+        <v>3066</v>
       </c>
     </row>
   </sheetData>
@@ -37878,7 +45490,7 @@
         <v>25</v>
       </c>
       <c r="I35" s="3">
-        <f t="shared" ref="I35:I52" si="1">G35-H35</f>
+        <f t="shared" ref="I35:I66" si="1">G35-H35</f>
         <v>660</v>
       </c>
       <c r="J35" s="3" t="s">
@@ -41560,7 +49172,7 @@
         <v>25</v>
       </c>
       <c r="I35" s="12">
-        <f t="shared" ref="I35:I53" si="1">G35-H35</f>
+        <f t="shared" ref="I35:I66" si="1">G35-H35</f>
         <v>1610</v>
       </c>
       <c r="J35" s="3" t="s">
@@ -47990,7 +55602,7 @@
         <v>25</v>
       </c>
       <c r="I35" s="18">
-        <f t="shared" ref="I35:I53" si="1">G35-H35</f>
+        <f t="shared" ref="I35:I66" si="1">G35-H35</f>
         <v>1510</v>
       </c>
       <c r="J35" s="18" t="s">

--- a/data/Apr/Data.xlsx
+++ b/data/Apr/Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Freelance\TextInputter\data\Apr\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10B71B07-6EFE-4FC8-B717-11C035502575}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{152E4F62-C679-4271-B697-7F243D8C48A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="9" activeTab="23" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="10" activeTab="24" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01-04" sheetId="4" r:id="rId1"/>
@@ -37,6 +37,7 @@
     <sheet name="25-04" sheetId="26" r:id="rId22"/>
     <sheet name="27-04" sheetId="27" r:id="rId23"/>
     <sheet name="28-04" sheetId="28" r:id="rId24"/>
+    <sheet name="29-04" sheetId="29" r:id="rId25"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -59,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9861" uniqueCount="3067">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10344" uniqueCount="3213">
   <si>
     <t>THU 4</t>
   </si>
@@ -8965,30 +8966,48 @@
     <t>NGAY 28-4</t>
   </si>
   <si>
+    <t>NGUYỄN MINH DUY</t>
+  </si>
+  <si>
+    <t>90/35 Trần Văn Ơn, Phường Tân Sơn Nhì</t>
+  </si>
+  <si>
+    <t>28-04-2026</t>
+  </si>
+  <si>
+    <t>THƯƠNG 1994</t>
+  </si>
+  <si>
+    <t>Tòa S501, Vinhome grand park, long thạnh mỹ</t>
+  </si>
+  <si>
+    <t>HƯƠNG TRẦN</t>
+  </si>
+  <si>
+    <t>261/26c chu văn an p12</t>
+  </si>
+  <si>
+    <t>Thanh Thanh Tô</t>
+  </si>
+  <si>
+    <t>HD017096</t>
+  </si>
+  <si>
+    <t>2/16 tân lập p8</t>
+  </si>
+  <si>
+    <t>HD016989</t>
+  </si>
+  <si>
     <t>AT 28-04</t>
   </si>
   <si>
-    <t>28-04-2026</t>
-  </si>
-  <si>
-    <t>HƯƠNG TRẦN</t>
-  </si>
-  <si>
-    <t>Thanh Thanh Tô</t>
-  </si>
-  <si>
-    <t>HD017096</t>
-  </si>
-  <si>
-    <t>2/16 tân lập p8</t>
-  </si>
-  <si>
-    <t>HD016989</t>
-  </si>
-  <si>
     <t>Lê Thảo</t>
   </si>
   <si>
+    <t>HD016900</t>
+  </si>
+  <si>
     <t>3 Đặng Dung, P Tân Định</t>
   </si>
   <si>
@@ -8998,6 +9017,15 @@
     <t>HD016775</t>
   </si>
   <si>
+    <t>Landmark 1 vinhome central park p thạnh mỹ tây</t>
+  </si>
+  <si>
+    <t>chi - fb Mi Na</t>
+  </si>
+  <si>
+    <t>HD017060</t>
+  </si>
+  <si>
     <t>1619/29 phạm thế hiển phường 6</t>
   </si>
   <si>
@@ -9013,6 +9041,12 @@
     <t>Thiên Thiên</t>
   </si>
   <si>
+    <t>HD017084</t>
+  </si>
+  <si>
+    <t>20 đường số 6, linh chiểu</t>
+  </si>
+  <si>
     <t>huyền nguyễn</t>
   </si>
   <si>
@@ -9022,6 +9056,9 @@
     <t>Sunwah White House fb Mzzton</t>
   </si>
   <si>
+    <t>HD017045</t>
+  </si>
+  <si>
     <t>90 nguyễn hữu cảnh thạnh mỹ tây</t>
   </si>
   <si>
@@ -9040,6 +9077,9 @@
     <t>HD016907</t>
   </si>
   <si>
+    <t>188 Nguyễn Văn Công, P.3</t>
+  </si>
+  <si>
     <t>HD017134</t>
   </si>
   <si>
@@ -9049,6 +9089,9 @@
     <t>HD016967</t>
   </si>
   <si>
+    <t>22/31/4 đường số 21, Phường 8 (phường Thông Tây Hội mới)</t>
+  </si>
+  <si>
     <t>HD016592</t>
   </si>
   <si>
@@ -9058,6 +9101,9 @@
     <t>HD017135</t>
   </si>
   <si>
+    <t>10/14 âu duong lân p3</t>
+  </si>
+  <si>
     <t>thảo fb Nguyễn Bình Phương Trinh</t>
   </si>
   <si>
@@ -9073,21 +9119,33 @@
     <t>HD016998</t>
   </si>
   <si>
+    <t>536/43/40 âu cơ p. bảy hiền</t>
+  </si>
+  <si>
     <t>HD016824</t>
   </si>
   <si>
+    <t>485 nguyễn đình chiểu</t>
+  </si>
+  <si>
     <t>Khánh Vy Đỗ</t>
   </si>
   <si>
     <t>HD017102</t>
   </si>
   <si>
+    <t>24 đường số 6 - tam phú</t>
+  </si>
+  <si>
     <t>Thảo Susi</t>
   </si>
   <si>
     <t>HD016982</t>
   </si>
   <si>
+    <t>10/16 đường số 8 phường Bình Hưng Hòa</t>
+  </si>
+  <si>
     <t>Lynn Pham</t>
   </si>
   <si>
@@ -9118,6 +9176,9 @@
     <t>HD016850</t>
   </si>
   <si>
+    <t>V6, Sunrise city south tower 23 nguyễn hữu thọ, phường tân hưng</t>
+  </si>
+  <si>
     <t>HD016826</t>
   </si>
   <si>
@@ -9127,24 +9188,51 @@
     <t>HD016990</t>
   </si>
   <si>
+    <t>220/18 Hồ Văn Huê, P.9</t>
+  </si>
+  <si>
     <t>HD017081</t>
   </si>
   <si>
     <t>HD017133</t>
   </si>
   <si>
+    <t>BN182</t>
+  </si>
+  <si>
+    <t>HD017028</t>
+  </si>
+  <si>
     <t>HD016798</t>
   </si>
   <si>
+    <t>Truc Trieu</t>
+  </si>
+  <si>
     <t>HD017106</t>
   </si>
   <si>
+    <t>Số nhà A6, Garden Home Thủ Đức, Đường số 3, QL13, Phường Hiệp Binh Phước</t>
+  </si>
+  <si>
+    <t>người nhận nana - fb Oanh Tống</t>
+  </si>
+  <si>
+    <t>HD016818</t>
+  </si>
+  <si>
     <t>HD016728</t>
   </si>
   <si>
+    <t>Vũ Thùy Dương</t>
+  </si>
+  <si>
     <t>HD016977</t>
   </si>
   <si>
+    <t>96/50/5 đường phạm đăng giảng, bình hưng hòa</t>
+  </si>
+  <si>
     <t>Duyên Huỳnh</t>
   </si>
   <si>
@@ -9169,97 +9257,448 @@
     <t>H0017097</t>
   </si>
   <si>
-    <t>người nhận nana - fb Oanh Tống</t>
-  </si>
-  <si>
-    <t>HD016818</t>
-  </si>
-  <si>
-    <t>24 đường số 6 - tam phú</t>
-  </si>
-  <si>
-    <t>261/26c chu văn an p12</t>
-  </si>
-  <si>
-    <t>22/31/4 đường số 21, Phường 8 (phường Thông Tây Hội mới)</t>
-  </si>
-  <si>
-    <t>HD017084</t>
-  </si>
-  <si>
-    <t>20 đường số 6, linh chiểu</t>
-  </si>
-  <si>
-    <t>HD017028</t>
-  </si>
-  <si>
-    <t>BN182</t>
-  </si>
-  <si>
-    <t>188 Nguyễn Văn Công, P.3</t>
-  </si>
-  <si>
-    <t>90/35 Trần Văn Ơn, Phường Tân Sơn Nhì</t>
-  </si>
-  <si>
-    <t>NGUYỄN MINH DUY</t>
-  </si>
-  <si>
-    <t>HD017045</t>
-  </si>
-  <si>
-    <t>Truc Trieu</t>
-  </si>
-  <si>
-    <t>Số nhà A6, Garden Home Thủ Đức, Đường số 3, QL13, Phường Hiệp Binh Phước</t>
-  </si>
-  <si>
-    <t>536/43/40 âu cơ p. bảy hiền</t>
-  </si>
-  <si>
-    <t>Landmark 1 vinhome central park p thạnh mỹ tây</t>
-  </si>
-  <si>
-    <t>Tòa S501, Vinhome grand park, long thạnh mỹ</t>
-  </si>
-  <si>
-    <t>THƯƠNG 1994</t>
-  </si>
-  <si>
-    <t>485 nguyễn đình chiểu</t>
-  </si>
-  <si>
-    <t>HD016900</t>
-  </si>
-  <si>
-    <t>220/18 Hồ Văn Huê, P.9</t>
-  </si>
-  <si>
-    <t>10/14 âu duong lân p3</t>
-  </si>
-  <si>
-    <t>10/16 đường số 8 phường Bình Hưng Hòa</t>
-  </si>
-  <si>
-    <t>chi - fb Mi Na</t>
-  </si>
-  <si>
-    <t>HD017060</t>
-  </si>
-  <si>
-    <t>V6, Sunrise city south tower 23 nguyễn hữu thọ, phường tân hưng</t>
-  </si>
-  <si>
-    <t>Vũ Thùy Dương</t>
-  </si>
-  <si>
-    <t>96/50/5 đường phạm đăng giảng, bình hưng hòa</t>
-  </si>
-  <si>
     <t>1707 Phạm thế hiển phường bình đông</t>
   </si>
   <si>
     <t>đơn chuyển AT 28-04</t>
+  </si>
+  <si>
+    <t>NGAY 29-4</t>
+  </si>
+  <si>
+    <t>HD017294</t>
+  </si>
+  <si>
+    <t>29-04-2026</t>
+  </si>
+  <si>
+    <t>Phương Như</t>
+  </si>
+  <si>
+    <t>HD017191</t>
+  </si>
+  <si>
+    <t>10 đường số 2 binh thuận tân thuận</t>
+  </si>
+  <si>
+    <t>AT 29-04</t>
+  </si>
+  <si>
+    <t>Như Ý Nguyễn</t>
+  </si>
+  <si>
+    <t>HD017549</t>
+  </si>
+  <si>
+    <t>4 đào trí phường phú thuận</t>
+  </si>
+  <si>
+    <t>Cindy Nguyễn</t>
+  </si>
+  <si>
+    <t>HD017482</t>
+  </si>
+  <si>
+    <t>12/7 đường P - Khu phố Mỹ Tú 2 - P. Tân Hưng</t>
+  </si>
+  <si>
+    <t>Võ Ngọc Đan Thanh</t>
+  </si>
+  <si>
+    <t>HD017534</t>
+  </si>
+  <si>
+    <t>300 Khuông Việt, phường Phú Trung</t>
+  </si>
+  <si>
+    <t>HD017550</t>
+  </si>
+  <si>
+    <t>HD017199</t>
+  </si>
+  <si>
+    <t>Toà Landmark 2</t>
+  </si>
+  <si>
+    <t>HD017210</t>
+  </si>
+  <si>
+    <t>9 tiên lân 17, bà điểm Phòng 306</t>
+  </si>
+  <si>
+    <t>Chanboramey 015738168</t>
+  </si>
+  <si>
+    <t>157 nguyễn du</t>
+  </si>
+  <si>
+    <t>HD017493</t>
+  </si>
+  <si>
+    <t>404 VÕ VĂN TẦN</t>
+  </si>
+  <si>
+    <t>HD017437</t>
+  </si>
+  <si>
+    <t>HD017518</t>
+  </si>
+  <si>
+    <t>212 b/d11 nguyen trai</t>
+  </si>
+  <si>
+    <t>Nguyễn Thu Hoa</t>
+  </si>
+  <si>
+    <t>HD017198</t>
+  </si>
+  <si>
+    <t>190C mai xuân thưởng.p2</t>
+  </si>
+  <si>
+    <t>HD017515</t>
+  </si>
+  <si>
+    <t>Lan Anh Nguyễn</t>
+  </si>
+  <si>
+    <t>HD017489</t>
+  </si>
+  <si>
+    <t>70 đường số 1 KDC nam long</t>
+  </si>
+  <si>
+    <t>smail- huyền trang</t>
+  </si>
+  <si>
+    <t>HD017006</t>
+  </si>
+  <si>
+    <t>124 đường 24b p.bình trị Đông b</t>
+  </si>
+  <si>
+    <t>Minh Nguyễn</t>
+  </si>
+  <si>
+    <t>HD017439</t>
+  </si>
+  <si>
+    <t>Hoa Hoa</t>
+  </si>
+  <si>
+    <t>HD017317</t>
+  </si>
+  <si>
+    <t>Chung cư topaz elite tạ quang bửu p4 Sảnh Dragon 1B</t>
+  </si>
+  <si>
+    <t>HD017442</t>
+  </si>
+  <si>
+    <t>Tran Kim</t>
+  </si>
+  <si>
+    <t>77A Đường số 9, p.Khánh hội</t>
+  </si>
+  <si>
+    <t>Chân Chân</t>
+  </si>
+  <si>
+    <t>HD017536</t>
+  </si>
+  <si>
+    <t>69/15 Võ Thị Liễu, An Phú Đông</t>
+  </si>
+  <si>
+    <t>Bé Ty - fb Anh Lan</t>
+  </si>
+  <si>
+    <t>HD017415</t>
+  </si>
+  <si>
+    <t>532/3/6 Kinh Dương Vương, Phường An Lạc</t>
+  </si>
+  <si>
+    <t>Lucia Nguyễn</t>
+  </si>
+  <si>
+    <t>HD017190</t>
+  </si>
+  <si>
+    <t>Block E eco green nguyễn văn linh</t>
+  </si>
+  <si>
+    <t>Diệu Linh</t>
+  </si>
+  <si>
+    <t>HD017206</t>
+  </si>
+  <si>
+    <t>103 đường số 6, phường Bình Hưng Hòa</t>
+  </si>
+  <si>
+    <t>Minh Hải ( Thanh Phan )</t>
+  </si>
+  <si>
+    <t>HD017443</t>
+  </si>
+  <si>
+    <t>Lê Tố Quyên</t>
+  </si>
+  <si>
+    <t>HD017197</t>
+  </si>
+  <si>
+    <t>149/1 +3 Nơ Trang Long p12</t>
+  </si>
+  <si>
+    <t>HD017179</t>
+  </si>
+  <si>
+    <t>HD017570</t>
+  </si>
+  <si>
+    <t>HD016638</t>
+  </si>
+  <si>
+    <t>Kim Phụng (inst -suicao20_12)</t>
+  </si>
+  <si>
+    <t>HD017491</t>
+  </si>
+  <si>
+    <t>HD017278</t>
+  </si>
+  <si>
+    <t>HD017481</t>
+  </si>
+  <si>
+    <t>Anh Lee</t>
+  </si>
+  <si>
+    <t>HD017305</t>
+  </si>
+  <si>
+    <t>89 lê thị chợ p. phú thuận</t>
+  </si>
+  <si>
+    <t>Thư Mon</t>
+  </si>
+  <si>
+    <t>HD017416</t>
+  </si>
+  <si>
+    <t>Chung cư sài gòn mia, đường 9a, kdc trung sơn, bình hưng</t>
+  </si>
+  <si>
+    <t>HD017205</t>
+  </si>
+  <si>
+    <t>Jemial Vo</t>
+  </si>
+  <si>
+    <t>HD017495</t>
+  </si>
+  <si>
+    <t>Trịnh Thảo Như</t>
+  </si>
+  <si>
+    <t>HD017282</t>
+  </si>
+  <si>
+    <t>Yến Nhi ( chị thảo )</t>
+  </si>
+  <si>
+    <t>HD017513</t>
+  </si>
+  <si>
+    <t>An Nghi</t>
+  </si>
+  <si>
+    <t>HD017459</t>
+  </si>
+  <si>
+    <t>007 Lô B, Đường C6, Cc Tây Thạnh, P. Tây Thạnh</t>
+  </si>
+  <si>
+    <t>HD017005</t>
+  </si>
+  <si>
+    <t>Gia Trân fb Hà Võ</t>
+  </si>
+  <si>
+    <t>HD017164</t>
+  </si>
+  <si>
+    <t>Nhung SaLin</t>
+  </si>
+  <si>
+    <t>HD017163</t>
+  </si>
+  <si>
+    <t>19a Trần Quang diệu p13</t>
+  </si>
+  <si>
+    <t>HD017297</t>
+  </si>
+  <si>
+    <t>hương</t>
+  </si>
+  <si>
+    <t>HD017535</t>
+  </si>
+  <si>
+    <t>97 đường 24A - bình trị đông B</t>
+  </si>
+  <si>
+    <t>HD017173</t>
+  </si>
+  <si>
+    <t>132 bến Vân đồn p6</t>
+  </si>
+  <si>
+    <t>Thiên Trang</t>
+  </si>
+  <si>
+    <t>HD017325</t>
+  </si>
+  <si>
+    <t>221 trần bình trọng p2</t>
+  </si>
+  <si>
+    <t>HD017209</t>
+  </si>
+  <si>
+    <t>HD017479</t>
+  </si>
+  <si>
+    <t>(HLH express): Tổng kho Sài Gòn 9, Lô G2, Đường K1, KCN Cát Lái</t>
+  </si>
+  <si>
+    <t>Cô Ngọc ( gửi Châu)</t>
+  </si>
+  <si>
+    <t>HD017166</t>
+  </si>
+  <si>
+    <t>Hằng</t>
+  </si>
+  <si>
+    <t>HD017480</t>
+  </si>
+  <si>
+    <t>Block A2 Topaz City, số 39 đường Cao Lỗ, P4</t>
+  </si>
+  <si>
+    <t>HD017572</t>
+  </si>
+  <si>
+    <t>SUMO</t>
+  </si>
+  <si>
+    <t>487 le van sy f12</t>
+  </si>
+  <si>
+    <t>438 phan văn trị, p. hạnh thông</t>
+  </si>
+  <si>
+    <t>406/8 Cộng Hoà, phường 13</t>
+  </si>
+  <si>
+    <t>Keo Kimyou</t>
+  </si>
+  <si>
+    <t>Lương Thúy</t>
+  </si>
+  <si>
+    <t>549/3 lê văn thọ</t>
+  </si>
+  <si>
+    <t>128/25 nguyễn lâm p3</t>
+  </si>
+  <si>
+    <t>CHỊ MYMY</t>
+  </si>
+  <si>
+    <t>HD017180</t>
+  </si>
+  <si>
+    <t>175/87/8/4 đường 2 tăng Nhơn Phú b</t>
+  </si>
+  <si>
+    <t>Minh Nguyệt + Lin Xiao + Hàng Aỉ</t>
+  </si>
+  <si>
+    <t>C16-17 lô C1, đường DD5, phường Đông Hưng Thuận</t>
+  </si>
+  <si>
+    <t>7a/5/42 thành thái p14</t>
+  </si>
+  <si>
+    <t>_____lay_____</t>
+  </si>
+  <si>
+    <t>164/22 Vo Thi Sau, D.3</t>
+  </si>
+  <si>
+    <t>thanh (NHẬN HÀNG CHO TRÀ LY)</t>
+  </si>
+  <si>
+    <t>HD016946</t>
+  </si>
+  <si>
+    <t>Loan Đặng</t>
+  </si>
+  <si>
+    <t>45 Lê Anh Xuân Bến Thành</t>
+  </si>
+  <si>
+    <t>39 hồ hảo hớn, P. cô giang</t>
+  </si>
+  <si>
+    <t>HD017537</t>
+  </si>
+  <si>
+    <t>Natalie Nguyen</t>
+  </si>
+  <si>
+    <t>HD017387</t>
+  </si>
+  <si>
+    <t>239/64 Trần Văn Đang, phường 11</t>
+  </si>
+  <si>
+    <t>481/11 Đoàn Văn Bơ, phường Xóm Chiếu</t>
+  </si>
+  <si>
+    <t>5 Lê Quý Đôn phường Võ Thị Sáu</t>
+  </si>
+  <si>
+    <t>Thúy Linh</t>
+  </si>
+  <si>
+    <t>Thuý Stella</t>
+  </si>
+  <si>
+    <t>68/25 trần quang khải p tân định</t>
+  </si>
+  <si>
+    <t>73 hoa sữa phường 7 cầu kiệu</t>
+  </si>
+  <si>
+    <t>HD017543</t>
+  </si>
+  <si>
+    <t>Chí Đinh</t>
+  </si>
+  <si>
+    <t>hẻm 191 cống quỳnh, nhà trọ an house</t>
+  </si>
+  <si>
+    <t>016701721-010535777</t>
+  </si>
+  <si>
+    <t>0898460039</t>
   </si>
 </sst>
 </file>
@@ -9388,7 +9827,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -9427,6 +9866,7 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="49" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -42524,10 +42964,12 @@
   <dimension ref="A1:P48"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="1" max="2" width="9.140625" customWidth="1"/>
     <col min="3" max="3" width="39.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="71.85546875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.5703125" customWidth="1"/>
+    <col min="7" max="11" width="9.140625" customWidth="1"/>
     <col min="12" max="12" width="10.42578125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="19.5703125" bestFit="1" customWidth="1"/>
   </cols>
@@ -42598,10 +43040,10 @@
         <v>18</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>3047</v>
+        <v>2968</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>3046</v>
+        <v>2969</v>
       </c>
       <c r="F3" s="4" t="s">
         <v>208</v>
@@ -42613,7 +43055,7 @@
         <v>50</v>
       </c>
       <c r="I3" s="3">
-        <f t="shared" ref="I3:I47" si="0">G3-H3</f>
+        <f t="shared" ref="I3:I48" si="0">G3-H3</f>
         <v>8980</v>
       </c>
       <c r="J3" s="3" t="s">
@@ -42623,7 +43065,7 @@
         <v>24</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>2969</v>
+        <v>2970</v>
       </c>
     </row>
     <row r="4" spans="1:16" s="9" customFormat="1" x14ac:dyDescent="0.25">
@@ -42659,7 +43101,7 @@
         <v>24</v>
       </c>
       <c r="L4" s="9" t="s">
-        <v>2969</v>
+        <v>2970</v>
       </c>
     </row>
     <row r="5" spans="1:16" s="9" customFormat="1" x14ac:dyDescent="0.25">
@@ -42695,7 +43137,7 @@
         <v>24</v>
       </c>
       <c r="L5" s="9" t="s">
-        <v>2969</v>
+        <v>2970</v>
       </c>
     </row>
     <row r="6" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -42706,10 +43148,10 @@
         <v>18</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>3054</v>
+        <v>2971</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>3053</v>
+        <v>2972</v>
       </c>
       <c r="F6" s="6" t="s">
         <v>2672</v>
@@ -42731,7 +43173,7 @@
         <v>24</v>
       </c>
       <c r="L6" s="5" t="s">
-        <v>2969</v>
+        <v>2970</v>
       </c>
     </row>
     <row r="7" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -42767,7 +43209,7 @@
         <v>24</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>2969</v>
+        <v>2970</v>
       </c>
     </row>
     <row r="8" spans="1:16" s="9" customFormat="1" x14ac:dyDescent="0.25">
@@ -42803,7 +43245,7 @@
         <v>24</v>
       </c>
       <c r="L8" s="9" t="s">
-        <v>2969</v>
+        <v>2970</v>
       </c>
     </row>
     <row r="9" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -42839,7 +43281,7 @@
         <v>24</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>2969</v>
+        <v>2970</v>
       </c>
     </row>
     <row r="10" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -42850,10 +43292,10 @@
         <v>18</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>2970</v>
+        <v>2973</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>3039</v>
+        <v>2974</v>
       </c>
       <c r="F10" s="4" t="s">
         <v>38</v>
@@ -42875,7 +43317,7 @@
         <v>24</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>2969</v>
+        <v>2970</v>
       </c>
     </row>
     <row r="11" spans="1:16" s="9" customFormat="1" x14ac:dyDescent="0.25">
@@ -42883,13 +43325,13 @@
         <v>18</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>2971</v>
+        <v>2975</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>2972</v>
+        <v>2976</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>2973</v>
+        <v>2977</v>
       </c>
       <c r="F11" s="10" t="s">
         <v>88</v>
@@ -42911,7 +43353,7 @@
         <v>24</v>
       </c>
       <c r="L11" s="9" t="s">
-        <v>2969</v>
+        <v>2970</v>
       </c>
     </row>
     <row r="12" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -42922,7 +43364,7 @@
         <v>47</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>2974</v>
+        <v>2978</v>
       </c>
       <c r="E12" s="7" t="s">
         <v>49</v>
@@ -42941,13 +43383,13 @@
         <v>880</v>
       </c>
       <c r="J12" s="7" t="s">
-        <v>2968</v>
+        <v>2979</v>
       </c>
       <c r="K12" s="7" t="s">
         <v>24</v>
       </c>
       <c r="L12" s="7" t="s">
-        <v>2969</v>
+        <v>2970</v>
       </c>
     </row>
     <row r="13" spans="1:16" s="9" customFormat="1" x14ac:dyDescent="0.25">
@@ -42955,13 +43397,13 @@
         <v>18</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>2975</v>
+        <v>2980</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>3056</v>
+        <v>2981</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>2976</v>
+        <v>2982</v>
       </c>
       <c r="F13" s="10" t="s">
         <v>2137</v>
@@ -42983,7 +43425,7 @@
         <v>24</v>
       </c>
       <c r="L13" s="9" t="s">
-        <v>2969</v>
+        <v>2970</v>
       </c>
     </row>
     <row r="14" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -42991,13 +43433,13 @@
         <v>18</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>2977</v>
+        <v>2983</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>2978</v>
+        <v>2984</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>3052</v>
+        <v>2985</v>
       </c>
       <c r="F14" s="4" t="s">
         <v>38</v>
@@ -43019,7 +43461,7 @@
         <v>24</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>2969</v>
+        <v>2970</v>
       </c>
     </row>
     <row r="15" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -43027,13 +43469,13 @@
         <v>18</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>3060</v>
+        <v>2986</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>3061</v>
+        <v>2987</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>2979</v>
+        <v>2988</v>
       </c>
       <c r="F15" s="8" t="s">
         <v>2238</v>
@@ -43049,13 +43491,13 @@
         <v>1550</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>2968</v>
+        <v>2979</v>
       </c>
       <c r="K15" s="7" t="s">
         <v>24</v>
       </c>
       <c r="L15" s="7" t="s">
-        <v>2969</v>
+        <v>2970</v>
       </c>
     </row>
     <row r="16" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -43063,13 +43505,13 @@
         <v>18</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>2980</v>
+        <v>2989</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>2981</v>
+        <v>2990</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>2982</v>
+        <v>2991</v>
       </c>
       <c r="F16" s="8" t="s">
         <v>143</v>
@@ -43085,13 +43527,13 @@
         <v>790</v>
       </c>
       <c r="J16" s="7" t="s">
-        <v>2968</v>
+        <v>2979</v>
       </c>
       <c r="K16" s="7" t="s">
         <v>24</v>
       </c>
       <c r="L16" s="7" t="s">
-        <v>2969</v>
+        <v>2970</v>
       </c>
     </row>
     <row r="17" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -43099,13 +43541,13 @@
         <v>18</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>2983</v>
+        <v>2992</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>3041</v>
+        <v>2993</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>3042</v>
+        <v>2994</v>
       </c>
       <c r="F17" s="4" t="s">
         <v>116</v>
@@ -43127,7 +43569,7 @@
         <v>24</v>
       </c>
       <c r="L17" s="3" t="s">
-        <v>2969</v>
+        <v>2970</v>
       </c>
     </row>
     <row r="18" spans="2:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
@@ -43135,10 +43577,10 @@
         <v>18</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>2984</v>
+        <v>2995</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>2985</v>
+        <v>2996</v>
       </c>
       <c r="E18" s="9" t="s">
         <v>698</v>
@@ -43163,7 +43605,7 @@
         <v>24</v>
       </c>
       <c r="L18" s="9" t="s">
-        <v>2969</v>
+        <v>2970</v>
       </c>
       <c r="M18" s="9" t="s">
         <v>361</v>
@@ -43174,13 +43616,13 @@
         <v>18</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>2986</v>
+        <v>2997</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>3048</v>
+        <v>2998</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>2987</v>
+        <v>2999</v>
       </c>
       <c r="F19" s="4" t="s">
         <v>38</v>
@@ -43202,7 +43644,7 @@
         <v>24</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>2969</v>
+        <v>2970</v>
       </c>
     </row>
     <row r="20" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -43210,13 +43652,13 @@
         <v>18</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>2988</v>
+        <v>3000</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>2989</v>
+        <v>3001</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>2990</v>
+        <v>3002</v>
       </c>
       <c r="F20" s="4" t="s">
         <v>88</v>
@@ -43238,7 +43680,7 @@
         <v>24</v>
       </c>
       <c r="L20" s="3" t="s">
-        <v>2969</v>
+        <v>2970</v>
       </c>
     </row>
     <row r="21" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -43246,13 +43688,13 @@
         <v>18</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>2991</v>
+        <v>3003</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>2992</v>
+        <v>3004</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>3045</v>
+        <v>3005</v>
       </c>
       <c r="F21" s="4" t="s">
         <v>46</v>
@@ -43274,7 +43716,7 @@
         <v>24</v>
       </c>
       <c r="L21" s="3" t="s">
-        <v>2969</v>
+        <v>2970</v>
       </c>
       <c r="M21" s="3" t="s">
         <v>68</v>
@@ -43288,7 +43730,7 @@
         <v>678</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>2993</v>
+        <v>3006</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>680</v>
@@ -43313,7 +43755,7 @@
         <v>24</v>
       </c>
       <c r="L22" s="3" t="s">
-        <v>2969</v>
+        <v>2970</v>
       </c>
     </row>
     <row r="23" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -43321,13 +43763,13 @@
         <v>18</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>2994</v>
+        <v>3007</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>2995</v>
+        <v>3008</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>3040</v>
+        <v>3009</v>
       </c>
       <c r="F23" s="4" t="s">
         <v>46</v>
@@ -43349,7 +43791,7 @@
         <v>24</v>
       </c>
       <c r="L23" s="3" t="s">
-        <v>2969</v>
+        <v>2970</v>
       </c>
     </row>
     <row r="24" spans="2:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -43360,7 +43802,7 @@
         <v>2327</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>2996</v>
+        <v>3010</v>
       </c>
       <c r="E24" s="7" t="s">
         <v>2329</v>
@@ -43379,13 +43821,13 @@
         <v>100</v>
       </c>
       <c r="J24" s="7" t="s">
-        <v>2968</v>
+        <v>2979</v>
       </c>
       <c r="K24" s="7" t="s">
         <v>24</v>
       </c>
       <c r="L24" s="7" t="s">
-        <v>2969</v>
+        <v>2970</v>
       </c>
       <c r="M24" s="7" t="s">
         <v>68</v>
@@ -43396,13 +43838,13 @@
         <v>18</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>2997</v>
+        <v>3011</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>2998</v>
+        <v>3012</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>3058</v>
+        <v>3013</v>
       </c>
       <c r="F25" s="8" t="s">
         <v>2238</v>
@@ -43418,13 +43860,13 @@
         <v>1910</v>
       </c>
       <c r="J25" s="7" t="s">
-        <v>2968</v>
+        <v>2979</v>
       </c>
       <c r="K25" s="7" t="s">
         <v>24</v>
       </c>
       <c r="L25" s="7" t="s">
-        <v>2969</v>
+        <v>2970</v>
       </c>
     </row>
     <row r="26" spans="2:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
@@ -43432,13 +43874,13 @@
         <v>18</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>2999</v>
+        <v>3014</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>3000</v>
+        <v>3015</v>
       </c>
       <c r="E26" s="9" t="s">
-        <v>3001</v>
+        <v>3016</v>
       </c>
       <c r="F26" s="10" t="s">
         <v>2196</v>
@@ -43460,7 +43902,7 @@
         <v>24</v>
       </c>
       <c r="L26" s="9" t="s">
-        <v>2969</v>
+        <v>2970</v>
       </c>
     </row>
     <row r="27" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -43468,13 +43910,13 @@
         <v>18</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>3002</v>
+        <v>3017</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>3003</v>
+        <v>3018</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>3051</v>
+        <v>3019</v>
       </c>
       <c r="F27" s="4" t="s">
         <v>88</v>
@@ -43496,7 +43938,7 @@
         <v>24</v>
       </c>
       <c r="L27" s="3" t="s">
-        <v>2969</v>
+        <v>2970</v>
       </c>
     </row>
     <row r="28" spans="2:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
@@ -43507,10 +43949,10 @@
         <v>1734</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>3004</v>
+        <v>3020</v>
       </c>
       <c r="E28" s="9" t="s">
-        <v>3055</v>
+        <v>3021</v>
       </c>
       <c r="F28" s="10" t="s">
         <v>2473</v>
@@ -43532,7 +43974,7 @@
         <v>24</v>
       </c>
       <c r="L28" s="9" t="s">
-        <v>2969</v>
+        <v>2970</v>
       </c>
     </row>
     <row r="29" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -43540,13 +43982,13 @@
         <v>18</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>3005</v>
+        <v>3022</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>3006</v>
+        <v>3023</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>3038</v>
+        <v>3024</v>
       </c>
       <c r="F29" s="4" t="s">
         <v>116</v>
@@ -43568,7 +44010,7 @@
         <v>24</v>
       </c>
       <c r="L29" s="3" t="s">
-        <v>2969</v>
+        <v>2970</v>
       </c>
     </row>
     <row r="30" spans="2:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -43576,13 +44018,13 @@
         <v>18</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>3007</v>
+        <v>3025</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>3008</v>
+        <v>3026</v>
       </c>
       <c r="E30" s="7" t="s">
-        <v>3059</v>
+        <v>3027</v>
       </c>
       <c r="F30" s="8" t="s">
         <v>22</v>
@@ -43598,13 +44040,13 @@
         <v>1120</v>
       </c>
       <c r="J30" s="7" t="s">
-        <v>2968</v>
+        <v>2979</v>
       </c>
       <c r="K30" s="7" t="s">
         <v>24</v>
       </c>
       <c r="L30" s="7" t="s">
-        <v>2969</v>
+        <v>2970</v>
       </c>
     </row>
     <row r="31" spans="2:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
@@ -43612,13 +44054,13 @@
         <v>18</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>3009</v>
+        <v>3028</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>3010</v>
+        <v>3029</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>3011</v>
+        <v>3030</v>
       </c>
       <c r="F31" s="10" t="s">
         <v>88</v>
@@ -43640,7 +44082,7 @@
         <v>24</v>
       </c>
       <c r="L31" s="9" t="s">
-        <v>2969</v>
+        <v>2970</v>
       </c>
     </row>
     <row r="32" spans="2:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
@@ -43648,13 +44090,13 @@
         <v>18</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>3012</v>
+        <v>3031</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>3013</v>
+        <v>3032</v>
       </c>
       <c r="E32" s="9" t="s">
-        <v>3014</v>
+        <v>3033</v>
       </c>
       <c r="F32" s="10" t="s">
         <v>2242</v>
@@ -43676,7 +44118,7 @@
         <v>24</v>
       </c>
       <c r="L32" s="9" t="s">
-        <v>2969</v>
+        <v>2970</v>
       </c>
     </row>
     <row r="33" spans="2:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
@@ -43684,10 +44126,10 @@
         <v>18</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>3015</v>
+        <v>3034</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>3016</v>
+        <v>3035</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>2815</v>
@@ -43712,7 +44154,7 @@
         <v>24</v>
       </c>
       <c r="L33" s="9" t="s">
-        <v>2969</v>
+        <v>2970</v>
       </c>
     </row>
     <row r="34" spans="2:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -43720,13 +44162,13 @@
         <v>18</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>3017</v>
+        <v>3036</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>3018</v>
+        <v>3037</v>
       </c>
       <c r="E34" s="7" t="s">
-        <v>3062</v>
+        <v>3038</v>
       </c>
       <c r="F34" s="8" t="s">
         <v>2187</v>
@@ -43742,13 +44184,13 @@
         <v>540</v>
       </c>
       <c r="J34" s="7" t="s">
-        <v>2968</v>
+        <v>2979</v>
       </c>
       <c r="K34" s="7" t="s">
         <v>24</v>
       </c>
       <c r="L34" s="7" t="s">
-        <v>2969</v>
+        <v>2970</v>
       </c>
     </row>
     <row r="35" spans="2:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
@@ -43759,7 +44201,7 @@
         <v>910</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>3019</v>
+        <v>3039</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>912</v>
@@ -43784,7 +44226,7 @@
         <v>24</v>
       </c>
       <c r="L35" s="9" t="s">
-        <v>2969</v>
+        <v>2970</v>
       </c>
     </row>
     <row r="36" spans="2:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
@@ -43792,13 +44234,13 @@
         <v>18</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>3020</v>
+        <v>3040</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>3021</v>
+        <v>3041</v>
       </c>
       <c r="E36" s="9" t="s">
-        <v>3057</v>
+        <v>3042</v>
       </c>
       <c r="F36" s="10" t="s">
         <v>81</v>
@@ -43820,7 +44262,7 @@
         <v>24</v>
       </c>
       <c r="L36" s="9" t="s">
-        <v>2969</v>
+        <v>2970</v>
       </c>
     </row>
     <row r="37" spans="2:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -43831,7 +44273,7 @@
         <v>178</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>3022</v>
+        <v>3043</v>
       </c>
       <c r="E37" s="7" t="s">
         <v>180</v>
@@ -43850,13 +44292,13 @@
         <v>770</v>
       </c>
       <c r="J37" s="7" t="s">
-        <v>2968</v>
+        <v>2979</v>
       </c>
       <c r="K37" s="7" t="s">
         <v>24</v>
       </c>
       <c r="L37" s="7" t="s">
-        <v>2969</v>
+        <v>2970</v>
       </c>
     </row>
     <row r="38" spans="2:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -43867,7 +44309,7 @@
         <v>1126</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>3023</v>
+        <v>3044</v>
       </c>
       <c r="E38" s="7" t="s">
         <v>1128</v>
@@ -43886,13 +44328,13 @@
         <v>-30</v>
       </c>
       <c r="J38" s="7" t="s">
-        <v>2968</v>
+        <v>2979</v>
       </c>
       <c r="K38" s="7" t="s">
         <v>24</v>
       </c>
       <c r="L38" s="7" t="s">
-        <v>2969</v>
+        <v>2970</v>
       </c>
     </row>
     <row r="39" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -43900,10 +44342,10 @@
         <v>18</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>3044</v>
+        <v>3045</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>3043</v>
+        <v>3046</v>
       </c>
       <c r="E39" s="3" t="s">
         <v>2008</v>
@@ -43928,7 +44370,7 @@
         <v>24</v>
       </c>
       <c r="L39" s="3" t="s">
-        <v>2969</v>
+        <v>2970</v>
       </c>
     </row>
     <row r="40" spans="2:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
@@ -43939,7 +44381,7 @@
         <v>900</v>
       </c>
       <c r="D40" s="9" t="s">
-        <v>3024</v>
+        <v>3047</v>
       </c>
       <c r="E40" s="9" t="s">
         <v>902</v>
@@ -43964,7 +44406,7 @@
         <v>24</v>
       </c>
       <c r="L40" s="9" t="s">
-        <v>2969</v>
+        <v>2970</v>
       </c>
     </row>
     <row r="41" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -43972,10 +44414,10 @@
         <v>18</v>
       </c>
       <c r="C41" s="3" t="s">
+        <v>3048</v>
+      </c>
+      <c r="D41" s="3" t="s">
         <v>3049</v>
-      </c>
-      <c r="D41" s="3" t="s">
-        <v>3025</v>
       </c>
       <c r="E41" s="3" t="s">
         <v>3050</v>
@@ -44000,7 +44442,7 @@
         <v>24</v>
       </c>
       <c r="L41" s="3" t="s">
-        <v>2969</v>
+        <v>2970</v>
       </c>
     </row>
     <row r="42" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -44008,10 +44450,10 @@
         <v>18</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>3036</v>
+        <v>3051</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>3037</v>
+        <v>3052</v>
       </c>
       <c r="E42" s="3" t="s">
         <v>1409</v>
@@ -44036,7 +44478,7 @@
         <v>24</v>
       </c>
       <c r="L42" s="3" t="s">
-        <v>2969</v>
+        <v>2970</v>
       </c>
     </row>
     <row r="43" spans="2:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
@@ -44047,7 +44489,7 @@
         <v>1876</v>
       </c>
       <c r="D43" s="9" t="s">
-        <v>3026</v>
+        <v>3053</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>1878</v>
@@ -44072,7 +44514,7 @@
         <v>24</v>
       </c>
       <c r="L43" s="9" t="s">
-        <v>2969</v>
+        <v>2970</v>
       </c>
     </row>
     <row r="44" spans="2:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -44080,13 +44522,13 @@
         <v>18</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>3063</v>
+        <v>3054</v>
       </c>
       <c r="D44" s="7" t="s">
-        <v>3027</v>
+        <v>3055</v>
       </c>
       <c r="E44" s="7" t="s">
-        <v>3064</v>
+        <v>3056</v>
       </c>
       <c r="F44" s="8" t="s">
         <v>22</v>
@@ -44102,13 +44544,13 @@
         <v>-30</v>
       </c>
       <c r="J44" s="7" t="s">
-        <v>2968</v>
+        <v>2979</v>
       </c>
       <c r="K44" s="7" t="s">
         <v>24</v>
       </c>
       <c r="L44" s="7" t="s">
-        <v>2969</v>
+        <v>2970</v>
       </c>
     </row>
     <row r="45" spans="2:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
@@ -44116,13 +44558,13 @@
         <v>18</v>
       </c>
       <c r="C45" s="9" t="s">
-        <v>3028</v>
+        <v>3057</v>
       </c>
       <c r="D45" s="9" t="s">
-        <v>3029</v>
+        <v>3058</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>3030</v>
+        <v>3059</v>
       </c>
       <c r="F45" s="10" t="s">
         <v>2196</v>
@@ -44144,7 +44586,7 @@
         <v>24</v>
       </c>
       <c r="L45" s="9" t="s">
-        <v>2969</v>
+        <v>2970</v>
       </c>
     </row>
     <row r="46" spans="2:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -44152,13 +44594,13 @@
         <v>18</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>3031</v>
+        <v>3060</v>
       </c>
       <c r="D46" s="7" t="s">
-        <v>3032</v>
+        <v>3061</v>
       </c>
       <c r="E46" s="7" t="s">
-        <v>3033</v>
+        <v>3062</v>
       </c>
       <c r="F46" s="8" t="s">
         <v>111</v>
@@ -44174,13 +44616,13 @@
         <v>900</v>
       </c>
       <c r="J46" s="7" t="s">
-        <v>2968</v>
+        <v>2979</v>
       </c>
       <c r="K46" s="7" t="s">
         <v>24</v>
       </c>
       <c r="L46" s="7" t="s">
-        <v>2969</v>
+        <v>2970</v>
       </c>
     </row>
     <row r="47" spans="2:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -44188,10 +44630,10 @@
         <v>18</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>3034</v>
+        <v>3063</v>
       </c>
       <c r="D47" s="7" t="s">
-        <v>3035</v>
+        <v>3064</v>
       </c>
       <c r="E47" s="7" t="s">
         <v>3065</v>
@@ -44210,13 +44652,13 @@
         <v>720</v>
       </c>
       <c r="J47" s="7" t="s">
-        <v>2968</v>
+        <v>2979</v>
       </c>
       <c r="K47" s="7" t="s">
         <v>24</v>
       </c>
       <c r="L47" s="7" t="s">
-        <v>2969</v>
+        <v>2970</v>
       </c>
     </row>
     <row r="48" spans="2:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -44242,11 +44684,11 @@
         <v>30</v>
       </c>
       <c r="I48" s="7">
-        <f>G48-H48</f>
+        <f t="shared" si="0"/>
         <v>450</v>
       </c>
       <c r="J48" s="7" t="s">
-        <v>2968</v>
+        <v>2979</v>
       </c>
       <c r="K48" s="7" t="s">
         <v>24</v>
@@ -44256,6 +44698,2184 @@
       </c>
       <c r="M48" s="7" t="s">
         <v>3066</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1800-000000000000}">
+  <dimension ref="A1:P60"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="2" width="9.140625" customWidth="1"/>
+    <col min="3" max="3" width="40.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="67.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.140625" customWidth="1"/>
+    <col min="7" max="11" width="9.140625" customWidth="1"/>
+    <col min="12" max="12" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>3067</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>1828</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>3068</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>1830</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>2242</v>
+      </c>
+      <c r="G3" s="9">
+        <v>795</v>
+      </c>
+      <c r="H3" s="9">
+        <v>25</v>
+      </c>
+      <c r="I3" s="9">
+        <f t="shared" ref="I3:I34" si="0">G3-H3</f>
+        <v>770</v>
+      </c>
+      <c r="J3" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="K3" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L3" s="9" t="s">
+        <v>3069</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>3070</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>3071</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>3072</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>2187</v>
+      </c>
+      <c r="G4" s="7">
+        <v>720</v>
+      </c>
+      <c r="H4" s="7">
+        <v>30</v>
+      </c>
+      <c r="I4" s="7">
+        <f t="shared" si="0"/>
+        <v>690</v>
+      </c>
+      <c r="J4" s="7" t="s">
+        <v>3073</v>
+      </c>
+      <c r="K4" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L4" s="7" t="s">
+        <v>3069</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>3074</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>3075</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>3076</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>2187</v>
+      </c>
+      <c r="G5" s="7">
+        <v>0</v>
+      </c>
+      <c r="H5" s="7">
+        <v>30</v>
+      </c>
+      <c r="I5" s="7">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J5" s="7" t="s">
+        <v>3073</v>
+      </c>
+      <c r="K5" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L5" s="7" t="s">
+        <v>3069</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>3077</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>3078</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>3079</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>2187</v>
+      </c>
+      <c r="G6" s="7">
+        <v>1980</v>
+      </c>
+      <c r="H6" s="7">
+        <v>30</v>
+      </c>
+      <c r="I6" s="7">
+        <f t="shared" si="0"/>
+        <v>1950</v>
+      </c>
+      <c r="J6" s="7" t="s">
+        <v>3073</v>
+      </c>
+      <c r="K6" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L6" s="7" t="s">
+        <v>3069</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>3080</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>3081</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>3082</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="G7" s="7">
+        <v>945</v>
+      </c>
+      <c r="H7" s="7">
+        <v>25</v>
+      </c>
+      <c r="I7" s="7">
+        <f t="shared" si="0"/>
+        <v>920</v>
+      </c>
+      <c r="J7" s="7" t="s">
+        <v>3073</v>
+      </c>
+      <c r="K7" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L7" s="7" t="s">
+        <v>3069</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>2151</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>3083</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>971</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="G8" s="7">
+        <v>0</v>
+      </c>
+      <c r="H8" s="7">
+        <v>25</v>
+      </c>
+      <c r="I8" s="7">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J8" s="7" t="s">
+        <v>3073</v>
+      </c>
+      <c r="K8" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L8" s="7" t="s">
+        <v>3069</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>3084</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>3085</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="G9" s="3">
+        <v>1170</v>
+      </c>
+      <c r="H9" s="3">
+        <v>20</v>
+      </c>
+      <c r="I9" s="3">
+        <f t="shared" si="0"/>
+        <v>1150</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L9" s="3" t="s">
+        <v>3069</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>3086</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>3087</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>287</v>
+      </c>
+      <c r="G10" s="7">
+        <v>35</v>
+      </c>
+      <c r="H10" s="7">
+        <v>35</v>
+      </c>
+      <c r="I10" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J10" s="7" t="s">
+        <v>3073</v>
+      </c>
+      <c r="K10" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L10" s="7" t="s">
+        <v>3069</v>
+      </c>
+      <c r="M10" s="7" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>3088</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>3194</v>
+      </c>
+      <c r="E11" s="9" t="s">
+        <v>3089</v>
+      </c>
+      <c r="F11" s="10" t="s">
+        <v>2137</v>
+      </c>
+      <c r="G11" s="9">
+        <v>0</v>
+      </c>
+      <c r="H11" s="9">
+        <v>25</v>
+      </c>
+      <c r="I11" s="9">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J11" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="K11" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L11" s="9" t="s">
+        <v>3069</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>3193</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>3090</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>3091</v>
+      </c>
+      <c r="F12" s="10" t="s">
+        <v>2473</v>
+      </c>
+      <c r="G12" s="9">
+        <v>1635</v>
+      </c>
+      <c r="H12" s="9">
+        <v>25</v>
+      </c>
+      <c r="I12" s="9">
+        <f t="shared" si="0"/>
+        <v>1610</v>
+      </c>
+      <c r="J12" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="K12" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L12" s="9" t="s">
+        <v>3069</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>3092</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="G13" s="3">
+        <v>0</v>
+      </c>
+      <c r="H13" s="3">
+        <v>20</v>
+      </c>
+      <c r="I13" s="3">
+        <f t="shared" si="0"/>
+        <v>-20</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K13" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L13" s="3" t="s">
+        <v>3069</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>847</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>3093</v>
+      </c>
+      <c r="E14" s="9" t="s">
+        <v>3094</v>
+      </c>
+      <c r="F14" s="10" t="s">
+        <v>2137</v>
+      </c>
+      <c r="G14" s="9">
+        <v>25</v>
+      </c>
+      <c r="H14" s="9">
+        <v>25</v>
+      </c>
+      <c r="I14" s="9">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J14" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="K14" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L14" s="9" t="s">
+        <v>3069</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>3095</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>3096</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>3097</v>
+      </c>
+      <c r="F15" s="8" t="s">
+        <v>2230</v>
+      </c>
+      <c r="G15" s="7">
+        <v>1805</v>
+      </c>
+      <c r="H15" s="7">
+        <v>25</v>
+      </c>
+      <c r="I15" s="7">
+        <f t="shared" si="0"/>
+        <v>1780</v>
+      </c>
+      <c r="J15" s="7" t="s">
+        <v>3073</v>
+      </c>
+      <c r="K15" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L15" s="7" t="s">
+        <v>3069</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>894</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>3098</v>
+      </c>
+      <c r="E16" s="9" t="s">
+        <v>896</v>
+      </c>
+      <c r="F16" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="G16" s="9">
+        <v>795</v>
+      </c>
+      <c r="H16" s="9">
+        <v>25</v>
+      </c>
+      <c r="I16" s="9">
+        <f t="shared" si="0"/>
+        <v>770</v>
+      </c>
+      <c r="J16" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="K16" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L16" s="9" t="s">
+        <v>3069</v>
+      </c>
+    </row>
+    <row r="17" spans="2:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>3099</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>3100</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>3101</v>
+      </c>
+      <c r="F17" s="8" t="s">
+        <v>2187</v>
+      </c>
+      <c r="G17" s="7">
+        <v>830</v>
+      </c>
+      <c r="H17" s="7">
+        <v>30</v>
+      </c>
+      <c r="I17" s="7">
+        <f t="shared" si="0"/>
+        <v>800</v>
+      </c>
+      <c r="J17" s="7" t="s">
+        <v>3073</v>
+      </c>
+      <c r="K17" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L17" s="7" t="s">
+        <v>3069</v>
+      </c>
+    </row>
+    <row r="18" spans="2:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>3102</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>3103</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>3104</v>
+      </c>
+      <c r="F18" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G18" s="7">
+        <v>890</v>
+      </c>
+      <c r="H18" s="7">
+        <v>30</v>
+      </c>
+      <c r="I18" s="7">
+        <f t="shared" si="0"/>
+        <v>860</v>
+      </c>
+      <c r="J18" s="7" t="s">
+        <v>3073</v>
+      </c>
+      <c r="K18" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L18" s="7" t="s">
+        <v>3069</v>
+      </c>
+    </row>
+    <row r="19" spans="2:13" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>3105</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>3106</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>3187</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>2144</v>
+      </c>
+      <c r="G19" s="5">
+        <v>820</v>
+      </c>
+      <c r="H19" s="5">
+        <v>30</v>
+      </c>
+      <c r="I19" s="5">
+        <f t="shared" si="0"/>
+        <v>790</v>
+      </c>
+      <c r="J19" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="K19" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L19" s="5" t="s">
+        <v>3069</v>
+      </c>
+    </row>
+    <row r="20" spans="2:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>3107</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>3108</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>3109</v>
+      </c>
+      <c r="F20" s="8" t="s">
+        <v>2238</v>
+      </c>
+      <c r="G20" s="7">
+        <v>910</v>
+      </c>
+      <c r="H20" s="7">
+        <v>30</v>
+      </c>
+      <c r="I20" s="7">
+        <f t="shared" si="0"/>
+        <v>880</v>
+      </c>
+      <c r="J20" s="7" t="s">
+        <v>3073</v>
+      </c>
+      <c r="K20" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L20" s="7" t="s">
+        <v>3069</v>
+      </c>
+    </row>
+    <row r="21" spans="2:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C21" s="9" t="s">
+        <v>3205</v>
+      </c>
+      <c r="D21" s="9" t="s">
+        <v>3110</v>
+      </c>
+      <c r="E21" s="9" t="s">
+        <v>3206</v>
+      </c>
+      <c r="F21" s="10" t="s">
+        <v>2137</v>
+      </c>
+      <c r="G21" s="9">
+        <v>815</v>
+      </c>
+      <c r="H21" s="9">
+        <v>25</v>
+      </c>
+      <c r="I21" s="9">
+        <f t="shared" si="0"/>
+        <v>790</v>
+      </c>
+      <c r="J21" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="K21" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L21" s="9" t="s">
+        <v>3069</v>
+      </c>
+    </row>
+    <row r="22" spans="2:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C22" s="9" t="s">
+        <v>3111</v>
+      </c>
+      <c r="D22" s="9" t="s">
+        <v>3198</v>
+      </c>
+      <c r="E22" s="9" t="s">
+        <v>3112</v>
+      </c>
+      <c r="F22" s="10" t="s">
+        <v>2196</v>
+      </c>
+      <c r="G22" s="9">
+        <v>1310</v>
+      </c>
+      <c r="H22" s="9">
+        <v>25</v>
+      </c>
+      <c r="I22" s="9">
+        <f t="shared" si="0"/>
+        <v>1285</v>
+      </c>
+      <c r="J22" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="K22" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L22" s="9" t="s">
+        <v>3069</v>
+      </c>
+      <c r="M22" s="9" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="23" spans="2:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>3113</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>3114</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>3115</v>
+      </c>
+      <c r="F23" s="8" t="s">
+        <v>2189</v>
+      </c>
+      <c r="G23" s="7">
+        <v>20</v>
+      </c>
+      <c r="H23" s="7">
+        <v>20</v>
+      </c>
+      <c r="I23" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J23" s="7" t="s">
+        <v>3073</v>
+      </c>
+      <c r="K23" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L23" s="7" t="s">
+        <v>3069</v>
+      </c>
+    </row>
+    <row r="24" spans="2:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>3116</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>3117</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>3118</v>
+      </c>
+      <c r="F24" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G24" s="7">
+        <v>1460</v>
+      </c>
+      <c r="H24" s="7">
+        <v>30</v>
+      </c>
+      <c r="I24" s="7">
+        <f t="shared" si="0"/>
+        <v>1430</v>
+      </c>
+      <c r="J24" s="7" t="s">
+        <v>3073</v>
+      </c>
+      <c r="K24" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L24" s="7" t="s">
+        <v>3069</v>
+      </c>
+    </row>
+    <row r="25" spans="2:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>3119</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>3120</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>3121</v>
+      </c>
+      <c r="F25" s="8" t="s">
+        <v>2187</v>
+      </c>
+      <c r="G25" s="7">
+        <v>800</v>
+      </c>
+      <c r="H25" s="7">
+        <v>30</v>
+      </c>
+      <c r="I25" s="7">
+        <f t="shared" si="0"/>
+        <v>770</v>
+      </c>
+      <c r="J25" s="7" t="s">
+        <v>3073</v>
+      </c>
+      <c r="K25" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L25" s="7" t="s">
+        <v>3069</v>
+      </c>
+    </row>
+    <row r="26" spans="2:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C26" s="9" t="s">
+        <v>3209</v>
+      </c>
+      <c r="D26" s="9" t="s">
+        <v>3208</v>
+      </c>
+      <c r="E26" s="9" t="s">
+        <v>3210</v>
+      </c>
+      <c r="F26" s="10" t="s">
+        <v>2137</v>
+      </c>
+      <c r="G26" s="9">
+        <v>465</v>
+      </c>
+      <c r="H26" s="9">
+        <v>25</v>
+      </c>
+      <c r="I26" s="9">
+        <f t="shared" si="0"/>
+        <v>440</v>
+      </c>
+      <c r="J26" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="K26" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L26" s="9" t="s">
+        <v>3069</v>
+      </c>
+    </row>
+    <row r="27" spans="2:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>3122</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>3123</v>
+      </c>
+      <c r="E27" s="7" t="s">
+        <v>3124</v>
+      </c>
+      <c r="F27" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G27" s="7">
+        <v>950</v>
+      </c>
+      <c r="H27" s="7">
+        <v>30</v>
+      </c>
+      <c r="I27" s="7">
+        <f t="shared" si="0"/>
+        <v>920</v>
+      </c>
+      <c r="J27" s="7" t="s">
+        <v>3073</v>
+      </c>
+      <c r="K27" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L27" s="7" t="s">
+        <v>3069</v>
+      </c>
+    </row>
+    <row r="28" spans="2:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>3125</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>3126</v>
+      </c>
+      <c r="E28" s="7" t="s">
+        <v>608</v>
+      </c>
+      <c r="F28" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G28" s="7">
+        <v>790</v>
+      </c>
+      <c r="H28" s="7">
+        <v>30</v>
+      </c>
+      <c r="I28" s="7">
+        <f t="shared" si="0"/>
+        <v>760</v>
+      </c>
+      <c r="J28" s="7" t="s">
+        <v>3073</v>
+      </c>
+      <c r="K28" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L28" s="7" t="s">
+        <v>3069</v>
+      </c>
+    </row>
+    <row r="29" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>3127</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>3128</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>3129</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="G29" s="3">
+        <v>1370</v>
+      </c>
+      <c r="H29" s="3">
+        <v>20</v>
+      </c>
+      <c r="I29" s="3">
+        <f t="shared" si="0"/>
+        <v>1350</v>
+      </c>
+      <c r="J29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L29" s="3" t="s">
+        <v>3069</v>
+      </c>
+    </row>
+    <row r="30" spans="2:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C30" s="9" t="s">
+        <v>3191</v>
+      </c>
+      <c r="D30" s="9" t="s">
+        <v>3130</v>
+      </c>
+      <c r="E30" s="9" t="s">
+        <v>3192</v>
+      </c>
+      <c r="F30" s="10" t="s">
+        <v>2137</v>
+      </c>
+      <c r="G30" s="9">
+        <v>0</v>
+      </c>
+      <c r="H30" s="9">
+        <v>25</v>
+      </c>
+      <c r="I30" s="9">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J30" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="K30" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L30" s="9" t="s">
+        <v>3069</v>
+      </c>
+    </row>
+    <row r="31" spans="2:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B31" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C31" s="9" t="s">
+        <v>3195</v>
+      </c>
+      <c r="D31" s="9" t="s">
+        <v>3131</v>
+      </c>
+      <c r="E31" s="9" t="s">
+        <v>3196</v>
+      </c>
+      <c r="F31" s="10" t="s">
+        <v>2137</v>
+      </c>
+      <c r="G31" s="9">
+        <v>825</v>
+      </c>
+      <c r="H31" s="9">
+        <v>25</v>
+      </c>
+      <c r="I31" s="9">
+        <f t="shared" si="0"/>
+        <v>800</v>
+      </c>
+      <c r="J31" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="K31" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L31" s="9" t="s">
+        <v>3069</v>
+      </c>
+    </row>
+    <row r="32" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B32" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>1452</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>3132</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>1454</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="G32" s="3">
+        <v>2090</v>
+      </c>
+      <c r="H32" s="3">
+        <v>25</v>
+      </c>
+      <c r="I32" s="3">
+        <f t="shared" si="0"/>
+        <v>2065</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K32" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L32" s="3" t="s">
+        <v>3069</v>
+      </c>
+      <c r="M32" s="3" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="33" spans="2:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B33" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C33" s="9" t="s">
+        <v>3133</v>
+      </c>
+      <c r="D33" s="9" t="s">
+        <v>3134</v>
+      </c>
+      <c r="E33" s="9" t="s">
+        <v>3203</v>
+      </c>
+      <c r="F33" s="10" t="s">
+        <v>2473</v>
+      </c>
+      <c r="G33" s="9">
+        <v>0</v>
+      </c>
+      <c r="H33" s="9">
+        <v>25</v>
+      </c>
+      <c r="I33" s="9">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J33" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="K33" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L33" s="9" t="s">
+        <v>3069</v>
+      </c>
+    </row>
+    <row r="34" spans="2:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B34" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C34" s="9" t="s">
+        <v>2163</v>
+      </c>
+      <c r="D34" s="9" t="s">
+        <v>3135</v>
+      </c>
+      <c r="E34" s="9" t="s">
+        <v>3197</v>
+      </c>
+      <c r="F34" s="10" t="s">
+        <v>2137</v>
+      </c>
+      <c r="G34" s="9">
+        <v>765</v>
+      </c>
+      <c r="H34" s="9">
+        <v>25</v>
+      </c>
+      <c r="I34" s="9">
+        <f t="shared" si="0"/>
+        <v>740</v>
+      </c>
+      <c r="J34" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="K34" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L34" s="9" t="s">
+        <v>3069</v>
+      </c>
+    </row>
+    <row r="35" spans="2:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B35" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>196</v>
+      </c>
+      <c r="D35" s="7" t="s">
+        <v>3136</v>
+      </c>
+      <c r="E35" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="F35" s="8" t="s">
+        <v>2187</v>
+      </c>
+      <c r="G35" s="7">
+        <v>850</v>
+      </c>
+      <c r="H35" s="7">
+        <v>30</v>
+      </c>
+      <c r="I35" s="7">
+        <f t="shared" ref="I35:I66" si="1">G35-H35</f>
+        <v>820</v>
+      </c>
+      <c r="J35" s="7" t="s">
+        <v>3073</v>
+      </c>
+      <c r="K35" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L35" s="7" t="s">
+        <v>3069</v>
+      </c>
+    </row>
+    <row r="36" spans="2:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B36" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C36" s="7" t="s">
+        <v>3137</v>
+      </c>
+      <c r="D36" s="7" t="s">
+        <v>3138</v>
+      </c>
+      <c r="E36" s="7" t="s">
+        <v>3139</v>
+      </c>
+      <c r="F36" s="8" t="s">
+        <v>2187</v>
+      </c>
+      <c r="G36" s="7">
+        <v>1510</v>
+      </c>
+      <c r="H36" s="7">
+        <v>30</v>
+      </c>
+      <c r="I36" s="7">
+        <f t="shared" si="1"/>
+        <v>1480</v>
+      </c>
+      <c r="J36" s="7" t="s">
+        <v>3073</v>
+      </c>
+      <c r="K36" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L36" s="7" t="s">
+        <v>3069</v>
+      </c>
+    </row>
+    <row r="37" spans="2:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B37" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C37" s="7" t="s">
+        <v>3140</v>
+      </c>
+      <c r="D37" s="7" t="s">
+        <v>3141</v>
+      </c>
+      <c r="E37" s="7" t="s">
+        <v>3142</v>
+      </c>
+      <c r="F37" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="G37" s="7">
+        <v>775</v>
+      </c>
+      <c r="H37" s="7">
+        <v>35</v>
+      </c>
+      <c r="I37" s="7">
+        <f t="shared" si="1"/>
+        <v>740</v>
+      </c>
+      <c r="J37" s="7" t="s">
+        <v>3073</v>
+      </c>
+      <c r="K37" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L37" s="7" t="s">
+        <v>3069</v>
+      </c>
+    </row>
+    <row r="38" spans="2:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B38" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C38" s="7" t="s">
+        <v>741</v>
+      </c>
+      <c r="D38" s="7" t="s">
+        <v>3143</v>
+      </c>
+      <c r="E38" s="7" t="s">
+        <v>743</v>
+      </c>
+      <c r="F38" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="G38" s="7">
+        <v>825</v>
+      </c>
+      <c r="H38" s="7">
+        <v>25</v>
+      </c>
+      <c r="I38" s="7">
+        <f t="shared" si="1"/>
+        <v>800</v>
+      </c>
+      <c r="J38" s="7" t="s">
+        <v>3073</v>
+      </c>
+      <c r="K38" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L38" s="7" t="s">
+        <v>3069</v>
+      </c>
+    </row>
+    <row r="39" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B39" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>3144</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>3145</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>3179</v>
+      </c>
+      <c r="F39" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="G39" s="3">
+        <v>945</v>
+      </c>
+      <c r="H39" s="3">
+        <v>25</v>
+      </c>
+      <c r="I39" s="3">
+        <f t="shared" si="1"/>
+        <v>920</v>
+      </c>
+      <c r="J39" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K39" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L39" s="3" t="s">
+        <v>3069</v>
+      </c>
+    </row>
+    <row r="40" spans="2:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B40" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C40" s="9" t="s">
+        <v>3146</v>
+      </c>
+      <c r="D40" s="9" t="s">
+        <v>3147</v>
+      </c>
+      <c r="E40" s="9" t="s">
+        <v>3190</v>
+      </c>
+      <c r="F40" s="10" t="s">
+        <v>2242</v>
+      </c>
+      <c r="G40" s="9">
+        <v>775</v>
+      </c>
+      <c r="H40" s="9">
+        <v>25</v>
+      </c>
+      <c r="I40" s="9">
+        <f t="shared" si="1"/>
+        <v>750</v>
+      </c>
+      <c r="J40" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="K40" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L40" s="9" t="s">
+        <v>3069</v>
+      </c>
+    </row>
+    <row r="41" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B41" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>3148</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>3149</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>3180</v>
+      </c>
+      <c r="F41" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="G41" s="3">
+        <v>605</v>
+      </c>
+      <c r="H41" s="3">
+        <v>25</v>
+      </c>
+      <c r="I41" s="3">
+        <f t="shared" si="1"/>
+        <v>580</v>
+      </c>
+      <c r="J41" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K41" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L41" s="3" t="s">
+        <v>3069</v>
+      </c>
+    </row>
+    <row r="42" spans="2:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B42" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C42" s="7" t="s">
+        <v>3150</v>
+      </c>
+      <c r="D42" s="7" t="s">
+        <v>3151</v>
+      </c>
+      <c r="E42" s="7" t="s">
+        <v>3152</v>
+      </c>
+      <c r="F42" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="G42" s="7">
+        <v>1555</v>
+      </c>
+      <c r="H42" s="7">
+        <v>25</v>
+      </c>
+      <c r="I42" s="7">
+        <f t="shared" si="1"/>
+        <v>1530</v>
+      </c>
+      <c r="J42" s="7" t="s">
+        <v>3073</v>
+      </c>
+      <c r="K42" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L42" s="7" t="s">
+        <v>3069</v>
+      </c>
+    </row>
+    <row r="43" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B43" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>2726</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>3153</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>2728</v>
+      </c>
+      <c r="F43" s="4" t="s">
+        <v>2133</v>
+      </c>
+      <c r="G43" s="3">
+        <v>1070</v>
+      </c>
+      <c r="H43" s="3">
+        <v>30</v>
+      </c>
+      <c r="I43" s="3">
+        <f t="shared" si="1"/>
+        <v>1040</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K43" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L43" s="3" t="s">
+        <v>3069</v>
+      </c>
+    </row>
+    <row r="44" spans="2:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B44" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C44" s="9" t="s">
+        <v>3154</v>
+      </c>
+      <c r="D44" s="9" t="s">
+        <v>3155</v>
+      </c>
+      <c r="E44" s="9" t="s">
+        <v>3207</v>
+      </c>
+      <c r="F44" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="G44" s="9">
+        <v>2460</v>
+      </c>
+      <c r="H44" s="9">
+        <v>20</v>
+      </c>
+      <c r="I44" s="9">
+        <f t="shared" si="1"/>
+        <v>2440</v>
+      </c>
+      <c r="J44" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="K44" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L44" s="9" t="s">
+        <v>3069</v>
+      </c>
+      <c r="M44" s="9" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="45" spans="2:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B45" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C45" s="9" t="s">
+        <v>3156</v>
+      </c>
+      <c r="D45" s="9" t="s">
+        <v>3157</v>
+      </c>
+      <c r="E45" s="9" t="s">
+        <v>3158</v>
+      </c>
+      <c r="F45" s="10" t="s">
+        <v>2473</v>
+      </c>
+      <c r="G45" s="9">
+        <v>945</v>
+      </c>
+      <c r="H45" s="9">
+        <v>25</v>
+      </c>
+      <c r="I45" s="9">
+        <f t="shared" si="1"/>
+        <v>920</v>
+      </c>
+      <c r="J45" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="K45" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L45" s="9" t="s">
+        <v>3069</v>
+      </c>
+    </row>
+    <row r="46" spans="2:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B46" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C46" s="7" t="s">
+        <v>1967</v>
+      </c>
+      <c r="D46" s="7" t="s">
+        <v>3159</v>
+      </c>
+      <c r="E46" s="7" t="s">
+        <v>1969</v>
+      </c>
+      <c r="F46" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="G46" s="7">
+        <v>805</v>
+      </c>
+      <c r="H46" s="7">
+        <v>35</v>
+      </c>
+      <c r="I46" s="7">
+        <f t="shared" si="1"/>
+        <v>770</v>
+      </c>
+      <c r="J46" s="7" t="s">
+        <v>3073</v>
+      </c>
+      <c r="K46" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L46" s="7" t="s">
+        <v>3069</v>
+      </c>
+    </row>
+    <row r="47" spans="2:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B47" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C47" s="7" t="s">
+        <v>3160</v>
+      </c>
+      <c r="D47" s="7" t="s">
+        <v>3161</v>
+      </c>
+      <c r="E47" s="7" t="s">
+        <v>3162</v>
+      </c>
+      <c r="F47" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G47" s="7">
+        <v>850</v>
+      </c>
+      <c r="H47" s="7">
+        <v>30</v>
+      </c>
+      <c r="I47" s="7">
+        <f t="shared" si="1"/>
+        <v>820</v>
+      </c>
+      <c r="J47" s="7" t="s">
+        <v>3073</v>
+      </c>
+      <c r="K47" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L47" s="7" t="s">
+        <v>3069</v>
+      </c>
+    </row>
+    <row r="48" spans="2:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B48" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C48" s="9" t="s">
+        <v>3204</v>
+      </c>
+      <c r="D48" s="9" t="s">
+        <v>3163</v>
+      </c>
+      <c r="E48" s="9" t="s">
+        <v>3164</v>
+      </c>
+      <c r="F48" s="10" t="s">
+        <v>2196</v>
+      </c>
+      <c r="G48" s="9">
+        <v>465</v>
+      </c>
+      <c r="H48" s="9">
+        <v>25</v>
+      </c>
+      <c r="I48" s="9">
+        <f t="shared" si="1"/>
+        <v>440</v>
+      </c>
+      <c r="J48" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="K48" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L48" s="9" t="s">
+        <v>3069</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B49" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C49" s="9" t="s">
+        <v>3165</v>
+      </c>
+      <c r="D49" s="9" t="s">
+        <v>3166</v>
+      </c>
+      <c r="E49" s="9" t="s">
+        <v>3167</v>
+      </c>
+      <c r="F49" s="10" t="s">
+        <v>2183</v>
+      </c>
+      <c r="G49" s="9">
+        <v>825</v>
+      </c>
+      <c r="H49" s="9">
+        <v>25</v>
+      </c>
+      <c r="I49" s="9">
+        <f t="shared" si="1"/>
+        <v>800</v>
+      </c>
+      <c r="J49" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="K49" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L49" s="9" t="s">
+        <v>3069</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B50" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>3182</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>3168</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>3183</v>
+      </c>
+      <c r="F50" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="G50" s="3">
+        <v>1345</v>
+      </c>
+      <c r="H50" s="3">
+        <v>25</v>
+      </c>
+      <c r="I50" s="3">
+        <f t="shared" si="1"/>
+        <v>1320</v>
+      </c>
+      <c r="J50" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K50" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L50" s="3" t="s">
+        <v>3069</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B51" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>3181</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>3169</v>
+      </c>
+      <c r="E51" s="3" t="s">
+        <v>3170</v>
+      </c>
+      <c r="F51" s="4" t="s">
+        <v>2133</v>
+      </c>
+      <c r="G51" s="3">
+        <v>0</v>
+      </c>
+      <c r="H51" s="3">
+        <v>30</v>
+      </c>
+      <c r="I51" s="3">
+        <f t="shared" si="1"/>
+        <v>-30</v>
+      </c>
+      <c r="J51" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K51" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L51" s="3" t="s">
+        <v>3069</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B52" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C52" s="9" t="s">
+        <v>3171</v>
+      </c>
+      <c r="D52" s="9" t="s">
+        <v>3172</v>
+      </c>
+      <c r="E52" s="9" t="s">
+        <v>3202</v>
+      </c>
+      <c r="F52" s="10" t="s">
+        <v>2196</v>
+      </c>
+      <c r="G52" s="9">
+        <v>0</v>
+      </c>
+      <c r="H52" s="9">
+        <v>25</v>
+      </c>
+      <c r="I52" s="9">
+        <f t="shared" si="1"/>
+        <v>-25</v>
+      </c>
+      <c r="J52" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="K52" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L52" s="9" t="s">
+        <v>3069</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B53" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>3045</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>3186</v>
+      </c>
+      <c r="E53" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="F53" s="4" t="s">
+        <v>2189</v>
+      </c>
+      <c r="G53" s="3">
+        <v>0</v>
+      </c>
+      <c r="H53" s="3">
+        <v>30</v>
+      </c>
+      <c r="I53" s="3">
+        <f t="shared" si="1"/>
+        <v>-30</v>
+      </c>
+      <c r="J53" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K53" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L53" s="3" t="s">
+        <v>3069</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B54" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C54" s="7" t="s">
+        <v>3173</v>
+      </c>
+      <c r="D54" s="7" t="s">
+        <v>3174</v>
+      </c>
+      <c r="E54" s="7" t="s">
+        <v>3175</v>
+      </c>
+      <c r="F54" s="8">
+        <v>8</v>
+      </c>
+      <c r="G54" s="7">
+        <v>0</v>
+      </c>
+      <c r="H54" s="7">
+        <v>25</v>
+      </c>
+      <c r="I54" s="7">
+        <f t="shared" si="1"/>
+        <v>-25</v>
+      </c>
+      <c r="J54" s="7" t="s">
+        <v>3073</v>
+      </c>
+      <c r="K54" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L54" s="7" t="s">
+        <v>3069</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B55" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C55" s="9" t="s">
+        <v>3199</v>
+      </c>
+      <c r="D55" s="9" t="s">
+        <v>3200</v>
+      </c>
+      <c r="E55" s="9" t="s">
+        <v>3201</v>
+      </c>
+      <c r="F55" s="10" t="s">
+        <v>2473</v>
+      </c>
+      <c r="G55" s="9">
+        <v>0</v>
+      </c>
+      <c r="H55" s="9">
+        <v>25</v>
+      </c>
+      <c r="I55" s="9">
+        <f t="shared" si="1"/>
+        <v>-25</v>
+      </c>
+      <c r="J55" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="K55" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L55" s="9" t="s">
+        <v>3069</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B56" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>3188</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>3176</v>
+      </c>
+      <c r="E56" s="3" t="s">
+        <v>3189</v>
+      </c>
+      <c r="F56" s="4" t="s">
+        <v>2189</v>
+      </c>
+      <c r="G56" s="3">
+        <v>0</v>
+      </c>
+      <c r="H56" s="3">
+        <v>40</v>
+      </c>
+      <c r="I56" s="3">
+        <f t="shared" si="1"/>
+        <v>-40</v>
+      </c>
+      <c r="J56" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K56" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L56" s="3" t="s">
+        <v>3069</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="B57" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C57" s="10" t="s">
+        <v>3211</v>
+      </c>
+      <c r="E57" s="10" t="s">
+        <v>2282</v>
+      </c>
+      <c r="F57" s="10">
+        <v>5</v>
+      </c>
+      <c r="G57" s="38">
+        <v>0</v>
+      </c>
+      <c r="H57" s="38">
+        <v>25</v>
+      </c>
+      <c r="I57" s="38">
+        <f>G57-H57</f>
+        <v>-25</v>
+      </c>
+      <c r="J57" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="K57" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L57" s="9" t="s">
+        <v>3069</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="B58" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C58" s="10" t="s">
+        <v>3177</v>
+      </c>
+      <c r="E58" s="9" t="s">
+        <v>3178</v>
+      </c>
+      <c r="F58" s="9" t="s">
+        <v>2473</v>
+      </c>
+      <c r="G58" s="38">
+        <v>6170</v>
+      </c>
+      <c r="H58" s="38">
+        <v>50</v>
+      </c>
+      <c r="I58" s="38">
+        <f t="shared" si="1"/>
+        <v>6120</v>
+      </c>
+      <c r="J58" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="K58" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L58" s="9" t="s">
+        <v>3069</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="B59" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C59" s="10" t="s">
+        <v>3212</v>
+      </c>
+      <c r="E59" s="10" t="s">
+        <v>2282</v>
+      </c>
+      <c r="F59" s="10">
+        <v>5</v>
+      </c>
+      <c r="G59" s="38">
+        <v>0</v>
+      </c>
+      <c r="H59" s="38">
+        <v>25</v>
+      </c>
+      <c r="I59" s="38">
+        <f>G59-H59</f>
+        <v>-25</v>
+      </c>
+      <c r="J59" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="K59" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L59" s="9" t="s">
+        <v>3069</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C60" s="4" t="s">
+        <v>3185</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>3184</v>
+      </c>
+      <c r="F60" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="G60" s="3">
+        <v>25</v>
+      </c>
+      <c r="H60" s="3">
+        <v>25</v>
+      </c>
+      <c r="I60" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J60" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K60" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L60" s="3" t="s">
+        <v>3069</v>
       </c>
     </row>
   </sheetData>
